--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,744 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>save.slot.title</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>槽位 {0}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Slot {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>save.slot.line</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{0}：{1}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>save.slot.empty</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>空槽</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Empty slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>save.slot.demo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>这是 Demo（0.1）的存档，正式版不能继续 Demo 进度，请新建战役。在此槽新建时原文件会另存保留，不会被删除。</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>This is a Demo (0.1) save. The full game cannot continue Demo progress; please start a new campaign. Starting one in this slot keeps the old file as a copy; it will not be deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>save.slot.demo_saved_at</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Demo 存档，保存于 {0}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Demo save, saved {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>save.slot.newer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>存档来自更新的游戏版本（存档格式 {0}，当前 {1}），请更新游戏后再读取。文件已保留。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>This save comes from a newer game version (format {0}, current {1}). Update the game to load it. The file is kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>save.slot.corrupt</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>存档无法读取：{0}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>This save cannot be loaded: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>save.slot.backup_ready</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>可以读取上一版备份（保存于 {0}）</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A previous backup is available (saved {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>save.slot.backup_none</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>没有可用的备份</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No backup is available</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>save.slot.backup_bad</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>备份也无法使用：{0}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>The backup cannot be used either: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>save.action.new</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>新建于此槽</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New here</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>save.action.load</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>读取</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>save.action.restore</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>读取备份</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Load backup</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>save.action.unavailable</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>不可用</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>save.reason.main_missing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>主存档文件丢失</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>The main save file is missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>save.reason.read_failed</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>无法读取文件</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>The file could not be read</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>save.reason.empty_file</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>文件是空的（可能在写入时被中断）</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>The file is empty (writing may have been interrupted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>save.reason.truncated</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>文件不完整（可能在写入时被中断）</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The file is incomplete (writing may have been interrupted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>save.reason.checksum</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>校验失败，文件已损坏或被改动</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Checksum mismatch: the file is damaged or was modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>save.reason.payload</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>存档内容无法解析</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>The save content could not be parsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>save.reason.migration_missing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>缺少从存档格式 {0} 升级的程序</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No upgrader exists for save format {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>save.reason.migration_failed</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>从存档格式 {0} 升级失败</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Upgrading from save format {0} failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>save.reason.demo</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Demo（0.1）存档不能在正式版读取</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Demo (0.1) saves cannot be loaded in the full game</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>save.reason.newer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>存档来自更新的游戏版本</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>The save comes from a newer game version</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>save.card.act</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>第 {0} 幕</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Act {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>save.card.day</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>第 {0} 日</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Day {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>save.card.seed</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>种子 {0}</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Seed {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>save.card.postgame</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>后日谈</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Epilogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>save.card.sandbox</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>沙盒</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sandbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>difficulty.standard.name</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>标准难度</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>save.continue.none</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>没有可读取的安全存档，请先新建战役</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No loadable save found. Start a new campaign first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>save.continue.demo_only</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>只找到 Demo（0.1）存档，正式版不能继续；请新建战役</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Only Demo (0.1) saves were found and cannot be continued. Start a new campaign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>save.confirm.overwrite_head</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{0} 已有存档：</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{0} already holds a save:</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>save.confirm.overwrite_tail</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>新建战役将覆盖此存档，是否继续？</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Starting a new campaign will overwrite it. Continue?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>save.confirm.kept_head</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>{0} 里的存档不能在正式版读取：</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>The save in {0} cannot be loaded by the full game:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>save.confirm.kept_tail</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>新建战役会占用此槽，原文件会另存为 {0} 保留，不会删除。是否继续？</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Starting a new campaign will use this slot. The original file is kept as {0} and will not be deleted. Continue?</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>save.notice.content_removed</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>游戏更新移除了“{0}”×{1}，已转换为 {2} 废料</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>The update removed "{0}" ×{1}; converted into {2} scrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>save.notice.unknown_content</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>未知内容</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Unknown content</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>save.notice.craft_cancelled</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>有 {0} 个合成任务用到了已移除的内容，已取消并全额退还</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{0} crafting job(s) used removed content and were cancelled with a full refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>save.notice.more</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>另有 {0} 条读档变更通知未逐条显示，已记入存档历史</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{0} more load-time change notice(s) were not shown one by one; they are recorded in the save history</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>save.notice.installed_kept</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>蓝图里装着已移除的“{0}”，暂时保留在蓝图中，请重新编辑该蓝图</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>A blueprint still holds the removed "{0}"; it is kept for now, please edit that blueprint</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,6 +1472,6558 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>input.action.move_forward.name</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>镜头上移 / 机器前进</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pan up / Move forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>input.action.move_back.name</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>镜头下移 / 机器后退</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pan down / Move back</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>input.action.move_left.name</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>镜头左移 / 机器左移</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pan left / Move left</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>input.action.move_right.name</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>镜头右移 / 机器右移</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pan right / Move right</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>input.action.strategy_pan_up.name</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>镜头上移（方向键）</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pan up (arrow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>input.action.strategy_pan_down.name</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>镜头下移（方向键）</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pan down (arrow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>input.action.strategy_pan_left.name</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>镜头左移（方向键）</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pan left (arrow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>input.action.strategy_pan_right.name</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>镜头右移（方向键）</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pan right (arrow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>input.action.zoom_in.name</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>拉近</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Zoom in</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>input.action.zoom_out.name</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>拉远</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Zoom out</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>input.action.focus_home_core.name</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>回到归还核心</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Go to Reclamation Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>input.action.follow_selection.name</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>跟随选中对象</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Follow selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>input.action.toggle_pause.name</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>暂停 / 继续</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pause / Resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>input.action.speed_half.name</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>速度 0.5x</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Speed 0.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>input.action.speed_normal.name</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>速度 1x</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Speed 1x</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>input.action.speed_double.name</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>速度 2x</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Speed 2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>input.action.speed_triple.name</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>速度 3x</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Speed 3x</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>input.action.primary_action.name</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>主动作（选择 / 确认）</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Primary action (select / confirm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>input.action.secondary_action.name</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>功能动作（命令 / 取消放置）</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Secondary action (order / cancel placement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>input.action.command_move.name</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>命令：移动</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Order: Move</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>input.action.command_attack.name</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>命令：攻击</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Order: Attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>input.action.command_guard.name</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>命令：守备</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Order: Guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>input.action.command_retreat.name</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>命令：撤退</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Order: Retreat</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>input.action.group1.name</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>选择编组 1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Select group 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>input.action.group2.name</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>选择编组 2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Select group 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>input.action.group3.name</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>选择编组 3</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Select group 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>input.action.group4.name</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>选择编组 4</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Select group 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>input.action.group5.name</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>选择编组 5</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Select group 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>input.action.group6.name</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>选择编组 6</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Select group 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>input.action.group7.name</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>选择编组 7</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Select group 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>input.action.group8.name</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>选择编组 8</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Select group 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>input.action.group9.name</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>选择编组 9</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Select group 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>input.action.group_assign1.name</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>设定编组 1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Set group 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>input.action.group_assign2.name</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>设定编组 2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Set group 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>input.action.group_assign3.name</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>设定编组 3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Set group 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>input.action.group_assign4.name</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>设定编组 4</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Set group 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>input.action.group_assign5.name</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>设定编组 5</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Set group 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>input.action.group_assign6.name</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>设定编组 6</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Set group 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>input.action.group_assign7.name</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>设定编组 7</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Set group 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>input.action.group_assign8.name</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>设定编组 8</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Set group 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>input.action.group_assign9.name</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>设定编组 9</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Set group 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>input.action.open_build_menu.name</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>建造菜单</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Build menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>input.action.hotbar1.name</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>快捷栏 1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Hotbar 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>input.action.hotbar2.name</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>快捷栏 2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Hotbar 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>input.action.hotbar3.name</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>快捷栏 3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Hotbar 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>input.action.hotbar4.name</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>快捷栏 4</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Hotbar 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>input.action.hotbar5.name</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>快捷栏 5</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Hotbar 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>input.action.hotbar6.name</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>快捷栏 6</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Hotbar 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>input.action.hotbar7.name</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>快捷栏 7</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Hotbar 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>input.action.hotbar8.name</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>快捷栏 8</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Hotbar 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>input.action.hotbar9.name</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>快捷栏 9</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Hotbar 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>input.action.hotbar10.name</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>快捷栏 10</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Hotbar 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>input.action.rotate.name</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>旋转</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Rotate</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>input.action.demolish_mode.name</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>拆除模式</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Demolish mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>input.action.eyedropper.name</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>吸管</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Eyedropper</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>input.action.upgrade_plan.name</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>升级规划</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Upgrade planner</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>input.action.copy.name</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>复制</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>input.action.paste.name</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>粘贴</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Paste</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>input.action.undo.name</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>撤销</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Undo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>input.action.redo.name</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>重做</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Redo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>input.action.layout_library.name</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>布局库</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Layout library</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>input.action.toggle_overlay.name</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>叠加层切换</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Toggle overlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>input.action.toggle_camera_view.name</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>接入 / 退出接入</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Uplink / Leave uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>input.action.cycle_control_target.name</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>循环切换机器</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Cycle machines</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>input.action.interact.name</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>交互</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Interact</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>input.action.jump_home.name</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>跳回家园</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Jump home</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>input.action.jump_previous_machine.name</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>跳回上一台机器</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Jump to previous machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>input.action.direct_skill_slot0.name</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>接入技能 1</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Uplink skill 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>input.action.direct_skill_slot1.name</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>接入技能 2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Uplink skill 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>input.action.direct_skill_slot2.name</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>接入技能 3</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Uplink skill 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>input.action.direct_skill_slot3.name</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>接入技能 4</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Uplink skill 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>input.action.direct_skill_slot4.name</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>接入技能 5</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Uplink skill 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>input.action.open_map.name</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>地图</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>input.action.toggle_mission_log.name</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>任务日志</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mission log</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>input.action.open_roster.name</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>机器名册</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Machine roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>input.action.open_research.name</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>研发树</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Research tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>input.action.open_firmware.name</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>固件库</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Firmware library</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>input.action.open_codex.name</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>图鉴</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>input.action.open_intel.name</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>情报</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>input.action.toggle_notification_center.name</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>通知中心</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Notification center</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>input.action.cancel.name</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>取消 / 返回 / 暂停菜单</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cancel / Back / Pause menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>input.action.ui_confirm.name</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>确认对话框</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Confirm dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>input.action.pin_tooltip.name</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>固定悬停提示</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Pin tooltip</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>input.action.quick_save.name</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>快速存档</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Quick save</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>input.action.quick_load.name</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>快速读档</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Quick load</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>notify.type.core_destroyed.name</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>核心被毁</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Core destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>notify.type.core_destroyed.single</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>归还核心被摧毁：{0}</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>The Reclamation Core was destroyed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>notify.type.core_destroyed.many</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>归还核心被摧毁（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>The Reclamation Core was destroyed ({0} times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>notify.type.machine_destroyed.name</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>机器损失</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Machine lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>notify.type.machine_destroyed.single</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>机器损失：{0}</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Machine lost: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>notify.type.machine_destroyed.many</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>{0} 台机器损失</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{0} machines lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_wiped.name</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>远征全灭</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Expedition wiped out</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_wiped.single</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>远征队已全部失去行动能力：{0}</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>The expedition was wiped out: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>notify.type.expedition_wiped.many</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>远征全灭（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Expedition wiped out ({0} times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>notify.type.failure.name</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>notify.type.failure.single</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>失败：{0}</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Failure: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>notify.type.failure.many</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>{0} 次失败</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{0} failures</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>notify.type.boss_phase.name</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>首领阶段转换</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Boss phase change</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>notify.type.boss_phase.single</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>主核心阶段变化：{0}</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>The main core changed phase: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>notify.type.boss_phase.many</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>主核心阶段变化（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>The main core changed phase ({0} times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>notify.type.boss_lockout.name</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>核心分区封锁</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Core sector lockout</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>notify.type.boss_lockout.single</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>核心分区封锁：{0}</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Core sector lockout: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>notify.type.boss_lockout.many</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>核心分区封锁警报（{0} 条）</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Core sector lockout alerts ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>notify.type.raid_arrival.name</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>突袭到达</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Raid arrived</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>notify.type.raid_arrival.single</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>突袭到达：{0}</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Raid arrived: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>notify.type.raid_arrival.many</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>{0} 支突袭到达</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{0} raids arrived</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night.name</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>静默夜开始</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Silent night begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night.single</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>静默夜开始：{0}</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>The silent night begins: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>notify.type.silent_night.many</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>静默夜开始（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>The silent night begins ({0} times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>notify.type.power_lost.name</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>缺电</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Power shortage</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>notify.type.power_lost.single</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>电力不足：{0}</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Power shortage: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>notify.type.power_lost.many</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>{0} 处缺电</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{0} power shortages</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>notify.type.signal_lost.name</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>信号中断</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Signal lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>notify.type.signal_lost.single</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>信号中断：{0}</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Signal lost: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>notify.type.signal_lost.many</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>{0} 处信号中断</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{0} signal losses</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>notify.type.storage_full.name</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>仓满</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Storage full</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>notify.type.storage_full.single</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>仓库已满：{0}</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Storage full: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>notify.type.storage_full.many</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>{0} 处仓满</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>{0} storage-full alerts</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>notify.type.emergency_rescue.name</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>紧急救援</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Emergency rescue</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>notify.type.emergency_rescue.single</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>核心派出紧急救援机：{0}</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>The core sent an emergency rescue unit: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>notify.type.emergency_rescue.many</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>紧急救援（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Emergency rescues ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>notify.type.save_migrated.name</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>读档变更</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Load-time change</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>notify.type.save_migrated.single</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>notify.type.save_migrated.many</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>{0} 条读档变更</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>{0} load-time changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>notify.type.weather.name</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>天气</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>notify.type.weather.single</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>天气：{0}</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Weather: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>notify.type.weather.many</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>{0} 条天气提醒</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>{0} weather alerts</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>notify.type.power_restored.name</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>供电恢复</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Power restored</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>notify.type.power_restored.single</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>供电恢复：{0}</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Power restored: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>notify.type.power_restored.many</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>{0} 处供电恢复</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>{0} power restorations</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>notify.type.signal_restored.name</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>信号恢复</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Signal restored</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>notify.type.signal_restored.single</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>信号恢复：{0}</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Signal restored: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>notify.type.signal_restored.many</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>{0} 处信号恢复</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>{0} signal restorations</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>notify.type.production_complete.name</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>生产完成</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Production complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>notify.type.production_complete.single</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>生产完成：{0}</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Production complete: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>notify.type.production_complete.many</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>{0} 项生产完成</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>{0} items produced</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>notify.type.analysis_complete.name</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>解析完成</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Analysis complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>notify.type.analysis_complete.single</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>解析完成：{0}</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Analysis complete: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>notify.type.analysis_complete.many</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>{0} 项解析完成</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>{0} analyses complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>notify.type.build_complete.name</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>建造完成</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Construction complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>notify.type.build_complete.single</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>完工：{0}</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Completed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>notify.type.build_complete.many</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>{0} 座建筑完工</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>{0} buildings completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>notify.type.objective_new.name</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>新任务</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>New objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>notify.type.objective_new.single</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>新目标：{0}</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>New objective: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>notify.type.objective_new.many</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>{0} 个新目标</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>{0} new objectives</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>notify.type.objective_done.name</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>目标完成</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Objective complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>notify.type.objective_done.single</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>目标完成：{0}</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Objective complete: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>notify.type.objective_done.many</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>{0} 个目标完成</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>{0} objectives complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>notify.type.expedition.name</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>远征动态</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Expedition</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>notify.type.expedition.single</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>远征：{0}</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Expedition: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>notify.type.expedition.many</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>{0} 条远征动态</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>{0} expedition updates</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>notify.type.boss_destroyed.name</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>首领击破</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Boss destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>notify.type.boss_destroyed.single</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>主核心已摧毁：{0}</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>The main core was destroyed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>notify.type.boss_destroyed.many</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>主核心已摧毁（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>The main core was destroyed ({0} times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>notify.type.beacon.name</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>导航信标</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Navigation beacon</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>notify.type.beacon.single</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>导航信标：{0}</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Navigation beacon: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>notify.type.beacon.many</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>{0} 条信标动态</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>{0} beacon updates</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>notify.type.research_done.name</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>研究完成</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Research complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>notify.type.research_done.single</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>研究完成：{0}</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Research complete: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>notify.type.research_done.many</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>{0} 项研究完成</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>{0} research projects complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>notify.type.auto_paused.name</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>自动暂停</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Auto-pause</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>notify.type.auto_paused.single</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>已自动暂停：由通知「{0}」触发，可在通知设置中关闭</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Auto-paused by the "{0}" notification. You can turn this off in notification settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>notify.type.auto_paused.many</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>已自动暂停（{0} 次）</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Auto-paused ({0} times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>notify.type.settings_changed.name</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>设置变更</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Settings changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>notify.type.settings_changed.single</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>notify.type.settings_changed.many</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>{0} 条设置变更</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>{0} settings changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.name</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>尚未开放</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Not yet available</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.single</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>「{0}」将在后续版本开放</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>"{0}" will be available in a later version</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>notify.type.feature_locked.many</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>{0} 个操作尚未开放</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>{0} actions are not yet available</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>notify.tier.urgent</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>紧急</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>notify.tier.warning</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>notify.tier.info</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>input.category.camera</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>镜头</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>input.category.time</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>input.category.command</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>指挥</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>建造</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>input.category.uplink</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>接入</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Panels</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>input.category.system</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>input.context.strategy</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>战略</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>input.context.build</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>建造</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>input.context.uplink</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>接入</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>input.context.interface</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>界面</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>input.mod.ctrl</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>input.mod.alt</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Alt</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Alt</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>input.mod.shift</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>input.chord.join</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>{0}+{1}</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>{0}+{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>input.key.none</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Unbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>input.key.space</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>空格</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>input.key.escape</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Esc</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Esc</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>input.key.return</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>回车</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>input.key.tab</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>input.key.back_quote</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>`</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>`</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>input.key.home</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>input.key.mouse0</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>鼠标左键</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Left mouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>input.key.mouse1</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>鼠标右键</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Right mouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>input.key.mouse2</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>鼠标中键</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Middle mouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>input.key.wheel_up</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>滚轮上</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Wheel up</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>input.key.wheel_down</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>滚轮下</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Wheel down</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>input.key.up_arrow</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>上方向键</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Up arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>input.key.down_arrow</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>下方向键</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Down arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>input.key.left_arrow</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>左方向键</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Left arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>input.key.right_arrow</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>右方向键</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Right arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>input.key.left_shift</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>左 Shift</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Left Shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>input.key.right_shift</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>右 Shift</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Right Shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>input.key.left_alt</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>左 Alt</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Left Alt</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>input.key.right_alt</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>右 Alt</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Right Alt</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>input.key.left_control</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>左 Ctrl</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Left Ctrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>input.key.right_control</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>右 Ctrl</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Right Ctrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>input.key.digit</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>input.rebind.listening</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>请按下新按键……（Esc 取消）</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Press a new key... (Esc to cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>input.rebind.conflict_title</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>按键冲突</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Key conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>input.rebind.conflict_line</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>{0} 已被「{1}」使用（{2}）</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>{0} is already used by "{1}" ({2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>input.rebind.conflict_tail</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>覆盖后「{0}」将变为未绑定。</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>If you overwrite it, "{0}" becomes unbound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>input.rebind.override</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>覆盖</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Overwrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>input.rebind.required_blocked</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>「{0}」必须保留按键，不能被覆盖；请先给它换一个键</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>"{0}" must keep a key and cannot be overwritten; rebind it first</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>input.rebind.done</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>已将「{0}」设为 {1}</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>"{0}" is now {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>input.rebind.mouse_only</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>「{0}」只能绑定鼠标按键</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>"{0}" can only be bound to a mouse button</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>input.rebind.reset_conflict</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>「{0}」的默认键已被别的动作占用，请先改那个动作</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>The default key of "{0}" is taken by another action; change that one first</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>input.rebind.cancelled</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>已取消改键</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Rebinding cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>input.rebind.reset_one</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>input.rebind.reset_all_title</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>恢复全部默认按键</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Reset all keys to default</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>input.rebind.reset_all_line</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>将丢失：你改过的 {0} 个按键</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>You will lose: {0} customised key(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>input.rebind.migrated</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>按键方案已更新为正式版：保留了你改过的 {0} 个按键，{1} 个因与新默认键冲突已恢复默认</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Key layout updated for the full game: kept {0} customised key(s); {1} restored to default because they clashed with new defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>input.rebind.migrated_defaults</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>按键方案已更新为正式版，部分默认按键有调整，可在暂停菜单 → 按键设置查看</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Key layout updated for the full game; some default keys changed. See Pause menu → Key bindings</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>input.status.reserved</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>后续版本开放</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Coming later</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>input.status.unbound_warning</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>未绑定：只能用鼠标或界面按钮操作</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Unbound: use the mouse or on-screen buttons</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>input.status.reserved_tip</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>这个操作对应的系统还没有开放，按键先保留，可以提前改键</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>This action's system is not available yet; you can still set its key</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>input.tooltip.contexts</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>生效范围：{0}</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Active in: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>ui.keybind.title</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>按键设置</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Key bindings</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ui.keybind.open_all</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>全部按键…</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>All keys...</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ui.keybind.search_placeholder</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>搜索动作或按键</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Search actions or keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ui.keybind.tab_all</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ui.keybind.empty</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>没有匹配“{0}”的动作</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>No actions match "{0}"</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ui.keybind.count</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>共 {0} 个动作，{1} 个已改键</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>{0} actions, {1} customised</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ui.keybind.reset_all</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>全部恢复默认</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Reset all</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ui.keybind.col_action</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>动作</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ui.keybind.col_key</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>按键</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ui.common.close</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ui.common.cancel</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ui.common.confirm</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ui.common.loading</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>加载中……</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Loading...</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ui.common.empty</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>暂无内容</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Nothing here yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ui.common.clear</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>清空</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ui.common.shortcut</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>快捷键：{0}</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Shortcut: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ui.common.codex_link</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>图鉴：{0}</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Codex: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ui.common.disabled_reason</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>不可用：{0}</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Unavailable: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ui.drag.cancelled</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>已取消拖动</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Drag cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ui.drag.no_target</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>没有放到可放置的位置</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Not dropped on a valid target</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ui.confirm.lose_prefix</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>将丢失：</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>You will lose:</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ui.confirm.irreversible</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>此操作无法撤销。</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>This cannot be undone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ui.tooltip.pin_hint</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>按住 {0} 固定提示</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Hold {0} to pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ui.tooltip.pinned</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>已固定：松开 {0} 或移开鼠标关闭</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Pinned: release {0} or move away to close</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>ui.tooltip.expand_sources</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>展开来源</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Show breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>ui.tooltip.collapse_sources</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>收起来源</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Hide breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>ui.tooltip.total</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>合计 {0}</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Total {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>ui.notify.title</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>通知中心</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ui.notify.entry_unread</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>{0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>{0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ui.notify.filter_all</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>全部等级</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>All levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ui.notify.filter_type_all</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>全部类型</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>All types</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>ui.notify.empty</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>没有符合条件的通知</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>No matching notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ui.notify.count</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>共 {0} 条，显示 {1} 条</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>{0} total, {1} shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>ui.notify.locate</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ui.notify.no_location</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>这条通知没有位置</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>This notification has no location</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ui.notify.other_region</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>位置在另一个区域，回到该区域后再定位</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>The location is in another region; go there first</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ui.notify.no_camera</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>当前没有可移动的镜头</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>No camera is available to move</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ui.notify.expand</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>展开 {0} 条</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Show {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ui.notify.collapse</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>收起</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Collapse</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ui.notify.settings</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>通知设置</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Notification settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ui.notify.auto_pause</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>触发时自动暂停</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Auto-pause when triggered</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ui.notify.duration</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>弹出提示停留：{0}</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Pop-up duration: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ui.notify.saved_history</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>读档变更</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Load-time changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ui.notify.time_day</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>第 {0} 日 {1}</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Day {0} {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ui.notify.time_real</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ui.notify.times</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>×{0}</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>×{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ui.notify.source_rule</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>由规则「{0}」触发</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Triggered by rule "{0}"</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ui.notify.source_system</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>来源：{0}</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Source: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ui.pause.title</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ui.pause.resume</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>继续游戏</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ui.pause.keybinds</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>按键设置</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Key bindings</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ui.pause.notifications</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>通知中心</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ui.pause.save_and_quit</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>保存并返回主菜单</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Save and return to menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ui.pause.quit_title</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>返回主菜单</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Return to main menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ui.pause.quit_line</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>当前进度会先保存到{0}</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Progress will be saved to {0} first</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ui.pause.quit_failed</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>保存失败，已留在游戏中：{0}</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Saving failed; you are still in the game: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ui.pause.gallery</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>界面基础件样例（开发）</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>UI kit gallery (dev)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>tooltip.power.title</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>tooltip.power.body</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>供给来自核心基础供电与发电机；需求按优先级（数字小的先）分配，分不到电的建筑会停机。</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Supply comes from the core's base output and generators. Demand is served by priority (lower number first); buildings that get no power shut down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>tooltip.power.base_core</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>核心基础供电</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Core base output</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>tooltip.power.supply_of</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>{0} 供电</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>{0} output</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>tooltip.power.demand_of</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>{0} 用电（优先级 {1}）</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>{0} draw (priority {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>tooltip.power.brownout_of</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>{0} 用电（优先级 {1}，已停机）</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>{0} draw (priority {1}, shut down)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>tooltip.power.surplus</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>盈余 {0}</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Surplus {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>tooltip.power.shortfall</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>差额 {0}</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Shortfall {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>tooltip.signal.title</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>信号带宽</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Signal bandwidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>tooltip.signal.body</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>带宽决定一次远征能带多少台机器，出征准备会按带宽检查。</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Bandwidth limits how many machines one expedition can take; expedition prep checks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>tooltip.signal.base</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>基础带宽</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Base bandwidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>tooltip.signal.tower</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>信号塔（通电）</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Signal tower (powered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>tooltip.signal.tower_off</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>信号塔（未通电，不提供带宽）</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Signal tower (unpowered, no bandwidth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>tooltip.signal.broadcast_off</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>关闭主动广播</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Broadcast turned off</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>status.working.name</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>工作中</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>status.idle.name</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>待机</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>status.no_material.name</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>缺料</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>No materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>status.no_power.name</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>缺电</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>No power</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>status.no_fluid.name</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>缺流体</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>No fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>status.output_blocked.name</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>输出堵塞</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Output blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>status.disabled.name</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>已禁用</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>status.damaged.name</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>损坏</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Damaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>status.destroyed.name</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>已摧毁</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>status.upgrading.name</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>升级中</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Upgrading</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>fmt.wan</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>{0}万</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>fmt.thousand</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>{0}k</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>fmt.million</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>{0}M</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>fmt.per_minute</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>{0}/分钟</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>{0}/min</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>fmt.percent</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>{0}%</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>fmt.seconds</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>{0} 秒</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>{0}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ui.gallery.title</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>界面基础件样例</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>UI kit gallery</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_notify</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>通知中心</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Notification center</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_confirm</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>确认框</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Confirm dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_tooltip</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>悬停提示</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Tooltip</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_menu</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>右键菜单</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Context menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_drag</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>拖放</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Drag and drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_search</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>搜索框</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Search box</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_tabs</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>标签页</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_list</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>虚拟化列表</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Virtualised list</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_chart</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>图表</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_hint</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>快捷键提示</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Shortcut hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_progress</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>进度条</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Progress bars</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ui.gallery.section_status</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>状态图标</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Status icons</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>ui.gallery.post_urgent</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>发一条紧急</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Post urgent</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>ui.gallery.post_warning</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>发一条警告</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Post warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ui.gallery.post_info</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>发一条信息</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Post info</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ui.gallery.post_burst</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>1 秒内发 50 条</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Post 50 in 1 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>ui.gallery.open_confirm</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>打开确认框</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Open confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>ui.gallery.confirm_title</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>拆除建筑</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Demolish building</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ui.gallery.confirm_line</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>未装载的战利品 ×{0}</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Unloaded loot ×{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ui.gallery.tooltip_target</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>悬停查看产量构成</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Hover for output breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ui.gallery.tooltip_title</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>装配站产量</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Assembly output</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ui.gallery.tooltip_body</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>每分钟产出的机器零件数。</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Machine parts produced per minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ui.gallery.source_base</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>基础产量</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Base output</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>ui.gallery.source_power</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>电力不足</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Power shortage</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ui.gallery.source_research</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>研究加成</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Research bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ui.gallery.menu_target</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>在这里点右键</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Right-click here</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>ui.gallery.menu_inspect</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>查看</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Inspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ui.gallery.menu_rename</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>改名</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ui.gallery.menu_demolish</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>拆除</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Demolish</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ui.gallery.menu_demolish_reason</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>核心不能拆除</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>The core cannot be demolished</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ui.gallery.menu_result</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>选择了：{0}</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Chose: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ui.gallery.drag_source</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>拖动芯片</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Drag chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ui.gallery.drag_slot</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>槽位 {0}</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Slot {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ui.gallery.drag_slot_locked</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>锁定槽位</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Locked slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ui.gallery.drag_locked_reason</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>槽位锁定，不能放入</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>The slot is locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ui.gallery.drag_result</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>放入了 {0}</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Dropped into {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ui.gallery.tab_a</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>产量</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>ui.gallery.tab_b</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>ui.gallery.tab_c</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ui.gallery.tab_body</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>当前标签：{0}</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Current tab: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ui.gallery.list_row</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>条目 {0}</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Entry {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ui.gallery.chart_line</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>近 60 秒产量</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Output, last 60 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ui.gallery.chart_bar</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>各类消耗</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Use by type</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ui.gallery.progress_label</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>研究进度</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Research progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>ui.gallery.progress_step</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>推进 10%</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Advance 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ui.gallery.progress_block</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>切换阻塞</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Toggle blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>ui.gallery.colorblind</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>色盲预览</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Colour-blind preview</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D422"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8024,6 +8024,1410 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>building.core.desc</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>战役的根基。核心被毁即失败；自带基础供电与应急缓存。</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>The heart of the campaign. If it falls, the campaign is lost; provides base power and an emergency cache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>building.generator.desc</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>运转后提供额外电力。可以建造多座。</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Provides extra power while running. You can build several.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>building.warehouse.desc</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>修好后扩充库存容量，并接收远征卸货。</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Once repaired, adds storage capacity and receives expedition cargo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr"/>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>building.signal_tower.desc</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>修好并通电后扩大信号带宽，开放破碎都市远征。</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>When repaired and powered, raises signal bandwidth and opens expeditions to the Fractured City.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr"/>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>building.assembly_station.desc</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>生产与改造机器。</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Produces and refits machines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>building.analysis_bench.desc</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>解析带回的技术模块，解锁新内容。</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Analyzes recovered tech modules to unlock new content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>building.repair_bay.desc</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>维修机的工作基点。</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Home base for repair machines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>building.beacon.desc</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>返航信标。建成、通电并启动后，战役迎来终局。</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>The homing beacon. Build, power and launch it to reach the campaign's finale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>grid.terrain.buildable.name</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>空地</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Open ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr"/>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>grid.terrain.water.name</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>水源</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>grid.terrain.oil.name</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>油井</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Oil well</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>grid.terrain.ore_metal.name</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>金属矿脉</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Metal vein</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>grid.terrain.ore_rare.name</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>稀土矿脉</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Rare-earth vein</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr"/>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>grid.terrain.ruin.name</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>废墟</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Ruins</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr"/>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>grid.terrain.cliff.name</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>悬崖</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Cliff</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr"/>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>grid.dir.n</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>北</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr"/>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>grid.dir.e</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>东</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr"/>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>grid.dir.s</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>南</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr"/>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>grid.dir.w</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>西</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr"/>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>grid.port.in</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr"/>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>grid.port.out</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr"/>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>grid.port.entry</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>{0}（朝{1}）</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>{0} (facing {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr"/>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>grid.reason.occupied</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>已被“{0}”占用</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Occupied by {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr"/>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>grid.reason.occupied_belt</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>已被传送带占用</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Occupied by a belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr"/>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>grid.reason.occupied_pipe</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>已被管线占用</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Occupied by a pipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr"/>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>grid.reason.obstacle</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>被“{0}”挡住</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Blocked by {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>grid.obstacle.wreckage</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>残骸</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Wreckage</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr"/>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>grid.obstacle.target</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>残骸靶</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Target wreck</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>grid.obstacle.exit</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>出口通道</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Exit lane</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr"/>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>grid.reason.terrain</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>地形不符：{0}上不能建造</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Unsuitable terrain: cannot build on {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr"/>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>grid.reason.needs_terrain</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>需要放在{0}上</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Must be placed on {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr"/>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>grid.reason.pollution</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>污染过重（{0} 级），需要先净化</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Pollution too high (level {0}); purify it first</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr"/>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>grid.reason.fog</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>超出已探索区域</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Outside the explored area</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr"/>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>grid.reason.core_reserve</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>归还核心周围 {0} 格是通道，不能建造</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>The {0} tiles around the Reclamation Core are a passage and cannot be built on</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr"/>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>grid.reason.max_count</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>已达到数量上限（{0} 座）</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Limit reached ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr"/>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>grid.reason.locked</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>尚未解锁：{0}</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Locked: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr"/>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>grid.reason.not_placeable</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>这种建筑不能手动放置</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>This building cannot be placed manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>grid.reason.unknown_type</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>未知的建筑类型</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Unknown building type</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>grid.reason.insufficient_scrap</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>废料不足：需要 {0}，现有 {1}</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Not enough scrap: need {0}, have {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr"/>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>grid.reason.no_building</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>这里没有建筑</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>There is no building here</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr"/>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>grid.reason.cannot_demolish_core</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>归还核心不能拆除</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>The Reclamation Core cannot be demolished</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr"/>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>grid.reason.demolish_damaged</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>受损的建筑不能拆除，请先修复</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Damaged buildings cannot be demolished; repair it first</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr"/>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>grid.reason.busy</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>这座建筑正在施工或维修，完成后再操作</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>This building is under construction or repair; try again when it is done</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr"/>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>grid.reason.cannot_rotate_core</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>归还核心不能旋转</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>The Reclamation Core cannot be rotated</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr"/>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>grid.reason.not_rebuildable</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>这座建筑无法重建，不能拆除</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>This building cannot be rebuilt, so it cannot be demolished</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr"/>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>grid.reason.no_region</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>只有在家园里才能建造</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>You can only build at home</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr"/>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>开局即可建造</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Available from the start</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr"/>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>grid.unlock.beacon</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>摧毁铸造前哨主核心并带回核心数据后解锁</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Unlocked after destroying the Foundry Outpost main core and bringing back its data</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr"/>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>ui.build.title</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>建造</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr"/>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>ui.build.entry</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>建造（{0}）</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Build ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr"/>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>ui.build.demolish</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>拆除模式（{0}）</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Demolish ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr"/>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>ui.build.rotate</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>旋转（{0}）</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Rotate ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr"/>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ui.build.exit</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr"/>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>ui.build.empty</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>当前没有可以建造的建筑</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Nothing is available to build yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr"/>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>ui.build.cost</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>{0} 废料 · {1} 秒</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>{0} scrap · {1}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr"/>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>ui.build.count_limited</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>已有 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Built {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr"/>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>ui.build.count_unlimited</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>已有 {0}</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Built {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr"/>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>ui.build.hint_idle</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>选择要建造的建筑。指着已有建筑按 {0} 旋转，按 {1} 进入拆除模式，Esc 退出。</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Pick a building. Point at a building and press {0} to rotate it, {1} for demolish mode, Esc to exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr"/>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ui.build.hint_place</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>左键放置 · {0} 旋转 · 右键取消 · Esc 退出</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Left-click to place · {0} rotate · Right-click cancel · Esc exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr"/>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ui.build.hint_demolish</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>左键标记拆除，再点一次取消标记 · 右键返回 · Esc 退出</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Left-click to mark for demolition, again to unmark · Right-click back · Esc exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr"/>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ui.build.valid</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>可以放置：{0}，朝{1}</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Can place: {0}, facing {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr"/>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ui.build.invalid</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>不能放置：{0}</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Cannot place: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr"/>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ui.build.invalid_rotate</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>不能旋转：{0}</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Cannot rotate: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr"/>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>ui.build.hover_building</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>{0}（朝{1}）</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>{0} (facing {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr"/>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ui.build.ports</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>端口：{0}</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Ports: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr"/>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>ui.build.no_ports</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>端口：无</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Ports: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr"/>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>ui.build.placed</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>已规划：{0}，等待机器施工</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Planned: {0}; waiting for a machine to build it</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr"/>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ui.build.demolish_marked</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>已标记拆除：{0}</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Marked for demolition: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr"/>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ui.build.demolish_unmarked</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>已取消拆除：{0}</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Demolition cancelled: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr"/>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ui.build.plan_cancelled</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>已取消规划：{0}，废料已全额退回</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Plan cancelled: {0}; scrap fully refunded</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr"/>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>ui.build.rotated</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>已旋转：{0}，现在朝{1}</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Rotated: {0}, now facing {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr"/>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ui.build.confirm_title</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>拆除{0}？</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Demolish {0}?</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr"/>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>ui.build.confirm_refund</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>返还 {0} 废料（实际投入的一半）</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Refunds {0} scrap (half of what was invested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr"/>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>ui.build.confirm_critical</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>这是关键建筑，拆除后相关功能会停用</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>This is a key building; its functions stop once demolished</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr"/>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>ui.build.confirm_ok</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>拆除</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Demolish</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr"/>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>ui.build.confirm_cancel</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr"/>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ui.build.locked_tip</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>尚未解锁：{0}</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Locked: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr"/>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ui.build.placeholder_note</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>建筑外形是占位方块（美术待替换）</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Building shapes are placeholder blocks (art pending)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9428,6 +9428,366 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr"/>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>world.surface.earth.name</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr"/>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>world.surface.relay_hall.name</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>地下中继大厅</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Underground Relay Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr"/>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>world.surface.data_center.name</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>数据中心</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Data Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr"/>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>world.territory.silent.name</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>静默·破碎都市</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Silent · Fractured City</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr"/>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>world.territory.foundry.name</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>铸造·铸造前哨</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Foundry · Foundry Outpost</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr"/>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>world.territory.clarity.name</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>澄净·沉淀湖</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Clarity · Sediment Lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr"/>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>world.territory.overclock.name</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>超频·热寂数据城</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Overclock · Heat-Death Data City</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr"/>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>world.territory.white_tide.name</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>白潮滩头</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>White Tide Beachhead</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr"/>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>world.hazard.none</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr"/>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>world.hazard.acid</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>酸沼带</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Acid marsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr"/>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>world.hazard.heat</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>高温辐射带</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Heat radiation belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr"/>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>world.preset.default.name</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr"/>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>world.legacy_terrain</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>原型地形（旧存档）</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Prototype terrain (older save)</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr"/>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>ui.world.generating</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>正在生成地形（{0} 个区块）…</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Generating terrain ({0} chunks)…</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr"/>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>grid.reason.world_limit</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>超出世界范围（离原点最多 {0} 格）</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Outside the world (at most {0} tiles from the origin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr"/>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ui.pause.world_seed</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>世界种子：{0}</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>World seed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr"/>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>ui.pause.copy_seed</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>复制种子</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Copy seed</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr"/>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>ui.pause.seed_copied</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>已复制种子 {0}</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Seed {0} copied</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr"/>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>ui.pause.world_settings</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>世界设置：{0} · 生成器 v{1} · {2}</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>World settings: {0} · generator v{1} · {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr"/>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>save.card.world</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>世界 {0}</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>World {0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3006,17 +3006,17 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>notify.type.core_destroyed.name</t>
+          <t>input.action.cycle_world_focus.name</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>核心被毁</t>
+          <t>切换关注点（家园 / 远征 / 突袭）</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Core destroyed</t>
+          <t>Cycle focus (home / expedition / raid)</t>
         </is>
       </c>
     </row>
@@ -3024,17 +3024,17 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>notify.type.core_destroyed.single</t>
+          <t>notify.type.core_destroyed.name</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>归还核心被摧毁：{0}</t>
+          <t>核心被毁</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>The Reclamation Core was destroyed: {0}</t>
+          <t>Core destroyed</t>
         </is>
       </c>
     </row>
@@ -3042,17 +3042,17 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>notify.type.core_destroyed.many</t>
+          <t>notify.type.core_destroyed.single</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>归还核心被摧毁（{0} 次）</t>
+          <t>归还核心被摧毁：{0}</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>The Reclamation Core was destroyed ({0} times)</t>
+          <t>The Reclamation Core was destroyed: {0}</t>
         </is>
       </c>
     </row>
@@ -3060,17 +3060,17 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>notify.type.machine_destroyed.name</t>
+          <t>notify.type.core_destroyed.many</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>机器损失</t>
+          <t>归还核心被摧毁（{0} 次）</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Machine lost</t>
+          <t>The Reclamation Core was destroyed ({0} times)</t>
         </is>
       </c>
     </row>
@@ -3078,17 +3078,17 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>notify.type.machine_destroyed.single</t>
+          <t>notify.type.machine_destroyed.name</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>机器损失：{0}</t>
+          <t>机器损失</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Machine lost: {0}</t>
+          <t>Machine lost</t>
         </is>
       </c>
     </row>
@@ -3096,17 +3096,17 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>notify.type.machine_destroyed.many</t>
+          <t>notify.type.machine_destroyed.single</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{0} 台机器损失</t>
+          <t>机器损失：{0}</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{0} machines lost</t>
+          <t>Machine lost: {0}</t>
         </is>
       </c>
     </row>
@@ -3114,17 +3114,17 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>notify.type.expedition_wiped.name</t>
+          <t>notify.type.machine_destroyed.many</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>远征全灭</t>
+          <t>{0} 台机器损失</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Expedition wiped out</t>
+          <t>{0} machines lost</t>
         </is>
       </c>
     </row>
@@ -3132,17 +3132,17 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>notify.type.expedition_wiped.single</t>
+          <t>notify.type.expedition_wiped.name</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>远征队已全部失去行动能力：{0}</t>
+          <t>远征全灭</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>The expedition was wiped out: {0}</t>
+          <t>Expedition wiped out</t>
         </is>
       </c>
     </row>
@@ -3150,17 +3150,17 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>notify.type.expedition_wiped.many</t>
+          <t>notify.type.expedition_wiped.single</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>远征全灭（{0} 次）</t>
+          <t>远征队已全部失去行动能力：{0}</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Expedition wiped out ({0} times)</t>
+          <t>The expedition was wiped out: {0}</t>
         </is>
       </c>
     </row>
@@ -3168,17 +3168,17 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>notify.type.failure.name</t>
+          <t>notify.type.expedition_wiped.many</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>远征全灭（{0} 次）</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>Expedition wiped out ({0} times)</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3186,17 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>notify.type.failure.single</t>
+          <t>notify.type.failure.name</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>失败：{0}</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Failure: {0}</t>
+          <t>Failure</t>
         </is>
       </c>
     </row>
@@ -3204,17 +3204,17 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>notify.type.failure.many</t>
+          <t>notify.type.failure.single</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{0} 次失败</t>
+          <t>失败：{0}</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{0} failures</t>
+          <t>Failure: {0}</t>
         </is>
       </c>
     </row>
@@ -3222,17 +3222,17 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>notify.type.boss_phase.name</t>
+          <t>notify.type.failure.many</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>首领阶段转换</t>
+          <t>{0} 次失败</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Boss phase change</t>
+          <t>{0} failures</t>
         </is>
       </c>
     </row>
@@ -3240,17 +3240,17 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>notify.type.boss_phase.single</t>
+          <t>notify.type.boss_phase.name</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>主核心阶段变化：{0}</t>
+          <t>首领阶段转换</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>The main core changed phase: {0}</t>
+          <t>Boss phase change</t>
         </is>
       </c>
     </row>
@@ -3258,17 +3258,17 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>notify.type.boss_phase.many</t>
+          <t>notify.type.boss_phase.single</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>主核心阶段变化（{0} 次）</t>
+          <t>主核心阶段变化：{0}</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>The main core changed phase ({0} times)</t>
+          <t>The main core changed phase: {0}</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>notify.type.boss_lockout.name</t>
+          <t>notify.type.boss_phase.many</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>核心分区封锁</t>
+          <t>主核心阶段变化（{0} 次）</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Core sector lockout</t>
+          <t>The main core changed phase ({0} times)</t>
         </is>
       </c>
     </row>
@@ -3294,17 +3294,17 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>notify.type.boss_lockout.single</t>
+          <t>notify.type.boss_lockout.name</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>核心分区封锁：{0}</t>
+          <t>核心分区封锁</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Core sector lockout: {0}</t>
+          <t>Core sector lockout</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>notify.type.boss_lockout.many</t>
+          <t>notify.type.boss_lockout.single</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>核心分区封锁警报（{0} 条）</t>
+          <t>核心分区封锁：{0}</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Core sector lockout alerts ({0})</t>
+          <t>Core sector lockout: {0}</t>
         </is>
       </c>
     </row>
@@ -3330,17 +3330,17 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>notify.type.raid_arrival.name</t>
+          <t>notify.type.boss_lockout.many</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>突袭到达</t>
+          <t>核心分区封锁警报（{0} 条）</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Raid arrived</t>
+          <t>Core sector lockout alerts ({0})</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3348,17 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>notify.type.raid_arrival.single</t>
+          <t>notify.type.raid_arrival.name</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>突袭到达：{0}</t>
+          <t>突袭到达</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Raid arrived: {0}</t>
+          <t>Raid arrived</t>
         </is>
       </c>
     </row>
@@ -3366,17 +3366,17 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>notify.type.raid_arrival.many</t>
+          <t>notify.type.raid_arrival.single</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{0} 支突袭到达</t>
+          <t>突袭到达：{0}</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{0} raids arrived</t>
+          <t>Raid arrived: {0}</t>
         </is>
       </c>
     </row>
@@ -3384,17 +3384,17 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>notify.type.silent_night.name</t>
+          <t>notify.type.raid_arrival.many</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>静默夜开始</t>
+          <t>{0} 支突袭到达</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Silent night begins</t>
+          <t>{0} raids arrived</t>
         </is>
       </c>
     </row>
@@ -3402,17 +3402,17 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>notify.type.silent_night.single</t>
+          <t>notify.type.silent_night.name</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>静默夜开始：{0}</t>
+          <t>静默夜开始</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>The silent night begins: {0}</t>
+          <t>Silent night begins</t>
         </is>
       </c>
     </row>
@@ -3420,17 +3420,17 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>notify.type.silent_night.many</t>
+          <t>notify.type.silent_night.single</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>静默夜开始（{0} 次）</t>
+          <t>静默夜开始：{0}</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>The silent night begins ({0} times)</t>
+          <t>The silent night begins: {0}</t>
         </is>
       </c>
     </row>
@@ -3438,17 +3438,17 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>notify.type.power_lost.name</t>
+          <t>notify.type.silent_night.many</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>缺电</t>
+          <t>静默夜开始（{0} 次）</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Power shortage</t>
+          <t>The silent night begins ({0} times)</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3456,17 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>notify.type.power_lost.single</t>
+          <t>notify.type.power_lost.name</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>电力不足：{0}</t>
+          <t>缺电</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Power shortage: {0}</t>
+          <t>Power shortage</t>
         </is>
       </c>
     </row>
@@ -3474,17 +3474,17 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>notify.type.power_lost.many</t>
+          <t>notify.type.power_lost.single</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{0} 处缺电</t>
+          <t>电力不足：{0}</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{0} power shortages</t>
+          <t>Power shortage: {0}</t>
         </is>
       </c>
     </row>
@@ -3492,17 +3492,17 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>notify.type.signal_lost.name</t>
+          <t>notify.type.power_lost.many</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>信号中断</t>
+          <t>{0} 处缺电</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Signal lost</t>
+          <t>{0} power shortages</t>
         </is>
       </c>
     </row>
@@ -3510,17 +3510,17 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>notify.type.signal_lost.single</t>
+          <t>notify.type.signal_lost.name</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>信号中断：{0}</t>
+          <t>信号中断</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Signal lost: {0}</t>
+          <t>Signal lost</t>
         </is>
       </c>
     </row>
@@ -3528,17 +3528,17 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>notify.type.signal_lost.many</t>
+          <t>notify.type.signal_lost.single</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{0} 处信号中断</t>
+          <t>信号中断：{0}</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>{0} signal losses</t>
+          <t>Signal lost: {0}</t>
         </is>
       </c>
     </row>
@@ -3546,17 +3546,17 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>notify.type.storage_full.name</t>
+          <t>notify.type.signal_lost.many</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>仓满</t>
+          <t>{0} 处信号中断</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Storage full</t>
+          <t>{0} signal losses</t>
         </is>
       </c>
     </row>
@@ -3564,17 +3564,17 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>notify.type.storage_full.single</t>
+          <t>notify.type.storage_full.name</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>仓库已满：{0}</t>
+          <t>仓满</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Storage full: {0}</t>
+          <t>Storage full</t>
         </is>
       </c>
     </row>
@@ -3582,17 +3582,17 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>notify.type.storage_full.many</t>
+          <t>notify.type.storage_full.single</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{0} 处仓满</t>
+          <t>仓库已满：{0}</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>{0} storage-full alerts</t>
+          <t>Storage full: {0}</t>
         </is>
       </c>
     </row>
@@ -3600,17 +3600,17 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>notify.type.emergency_rescue.name</t>
+          <t>notify.type.storage_full.many</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>紧急救援</t>
+          <t>{0} 处仓满</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Emergency rescue</t>
+          <t>{0} storage-full alerts</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>notify.type.emergency_rescue.single</t>
+          <t>notify.type.emergency_rescue.name</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>核心派出紧急救援机：{0}</t>
+          <t>紧急救援</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>The core sent an emergency rescue unit: {0}</t>
+          <t>Emergency rescue</t>
         </is>
       </c>
     </row>
@@ -3636,17 +3636,17 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>notify.type.emergency_rescue.many</t>
+          <t>notify.type.emergency_rescue.single</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>紧急救援（{0} 次）</t>
+          <t>核心派出紧急救援机：{0}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Emergency rescues ({0})</t>
+          <t>The core sent an emergency rescue unit: {0}</t>
         </is>
       </c>
     </row>
@@ -3654,17 +3654,17 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>notify.type.save_migrated.name</t>
+          <t>notify.type.emergency_rescue.many</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>读档变更</t>
+          <t>紧急救援（{0} 次）</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Load-time change</t>
+          <t>Emergency rescues ({0})</t>
         </is>
       </c>
     </row>
@@ -3672,17 +3672,17 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>notify.type.save_migrated.single</t>
+          <t>notify.type.save_migrated.name</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>读档变更</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Load-time change</t>
         </is>
       </c>
     </row>
@@ -3690,17 +3690,17 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>notify.type.save_migrated.many</t>
+          <t>notify.type.save_migrated.single</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{0} 条读档变更</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>{0} load-time changes</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>notify.type.weather.name</t>
+          <t>notify.type.save_migrated.many</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>天气</t>
+          <t>{0} 条读档变更</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>{0} load-time changes</t>
         </is>
       </c>
     </row>
@@ -3726,17 +3726,17 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>notify.type.weather.single</t>
+          <t>notify.type.weather.name</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>天气：{0}</t>
+          <t>天气</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Weather: {0}</t>
+          <t>Weather</t>
         </is>
       </c>
     </row>
@@ -3744,17 +3744,17 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>notify.type.weather.many</t>
+          <t>notify.type.weather.single</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{0} 条天气提醒</t>
+          <t>天气：{0}</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>{0} weather alerts</t>
+          <t>Weather: {0}</t>
         </is>
       </c>
     </row>
@@ -3762,17 +3762,17 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.name</t>
+          <t>notify.type.weather.many</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>供电恢复</t>
+          <t>{0} 条天气提醒</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Power restored</t>
+          <t>{0} weather alerts</t>
         </is>
       </c>
     </row>
@@ -3780,17 +3780,17 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.single</t>
+          <t>notify.type.power_restored.name</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>供电恢复：{0}</t>
+          <t>供电恢复</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Power restored: {0}</t>
+          <t>Power restored</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3798,17 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.many</t>
+          <t>notify.type.power_restored.single</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{0} 处供电恢复</t>
+          <t>供电恢复：{0}</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>{0} power restorations</t>
+          <t>Power restored: {0}</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.name</t>
+          <t>notify.type.power_restored.many</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>信号恢复</t>
+          <t>{0} 处供电恢复</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Signal restored</t>
+          <t>{0} power restorations</t>
         </is>
       </c>
     </row>
@@ -3834,17 +3834,17 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.single</t>
+          <t>notify.type.signal_restored.name</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>信号恢复：{0}</t>
+          <t>信号恢复</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Signal restored: {0}</t>
+          <t>Signal restored</t>
         </is>
       </c>
     </row>
@@ -3852,17 +3852,17 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.many</t>
+          <t>notify.type.signal_restored.single</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{0} 处信号恢复</t>
+          <t>信号恢复：{0}</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>{0} signal restorations</t>
+          <t>Signal restored: {0}</t>
         </is>
       </c>
     </row>
@@ -3870,17 +3870,17 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.name</t>
+          <t>notify.type.signal_restored.many</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>生产完成</t>
+          <t>{0} 处信号恢复</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Production complete</t>
+          <t>{0} signal restorations</t>
         </is>
       </c>
     </row>
@@ -3888,17 +3888,17 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.single</t>
+          <t>notify.type.production_complete.name</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>生产完成：{0}</t>
+          <t>生产完成</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Production complete: {0}</t>
+          <t>Production complete</t>
         </is>
       </c>
     </row>
@@ -3906,17 +3906,17 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.many</t>
+          <t>notify.type.production_complete.single</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{0} 项生产完成</t>
+          <t>生产完成：{0}</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>{0} items produced</t>
+          <t>Production complete: {0}</t>
         </is>
       </c>
     </row>
@@ -3924,17 +3924,17 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.name</t>
+          <t>notify.type.production_complete.many</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>解析完成</t>
+          <t>{0} 项生产完成</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Analysis complete</t>
+          <t>{0} items produced</t>
         </is>
       </c>
     </row>
@@ -3942,17 +3942,17 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.single</t>
+          <t>notify.type.analysis_complete.name</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>解析完成：{0}</t>
+          <t>解析完成</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Analysis complete: {0}</t>
+          <t>Analysis complete</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.many</t>
+          <t>notify.type.analysis_complete.single</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{0} 项解析完成</t>
+          <t>解析完成：{0}</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>{0} analyses complete</t>
+          <t>Analysis complete: {0}</t>
         </is>
       </c>
     </row>
@@ -3978,17 +3978,17 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.name</t>
+          <t>notify.type.analysis_complete.many</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>建造完成</t>
+          <t>{0} 项解析完成</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Construction complete</t>
+          <t>{0} analyses complete</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3996,17 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.single</t>
+          <t>notify.type.build_complete.name</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>完工：{0}</t>
+          <t>建造完成</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Completed: {0}</t>
+          <t>Construction complete</t>
         </is>
       </c>
     </row>
@@ -4014,17 +4014,17 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.many</t>
+          <t>notify.type.build_complete.single</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{0} 座建筑完工</t>
+          <t>完工：{0}</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>{0} buildings completed</t>
+          <t>Completed: {0}</t>
         </is>
       </c>
     </row>
@@ -4032,17 +4032,17 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.name</t>
+          <t>notify.type.build_complete.many</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>新任务</t>
+          <t>{0} 座建筑完工</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>New objective</t>
+          <t>{0} buildings completed</t>
         </is>
       </c>
     </row>
@@ -4050,17 +4050,17 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.single</t>
+          <t>notify.type.objective_new.name</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>新目标：{0}</t>
+          <t>新任务</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>New objective: {0}</t>
+          <t>New objective</t>
         </is>
       </c>
     </row>
@@ -4068,17 +4068,17 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.many</t>
+          <t>notify.type.objective_new.single</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{0} 个新目标</t>
+          <t>新目标：{0}</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>{0} new objectives</t>
+          <t>New objective: {0}</t>
         </is>
       </c>
     </row>
@@ -4086,17 +4086,17 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.name</t>
+          <t>notify.type.objective_new.many</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>目标完成</t>
+          <t>{0} 个新目标</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Objective complete</t>
+          <t>{0} new objectives</t>
         </is>
       </c>
     </row>
@@ -4104,17 +4104,17 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.single</t>
+          <t>notify.type.objective_done.name</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>目标完成：{0}</t>
+          <t>目标完成</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Objective complete: {0}</t>
+          <t>Objective complete</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.many</t>
+          <t>notify.type.objective_done.single</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{0} 个目标完成</t>
+          <t>目标完成：{0}</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>{0} objectives complete</t>
+          <t>Objective complete: {0}</t>
         </is>
       </c>
     </row>
@@ -4140,17 +4140,17 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>notify.type.expedition.name</t>
+          <t>notify.type.objective_done.many</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>远征动态</t>
+          <t>{0} 个目标完成</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>{0} objectives complete</t>
         </is>
       </c>
     </row>
@@ -4158,17 +4158,17 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>notify.type.expedition.single</t>
+          <t>notify.type.expedition.name</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>远征：{0}</t>
+          <t>远征动态</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Expedition: {0}</t>
+          <t>Expedition</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>notify.type.expedition.many</t>
+          <t>notify.type.expedition.single</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{0} 条远征动态</t>
+          <t>远征：{0}</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>{0} expedition updates</t>
+          <t>Expedition: {0}</t>
         </is>
       </c>
     </row>
@@ -4194,17 +4194,17 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.name</t>
+          <t>notify.type.expedition.many</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>首领击破</t>
+          <t>{0} 条远征动态</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Boss destroyed</t>
+          <t>{0} expedition updates</t>
         </is>
       </c>
     </row>
@@ -4212,17 +4212,17 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.single</t>
+          <t>notify.type.boss_destroyed.name</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>主核心已摧毁：{0}</t>
+          <t>首领击破</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The main core was destroyed: {0}</t>
+          <t>Boss destroyed</t>
         </is>
       </c>
     </row>
@@ -4230,17 +4230,17 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.many</t>
+          <t>notify.type.boss_destroyed.single</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>主核心已摧毁（{0} 次）</t>
+          <t>主核心已摧毁：{0}</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The main core was destroyed ({0} times)</t>
+          <t>The main core was destroyed: {0}</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>notify.type.beacon.name</t>
+          <t>notify.type.boss_destroyed.many</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>导航信标</t>
+          <t>主核心已摧毁（{0} 次）</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Navigation beacon</t>
+          <t>The main core was destroyed ({0} times)</t>
         </is>
       </c>
     </row>
@@ -4266,17 +4266,17 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>notify.type.beacon.single</t>
+          <t>notify.type.beacon.name</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>导航信标：{0}</t>
+          <t>导航信标</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Navigation beacon: {0}</t>
+          <t>Navigation beacon</t>
         </is>
       </c>
     </row>
@@ -4284,17 +4284,17 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>notify.type.beacon.many</t>
+          <t>notify.type.beacon.single</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{0} 条信标动态</t>
+          <t>导航信标：{0}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>{0} beacon updates</t>
+          <t>Navigation beacon: {0}</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>notify.type.research_done.name</t>
+          <t>notify.type.beacon.many</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>研究完成</t>
+          <t>{0} 条信标动态</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Research complete</t>
+          <t>{0} beacon updates</t>
         </is>
       </c>
     </row>
@@ -4320,17 +4320,17 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>notify.type.research_done.single</t>
+          <t>notify.type.research_done.name</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>研究完成：{0}</t>
+          <t>研究完成</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Research complete: {0}</t>
+          <t>Research complete</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>notify.type.research_done.many</t>
+          <t>notify.type.research_done.single</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{0} 项研究完成</t>
+          <t>研究完成：{0}</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>{0} research projects complete</t>
+          <t>Research complete: {0}</t>
         </is>
       </c>
     </row>
@@ -4356,17 +4356,17 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.name</t>
+          <t>notify.type.research_done.many</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>自动暂停</t>
+          <t>{0} 项研究完成</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Auto-pause</t>
+          <t>{0} research projects complete</t>
         </is>
       </c>
     </row>
@@ -4374,17 +4374,17 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.single</t>
+          <t>notify.type.auto_paused.name</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>已自动暂停：由通知「{0}」触发，可在通知设置中关闭</t>
+          <t>自动暂停</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Auto-paused by the "{0}" notification. You can turn this off in notification settings.</t>
+          <t>Auto-pause</t>
         </is>
       </c>
     </row>
@@ -4392,17 +4392,17 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.many</t>
+          <t>notify.type.auto_paused.single</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>已自动暂停（{0} 次）</t>
+          <t>已自动暂停：由通知「{0}」触发，可在通知设置中关闭</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Auto-paused ({0} times)</t>
+          <t>Auto-paused by the "{0}" notification. You can turn this off in notification settings.</t>
         </is>
       </c>
     </row>
@@ -4410,17 +4410,17 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.name</t>
+          <t>notify.type.auto_paused.many</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>设置变更</t>
+          <t>已自动暂停（{0} 次）</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Settings changed</t>
+          <t>Auto-paused ({0} times)</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.single</t>
+          <t>notify.type.settings_changed.name</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>设置变更</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Settings changed</t>
         </is>
       </c>
     </row>
@@ -4446,17 +4446,17 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.many</t>
+          <t>notify.type.settings_changed.single</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{0} 条设置变更</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>{0} settings changes</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -4464,17 +4464,17 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.settings_changed.many</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>尚未开放</t>
+          <t>{0} 条设置变更</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Not yet available</t>
+          <t>{0} settings changes</t>
         </is>
       </c>
     </row>
@@ -4482,17 +4482,17 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.feature_locked.name</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>「{0}」将在后续版本开放</t>
+          <t>尚未开放</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>"{0}" will be available in a later version</t>
+          <t>Not yet available</t>
         </is>
       </c>
     </row>
@@ -4500,17 +4500,17 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.feature_locked.single</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>{0} 个操作尚未开放</t>
+          <t>「{0}」将在后续版本开放</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>{0} actions are not yet available</t>
+          <t>"{0}" will be available in a later version</t>
         </is>
       </c>
     </row>
@@ -4518,17 +4518,17 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>notify.tier.urgent</t>
+          <t>notify.type.feature_locked.many</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>紧急</t>
+          <t>{0} 个操作尚未开放</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>{0} actions are not yet available</t>
         </is>
       </c>
     </row>
@@ -4536,17 +4536,17 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>notify.tier.warning</t>
+          <t>notify.tier.urgent</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>警告</t>
+          <t>紧急</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>notify.tier.info</t>
+          <t>notify.tier.warning</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>信息</t>
+          <t>警告</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -4572,17 +4572,17 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>input.category.camera</t>
+          <t>notify.tier.info</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>镜头</t>
+          <t>信息</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Info</t>
         </is>
       </c>
     </row>
@@ -4590,17 +4590,17 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>input.category.time</t>
+          <t>input.category.camera</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>镜头</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -4608,17 +4608,17 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>input.category.command</t>
+          <t>input.category.time</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>指挥</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Command</t>
+          <t>Time</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4626,17 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.command</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>建造</t>
+          <t>指挥</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Command</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>input.category.uplink</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>建造</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -4662,17 +4662,17 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>input.category.panel</t>
+          <t>input.category.uplink</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>面板</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Panels</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -4680,17 +4680,17 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>input.category.system</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>面板</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Panels</t>
         </is>
       </c>
     </row>
@@ -4698,17 +4698,17 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>input.context.strategy</t>
+          <t>input.category.system</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>战略</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -4716,17 +4716,17 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>input.context.build</t>
+          <t>input.context.strategy</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>建造</t>
+          <t>战略</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Strategy</t>
         </is>
       </c>
     </row>
@@ -4734,17 +4734,17 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>input.context.uplink</t>
+          <t>input.context.build</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>建造</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -4752,17 +4752,17 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>input.context.interface</t>
+          <t>input.context.uplink</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>界面</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -4770,17 +4770,17 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>input.mod.ctrl</t>
+          <t>input.context.interface</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>界面</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>Interface</t>
         </is>
       </c>
     </row>
@@ -4788,17 +4788,17 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>input.mod.alt</t>
+          <t>input.mod.ctrl</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Alt</t>
+          <t>Ctrl</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Alt</t>
+          <t>Ctrl</t>
         </is>
       </c>
     </row>
@@ -4806,17 +4806,17 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>input.mod.shift</t>
+          <t>input.mod.alt</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Alt</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Alt</t>
         </is>
       </c>
     </row>
@@ -4824,17 +4824,17 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>input.chord.join</t>
+          <t>input.mod.shift</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{0}+{1}</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>{0}+{1}</t>
+          <t>Shift</t>
         </is>
       </c>
     </row>
@@ -4842,17 +4842,17 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>input.key.none</t>
+          <t>input.chord.join</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>未绑定</t>
+          <t>{0}+{1}</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Unbound</t>
+          <t>{0}+{1}</t>
         </is>
       </c>
     </row>
@@ -4860,17 +4860,17 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>input.key.space</t>
+          <t>input.key.none</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>未绑定</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Unbound</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4878,17 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>input.key.escape</t>
+          <t>input.key.space</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Esc</t>
+          <t>空格</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Esc</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -4896,17 +4896,17 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>input.key.return</t>
+          <t>input.key.escape</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>回车</t>
+          <t>Esc</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Esc</t>
         </is>
       </c>
     </row>
@@ -4914,17 +4914,17 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>input.key.tab</t>
+          <t>input.key.return</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>回车</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Enter</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4932,17 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>input.key.back_quote</t>
+          <t>input.key.tab</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>Tab</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4950,17 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>input.key.home</t>
+          <t>input.key.back_quote</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>`</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>`</t>
         </is>
       </c>
     </row>
@@ -4968,17 +4968,17 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>input.key.mouse0</t>
+          <t>input.key.home</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>鼠标左键</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Left mouse</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -4986,17 +4986,17 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>input.key.mouse1</t>
+          <t>input.key.mouse0</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>鼠标右键</t>
+          <t>鼠标左键</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Right mouse</t>
+          <t>Left mouse</t>
         </is>
       </c>
     </row>
@@ -5004,17 +5004,17 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>input.key.mouse2</t>
+          <t>input.key.mouse1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>鼠标中键</t>
+          <t>鼠标右键</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Middle mouse</t>
+          <t>Right mouse</t>
         </is>
       </c>
     </row>
@@ -5022,17 +5022,17 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>input.key.wheel_up</t>
+          <t>input.key.mouse2</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>滚轮上</t>
+          <t>鼠标中键</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Wheel up</t>
+          <t>Middle mouse</t>
         </is>
       </c>
     </row>
@@ -5040,17 +5040,17 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>input.key.wheel_down</t>
+          <t>input.key.wheel_up</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>滚轮下</t>
+          <t>滚轮上</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Wheel down</t>
+          <t>Wheel up</t>
         </is>
       </c>
     </row>
@@ -5058,17 +5058,17 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>input.key.up_arrow</t>
+          <t>input.key.wheel_down</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>上方向键</t>
+          <t>滚轮下</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Up arrow</t>
+          <t>Wheel down</t>
         </is>
       </c>
     </row>
@@ -5076,17 +5076,17 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>input.key.down_arrow</t>
+          <t>input.key.up_arrow</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>下方向键</t>
+          <t>上方向键</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Down arrow</t>
+          <t>Up arrow</t>
         </is>
       </c>
     </row>
@@ -5094,17 +5094,17 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>input.key.left_arrow</t>
+          <t>input.key.down_arrow</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>左方向键</t>
+          <t>下方向键</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Left arrow</t>
+          <t>Down arrow</t>
         </is>
       </c>
     </row>
@@ -5112,17 +5112,17 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>input.key.right_arrow</t>
+          <t>input.key.left_arrow</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>右方向键</t>
+          <t>左方向键</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Right arrow</t>
+          <t>Left arrow</t>
         </is>
       </c>
     </row>
@@ -5130,17 +5130,17 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>input.key.left_shift</t>
+          <t>input.key.right_arrow</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>左 Shift</t>
+          <t>右方向键</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Left Shift</t>
+          <t>Right arrow</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5148,17 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>input.key.right_shift</t>
+          <t>input.key.left_shift</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>右 Shift</t>
+          <t>左 Shift</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Right Shift</t>
+          <t>Left Shift</t>
         </is>
       </c>
     </row>
@@ -5166,17 +5166,17 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>input.key.left_alt</t>
+          <t>input.key.right_shift</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>左 Alt</t>
+          <t>右 Shift</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Left Alt</t>
+          <t>Right Shift</t>
         </is>
       </c>
     </row>
@@ -5184,17 +5184,17 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>input.key.right_alt</t>
+          <t>input.key.left_alt</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>右 Alt</t>
+          <t>左 Alt</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Right Alt</t>
+          <t>Left Alt</t>
         </is>
       </c>
     </row>
@@ -5202,17 +5202,17 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>input.key.left_control</t>
+          <t>input.key.right_alt</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>左 Ctrl</t>
+          <t>右 Alt</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Left Ctrl</t>
+          <t>Right Alt</t>
         </is>
       </c>
     </row>
@@ -5220,17 +5220,17 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>input.key.right_control</t>
+          <t>input.key.left_control</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>右 Ctrl</t>
+          <t>左 Ctrl</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Right Ctrl</t>
+          <t>Left Ctrl</t>
         </is>
       </c>
     </row>
@@ -5238,17 +5238,17 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>input.key.digit</t>
+          <t>input.key.right_control</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>右 Ctrl</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Right Ctrl</t>
         </is>
       </c>
     </row>
@@ -5256,17 +5256,17 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>input.rebind.listening</t>
+          <t>input.key.digit</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>请按下新按键……（Esc 取消）</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Press a new key... (Esc to cancel)</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -5274,17 +5274,17 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>input.rebind.conflict_title</t>
+          <t>input.rebind.listening</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>按键冲突</t>
+          <t>请按下新按键……（Esc 取消）</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Key conflict</t>
+          <t>Press a new key... (Esc to cancel)</t>
         </is>
       </c>
     </row>
@@ -5292,17 +5292,17 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>input.rebind.conflict_line</t>
+          <t>input.rebind.conflict_title</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>{0} 已被「{1}」使用（{2}）</t>
+          <t>按键冲突</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>{0} is already used by "{1}" ({2})</t>
+          <t>Key conflict</t>
         </is>
       </c>
     </row>
@@ -5310,17 +5310,17 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>input.rebind.conflict_tail</t>
+          <t>input.rebind.conflict_line</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>覆盖后「{0}」将变为未绑定。</t>
+          <t>{0} 已被「{1}」使用（{2}）</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>If you overwrite it, "{0}" becomes unbound.</t>
+          <t>{0} is already used by "{1}" ({2})</t>
         </is>
       </c>
     </row>
@@ -5328,17 +5328,17 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>input.rebind.override</t>
+          <t>input.rebind.conflict_tail</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>覆盖</t>
+          <t>覆盖后「{0}」将变为未绑定。</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Overwrite</t>
+          <t>If you overwrite it, "{0}" becomes unbound.</t>
         </is>
       </c>
     </row>
@@ -5346,17 +5346,17 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>input.rebind.required_blocked</t>
+          <t>input.rebind.override</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>「{0}」必须保留按键，不能被覆盖；请先给它换一个键</t>
+          <t>覆盖</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>"{0}" must keep a key and cannot be overwritten; rebind it first</t>
+          <t>Overwrite</t>
         </is>
       </c>
     </row>
@@ -5364,17 +5364,17 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>input.rebind.done</t>
+          <t>input.rebind.required_blocked</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>已将「{0}」设为 {1}</t>
+          <t>「{0}」必须保留按键，不能被覆盖；请先给它换一个键</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>"{0}" is now {1}</t>
+          <t>"{0}" must keep a key and cannot be overwritten; rebind it first</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>input.rebind.mouse_only</t>
+          <t>input.rebind.done</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>「{0}」只能绑定鼠标按键</t>
+          <t>已将「{0}」设为 {1}</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>"{0}" can only be bound to a mouse button</t>
+          <t>"{0}" is now {1}</t>
         </is>
       </c>
     </row>
@@ -5400,17 +5400,17 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>input.rebind.reset_conflict</t>
+          <t>input.rebind.mouse_only</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>「{0}」的默认键已被别的动作占用，请先改那个动作</t>
+          <t>「{0}」只能绑定鼠标按键</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>The default key of "{0}" is taken by another action; change that one first</t>
+          <t>"{0}" can only be bound to a mouse button</t>
         </is>
       </c>
     </row>
@@ -5418,17 +5418,17 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>input.rebind.cancelled</t>
+          <t>input.rebind.reset_conflict</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>已取消改键</t>
+          <t>「{0}」的默认键已被别的动作占用，请先改那个动作</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Rebinding cancelled</t>
+          <t>The default key of "{0}" is taken by another action; change that one first</t>
         </is>
       </c>
     </row>
@@ -5436,17 +5436,17 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>input.rebind.reset_one</t>
+          <t>input.rebind.cancelled</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>已取消改键</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Rebinding cancelled</t>
         </is>
       </c>
     </row>
@@ -5454,17 +5454,17 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>input.rebind.reset_all_title</t>
+          <t>input.rebind.reset_one</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>恢复全部默认按键</t>
+          <t>恢复默认</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Reset all keys to default</t>
+          <t>Default</t>
         </is>
       </c>
     </row>
@@ -5472,17 +5472,17 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>input.rebind.reset_all_line</t>
+          <t>input.rebind.reset_all_title</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>将丢失：你改过的 {0} 个按键</t>
+          <t>恢复全部默认按键</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>You will lose: {0} customised key(s)</t>
+          <t>Reset all keys to default</t>
         </is>
       </c>
     </row>
@@ -5490,17 +5490,17 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>input.rebind.migrated</t>
+          <t>input.rebind.reset_all_line</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>按键方案已更新为正式版：保留了你改过的 {0} 个按键，{1} 个因与新默认键冲突已恢复默认</t>
+          <t>将丢失：你改过的 {0} 个按键</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Key layout updated for the full game: kept {0} customised key(s); {1} restored to default because they clashed with new defaults</t>
+          <t>You will lose: {0} customised key(s)</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5508,17 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>input.rebind.migrated_defaults</t>
+          <t>input.rebind.migrated</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>按键方案已更新为正式版，部分默认按键有调整，可在暂停菜单 → 按键设置查看</t>
+          <t>按键方案已更新为正式版：保留了你改过的 {0} 个按键，{1} 个因与新默认键冲突已恢复默认</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Key layout updated for the full game; some default keys changed. See Pause menu → Key bindings</t>
+          <t>Key layout updated for the full game: kept {0} customised key(s); {1} restored to default because they clashed with new defaults</t>
         </is>
       </c>
     </row>
@@ -5526,17 +5526,17 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>input.status.reserved</t>
+          <t>input.rebind.migrated_defaults</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>后续版本开放</t>
+          <t>按键方案已更新为正式版，部分默认按键有调整，可在暂停菜单 → 按键设置查看</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Coming later</t>
+          <t>Key layout updated for the full game; some default keys changed. See Pause menu → Key bindings</t>
         </is>
       </c>
     </row>
@@ -5544,17 +5544,17 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>input.status.unbound_warning</t>
+          <t>input.status.reserved</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>未绑定：只能用鼠标或界面按钮操作</t>
+          <t>后续版本开放</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Unbound: use the mouse or on-screen buttons</t>
+          <t>Coming later</t>
         </is>
       </c>
     </row>
@@ -5562,17 +5562,17 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>input.status.reserved_tip</t>
+          <t>input.status.unbound_warning</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>这个操作对应的系统还没有开放，按键先保留，可以提前改键</t>
+          <t>未绑定：只能用鼠标或界面按钮操作</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>This action's system is not available yet; you can still set its key</t>
+          <t>Unbound: use the mouse or on-screen buttons</t>
         </is>
       </c>
     </row>
@@ -5580,17 +5580,17 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>input.tooltip.contexts</t>
+          <t>input.status.reserved_tip</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>生效范围：{0}</t>
+          <t>这个操作对应的系统还没有开放，按键先保留，可以提前改键</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Active in: {0}</t>
+          <t>This action's system is not available yet; you can still set its key</t>
         </is>
       </c>
     </row>
@@ -5598,17 +5598,17 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ui.keybind.title</t>
+          <t>input.tooltip.contexts</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>按键设置</t>
+          <t>生效范围：{0}</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Key bindings</t>
+          <t>Active in: {0}</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ui.keybind.open_all</t>
+          <t>ui.keybind.title</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>全部按键…</t>
+          <t>按键设置</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>All keys...</t>
+          <t>Key bindings</t>
         </is>
       </c>
     </row>
@@ -5634,17 +5634,17 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ui.keybind.search_placeholder</t>
+          <t>ui.keybind.open_all</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>搜索动作或按键</t>
+          <t>全部按键…</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Search actions or keys</t>
+          <t>All keys...</t>
         </is>
       </c>
     </row>
@@ -5652,17 +5652,17 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ui.keybind.tab_all</t>
+          <t>ui.keybind.search_placeholder</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>搜索动作或按键</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search actions or keys</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5670,17 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ui.keybind.empty</t>
+          <t>ui.keybind.tab_all</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>没有匹配“{0}”的动作</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>No actions match "{0}"</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -5688,17 +5688,17 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ui.keybind.count</t>
+          <t>ui.keybind.empty</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>共 {0} 个动作，{1} 个已改键</t>
+          <t>没有匹配“{0}”的动作</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>{0} actions, {1} customised</t>
+          <t>No actions match "{0}"</t>
         </is>
       </c>
     </row>
@@ -5706,17 +5706,17 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ui.keybind.reset_all</t>
+          <t>ui.keybind.count</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>全部恢复默认</t>
+          <t>共 {0} 个动作，{1} 个已改键</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Reset all</t>
+          <t>{0} actions, {1} customised</t>
         </is>
       </c>
     </row>
@@ -5724,17 +5724,17 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ui.keybind.col_action</t>
+          <t>ui.keybind.reset_all</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>动作</t>
+          <t>全部恢复默认</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Reset all</t>
         </is>
       </c>
     </row>
@@ -5742,17 +5742,17 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ui.keybind.col_key</t>
+          <t>ui.keybind.col_action</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>按键</t>
+          <t>动作</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -5760,17 +5760,17 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ui.common.close</t>
+          <t>ui.keybind.col_key</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>按键</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Key</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>ui.common.cancel</t>
+          <t>ui.common.close</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -5796,17 +5796,17 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ui.common.confirm</t>
+          <t>ui.common.cancel</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -5814,17 +5814,17 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ui.common.loading</t>
+          <t>ui.common.confirm</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>加载中……</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
@@ -5832,17 +5832,17 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ui.common.empty</t>
+          <t>ui.common.loading</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>暂无内容</t>
+          <t>加载中……</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Nothing here yet</t>
+          <t>Loading...</t>
         </is>
       </c>
     </row>
@@ -5850,17 +5850,17 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ui.common.clear</t>
+          <t>ui.common.empty</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>清空</t>
+          <t>暂无内容</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Nothing here yet</t>
         </is>
       </c>
     </row>
@@ -5868,17 +5868,17 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ui.common.shortcut</t>
+          <t>ui.common.clear</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>快捷键：{0}</t>
+          <t>清空</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Shortcut: {0}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -5886,17 +5886,17 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ui.common.codex_link</t>
+          <t>ui.common.shortcut</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>图鉴：{0}</t>
+          <t>快捷键：{0}</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Codex: {0}</t>
+          <t>Shortcut: {0}</t>
         </is>
       </c>
     </row>
@@ -5904,17 +5904,17 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ui.common.disabled_reason</t>
+          <t>ui.common.codex_link</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>不可用：{0}</t>
+          <t>图鉴：{0}</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Unavailable: {0}</t>
+          <t>Codex: {0}</t>
         </is>
       </c>
     </row>
@@ -5922,17 +5922,17 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ui.drag.cancelled</t>
+          <t>ui.common.disabled_reason</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>已取消拖动</t>
+          <t>不可用：{0}</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Drag cancelled</t>
+          <t>Unavailable: {0}</t>
         </is>
       </c>
     </row>
@@ -5940,17 +5940,17 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ui.drag.no_target</t>
+          <t>ui.drag.cancelled</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>没有放到可放置的位置</t>
+          <t>已取消拖动</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Not dropped on a valid target</t>
+          <t>Drag cancelled</t>
         </is>
       </c>
     </row>
@@ -5958,17 +5958,17 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ui.confirm.lose_prefix</t>
+          <t>ui.drag.no_target</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>将丢失：</t>
+          <t>没有放到可放置的位置</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>You will lose:</t>
+          <t>Not dropped on a valid target</t>
         </is>
       </c>
     </row>
@@ -5976,17 +5976,17 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ui.confirm.irreversible</t>
+          <t>ui.confirm.lose_prefix</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>此操作无法撤销。</t>
+          <t>将丢失：</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>This cannot be undone.</t>
+          <t>You will lose:</t>
         </is>
       </c>
     </row>
@@ -5994,17 +5994,17 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ui.tooltip.pin_hint</t>
+          <t>ui.confirm.irreversible</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>按住 {0} 固定提示</t>
+          <t>此操作无法撤销。</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Hold {0} to pin</t>
+          <t>This cannot be undone.</t>
         </is>
       </c>
     </row>
@@ -6012,17 +6012,17 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ui.tooltip.pinned</t>
+          <t>ui.tooltip.pin_hint</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>已固定：松开 {0} 或移开鼠标关闭</t>
+          <t>按住 {0} 固定提示</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Pinned: release {0} or move away to close</t>
+          <t>Hold {0} to pin</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ui.tooltip.expand_sources</t>
+          <t>ui.tooltip.pinned</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>展开来源</t>
+          <t>已固定：松开 {0} 或移开鼠标关闭</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Show breakdown</t>
+          <t>Pinned: release {0} or move away to close</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ui.tooltip.collapse_sources</t>
+          <t>ui.tooltip.expand_sources</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>收起来源</t>
+          <t>展开来源</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Hide breakdown</t>
+          <t>Show breakdown</t>
         </is>
       </c>
     </row>
@@ -6066,17 +6066,17 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>ui.tooltip.total</t>
+          <t>ui.tooltip.collapse_sources</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>合计 {0}</t>
+          <t>收起来源</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Total {0}</t>
+          <t>Hide breakdown</t>
         </is>
       </c>
     </row>
@@ -6084,17 +6084,17 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>ui.notify.title</t>
+          <t>ui.tooltip.total</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>通知中心</t>
+          <t>合计 {0}</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Total {0}</t>
         </is>
       </c>
     </row>
@@ -6102,17 +6102,17 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>ui.notify.entry_unread</t>
+          <t>ui.notify.title</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>通知中心</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
@@ -6120,17 +6120,17 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ui.notify.filter_all</t>
+          <t>ui.notify.entry_unread</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>全部等级</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>All levels</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -6138,17 +6138,17 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>ui.notify.filter_type_all</t>
+          <t>ui.notify.filter_all</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>全部类型</t>
+          <t>全部等级</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>All types</t>
+          <t>All levels</t>
         </is>
       </c>
     </row>
@@ -6156,17 +6156,17 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ui.notify.empty</t>
+          <t>ui.notify.filter_type_all</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>没有符合条件的通知</t>
+          <t>全部类型</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>No matching notifications</t>
+          <t>All types</t>
         </is>
       </c>
     </row>
@@ -6174,17 +6174,17 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ui.notify.count</t>
+          <t>ui.notify.empty</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>共 {0} 条，显示 {1} 条</t>
+          <t>没有符合条件的通知</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>{0} total, {1} shown</t>
+          <t>No matching notifications</t>
         </is>
       </c>
     </row>
@@ -6192,17 +6192,17 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ui.notify.locate</t>
+          <t>ui.notify.count</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>定位</t>
+          <t>共 {0} 条，显示 {1} 条</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Locate</t>
+          <t>{0} total, {1} shown</t>
         </is>
       </c>
     </row>
@@ -6210,17 +6210,17 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ui.notify.no_location</t>
+          <t>ui.notify.locate</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>这条通知没有位置</t>
+          <t>定位</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>This notification has no location</t>
+          <t>Locate</t>
         </is>
       </c>
     </row>
@@ -6228,17 +6228,17 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ui.notify.other_region</t>
+          <t>ui.notify.no_location</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>位置在另一个区域，回到该区域后再定位</t>
+          <t>这条通知没有位置</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>The location is in another region; go there first</t>
+          <t>This notification has no location</t>
         </is>
       </c>
     </row>
@@ -6246,17 +6246,17 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ui.notify.no_camera</t>
+          <t>ui.notify.other_region</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>当前没有可移动的镜头</t>
+          <t>位置在另一个区域，回到该区域后再定位</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>No camera is available to move</t>
+          <t>The location is in another region; go there first</t>
         </is>
       </c>
     </row>
@@ -6264,17 +6264,17 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ui.notify.expand</t>
+          <t>ui.notify.no_camera</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>展开 {0} 条</t>
+          <t>当前没有可移动的镜头</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Show {0}</t>
+          <t>No camera is available to move</t>
         </is>
       </c>
     </row>
@@ -6282,17 +6282,17 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ui.notify.collapse</t>
+          <t>ui.notify.expand</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>收起</t>
+          <t>展开 {0} 条</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Show {0}</t>
         </is>
       </c>
     </row>
@@ -6300,17 +6300,17 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ui.notify.settings</t>
+          <t>ui.notify.collapse</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>通知设置</t>
+          <t>收起</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Notification settings</t>
+          <t>Collapse</t>
         </is>
       </c>
     </row>
@@ -6318,17 +6318,17 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ui.notify.auto_pause</t>
+          <t>ui.notify.settings</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>触发时自动暂停</t>
+          <t>通知设置</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Auto-pause when triggered</t>
+          <t>Notification settings</t>
         </is>
       </c>
     </row>
@@ -6336,17 +6336,17 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ui.notify.duration</t>
+          <t>ui.notify.auto_pause</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>弹出提示停留：{0}</t>
+          <t>触发时自动暂停</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Pop-up duration: {0}</t>
+          <t>Auto-pause when triggered</t>
         </is>
       </c>
     </row>
@@ -6354,17 +6354,17 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ui.notify.saved_history</t>
+          <t>ui.notify.duration</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>读档变更</t>
+          <t>弹出提示停留：{0}</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Load-time changes</t>
+          <t>Pop-up duration: {0}</t>
         </is>
       </c>
     </row>
@@ -6372,17 +6372,17 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ui.notify.time_day</t>
+          <t>ui.notify.saved_history</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>第 {0} 日 {1}</t>
+          <t>读档变更</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Day {0} {1}</t>
+          <t>Load-time changes</t>
         </is>
       </c>
     </row>
@@ -6390,17 +6390,17 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>ui.notify.time_real</t>
+          <t>ui.notify.time_day</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>第 {0} 日 {1}</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Day {0} {1}</t>
         </is>
       </c>
     </row>
@@ -6408,17 +6408,17 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ui.notify.times</t>
+          <t>ui.notify.time_real</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>×{0}</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>×{0}</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -6426,17 +6426,17 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>ui.notify.source_rule</t>
+          <t>ui.notify.times</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>由规则「{0}」触发</t>
+          <t>×{0}</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Triggered by rule "{0}"</t>
+          <t>×{0}</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>ui.notify.source_system</t>
+          <t>ui.notify.source_rule</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>来源：{0}</t>
+          <t>由规则「{0}」触发</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Source: {0}</t>
+          <t>Triggered by rule "{0}"</t>
         </is>
       </c>
     </row>
@@ -6462,17 +6462,17 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ui.pause.title</t>
+          <t>ui.notify.source_system</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>来源：{0}</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Source: {0}</t>
         </is>
       </c>
     </row>
@@ -6480,17 +6480,17 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>ui.pause.resume</t>
+          <t>ui.pause.title</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>继续游戏</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Paused</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>ui.pause.keybinds</t>
+          <t>ui.pause.resume</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>按键设置</t>
+          <t>继续游戏</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Key bindings</t>
+          <t>Resume</t>
         </is>
       </c>
     </row>
@@ -6516,17 +6516,17 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>ui.pause.notifications</t>
+          <t>ui.pause.keybinds</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>通知中心</t>
+          <t>按键设置</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Key bindings</t>
         </is>
       </c>
     </row>
@@ -6534,17 +6534,17 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ui.pause.save_and_quit</t>
+          <t>ui.pause.notifications</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>保存并返回主菜单</t>
+          <t>通知中心</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Save and return to menu</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
@@ -6552,17 +6552,17 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ui.pause.quit_title</t>
+          <t>ui.pause.save_and_quit</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>返回主菜单</t>
+          <t>保存并返回主菜单</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Return to main menu</t>
+          <t>Save and return to menu</t>
         </is>
       </c>
     </row>
@@ -6570,17 +6570,17 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ui.pause.quit_line</t>
+          <t>ui.pause.quit_title</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>当前进度会先保存到{0}</t>
+          <t>返回主菜单</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Progress will be saved to {0} first</t>
+          <t>Return to main menu</t>
         </is>
       </c>
     </row>
@@ -6588,17 +6588,17 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ui.pause.quit_failed</t>
+          <t>ui.pause.quit_line</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>保存失败，已留在游戏中：{0}</t>
+          <t>当前进度会先保存到{0}</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Saving failed; you are still in the game: {0}</t>
+          <t>Progress will be saved to {0} first</t>
         </is>
       </c>
     </row>
@@ -6606,17 +6606,17 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ui.pause.gallery</t>
+          <t>ui.pause.quit_failed</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>界面基础件样例（开发）</t>
+          <t>保存失败，已留在游戏中：{0}</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>UI kit gallery (dev)</t>
+          <t>Saving failed; you are still in the game: {0}</t>
         </is>
       </c>
     </row>
@@ -6624,17 +6624,17 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>tooltip.power.title</t>
+          <t>ui.pause.gallery</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>界面基础件样例（开发）</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>UI kit gallery (dev)</t>
         </is>
       </c>
     </row>
@@ -6642,17 +6642,17 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>tooltip.power.body</t>
+          <t>tooltip.power.title</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>供给来自核心基础供电与发电机；需求按优先级（数字小的先）分配，分不到电的建筑会停机。</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Supply comes from the core's base output and generators. Demand is served by priority (lower number first); buildings that get no power shut down.</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6660,17 +6660,17 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>tooltip.power.base_core</t>
+          <t>tooltip.power.body</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>核心基础供电</t>
+          <t>供给来自核心基础供电与发电机；需求按优先级（数字小的先）分配，分不到电的建筑会停机。</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Core base output</t>
+          <t>Supply comes from the core's base output and generators. Demand is served by priority (lower number first); buildings that get no power shut down.</t>
         </is>
       </c>
     </row>
@@ -6678,17 +6678,17 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>tooltip.power.supply_of</t>
+          <t>tooltip.power.base_core</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>{0} 供电</t>
+          <t>核心基础供电</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>{0} output</t>
+          <t>Core base output</t>
         </is>
       </c>
     </row>
@@ -6696,17 +6696,17 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>tooltip.power.demand_of</t>
+          <t>tooltip.power.supply_of</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>{0} 用电（优先级 {1}）</t>
+          <t>{0} 供电</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>{0} draw (priority {1})</t>
+          <t>{0} output</t>
         </is>
       </c>
     </row>
@@ -6714,17 +6714,17 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>tooltip.power.brownout_of</t>
+          <t>tooltip.power.demand_of</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>{0} 用电（优先级 {1}，已停机）</t>
+          <t>{0} 用电（优先级 {1}）</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>{0} draw (priority {1}, shut down)</t>
+          <t>{0} draw (priority {1})</t>
         </is>
       </c>
     </row>
@@ -6732,17 +6732,17 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>tooltip.power.surplus</t>
+          <t>tooltip.power.brownout_of</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>盈余 {0}</t>
+          <t>{0} 用电（优先级 {1}，已停机）</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Surplus {0}</t>
+          <t>{0} draw (priority {1}, shut down)</t>
         </is>
       </c>
     </row>
@@ -6750,17 +6750,17 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>tooltip.power.shortfall</t>
+          <t>tooltip.power.surplus</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>差额 {0}</t>
+          <t>盈余 {0}</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Shortfall {0}</t>
+          <t>Surplus {0}</t>
         </is>
       </c>
     </row>
@@ -6768,17 +6768,17 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>tooltip.signal.title</t>
+          <t>tooltip.power.shortfall</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>信号带宽</t>
+          <t>差额 {0}</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Signal bandwidth</t>
+          <t>Shortfall {0}</t>
         </is>
       </c>
     </row>
@@ -6786,17 +6786,17 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>tooltip.signal.body</t>
+          <t>tooltip.signal.title</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>带宽决定一次远征能带多少台机器，出征准备会按带宽检查。</t>
+          <t>信号带宽</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Bandwidth limits how many machines one expedition can take; expedition prep checks it.</t>
+          <t>Signal bandwidth</t>
         </is>
       </c>
     </row>
@@ -6804,17 +6804,17 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>tooltip.signal.base</t>
+          <t>tooltip.signal.body</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>基础带宽</t>
+          <t>带宽决定一次远征能带多少台机器，出征准备会按带宽检查。</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Base bandwidth</t>
+          <t>Bandwidth limits how many machines one expedition can take; expedition prep checks it.</t>
         </is>
       </c>
     </row>
@@ -6822,17 +6822,17 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>tooltip.signal.tower</t>
+          <t>tooltip.signal.base</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>信号塔（通电）</t>
+          <t>基础带宽</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Signal tower (powered)</t>
+          <t>Base bandwidth</t>
         </is>
       </c>
     </row>
@@ -6840,17 +6840,17 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>tooltip.signal.tower_off</t>
+          <t>tooltip.signal.tower</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>信号塔（未通电，不提供带宽）</t>
+          <t>信号塔（通电）</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Signal tower (unpowered, no bandwidth)</t>
+          <t>Signal tower (powered)</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>tooltip.signal.broadcast_off</t>
+          <t>tooltip.signal.tower_off</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>关闭主动广播</t>
+          <t>信号塔（未通电，不提供带宽）</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Broadcast turned off</t>
+          <t>Signal tower (unpowered, no bandwidth)</t>
         </is>
       </c>
     </row>
@@ -6876,17 +6876,17 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>status.working.name</t>
+          <t>tooltip.signal.broadcast_off</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>关闭主动广播</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Broadcast turned off</t>
         </is>
       </c>
     </row>
@@ -6894,17 +6894,17 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>status.idle.name</t>
+          <t>status.working.name</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>待机</t>
+          <t>工作中</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -6912,17 +6912,17 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>status.no_material.name</t>
+          <t>status.idle.name</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>缺料</t>
+          <t>待机</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>No materials</t>
+          <t>Idle</t>
         </is>
       </c>
     </row>
@@ -6930,17 +6930,17 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>status.no_power.name</t>
+          <t>status.no_material.name</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>缺电</t>
+          <t>缺料</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>No power</t>
+          <t>No materials</t>
         </is>
       </c>
     </row>
@@ -6948,17 +6948,17 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>status.no_fluid.name</t>
+          <t>status.no_power.name</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>缺流体</t>
+          <t>缺电</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>No fluid</t>
+          <t>No power</t>
         </is>
       </c>
     </row>
@@ -6966,17 +6966,17 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>status.output_blocked.name</t>
+          <t>status.no_fluid.name</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>输出堵塞</t>
+          <t>缺流体</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Output blocked</t>
+          <t>No fluid</t>
         </is>
       </c>
     </row>
@@ -6984,17 +6984,17 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>status.disabled.name</t>
+          <t>status.output_blocked.name</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>已禁用</t>
+          <t>输出堵塞</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Output blocked</t>
         </is>
       </c>
     </row>
@@ -7002,17 +7002,17 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>status.damaged.name</t>
+          <t>status.disabled.name</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>损坏</t>
+          <t>已禁用</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Damaged</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -7020,17 +7020,17 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>status.destroyed.name</t>
+          <t>status.damaged.name</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>已摧毁</t>
+          <t>损坏</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Destroyed</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -7038,17 +7038,17 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>status.upgrading.name</t>
+          <t>status.destroyed.name</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>升级中</t>
+          <t>已摧毁</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Upgrading</t>
+          <t>Destroyed</t>
         </is>
       </c>
     </row>
@@ -7056,17 +7056,17 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>fmt.wan</t>
+          <t>status.upgrading.name</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>{0}万</t>
+          <t>升级中</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Upgrading</t>
         </is>
       </c>
     </row>
@@ -7074,17 +7074,17 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>fmt.thousand</t>
+          <t>fmt.wan</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
+          <t>{0}万</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
           <t>{0}</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>{0}k</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>fmt.million</t>
+          <t>fmt.thousand</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>{0}M</t>
+          <t>{0}k</t>
         </is>
       </c>
     </row>
@@ -7110,17 +7110,17 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>fmt.per_minute</t>
+          <t>fmt.million</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>{0}/分钟</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>{0}/min</t>
+          <t>{0}M</t>
         </is>
       </c>
     </row>
@@ -7128,17 +7128,17 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>fmt.percent</t>
+          <t>fmt.per_minute</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>{0}%</t>
+          <t>{0}/分钟</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>{0}%</t>
+          <t>{0}/min</t>
         </is>
       </c>
     </row>
@@ -7146,17 +7146,17 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>fmt.seconds</t>
+          <t>fmt.percent</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>{0} 秒</t>
+          <t>{0}%</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>{0}%</t>
         </is>
       </c>
     </row>
@@ -7164,17 +7164,17 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>ui.gallery.title</t>
+          <t>fmt.seconds</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>界面基础件样例</t>
+          <t>{0} 秒</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>UI kit gallery</t>
+          <t>{0}s</t>
         </is>
       </c>
     </row>
@@ -7182,17 +7182,17 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ui.gallery.section_notify</t>
+          <t>ui.gallery.title</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>通知中心</t>
+          <t>界面基础件样例</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Notification center</t>
+          <t>UI kit gallery</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7200,17 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ui.gallery.section_confirm</t>
+          <t>ui.gallery.section_notify</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>确认框</t>
+          <t>通知中心</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Confirm dialog</t>
+          <t>Notification center</t>
         </is>
       </c>
     </row>
@@ -7218,17 +7218,17 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ui.gallery.section_tooltip</t>
+          <t>ui.gallery.section_confirm</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>悬停提示</t>
+          <t>确认框</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>Confirm dialog</t>
         </is>
       </c>
     </row>
@@ -7236,17 +7236,17 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ui.gallery.section_menu</t>
+          <t>ui.gallery.section_tooltip</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>右键菜单</t>
+          <t>悬停提示</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Context menu</t>
+          <t>Tooltip</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ui.gallery.section_drag</t>
+          <t>ui.gallery.section_menu</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>拖放</t>
+          <t>右键菜单</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Drag and drop</t>
+          <t>Context menu</t>
         </is>
       </c>
     </row>
@@ -7272,17 +7272,17 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ui.gallery.section_search</t>
+          <t>ui.gallery.section_drag</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>搜索框</t>
+          <t>拖放</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Search box</t>
+          <t>Drag and drop</t>
         </is>
       </c>
     </row>
@@ -7290,17 +7290,17 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>ui.gallery.section_tabs</t>
+          <t>ui.gallery.section_search</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>标签页</t>
+          <t>搜索框</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Search box</t>
         </is>
       </c>
     </row>
@@ -7308,17 +7308,17 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>ui.gallery.section_list</t>
+          <t>ui.gallery.section_tabs</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>虚拟化列表</t>
+          <t>标签页</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Virtualised list</t>
+          <t>Tabs</t>
         </is>
       </c>
     </row>
@@ -7326,17 +7326,17 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>ui.gallery.section_chart</t>
+          <t>ui.gallery.section_list</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>图表</t>
+          <t>虚拟化列表</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Virtualised list</t>
         </is>
       </c>
     </row>
@@ -7344,17 +7344,17 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>ui.gallery.section_hint</t>
+          <t>ui.gallery.section_chart</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>快捷键提示</t>
+          <t>图表</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Shortcut hints</t>
+          <t>Charts</t>
         </is>
       </c>
     </row>
@@ -7362,17 +7362,17 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>ui.gallery.section_progress</t>
+          <t>ui.gallery.section_hint</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>进度条</t>
+          <t>快捷键提示</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Progress bars</t>
+          <t>Shortcut hints</t>
         </is>
       </c>
     </row>
@@ -7380,17 +7380,17 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>ui.gallery.section_status</t>
+          <t>ui.gallery.section_progress</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>状态图标</t>
+          <t>进度条</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Status icons</t>
+          <t>Progress bars</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7398,17 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>ui.gallery.post_urgent</t>
+          <t>ui.gallery.section_status</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>发一条紧急</t>
+          <t>状态图标</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Post urgent</t>
+          <t>Status icons</t>
         </is>
       </c>
     </row>
@@ -7416,17 +7416,17 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>ui.gallery.post_warning</t>
+          <t>ui.gallery.post_urgent</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>发一条警告</t>
+          <t>发一条紧急</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Post warning</t>
+          <t>Post urgent</t>
         </is>
       </c>
     </row>
@@ -7434,17 +7434,17 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ui.gallery.post_info</t>
+          <t>ui.gallery.post_warning</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>发一条信息</t>
+          <t>发一条警告</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Post info</t>
+          <t>Post warning</t>
         </is>
       </c>
     </row>
@@ -7452,17 +7452,17 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>ui.gallery.post_burst</t>
+          <t>ui.gallery.post_info</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>1 秒内发 50 条</t>
+          <t>发一条信息</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Post 50 in 1 s</t>
+          <t>Post info</t>
         </is>
       </c>
     </row>
@@ -7470,17 +7470,17 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>ui.gallery.open_confirm</t>
+          <t>ui.gallery.post_burst</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>打开确认框</t>
+          <t>1 秒内发 50 条</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Open confirm</t>
+          <t>Post 50 in 1 s</t>
         </is>
       </c>
     </row>
@@ -7488,17 +7488,17 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>ui.gallery.confirm_title</t>
+          <t>ui.gallery.open_confirm</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>拆除建筑</t>
+          <t>打开确认框</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Demolish building</t>
+          <t>Open confirm</t>
         </is>
       </c>
     </row>
@@ -7506,17 +7506,17 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ui.gallery.confirm_line</t>
+          <t>ui.gallery.confirm_title</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>未装载的战利品 ×{0}</t>
+          <t>拆除建筑</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Unloaded loot ×{0}</t>
+          <t>Demolish building</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7524,17 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>ui.gallery.tooltip_target</t>
+          <t>ui.gallery.confirm_line</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>悬停查看产量构成</t>
+          <t>未装载的战利品 ×{0}</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Hover for output breakdown</t>
+          <t>Unloaded loot ×{0}</t>
         </is>
       </c>
     </row>
@@ -7542,17 +7542,17 @@
       <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
-          <t>ui.gallery.tooltip_title</t>
+          <t>ui.gallery.tooltip_target</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>装配站产量</t>
+          <t>悬停查看产量构成</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Assembly output</t>
+          <t>Hover for output breakdown</t>
         </is>
       </c>
     </row>
@@ -7560,17 +7560,17 @@
       <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ui.gallery.tooltip_body</t>
+          <t>ui.gallery.tooltip_title</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>每分钟产出的机器零件数。</t>
+          <t>装配站产量</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Machine parts produced per minute.</t>
+          <t>Assembly output</t>
         </is>
       </c>
     </row>
@@ -7578,17 +7578,17 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>ui.gallery.source_base</t>
+          <t>ui.gallery.tooltip_body</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>基础产量</t>
+          <t>每分钟产出的机器零件数。</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Base output</t>
+          <t>Machine parts produced per minute.</t>
         </is>
       </c>
     </row>
@@ -7596,17 +7596,17 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ui.gallery.source_power</t>
+          <t>ui.gallery.source_base</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>电力不足</t>
+          <t>基础产量</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Power shortage</t>
+          <t>Base output</t>
         </is>
       </c>
     </row>
@@ -7614,17 +7614,17 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>ui.gallery.source_research</t>
+          <t>ui.gallery.source_power</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>研究加成</t>
+          <t>电力不足</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Research bonus</t>
+          <t>Power shortage</t>
         </is>
       </c>
     </row>
@@ -7632,17 +7632,17 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_target</t>
+          <t>ui.gallery.source_research</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>在这里点右键</t>
+          <t>研究加成</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Right-click here</t>
+          <t>Research bonus</t>
         </is>
       </c>
     </row>
@@ -7650,17 +7650,17 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_inspect</t>
+          <t>ui.gallery.menu_target</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>查看</t>
+          <t>在这里点右键</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Right-click here</t>
         </is>
       </c>
     </row>
@@ -7668,17 +7668,17 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_rename</t>
+          <t>ui.gallery.menu_inspect</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>改名</t>
+          <t>查看</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Inspect</t>
         </is>
       </c>
     </row>
@@ -7686,17 +7686,17 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_demolish</t>
+          <t>ui.gallery.menu_rename</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>拆除</t>
+          <t>改名</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Demolish</t>
+          <t>Rename</t>
         </is>
       </c>
     </row>
@@ -7704,17 +7704,17 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_demolish_reason</t>
+          <t>ui.gallery.menu_demolish</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>核心不能拆除</t>
+          <t>拆除</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>The core cannot be demolished</t>
+          <t>Demolish</t>
         </is>
       </c>
     </row>
@@ -7722,17 +7722,17 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_result</t>
+          <t>ui.gallery.menu_demolish_reason</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>选择了：{0}</t>
+          <t>核心不能拆除</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Chose: {0}</t>
+          <t>The core cannot be demolished</t>
         </is>
       </c>
     </row>
@@ -7740,17 +7740,17 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_source</t>
+          <t>ui.gallery.menu_result</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>拖动芯片</t>
+          <t>选择了：{0}</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Drag chip</t>
+          <t>Chose: {0}</t>
         </is>
       </c>
     </row>
@@ -7758,17 +7758,17 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_slot</t>
+          <t>ui.gallery.drag_source</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>槽位 {0}</t>
+          <t>拖动芯片</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Slot {0}</t>
+          <t>Drag chip</t>
         </is>
       </c>
     </row>
@@ -7776,17 +7776,17 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_slot_locked</t>
+          <t>ui.gallery.drag_slot</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>锁定槽位</t>
+          <t>槽位 {0}</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Locked slot</t>
+          <t>Slot {0}</t>
         </is>
       </c>
     </row>
@@ -7794,17 +7794,17 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_locked_reason</t>
+          <t>ui.gallery.drag_slot_locked</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>槽位锁定，不能放入</t>
+          <t>锁定槽位</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>The slot is locked</t>
+          <t>Locked slot</t>
         </is>
       </c>
     </row>
@@ -7812,17 +7812,17 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_result</t>
+          <t>ui.gallery.drag_locked_reason</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>放入了 {0}</t>
+          <t>槽位锁定，不能放入</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Dropped into {0}</t>
+          <t>The slot is locked</t>
         </is>
       </c>
     </row>
@@ -7830,17 +7830,17 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_a</t>
+          <t>ui.gallery.drag_result</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>产量</t>
+          <t>放入了 {0}</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Dropped into {0}</t>
         </is>
       </c>
     </row>
@@ -7848,17 +7848,17 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_b</t>
+          <t>ui.gallery.tab_a</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>产量</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Output</t>
         </is>
       </c>
     </row>
@@ -7866,17 +7866,17 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_c</t>
+          <t>ui.gallery.tab_b</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Use</t>
         </is>
       </c>
     </row>
@@ -7884,17 +7884,17 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_body</t>
+          <t>ui.gallery.tab_c</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>当前标签：{0}</t>
+          <t>库存</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Current tab: {0}</t>
+          <t>Stock</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>ui.gallery.list_row</t>
+          <t>ui.gallery.tab_body</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>条目 {0}</t>
+          <t>当前标签：{0}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Entry {0}</t>
+          <t>Current tab: {0}</t>
         </is>
       </c>
     </row>
@@ -7920,17 +7920,17 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>ui.gallery.chart_line</t>
+          <t>ui.gallery.list_row</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>近 60 秒产量</t>
+          <t>条目 {0}</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Output, last 60 s</t>
+          <t>Entry {0}</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>ui.gallery.chart_bar</t>
+          <t>ui.gallery.chart_line</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>各类消耗</t>
+          <t>近 60 秒产量</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Use by type</t>
+          <t>Output, last 60 s</t>
         </is>
       </c>
     </row>
@@ -7956,17 +7956,17 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ui.gallery.progress_label</t>
+          <t>ui.gallery.chart_bar</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>研究进度</t>
+          <t>各类消耗</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Research progress</t>
+          <t>Use by type</t>
         </is>
       </c>
     </row>
@@ -7974,17 +7974,17 @@
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>ui.gallery.progress_step</t>
+          <t>ui.gallery.progress_label</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>推进 10%</t>
+          <t>研究进度</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Advance 10%</t>
+          <t>Research progress</t>
         </is>
       </c>
     </row>
@@ -7992,17 +7992,17 @@
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ui.gallery.progress_block</t>
+          <t>ui.gallery.progress_step</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>切换阻塞</t>
+          <t>推进 10%</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Toggle blocked</t>
+          <t>Advance 10%</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
-          <t>ui.gallery.colorblind</t>
+          <t>ui.gallery.progress_block</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>色盲预览</t>
+          <t>切换阻塞</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Colour-blind preview</t>
+          <t>Toggle blocked</t>
         </is>
       </c>
     </row>
@@ -8028,17 +8028,17 @@
       <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
-          <t>building.core.desc</t>
+          <t>ui.gallery.colorblind</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>战役的根基。核心被毁即失败；自带基础供电与应急缓存。</t>
+          <t>色盲预览</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>The heart of the campaign. If it falls, the campaign is lost; provides base power and an emergency cache.</t>
+          <t>Colour-blind preview</t>
         </is>
       </c>
     </row>
@@ -8046,17 +8046,17 @@
       <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
-          <t>building.generator.desc</t>
+          <t>building.core.desc</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>运转后提供额外电力。可以建造多座。</t>
+          <t>战役的根基。核心被毁即失败；自带基础供电与应急缓存。</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Provides extra power while running. You can build several.</t>
+          <t>The heart of the campaign. If it falls, the campaign is lost; provides base power and an emergency cache.</t>
         </is>
       </c>
     </row>
@@ -8064,17 +8064,17 @@
       <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
-          <t>building.warehouse.desc</t>
+          <t>building.generator.desc</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>修好后扩充库存容量，并接收远征卸货。</t>
+          <t>运转后提供额外电力。可以建造多座。</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Once repaired, adds storage capacity and receives expedition cargo.</t>
+          <t>Provides extra power while running. You can build several.</t>
         </is>
       </c>
     </row>
@@ -8082,17 +8082,17 @@
       <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
-          <t>building.signal_tower.desc</t>
+          <t>building.warehouse.desc</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>修好并通电后扩大信号带宽，开放破碎都市远征。</t>
+          <t>修好后扩充库存容量，并接收远征卸货。</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>When repaired and powered, raises signal bandwidth and opens expeditions to the Fractured City.</t>
+          <t>Once repaired, adds storage capacity and receives expedition cargo.</t>
         </is>
       </c>
     </row>
@@ -8100,17 +8100,17 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
-          <t>building.assembly_station.desc</t>
+          <t>building.signal_tower.desc</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>生产与改造机器。</t>
+          <t>修好并通电后扩大信号带宽，开放破碎都市远征。</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Produces and refits machines.</t>
+          <t>When repaired and powered, raises signal bandwidth and opens expeditions to the Fractured City.</t>
         </is>
       </c>
     </row>
@@ -8118,17 +8118,17 @@
       <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
-          <t>building.analysis_bench.desc</t>
+          <t>building.assembly_station.desc</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>解析带回的技术模块，解锁新内容。</t>
+          <t>生产与改造机器。</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Analyzes recovered tech modules to unlock new content.</t>
+          <t>Produces and refits machines.</t>
         </is>
       </c>
     </row>
@@ -8136,17 +8136,17 @@
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
-          <t>building.repair_bay.desc</t>
+          <t>building.analysis_bench.desc</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>维修机的工作基点。</t>
+          <t>解析带回的技术模块，解锁新内容。</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Home base for repair machines.</t>
+          <t>Analyzes recovered tech modules to unlock new content.</t>
         </is>
       </c>
     </row>
@@ -8154,17 +8154,17 @@
       <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
-          <t>building.beacon.desc</t>
+          <t>building.repair_bay.desc</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>返航信标。建成、通电并启动后，战役迎来终局。</t>
+          <t>维修机的工作基点。</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>The homing beacon. Build, power and launch it to reach the campaign's finale.</t>
+          <t>Home base for repair machines.</t>
         </is>
       </c>
     </row>
@@ -8172,17 +8172,17 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>grid.terrain.buildable.name</t>
+          <t>building.beacon.desc</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>空地</t>
+          <t>返航信标。建成、通电并启动后，战役迎来终局。</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Open ground</t>
+          <t>The homing beacon. Build, power and launch it to reach the campaign's finale.</t>
         </is>
       </c>
     </row>
@@ -8190,17 +8190,17 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>grid.terrain.water.name</t>
+          <t>grid.terrain.buildable.name</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>水源</t>
+          <t>空地</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Open ground</t>
         </is>
       </c>
     </row>
@@ -8208,17 +8208,17 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>grid.terrain.oil.name</t>
+          <t>grid.terrain.water.name</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>油井</t>
+          <t>水源</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Oil well</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -8226,17 +8226,17 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
-          <t>grid.terrain.ore_metal.name</t>
+          <t>grid.terrain.oil.name</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>金属矿脉</t>
+          <t>油井</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Metal vein</t>
+          <t>Oil well</t>
         </is>
       </c>
     </row>
@@ -8244,17 +8244,17 @@
       <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
-          <t>grid.terrain.ore_rare.name</t>
+          <t>grid.terrain.ore_metal.name</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>稀土矿脉</t>
+          <t>金属矿脉</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Rare-earth vein</t>
+          <t>Metal vein</t>
         </is>
       </c>
     </row>
@@ -8262,17 +8262,17 @@
       <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
-          <t>grid.terrain.ruin.name</t>
+          <t>grid.terrain.ore_rare.name</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>废墟</t>
+          <t>稀土矿脉</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Ruins</t>
+          <t>Rare-earth vein</t>
         </is>
       </c>
     </row>
@@ -8280,17 +8280,17 @@
       <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
-          <t>grid.terrain.cliff.name</t>
+          <t>grid.terrain.ruin.name</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>悬崖</t>
+          <t>废墟</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Cliff</t>
+          <t>Ruins</t>
         </is>
       </c>
     </row>
@@ -8298,17 +8298,17 @@
       <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>grid.dir.n</t>
+          <t>grid.terrain.cliff.name</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>北</t>
+          <t>悬崖</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Cliff</t>
         </is>
       </c>
     </row>
@@ -8316,17 +8316,17 @@
       <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>grid.dir.e</t>
+          <t>grid.dir.n</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>东</t>
+          <t>北</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -8334,17 +8334,17 @@
       <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
-          <t>grid.dir.s</t>
+          <t>grid.dir.e</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>南</t>
+          <t>东</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -8352,17 +8352,17 @@
       <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
-          <t>grid.dir.w</t>
+          <t>grid.dir.s</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>西</t>
+          <t>南</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -8370,17 +8370,17 @@
       <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
-          <t>grid.port.in</t>
+          <t>grid.dir.w</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>输入</t>
+          <t>西</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -8388,17 +8388,17 @@
       <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
-          <t>grid.port.out</t>
+          <t>grid.port.in</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>输出</t>
+          <t>输入</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input</t>
         </is>
       </c>
     </row>
@@ -8406,17 +8406,17 @@
       <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
-          <t>grid.port.entry</t>
+          <t>grid.port.out</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>{0}（朝{1}）</t>
+          <t>输出</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>{0} (facing {1})</t>
+          <t>Output</t>
         </is>
       </c>
     </row>
@@ -8424,17 +8424,17 @@
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
-          <t>grid.reason.occupied</t>
+          <t>grid.port.entry</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>已被“{0}”占用</t>
+          <t>{0}（朝{1}）</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Occupied by {0}</t>
+          <t>{0} (facing {1})</t>
         </is>
       </c>
     </row>
@@ -8442,17 +8442,17 @@
       <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
-          <t>grid.reason.occupied_belt</t>
+          <t>grid.reason.occupied</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>已被传送带占用</t>
+          <t>已被“{0}”占用</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Occupied by a belt</t>
+          <t>Occupied by {0}</t>
         </is>
       </c>
     </row>
@@ -8460,17 +8460,17 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>grid.reason.occupied_pipe</t>
+          <t>grid.reason.occupied_belt</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>已被管线占用</t>
+          <t>已被传送带占用</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Occupied by a pipe</t>
+          <t>Occupied by a belt</t>
         </is>
       </c>
     </row>
@@ -8478,17 +8478,17 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>grid.reason.obstacle</t>
+          <t>grid.reason.occupied_pipe</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>被“{0}”挡住</t>
+          <t>已被管线占用</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Blocked by {0}</t>
+          <t>Occupied by a pipe</t>
         </is>
       </c>
     </row>
@@ -8496,17 +8496,17 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>grid.obstacle.wreckage</t>
+          <t>grid.reason.obstacle</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>残骸</t>
+          <t>被“{0}”挡住</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Wreckage</t>
+          <t>Blocked by {0}</t>
         </is>
       </c>
     </row>
@@ -8514,17 +8514,17 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>grid.obstacle.target</t>
+          <t>grid.obstacle.wreckage</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>残骸靶</t>
+          <t>残骸</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Target wreck</t>
+          <t>Wreckage</t>
         </is>
       </c>
     </row>
@@ -8532,17 +8532,17 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>grid.obstacle.exit</t>
+          <t>grid.obstacle.target</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>出口通道</t>
+          <t>残骸靶</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Exit lane</t>
+          <t>Target wreck</t>
         </is>
       </c>
     </row>
@@ -8550,17 +8550,17 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>grid.reason.terrain</t>
+          <t>grid.obstacle.exit</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>地形不符：{0}上不能建造</t>
+          <t>出口通道</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Unsuitable terrain: cannot build on {0}</t>
+          <t>Exit lane</t>
         </is>
       </c>
     </row>
@@ -8568,17 +8568,17 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>grid.reason.needs_terrain</t>
+          <t>grid.reason.terrain</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>需要放在{0}上</t>
+          <t>地形不符：{0}上不能建造</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Must be placed on {0}</t>
+          <t>Unsuitable terrain: cannot build on {0}</t>
         </is>
       </c>
     </row>
@@ -8586,17 +8586,17 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>grid.reason.pollution</t>
+          <t>grid.reason.needs_terrain</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>污染过重（{0} 级），需要先净化</t>
+          <t>需要放在{0}上</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Pollution too high (level {0}); purify it first</t>
+          <t>Must be placed on {0}</t>
         </is>
       </c>
     </row>
@@ -8604,17 +8604,17 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>grid.reason.fog</t>
+          <t>grid.reason.pollution</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>超出已探索区域</t>
+          <t>污染过重（{0} 级），需要先净化</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Outside the explored area</t>
+          <t>Pollution too high (level {0}); purify it first</t>
         </is>
       </c>
     </row>
@@ -8622,17 +8622,17 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>grid.reason.core_reserve</t>
+          <t>grid.reason.fog</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>归还核心周围 {0} 格是通道，不能建造</t>
+          <t>超出已探索区域</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>The {0} tiles around the Reclamation Core are a passage and cannot be built on</t>
+          <t>Outside the explored area</t>
         </is>
       </c>
     </row>
@@ -8640,17 +8640,17 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>grid.reason.max_count</t>
+          <t>grid.reason.core_reserve</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>已达到数量上限（{0} 座）</t>
+          <t>归还核心周围 {0} 格是通道，不能建造</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Limit reached ({0})</t>
+          <t>The {0} tiles around the Reclamation Core are a passage and cannot be built on</t>
         </is>
       </c>
     </row>
@@ -8658,17 +8658,17 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>grid.reason.locked</t>
+          <t>grid.reason.max_count</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>尚未解锁：{0}</t>
+          <t>已达到数量上限（{0} 座）</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Locked: {0}</t>
+          <t>Limit reached ({0})</t>
         </is>
       </c>
     </row>
@@ -8676,17 +8676,17 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>grid.reason.not_placeable</t>
+          <t>grid.reason.locked</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>这种建筑不能手动放置</t>
+          <t>尚未解锁：{0}</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>This building cannot be placed manually</t>
+          <t>Locked: {0}</t>
         </is>
       </c>
     </row>
@@ -8694,17 +8694,17 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>grid.reason.unknown_type</t>
+          <t>grid.reason.not_placeable</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>未知的建筑类型</t>
+          <t>这种建筑不能手动放置</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Unknown building type</t>
+          <t>This building cannot be placed manually</t>
         </is>
       </c>
     </row>
@@ -8712,17 +8712,17 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>grid.reason.insufficient_scrap</t>
+          <t>grid.reason.unknown_type</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>废料不足：需要 {0}，现有 {1}</t>
+          <t>未知的建筑类型</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Not enough scrap: need {0}, have {1}</t>
+          <t>Unknown building type</t>
         </is>
       </c>
     </row>
@@ -8730,17 +8730,17 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>grid.reason.no_building</t>
+          <t>grid.reason.insufficient_scrap</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>这里没有建筑</t>
+          <t>废料不足：需要 {0}，现有 {1}</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>There is no building here</t>
+          <t>Not enough scrap: need {0}, have {1}</t>
         </is>
       </c>
     </row>
@@ -8748,17 +8748,17 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>grid.reason.cannot_demolish_core</t>
+          <t>grid.reason.no_building</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>归还核心不能拆除</t>
+          <t>这里没有建筑</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>The Reclamation Core cannot be demolished</t>
+          <t>There is no building here</t>
         </is>
       </c>
     </row>
@@ -8766,17 +8766,17 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>grid.reason.demolish_damaged</t>
+          <t>grid.reason.cannot_demolish_core</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>受损的建筑不能拆除，请先修复</t>
+          <t>归还核心不能拆除</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Damaged buildings cannot be demolished; repair it first</t>
+          <t>The Reclamation Core cannot be demolished</t>
         </is>
       </c>
     </row>
@@ -8784,17 +8784,17 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>grid.reason.busy</t>
+          <t>grid.reason.demolish_damaged</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>这座建筑正在施工或维修，完成后再操作</t>
+          <t>受损的建筑不能拆除，请先修复</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>This building is under construction or repair; try again when it is done</t>
+          <t>Damaged buildings cannot be demolished; repair it first</t>
         </is>
       </c>
     </row>
@@ -8802,17 +8802,17 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>grid.reason.cannot_rotate_core</t>
+          <t>grid.reason.busy</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>归还核心不能旋转</t>
+          <t>这座建筑正在施工或维修，完成后再操作</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>The Reclamation Core cannot be rotated</t>
+          <t>This building is under construction or repair; try again when it is done</t>
         </is>
       </c>
     </row>
@@ -8820,17 +8820,17 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>grid.reason.not_rebuildable</t>
+          <t>grid.reason.cannot_rotate_core</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>这座建筑无法重建，不能拆除</t>
+          <t>归还核心不能旋转</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>This building cannot be rebuilt, so it cannot be demolished</t>
+          <t>The Reclamation Core cannot be rotated</t>
         </is>
       </c>
     </row>
@@ -8838,17 +8838,17 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>grid.reason.no_region</t>
+          <t>grid.reason.not_rebuildable</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>只有在家园里才能建造</t>
+          <t>这座建筑无法重建，不能拆除</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>You can only build at home</t>
+          <t>This building cannot be rebuilt, so it cannot be demolished</t>
         </is>
       </c>
     </row>
@@ -8856,17 +8856,17 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>grid.reason.no_region</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>开局即可建造</t>
+          <t>只有在家园里才能建造</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Available from the start</t>
+          <t>You can only build at home</t>
         </is>
       </c>
     </row>
@@ -8874,17 +8874,17 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>grid.unlock.beacon</t>
+          <t>grid.unlock.always</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>摧毁铸造前哨主核心并带回核心数据后解锁</t>
+          <t>开局即可建造</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Unlocked after destroying the Foundry Outpost main core and bringing back its data</t>
+          <t>Available from the start</t>
         </is>
       </c>
     </row>
@@ -8892,17 +8892,17 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>ui.build.title</t>
+          <t>grid.unlock.beacon</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>建造</t>
+          <t>摧毁铸造前哨主核心并带回核心数据后解锁</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Unlocked after destroying the Foundry Outpost main core and bringing back its data</t>
         </is>
       </c>
     </row>
@@ -8910,17 +8910,17 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>ui.build.entry</t>
+          <t>ui.build.title</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>建造（{0}）</t>
+          <t>建造</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Build ({0})</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -8928,17 +8928,17 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>ui.build.demolish</t>
+          <t>ui.build.entry</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>拆除模式（{0}）</t>
+          <t>建造（{0}）</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Demolish ({0})</t>
+          <t>Build ({0})</t>
         </is>
       </c>
     </row>
@@ -8946,17 +8946,17 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>ui.build.rotate</t>
+          <t>ui.build.demolish</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>旋转（{0}）</t>
+          <t>拆除模式（{0}）</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Rotate ({0})</t>
+          <t>Demolish ({0})</t>
         </is>
       </c>
     </row>
@@ -8964,17 +8964,17 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>ui.build.exit</t>
+          <t>ui.build.rotate</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>旋转（{0}）</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Rotate ({0})</t>
         </is>
       </c>
     </row>
@@ -8982,17 +8982,17 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>ui.build.empty</t>
+          <t>ui.build.exit</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>当前没有可以建造的建筑</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Nothing is available to build yet</t>
+          <t>Exit</t>
         </is>
       </c>
     </row>
@@ -9000,17 +9000,17 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>ui.build.cost</t>
+          <t>ui.build.empty</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>{0} 废料 · {1} 秒</t>
+          <t>当前没有可以建造的建筑</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>{0} scrap · {1}s</t>
+          <t>Nothing is available to build yet</t>
         </is>
       </c>
     </row>
@@ -9018,17 +9018,17 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>ui.build.count_limited</t>
+          <t>ui.build.cost</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>已有 {0}/{1}</t>
+          <t>{0} 废料 · {1} 秒</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Built {0}/{1}</t>
+          <t>{0} scrap · {1}s</t>
         </is>
       </c>
     </row>
@@ -9036,17 +9036,17 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>ui.build.count_unlimited</t>
+          <t>ui.build.count_limited</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>已有 {0}</t>
+          <t>已有 {0}/{1}</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Built {0}</t>
+          <t>Built {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -9054,17 +9054,17 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>ui.build.hint_idle</t>
+          <t>ui.build.count_unlimited</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>选择要建造的建筑。指着已有建筑按 {0} 旋转，按 {1} 进入拆除模式，Esc 退出。</t>
+          <t>已有 {0}</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Pick a building. Point at a building and press {0} to rotate it, {1} for demolish mode, Esc to exit.</t>
+          <t>Built {0}</t>
         </is>
       </c>
     </row>
@@ -9072,17 +9072,17 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>ui.build.hint_place</t>
+          <t>ui.build.hint_idle</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>左键放置 · {0} 旋转 · 右键取消 · Esc 退出</t>
+          <t>选择要建造的建筑。指着已有建筑按 {0} 旋转，按 {1} 进入拆除模式，Esc 退出。</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Left-click to place · {0} rotate · Right-click cancel · Esc exit</t>
+          <t>Pick a building. Point at a building and press {0} to rotate it, {1} for demolish mode, Esc to exit.</t>
         </is>
       </c>
     </row>
@@ -9090,17 +9090,17 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>ui.build.hint_demolish</t>
+          <t>ui.build.hint_place</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>左键标记拆除，再点一次取消标记 · 右键返回 · Esc 退出</t>
+          <t>左键放置 · {0} 旋转 · 右键取消 · Esc 退出</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Left-click to mark for demolition, again to unmark · Right-click back · Esc exit</t>
+          <t>Left-click to place · {0} rotate · Right-click cancel · Esc exit</t>
         </is>
       </c>
     </row>
@@ -9108,17 +9108,17 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>ui.build.valid</t>
+          <t>ui.build.hint_demolish</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>可以放置：{0}，朝{1}</t>
+          <t>左键标记拆除，再点一次取消标记 · 右键返回 · Esc 退出</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Can place: {0}, facing {1}</t>
+          <t>Left-click to mark for demolition, again to unmark · Right-click back · Esc exit</t>
         </is>
       </c>
     </row>
@@ -9126,17 +9126,17 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>ui.build.invalid</t>
+          <t>ui.build.valid</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>不能放置：{0}</t>
+          <t>可以放置：{0}，朝{1}</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Cannot place: {0}</t>
+          <t>Can place: {0}, facing {1}</t>
         </is>
       </c>
     </row>
@@ -9144,17 +9144,17 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>ui.build.invalid_rotate</t>
+          <t>ui.build.invalid</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>不能旋转：{0}</t>
+          <t>不能放置：{0}</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Cannot rotate: {0}</t>
+          <t>Cannot place: {0}</t>
         </is>
       </c>
     </row>
@@ -9162,17 +9162,17 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>ui.build.hover_building</t>
+          <t>ui.build.invalid_rotate</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>{0}（朝{1}）</t>
+          <t>不能旋转：{0}</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>{0} (facing {1})</t>
+          <t>Cannot rotate: {0}</t>
         </is>
       </c>
     </row>
@@ -9180,17 +9180,17 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>ui.build.ports</t>
+          <t>ui.build.hover_building</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>端口：{0}</t>
+          <t>{0}（朝{1}）</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Ports: {0}</t>
+          <t>{0} (facing {1})</t>
         </is>
       </c>
     </row>
@@ -9198,17 +9198,17 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>ui.build.no_ports</t>
+          <t>ui.build.ports</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>端口：无</t>
+          <t>端口：{0}</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Ports: none</t>
+          <t>Ports: {0}</t>
         </is>
       </c>
     </row>
@@ -9216,17 +9216,17 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>ui.build.placed</t>
+          <t>ui.build.no_ports</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>已规划：{0}，等待机器施工</t>
+          <t>端口：无</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Planned: {0}; waiting for a machine to build it</t>
+          <t>Ports: none</t>
         </is>
       </c>
     </row>
@@ -9234,17 +9234,17 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>ui.build.demolish_marked</t>
+          <t>ui.build.placed</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>已标记拆除：{0}</t>
+          <t>已规划：{0}，等待机器施工</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Marked for demolition: {0}</t>
+          <t>Planned: {0}; waiting for a machine to build it</t>
         </is>
       </c>
     </row>
@@ -9252,17 +9252,17 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>ui.build.demolish_unmarked</t>
+          <t>ui.build.demolish_marked</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>已取消拆除：{0}</t>
+          <t>已标记拆除：{0}</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Demolition cancelled: {0}</t>
+          <t>Marked for demolition: {0}</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>ui.build.plan_cancelled</t>
+          <t>ui.build.demolish_unmarked</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>已取消规划：{0}，废料已全额退回</t>
+          <t>已取消拆除：{0}</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Plan cancelled: {0}; scrap fully refunded</t>
+          <t>Demolition cancelled: {0}</t>
         </is>
       </c>
     </row>
@@ -9288,17 +9288,17 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>ui.build.rotated</t>
+          <t>ui.build.plan_cancelled</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>已旋转：{0}，现在朝{1}</t>
+          <t>已取消规划：{0}，废料已全额退回</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Rotated: {0}, now facing {1}</t>
+          <t>Plan cancelled: {0}; scrap fully refunded</t>
         </is>
       </c>
     </row>
@@ -9306,17 +9306,17 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>ui.build.confirm_title</t>
+          <t>ui.build.rotated</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>拆除{0}？</t>
+          <t>已旋转：{0}，现在朝{1}</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Demolish {0}?</t>
+          <t>Rotated: {0}, now facing {1}</t>
         </is>
       </c>
     </row>
@@ -9324,17 +9324,17 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>ui.build.confirm_refund</t>
+          <t>ui.build.confirm_title</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>返还 {0} 废料（实际投入的一半）</t>
+          <t>拆除{0}？</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Refunds {0} scrap (half of what was invested)</t>
+          <t>Demolish {0}?</t>
         </is>
       </c>
     </row>
@@ -9342,17 +9342,17 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>ui.build.confirm_critical</t>
+          <t>ui.build.confirm_refund</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>这是关键建筑，拆除后相关功能会停用</t>
+          <t>返还 {0} 废料（实际投入的一半）</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>This is a key building; its functions stop once demolished</t>
+          <t>Refunds {0} scrap (half of what was invested)</t>
         </is>
       </c>
     </row>
@@ -9360,17 +9360,17 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>ui.build.confirm_ok</t>
+          <t>ui.build.confirm_critical</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>拆除</t>
+          <t>这是关键建筑，拆除后相关功能会停用</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Demolish</t>
+          <t>This is a key building; its functions stop once demolished</t>
         </is>
       </c>
     </row>
@@ -9378,17 +9378,17 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>ui.build.confirm_cancel</t>
+          <t>ui.build.confirm_ok</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>拆除</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Demolish</t>
         </is>
       </c>
     </row>
@@ -9396,17 +9396,17 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ui.build.locked_tip</t>
+          <t>ui.build.confirm_cancel</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>尚未解锁：{0}</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Locked: {0}</t>
+          <t>Keep</t>
         </is>
       </c>
     </row>
@@ -9414,17 +9414,17 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ui.build.placeholder_note</t>
+          <t>ui.build.locked_tip</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>建筑外形是占位方块（美术待替换）</t>
+          <t>尚未解锁：{0}</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Building shapes are placeholder blocks (art pending)</t>
+          <t>Locked: {0}</t>
         </is>
       </c>
     </row>
@@ -9432,17 +9432,17 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>world.surface.earth.name</t>
+          <t>ui.build.placeholder_note</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>建筑外形是占位方块（美术待替换）</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Building shapes are placeholder blocks (art pending)</t>
         </is>
       </c>
     </row>
@@ -9450,17 +9450,17 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>world.surface.relay_hall.name</t>
+          <t>world.surface.earth.name</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>地下中继大厅</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Underground Relay Hall</t>
+          <t>Earth</t>
         </is>
       </c>
     </row>
@@ -9468,17 +9468,17 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>world.surface.data_center.name</t>
+          <t>world.surface.relay_hall.name</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>数据中心</t>
+          <t>地下中继大厅</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Data Center</t>
+          <t>Underground Relay Hall</t>
         </is>
       </c>
     </row>
@@ -9486,17 +9486,17 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>world.territory.silent.name</t>
+          <t>world.surface.data_center.name</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>静默·破碎都市</t>
+          <t>数据中心</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Silent · Fractured City</t>
+          <t>Data Center</t>
         </is>
       </c>
     </row>
@@ -9504,17 +9504,17 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>world.territory.foundry.name</t>
+          <t>world.territory.silent.name</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>铸造·铸造前哨</t>
+          <t>静默·破碎都市</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Foundry · Foundry Outpost</t>
+          <t>Silent · Fractured City</t>
         </is>
       </c>
     </row>
@@ -9522,17 +9522,17 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>world.territory.clarity.name</t>
+          <t>world.territory.foundry.name</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>澄净·沉淀湖</t>
+          <t>铸造·铸造前哨</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Clarity · Sediment Lake</t>
+          <t>Foundry · Foundry Outpost</t>
         </is>
       </c>
     </row>
@@ -9540,17 +9540,17 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>world.territory.overclock.name</t>
+          <t>world.territory.clarity.name</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>超频·热寂数据城</t>
+          <t>澄净·沉淀湖</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Overclock · Heat-Death Data City</t>
+          <t>Clarity · Sediment Lake</t>
         </is>
       </c>
     </row>
@@ -9558,17 +9558,17 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>world.territory.white_tide.name</t>
+          <t>world.territory.overclock.name</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>白潮滩头</t>
+          <t>超频·热寂数据城</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>White Tide Beachhead</t>
+          <t>Overclock · Heat-Death Data City</t>
         </is>
       </c>
     </row>
@@ -9576,17 +9576,17 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>world.hazard.none</t>
+          <t>world.territory.white_tide.name</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>白潮滩头</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>White Tide Beachhead</t>
         </is>
       </c>
     </row>
@@ -9594,17 +9594,17 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>world.hazard.acid</t>
+          <t>world.hazard.none</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>酸沼带</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Acid marsh</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9612,17 +9612,17 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>world.hazard.heat</t>
+          <t>world.hazard.acid</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>高温辐射带</t>
+          <t>酸沼带</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Heat radiation belt</t>
+          <t>Acid marsh</t>
         </is>
       </c>
     </row>
@@ -9630,17 +9630,17 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>world.preset.default.name</t>
+          <t>world.hazard.heat</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>高温辐射带</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Heat radiation belt</t>
         </is>
       </c>
     </row>
@@ -9648,17 +9648,17 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>world.legacy_terrain</t>
+          <t>world.preset.default.name</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>原型地形（旧存档）</t>
+          <t>标准</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Prototype terrain (older save)</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -9666,17 +9666,17 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>ui.world.generating</t>
+          <t>world.legacy_terrain</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>正在生成地形（{0} 个区块）…</t>
+          <t>原型地形（旧存档）</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Generating terrain ({0} chunks)…</t>
+          <t>Prototype terrain (older save)</t>
         </is>
       </c>
     </row>
@@ -9684,17 +9684,17 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>grid.reason.world_limit</t>
+          <t>ui.world.generating</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>超出世界范围（离原点最多 {0} 格）</t>
+          <t>正在生成地形（{0} 个区块）…</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Outside the world (at most {0} tiles from the origin)</t>
+          <t>Generating terrain ({0} chunks)…</t>
         </is>
       </c>
     </row>
@@ -9702,17 +9702,17 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>ui.pause.world_seed</t>
+          <t>grid.reason.world_limit</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>世界种子：{0}</t>
+          <t>超出世界范围（离原点最多 {0} 格）</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>World seed: {0}</t>
+          <t>Outside the world (at most {0} tiles from the origin)</t>
         </is>
       </c>
     </row>
@@ -9720,17 +9720,17 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>ui.pause.copy_seed</t>
+          <t>ui.pause.world_seed</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>复制种子</t>
+          <t>世界种子：{0}</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Copy seed</t>
+          <t>World seed: {0}</t>
         </is>
       </c>
     </row>
@@ -9738,17 +9738,17 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>ui.pause.seed_copied</t>
+          <t>ui.pause.copy_seed</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>已复制种子 {0}</t>
+          <t>复制种子</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Seed {0} copied</t>
+          <t>Copy seed</t>
         </is>
       </c>
     </row>
@@ -9756,17 +9756,17 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>ui.pause.world_settings</t>
+          <t>ui.pause.seed_copied</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>世界设置：{0} · 生成器 v{1} · {2}</t>
+          <t>已复制种子 {0}</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>World settings: {0} · generator v{1} · {2}</t>
+          <t>Seed {0} copied</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,539 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
+          <t>ui.pause.world_settings</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>世界设置：{0} · 生成器 v{1} · {2}</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>World settings: {0} · generator v{1} · {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr"/>
+      <c r="B521" t="inlineStr">
+        <is>
           <t>save.card.world</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
+      <c r="C521" t="inlineStr">
         <is>
           <t>世界 {0}</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr">
+      <c r="D521" t="inlineStr">
         <is>
           <t>World {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr"/>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>ui.world.day_time</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>第 {0} 日 {1}</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Day {0} {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr"/>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>ui.world.speed</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>{0}x</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>{0}x</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr"/>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>ui.world.pause</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Pause</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr"/>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>ui.world.resume</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>继续</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr"/>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>ui.world.status_paused</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>已暂停</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr"/>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>ui.world.status_running</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>运行中 {0}</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Running {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr"/>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>ui.world.status_direct_locked</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>接入中：世界锁定 1x</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Uplinked: world locked at 1x</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr"/>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>ui.world.tip.time</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>游戏时间：第 {0} 日 {1}（1 个游戏日 = 1x 下 {2} 分钟）</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Game time: day {0} {1} (1 game day = {2} min at 1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr"/>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>ui.world.tip.speed</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>整个世界的速度 {0}（{1}）。家园、远征、行进中的突袭同时加速，结果与 1x 相同</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>World speed {0} ({1}). Home, expeditions and raids on the move all speed up together; results match 1x</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr"/>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>ui.world.tip.pause</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>暂停 / 继续整个世界（{0}）。暂停时仍可选择、下令、规划建造</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Pause / resume the whole world ({0}). While paused you can still select, order and plan construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr"/>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>ui.world.tip.direct_locked</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>接入一台机器时，整个世界固定以 1x 运行；退出接入后恢复所选速度</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>While uplinked to a machine the whole world runs at 1x; your chosen speed returns when you leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr"/>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>ui.world.focus.title</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>关注点</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr"/>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>ui.world.focus.home</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>家园</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr"/>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>ui.world.focus.expedition</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>远征·{0}（{1} 台）</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Expedition · {0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr"/>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>ui.world.focus.raid</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>突袭 ×{0}（约 {1} 后到达）</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Raid ×{0} (arrives in ~{1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr"/>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>ui.world.focus.raid_arrived</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>突袭 ×{0}（已到达）</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Raid ×{0} (arrived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr"/>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ui.world.focus.current</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>▸ {0}</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>▸ {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr"/>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>ui.world.focus.tip</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>镜头飞到这里（{0} 依次切换关注点，{1} 回到归还核心）。整个世界一直在运行，镜头只决定你看哪里</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Fly the camera here ({0} cycles focus, {1} returns to the Reclamation Core). The whole world keeps running; the camera only decides what you watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr"/>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>ui.world.eta</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>{0} 小时 {1} 分（游戏时间）</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>{0} h {1} min (game time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr"/>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>ui.world.site_unloaded</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>该地点已不在运行（远征已结束），无法定位</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>That place is no longer active (the expedition has ended)</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr"/>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>ui.world.expedition_wiped_here</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>远征队全灭：镜头留在远征地点，确认放弃后回到家园；也可以先切回家园处理别的事</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Expedition wiped out: the camera stays here until you confirm abandoning; you can switch back home meanwhile</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr"/>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>ui.world.placeholder</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>（占位表现：地貌为地形图层色块，突袭为标记柱）</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>(Placeholder visuals: terrain tiles and raid marker)</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr"/>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>world.site.home_valley.name</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>归还谷地</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Reclamation Valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr"/>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>world.site.silent_ruins.name</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>破碎都市</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Fractured City</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr"/>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>world.site.foundry_outpost.name</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>铸造前哨外围</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Foundry Outpost Outskirts</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr"/>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>world.transit.raid.label</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>突袭 ×{0}</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Raid ×{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr"/>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>world.transit.raid.arrived_detail</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>{0} 个敌方单位抵达家园外围（来自 {1}）</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>{0} enemy units reached the home perimeter (from {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr"/>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>expedition.reason.underway</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>已有远征队在外：撤离或放弃后才能再次派遣</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>An expedition is already out: evacuate or abandon it before sending another</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D549"/>
+  <dimension ref="A1:D589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10310,6 +10310,726 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" t="inlineStr"/>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>logistics.tier.t1</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>传送带 T1</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Belt T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr"/>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>logistics.tier.t2</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>传送带 T2</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Belt T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr"/>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>logistics.tier.t3</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>传送带 T3</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Belt T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr"/>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>logistics.block.none</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>运转中</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr"/>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>logistics.block.end_of_belt</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>传送带到头了：末端没有接传送带或建筑输入口</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>End of belt: nothing is connected at the end</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr"/>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>logistics.block.downstream_full</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>下游 ({0}, {1}) 已满</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Downstream ({0}, {1}) is full</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr"/>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>logistics.block.sink_full</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>下游 {0} 的输入已满</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>{0}'s input downstream is full</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr"/>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>logistics.block.sink_unnamed</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>输入端口 #{0}</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>input port #{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>logistics.block.merge_wait</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>汇入点 ({0}, {1}) 轮到另一路：两路交替汇入</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Merge at ({0}, {1}) is serving the other lane: lanes alternate</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr"/>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>logistics.hover.summary</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>{0}｜{1} 件｜实测 {2} 件/分钟（设计 {3}）｜{4}</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>{0} | {1} items | {2}/min measured ({3} rated) | {4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr"/>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>logistics.hover.loop</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>（环形）</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>(loop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr"/>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>logistics.hover.measuring</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>统计中</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>measuring</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr"/>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>logistics.reason.occupied</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>这一格已经有传送带</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>There is already a belt here</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr"/>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>logistics.reason.not_found</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>这里没有传送带</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>There is no belt here</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr"/>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>logistics.reason.invalid_tier</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>没有这个等级的传送带</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>No such belt tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr"/>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>logistics.reason.invalid_direction</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>传送带方向无效</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Invalid belt direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr"/>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>logistics.reason.no_space</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>这一格放不下更多物品</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>No room for more items on this belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr"/>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>logistics.reason.port_occupied</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>这里已经有同类端口</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>There is already a port of this kind here</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr"/>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>logistics.reason.port_not_found</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>没有这个端口</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>No such port</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr"/>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>logistics.reason.invalid_argument</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>参数无效</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Invalid argument</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr"/>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>logistics.reason.out_of_range</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>超出传送带可用范围</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Out of belt range</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr"/>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>logistics.reason.not_running</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>家园未载入，传送带暂不可用</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Home is not loaded; belts are unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr"/>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>logistics.reason.save_preserved</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>存档里的传送带来自更新的版本，本版本读不了；为保护原数据，这局不能铺设或修改传送带</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>The belts in this save come from a newer version and cannot be read here; to protect that data, belts cannot be placed or changed in this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr"/>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>logistics.load.corrupt</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>传送带存档有 {0} 个网络损坏，已丢弃（{1} 件物品计入移出）：{2}</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>{0} belt network(s) in the save were damaged and dropped ({1} items written off): {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr"/>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>logistics.load.unreadable</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>传送带存档读不了（{0}）：{1} 个网络、{2} 件物品原样保留在存档里，不会被覆盖；这局不能铺设或修改传送带</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>The belts in this save cannot be read ({0}): {1} network(s) and {2} items are kept untouched in the save; belts cannot be placed or changed in this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr"/>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.separator</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>；</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">; </t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr"/>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.unknown</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>未知问题</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>unknown problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr"/>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.snapshot_null</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>没有传送带数据</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>no belt data</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr"/>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.not_empty</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>内部错误：恢复目标不是空网络</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>internal error: restore target not empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr"/>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.format_version</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>来自不认识的存档格式版本（可能由更新的游戏版本保存）</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>saved in an unknown format version (possibly by a newer game version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr"/>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_empty</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>网络数据为空或过短</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>network data empty or too short</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr"/>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_checksum</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>网络数据校验和不符</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>network data checksum mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr"/>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_magic</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>网络数据格式标记不符</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>network data format marker mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr"/>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_header</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>网络数据头与记录不一致</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>network header does not match its record</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr"/>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_truncated</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>网络数据被截断</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>network data truncated</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr"/>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_cell</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>网络里有无法恢复的传送带（坐标重复或数值非法）</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>a belt in the network cannot be restored (duplicate or invalid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr"/>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_item</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>网络里有位置非法或重叠的物品</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>an item in the network has an invalid or overlapping position</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr"/>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.chunk_count</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>网络物品总数不符</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>network item count mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr"/>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>logistics.load.reason.ports_corrupt</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>端口数据损坏已丢弃（建筑会重新登记端口）</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>port data damaged and dropped (buildings re-register their ports)</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr"/>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>logistics.placeholder</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>（占位表现：传送带为色块与箭头，物品为按种类着色的方块；物品图标随 FG4 物品表替换）</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>(Placeholder visuals: belts are tiles with arrows, items are colour-coded squares; icons arrive with the FG4 item table)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D589"/>
+  <dimension ref="A1:D610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11030,6 +11030,384 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" t="inlineStr"/>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>combat.fire.no_attacker</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>攻击者不存在或已阵亡</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>The attacker no longer exists or has been destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr"/>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>combat.fire.no_weapon</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>这台机器没有可用的武器装配</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>This machine has no usable weapon loadout</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr"/>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>combat.fire.no_output</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>当前装配没有可攻击的主武器出口（8 号汇槽为空）</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>The loadout has no attacking primary output (sink slot 8 is empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr"/>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>combat.fire.overheated</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>武器过热：热量降到 {0} 以下才能再开火</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Weapon overheated: wait until heat drops below {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr"/>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>combat.fire.cooldown</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>武器冷却中</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Weapon cooling down</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr"/>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>combat.fire.target_dead</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>目标已阵亡</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>The target is already destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr"/>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>combat.fire.target_missing</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>目标不存在</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>The target does not exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr"/>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>combat.fire.out_of_range</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>目标不在射程内</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>The target is out of range</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr"/>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>combat.fire.not_hostile</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>不能攻击这个目标</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>This target cannot be attacked</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr"/>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>combat.fire.invulnerable</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>目标当前无法被击伤（{0}）</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>The target cannot be damaged right now ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr"/>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>combat.load.rebuilt</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>{0} 的战斗状态读不了（{1}）：已按机器与敌人记录恢复（位置、耐久保留；飞行中的弹体、冷却与编队命令重置）</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Combat state for {0} could not be read ({1}): restored from machine and enemy records (positions and durability kept; projectiles in flight, cooldowns and squad orders reset)</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr"/>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>combat.load.reason.bad_magic</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>数据格式标记不符</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>format marker mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr"/>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>combat.load.reason.unknown_format</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>来自不认识的存档格式版本（可能由更新的游戏版本保存）</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>saved in an unknown format version (possibly by a newer game version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr"/>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>combat.load.reason.bad_checksum</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>数据校验和不符</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>checksum mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr"/>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>combat.load.reason.truncated</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>数据被截断</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>data truncated</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr"/>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>combat.load.reason.invalid_value</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>数据里有非法数值</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>invalid values in the data</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr"/>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>combat.load.reason.bad_payload</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>数据无法解码</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>data could not be decoded</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr"/>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>combat.site.home</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>家园</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr"/>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>combat.site.fractured_city</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>破碎都市</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Fractured City</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr"/>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>combat.site.foundry_outpost</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>铸造前哨外围</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Foundry Outpost outskirts</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr"/>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>combat.placeholder</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>（占位表现：突袭者与炮塔原型为按阵营着色的圆片与血量环，弹体为发光短线；正式模型随 FG6 替换）</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>(Placeholder visuals: raider and turret prototypes are faction-coloured discs with a durability ring, projectiles are glowing streaks; real models arrive with FG6)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3780,17 +3780,17 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.name</t>
+          <t>notify.type.unreachable.name</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>供电恢复</t>
+          <t>无法到达</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Power restored</t>
+          <t>Unreachable</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3798,17 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.single</t>
+          <t>notify.type.unreachable.single</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>供电恢复：{0}</t>
+          <t>无法到达：{0}</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Power restored: {0}</t>
+          <t>Unreachable: {0}</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>notify.type.power_restored.many</t>
+          <t>notify.type.unreachable.many</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{0} 处供电恢复</t>
+          <t>{0} 处无法到达</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>{0} power restorations</t>
+          <t>{0} unreachable targets</t>
         </is>
       </c>
     </row>
@@ -3834,17 +3834,17 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.name</t>
+          <t>notify.type.power_restored.name</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>信号恢复</t>
+          <t>供电恢复</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Signal restored</t>
+          <t>Power restored</t>
         </is>
       </c>
     </row>
@@ -3852,17 +3852,17 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.single</t>
+          <t>notify.type.power_restored.single</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>信号恢复：{0}</t>
+          <t>供电恢复：{0}</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Signal restored: {0}</t>
+          <t>Power restored: {0}</t>
         </is>
       </c>
     </row>
@@ -3870,17 +3870,17 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>notify.type.signal_restored.many</t>
+          <t>notify.type.power_restored.many</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{0} 处信号恢复</t>
+          <t>{0} 处供电恢复</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>{0} signal restorations</t>
+          <t>{0} power restorations</t>
         </is>
       </c>
     </row>
@@ -3888,17 +3888,17 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.name</t>
+          <t>notify.type.signal_restored.name</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>生产完成</t>
+          <t>信号恢复</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Production complete</t>
+          <t>Signal restored</t>
         </is>
       </c>
     </row>
@@ -3906,17 +3906,17 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.single</t>
+          <t>notify.type.signal_restored.single</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>生产完成：{0}</t>
+          <t>信号恢复：{0}</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Production complete: {0}</t>
+          <t>Signal restored: {0}</t>
         </is>
       </c>
     </row>
@@ -3924,17 +3924,17 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>notify.type.production_complete.many</t>
+          <t>notify.type.signal_restored.many</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{0} 项生产完成</t>
+          <t>{0} 处信号恢复</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>{0} items produced</t>
+          <t>{0} signal restorations</t>
         </is>
       </c>
     </row>
@@ -3942,17 +3942,17 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.name</t>
+          <t>notify.type.production_complete.name</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>解析完成</t>
+          <t>生产完成</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Analysis complete</t>
+          <t>Production complete</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.single</t>
+          <t>notify.type.production_complete.single</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>解析完成：{0}</t>
+          <t>生产完成：{0}</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Analysis complete: {0}</t>
+          <t>Production complete: {0}</t>
         </is>
       </c>
     </row>
@@ -3978,17 +3978,17 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>notify.type.analysis_complete.many</t>
+          <t>notify.type.production_complete.many</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{0} 项解析完成</t>
+          <t>{0} 项生产完成</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>{0} analyses complete</t>
+          <t>{0} items produced</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3996,17 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.name</t>
+          <t>notify.type.analysis_complete.name</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>建造完成</t>
+          <t>解析完成</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Construction complete</t>
+          <t>Analysis complete</t>
         </is>
       </c>
     </row>
@@ -4014,17 +4014,17 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.single</t>
+          <t>notify.type.analysis_complete.single</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>完工：{0}</t>
+          <t>解析完成：{0}</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Completed: {0}</t>
+          <t>Analysis complete: {0}</t>
         </is>
       </c>
     </row>
@@ -4032,17 +4032,17 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>notify.type.build_complete.many</t>
+          <t>notify.type.analysis_complete.many</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{0} 座建筑完工</t>
+          <t>{0} 项解析完成</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>{0} buildings completed</t>
+          <t>{0} analyses complete</t>
         </is>
       </c>
     </row>
@@ -4050,17 +4050,17 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.name</t>
+          <t>notify.type.build_complete.name</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>新任务</t>
+          <t>建造完成</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>New objective</t>
+          <t>Construction complete</t>
         </is>
       </c>
     </row>
@@ -4068,17 +4068,17 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.single</t>
+          <t>notify.type.build_complete.single</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>新目标：{0}</t>
+          <t>完工：{0}</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>New objective: {0}</t>
+          <t>Completed: {0}</t>
         </is>
       </c>
     </row>
@@ -4086,17 +4086,17 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>notify.type.objective_new.many</t>
+          <t>notify.type.build_complete.many</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{0} 个新目标</t>
+          <t>{0} 座建筑完工</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>{0} new objectives</t>
+          <t>{0} buildings completed</t>
         </is>
       </c>
     </row>
@@ -4104,17 +4104,17 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.name</t>
+          <t>notify.type.objective_new.name</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>目标完成</t>
+          <t>新任务</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Objective complete</t>
+          <t>New objective</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.single</t>
+          <t>notify.type.objective_new.single</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>目标完成：{0}</t>
+          <t>新目标：{0}</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Objective complete: {0}</t>
+          <t>New objective: {0}</t>
         </is>
       </c>
     </row>
@@ -4140,17 +4140,17 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>notify.type.objective_done.many</t>
+          <t>notify.type.objective_new.many</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{0} 个目标完成</t>
+          <t>{0} 个新目标</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>{0} objectives complete</t>
+          <t>{0} new objectives</t>
         </is>
       </c>
     </row>
@@ -4158,17 +4158,17 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>notify.type.expedition.name</t>
+          <t>notify.type.objective_done.name</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>远征动态</t>
+          <t>目标完成</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>Objective complete</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>notify.type.expedition.single</t>
+          <t>notify.type.objective_done.single</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>远征：{0}</t>
+          <t>目标完成：{0}</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Expedition: {0}</t>
+          <t>Objective complete: {0}</t>
         </is>
       </c>
     </row>
@@ -4194,17 +4194,17 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>notify.type.expedition.many</t>
+          <t>notify.type.objective_done.many</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{0} 条远征动态</t>
+          <t>{0} 个目标完成</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>{0} expedition updates</t>
+          <t>{0} objectives complete</t>
         </is>
       </c>
     </row>
@@ -4212,17 +4212,17 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.name</t>
+          <t>notify.type.expedition.name</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>首领击破</t>
+          <t>远征动态</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Boss destroyed</t>
+          <t>Expedition</t>
         </is>
       </c>
     </row>
@@ -4230,17 +4230,17 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.single</t>
+          <t>notify.type.expedition.single</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>主核心已摧毁：{0}</t>
+          <t>远征：{0}</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The main core was destroyed: {0}</t>
+          <t>Expedition: {0}</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>notify.type.boss_destroyed.many</t>
+          <t>notify.type.expedition.many</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>主核心已摧毁（{0} 次）</t>
+          <t>{0} 条远征动态</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>The main core was destroyed ({0} times)</t>
+          <t>{0} expedition updates</t>
         </is>
       </c>
     </row>
@@ -4266,17 +4266,17 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>notify.type.beacon.name</t>
+          <t>notify.type.boss_destroyed.name</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>导航信标</t>
+          <t>首领击破</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Navigation beacon</t>
+          <t>Boss destroyed</t>
         </is>
       </c>
     </row>
@@ -4284,17 +4284,17 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>notify.type.beacon.single</t>
+          <t>notify.type.boss_destroyed.single</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>导航信标：{0}</t>
+          <t>主核心已摧毁：{0}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Navigation beacon: {0}</t>
+          <t>The main core was destroyed: {0}</t>
         </is>
       </c>
     </row>
@@ -4302,17 +4302,17 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>notify.type.beacon.many</t>
+          <t>notify.type.boss_destroyed.many</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{0} 条信标动态</t>
+          <t>主核心已摧毁（{0} 次）</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>{0} beacon updates</t>
+          <t>The main core was destroyed ({0} times)</t>
         </is>
       </c>
     </row>
@@ -4320,17 +4320,17 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>notify.type.research_done.name</t>
+          <t>notify.type.beacon.name</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>研究完成</t>
+          <t>导航信标</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Research complete</t>
+          <t>Navigation beacon</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>notify.type.research_done.single</t>
+          <t>notify.type.beacon.single</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>研究完成：{0}</t>
+          <t>导航信标：{0}</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Research complete: {0}</t>
+          <t>Navigation beacon: {0}</t>
         </is>
       </c>
     </row>
@@ -4356,17 +4356,17 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>notify.type.research_done.many</t>
+          <t>notify.type.beacon.many</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{0} 项研究完成</t>
+          <t>{0} 条信标动态</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>{0} research projects complete</t>
+          <t>{0} beacon updates</t>
         </is>
       </c>
     </row>
@@ -4374,17 +4374,17 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.name</t>
+          <t>notify.type.research_done.name</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>自动暂停</t>
+          <t>研究完成</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Auto-pause</t>
+          <t>Research complete</t>
         </is>
       </c>
     </row>
@@ -4392,17 +4392,17 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.single</t>
+          <t>notify.type.research_done.single</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>已自动暂停：由通知「{0}」触发，可在通知设置中关闭</t>
+          <t>研究完成：{0}</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Auto-paused by the "{0}" notification. You can turn this off in notification settings.</t>
+          <t>Research complete: {0}</t>
         </is>
       </c>
     </row>
@@ -4410,17 +4410,17 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>notify.type.auto_paused.many</t>
+          <t>notify.type.research_done.many</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>已自动暂停（{0} 次）</t>
+          <t>{0} 项研究完成</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Auto-paused ({0} times)</t>
+          <t>{0} research projects complete</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.name</t>
+          <t>notify.type.auto_paused.name</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>设置变更</t>
+          <t>自动暂停</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Settings changed</t>
+          <t>Auto-pause</t>
         </is>
       </c>
     </row>
@@ -4446,17 +4446,17 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.single</t>
+          <t>notify.type.auto_paused.single</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>已自动暂停：由通知「{0}」触发，可在通知设置中关闭</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Auto-paused by the "{0}" notification. You can turn this off in notification settings.</t>
         </is>
       </c>
     </row>
@@ -4464,17 +4464,17 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>notify.type.settings_changed.many</t>
+          <t>notify.type.auto_paused.many</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>{0} 条设置变更</t>
+          <t>已自动暂停（{0} 次）</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>{0} settings changes</t>
+          <t>Auto-paused ({0} times)</t>
         </is>
       </c>
     </row>
@@ -4482,17 +4482,17 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.name</t>
+          <t>notify.type.settings_changed.name</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>尚未开放</t>
+          <t>设置变更</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Not yet available</t>
+          <t>Settings changed</t>
         </is>
       </c>
     </row>
@@ -4500,17 +4500,17 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.single</t>
+          <t>notify.type.settings_changed.single</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>「{0}」将在后续版本开放</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>"{0}" will be available in a later version</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -4518,17 +4518,17 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>notify.type.feature_locked.many</t>
+          <t>notify.type.settings_changed.many</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>{0} 个操作尚未开放</t>
+          <t>{0} 条设置变更</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>{0} actions are not yet available</t>
+          <t>{0} settings changes</t>
         </is>
       </c>
     </row>
@@ -4536,17 +4536,17 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>notify.tier.urgent</t>
+          <t>notify.type.feature_locked.name</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>紧急</t>
+          <t>尚未开放</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Not yet available</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>notify.tier.warning</t>
+          <t>notify.type.feature_locked.single</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>警告</t>
+          <t>「{0}」将在后续版本开放</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>"{0}" will be available in a later version</t>
         </is>
       </c>
     </row>
@@ -4572,17 +4572,17 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>notify.tier.info</t>
+          <t>notify.type.feature_locked.many</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>信息</t>
+          <t>{0} 个操作尚未开放</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>{0} actions are not yet available</t>
         </is>
       </c>
     </row>
@@ -4590,17 +4590,17 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>input.category.camera</t>
+          <t>notify.tier.urgent</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>镜头</t>
+          <t>紧急</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
@@ -4608,17 +4608,17 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>input.category.time</t>
+          <t>notify.tier.warning</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>警告</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4626,17 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>input.category.command</t>
+          <t>notify.tier.info</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>指挥</t>
+          <t>信息</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Command</t>
+          <t>Info</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4644,17 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.camera</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>建造</t>
+          <t>镜头</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -4662,17 +4662,17 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>input.category.uplink</t>
+          <t>input.category.time</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>Time</t>
         </is>
       </c>
     </row>
@@ -4680,17 +4680,17 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>input.category.panel</t>
+          <t>input.category.command</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>面板</t>
+          <t>指挥</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Panels</t>
+          <t>Command</t>
         </is>
       </c>
     </row>
@@ -4698,17 +4698,17 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>input.category.system</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>建造</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -4716,17 +4716,17 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>input.context.strategy</t>
+          <t>input.category.uplink</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>战略</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -4734,17 +4734,17 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>input.context.build</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>建造</t>
+          <t>面板</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Panels</t>
         </is>
       </c>
     </row>
@@ -4752,17 +4752,17 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>input.context.uplink</t>
+          <t>input.category.system</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -4770,17 +4770,17 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>input.context.interface</t>
+          <t>input.context.strategy</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>界面</t>
+          <t>战略</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Strategy</t>
         </is>
       </c>
     </row>
@@ -4788,17 +4788,17 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>input.mod.ctrl</t>
+          <t>input.context.build</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>建造</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Ctrl</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -4806,17 +4806,17 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>input.mod.alt</t>
+          <t>input.context.uplink</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Alt</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Alt</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -4824,17 +4824,17 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>input.mod.shift</t>
+          <t>input.context.interface</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>界面</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Interface</t>
         </is>
       </c>
     </row>
@@ -4842,17 +4842,17 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>input.chord.join</t>
+          <t>input.mod.ctrl</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>{0}+{1}</t>
+          <t>Ctrl</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>{0}+{1}</t>
+          <t>Ctrl</t>
         </is>
       </c>
     </row>
@@ -4860,17 +4860,17 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>input.key.none</t>
+          <t>input.mod.alt</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>未绑定</t>
+          <t>Alt</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Unbound</t>
+          <t>Alt</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4878,17 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>input.key.space</t>
+          <t>input.mod.shift</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Shift</t>
         </is>
       </c>
     </row>
@@ -4896,17 +4896,17 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>input.key.escape</t>
+          <t>input.chord.join</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Esc</t>
+          <t>{0}+{1}</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Esc</t>
+          <t>{0}+{1}</t>
         </is>
       </c>
     </row>
@@ -4914,17 +4914,17 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>input.key.return</t>
+          <t>input.key.none</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>回车</t>
+          <t>未绑定</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Unbound</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4932,17 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>input.key.tab</t>
+          <t>input.key.space</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>空格</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4950,17 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>input.key.back_quote</t>
+          <t>input.key.escape</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>Esc</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>Esc</t>
         </is>
       </c>
     </row>
@@ -4968,17 +4968,17 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>input.key.home</t>
+          <t>input.key.return</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>回车</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Enter</t>
         </is>
       </c>
     </row>
@@ -4986,17 +4986,17 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>input.key.mouse0</t>
+          <t>input.key.tab</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>鼠标左键</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Left mouse</t>
+          <t>Tab</t>
         </is>
       </c>
     </row>
@@ -5004,17 +5004,17 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>input.key.mouse1</t>
+          <t>input.key.back_quote</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>鼠标右键</t>
+          <t>`</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Right mouse</t>
+          <t>`</t>
         </is>
       </c>
     </row>
@@ -5022,17 +5022,17 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>input.key.mouse2</t>
+          <t>input.key.home</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>鼠标中键</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Middle mouse</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -5040,17 +5040,17 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>input.key.wheel_up</t>
+          <t>input.key.mouse0</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>滚轮上</t>
+          <t>鼠标左键</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Wheel up</t>
+          <t>Left mouse</t>
         </is>
       </c>
     </row>
@@ -5058,17 +5058,17 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>input.key.wheel_down</t>
+          <t>input.key.mouse1</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>滚轮下</t>
+          <t>鼠标右键</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Wheel down</t>
+          <t>Right mouse</t>
         </is>
       </c>
     </row>
@@ -5076,17 +5076,17 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>input.key.up_arrow</t>
+          <t>input.key.mouse2</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>上方向键</t>
+          <t>鼠标中键</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Up arrow</t>
+          <t>Middle mouse</t>
         </is>
       </c>
     </row>
@@ -5094,17 +5094,17 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>input.key.down_arrow</t>
+          <t>input.key.wheel_up</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>下方向键</t>
+          <t>滚轮上</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Down arrow</t>
+          <t>Wheel up</t>
         </is>
       </c>
     </row>
@@ -5112,17 +5112,17 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>input.key.left_arrow</t>
+          <t>input.key.wheel_down</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>左方向键</t>
+          <t>滚轮下</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Left arrow</t>
+          <t>Wheel down</t>
         </is>
       </c>
     </row>
@@ -5130,17 +5130,17 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>input.key.right_arrow</t>
+          <t>input.key.up_arrow</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>右方向键</t>
+          <t>上方向键</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Right arrow</t>
+          <t>Up arrow</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5148,17 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>input.key.left_shift</t>
+          <t>input.key.down_arrow</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>左 Shift</t>
+          <t>下方向键</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Left Shift</t>
+          <t>Down arrow</t>
         </is>
       </c>
     </row>
@@ -5166,17 +5166,17 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>input.key.right_shift</t>
+          <t>input.key.left_arrow</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>右 Shift</t>
+          <t>左方向键</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Right Shift</t>
+          <t>Left arrow</t>
         </is>
       </c>
     </row>
@@ -5184,17 +5184,17 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>input.key.left_alt</t>
+          <t>input.key.right_arrow</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>左 Alt</t>
+          <t>右方向键</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Left Alt</t>
+          <t>Right arrow</t>
         </is>
       </c>
     </row>
@@ -5202,17 +5202,17 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>input.key.right_alt</t>
+          <t>input.key.left_shift</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>右 Alt</t>
+          <t>左 Shift</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Right Alt</t>
+          <t>Left Shift</t>
         </is>
       </c>
     </row>
@@ -5220,17 +5220,17 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>input.key.left_control</t>
+          <t>input.key.right_shift</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>左 Ctrl</t>
+          <t>右 Shift</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Left Ctrl</t>
+          <t>Right Shift</t>
         </is>
       </c>
     </row>
@@ -5238,17 +5238,17 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>input.key.right_control</t>
+          <t>input.key.left_alt</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>右 Ctrl</t>
+          <t>左 Alt</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Right Ctrl</t>
+          <t>Left Alt</t>
         </is>
       </c>
     </row>
@@ -5256,17 +5256,17 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>input.key.digit</t>
+          <t>input.key.right_alt</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>右 Alt</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Right Alt</t>
         </is>
       </c>
     </row>
@@ -5274,17 +5274,17 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>input.rebind.listening</t>
+          <t>input.key.left_control</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>请按下新按键……（Esc 取消）</t>
+          <t>左 Ctrl</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Press a new key... (Esc to cancel)</t>
+          <t>Left Ctrl</t>
         </is>
       </c>
     </row>
@@ -5292,17 +5292,17 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>input.rebind.conflict_title</t>
+          <t>input.key.right_control</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>按键冲突</t>
+          <t>右 Ctrl</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Key conflict</t>
+          <t>Right Ctrl</t>
         </is>
       </c>
     </row>
@@ -5310,17 +5310,17 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>input.rebind.conflict_line</t>
+          <t>input.key.digit</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>{0} 已被「{1}」使用（{2}）</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>{0} is already used by "{1}" ({2})</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -5328,17 +5328,17 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>input.rebind.conflict_tail</t>
+          <t>input.rebind.listening</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>覆盖后「{0}」将变为未绑定。</t>
+          <t>请按下新按键……（Esc 取消）</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>If you overwrite it, "{0}" becomes unbound.</t>
+          <t>Press a new key... (Esc to cancel)</t>
         </is>
       </c>
     </row>
@@ -5346,17 +5346,17 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>input.rebind.override</t>
+          <t>input.rebind.conflict_title</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>覆盖</t>
+          <t>按键冲突</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Overwrite</t>
+          <t>Key conflict</t>
         </is>
       </c>
     </row>
@@ -5364,17 +5364,17 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>input.rebind.required_blocked</t>
+          <t>input.rebind.conflict_line</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>「{0}」必须保留按键，不能被覆盖；请先给它换一个键</t>
+          <t>{0} 已被「{1}」使用（{2}）</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>"{0}" must keep a key and cannot be overwritten; rebind it first</t>
+          <t>{0} is already used by "{1}" ({2})</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>input.rebind.done</t>
+          <t>input.rebind.conflict_tail</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>已将「{0}」设为 {1}</t>
+          <t>覆盖后「{0}」将变为未绑定。</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>"{0}" is now {1}</t>
+          <t>If you overwrite it, "{0}" becomes unbound.</t>
         </is>
       </c>
     </row>
@@ -5400,17 +5400,17 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>input.rebind.mouse_only</t>
+          <t>input.rebind.override</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>「{0}」只能绑定鼠标按键</t>
+          <t>覆盖</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>"{0}" can only be bound to a mouse button</t>
+          <t>Overwrite</t>
         </is>
       </c>
     </row>
@@ -5418,17 +5418,17 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>input.rebind.reset_conflict</t>
+          <t>input.rebind.required_blocked</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>「{0}」的默认键已被别的动作占用，请先改那个动作</t>
+          <t>「{0}」必须保留按键，不能被覆盖；请先给它换一个键</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>The default key of "{0}" is taken by another action; change that one first</t>
+          <t>"{0}" must keep a key and cannot be overwritten; rebind it first</t>
         </is>
       </c>
     </row>
@@ -5436,17 +5436,17 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>input.rebind.cancelled</t>
+          <t>input.rebind.done</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>已取消改键</t>
+          <t>已将「{0}」设为 {1}</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Rebinding cancelled</t>
+          <t>"{0}" is now {1}</t>
         </is>
       </c>
     </row>
@@ -5454,17 +5454,17 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>input.rebind.reset_one</t>
+          <t>input.rebind.mouse_only</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>「{0}」只能绑定鼠标按键</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>"{0}" can only be bound to a mouse button</t>
         </is>
       </c>
     </row>
@@ -5472,17 +5472,17 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>input.rebind.reset_all_title</t>
+          <t>input.rebind.reset_conflict</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>恢复全部默认按键</t>
+          <t>「{0}」的默认键已被别的动作占用，请先改那个动作</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Reset all keys to default</t>
+          <t>The default key of "{0}" is taken by another action; change that one first</t>
         </is>
       </c>
     </row>
@@ -5490,17 +5490,17 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>input.rebind.reset_all_line</t>
+          <t>input.rebind.cancelled</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>将丢失：你改过的 {0} 个按键</t>
+          <t>已取消改键</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>You will lose: {0} customised key(s)</t>
+          <t>Rebinding cancelled</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5508,17 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>input.rebind.migrated</t>
+          <t>input.rebind.reset_one</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>按键方案已更新为正式版：保留了你改过的 {0} 个按键，{1} 个因与新默认键冲突已恢复默认</t>
+          <t>恢复默认</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Key layout updated for the full game: kept {0} customised key(s); {1} restored to default because they clashed with new defaults</t>
+          <t>Default</t>
         </is>
       </c>
     </row>
@@ -5526,17 +5526,17 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>input.rebind.migrated_defaults</t>
+          <t>input.rebind.reset_all_title</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>按键方案已更新为正式版，部分默认按键有调整，可在暂停菜单 → 按键设置查看</t>
+          <t>恢复全部默认按键</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Key layout updated for the full game; some default keys changed. See Pause menu → Key bindings</t>
+          <t>Reset all keys to default</t>
         </is>
       </c>
     </row>
@@ -5544,17 +5544,17 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>input.status.reserved</t>
+          <t>input.rebind.reset_all_line</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>后续版本开放</t>
+          <t>将丢失：你改过的 {0} 个按键</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Coming later</t>
+          <t>You will lose: {0} customised key(s)</t>
         </is>
       </c>
     </row>
@@ -5562,17 +5562,17 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>input.status.unbound_warning</t>
+          <t>input.rebind.migrated</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>未绑定：只能用鼠标或界面按钮操作</t>
+          <t>按键方案已更新为正式版：保留了你改过的 {0} 个按键，{1} 个因与新默认键冲突已恢复默认</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Unbound: use the mouse or on-screen buttons</t>
+          <t>Key layout updated for the full game: kept {0} customised key(s); {1} restored to default because they clashed with new defaults</t>
         </is>
       </c>
     </row>
@@ -5580,17 +5580,17 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>input.status.reserved_tip</t>
+          <t>input.rebind.migrated_defaults</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>这个操作对应的系统还没有开放，按键先保留，可以提前改键</t>
+          <t>按键方案已更新为正式版，部分默认按键有调整，可在暂停菜单 → 按键设置查看</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>This action's system is not available yet; you can still set its key</t>
+          <t>Key layout updated for the full game; some default keys changed. See Pause menu → Key bindings</t>
         </is>
       </c>
     </row>
@@ -5598,17 +5598,17 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>input.tooltip.contexts</t>
+          <t>input.status.reserved</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>生效范围：{0}</t>
+          <t>后续版本开放</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Active in: {0}</t>
+          <t>Coming later</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ui.keybind.title</t>
+          <t>input.status.unbound_warning</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>按键设置</t>
+          <t>未绑定：只能用鼠标或界面按钮操作</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Key bindings</t>
+          <t>Unbound: use the mouse or on-screen buttons</t>
         </is>
       </c>
     </row>
@@ -5634,17 +5634,17 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ui.keybind.open_all</t>
+          <t>input.status.reserved_tip</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>全部按键…</t>
+          <t>这个操作对应的系统还没有开放，按键先保留，可以提前改键</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>All keys...</t>
+          <t>This action's system is not available yet; you can still set its key</t>
         </is>
       </c>
     </row>
@@ -5652,17 +5652,17 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ui.keybind.search_placeholder</t>
+          <t>input.tooltip.contexts</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>搜索动作或按键</t>
+          <t>生效范围：{0}</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Search actions or keys</t>
+          <t>Active in: {0}</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5670,17 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ui.keybind.tab_all</t>
+          <t>ui.keybind.title</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>按键设置</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Key bindings</t>
         </is>
       </c>
     </row>
@@ -5688,17 +5688,17 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ui.keybind.empty</t>
+          <t>ui.keybind.open_all</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>没有匹配“{0}”的动作</t>
+          <t>全部按键…</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>No actions match "{0}"</t>
+          <t>All keys...</t>
         </is>
       </c>
     </row>
@@ -5706,17 +5706,17 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ui.keybind.count</t>
+          <t>ui.keybind.search_placeholder</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>共 {0} 个动作，{1} 个已改键</t>
+          <t>搜索动作或按键</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>{0} actions, {1} customised</t>
+          <t>Search actions or keys</t>
         </is>
       </c>
     </row>
@@ -5724,17 +5724,17 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ui.keybind.reset_all</t>
+          <t>ui.keybind.tab_all</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>全部恢复默认</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Reset all</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -5742,17 +5742,17 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ui.keybind.col_action</t>
+          <t>ui.keybind.empty</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>动作</t>
+          <t>没有匹配“{0}”的动作</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>No actions match "{0}"</t>
         </is>
       </c>
     </row>
@@ -5760,17 +5760,17 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ui.keybind.col_key</t>
+          <t>ui.keybind.count</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>按键</t>
+          <t>共 {0} 个动作，{1} 个已改键</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>{0} actions, {1} customised</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>ui.common.close</t>
+          <t>ui.keybind.reset_all</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>全部恢复默认</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Reset all</t>
         </is>
       </c>
     </row>
@@ -5796,17 +5796,17 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ui.common.cancel</t>
+          <t>ui.keybind.col_action</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>动作</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -5814,17 +5814,17 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ui.common.confirm</t>
+          <t>ui.keybind.col_key</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>按键</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Key</t>
         </is>
       </c>
     </row>
@@ -5832,17 +5832,17 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ui.common.loading</t>
+          <t>ui.common.close</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>加载中……</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Loading...</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -5850,17 +5850,17 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ui.common.empty</t>
+          <t>ui.common.cancel</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>暂无内容</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Nothing here yet</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -5868,17 +5868,17 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ui.common.clear</t>
+          <t>ui.common.confirm</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>清空</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
@@ -5886,17 +5886,17 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ui.common.shortcut</t>
+          <t>ui.common.loading</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>快捷键：{0}</t>
+          <t>加载中……</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Shortcut: {0}</t>
+          <t>Loading...</t>
         </is>
       </c>
     </row>
@@ -5904,17 +5904,17 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ui.common.codex_link</t>
+          <t>ui.common.empty</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>图鉴：{0}</t>
+          <t>暂无内容</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Codex: {0}</t>
+          <t>Nothing here yet</t>
         </is>
       </c>
     </row>
@@ -5922,17 +5922,17 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ui.common.disabled_reason</t>
+          <t>ui.common.clear</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>不可用：{0}</t>
+          <t>清空</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Unavailable: {0}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -5940,17 +5940,17 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ui.drag.cancelled</t>
+          <t>ui.common.shortcut</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>已取消拖动</t>
+          <t>快捷键：{0}</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Drag cancelled</t>
+          <t>Shortcut: {0}</t>
         </is>
       </c>
     </row>
@@ -5958,17 +5958,17 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ui.drag.no_target</t>
+          <t>ui.common.codex_link</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>没有放到可放置的位置</t>
+          <t>图鉴：{0}</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Not dropped on a valid target</t>
+          <t>Codex: {0}</t>
         </is>
       </c>
     </row>
@@ -5976,17 +5976,17 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ui.confirm.lose_prefix</t>
+          <t>ui.common.disabled_reason</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>将丢失：</t>
+          <t>不可用：{0}</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>You will lose:</t>
+          <t>Unavailable: {0}</t>
         </is>
       </c>
     </row>
@@ -5994,17 +5994,17 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ui.confirm.irreversible</t>
+          <t>ui.drag.cancelled</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>此操作无法撤销。</t>
+          <t>已取消拖动</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>This cannot be undone.</t>
+          <t>Drag cancelled</t>
         </is>
       </c>
     </row>
@@ -6012,17 +6012,17 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ui.tooltip.pin_hint</t>
+          <t>ui.drag.no_target</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>按住 {0} 固定提示</t>
+          <t>没有放到可放置的位置</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Hold {0} to pin</t>
+          <t>Not dropped on a valid target</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ui.tooltip.pinned</t>
+          <t>ui.confirm.lose_prefix</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>已固定：松开 {0} 或移开鼠标关闭</t>
+          <t>将丢失：</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Pinned: release {0} or move away to close</t>
+          <t>You will lose:</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ui.tooltip.expand_sources</t>
+          <t>ui.confirm.irreversible</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>展开来源</t>
+          <t>此操作无法撤销。</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Show breakdown</t>
+          <t>This cannot be undone.</t>
         </is>
       </c>
     </row>
@@ -6066,17 +6066,17 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>ui.tooltip.collapse_sources</t>
+          <t>ui.tooltip.pin_hint</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>收起来源</t>
+          <t>按住 {0} 固定提示</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Hide breakdown</t>
+          <t>Hold {0} to pin</t>
         </is>
       </c>
     </row>
@@ -6084,17 +6084,17 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>ui.tooltip.total</t>
+          <t>ui.tooltip.pinned</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>合计 {0}</t>
+          <t>已固定：松开 {0} 或移开鼠标关闭</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Total {0}</t>
+          <t>Pinned: release {0} or move away to close</t>
         </is>
       </c>
     </row>
@@ -6102,17 +6102,17 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>ui.notify.title</t>
+          <t>ui.tooltip.expand_sources</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>通知中心</t>
+          <t>展开来源</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Show breakdown</t>
         </is>
       </c>
     </row>
@@ -6120,17 +6120,17 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ui.notify.entry_unread</t>
+          <t>ui.tooltip.collapse_sources</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>收起来源</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Hide breakdown</t>
         </is>
       </c>
     </row>
@@ -6138,17 +6138,17 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>ui.notify.filter_all</t>
+          <t>ui.tooltip.total</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>全部等级</t>
+          <t>合计 {0}</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>All levels</t>
+          <t>Total {0}</t>
         </is>
       </c>
     </row>
@@ -6156,17 +6156,17 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ui.notify.filter_type_all</t>
+          <t>ui.notify.title</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>全部类型</t>
+          <t>通知中心</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>All types</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
@@ -6174,17 +6174,17 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ui.notify.empty</t>
+          <t>ui.notify.entry_unread</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>没有符合条件的通知</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>No matching notifications</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -6192,17 +6192,17 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ui.notify.count</t>
+          <t>ui.notify.filter_all</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>共 {0} 条，显示 {1} 条</t>
+          <t>全部等级</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>{0} total, {1} shown</t>
+          <t>All levels</t>
         </is>
       </c>
     </row>
@@ -6210,17 +6210,17 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ui.notify.locate</t>
+          <t>ui.notify.filter_type_all</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>定位</t>
+          <t>全部类型</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Locate</t>
+          <t>All types</t>
         </is>
       </c>
     </row>
@@ -6228,17 +6228,17 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ui.notify.no_location</t>
+          <t>ui.notify.empty</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>这条通知没有位置</t>
+          <t>没有符合条件的通知</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>This notification has no location</t>
+          <t>No matching notifications</t>
         </is>
       </c>
     </row>
@@ -6246,17 +6246,17 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ui.notify.other_region</t>
+          <t>ui.notify.count</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>位置在另一个区域，回到该区域后再定位</t>
+          <t>共 {0} 条，显示 {1} 条</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>The location is in another region; go there first</t>
+          <t>{0} total, {1} shown</t>
         </is>
       </c>
     </row>
@@ -6264,17 +6264,17 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ui.notify.no_camera</t>
+          <t>ui.notify.locate</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>当前没有可移动的镜头</t>
+          <t>定位</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>No camera is available to move</t>
+          <t>Locate</t>
         </is>
       </c>
     </row>
@@ -6282,17 +6282,17 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ui.notify.expand</t>
+          <t>ui.notify.no_location</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>展开 {0} 条</t>
+          <t>这条通知没有位置</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Show {0}</t>
+          <t>This notification has no location</t>
         </is>
       </c>
     </row>
@@ -6300,17 +6300,17 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ui.notify.collapse</t>
+          <t>ui.notify.other_region</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>收起</t>
+          <t>位置在另一个区域，回到该区域后再定位</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>The location is in another region; go there first</t>
         </is>
       </c>
     </row>
@@ -6318,17 +6318,17 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ui.notify.settings</t>
+          <t>ui.notify.no_camera</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>通知设置</t>
+          <t>当前没有可移动的镜头</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Notification settings</t>
+          <t>No camera is available to move</t>
         </is>
       </c>
     </row>
@@ -6336,17 +6336,17 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ui.notify.auto_pause</t>
+          <t>ui.notify.expand</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>触发时自动暂停</t>
+          <t>展开 {0} 条</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Auto-pause when triggered</t>
+          <t>Show {0}</t>
         </is>
       </c>
     </row>
@@ -6354,17 +6354,17 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ui.notify.duration</t>
+          <t>ui.notify.collapse</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>弹出提示停留：{0}</t>
+          <t>收起</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Pop-up duration: {0}</t>
+          <t>Collapse</t>
         </is>
       </c>
     </row>
@@ -6372,17 +6372,17 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ui.notify.saved_history</t>
+          <t>ui.notify.settings</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>读档变更</t>
+          <t>通知设置</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Load-time changes</t>
+          <t>Notification settings</t>
         </is>
       </c>
     </row>
@@ -6390,17 +6390,17 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>ui.notify.time_day</t>
+          <t>ui.notify.auto_pause</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>第 {0} 日 {1}</t>
+          <t>触发时自动暂停</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Day {0} {1}</t>
+          <t>Auto-pause when triggered</t>
         </is>
       </c>
     </row>
@@ -6408,17 +6408,17 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ui.notify.time_real</t>
+          <t>ui.notify.duration</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>弹出提示停留：{0}</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Pop-up duration: {0}</t>
         </is>
       </c>
     </row>
@@ -6426,17 +6426,17 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>ui.notify.times</t>
+          <t>ui.notify.saved_history</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>×{0}</t>
+          <t>读档变更</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>×{0}</t>
+          <t>Load-time changes</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>ui.notify.source_rule</t>
+          <t>ui.notify.time_day</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>由规则「{0}」触发</t>
+          <t>第 {0} 日 {1}</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Triggered by rule "{0}"</t>
+          <t>Day {0} {1}</t>
         </is>
       </c>
     </row>
@@ -6462,17 +6462,17 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ui.notify.source_system</t>
+          <t>ui.notify.time_real</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>来源：{0}</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Source: {0}</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -6480,17 +6480,17 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>ui.pause.title</t>
+          <t>ui.notify.times</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>×{0}</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>×{0}</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>ui.pause.resume</t>
+          <t>ui.notify.source_rule</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>继续游戏</t>
+          <t>由规则「{0}」触发</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Triggered by rule "{0}"</t>
         </is>
       </c>
     </row>
@@ -6516,17 +6516,17 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>ui.pause.keybinds</t>
+          <t>ui.notify.source_system</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>按键设置</t>
+          <t>来源：{0}</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Key bindings</t>
+          <t>Source: {0}</t>
         </is>
       </c>
     </row>
@@ -6534,17 +6534,17 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ui.pause.notifications</t>
+          <t>ui.pause.title</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>通知中心</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Paused</t>
         </is>
       </c>
     </row>
@@ -6552,17 +6552,17 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ui.pause.save_and_quit</t>
+          <t>ui.pause.resume</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>保存并返回主菜单</t>
+          <t>继续游戏</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Save and return to menu</t>
+          <t>Resume</t>
         </is>
       </c>
     </row>
@@ -6570,17 +6570,17 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ui.pause.quit_title</t>
+          <t>ui.pause.keybinds</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>返回主菜单</t>
+          <t>按键设置</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Return to main menu</t>
+          <t>Key bindings</t>
         </is>
       </c>
     </row>
@@ -6588,17 +6588,17 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ui.pause.quit_line</t>
+          <t>ui.pause.notifications</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>当前进度会先保存到{0}</t>
+          <t>通知中心</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Progress will be saved to {0} first</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
@@ -6606,17 +6606,17 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ui.pause.quit_failed</t>
+          <t>ui.pause.save_and_quit</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>保存失败，已留在游戏中：{0}</t>
+          <t>保存并返回主菜单</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Saving failed; you are still in the game: {0}</t>
+          <t>Save and return to menu</t>
         </is>
       </c>
     </row>
@@ -6624,17 +6624,17 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ui.pause.gallery</t>
+          <t>ui.pause.quit_title</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>界面基础件样例（开发）</t>
+          <t>返回主菜单</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>UI kit gallery (dev)</t>
+          <t>Return to main menu</t>
         </is>
       </c>
     </row>
@@ -6642,17 +6642,17 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>tooltip.power.title</t>
+          <t>ui.pause.quit_line</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>当前进度会先保存到{0}</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Progress will be saved to {0} first</t>
         </is>
       </c>
     </row>
@@ -6660,17 +6660,17 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>tooltip.power.body</t>
+          <t>ui.pause.quit_failed</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>供给来自核心基础供电与发电机；需求按优先级（数字小的先）分配，分不到电的建筑会停机。</t>
+          <t>保存失败，已留在游戏中：{0}</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Supply comes from the core's base output and generators. Demand is served by priority (lower number first); buildings that get no power shut down.</t>
+          <t>Saving failed; you are still in the game: {0}</t>
         </is>
       </c>
     </row>
@@ -6678,17 +6678,17 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>tooltip.power.base_core</t>
+          <t>ui.pause.gallery</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>核心基础供电</t>
+          <t>界面基础件样例（开发）</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Core base output</t>
+          <t>UI kit gallery (dev)</t>
         </is>
       </c>
     </row>
@@ -6696,17 +6696,17 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>tooltip.power.supply_of</t>
+          <t>tooltip.power.title</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>{0} 供电</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>{0} output</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6714,17 +6714,17 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>tooltip.power.demand_of</t>
+          <t>tooltip.power.body</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>{0} 用电（优先级 {1}）</t>
+          <t>供给来自核心基础供电与发电机；需求按优先级（数字小的先）分配，分不到电的建筑会停机。</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>{0} draw (priority {1})</t>
+          <t>Supply comes from the core's base output and generators. Demand is served by priority (lower number first); buildings that get no power shut down.</t>
         </is>
       </c>
     </row>
@@ -6732,17 +6732,17 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>tooltip.power.brownout_of</t>
+          <t>tooltip.power.base_core</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>{0} 用电（优先级 {1}，已停机）</t>
+          <t>核心基础供电</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>{0} draw (priority {1}, shut down)</t>
+          <t>Core base output</t>
         </is>
       </c>
     </row>
@@ -6750,17 +6750,17 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>tooltip.power.surplus</t>
+          <t>tooltip.power.supply_of</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>盈余 {0}</t>
+          <t>{0} 供电</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Surplus {0}</t>
+          <t>{0} output</t>
         </is>
       </c>
     </row>
@@ -6768,17 +6768,17 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>tooltip.power.shortfall</t>
+          <t>tooltip.power.demand_of</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>差额 {0}</t>
+          <t>{0} 用电（优先级 {1}）</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Shortfall {0}</t>
+          <t>{0} draw (priority {1})</t>
         </is>
       </c>
     </row>
@@ -6786,17 +6786,17 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>tooltip.signal.title</t>
+          <t>tooltip.power.brownout_of</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>信号带宽</t>
+          <t>{0} 用电（优先级 {1}，已停机）</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Signal bandwidth</t>
+          <t>{0} draw (priority {1}, shut down)</t>
         </is>
       </c>
     </row>
@@ -6804,17 +6804,17 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>tooltip.signal.body</t>
+          <t>tooltip.power.surplus</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>带宽决定一次远征能带多少台机器，出征准备会按带宽检查。</t>
+          <t>盈余 {0}</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Bandwidth limits how many machines one expedition can take; expedition prep checks it.</t>
+          <t>Surplus {0}</t>
         </is>
       </c>
     </row>
@@ -6822,17 +6822,17 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>tooltip.signal.base</t>
+          <t>tooltip.power.shortfall</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>基础带宽</t>
+          <t>差额 {0}</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Base bandwidth</t>
+          <t>Shortfall {0}</t>
         </is>
       </c>
     </row>
@@ -6840,17 +6840,17 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>tooltip.signal.tower</t>
+          <t>tooltip.signal.title</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>信号塔（通电）</t>
+          <t>信号带宽</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Signal tower (powered)</t>
+          <t>Signal bandwidth</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>tooltip.signal.tower_off</t>
+          <t>tooltip.signal.body</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>信号塔（未通电，不提供带宽）</t>
+          <t>带宽决定一次远征能带多少台机器，出征准备会按带宽检查。</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Signal tower (unpowered, no bandwidth)</t>
+          <t>Bandwidth limits how many machines one expedition can take; expedition prep checks it.</t>
         </is>
       </c>
     </row>
@@ -6876,17 +6876,17 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>tooltip.signal.broadcast_off</t>
+          <t>tooltip.signal.base</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>关闭主动广播</t>
+          <t>基础带宽</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Broadcast turned off</t>
+          <t>Base bandwidth</t>
         </is>
       </c>
     </row>
@@ -6894,17 +6894,17 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>status.working.name</t>
+          <t>tooltip.signal.tower</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>信号塔（通电）</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Signal tower (powered)</t>
         </is>
       </c>
     </row>
@@ -6912,17 +6912,17 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>status.idle.name</t>
+          <t>tooltip.signal.tower_off</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>待机</t>
+          <t>信号塔（未通电，不提供带宽）</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>Signal tower (unpowered, no bandwidth)</t>
         </is>
       </c>
     </row>
@@ -6930,17 +6930,17 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>status.no_material.name</t>
+          <t>tooltip.signal.broadcast_off</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>缺料</t>
+          <t>关闭主动广播</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>No materials</t>
+          <t>Broadcast turned off</t>
         </is>
       </c>
     </row>
@@ -6948,17 +6948,17 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>status.no_power.name</t>
+          <t>status.working.name</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>缺电</t>
+          <t>工作中</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>No power</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -6966,17 +6966,17 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>status.no_fluid.name</t>
+          <t>status.idle.name</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>缺流体</t>
+          <t>待机</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>No fluid</t>
+          <t>Idle</t>
         </is>
       </c>
     </row>
@@ -6984,17 +6984,17 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>status.output_blocked.name</t>
+          <t>status.no_material.name</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>输出堵塞</t>
+          <t>缺料</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Output blocked</t>
+          <t>No materials</t>
         </is>
       </c>
     </row>
@@ -7002,17 +7002,17 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>status.disabled.name</t>
+          <t>status.no_power.name</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>已禁用</t>
+          <t>缺电</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>No power</t>
         </is>
       </c>
     </row>
@@ -7020,17 +7020,17 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>status.damaged.name</t>
+          <t>status.no_fluid.name</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>损坏</t>
+          <t>缺流体</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Damaged</t>
+          <t>No fluid</t>
         </is>
       </c>
     </row>
@@ -7038,17 +7038,17 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>status.destroyed.name</t>
+          <t>status.output_blocked.name</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>已摧毁</t>
+          <t>输出堵塞</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Destroyed</t>
+          <t>Output blocked</t>
         </is>
       </c>
     </row>
@@ -7056,17 +7056,17 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>status.upgrading.name</t>
+          <t>status.disabled.name</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>升级中</t>
+          <t>已禁用</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Upgrading</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -7074,17 +7074,17 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>fmt.wan</t>
+          <t>status.damaged.name</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>{0}万</t>
+          <t>损坏</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -7092,17 +7092,17 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>fmt.thousand</t>
+          <t>status.destroyed.name</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>已摧毁</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>{0}k</t>
+          <t>Destroyed</t>
         </is>
       </c>
     </row>
@@ -7110,17 +7110,17 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>fmt.million</t>
+          <t>status.upgrading.name</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>升级中</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>{0}M</t>
+          <t>Upgrading</t>
         </is>
       </c>
     </row>
@@ -7128,17 +7128,17 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>fmt.per_minute</t>
+          <t>fmt.wan</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>{0}/分钟</t>
+          <t>{0}万</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>{0}/min</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -7146,17 +7146,17 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>fmt.percent</t>
+          <t>fmt.thousand</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>{0}%</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>{0}%</t>
+          <t>{0}k</t>
         </is>
       </c>
     </row>
@@ -7164,17 +7164,17 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>fmt.seconds</t>
+          <t>fmt.million</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>{0} 秒</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>{0}M</t>
         </is>
       </c>
     </row>
@@ -7182,17 +7182,17 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ui.gallery.title</t>
+          <t>fmt.per_minute</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>界面基础件样例</t>
+          <t>{0}/分钟</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>UI kit gallery</t>
+          <t>{0}/min</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7200,17 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ui.gallery.section_notify</t>
+          <t>fmt.percent</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>通知中心</t>
+          <t>{0}%</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Notification center</t>
+          <t>{0}%</t>
         </is>
       </c>
     </row>
@@ -7218,17 +7218,17 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ui.gallery.section_confirm</t>
+          <t>fmt.seconds</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>确认框</t>
+          <t>{0} 秒</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Confirm dialog</t>
+          <t>{0}s</t>
         </is>
       </c>
     </row>
@@ -7236,17 +7236,17 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ui.gallery.section_tooltip</t>
+          <t>ui.gallery.title</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>悬停提示</t>
+          <t>界面基础件样例</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>UI kit gallery</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ui.gallery.section_menu</t>
+          <t>ui.gallery.section_notify</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>右键菜单</t>
+          <t>通知中心</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Context menu</t>
+          <t>Notification center</t>
         </is>
       </c>
     </row>
@@ -7272,17 +7272,17 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ui.gallery.section_drag</t>
+          <t>ui.gallery.section_confirm</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>拖放</t>
+          <t>确认框</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Drag and drop</t>
+          <t>Confirm dialog</t>
         </is>
       </c>
     </row>
@@ -7290,17 +7290,17 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>ui.gallery.section_search</t>
+          <t>ui.gallery.section_tooltip</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>搜索框</t>
+          <t>悬停提示</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Search box</t>
+          <t>Tooltip</t>
         </is>
       </c>
     </row>
@@ -7308,17 +7308,17 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>ui.gallery.section_tabs</t>
+          <t>ui.gallery.section_menu</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>标签页</t>
+          <t>右键菜单</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Context menu</t>
         </is>
       </c>
     </row>
@@ -7326,17 +7326,17 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>ui.gallery.section_list</t>
+          <t>ui.gallery.section_drag</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>虚拟化列表</t>
+          <t>拖放</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Virtualised list</t>
+          <t>Drag and drop</t>
         </is>
       </c>
     </row>
@@ -7344,17 +7344,17 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>ui.gallery.section_chart</t>
+          <t>ui.gallery.section_search</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>图表</t>
+          <t>搜索框</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Search box</t>
         </is>
       </c>
     </row>
@@ -7362,17 +7362,17 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>ui.gallery.section_hint</t>
+          <t>ui.gallery.section_tabs</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>快捷键提示</t>
+          <t>标签页</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Shortcut hints</t>
+          <t>Tabs</t>
         </is>
       </c>
     </row>
@@ -7380,17 +7380,17 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>ui.gallery.section_progress</t>
+          <t>ui.gallery.section_list</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>进度条</t>
+          <t>虚拟化列表</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Progress bars</t>
+          <t>Virtualised list</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7398,17 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>ui.gallery.section_status</t>
+          <t>ui.gallery.section_chart</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>状态图标</t>
+          <t>图表</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Status icons</t>
+          <t>Charts</t>
         </is>
       </c>
     </row>
@@ -7416,17 +7416,17 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>ui.gallery.post_urgent</t>
+          <t>ui.gallery.section_hint</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>发一条紧急</t>
+          <t>快捷键提示</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Post urgent</t>
+          <t>Shortcut hints</t>
         </is>
       </c>
     </row>
@@ -7434,17 +7434,17 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ui.gallery.post_warning</t>
+          <t>ui.gallery.section_progress</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>发一条警告</t>
+          <t>进度条</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Post warning</t>
+          <t>Progress bars</t>
         </is>
       </c>
     </row>
@@ -7452,17 +7452,17 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>ui.gallery.post_info</t>
+          <t>ui.gallery.section_status</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>发一条信息</t>
+          <t>状态图标</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Post info</t>
+          <t>Status icons</t>
         </is>
       </c>
     </row>
@@ -7470,17 +7470,17 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>ui.gallery.post_burst</t>
+          <t>ui.gallery.post_urgent</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>1 秒内发 50 条</t>
+          <t>发一条紧急</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Post 50 in 1 s</t>
+          <t>Post urgent</t>
         </is>
       </c>
     </row>
@@ -7488,17 +7488,17 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>ui.gallery.open_confirm</t>
+          <t>ui.gallery.post_warning</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>打开确认框</t>
+          <t>发一条警告</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Open confirm</t>
+          <t>Post warning</t>
         </is>
       </c>
     </row>
@@ -7506,17 +7506,17 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ui.gallery.confirm_title</t>
+          <t>ui.gallery.post_info</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>拆除建筑</t>
+          <t>发一条信息</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Demolish building</t>
+          <t>Post info</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7524,17 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>ui.gallery.confirm_line</t>
+          <t>ui.gallery.post_burst</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>未装载的战利品 ×{0}</t>
+          <t>1 秒内发 50 条</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Unloaded loot ×{0}</t>
+          <t>Post 50 in 1 s</t>
         </is>
       </c>
     </row>
@@ -7542,17 +7542,17 @@
       <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
-          <t>ui.gallery.tooltip_target</t>
+          <t>ui.gallery.open_confirm</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>悬停查看产量构成</t>
+          <t>打开确认框</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Hover for output breakdown</t>
+          <t>Open confirm</t>
         </is>
       </c>
     </row>
@@ -7560,17 +7560,17 @@
       <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ui.gallery.tooltip_title</t>
+          <t>ui.gallery.confirm_title</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>装配站产量</t>
+          <t>拆除建筑</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Assembly output</t>
+          <t>Demolish building</t>
         </is>
       </c>
     </row>
@@ -7578,17 +7578,17 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>ui.gallery.tooltip_body</t>
+          <t>ui.gallery.confirm_line</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>每分钟产出的机器零件数。</t>
+          <t>未装载的战利品 ×{0}</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Machine parts produced per minute.</t>
+          <t>Unloaded loot ×{0}</t>
         </is>
       </c>
     </row>
@@ -7596,17 +7596,17 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ui.gallery.source_base</t>
+          <t>ui.gallery.tooltip_target</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>基础产量</t>
+          <t>悬停查看产量构成</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Base output</t>
+          <t>Hover for output breakdown</t>
         </is>
       </c>
     </row>
@@ -7614,17 +7614,17 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>ui.gallery.source_power</t>
+          <t>ui.gallery.tooltip_title</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>电力不足</t>
+          <t>装配站产量</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Power shortage</t>
+          <t>Assembly output</t>
         </is>
       </c>
     </row>
@@ -7632,17 +7632,17 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>ui.gallery.source_research</t>
+          <t>ui.gallery.tooltip_body</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>研究加成</t>
+          <t>每分钟产出的机器零件数。</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Research bonus</t>
+          <t>Machine parts produced per minute.</t>
         </is>
       </c>
     </row>
@@ -7650,17 +7650,17 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_target</t>
+          <t>ui.gallery.source_base</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>在这里点右键</t>
+          <t>基础产量</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Right-click here</t>
+          <t>Base output</t>
         </is>
       </c>
     </row>
@@ -7668,17 +7668,17 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_inspect</t>
+          <t>ui.gallery.source_power</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>查看</t>
+          <t>电力不足</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Power shortage</t>
         </is>
       </c>
     </row>
@@ -7686,17 +7686,17 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_rename</t>
+          <t>ui.gallery.source_research</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>改名</t>
+          <t>研究加成</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Research bonus</t>
         </is>
       </c>
     </row>
@@ -7704,17 +7704,17 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_demolish</t>
+          <t>ui.gallery.menu_target</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>拆除</t>
+          <t>在这里点右键</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Demolish</t>
+          <t>Right-click here</t>
         </is>
       </c>
     </row>
@@ -7722,17 +7722,17 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_demolish_reason</t>
+          <t>ui.gallery.menu_inspect</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>核心不能拆除</t>
+          <t>查看</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>The core cannot be demolished</t>
+          <t>Inspect</t>
         </is>
       </c>
     </row>
@@ -7740,17 +7740,17 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>ui.gallery.menu_result</t>
+          <t>ui.gallery.menu_rename</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>选择了：{0}</t>
+          <t>改名</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Chose: {0}</t>
+          <t>Rename</t>
         </is>
       </c>
     </row>
@@ -7758,17 +7758,17 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_source</t>
+          <t>ui.gallery.menu_demolish</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>拖动芯片</t>
+          <t>拆除</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Drag chip</t>
+          <t>Demolish</t>
         </is>
       </c>
     </row>
@@ -7776,17 +7776,17 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_slot</t>
+          <t>ui.gallery.menu_demolish_reason</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>槽位 {0}</t>
+          <t>核心不能拆除</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Slot {0}</t>
+          <t>The core cannot be demolished</t>
         </is>
       </c>
     </row>
@@ -7794,17 +7794,17 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_slot_locked</t>
+          <t>ui.gallery.menu_result</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>锁定槽位</t>
+          <t>选择了：{0}</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Locked slot</t>
+          <t>Chose: {0}</t>
         </is>
       </c>
     </row>
@@ -7812,17 +7812,17 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_locked_reason</t>
+          <t>ui.gallery.drag_source</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>槽位锁定，不能放入</t>
+          <t>拖动芯片</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>The slot is locked</t>
+          <t>Drag chip</t>
         </is>
       </c>
     </row>
@@ -7830,17 +7830,17 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ui.gallery.drag_result</t>
+          <t>ui.gallery.drag_slot</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>放入了 {0}</t>
+          <t>槽位 {0}</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Dropped into {0}</t>
+          <t>Slot {0}</t>
         </is>
       </c>
     </row>
@@ -7848,17 +7848,17 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_a</t>
+          <t>ui.gallery.drag_slot_locked</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>产量</t>
+          <t>锁定槽位</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Locked slot</t>
         </is>
       </c>
     </row>
@@ -7866,17 +7866,17 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_b</t>
+          <t>ui.gallery.drag_locked_reason</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>槽位锁定，不能放入</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>The slot is locked</t>
         </is>
       </c>
     </row>
@@ -7884,17 +7884,17 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_c</t>
+          <t>ui.gallery.drag_result</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>库存</t>
+          <t>放入了 {0}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Dropped into {0}</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>ui.gallery.tab_body</t>
+          <t>ui.gallery.tab_a</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>当前标签：{0}</t>
+          <t>产量</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Current tab: {0}</t>
+          <t>Output</t>
         </is>
       </c>
     </row>
@@ -7920,17 +7920,17 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>ui.gallery.list_row</t>
+          <t>ui.gallery.tab_b</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>条目 {0}</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Entry {0}</t>
+          <t>Use</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>ui.gallery.chart_line</t>
+          <t>ui.gallery.tab_c</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>近 60 秒产量</t>
+          <t>库存</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Output, last 60 s</t>
+          <t>Stock</t>
         </is>
       </c>
     </row>
@@ -7956,17 +7956,17 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ui.gallery.chart_bar</t>
+          <t>ui.gallery.tab_body</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>各类消耗</t>
+          <t>当前标签：{0}</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Use by type</t>
+          <t>Current tab: {0}</t>
         </is>
       </c>
     </row>
@@ -7974,17 +7974,17 @@
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>ui.gallery.progress_label</t>
+          <t>ui.gallery.list_row</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>研究进度</t>
+          <t>条目 {0}</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Research progress</t>
+          <t>Entry {0}</t>
         </is>
       </c>
     </row>
@@ -7992,17 +7992,17 @@
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ui.gallery.progress_step</t>
+          <t>ui.gallery.chart_line</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>推进 10%</t>
+          <t>近 60 秒产量</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Advance 10%</t>
+          <t>Output, last 60 s</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
-          <t>ui.gallery.progress_block</t>
+          <t>ui.gallery.chart_bar</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>切换阻塞</t>
+          <t>各类消耗</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Toggle blocked</t>
+          <t>Use by type</t>
         </is>
       </c>
     </row>
@@ -8028,17 +8028,17 @@
       <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
-          <t>ui.gallery.colorblind</t>
+          <t>ui.gallery.progress_label</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>色盲预览</t>
+          <t>研究进度</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Colour-blind preview</t>
+          <t>Research progress</t>
         </is>
       </c>
     </row>
@@ -8046,17 +8046,17 @@
       <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
-          <t>building.core.desc</t>
+          <t>ui.gallery.progress_step</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>战役的根基。核心被毁即失败；自带基础供电与应急缓存。</t>
+          <t>推进 10%</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>The heart of the campaign. If it falls, the campaign is lost; provides base power and an emergency cache.</t>
+          <t>Advance 10%</t>
         </is>
       </c>
     </row>
@@ -8064,17 +8064,17 @@
       <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
-          <t>building.generator.desc</t>
+          <t>ui.gallery.progress_block</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>运转后提供额外电力。可以建造多座。</t>
+          <t>切换阻塞</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Provides extra power while running. You can build several.</t>
+          <t>Toggle blocked</t>
         </is>
       </c>
     </row>
@@ -8082,17 +8082,17 @@
       <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
-          <t>building.warehouse.desc</t>
+          <t>ui.gallery.colorblind</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>修好后扩充库存容量，并接收远征卸货。</t>
+          <t>色盲预览</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Once repaired, adds storage capacity and receives expedition cargo.</t>
+          <t>Colour-blind preview</t>
         </is>
       </c>
     </row>
@@ -8100,17 +8100,17 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
-          <t>building.signal_tower.desc</t>
+          <t>building.core.desc</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>修好并通电后扩大信号带宽，开放破碎都市远征。</t>
+          <t>战役的根基。核心被毁即失败；自带基础供电与应急缓存。</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>When repaired and powered, raises signal bandwidth and opens expeditions to the Fractured City.</t>
+          <t>The heart of the campaign. If it falls, the campaign is lost; provides base power and an emergency cache.</t>
         </is>
       </c>
     </row>
@@ -8118,17 +8118,17 @@
       <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
-          <t>building.assembly_station.desc</t>
+          <t>building.generator.desc</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>生产与改造机器。</t>
+          <t>运转后提供额外电力。可以建造多座。</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Produces and refits machines.</t>
+          <t>Provides extra power while running. You can build several.</t>
         </is>
       </c>
     </row>
@@ -8136,17 +8136,17 @@
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
-          <t>building.analysis_bench.desc</t>
+          <t>building.warehouse.desc</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>解析带回的技术模块，解锁新内容。</t>
+          <t>修好后扩充库存容量，并接收远征卸货。</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Analyzes recovered tech modules to unlock new content.</t>
+          <t>Once repaired, adds storage capacity and receives expedition cargo.</t>
         </is>
       </c>
     </row>
@@ -8154,17 +8154,17 @@
       <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
-          <t>building.repair_bay.desc</t>
+          <t>building.signal_tower.desc</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>维修机的工作基点。</t>
+          <t>修好并通电后扩大信号带宽，开放破碎都市远征。</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Home base for repair machines.</t>
+          <t>When repaired and powered, raises signal bandwidth and opens expeditions to the Fractured City.</t>
         </is>
       </c>
     </row>
@@ -8172,17 +8172,17 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>building.beacon.desc</t>
+          <t>building.assembly_station.desc</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>返航信标。建成、通电并启动后，战役迎来终局。</t>
+          <t>生产与改造机器。</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>The homing beacon. Build, power and launch it to reach the campaign's finale.</t>
+          <t>Produces and refits machines.</t>
         </is>
       </c>
     </row>
@@ -8190,17 +8190,17 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>grid.terrain.buildable.name</t>
+          <t>building.analysis_bench.desc</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>空地</t>
+          <t>解析带回的技术模块，解锁新内容。</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Open ground</t>
+          <t>Analyzes recovered tech modules to unlock new content.</t>
         </is>
       </c>
     </row>
@@ -8208,17 +8208,17 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>grid.terrain.water.name</t>
+          <t>building.repair_bay.desc</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>水源</t>
+          <t>维修机的工作基点。</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Home base for repair machines.</t>
         </is>
       </c>
     </row>
@@ -8226,17 +8226,17 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
-          <t>grid.terrain.oil.name</t>
+          <t>building.beacon.desc</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>油井</t>
+          <t>返航信标。建成、通电并启动后，战役迎来终局。</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Oil well</t>
+          <t>The homing beacon. Build, power and launch it to reach the campaign's finale.</t>
         </is>
       </c>
     </row>
@@ -8244,17 +8244,17 @@
       <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
-          <t>grid.terrain.ore_metal.name</t>
+          <t>grid.terrain.buildable.name</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>金属矿脉</t>
+          <t>空地</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Metal vein</t>
+          <t>Open ground</t>
         </is>
       </c>
     </row>
@@ -8262,17 +8262,17 @@
       <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
-          <t>grid.terrain.ore_rare.name</t>
+          <t>grid.terrain.water.name</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>稀土矿脉</t>
+          <t>水源</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Rare-earth vein</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -8280,17 +8280,17 @@
       <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
-          <t>grid.terrain.ruin.name</t>
+          <t>grid.terrain.oil.name</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>废墟</t>
+          <t>油井</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Ruins</t>
+          <t>Oil well</t>
         </is>
       </c>
     </row>
@@ -8298,17 +8298,17 @@
       <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>grid.terrain.cliff.name</t>
+          <t>grid.terrain.ore_metal.name</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>悬崖</t>
+          <t>金属矿脉</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Cliff</t>
+          <t>Metal vein</t>
         </is>
       </c>
     </row>
@@ -8316,17 +8316,17 @@
       <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>grid.dir.n</t>
+          <t>grid.terrain.ore_rare.name</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>北</t>
+          <t>稀土矿脉</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Rare-earth vein</t>
         </is>
       </c>
     </row>
@@ -8334,17 +8334,17 @@
       <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
-          <t>grid.dir.e</t>
+          <t>grid.terrain.ruin.name</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>东</t>
+          <t>废墟</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Ruins</t>
         </is>
       </c>
     </row>
@@ -8352,17 +8352,17 @@
       <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
-          <t>grid.dir.s</t>
+          <t>grid.terrain.cliff.name</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>南</t>
+          <t>悬崖</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Cliff</t>
         </is>
       </c>
     </row>
@@ -8370,17 +8370,17 @@
       <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
-          <t>grid.dir.w</t>
+          <t>grid.dir.n</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>西</t>
+          <t>北</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -8388,17 +8388,17 @@
       <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
-          <t>grid.port.in</t>
+          <t>grid.dir.e</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>输入</t>
+          <t>东</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -8406,17 +8406,17 @@
       <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
-          <t>grid.port.out</t>
+          <t>grid.dir.s</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>输出</t>
+          <t>南</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -8424,17 +8424,17 @@
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
-          <t>grid.port.entry</t>
+          <t>grid.dir.w</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>{0}（朝{1}）</t>
+          <t>西</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>{0} (facing {1})</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -8442,17 +8442,17 @@
       <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
-          <t>grid.reason.occupied</t>
+          <t>grid.port.in</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>已被“{0}”占用</t>
+          <t>输入</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Occupied by {0}</t>
+          <t>Input</t>
         </is>
       </c>
     </row>
@@ -8460,17 +8460,17 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>grid.reason.occupied_belt</t>
+          <t>grid.port.out</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>已被传送带占用</t>
+          <t>输出</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Occupied by a belt</t>
+          <t>Output</t>
         </is>
       </c>
     </row>
@@ -8478,17 +8478,17 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>grid.reason.occupied_pipe</t>
+          <t>grid.port.entry</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>已被管线占用</t>
+          <t>{0}（朝{1}）</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Occupied by a pipe</t>
+          <t>{0} (facing {1})</t>
         </is>
       </c>
     </row>
@@ -8496,17 +8496,17 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>grid.reason.obstacle</t>
+          <t>grid.reason.occupied</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>被“{0}”挡住</t>
+          <t>已被“{0}”占用</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Blocked by {0}</t>
+          <t>Occupied by {0}</t>
         </is>
       </c>
     </row>
@@ -8514,17 +8514,17 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>grid.obstacle.wreckage</t>
+          <t>grid.reason.occupied_belt</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>残骸</t>
+          <t>已被传送带占用</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Wreckage</t>
+          <t>Occupied by a belt</t>
         </is>
       </c>
     </row>
@@ -8532,17 +8532,17 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>grid.obstacle.target</t>
+          <t>grid.reason.occupied_pipe</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>残骸靶</t>
+          <t>已被管线占用</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Target wreck</t>
+          <t>Occupied by a pipe</t>
         </is>
       </c>
     </row>
@@ -8550,17 +8550,17 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>grid.obstacle.exit</t>
+          <t>grid.reason.obstacle</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>出口通道</t>
+          <t>被“{0}”挡住</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Exit lane</t>
+          <t>Blocked by {0}</t>
         </is>
       </c>
     </row>
@@ -8568,17 +8568,17 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>grid.reason.terrain</t>
+          <t>grid.obstacle.wreckage</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>地形不符：{0}上不能建造</t>
+          <t>残骸</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Unsuitable terrain: cannot build on {0}</t>
+          <t>Wreckage</t>
         </is>
       </c>
     </row>
@@ -8586,17 +8586,17 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>grid.reason.needs_terrain</t>
+          <t>grid.obstacle.target</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>需要放在{0}上</t>
+          <t>残骸靶</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Must be placed on {0}</t>
+          <t>Target wreck</t>
         </is>
       </c>
     </row>
@@ -8604,17 +8604,17 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>grid.reason.pollution</t>
+          <t>grid.obstacle.exit</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>污染过重（{0} 级），需要先净化</t>
+          <t>出口通道</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Pollution too high (level {0}); purify it first</t>
+          <t>Exit lane</t>
         </is>
       </c>
     </row>
@@ -8622,17 +8622,17 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>grid.reason.fog</t>
+          <t>grid.reason.terrain</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>超出已探索区域</t>
+          <t>地形不符：{0}上不能建造</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Outside the explored area</t>
+          <t>Unsuitable terrain: cannot build on {0}</t>
         </is>
       </c>
     </row>
@@ -8640,17 +8640,17 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>grid.reason.core_reserve</t>
+          <t>grid.reason.needs_terrain</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>归还核心周围 {0} 格是通道，不能建造</t>
+          <t>需要放在{0}上</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>The {0} tiles around the Reclamation Core are a passage and cannot be built on</t>
+          <t>Must be placed on {0}</t>
         </is>
       </c>
     </row>
@@ -8658,17 +8658,17 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>grid.reason.max_count</t>
+          <t>grid.reason.pollution</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>已达到数量上限（{0} 座）</t>
+          <t>污染过重（{0} 级），需要先净化</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Limit reached ({0})</t>
+          <t>Pollution too high (level {0}); purify it first</t>
         </is>
       </c>
     </row>
@@ -8676,17 +8676,17 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>grid.reason.locked</t>
+          <t>grid.reason.fog</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>尚未解锁：{0}</t>
+          <t>超出已探索区域</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Locked: {0}</t>
+          <t>Outside the explored area</t>
         </is>
       </c>
     </row>
@@ -8694,17 +8694,17 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>grid.reason.not_placeable</t>
+          <t>grid.reason.core_reserve</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>这种建筑不能手动放置</t>
+          <t>归还核心周围 {0} 格是通道，不能建造</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>This building cannot be placed manually</t>
+          <t>The {0} tiles around the Reclamation Core are a passage and cannot be built on</t>
         </is>
       </c>
     </row>
@@ -8712,17 +8712,17 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>grid.reason.unknown_type</t>
+          <t>grid.reason.max_count</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>未知的建筑类型</t>
+          <t>已达到数量上限（{0} 座）</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Unknown building type</t>
+          <t>Limit reached ({0})</t>
         </is>
       </c>
     </row>
@@ -8730,17 +8730,17 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>grid.reason.insufficient_scrap</t>
+          <t>grid.reason.locked</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>废料不足：需要 {0}，现有 {1}</t>
+          <t>尚未解锁：{0}</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Not enough scrap: need {0}, have {1}</t>
+          <t>Locked: {0}</t>
         </is>
       </c>
     </row>
@@ -8748,17 +8748,17 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>grid.reason.no_building</t>
+          <t>grid.reason.not_placeable</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>这里没有建筑</t>
+          <t>这种建筑不能手动放置</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>There is no building here</t>
+          <t>This building cannot be placed manually</t>
         </is>
       </c>
     </row>
@@ -8766,17 +8766,17 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>grid.reason.cannot_demolish_core</t>
+          <t>grid.reason.unknown_type</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>归还核心不能拆除</t>
+          <t>未知的建筑类型</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>The Reclamation Core cannot be demolished</t>
+          <t>Unknown building type</t>
         </is>
       </c>
     </row>
@@ -8784,17 +8784,17 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>grid.reason.demolish_damaged</t>
+          <t>grid.reason.insufficient_scrap</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>受损的建筑不能拆除，请先修复</t>
+          <t>废料不足：需要 {0}，现有 {1}</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Damaged buildings cannot be demolished; repair it first</t>
+          <t>Not enough scrap: need {0}, have {1}</t>
         </is>
       </c>
     </row>
@@ -8802,17 +8802,17 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>grid.reason.busy</t>
+          <t>grid.reason.no_building</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>这座建筑正在施工或维修，完成后再操作</t>
+          <t>这里没有建筑</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>This building is under construction or repair; try again when it is done</t>
+          <t>There is no building here</t>
         </is>
       </c>
     </row>
@@ -8820,17 +8820,17 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>grid.reason.cannot_rotate_core</t>
+          <t>grid.reason.cannot_demolish_core</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>归还核心不能旋转</t>
+          <t>归还核心不能拆除</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>The Reclamation Core cannot be rotated</t>
+          <t>The Reclamation Core cannot be demolished</t>
         </is>
       </c>
     </row>
@@ -8838,17 +8838,17 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>grid.reason.not_rebuildable</t>
+          <t>grid.reason.demolish_damaged</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>这座建筑无法重建，不能拆除</t>
+          <t>受损的建筑不能拆除，请先修复</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>This building cannot be rebuilt, so it cannot be demolished</t>
+          <t>Damaged buildings cannot be demolished; repair it first</t>
         </is>
       </c>
     </row>
@@ -8856,17 +8856,17 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>grid.reason.no_region</t>
+          <t>grid.reason.busy</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>只有在家园里才能建造</t>
+          <t>这座建筑正在施工或维修，完成后再操作</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>You can only build at home</t>
+          <t>This building is under construction or repair; try again when it is done</t>
         </is>
       </c>
     </row>
@@ -8874,17 +8874,17 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>grid.reason.cannot_rotate_core</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>开局即可建造</t>
+          <t>归还核心不能旋转</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Available from the start</t>
+          <t>The Reclamation Core cannot be rotated</t>
         </is>
       </c>
     </row>
@@ -8892,17 +8892,17 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>grid.unlock.beacon</t>
+          <t>grid.reason.not_rebuildable</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>摧毁铸造前哨主核心并带回核心数据后解锁</t>
+          <t>这座建筑无法重建，不能拆除</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Unlocked after destroying the Foundry Outpost main core and bringing back its data</t>
+          <t>This building cannot be rebuilt, so it cannot be demolished</t>
         </is>
       </c>
     </row>
@@ -8910,17 +8910,17 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>ui.build.title</t>
+          <t>grid.reason.no_region</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>建造</t>
+          <t>只有在家园里才能建造</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>You can only build at home</t>
         </is>
       </c>
     </row>
@@ -8928,17 +8928,17 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>ui.build.entry</t>
+          <t>grid.unlock.always</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>建造（{0}）</t>
+          <t>开局即可建造</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Build ({0})</t>
+          <t>Available from the start</t>
         </is>
       </c>
     </row>
@@ -8946,17 +8946,17 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>ui.build.demolish</t>
+          <t>grid.unlock.beacon</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>拆除模式（{0}）</t>
+          <t>摧毁铸造前哨主核心并带回核心数据后解锁</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Demolish ({0})</t>
+          <t>Unlocked after destroying the Foundry Outpost main core and bringing back its data</t>
         </is>
       </c>
     </row>
@@ -8964,17 +8964,17 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>ui.build.rotate</t>
+          <t>ui.build.title</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>旋转（{0}）</t>
+          <t>建造</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Rotate ({0})</t>
+          <t>Build</t>
         </is>
       </c>
     </row>
@@ -8982,17 +8982,17 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>ui.build.exit</t>
+          <t>ui.build.entry</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>建造（{0}）</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Build ({0})</t>
         </is>
       </c>
     </row>
@@ -9000,17 +9000,17 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>ui.build.empty</t>
+          <t>ui.build.demolish</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>当前没有可以建造的建筑</t>
+          <t>拆除模式（{0}）</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Nothing is available to build yet</t>
+          <t>Demolish ({0})</t>
         </is>
       </c>
     </row>
@@ -9018,17 +9018,17 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>ui.build.cost</t>
+          <t>ui.build.rotate</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>{0} 废料 · {1} 秒</t>
+          <t>旋转（{0}）</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>{0} scrap · {1}s</t>
+          <t>Rotate ({0})</t>
         </is>
       </c>
     </row>
@@ -9036,17 +9036,17 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>ui.build.count_limited</t>
+          <t>ui.build.exit</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>已有 {0}/{1}</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Built {0}/{1}</t>
+          <t>Exit</t>
         </is>
       </c>
     </row>
@@ -9054,17 +9054,17 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>ui.build.count_unlimited</t>
+          <t>ui.build.empty</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>已有 {0}</t>
+          <t>当前没有可以建造的建筑</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Built {0}</t>
+          <t>Nothing is available to build yet</t>
         </is>
       </c>
     </row>
@@ -9072,17 +9072,17 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>ui.build.hint_idle</t>
+          <t>ui.build.cost</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>选择要建造的建筑。指着已有建筑按 {0} 旋转，按 {1} 进入拆除模式，Esc 退出。</t>
+          <t>{0} 废料 · {1} 秒</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Pick a building. Point at a building and press {0} to rotate it, {1} for demolish mode, Esc to exit.</t>
+          <t>{0} scrap · {1}s</t>
         </is>
       </c>
     </row>
@@ -9090,17 +9090,17 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>ui.build.hint_place</t>
+          <t>ui.build.count_limited</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>左键放置 · {0} 旋转 · 右键取消 · Esc 退出</t>
+          <t>已有 {0}/{1}</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Left-click to place · {0} rotate · Right-click cancel · Esc exit</t>
+          <t>Built {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -9108,17 +9108,17 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>ui.build.hint_demolish</t>
+          <t>ui.build.count_unlimited</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>左键标记拆除，再点一次取消标记 · 右键返回 · Esc 退出</t>
+          <t>已有 {0}</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Left-click to mark for demolition, again to unmark · Right-click back · Esc exit</t>
+          <t>Built {0}</t>
         </is>
       </c>
     </row>
@@ -9126,17 +9126,17 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>ui.build.valid</t>
+          <t>ui.build.hint_idle</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>可以放置：{0}，朝{1}</t>
+          <t>选择要建造的建筑。指着已有建筑按 {0} 旋转，按 {1} 进入拆除模式，Esc 退出。</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Can place: {0}, facing {1}</t>
+          <t>Pick a building. Point at a building and press {0} to rotate it, {1} for demolish mode, Esc to exit.</t>
         </is>
       </c>
     </row>
@@ -9144,17 +9144,17 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>ui.build.invalid</t>
+          <t>ui.build.hint_place</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>不能放置：{0}</t>
+          <t>左键放置 · {0} 旋转 · 右键取消 · Esc 退出</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Cannot place: {0}</t>
+          <t>Left-click to place · {0} rotate · Right-click cancel · Esc exit</t>
         </is>
       </c>
     </row>
@@ -9162,17 +9162,17 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>ui.build.invalid_rotate</t>
+          <t>ui.build.hint_demolish</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>不能旋转：{0}</t>
+          <t>左键标记拆除，再点一次取消标记 · 右键返回 · Esc 退出</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Cannot rotate: {0}</t>
+          <t>Left-click to mark for demolition, again to unmark · Right-click back · Esc exit</t>
         </is>
       </c>
     </row>
@@ -9180,17 +9180,17 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>ui.build.hover_building</t>
+          <t>ui.build.valid</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>{0}（朝{1}）</t>
+          <t>可以放置：{0}，朝{1}</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>{0} (facing {1})</t>
+          <t>Can place: {0}, facing {1}</t>
         </is>
       </c>
     </row>
@@ -9198,17 +9198,17 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>ui.build.ports</t>
+          <t>ui.build.invalid</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>端口：{0}</t>
+          <t>不能放置：{0}</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Ports: {0}</t>
+          <t>Cannot place: {0}</t>
         </is>
       </c>
     </row>
@@ -9216,17 +9216,17 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>ui.build.no_ports</t>
+          <t>ui.build.invalid_rotate</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>端口：无</t>
+          <t>不能旋转：{0}</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Ports: none</t>
+          <t>Cannot rotate: {0}</t>
         </is>
       </c>
     </row>
@@ -9234,17 +9234,17 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>ui.build.placed</t>
+          <t>ui.build.hover_building</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>已规划：{0}，等待机器施工</t>
+          <t>{0}（朝{1}）</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Planned: {0}; waiting for a machine to build it</t>
+          <t>{0} (facing {1})</t>
         </is>
       </c>
     </row>
@@ -9252,17 +9252,17 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>ui.build.demolish_marked</t>
+          <t>ui.build.ports</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>已标记拆除：{0}</t>
+          <t>端口：{0}</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Marked for demolition: {0}</t>
+          <t>Ports: {0}</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>ui.build.demolish_unmarked</t>
+          <t>ui.build.no_ports</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>已取消拆除：{0}</t>
+          <t>端口：无</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Demolition cancelled: {0}</t>
+          <t>Ports: none</t>
         </is>
       </c>
     </row>
@@ -9288,17 +9288,17 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>ui.build.plan_cancelled</t>
+          <t>ui.build.placed</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>已取消规划：{0}，废料已全额退回</t>
+          <t>已规划：{0}，等待机器施工</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Plan cancelled: {0}; scrap fully refunded</t>
+          <t>Planned: {0}; waiting for a machine to build it</t>
         </is>
       </c>
     </row>
@@ -9306,17 +9306,17 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>ui.build.rotated</t>
+          <t>ui.build.demolish_marked</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>已旋转：{0}，现在朝{1}</t>
+          <t>已标记拆除：{0}</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Rotated: {0}, now facing {1}</t>
+          <t>Marked for demolition: {0}</t>
         </is>
       </c>
     </row>
@@ -9324,17 +9324,17 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>ui.build.confirm_title</t>
+          <t>ui.build.demolish_unmarked</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>拆除{0}？</t>
+          <t>已取消拆除：{0}</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Demolish {0}?</t>
+          <t>Demolition cancelled: {0}</t>
         </is>
       </c>
     </row>
@@ -9342,17 +9342,17 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>ui.build.confirm_refund</t>
+          <t>ui.build.plan_cancelled</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>返还 {0} 废料（实际投入的一半）</t>
+          <t>已取消规划：{0}，废料已全额退回</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Refunds {0} scrap (half of what was invested)</t>
+          <t>Plan cancelled: {0}; scrap fully refunded</t>
         </is>
       </c>
     </row>
@@ -9360,17 +9360,17 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>ui.build.confirm_critical</t>
+          <t>ui.build.rotated</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>这是关键建筑，拆除后相关功能会停用</t>
+          <t>已旋转：{0}，现在朝{1}</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>This is a key building; its functions stop once demolished</t>
+          <t>Rotated: {0}, now facing {1}</t>
         </is>
       </c>
     </row>
@@ -9378,17 +9378,17 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>ui.build.confirm_ok</t>
+          <t>ui.build.confirm_title</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>拆除</t>
+          <t>拆除{0}？</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Demolish</t>
+          <t>Demolish {0}?</t>
         </is>
       </c>
     </row>
@@ -9396,17 +9396,17 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ui.build.confirm_cancel</t>
+          <t>ui.build.confirm_refund</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>返还 {0} 废料（实际投入的一半）</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Refunds {0} scrap (half of what was invested)</t>
         </is>
       </c>
     </row>
@@ -9414,17 +9414,17 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ui.build.locked_tip</t>
+          <t>ui.build.confirm_critical</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>尚未解锁：{0}</t>
+          <t>这是关键建筑，拆除后相关功能会停用</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Locked: {0}</t>
+          <t>This is a key building; its functions stop once demolished</t>
         </is>
       </c>
     </row>
@@ -9432,17 +9432,17 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>ui.build.placeholder_note</t>
+          <t>ui.build.confirm_ok</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>建筑外形是占位方块（美术待替换）</t>
+          <t>拆除</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Building shapes are placeholder blocks (art pending)</t>
+          <t>Demolish</t>
         </is>
       </c>
     </row>
@@ -9450,17 +9450,17 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>world.surface.earth.name</t>
+          <t>ui.build.confirm_cancel</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Keep</t>
         </is>
       </c>
     </row>
@@ -9468,17 +9468,17 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>world.surface.relay_hall.name</t>
+          <t>ui.build.locked_tip</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>地下中继大厅</t>
+          <t>尚未解锁：{0}</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Underground Relay Hall</t>
+          <t>Locked: {0}</t>
         </is>
       </c>
     </row>
@@ -9486,17 +9486,17 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>world.surface.data_center.name</t>
+          <t>ui.build.placeholder_note</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>数据中心</t>
+          <t>建筑外形是占位方块（美术待替换）</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Data Center</t>
+          <t>Building shapes are placeholder blocks (art pending)</t>
         </is>
       </c>
     </row>
@@ -9504,17 +9504,17 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>world.territory.silent.name</t>
+          <t>world.surface.earth.name</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>静默·破碎都市</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Silent · Fractured City</t>
+          <t>Earth</t>
         </is>
       </c>
     </row>
@@ -9522,17 +9522,17 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>world.territory.foundry.name</t>
+          <t>world.surface.relay_hall.name</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>铸造·铸造前哨</t>
+          <t>地下中继大厅</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Foundry · Foundry Outpost</t>
+          <t>Underground Relay Hall</t>
         </is>
       </c>
     </row>
@@ -9540,17 +9540,17 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>world.territory.clarity.name</t>
+          <t>world.surface.data_center.name</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>澄净·沉淀湖</t>
+          <t>数据中心</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Clarity · Sediment Lake</t>
+          <t>Data Center</t>
         </is>
       </c>
     </row>
@@ -9558,17 +9558,17 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>world.territory.overclock.name</t>
+          <t>world.territory.silent.name</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>超频·热寂数据城</t>
+          <t>静默·破碎都市</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Overclock · Heat-Death Data City</t>
+          <t>Silent · Fractured City</t>
         </is>
       </c>
     </row>
@@ -9576,17 +9576,17 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>world.territory.white_tide.name</t>
+          <t>world.territory.foundry.name</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>白潮滩头</t>
+          <t>铸造·铸造前哨</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>White Tide Beachhead</t>
+          <t>Foundry · Foundry Outpost</t>
         </is>
       </c>
     </row>
@@ -9594,17 +9594,17 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>world.hazard.none</t>
+          <t>world.territory.clarity.name</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>澄净·沉淀湖</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clarity · Sediment Lake</t>
         </is>
       </c>
     </row>
@@ -9612,17 +9612,17 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>world.hazard.acid</t>
+          <t>world.territory.overclock.name</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>酸沼带</t>
+          <t>超频·热寂数据城</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Acid marsh</t>
+          <t>Overclock · Heat-Death Data City</t>
         </is>
       </c>
     </row>
@@ -9630,17 +9630,17 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>world.hazard.heat</t>
+          <t>world.territory.white_tide.name</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>高温辐射带</t>
+          <t>白潮滩头</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Heat radiation belt</t>
+          <t>White Tide Beachhead</t>
         </is>
       </c>
     </row>
@@ -9648,17 +9648,17 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>world.preset.default.name</t>
+          <t>world.hazard.none</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9666,17 +9666,17 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>world.legacy_terrain</t>
+          <t>world.hazard.acid</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>原型地形（旧存档）</t>
+          <t>酸沼带</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Prototype terrain (older save)</t>
+          <t>Acid marsh</t>
         </is>
       </c>
     </row>
@@ -9684,17 +9684,17 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>ui.world.generating</t>
+          <t>world.hazard.heat</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>正在生成地形（{0} 个区块）…</t>
+          <t>高温辐射带</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Generating terrain ({0} chunks)…</t>
+          <t>Heat radiation belt</t>
         </is>
       </c>
     </row>
@@ -9702,17 +9702,17 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>grid.reason.world_limit</t>
+          <t>world.preset.default.name</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>超出世界范围（离原点最多 {0} 格）</t>
+          <t>标准</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Outside the world (at most {0} tiles from the origin)</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -9720,17 +9720,17 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>ui.pause.world_seed</t>
+          <t>world.legacy_terrain</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>世界种子：{0}</t>
+          <t>原型地形（旧存档）</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>World seed: {0}</t>
+          <t>Prototype terrain (older save)</t>
         </is>
       </c>
     </row>
@@ -9738,17 +9738,17 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>ui.pause.copy_seed</t>
+          <t>ui.world.generating</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>复制种子</t>
+          <t>正在生成地形（{0} 个区块）…</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Copy seed</t>
+          <t>Generating terrain ({0} chunks)…</t>
         </is>
       </c>
     </row>
@@ -9756,17 +9756,17 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>ui.pause.seed_copied</t>
+          <t>grid.reason.world_limit</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>已复制种子 {0}</t>
+          <t>超出世界范围（离原点最多 {0} 格）</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Seed {0} copied</t>
+          <t>Outside the world (at most {0} tiles from the origin)</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,17 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>ui.pause.world_settings</t>
+          <t>ui.pause.world_seed</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>世界设置：{0} · 生成器 v{1} · {2}</t>
+          <t>世界种子：{0}</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>World settings: {0} · generator v{1} · {2}</t>
+          <t>World seed: {0}</t>
         </is>
       </c>
     </row>
@@ -9792,17 +9792,17 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>save.card.world</t>
+          <t>ui.pause.copy_seed</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>世界 {0}</t>
+          <t>复制种子</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>World {0}</t>
+          <t>Copy seed</t>
         </is>
       </c>
     </row>
@@ -9810,17 +9810,17 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>ui.world.day_time</t>
+          <t>ui.pause.seed_copied</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>第 {0} 日 {1}</t>
+          <t>已复制种子 {0}</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Day {0} {1}</t>
+          <t>Seed {0} copied</t>
         </is>
       </c>
     </row>
@@ -9828,17 +9828,17 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
-          <t>ui.world.speed</t>
+          <t>ui.pause.world_settings</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>{0}x</t>
+          <t>世界设置：{0} · 生成器 v{1} · {2}</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>{0}x</t>
+          <t>World settings: {0} · generator v{1} · {2}</t>
         </is>
       </c>
     </row>
@@ -9846,17 +9846,17 @@
       <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>ui.world.pause</t>
+          <t>save.card.world</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>世界 {0}</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>World {0}</t>
         </is>
       </c>
     </row>
@@ -9864,17 +9864,17 @@
       <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
-          <t>ui.world.resume</t>
+          <t>ui.world.day_time</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>第 {0} 日 {1}</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Day {0} {1}</t>
         </is>
       </c>
     </row>
@@ -9882,17 +9882,17 @@
       <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
-          <t>ui.world.status_paused</t>
+          <t>ui.world.speed</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>已暂停</t>
+          <t>{0}x</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>{0}x</t>
         </is>
       </c>
     </row>
@@ -9900,17 +9900,17 @@
       <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
-          <t>ui.world.status_running</t>
+          <t>ui.world.pause</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>运行中 {0}</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Running {0}</t>
+          <t>Pause</t>
         </is>
       </c>
     </row>
@@ -9918,17 +9918,17 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>ui.world.status_direct_locked</t>
+          <t>ui.world.resume</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>接入中：世界锁定 1x</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Uplinked: world locked at 1x</t>
+          <t>Resume</t>
         </is>
       </c>
     </row>
@@ -9936,17 +9936,17 @@
       <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
-          <t>ui.world.tip.time</t>
+          <t>ui.world.status_paused</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>游戏时间：第 {0} 日 {1}（1 个游戏日 = 1x 下 {2} 分钟）</t>
+          <t>已暂停</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Game time: day {0} {1} (1 game day = {2} min at 1x)</t>
+          <t>Paused</t>
         </is>
       </c>
     </row>
@@ -9954,17 +9954,17 @@
       <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
-          <t>ui.world.tip.speed</t>
+          <t>ui.world.status_running</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>整个世界的速度 {0}（{1}）。家园、远征、行进中的突袭同时加速，结果与 1x 相同</t>
+          <t>运行中 {0}</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>World speed {0} ({1}). Home, expeditions and raids on the move all speed up together; results match 1x</t>
+          <t>Running {0}</t>
         </is>
       </c>
     </row>
@@ -9972,17 +9972,17 @@
       <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
-          <t>ui.world.tip.pause</t>
+          <t>ui.world.status_direct_locked</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>暂停 / 继续整个世界（{0}）。暂停时仍可选择、下令、规划建造</t>
+          <t>接入中：世界锁定 1x</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Pause / resume the whole world ({0}). While paused you can still select, order and plan construction</t>
+          <t>Uplinked: world locked at 1x</t>
         </is>
       </c>
     </row>
@@ -9990,17 +9990,17 @@
       <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
-          <t>ui.world.tip.direct_locked</t>
+          <t>ui.world.tip.time</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>接入一台机器时，整个世界固定以 1x 运行；退出接入后恢复所选速度</t>
+          <t>游戏时间：第 {0} 日 {1}（1 个游戏日 = 1x 下 {2} 分钟）</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>While uplinked to a machine the whole world runs at 1x; your chosen speed returns when you leave</t>
+          <t>Game time: day {0} {1} (1 game day = {2} min at 1x)</t>
         </is>
       </c>
     </row>
@@ -10008,17 +10008,17 @@
       <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
-          <t>ui.world.focus.title</t>
+          <t>ui.world.tip.speed</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>关注点</t>
+          <t>整个世界的速度 {0}（{1}）。家园、远征、行进中的突袭同时加速，结果与 1x 相同</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>World speed {0} ({1}). Home, expeditions and raids on the move all speed up together; results match 1x</t>
         </is>
       </c>
     </row>
@@ -10026,17 +10026,17 @@
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
-          <t>ui.world.focus.home</t>
+          <t>ui.world.tip.pause</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>家园</t>
+          <t>暂停 / 继续整个世界（{0}）。暂停时仍可选择、下令、规划建造</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Pause / resume the whole world ({0}). While paused you can still select, order and plan construction</t>
         </is>
       </c>
     </row>
@@ -10044,17 +10044,17 @@
       <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
-          <t>ui.world.focus.expedition</t>
+          <t>ui.world.tip.direct_locked</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>远征·{0}（{1} 台）</t>
+          <t>接入一台机器时，整个世界固定以 1x 运行；退出接入后恢复所选速度</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Expedition · {0} ({1})</t>
+          <t>While uplinked to a machine the whole world runs at 1x; your chosen speed returns when you leave</t>
         </is>
       </c>
     </row>
@@ -10062,17 +10062,17 @@
       <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
-          <t>ui.world.focus.raid</t>
+          <t>ui.world.focus.title</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>突袭 ×{0}（约 {1} 后到达）</t>
+          <t>关注点</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Raid ×{0} (arrives in ~{1})</t>
+          <t>Focus</t>
         </is>
       </c>
     </row>
@@ -10080,17 +10080,17 @@
       <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
-          <t>ui.world.focus.raid_arrived</t>
+          <t>ui.world.focus.home</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>突袭 ×{0}（已到达）</t>
+          <t>家园</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Raid ×{0} (arrived)</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -10098,17 +10098,17 @@
       <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
-          <t>ui.world.focus.current</t>
+          <t>ui.world.focus.expedition</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>▸ {0}</t>
+          <t>远征·{0}（{1} 台）</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>▸ {0}</t>
+          <t>Expedition · {0} ({1})</t>
         </is>
       </c>
     </row>
@@ -10116,17 +10116,17 @@
       <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
-          <t>ui.world.focus.tip</t>
+          <t>ui.world.focus.raid</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>镜头飞到这里（{0} 依次切换关注点，{1} 回到归还核心）。整个世界一直在运行，镜头只决定你看哪里</t>
+          <t>突袭 ×{0}（约 {1} 后到达）</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Fly the camera here ({0} cycles focus, {1} returns to the Reclamation Core). The whole world keeps running; the camera only decides what you watch</t>
+          <t>Raid ×{0} (arrives in ~{1})</t>
         </is>
       </c>
     </row>
@@ -10134,17 +10134,17 @@
       <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
-          <t>ui.world.eta</t>
+          <t>ui.world.focus.raid_arrived</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>{0} 小时 {1} 分（游戏时间）</t>
+          <t>突袭 ×{0}（已到达）</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>{0} h {1} min (game time)</t>
+          <t>Raid ×{0} (arrived)</t>
         </is>
       </c>
     </row>
@@ -10152,17 +10152,17 @@
       <c r="A541" t="inlineStr"/>
       <c r="B541" t="inlineStr">
         <is>
-          <t>ui.world.site_unloaded</t>
+          <t>ui.world.focus.current</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>该地点已不在运行（远征已结束），无法定位</t>
+          <t>▸ {0}</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>That place is no longer active (the expedition has ended)</t>
+          <t>▸ {0}</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       <c r="A542" t="inlineStr"/>
       <c r="B542" t="inlineStr">
         <is>
-          <t>ui.world.expedition_wiped_here</t>
+          <t>ui.world.focus.tip</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>远征队全灭：镜头留在远征地点，确认放弃后回到家园；也可以先切回家园处理别的事</t>
+          <t>镜头飞到这里（{0} 依次切换关注点，{1} 回到归还核心）。整个世界一直在运行，镜头只决定你看哪里</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Expedition wiped out: the camera stays here until you confirm abandoning; you can switch back home meanwhile</t>
+          <t>Fly the camera here ({0} cycles focus, {1} returns to the Reclamation Core). The whole world keeps running; the camera only decides what you watch</t>
         </is>
       </c>
     </row>
@@ -10188,17 +10188,17 @@
       <c r="A543" t="inlineStr"/>
       <c r="B543" t="inlineStr">
         <is>
-          <t>ui.world.placeholder</t>
+          <t>ui.world.eta</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>（占位表现：地貌为地形图层色块，突袭为标记柱）</t>
+          <t>{0} 小时 {1} 分（游戏时间）</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>(Placeholder visuals: terrain tiles and raid marker)</t>
+          <t>{0} h {1} min (game time)</t>
         </is>
       </c>
     </row>
@@ -10206,17 +10206,17 @@
       <c r="A544" t="inlineStr"/>
       <c r="B544" t="inlineStr">
         <is>
-          <t>world.site.home_valley.name</t>
+          <t>ui.world.site_unloaded</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>归还谷地</t>
+          <t>该地点已不在运行（远征已结束），无法定位</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Reclamation Valley</t>
+          <t>That place is no longer active (the expedition has ended)</t>
         </is>
       </c>
     </row>
@@ -10224,17 +10224,17 @@
       <c r="A545" t="inlineStr"/>
       <c r="B545" t="inlineStr">
         <is>
-          <t>world.site.silent_ruins.name</t>
+          <t>ui.world.expedition_wiped_here</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>破碎都市</t>
+          <t>远征队全灭：镜头留在远征地点，确认放弃后回到家园；也可以先切回家园处理别的事</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Fractured City</t>
+          <t>Expedition wiped out: the camera stays here until you confirm abandoning; you can switch back home meanwhile</t>
         </is>
       </c>
     </row>
@@ -10242,17 +10242,17 @@
       <c r="A546" t="inlineStr"/>
       <c r="B546" t="inlineStr">
         <is>
-          <t>world.site.foundry_outpost.name</t>
+          <t>ui.world.placeholder</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>铸造前哨外围</t>
+          <t>（占位表现：地貌为地形图层色块，突袭为标记柱）</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Foundry Outpost Outskirts</t>
+          <t>(Placeholder visuals: terrain tiles and raid marker)</t>
         </is>
       </c>
     </row>
@@ -10260,17 +10260,17 @@
       <c r="A547" t="inlineStr"/>
       <c r="B547" t="inlineStr">
         <is>
-          <t>world.transit.raid.label</t>
+          <t>world.site.home_valley.name</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>突袭 ×{0}</t>
+          <t>归还谷地</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Raid ×{0}</t>
+          <t>Reclamation Valley</t>
         </is>
       </c>
     </row>
@@ -10278,17 +10278,17 @@
       <c r="A548" t="inlineStr"/>
       <c r="B548" t="inlineStr">
         <is>
-          <t>world.transit.raid.arrived_detail</t>
+          <t>world.site.silent_ruins.name</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>{0} 个敌方单位抵达家园外围（来自 {1}）</t>
+          <t>破碎都市</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>{0} enemy units reached the home perimeter (from {1})</t>
+          <t>Fractured City</t>
         </is>
       </c>
     </row>
@@ -10296,17 +10296,17 @@
       <c r="A549" t="inlineStr"/>
       <c r="B549" t="inlineStr">
         <is>
-          <t>expedition.reason.underway</t>
+          <t>world.site.foundry_outpost.name</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>已有远征队在外：撤离或放弃后才能再次派遣</t>
+          <t>铸造前哨外围</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>An expedition is already out: evacuate or abandon it before sending another</t>
+          <t>Foundry Outpost Outskirts</t>
         </is>
       </c>
     </row>
@@ -10314,17 +10314,17 @@
       <c r="A550" t="inlineStr"/>
       <c r="B550" t="inlineStr">
         <is>
-          <t>logistics.tier.t1</t>
+          <t>world.transit.raid.label</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>传送带 T1</t>
+          <t>突袭 ×{0}</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Belt T1</t>
+          <t>Raid ×{0}</t>
         </is>
       </c>
     </row>
@@ -10332,17 +10332,17 @@
       <c r="A551" t="inlineStr"/>
       <c r="B551" t="inlineStr">
         <is>
-          <t>logistics.tier.t2</t>
+          <t>world.transit.raid.arrived_detail</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>传送带 T2</t>
+          <t>{0} 个敌方单位抵达家园外围（来自 {1}）</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Belt T2</t>
+          <t>{0} enemy units reached the home perimeter (from {1})</t>
         </is>
       </c>
     </row>
@@ -10350,17 +10350,17 @@
       <c r="A552" t="inlineStr"/>
       <c r="B552" t="inlineStr">
         <is>
-          <t>logistics.tier.t3</t>
+          <t>expedition.reason.underway</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>传送带 T3</t>
+          <t>已有远征队在外：撤离或放弃后才能再次派遣</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Belt T3</t>
+          <t>An expedition is already out: evacuate or abandon it before sending another</t>
         </is>
       </c>
     </row>
@@ -10368,17 +10368,17 @@
       <c r="A553" t="inlineStr"/>
       <c r="B553" t="inlineStr">
         <is>
-          <t>logistics.block.none</t>
+          <t>logistics.tier.t1</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>运转中</t>
+          <t>传送带 T1</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Running</t>
+          <t>Belt T1</t>
         </is>
       </c>
     </row>
@@ -10386,17 +10386,17 @@
       <c r="A554" t="inlineStr"/>
       <c r="B554" t="inlineStr">
         <is>
-          <t>logistics.block.end_of_belt</t>
+          <t>logistics.tier.t2</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>传送带到头了：末端没有接传送带或建筑输入口</t>
+          <t>传送带 T2</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>End of belt: nothing is connected at the end</t>
+          <t>Belt T2</t>
         </is>
       </c>
     </row>
@@ -10404,17 +10404,17 @@
       <c r="A555" t="inlineStr"/>
       <c r="B555" t="inlineStr">
         <is>
-          <t>logistics.block.downstream_full</t>
+          <t>logistics.tier.t3</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>下游 ({0}, {1}) 已满</t>
+          <t>传送带 T3</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Downstream ({0}, {1}) is full</t>
+          <t>Belt T3</t>
         </is>
       </c>
     </row>
@@ -10422,17 +10422,17 @@
       <c r="A556" t="inlineStr"/>
       <c r="B556" t="inlineStr">
         <is>
-          <t>logistics.block.sink_full</t>
+          <t>logistics.block.none</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>下游 {0} 的输入已满</t>
+          <t>运转中</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>{0}'s input downstream is full</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
@@ -10440,17 +10440,17 @@
       <c r="A557" t="inlineStr"/>
       <c r="B557" t="inlineStr">
         <is>
-          <t>logistics.block.sink_unnamed</t>
+          <t>logistics.block.end_of_belt</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>输入端口 #{0}</t>
+          <t>传送带到头了：末端没有接传送带或建筑输入口</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>input port #{0}</t>
+          <t>End of belt: nothing is connected at the end</t>
         </is>
       </c>
     </row>
@@ -10458,17 +10458,17 @@
       <c r="A558" t="inlineStr"/>
       <c r="B558" t="inlineStr">
         <is>
-          <t>logistics.block.merge_wait</t>
+          <t>logistics.block.downstream_full</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>汇入点 ({0}, {1}) 轮到另一路：两路交替汇入</t>
+          <t>下游 ({0}, {1}) 已满</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Merge at ({0}, {1}) is serving the other lane: lanes alternate</t>
+          <t>Downstream ({0}, {1}) is full</t>
         </is>
       </c>
     </row>
@@ -10476,17 +10476,17 @@
       <c r="A559" t="inlineStr"/>
       <c r="B559" t="inlineStr">
         <is>
-          <t>logistics.hover.summary</t>
+          <t>logistics.block.sink_full</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>{0}｜{1} 件｜实测 {2} 件/分钟（设计 {3}）｜{4}</t>
+          <t>下游 {0} 的输入已满</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>{0} | {1} items | {2}/min measured ({3} rated) | {4}</t>
+          <t>{0}'s input downstream is full</t>
         </is>
       </c>
     </row>
@@ -10494,17 +10494,17 @@
       <c r="A560" t="inlineStr"/>
       <c r="B560" t="inlineStr">
         <is>
-          <t>logistics.hover.loop</t>
+          <t>logistics.block.sink_unnamed</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>（环形）</t>
+          <t>输入端口 #{0}</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>(loop)</t>
+          <t>input port #{0}</t>
         </is>
       </c>
     </row>
@@ -10512,17 +10512,17 @@
       <c r="A561" t="inlineStr"/>
       <c r="B561" t="inlineStr">
         <is>
-          <t>logistics.hover.measuring</t>
+          <t>logistics.block.merge_wait</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>统计中</t>
+          <t>汇入点 ({0}, {1}) 轮到另一路：两路交替汇入</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>measuring</t>
+          <t>Merge at ({0}, {1}) is serving the other lane: lanes alternate</t>
         </is>
       </c>
     </row>
@@ -10530,17 +10530,17 @@
       <c r="A562" t="inlineStr"/>
       <c r="B562" t="inlineStr">
         <is>
-          <t>logistics.reason.occupied</t>
+          <t>logistics.hover.summary</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>这一格已经有传送带</t>
+          <t>{0}｜{1} 件｜实测 {2} 件/分钟（设计 {3}）｜{4}</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>There is already a belt here</t>
+          <t>{0} | {1} items | {2}/min measured ({3} rated) | {4}</t>
         </is>
       </c>
     </row>
@@ -10548,17 +10548,17 @@
       <c r="A563" t="inlineStr"/>
       <c r="B563" t="inlineStr">
         <is>
-          <t>logistics.reason.not_found</t>
+          <t>logistics.hover.loop</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>这里没有传送带</t>
+          <t>（环形）</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>There is no belt here</t>
+          <t>(loop)</t>
         </is>
       </c>
     </row>
@@ -10566,17 +10566,17 @@
       <c r="A564" t="inlineStr"/>
       <c r="B564" t="inlineStr">
         <is>
-          <t>logistics.reason.invalid_tier</t>
+          <t>logistics.hover.measuring</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>没有这个等级的传送带</t>
+          <t>统计中</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>No such belt tier</t>
+          <t>measuring</t>
         </is>
       </c>
     </row>
@@ -10584,17 +10584,17 @@
       <c r="A565" t="inlineStr"/>
       <c r="B565" t="inlineStr">
         <is>
-          <t>logistics.reason.invalid_direction</t>
+          <t>logistics.reason.occupied</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>传送带方向无效</t>
+          <t>这一格已经有传送带</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Invalid belt direction</t>
+          <t>There is already a belt here</t>
         </is>
       </c>
     </row>
@@ -10602,17 +10602,17 @@
       <c r="A566" t="inlineStr"/>
       <c r="B566" t="inlineStr">
         <is>
-          <t>logistics.reason.no_space</t>
+          <t>logistics.reason.not_found</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>这一格放不下更多物品</t>
+          <t>这里没有传送带</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>No room for more items on this belt</t>
+          <t>There is no belt here</t>
         </is>
       </c>
     </row>
@@ -10620,17 +10620,17 @@
       <c r="A567" t="inlineStr"/>
       <c r="B567" t="inlineStr">
         <is>
-          <t>logistics.reason.port_occupied</t>
+          <t>logistics.reason.invalid_tier</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>这里已经有同类端口</t>
+          <t>没有这个等级的传送带</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>There is already a port of this kind here</t>
+          <t>No such belt tier</t>
         </is>
       </c>
     </row>
@@ -10638,17 +10638,17 @@
       <c r="A568" t="inlineStr"/>
       <c r="B568" t="inlineStr">
         <is>
-          <t>logistics.reason.port_not_found</t>
+          <t>logistics.reason.invalid_direction</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>没有这个端口</t>
+          <t>传送带方向无效</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>No such port</t>
+          <t>Invalid belt direction</t>
         </is>
       </c>
     </row>
@@ -10656,17 +10656,17 @@
       <c r="A569" t="inlineStr"/>
       <c r="B569" t="inlineStr">
         <is>
-          <t>logistics.reason.invalid_argument</t>
+          <t>logistics.reason.no_space</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>参数无效</t>
+          <t>这一格放不下更多物品</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Invalid argument</t>
+          <t>No room for more items on this belt</t>
         </is>
       </c>
     </row>
@@ -10674,17 +10674,17 @@
       <c r="A570" t="inlineStr"/>
       <c r="B570" t="inlineStr">
         <is>
-          <t>logistics.reason.out_of_range</t>
+          <t>logistics.reason.port_occupied</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>超出传送带可用范围</t>
+          <t>这里已经有同类端口</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Out of belt range</t>
+          <t>There is already a port of this kind here</t>
         </is>
       </c>
     </row>
@@ -10692,17 +10692,17 @@
       <c r="A571" t="inlineStr"/>
       <c r="B571" t="inlineStr">
         <is>
-          <t>logistics.reason.not_running</t>
+          <t>logistics.reason.port_not_found</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>家园未载入，传送带暂不可用</t>
+          <t>没有这个端口</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Home is not loaded; belts are unavailable</t>
+          <t>No such port</t>
         </is>
       </c>
     </row>
@@ -10710,17 +10710,17 @@
       <c r="A572" t="inlineStr"/>
       <c r="B572" t="inlineStr">
         <is>
-          <t>logistics.reason.save_preserved</t>
+          <t>logistics.reason.invalid_argument</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>存档里的传送带来自更新的版本，本版本读不了；为保护原数据，这局不能铺设或修改传送带</t>
+          <t>参数无效</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>The belts in this save come from a newer version and cannot be read here; to protect that data, belts cannot be placed or changed in this session</t>
+          <t>Invalid argument</t>
         </is>
       </c>
     </row>
@@ -10728,17 +10728,17 @@
       <c r="A573" t="inlineStr"/>
       <c r="B573" t="inlineStr">
         <is>
-          <t>logistics.load.corrupt</t>
+          <t>logistics.reason.out_of_range</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>传送带存档有 {0} 个网络损坏，已丢弃（{1} 件物品计入移出）：{2}</t>
+          <t>超出传送带可用范围</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>{0} belt network(s) in the save were damaged and dropped ({1} items written off): {2}</t>
+          <t>Out of belt range</t>
         </is>
       </c>
     </row>
@@ -10746,17 +10746,17 @@
       <c r="A574" t="inlineStr"/>
       <c r="B574" t="inlineStr">
         <is>
-          <t>logistics.load.unreadable</t>
+          <t>logistics.reason.not_running</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>传送带存档读不了（{0}）：{1} 个网络、{2} 件物品原样保留在存档里，不会被覆盖；这局不能铺设或修改传送带</t>
+          <t>家园未载入，传送带暂不可用</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>The belts in this save cannot be read ({0}): {1} network(s) and {2} items are kept untouched in the save; belts cannot be placed or changed in this session</t>
+          <t>Home is not loaded; belts are unavailable</t>
         </is>
       </c>
     </row>
@@ -10764,17 +10764,17 @@
       <c r="A575" t="inlineStr"/>
       <c r="B575" t="inlineStr">
         <is>
-          <t>logistics.load.reason.separator</t>
+          <t>logistics.reason.save_preserved</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>；</t>
+          <t>存档里的传送带来自更新的版本，本版本读不了；为保护原数据，这局不能铺设或修改传送带</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t xml:space="preserve">; </t>
+          <t>The belts in this save come from a newer version and cannot be read here; to protect that data, belts cannot be placed or changed in this session</t>
         </is>
       </c>
     </row>
@@ -10782,17 +10782,17 @@
       <c r="A576" t="inlineStr"/>
       <c r="B576" t="inlineStr">
         <is>
-          <t>logistics.load.reason.unknown</t>
+          <t>logistics.load.corrupt</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>未知问题</t>
+          <t>传送带存档有 {0} 个网络损坏，已丢弃（{1} 件物品计入移出）：{2}</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>unknown problem</t>
+          <t>{0} belt network(s) in the save were damaged and dropped ({1} items written off): {2}</t>
         </is>
       </c>
     </row>
@@ -10800,17 +10800,17 @@
       <c r="A577" t="inlineStr"/>
       <c r="B577" t="inlineStr">
         <is>
-          <t>logistics.load.reason.snapshot_null</t>
+          <t>logistics.load.unreadable</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>没有传送带数据</t>
+          <t>传送带存档读不了（{0}）：{1} 个网络、{2} 件物品原样保留在存档里，不会被覆盖；这局不能铺设或修改传送带</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>no belt data</t>
+          <t>The belts in this save cannot be read ({0}): {1} network(s) and {2} items are kept untouched in the save; belts cannot be placed or changed in this session</t>
         </is>
       </c>
     </row>
@@ -10818,17 +10818,17 @@
       <c r="A578" t="inlineStr"/>
       <c r="B578" t="inlineStr">
         <is>
-          <t>logistics.load.reason.not_empty</t>
+          <t>logistics.load.reason.separator</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>内部错误：恢复目标不是空网络</t>
+          <t>；</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>internal error: restore target not empty</t>
+          <t xml:space="preserve">; </t>
         </is>
       </c>
     </row>
@@ -10836,17 +10836,17 @@
       <c r="A579" t="inlineStr"/>
       <c r="B579" t="inlineStr">
         <is>
-          <t>logistics.load.reason.format_version</t>
+          <t>logistics.load.reason.unknown</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>来自不认识的存档格式版本（可能由更新的游戏版本保存）</t>
+          <t>未知问题</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>saved in an unknown format version (possibly by a newer game version)</t>
+          <t>unknown problem</t>
         </is>
       </c>
     </row>
@@ -10854,17 +10854,17 @@
       <c r="A580" t="inlineStr"/>
       <c r="B580" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_empty</t>
+          <t>logistics.load.reason.snapshot_null</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>网络数据为空或过短</t>
+          <t>没有传送带数据</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>network data empty or too short</t>
+          <t>no belt data</t>
         </is>
       </c>
     </row>
@@ -10872,17 +10872,17 @@
       <c r="A581" t="inlineStr"/>
       <c r="B581" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_checksum</t>
+          <t>logistics.load.reason.not_empty</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>网络数据校验和不符</t>
+          <t>内部错误：恢复目标不是空网络</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>network data checksum mismatch</t>
+          <t>internal error: restore target not empty</t>
         </is>
       </c>
     </row>
@@ -10890,17 +10890,17 @@
       <c r="A582" t="inlineStr"/>
       <c r="B582" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_magic</t>
+          <t>logistics.load.reason.format_version</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>网络数据格式标记不符</t>
+          <t>来自不认识的存档格式版本（可能由更新的游戏版本保存）</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>network data format marker mismatch</t>
+          <t>saved in an unknown format version (possibly by a newer game version)</t>
         </is>
       </c>
     </row>
@@ -10908,17 +10908,17 @@
       <c r="A583" t="inlineStr"/>
       <c r="B583" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_header</t>
+          <t>logistics.load.reason.chunk_empty</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>网络数据头与记录不一致</t>
+          <t>网络数据为空或过短</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>network header does not match its record</t>
+          <t>network data empty or too short</t>
         </is>
       </c>
     </row>
@@ -10926,17 +10926,17 @@
       <c r="A584" t="inlineStr"/>
       <c r="B584" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_truncated</t>
+          <t>logistics.load.reason.chunk_checksum</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>网络数据被截断</t>
+          <t>网络数据校验和不符</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>network data truncated</t>
+          <t>network data checksum mismatch</t>
         </is>
       </c>
     </row>
@@ -10944,17 +10944,17 @@
       <c r="A585" t="inlineStr"/>
       <c r="B585" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_cell</t>
+          <t>logistics.load.reason.chunk_magic</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>网络里有无法恢复的传送带（坐标重复或数值非法）</t>
+          <t>网络数据格式标记不符</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>a belt in the network cannot be restored (duplicate or invalid)</t>
+          <t>network data format marker mismatch</t>
         </is>
       </c>
     </row>
@@ -10962,17 +10962,17 @@
       <c r="A586" t="inlineStr"/>
       <c r="B586" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_item</t>
+          <t>logistics.load.reason.chunk_header</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>网络里有位置非法或重叠的物品</t>
+          <t>网络数据头与记录不一致</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>an item in the network has an invalid or overlapping position</t>
+          <t>network header does not match its record</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       <c r="A587" t="inlineStr"/>
       <c r="B587" t="inlineStr">
         <is>
-          <t>logistics.load.reason.chunk_count</t>
+          <t>logistics.load.reason.chunk_truncated</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>网络物品总数不符</t>
+          <t>网络数据被截断</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>network item count mismatch</t>
+          <t>network data truncated</t>
         </is>
       </c>
     </row>
@@ -10998,17 +10998,17 @@
       <c r="A588" t="inlineStr"/>
       <c r="B588" t="inlineStr">
         <is>
-          <t>logistics.load.reason.ports_corrupt</t>
+          <t>logistics.load.reason.chunk_cell</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>端口数据损坏已丢弃（建筑会重新登记端口）</t>
+          <t>网络里有无法恢复的传送带（坐标重复或数值非法）</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>port data damaged and dropped (buildings re-register their ports)</t>
+          <t>a belt in the network cannot be restored (duplicate or invalid)</t>
         </is>
       </c>
     </row>
@@ -11016,17 +11016,17 @@
       <c r="A589" t="inlineStr"/>
       <c r="B589" t="inlineStr">
         <is>
-          <t>logistics.placeholder</t>
+          <t>logistics.load.reason.chunk_item</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>（占位表现：传送带为色块与箭头，物品为按种类着色的方块；物品图标随 FG4 物品表替换）</t>
+          <t>网络里有位置非法或重叠的物品</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>(Placeholder visuals: belts are tiles with arrows, items are colour-coded squares; icons arrive with the FG4 item table)</t>
+          <t>an item in the network has an invalid or overlapping position</t>
         </is>
       </c>
     </row>
@@ -11034,17 +11034,17 @@
       <c r="A590" t="inlineStr"/>
       <c r="B590" t="inlineStr">
         <is>
-          <t>combat.fire.no_attacker</t>
+          <t>logistics.load.reason.chunk_count</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>攻击者不存在或已阵亡</t>
+          <t>网络物品总数不符</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>The attacker no longer exists or has been destroyed</t>
+          <t>network item count mismatch</t>
         </is>
       </c>
     </row>
@@ -11052,17 +11052,17 @@
       <c r="A591" t="inlineStr"/>
       <c r="B591" t="inlineStr">
         <is>
-          <t>combat.fire.no_weapon</t>
+          <t>logistics.load.reason.ports_corrupt</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>这台机器没有可用的武器装配</t>
+          <t>端口数据损坏已丢弃（建筑会重新登记端口）</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>This machine has no usable weapon loadout</t>
+          <t>port data damaged and dropped (buildings re-register their ports)</t>
         </is>
       </c>
     </row>
@@ -11070,17 +11070,17 @@
       <c r="A592" t="inlineStr"/>
       <c r="B592" t="inlineStr">
         <is>
-          <t>combat.fire.no_output</t>
+          <t>logistics.placeholder</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>当前装配没有可攻击的主武器出口（8 号汇槽为空）</t>
+          <t>（占位表现：传送带为色块与箭头，物品为按种类着色的方块；物品图标随 FG4 物品表替换）</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>The loadout has no attacking primary output (sink slot 8 is empty)</t>
+          <t>(Placeholder visuals: belts are tiles with arrows, items are colour-coded squares; icons arrive with the FG4 item table)</t>
         </is>
       </c>
     </row>
@@ -11088,17 +11088,17 @@
       <c r="A593" t="inlineStr"/>
       <c r="B593" t="inlineStr">
         <is>
-          <t>combat.fire.overheated</t>
+          <t>combat.fire.no_attacker</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>武器过热：热量降到 {0} 以下才能再开火</t>
+          <t>攻击者不存在或已阵亡</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Weapon overheated: wait until heat drops below {0}</t>
+          <t>The attacker no longer exists or has been destroyed</t>
         </is>
       </c>
     </row>
@@ -11106,17 +11106,17 @@
       <c r="A594" t="inlineStr"/>
       <c r="B594" t="inlineStr">
         <is>
-          <t>combat.fire.cooldown</t>
+          <t>combat.fire.no_weapon</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>武器冷却中</t>
+          <t>这台机器没有可用的武器装配</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Weapon cooling down</t>
+          <t>This machine has no usable weapon loadout</t>
         </is>
       </c>
     </row>
@@ -11124,17 +11124,17 @@
       <c r="A595" t="inlineStr"/>
       <c r="B595" t="inlineStr">
         <is>
-          <t>combat.fire.target_dead</t>
+          <t>combat.fire.no_output</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>目标已阵亡</t>
+          <t>当前装配没有可攻击的主武器出口（8 号汇槽为空）</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>The target is already destroyed</t>
+          <t>The loadout has no attacking primary output (sink slot 8 is empty)</t>
         </is>
       </c>
     </row>
@@ -11142,17 +11142,17 @@
       <c r="A596" t="inlineStr"/>
       <c r="B596" t="inlineStr">
         <is>
-          <t>combat.fire.target_missing</t>
+          <t>combat.fire.overheated</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>目标不存在</t>
+          <t>武器过热：热量降到 {0} 以下才能再开火</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>The target does not exist</t>
+          <t>Weapon overheated: wait until heat drops below {0}</t>
         </is>
       </c>
     </row>
@@ -11160,17 +11160,17 @@
       <c r="A597" t="inlineStr"/>
       <c r="B597" t="inlineStr">
         <is>
-          <t>combat.fire.out_of_range</t>
+          <t>combat.fire.cooldown</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>目标不在射程内</t>
+          <t>武器冷却中</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>The target is out of range</t>
+          <t>Weapon cooling down</t>
         </is>
       </c>
     </row>
@@ -11178,17 +11178,17 @@
       <c r="A598" t="inlineStr"/>
       <c r="B598" t="inlineStr">
         <is>
-          <t>combat.fire.not_hostile</t>
+          <t>combat.fire.target_dead</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>不能攻击这个目标</t>
+          <t>目标已阵亡</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>This target cannot be attacked</t>
+          <t>The target is already destroyed</t>
         </is>
       </c>
     </row>
@@ -11196,17 +11196,17 @@
       <c r="A599" t="inlineStr"/>
       <c r="B599" t="inlineStr">
         <is>
-          <t>combat.fire.invulnerable</t>
+          <t>combat.fire.target_missing</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>目标当前无法被击伤（{0}）</t>
+          <t>目标不存在</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>The target cannot be damaged right now ({0})</t>
+          <t>The target does not exist</t>
         </is>
       </c>
     </row>
@@ -11214,17 +11214,17 @@
       <c r="A600" t="inlineStr"/>
       <c r="B600" t="inlineStr">
         <is>
-          <t>combat.load.rebuilt</t>
+          <t>combat.fire.out_of_range</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>{0} 的战斗状态读不了（{1}）：已按机器与敌人记录恢复（位置、耐久保留；飞行中的弹体、冷却与编队命令重置）</t>
+          <t>目标不在射程内</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Combat state for {0} could not be read ({1}): restored from machine and enemy records (positions and durability kept; projectiles in flight, cooldowns and squad orders reset)</t>
+          <t>The target is out of range</t>
         </is>
       </c>
     </row>
@@ -11232,17 +11232,17 @@
       <c r="A601" t="inlineStr"/>
       <c r="B601" t="inlineStr">
         <is>
-          <t>combat.load.reason.bad_magic</t>
+          <t>combat.fire.not_hostile</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>数据格式标记不符</t>
+          <t>不能攻击这个目标</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>format marker mismatch</t>
+          <t>This target cannot be attacked</t>
         </is>
       </c>
     </row>
@@ -11250,17 +11250,17 @@
       <c r="A602" t="inlineStr"/>
       <c r="B602" t="inlineStr">
         <is>
-          <t>combat.load.reason.unknown_format</t>
+          <t>combat.fire.invulnerable</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>来自不认识的存档格式版本（可能由更新的游戏版本保存）</t>
+          <t>目标当前无法被击伤（{0}）</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>saved in an unknown format version (possibly by a newer game version)</t>
+          <t>The target cannot be damaged right now ({0})</t>
         </is>
       </c>
     </row>
@@ -11268,17 +11268,17 @@
       <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
-          <t>combat.load.reason.bad_checksum</t>
+          <t>combat.load.rebuilt</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>数据校验和不符</t>
+          <t>{0} 的战斗状态读不了（{1}）：已按机器与敌人记录恢复（位置、耐久保留；飞行中的弹体、冷却与编队命令重置）</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>checksum mismatch</t>
+          <t>Combat state for {0} could not be read ({1}): restored from machine and enemy records (positions and durability kept; projectiles in flight, cooldowns and squad orders reset)</t>
         </is>
       </c>
     </row>
@@ -11286,17 +11286,17 @@
       <c r="A604" t="inlineStr"/>
       <c r="B604" t="inlineStr">
         <is>
-          <t>combat.load.reason.truncated</t>
+          <t>combat.load.reason.bad_magic</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>数据被截断</t>
+          <t>数据格式标记不符</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>data truncated</t>
+          <t>format marker mismatch</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       <c r="A605" t="inlineStr"/>
       <c r="B605" t="inlineStr">
         <is>
-          <t>combat.load.reason.invalid_value</t>
+          <t>combat.load.reason.unknown_format</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>数据里有非法数值</t>
+          <t>来自不认识的存档格式版本（可能由更新的游戏版本保存）</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>invalid values in the data</t>
+          <t>saved in an unknown format version (possibly by a newer game version)</t>
         </is>
       </c>
     </row>
@@ -11322,17 +11322,17 @@
       <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
-          <t>combat.load.reason.bad_payload</t>
+          <t>combat.load.reason.bad_checksum</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>数据无法解码</t>
+          <t>数据校验和不符</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>data could not be decoded</t>
+          <t>checksum mismatch</t>
         </is>
       </c>
     </row>
@@ -11340,17 +11340,17 @@
       <c r="A607" t="inlineStr"/>
       <c r="B607" t="inlineStr">
         <is>
-          <t>combat.site.home</t>
+          <t>combat.load.reason.truncated</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>家园</t>
+          <t>数据被截断</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>data truncated</t>
         </is>
       </c>
     </row>
@@ -11358,17 +11358,17 @@
       <c r="A608" t="inlineStr"/>
       <c r="B608" t="inlineStr">
         <is>
-          <t>combat.site.fractured_city</t>
+          <t>combat.load.reason.invalid_value</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>破碎都市</t>
+          <t>数据里有非法数值</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Fractured City</t>
+          <t>invalid values in the data</t>
         </is>
       </c>
     </row>
@@ -11376,17 +11376,17 @@
       <c r="A609" t="inlineStr"/>
       <c r="B609" t="inlineStr">
         <is>
-          <t>combat.site.foundry_outpost</t>
+          <t>combat.load.reason.bad_payload</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>铸造前哨外围</t>
+          <t>数据无法解码</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Foundry Outpost outskirts</t>
+          <t>data could not be decoded</t>
         </is>
       </c>
     </row>
@@ -11394,17 +11394,485 @@
       <c r="A610" t="inlineStr"/>
       <c r="B610" t="inlineStr">
         <is>
+          <t>combat.site.home</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>家园</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr"/>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>combat.site.fractured_city</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>破碎都市</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Fractured City</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr"/>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>combat.site.foundry_outpost</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>铸造前哨外围</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Foundry Outpost outskirts</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr"/>
+      <c r="B613" t="inlineStr">
+        <is>
           <t>combat.placeholder</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>（占位表现：突袭者与炮塔原型为按阵营着色的圆片与血量环，弹体为发光短线；正式模型随 FG6 替换）</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr">
+      <c r="D613" t="inlineStr">
         <is>
           <t>(Placeholder visuals: raider and turret prototypes are faction-coloured discs with a durability ring, projectiles are glowing streaks; real models arrive with FG6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr"/>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>nav.fail.start_blocked</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>起点被完全围住：周围一圈都走不了</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>The start is boxed in: nothing around it is walkable</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr"/>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>nav.fail.goal_blocked</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>目标处无处可站：压在建筑、悬崖或水上，附近也没有空地</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Nowhere to stand at the target: it is covered by a building, cliff or water with no open ground nearby</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr"/>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>nav.fail.unreachable</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>目标被完全阻断：悬崖、水或建筑把路围死了，找不到任何通路</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>The target is completely cut off: cliffs, water or buildings block every route</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr"/>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>nav.fail.search_limit</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>目标太远或绕路过长，超出寻路范围</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>The target is too far or the detour too long for pathfinding</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr"/>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>nav.fail.out_of_world</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>目标超出世界边界</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>The target is beyond the edge of the world</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr"/>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>nav.fail.unknown_terrain</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>目标所在区域的地形未知</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>The terrain around the target is unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr"/>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>nav.fail.in_fog</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>（目标在未探索区域）</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (the target is in unexplored territory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr"/>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>nav.fail.fix</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>移除挡路的建筑，或换一个目标</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Remove the blocking building or pick another target</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr"/>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>nav.squad.unreachable</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>机器 #{0} 无法到达目标：{1}。命令已结束</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Machine #{0} cannot reach the target: {1}. Order ended</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr"/>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>nav.work.unreachable</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>{0} 去不了工作地点（{1}）：{2}。{3}。工单转为等待，30 秒后重试</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>{0} cannot reach the work site ({1}): {2}. {3}. The work order is waiting and will retry in 30 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr"/>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>nav.load.rebuilt</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>寻路状态读不了：等路线的单位已重新规划路线</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Pathfinding state could not be read: units waiting for a route have re-planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr"/>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>nav.work.reason</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>目标无法到达：{0}。30 秒后重试</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Target unreachable: {0}. Retrying in 30 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr"/>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>nav.build.unreachable_warning</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>注意：放在这里后，机器将无法到达 {0}（仍可放置）</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Warning: placing here leaves {0} unreachable for machines (you can still place it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr"/>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>nav.transit.blocked</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>通往核心的路被完全堵住，停在最近处：{0}</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Every route to the core is blocked; halted at the closest point: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr"/>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>nav.route.awaiting</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>正在规划路线…</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Planning route...</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr"/>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>outpost.name</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>敌方据点</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Enemy outpost</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr"/>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>outpost.patrol.name</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>敌方巡逻</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Enemy patrol</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr"/>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>outpost.marker</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>{0}（驻军 {1}）</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>{0} (garrison {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr"/>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>outpost.patrol.marker</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>{0}（{1} 台）</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>{0} ({1} units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr"/>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>outpost.wake.proximity</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>己方单位靠近</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Friendly units approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr"/>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>outpost.wake.raid</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>突袭导演调用</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Raid director call</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr"/>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>outpost.wake.event</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>事件触发</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Event trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr"/>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>outpost.placeholder</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>（占位：据点与巡逻为按阵营着色的立柱与圆片；正式内容由 FG3-GEN-01 / FG8-GEN-02 生成）</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>(Placeholder: outposts and patrols are faction-coloured pillars and discs; real content is generated by FG3-GEN-01 / FG8-GEN-02)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D734"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13640,6 +13640,834 @@
         </is>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" t="inlineStr"/>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.source_slot</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>0 号格是电源源点，不能标为接入口</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Slot 0 is the power source and cannot be an uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr"/>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.sink_slot</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>8 号格是主组件，不能标为接入口</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Slot 8 is the main component and cannot be an uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr"/>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.out_of_range</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>没有 {0} 号格</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>There is no slot {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr"/>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.same_slot</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>{0} 号格已经是接入口</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Slot {0} is already the uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr"/>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.second</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>每张蓝图最多 1 个接入口：先取消 {0} 号格的接入口，再标新的位置</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>A blueprint can have only one uplink port: clear the port on slot {0} first, then mark the new slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr"/>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.occupied</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>{0} 号格装着芯片：接入口必须是空格，先把芯片卸回基元仓</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Slot {0} holds a chip: the uplink port must be an empty slot, so return the chip to the store first</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr"/>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.none</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>这张蓝图没有接入口</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>This blueprint has no uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr"/>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.cell_is_uplink</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>{0} 号格是接入口：先取消接入口，才能在这里装芯片</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Slot {0} is the uplink port: clear the port before installing a chip here</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr"/>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>circuit.uplink.reason.no_slot</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>先点选一个空的 1～7 号格，再标为接入口</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Pick an empty slot 1-7 first, then mark it as the uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr"/>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>circuit.uplink.tag</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>接入口</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr"/>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>circuit.uplink.mark</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>标为接入口</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Mark as uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr"/>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>circuit.uplink.unmark</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>取消接入口</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Clear uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr"/>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>circuit.uplink.marked</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>已把 {0} 号格标为接入口</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Slot {0} is now the uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr"/>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>circuit.uplink.cleared</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>已取消接入口</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Uplink port cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr"/>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>circuit.uplink.slot_detail</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>◇ 接入口：你接入这台机器时，信号核的固件按槽位顺序插在这一格（最多 {0} 个，不占电路负载）；AI 驾驶时它只是空槽，照样传导。</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>◇ Uplink port: when you uplink into this machine, Signal Core firmware is inserted here in slot order (up to {0}, not counted against circuit load). Under AI control it is an empty slot that still conducts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr"/>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>circuit.uplink.title</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>双态编译预览</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Dual compile preview</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr"/>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>circuit.uplink.col_ai</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>AI 驾驶时</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>AI driving</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr"/>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>circuit.uplink.col_uplinked</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>你接入时</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>When you uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr"/>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff_title</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>接入后的变化</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>What changes when you uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr"/>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>circuit.uplink.core_line</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>按当前信号核计算（{0}）</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Using your current Signal Core ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr"/>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>circuit.uplink.none_word</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr"/>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.no_uplink</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>接入口：没有</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Uplink port: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr"/>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.uplink_empty</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>接入口 {0} 号格：空（按空槽传导）</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Uplink slot {0}: empty (conducts as an empty slot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr"/>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.uplink_filled</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>接入口 {0} 号格：{1}（{2}/{3}）</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Uplink slot {0}: {1} ({2}/{3})</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr"/>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.paths</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>有效路径 {0} 条</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>{0} valid paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr"/>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.no_output</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>没有可攻击输出</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>No attack output</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr"/>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.damage</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>平均伤害 {0}</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Average damage {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr"/>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.heat</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>热量预算 {0}</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Heat budget {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr"/>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.reaction</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>反应：{0}</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Reaction: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr"/>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.reaction_none</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>反应：无</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Reaction: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr"/>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>circuit.uplink.line.firmware</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>生效固件：{0}</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Active firmware: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr"/>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.none</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>与 AI 驾驶时相同</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Same as under AI control</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr"/>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.path_added</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>＋新增路径 {0}（伤害 {1}）</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>+ New path {0} (damage {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr"/>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.path</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>＋路径 {0} 插入 {1}：伤害 {2} → {3}</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>+ Path {0} gets {1}: damage {2} → {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr"/>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.path_same</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>＋路径 {0} 插入 {1}（伤害不变 {2}，效果见固件说明）</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>+ Path {0} gets {1} (damage unchanged at {2}; see the firmware description)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr"/>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.reaction_added</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>＋新增反应：{0}</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>+ New reaction: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr"/>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.reaction_changed</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>反应变化：{0} → {1}</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Reaction changes: {0} → {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr"/>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.heat</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>热量预算 {0} → {1}</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Heat budget {0} → {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr"/>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>circuit.uplink.diff.damage</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>平均伤害 {0} → {1}</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Average damage {0} → {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr"/>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>circuit.uplink.note.no_uplink</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>这张蓝图没有接入口：接入后可以驾驶、瞄准、使用主动作，但不插入固件。在电路上选一个空格“标为接入口”即可加上</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>This blueprint has no uplink port: you can drive, aim and use the main action, but no firmware is inserted. Pick an empty slot and mark it as the uplink port to add one</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr"/>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>circuit.uplink.note.core_empty</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>信号核没有固件：接入后接入口为空，与 AI 驾驶时相同（按 {0} 打开信号核装固件）</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>The Signal Core has no firmware: after uplinking the port stays empty, same as AI control (press {0} to open the Signal Core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr"/>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>circuit.uplink.note.off_path</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>接入口 {0} 号格不在任何源→汇路径上：插进去的固件不会生效——把导线连过这一格</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Uplink slot {0} is not on any source→sink path, so inserted firmware has no effect: route a wire through it</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr"/>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>circuit.uplink.skip.over_quota</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>未插入：{0}（超出接入口配额 {1} 个）</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Not inserted: {0} (over the uplink quota of {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr"/>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>circuit.uplink.skip.path_limit</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>未插入：{0}（插入后路径会超过上限 {1} 条）</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Not inserted: {0} (paths would exceed the limit of {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr"/>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>circuit.uplink.skip.unknown</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>未插入：{0}（不是已知的固件）</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Not inserted: {0} (not a known firmware)</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr"/>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>circuit.uplink.skip.no_uplink</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>未插入：{0}（此机器没有接入口）</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Not inserted: {0} (this machine has no uplink port)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14468,6 +14468,636 @@
         </is>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="inlineStr"/>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.no_campaign</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>没有进行中的战役</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>No campaign in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr"/>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.no_selection</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>先选中一台机器（左键点选或框选），再按 {0} 接入；也可以在机器列表里直接点它</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Select a machine first (click or box-select), then press {0}; or click it in the machine list</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr"/>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.not_found</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>找不到这台机器</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>That machine no longer exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr"/>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.dead</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>{0} 已阵亡，不能接入</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>{0} has been destroyed and cannot be uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr"/>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.other_site</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>{0} 不在当前查看的地点：先把镜头切到它所在的地点</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>{0} is not at the site you are viewing: move the camera to its site first</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr"/>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.out_of_coverage</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>超出信号覆盖：{0} 不在与归还核心连通的覆盖范围里，需要信号中继塔或中继模块</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Out of coverage: {0} is outside the coverage connected to the Reclamation Core; build a signal relay tower or fit a relay module</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr"/>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.jammed</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>被干扰：{0} 在干扰场里，让它先离开干扰场</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Jammed: {0} is inside a jamming field; move it out first</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr"/>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.silent_night</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>静默夜：信号发不出去，天亮后再接入</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Silent night: the signal cannot go out; uplink again after dawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr"/>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.in_factory</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>{0} 还在装配站里：出厂后才能接入</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>{0} is still in the Assembly Station: uplink after it rolls out</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr"/>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.on_repair_bay</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>{0} 在维修台上：维修结束后才能接入</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>{0} is on the repair bay: uplink after the repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr"/>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.in_delivery</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>{0} 正在投送途中：到达后才能接入</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>{0} is being delivered: uplink after it arrives</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr"/>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.modal</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>先关闭当前面板再接入</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Close the open panel before uplinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr"/>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.busy</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>正在接入 {0}，请稍候</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Uplinking into {0}, please wait</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr"/>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.already</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>信号已经在 {0} 里</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>The signal is already in {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr"/>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.no_candidate</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>这里没有别的机器可以切换</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>There is no other machine here to switch to</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr"/>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.view_leaving</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>镜头正在拉回战略视角：落地后再接入</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>The camera is pulling back to the strategic view: uplink once it lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr"/>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>signal.uplink.reason.enemy</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>{0} 不是友方机器</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>{0} is not a friendly machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr"/>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>signal.uplink.pending</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>正在接入 {0}…</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Uplinking into {0}…</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr"/>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>signal.uplink.pending_paused</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>接入 {0}：恢复运行后完成（Esc 取消）</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Uplink to {0}: completes when the game resumes (Esc to cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr"/>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>signal.uplink.cancel.dead</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>接入途中 {0} 阵亡：接入已取消，信号留在原处</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>{0} was destroyed during the uplink: uplink cancelled, the signal stays where it was</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr"/>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>signal.uplink.cancel.gone</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>接入途中 {0} 不可接入了（{1}）：接入已取消，信号留在原处</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>{0} became unavailable during the uplink ({1}): uplink cancelled, the signal stays where it was</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr"/>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>signal.uplink.cancel.player</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>已取消接入 {0}</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Uplink to {0} cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr"/>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>signal.uplink.entered</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>已接入 {0}</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Uplinked into {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr"/>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>signal.uplink.left</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>已离开 {0}：固件随信号带走，机器回到本地配置</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Left {0}: your firmware went with the signal and the machine is back on its own loadout</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr"/>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>signal.uplink.restored</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>读档：信号仍在 {0} 里</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Loaded: the signal is still in {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr"/>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>signal.uplink.restore_failed</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>读档：{0} 已不可接入，信号回到归还核心</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Loaded: {0} can no longer be uplinked, so the signal is back at the core</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr"/>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.inserted</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>接入口：{0}</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Uplink port: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr"/>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.no_uplink</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>此机器没有接入口：可以驾驶、瞄准和攻击，但不插入固件</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>This machine has no uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr"/>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.core_empty</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>信号核没有固件：接入口为空（按 {0} 打开信号核）</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>The Signal Core has no firmware: the uplink port is empty (press {0} to open the Signal Core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr"/>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.off_path</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>接入口不在导线上：插入的固件不生效</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>The uplink port is not on a wire: inserted firmware has no effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr"/>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.cooling</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>{0}（冷却 {1} 秒）</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>{0} (cooldown {1}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr"/>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.sep</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>；</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t xml:space="preserve">; </t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr"/>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>signal.uplink.status.list_sep</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>、</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t xml:space="preserve">, </t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr"/>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>signal.uplink.core_fired</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>{0} 发动：冷却 {1} 秒（冷却跟着信号，换机器也不会重置）</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>{0} fired: {1}s cooldown (the cooldown follows the signal and does not reset on another machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr"/>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>signal.uplink.list_tip</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>点一下直接接入这台机器（选中后按 {0} 也可以；接入后按 {1} 在机器间切换）</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Click to uplink into this machine directly (or select it and press {0}; press {1} to switch machines while uplinked)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15098,6 +15098,312 @@
         </is>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" t="inlineStr"/>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>signal.link.reason_name.out_of_coverage</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>走出信号覆盖</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>left signal coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr"/>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>signal.link.reason_name.jammed</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>进入干扰场</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>entered a jamming field</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr"/>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>signal.link.reason_name.silent_night</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>静默夜</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>silent night</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr"/>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>signal.link.reason_name.destroyed</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>机器阵亡</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>machine destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr"/>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>signal.link.warn.edge</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>接近信号覆盖边缘：{0} 离边缘还有 {1} 格，走出去信号会被弹回归还核心</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Near the edge of signal coverage: {0} is {1} cells from the edge; leaving it sends the signal back to the core</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr"/>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>signal.link.warn.jammed</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>{0} 受到干扰：{1} 秒内离开干扰区可恢复，否则信号弹回归还核心</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>{0} is being jammed: leave the field within {1}s or the signal returns to the core</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr"/>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>signal.link.warn.out_of_coverage</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>{0} 走出了信号覆盖：{1} 秒内回到覆盖内可恢复，否则信号弹回归还核心</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>{0} left signal coverage: get back within {1}s or the signal returns to the core</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr"/>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>signal.link.warn.silent_night</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>静默夜将在 {0} 秒后开始：届时信号会被弹回归还核心，接入中的机器进入安全模式</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Silent night begins in {0}s: the signal will be sent back to the core and the uplinked machine will enter safe mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr"/>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>signal.link.recovered</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>{0} 信号恢复</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>{0}: signal restored</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr"/>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>signal.link.break.jammed</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>断链：{0} 在干扰场里失联，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Link lost: {0} was jammed and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr"/>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>signal.link.break.out_of_coverage</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>断链：{0} 走出了信号覆盖，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Link lost: {0} left signal coverage and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr"/>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>signal.link.break.silent_night</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>断链：静默夜开始，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Link lost: silent night began and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr"/>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>signal.link.break.destroyed_rebound</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>{0} 阵亡：信号弹到最近能接入的 {1}</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>{0} was destroyed: the signal jumped to the nearest machine it can reach, {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr"/>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>signal.link.break.destroyed_core</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>{0} 阵亡：附近没有能接入的机器，信号回到归还核心</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>{0} was destroyed: no machine nearby can take the signal, so it returned to the core</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr"/>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.exit</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>{0} 信号恢复，退出安全模式</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>{0}: signal restored, safe mode ended</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr"/>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.list_tag</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>安全</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr"/>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.tooltip</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>安全模式（{1}）：{0} 只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；断链条件消失后自动退出，也可以重新接入</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Safe mode ({1}): {0} runs only its local regular firmware with an empty uplink port and follows its last order or AI doctrine; it ends once the link problem is gone, or when you uplink again</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D832"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12006,17 +12006,17 @@
       <c r="A644" t="inlineStr"/>
       <c r="B644" t="inlineStr">
         <is>
-          <t>signal.core.title</t>
+          <t>firmware.fw_capacitor.name</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>信号核</t>
+          <t>电容蓄力</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Signal Core</t>
+          <t>Capacitor Charge</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       <c r="A645" t="inlineStr"/>
       <c r="B645" t="inlineStr">
         <is>
-          <t>signal.core.slot_count</t>
+          <t>firmware.fw_swarm.name</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>槽位 {0}/{1}</t>
+          <t>集群协议</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Slots {0}/{1}</t>
+          <t>Swarm Protocol</t>
         </is>
       </c>
     </row>
@@ -12042,17 +12042,17 @@
       <c r="A646" t="inlineStr"/>
       <c r="B646" t="inlineStr">
         <is>
-          <t>signal.core.slot_index</t>
+          <t>firmware.fw_amplify.name</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>{0} 号槽</t>
+          <t>反应增幅</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Slot {0}</t>
+          <t>Reaction Amplifier</t>
         </is>
       </c>
     </row>
@@ -12060,17 +12060,17 @@
       <c r="A647" t="inlineStr"/>
       <c r="B647" t="inlineStr">
         <is>
-          <t>signal.core.slot_empty</t>
+          <t>firmware.fw_execute.name</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>（空）</t>
+          <t>处决</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>(empty)</t>
+          <t>Execute</t>
         </is>
       </c>
     </row>
@@ -12078,17 +12078,17 @@
       <c r="A648" t="inlineStr"/>
       <c r="B648" t="inlineStr">
         <is>
-          <t>signal.core.slot_locked</t>
+          <t>signal.core.title</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>未解锁：需要超控阵列 T{0}</t>
+          <t>信号核</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Locked: needs Override Array T{0}</t>
+          <t>Signal Core</t>
         </is>
       </c>
     </row>
@@ -12096,17 +12096,17 @@
       <c r="A649" t="inlineStr"/>
       <c r="B649" t="inlineStr">
         <is>
-          <t>signal.core.slots_title</t>
+          <t>signal.core.slot_count</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>槽位（1 号槽优先插入接入口）</t>
+          <t>槽位 {0}/{1}</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Slots (slot 1 is inserted first)</t>
+          <t>Slots {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12114,17 +12114,17 @@
       <c r="A650" t="inlineStr"/>
       <c r="B650" t="inlineStr">
         <is>
-          <t>signal.core.hint</t>
+          <t>signal.core.slot_index</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>把固件拖到槽位，或先点槽位再点“装入”；只能在家园修改。</t>
+          <t>{0} 号槽</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Drag firmware onto a slot, or pick a slot and press Load. Can only be changed at home.</t>
+          <t>Slot {0}</t>
         </is>
       </c>
     </row>
@@ -12132,17 +12132,17 @@
       <c r="A651" t="inlineStr"/>
       <c r="B651" t="inlineStr">
         <is>
-          <t>signal.core.bag_title</t>
+          <t>signal.core.slot_empty</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>基元仓 {0}/{1}</t>
+          <t>（空）</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Primitive Store {0}/{1}</t>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -12150,17 +12150,17 @@
       <c r="A652" t="inlineStr"/>
       <c r="B652" t="inlineStr">
         <is>
-          <t>signal.core.bag_empty</t>
+          <t>signal.core.slot_locked</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>基元仓里没有固件芯片：可以在下方刻印</t>
+          <t>未解锁：需要超控阵列 T{0}</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>No firmware chips in the store: print one below</t>
+          <t>Locked: needs Override Array T{0}</t>
         </is>
       </c>
     </row>
@@ -12168,17 +12168,17 @@
       <c r="A653" t="inlineStr"/>
       <c r="B653" t="inlineStr">
         <is>
-          <t>signal.core.reserved</t>
+          <t>signal.core.slots_title</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>（合成台已预留）</t>
+          <t>槽位（1 号槽优先插入接入口）</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>(reserved by the workbench)</t>
+          <t>Slots (slot 1 is inserted first)</t>
         </is>
       </c>
     </row>
@@ -12186,17 +12186,17 @@
       <c r="A654" t="inlineStr"/>
       <c r="B654" t="inlineStr">
         <is>
-          <t>signal.core.loadout_empty</t>
+          <t>signal.core.hint</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>没有固件</t>
+          <t>把固件拖到槽位，或先点槽位再点“装入”；只能在家园修改。</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>no firmware</t>
+          <t>Drag firmware onto a slot, or pick a slot and press Load. Can only be changed at home.</t>
         </is>
       </c>
     </row>
@@ -12204,17 +12204,17 @@
       <c r="A655" t="inlineStr"/>
       <c r="B655" t="inlineStr">
         <is>
-          <t>signal.core.kind.core</t>
+          <t>signal.core.bag_title</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>◆ 核心</t>
+          <t>基元仓 {0}/{1}</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>◆ Core</t>
+          <t>Primitive Store {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12222,17 +12222,17 @@
       <c r="A656" t="inlineStr"/>
       <c r="B656" t="inlineStr">
         <is>
-          <t>signal.core.kind.regular</t>
+          <t>signal.core.bag_empty</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>● 常规</t>
+          <t>基元仓里没有固件芯片：可以在下方刻印</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>● Regular</t>
+          <t>No firmware chips in the store: print one below</t>
         </is>
       </c>
     </row>
@@ -12240,17 +12240,17 @@
       <c r="A657" t="inlineStr"/>
       <c r="B657" t="inlineStr">
         <is>
-          <t>signal.core.kind.chip</t>
+          <t>signal.core.reserved</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>■ 基元芯片</t>
+          <t>（合成台已预留）</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>■ Primitive chip</t>
+          <t>(reserved by the workbench)</t>
         </is>
       </c>
     </row>
@@ -12258,17 +12258,17 @@
       <c r="A658" t="inlineStr"/>
       <c r="B658" t="inlineStr">
         <is>
-          <t>signal.core.kind.core_tip</t>
+          <t>signal.core.loadout_empty</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>核心固件：越过安全限制或需要核心的实时算力，只能由信号携带，放不进机器电路。</t>
+          <t>没有固件</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Core firmware bypasses safety limits or needs the core's live computing, so only the signal can carry it; it cannot go into a machine circuit.</t>
+          <t>no firmware</t>
         </is>
       </c>
     </row>
@@ -12276,17 +12276,17 @@
       <c r="A659" t="inlineStr"/>
       <c r="B659" t="inlineStr">
         <is>
-          <t>signal.core.kind.regular_tip</t>
+          <t>signal.core.kind.core</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>常规固件：可以装在机器上，也可以放进信号核。</t>
+          <t>◆ 核心</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Regular firmware can be installed on machines or carried in the Signal Core.</t>
+          <t>◆ Core</t>
         </is>
       </c>
     </row>
@@ -12294,17 +12294,17 @@
       <c r="A660" t="inlineStr"/>
       <c r="B660" t="inlineStr">
         <is>
-          <t>signal.core.kind.chip_tip</t>
+          <t>signal.core.kind.regular</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>基元芯片装在蓝图的 3×3 电路板上，不能放进信号核。</t>
+          <t>● 常规</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Primitive chips go on a blueprint's 3×3 circuit board, not in the Signal Core.</t>
+          <t>● Regular</t>
         </is>
       </c>
     </row>
@@ -12312,17 +12312,17 @@
       <c r="A661" t="inlineStr"/>
       <c r="B661" t="inlineStr">
         <is>
-          <t>signal.core.equip</t>
+          <t>signal.core.kind.chip</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>装入 {0} 号槽</t>
+          <t>■ 基元芯片</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Load into slot {0}</t>
+          <t>■ Primitive chip</t>
         </is>
       </c>
     </row>
@@ -12330,17 +12330,17 @@
       <c r="A662" t="inlineStr"/>
       <c r="B662" t="inlineStr">
         <is>
-          <t>signal.core.unequip</t>
+          <t>signal.core.kind.core_tip</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>卸下</t>
+          <t>核心固件：越过安全限制或需要核心的实时算力，只能由信号携带，放不进机器电路。</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Unload</t>
+          <t>Core firmware bypasses safety limits or needs the core's live computing, so only the signal can carry it; it cannot go into a machine circuit.</t>
         </is>
       </c>
     </row>
@@ -12348,17 +12348,17 @@
       <c r="A663" t="inlineStr"/>
       <c r="B663" t="inlineStr">
         <is>
-          <t>signal.core.move_up</t>
+          <t>signal.core.kind.regular_tip</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>前移</t>
+          <t>常规固件：可以装在机器上，也可以放进信号核。</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Move up</t>
+          <t>Regular firmware can be installed on machines or carried in the Signal Core.</t>
         </is>
       </c>
     </row>
@@ -12366,17 +12366,17 @@
       <c r="A664" t="inlineStr"/>
       <c r="B664" t="inlineStr">
         <is>
-          <t>signal.core.equipped</t>
+          <t>signal.core.kind.chip_tip</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>“{0}”已装入 {1} 号槽</t>
+          <t>基元芯片装在蓝图的 3×3 电路板上，不能放进信号核。</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>"{0}" loaded into slot {1}</t>
+          <t>Primitive chips go on a blueprint's 3×3 circuit board, not in the Signal Core.</t>
         </is>
       </c>
     </row>
@@ -12384,17 +12384,17 @@
       <c r="A665" t="inlineStr"/>
       <c r="B665" t="inlineStr">
         <is>
-          <t>signal.core.swapped</t>
+          <t>signal.core.equip</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>“{0}”已装入 {1} 号槽，“{2}”卸回基元仓</t>
+          <t>装入 {0} 号槽</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>"{0}" loaded into slot {1}; "{2}" returned to the store</t>
+          <t>Load into slot {0}</t>
         </is>
       </c>
     </row>
@@ -12402,17 +12402,17 @@
       <c r="A666" t="inlineStr"/>
       <c r="B666" t="inlineStr">
         <is>
-          <t>signal.core.unequipped</t>
+          <t>signal.core.unequip</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>“{0}”已卸回基元仓</t>
+          <t>卸下</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>"{0}" returned to the store</t>
+          <t>Unload</t>
         </is>
       </c>
     </row>
@@ -12420,17 +12420,17 @@
       <c r="A667" t="inlineStr"/>
       <c r="B667" t="inlineStr">
         <is>
-          <t>signal.core.moved</t>
+          <t>signal.core.move_up</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>{0} 号槽与 {1} 号槽已对调</t>
+          <t>前移</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Slots {0} and {1} swapped</t>
+          <t>Move up</t>
         </is>
       </c>
     </row>
@@ -12438,17 +12438,17 @@
       <c r="A668" t="inlineStr"/>
       <c r="B668" t="inlineStr">
         <is>
-          <t>signal.core.print_title</t>
+          <t>signal.core.equipped</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>刻印固件芯片（装配站，{0} 废料 / 枚）</t>
+          <t>“{0}”已装入 {1} 号槽</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Print firmware chips (Assembly Station, {0} scrap each)</t>
+          <t>"{0}" loaded into slot {1}</t>
         </is>
       </c>
     </row>
@@ -12456,17 +12456,17 @@
       <c r="A669" t="inlineStr"/>
       <c r="B669" t="inlineStr">
         <is>
-          <t>signal.core.print</t>
+          <t>signal.core.swapped</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>刻印</t>
+          <t>“{0}”已装入 {1} 号槽，“{2}”卸回基元仓</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>"{0}" loaded into slot {1}; "{2}" returned to the store</t>
         </is>
       </c>
     </row>
@@ -12474,17 +12474,17 @@
       <c r="A670" t="inlineStr"/>
       <c r="B670" t="inlineStr">
         <is>
-          <t>signal.core.print_none</t>
+          <t>signal.core.unequipped</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>没有已解锁的固件</t>
+          <t>“{0}”已卸回基元仓</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>No firmware unlocked</t>
+          <t>"{0}" returned to the store</t>
         </is>
       </c>
     </row>
@@ -12492,17 +12492,17 @@
       <c r="A671" t="inlineStr"/>
       <c r="B671" t="inlineStr">
         <is>
-          <t>signal.core.printed</t>
+          <t>signal.core.moved</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>已刻印“{0}”，放进基元仓</t>
+          <t>{0} 号槽与 {1} 号槽已对调</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Printed "{0}" into the store</t>
+          <t>Slots {0} and {1} swapped</t>
         </is>
       </c>
     </row>
@@ -12510,17 +12510,17 @@
       <c r="A672" t="inlineStr"/>
       <c r="B672" t="inlineStr">
         <is>
-          <t>signal.core.presets_title</t>
+          <t>signal.core.print_title</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>预设（只能在家园切换）</t>
+          <t>刻印固件芯片（装配站，{0} 废料 / 枚）</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Presets (switch at home only)</t>
+          <t>Print firmware chips (Assembly Station, {0} scrap each)</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       <c r="A673" t="inlineStr"/>
       <c r="B673" t="inlineStr">
         <is>
-          <t>signal.core.preset.none</t>
+          <t>signal.core.print</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>还没有预设：装好固件后点“另存为新预设”</t>
+          <t>刻印</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>No presets yet: load firmware, then press Save as new</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -12546,17 +12546,17 @@
       <c r="A674" t="inlineStr"/>
       <c r="B674" t="inlineStr">
         <is>
-          <t>signal.core.preset.active</t>
+          <t>signal.core.print_none</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>当前预设：{0}</t>
+          <t>没有已解锁的固件</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Current preset: {0}</t>
+          <t>No firmware unlocked</t>
         </is>
       </c>
     </row>
@@ -12564,17 +12564,17 @@
       <c r="A675" t="inlineStr"/>
       <c r="B675" t="inlineStr">
         <is>
-          <t>signal.core.preset.modified</t>
+          <t>signal.core.printed</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>当前预设：{0}（已改动）</t>
+          <t>已刻印“{0}”，放进基元仓</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Current preset: {0} (modified)</t>
+          <t>Printed "{0}" into the store</t>
         </is>
       </c>
     </row>
@@ -12582,17 +12582,17 @@
       <c r="A676" t="inlineStr"/>
       <c r="B676" t="inlineStr">
         <is>
-          <t>signal.core.preset.no_active</t>
+          <t>signal.core.presets_title</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>当前配置没有存为预设</t>
+          <t>预设（只能在家园切换）</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>The current loadout is not saved as a preset</t>
+          <t>Presets (switch at home only)</t>
         </is>
       </c>
     </row>
@@ -12600,17 +12600,17 @@
       <c r="A677" t="inlineStr"/>
       <c r="B677" t="inlineStr">
         <is>
-          <t>signal.core.preset.item</t>
+          <t>signal.core.preset.none</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>{0}：{1}</t>
+          <t>还没有预设：装好固件后点“另存为新预设”</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>{0}: {1}</t>
+          <t>No presets yet: load firmware, then press Save as new</t>
         </is>
       </c>
     </row>
@@ -12618,17 +12618,17 @@
       <c r="A678" t="inlineStr"/>
       <c r="B678" t="inlineStr">
         <is>
-          <t>signal.core.preset.default_name</t>
+          <t>signal.core.preset.active</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>配置 {0}</t>
+          <t>当前预设：{0}</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Loadout {0}</t>
+          <t>Current preset: {0}</t>
         </is>
       </c>
     </row>
@@ -12636,17 +12636,17 @@
       <c r="A679" t="inlineStr"/>
       <c r="B679" t="inlineStr">
         <is>
-          <t>signal.core.preset.name_label</t>
+          <t>signal.core.preset.modified</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>当前预设：{0}（已改动）</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Current preset: {0} (modified)</t>
         </is>
       </c>
     </row>
@@ -12654,17 +12654,17 @@
       <c r="A680" t="inlineStr"/>
       <c r="B680" t="inlineStr">
         <is>
-          <t>signal.core.preset.apply</t>
+          <t>signal.core.preset.no_active</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>切换</t>
+          <t>当前配置没有存为预设</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>The current loadout is not saved as a preset</t>
         </is>
       </c>
     </row>
@@ -12672,17 +12672,17 @@
       <c r="A681" t="inlineStr"/>
       <c r="B681" t="inlineStr">
         <is>
-          <t>signal.core.preset.save_new</t>
+          <t>signal.core.preset.item</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>另存为新预设</t>
+          <t>{0}：{1}</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Save as new</t>
+          <t>{0}: {1}</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       <c r="A682" t="inlineStr"/>
       <c r="B682" t="inlineStr">
         <is>
-          <t>signal.core.preset.overwrite</t>
+          <t>signal.core.preset.default_name</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>覆盖所选</t>
+          <t>配置 {0}</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Overwrite</t>
+          <t>Loadout {0}</t>
         </is>
       </c>
     </row>
@@ -12708,17 +12708,17 @@
       <c r="A683" t="inlineStr"/>
       <c r="B683" t="inlineStr">
         <is>
-          <t>signal.core.preset.rename</t>
+          <t>signal.core.preset.name_label</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>重命名所选</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -12726,17 +12726,17 @@
       <c r="A684" t="inlineStr"/>
       <c r="B684" t="inlineStr">
         <is>
-          <t>signal.core.preset.delete</t>
+          <t>signal.core.preset.apply</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>删除所选</t>
+          <t>切换</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Switch</t>
         </is>
       </c>
     </row>
@@ -12744,17 +12744,17 @@
       <c r="A685" t="inlineStr"/>
       <c r="B685" t="inlineStr">
         <is>
-          <t>signal.core.preset.saved</t>
+          <t>signal.core.preset.save_new</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>已保存预设“{0}”</t>
+          <t>另存为新预设</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Saved preset "{0}"</t>
+          <t>Save as new</t>
         </is>
       </c>
     </row>
@@ -12762,17 +12762,17 @@
       <c r="A686" t="inlineStr"/>
       <c r="B686" t="inlineStr">
         <is>
-          <t>signal.core.preset.overwritten</t>
+          <t>signal.core.preset.overwrite</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>已用当前配置覆盖预设“{0}”</t>
+          <t>覆盖所选</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Overwrote preset "{0}" with the current loadout</t>
+          <t>Overwrite</t>
         </is>
       </c>
     </row>
@@ -12780,17 +12780,17 @@
       <c r="A687" t="inlineStr"/>
       <c r="B687" t="inlineStr">
         <is>
-          <t>signal.core.preset.renamed</t>
+          <t>signal.core.preset.rename</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>预设已改名为“{0}”</t>
+          <t>重命名所选</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Preset renamed to "{0}"</t>
+          <t>Rename</t>
         </is>
       </c>
     </row>
@@ -12798,17 +12798,17 @@
       <c r="A688" t="inlineStr"/>
       <c r="B688" t="inlineStr">
         <is>
-          <t>signal.core.preset.deleted</t>
+          <t>signal.core.preset.delete</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>已删除预设“{0}”</t>
+          <t>删除所选</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Deleted preset "{0}"</t>
+          <t>Delete</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       <c r="A689" t="inlineStr"/>
       <c r="B689" t="inlineStr">
         <is>
-          <t>signal.core.preset.applied</t>
+          <t>signal.core.preset.saved</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>已切换到预设“{0}”</t>
+          <t>已保存预设“{0}”</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Switched to preset "{0}"</t>
+          <t>Saved preset "{0}"</t>
         </is>
       </c>
     </row>
@@ -12834,17 +12834,17 @@
       <c r="A690" t="inlineStr"/>
       <c r="B690" t="inlineStr">
         <is>
-          <t>signal.core.preset.applied_missing</t>
+          <t>signal.core.preset.overwritten</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>已切换到预设“{0}”；缺少 {1}（基元仓里没有），对应槽位留空</t>
+          <t>已用当前配置覆盖预设“{0}”</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Switched to preset "{0}"; missing {1} (not in the store), so those slots stay empty</t>
+          <t>Overwrote preset "{0}" with the current loadout</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       <c r="A691" t="inlineStr"/>
       <c r="B691" t="inlineStr">
         <is>
-          <t>signal.core.preset.confirm_overwrite</t>
+          <t>signal.core.preset.renamed</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>覆盖预设“{0}”？</t>
+          <t>预设已改名为“{0}”</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Overwrite preset "{0}"?</t>
+          <t>Preset renamed to "{0}"</t>
         </is>
       </c>
     </row>
@@ -12870,17 +12870,17 @@
       <c r="A692" t="inlineStr"/>
       <c r="B692" t="inlineStr">
         <is>
-          <t>signal.core.preset.confirm_delete</t>
+          <t>signal.core.preset.deleted</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>删除预设“{0}”？</t>
+          <t>已删除预设“{0}”</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Delete preset "{0}"?</t>
+          <t>Deleted preset "{0}"</t>
         </is>
       </c>
     </row>
@@ -12888,17 +12888,17 @@
       <c r="A693" t="inlineStr"/>
       <c r="B693" t="inlineStr">
         <is>
-          <t>signal.core.preset.old_line</t>
+          <t>signal.core.preset.applied</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>原来的配置：{0}</t>
+          <t>已切换到预设“{0}”</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Old loadout: {0}</t>
+          <t>Switched to preset "{0}"</t>
         </is>
       </c>
     </row>
@@ -12906,17 +12906,17 @@
       <c r="A694" t="inlineStr"/>
       <c r="B694" t="inlineStr">
         <is>
-          <t>signal.core.preset.new_line</t>
+          <t>signal.core.preset.applied_missing</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>新的配置：{0}</t>
+          <t>已切换到预设“{0}”；缺少 {1}（基元仓里没有），对应槽位留空</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>New loadout: {0}</t>
+          <t>Switched to preset "{0}"; missing {1} (not in the store), so those slots stay empty</t>
         </is>
       </c>
     </row>
@@ -12924,17 +12924,17 @@
       <c r="A695" t="inlineStr"/>
       <c r="B695" t="inlineStr">
         <is>
-          <t>signal.core.summary</t>
+          <t>signal.core.preset.confirm_overwrite</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>信号核：{0}</t>
+          <t>覆盖预设“{0}”？</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Signal Core: {0}</t>
+          <t>Overwrite preset "{0}"?</t>
         </is>
       </c>
     </row>
@@ -12942,17 +12942,17 @@
       <c r="A696" t="inlineStr"/>
       <c r="B696" t="inlineStr">
         <is>
-          <t>signal.core.summary_empty</t>
+          <t>signal.core.preset.confirm_delete</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>信号核：没有固件</t>
+          <t>删除预设“{0}”？</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Signal Core: no firmware</t>
+          <t>Delete preset "{0}"?</t>
         </is>
       </c>
     </row>
@@ -12960,17 +12960,17 @@
       <c r="A697" t="inlineStr"/>
       <c r="B697" t="inlineStr">
         <is>
-          <t>signal.core.summary_sep</t>
+          <t>signal.core.preset.old_line</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>原来的配置：{0}</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>Old loadout: {0}</t>
         </is>
       </c>
     </row>
@@ -12978,17 +12978,17 @@
       <c r="A698" t="inlineStr"/>
       <c r="B698" t="inlineStr">
         <is>
-          <t>signal.core.edit</t>
+          <t>signal.core.preset.new_line</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>编辑信号核</t>
+          <t>新的配置：{0}</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Edit Signal Core</t>
+          <t>New loadout: {0}</t>
         </is>
       </c>
     </row>
@@ -12996,17 +12996,17 @@
       <c r="A699" t="inlineStr"/>
       <c r="B699" t="inlineStr">
         <is>
-          <t>signal.core.circuit_core_option</t>
+          <t>signal.core.summary</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>◆ {0}（核心固件：只能由信号携带）</t>
+          <t>信号核：{0}</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>◆ {0} (core firmware: signal only)</t>
+          <t>Signal Core: {0}</t>
         </is>
       </c>
     </row>
@@ -13014,17 +13014,17 @@
       <c r="A700" t="inlineStr"/>
       <c r="B700" t="inlineStr">
         <is>
-          <t>signal.core.expedition_reminder</t>
+          <t>signal.core.summary_empty</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>提醒：出发后，远征途中不能修改信号核（只能在家园修改）。</t>
+          <t>信号核：没有固件</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Reminder: once the expedition departs, the Signal Core cannot be changed until you are back home.</t>
+          <t>Signal Core: no firmware</t>
         </is>
       </c>
     </row>
@@ -13032,17 +13032,17 @@
       <c r="A701" t="inlineStr"/>
       <c r="B701" t="inlineStr">
         <is>
-          <t>signal.core.close</t>
+          <t>signal.core.summary_sep</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -13050,17 +13050,17 @@
       <c r="A702" t="inlineStr"/>
       <c r="B702" t="inlineStr">
         <is>
-          <t>signal.reason.no_campaign</t>
+          <t>signal.core.edit</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>没有进行中的战役</t>
+          <t>编辑信号核</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>No campaign in progress</t>
+          <t>Edit Signal Core</t>
         </is>
       </c>
     </row>
@@ -13068,17 +13068,17 @@
       <c r="A703" t="inlineStr"/>
       <c r="B703" t="inlineStr">
         <is>
-          <t>signal.reason.expedition</t>
+          <t>signal.core.circuit_core_option</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>远征途中不能修改信号核：撤离或放弃远征、回到家园后再改</t>
+          <t>◆ {0}（核心固件：只能由信号携带）</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>The Signal Core cannot be changed during an expedition: evacuate or abandon it and change it at home</t>
+          <t>◆ {0} (core firmware: signal only)</t>
         </is>
       </c>
     </row>
@@ -13086,17 +13086,17 @@
       <c r="A704" t="inlineStr"/>
       <c r="B704" t="inlineStr">
         <is>
-          <t>signal.reason.bag_full</t>
+          <t>signal.core.expedition_reminder</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>基元仓已满：先腾出一个空位（固件仍留在信号核里）</t>
+          <t>提醒：出发后，远征途中不能修改信号核（只能在家园修改）。</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>The primitive store is full: free a space first (the firmware stays in the Signal Core)</t>
+          <t>Reminder: once the expedition departs, the Signal Core cannot be changed until you are back home.</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       <c r="A705" t="inlineStr"/>
       <c r="B705" t="inlineStr">
         <is>
-          <t>signal.reason.core_signal_only</t>
+          <t>signal.core.close</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>核心固件只能由信号携带</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Core firmware can only be carried by the signal</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -13122,17 +13122,17 @@
       <c r="A706" t="inlineStr"/>
       <c r="B706" t="inlineStr">
         <is>
-          <t>signal.reason.not_firmware</t>
+          <t>signal.reason.no_campaign</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>只有固件能放进信号核（基元芯片装在电路板上）</t>
+          <t>没有进行中的战役</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Only firmware fits in the Signal Core (primitive chips go on circuit boards)</t>
+          <t>No campaign in progress</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       <c r="A707" t="inlineStr"/>
       <c r="B707" t="inlineStr">
         <is>
-          <t>signal.reason.firmware_not_chip</t>
+          <t>signal.reason.expedition</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>固件芯片不能装进 3×3 电路格：常规固件装在蓝图的固件槽，或放进信号核</t>
+          <t>远征途中不能修改信号核：撤离或放弃远征、回到家园后再改</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Firmware chips do not go into the 3×3 circuit grid: put regular firmware in a blueprint's firmware slot or in the Signal Core</t>
+          <t>The Signal Core cannot be changed during an expedition: evacuate or abandon it and change it at home</t>
         </is>
       </c>
     </row>
@@ -13158,17 +13158,17 @@
       <c r="A708" t="inlineStr"/>
       <c r="B708" t="inlineStr">
         <is>
-          <t>signal.reason.core_in_circuit</t>
+          <t>signal.reason.bag_full</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>“{0}”是核心固件，只能由信号携带：从机器电路里移除后才能保存</t>
+          <t>基元仓已满：先腾出一个空位（固件仍留在信号核里）</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>"{0}" is core firmware and can only be carried by the signal: remove it from the machine circuit before saving</t>
+          <t>The primitive store is full: free a space first (the firmware stays in the Signal Core)</t>
         </is>
       </c>
     </row>
@@ -13176,17 +13176,17 @@
       <c r="A709" t="inlineStr"/>
       <c r="B709" t="inlineStr">
         <is>
-          <t>signal.reason.not_found</t>
+          <t>signal.reason.core_signal_only</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>找不到这枚芯片</t>
+          <t>核心固件只能由信号携带</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>That chip no longer exists</t>
+          <t>Core firmware can only be carried by the signal</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       <c r="A710" t="inlineStr"/>
       <c r="B710" t="inlineStr">
         <is>
-          <t>signal.reason.already_in_bag</t>
+          <t>signal.reason.not_firmware</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>它已经在基元仓里</t>
+          <t>只有固件能放进信号核（基元芯片装在电路板上）</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>It is already in the store</t>
+          <t>Only firmware fits in the Signal Core (primitive chips go on circuit boards)</t>
         </is>
       </c>
     </row>
@@ -13212,17 +13212,17 @@
       <c r="A711" t="inlineStr"/>
       <c r="B711" t="inlineStr">
         <is>
-          <t>signal.reason.not_in_bag</t>
+          <t>signal.reason.firmware_not_chip</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>这枚芯片不在基元仓里（可能已装在别处或待领取）</t>
+          <t>固件芯片不能装进 3×3 电路格：常规固件装在蓝图的固件槽，或放进信号核</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>That chip is not in the store (it may be installed elsewhere or waiting to be claimed)</t>
+          <t>Firmware chips do not go into the 3×3 circuit grid: put regular firmware in a blueprint's firmware slot or in the Signal Core</t>
         </is>
       </c>
     </row>
@@ -13230,17 +13230,17 @@
       <c r="A712" t="inlineStr"/>
       <c r="B712" t="inlineStr">
         <is>
-          <t>signal.reason.reserved</t>
+          <t>signal.reason.core_in_circuit</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>这枚芯片已被合成台预留为材料</t>
+          <t>“{0}”是核心固件，只能由信号携带：从机器电路里移除后才能保存</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>That chip is reserved as a crafting material</t>
+          <t>"{0}" is core firmware and can only be carried by the signal: remove it from the machine circuit before saving</t>
         </is>
       </c>
     </row>
@@ -13248,17 +13248,17 @@
       <c r="A713" t="inlineStr"/>
       <c r="B713" t="inlineStr">
         <is>
-          <t>signal.reason.slot_invalid</t>
+          <t>signal.reason.not_found</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>没有这个槽位</t>
+          <t>找不到这枚芯片</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>No such slot</t>
+          <t>That chip no longer exists</t>
         </is>
       </c>
     </row>
@@ -13266,17 +13266,17 @@
       <c r="A714" t="inlineStr"/>
       <c r="B714" t="inlineStr">
         <is>
-          <t>signal.reason.slot_locked</t>
+          <t>signal.reason.already_in_bag</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>{0} 号槽尚未解锁：需要超控阵列 T{1}</t>
+          <t>它已经在基元仓里</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Slot {0} is locked: needs Override Array T{1}</t>
+          <t>It is already in the store</t>
         </is>
       </c>
     </row>
@@ -13284,17 +13284,17 @@
       <c r="A715" t="inlineStr"/>
       <c r="B715" t="inlineStr">
         <is>
-          <t>signal.reason.slot_empty</t>
+          <t>signal.reason.not_in_bag</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>{0} 号槽是空的</t>
+          <t>这枚芯片不在基元仓里（可能已装在别处或待领取）</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Slot {0} is empty</t>
+          <t>That chip is not in the store (it may be installed elsewhere or waiting to be claimed)</t>
         </is>
       </c>
     </row>
@@ -13302,17 +13302,17 @@
       <c r="A716" t="inlineStr"/>
       <c r="B716" t="inlineStr">
         <is>
-          <t>signal.reason.same_slot</t>
+          <t>signal.reason.reserved</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>已经在这个槽位里</t>
+          <t>这枚芯片已被合成台预留为材料</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>It is already in that slot</t>
+          <t>That chip is reserved as a crafting material</t>
         </is>
       </c>
     </row>
@@ -13320,17 +13320,17 @@
       <c r="A717" t="inlineStr"/>
       <c r="B717" t="inlineStr">
         <is>
-          <t>signal.reason.preset_limit</t>
+          <t>signal.reason.slot_invalid</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>预设已达上限 {0} 个：先删除一个</t>
+          <t>没有这个槽位</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>You already have {0} presets: delete one first</t>
+          <t>No such slot</t>
         </is>
       </c>
     </row>
@@ -13338,17 +13338,17 @@
       <c r="A718" t="inlineStr"/>
       <c r="B718" t="inlineStr">
         <is>
-          <t>signal.reason.preset_not_found</t>
+          <t>signal.reason.slot_locked</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>找不到这个预设</t>
+          <t>{0} 号槽尚未解锁：需要超控阵列 T{1}</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>That preset no longer exists</t>
+          <t>Slot {0} is locked: needs Override Array T{1}</t>
         </is>
       </c>
     </row>
@@ -13356,17 +13356,17 @@
       <c r="A719" t="inlineStr"/>
       <c r="B719" t="inlineStr">
         <is>
-          <t>signal.reason.preset_name_long</t>
+          <t>signal.reason.slot_empty</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>名称最多 {0} 个字</t>
+          <t>{0} 号槽是空的</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Names can be at most {0} characters</t>
+          <t>Slot {0} is empty</t>
         </is>
       </c>
     </row>
@@ -13374,17 +13374,17 @@
       <c r="A720" t="inlineStr"/>
       <c r="B720" t="inlineStr">
         <is>
-          <t>signal.reason.preset_name_empty</t>
+          <t>signal.reason.same_slot</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>名称不能为空</t>
+          <t>已经在这个槽位里</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>The name cannot be empty</t>
+          <t>It is already in that slot</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13392,17 @@
       <c r="A721" t="inlineStr"/>
       <c r="B721" t="inlineStr">
         <is>
-          <t>signal.reason.preset_bag_full</t>
+          <t>signal.reason.preset_limit</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>切换要把 {0} 枚固件卸回基元仓，但只剩 {1} 个空位</t>
+          <t>预设已达上限 {0} 个：先删除一个</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Switching would return {0} firmware to the store, but only {1} spaces are free</t>
+          <t>You already have {0} presets: delete one first</t>
         </is>
       </c>
     </row>
@@ -13410,17 +13410,17 @@
       <c r="A722" t="inlineStr"/>
       <c r="B722" t="inlineStr">
         <is>
-          <t>signal.reason.preset_not_selected</t>
+          <t>signal.reason.preset_not_found</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>先在下拉框里选一个预设</t>
+          <t>找不到这个预设</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Pick a preset in the list first</t>
+          <t>That preset no longer exists</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13428,17 @@
       <c r="A723" t="inlineStr"/>
       <c r="B723" t="inlineStr">
         <is>
-          <t>signal.reason.print_locked</t>
+          <t>signal.reason.preset_name_long</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>“{0}”尚未解锁，不能刻印</t>
+          <t>名称最多 {0} 个字</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>"{0}" is not unlocked yet</t>
+          <t>Names can be at most {0} characters</t>
         </is>
       </c>
     </row>
@@ -13446,17 +13446,17 @@
       <c r="A724" t="inlineStr"/>
       <c r="B724" t="inlineStr">
         <is>
-          <t>signal.reason.print_bag_full</t>
+          <t>signal.reason.preset_name_empty</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>基元仓已满，不能刻印：先腾出空位或领取待领取的芯片</t>
+          <t>名称不能为空</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>The store is full: free a space or claim waiting chips first</t>
+          <t>The name cannot be empty</t>
         </is>
       </c>
     </row>
@@ -13464,17 +13464,17 @@
       <c r="A725" t="inlineStr"/>
       <c r="B725" t="inlineStr">
         <is>
-          <t>signal.reason.print_no_power</t>
+          <t>signal.reason.preset_bag_full</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>装配站未完工或没有电，不能刻印</t>
+          <t>切换要把 {0} 枚固件卸回基元仓，但只剩 {1} 个空位</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>The Assembly Station is not built or has no power</t>
+          <t>Switching would return {0} firmware to the store, but only {1} spaces are free</t>
         </is>
       </c>
     </row>
@@ -13482,17 +13482,17 @@
       <c r="A726" t="inlineStr"/>
       <c r="B726" t="inlineStr">
         <is>
-          <t>signal.reason.print_scrap</t>
+          <t>signal.reason.preset_not_selected</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>废料不足：刻印需要 {0}</t>
+          <t>先在下拉框里选一个预设</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Not enough scrap: printing needs {0}</t>
+          <t>Pick a preset in the list first</t>
         </is>
       </c>
     </row>
@@ -13500,17 +13500,17 @@
       <c r="A727" t="inlineStr"/>
       <c r="B727" t="inlineStr">
         <is>
-          <t>signal.reason.print_unknown</t>
+          <t>signal.reason.print_locked</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>“{0}”不是固件，不能刻印</t>
+          <t>“{0}”尚未解锁，不能刻印</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>"{0}" is not firmware</t>
+          <t>"{0}" is not unlocked yet</t>
         </is>
       </c>
     </row>
@@ -13518,17 +13518,17 @@
       <c r="A728" t="inlineStr"/>
       <c r="B728" t="inlineStr">
         <is>
-          <t>signal.reason.nothing_selected</t>
+          <t>signal.reason.print_bag_full</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>先选一枚固件</t>
+          <t>基元仓已满，不能刻印：先腾出空位或领取待领取的芯片</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Pick a firmware chip first</t>
+          <t>The store is full: free a space or claim waiting chips first</t>
         </is>
       </c>
     </row>
@@ -13536,17 +13536,17 @@
       <c r="A729" t="inlineStr"/>
       <c r="B729" t="inlineStr">
         <is>
-          <t>signal.hud.at_core</t>
+          <t>signal.reason.print_no_power</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>信号：归还核心</t>
+          <t>装配站未完工或没有电，不能刻印</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Signal: Reclamation Core</t>
+          <t>The Assembly Station is not built or has no power</t>
         </is>
       </c>
     </row>
@@ -13554,17 +13554,17 @@
       <c r="A730" t="inlineStr"/>
       <c r="B730" t="inlineStr">
         <is>
-          <t>signal.hud.in_machine</t>
+          <t>signal.reason.print_scrap</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>信号：{0}</t>
+          <t>废料不足：刻印需要 {0}</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Signal: {0}</t>
+          <t>Not enough scrap: printing needs {0}</t>
         </is>
       </c>
     </row>
@@ -13572,17 +13572,17 @@
       <c r="A731" t="inlineStr"/>
       <c r="B731" t="inlineStr">
         <is>
-          <t>signal.hud.core_button</t>
+          <t>signal.reason.print_unknown</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>信号核 {0}/{1}</t>
+          <t>“{0}”不是固件，不能刻印</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Signal Core {0}/{1}</t>
+          <t>"{0}" is not firmware</t>
         </is>
       </c>
     </row>
@@ -13590,17 +13590,17 @@
       <c r="A732" t="inlineStr"/>
       <c r="B732" t="inlineStr">
         <is>
-          <t>signal.hud.core_button_locked</t>
+          <t>signal.reason.nothing_selected</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>信号核 {0}/{1} · 远征中锁定</t>
+          <t>先选一枚固件</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Signal Core {0}/{1} · locked on expedition</t>
+          <t>Pick a firmware chip first</t>
         </is>
       </c>
     </row>
@@ -13608,17 +13608,17 @@
       <c r="A733" t="inlineStr"/>
       <c r="B733" t="inlineStr">
         <is>
-          <t>signal.hud.tip_title</t>
+          <t>signal.hud.at_core</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>信号在哪里</t>
+          <t>信号：归还核心</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Where the signal is</t>
+          <t>Signal: Reclamation Core</t>
         </is>
       </c>
     </row>
@@ -13626,17 +13626,17 @@
       <c r="A734" t="inlineStr"/>
       <c r="B734" t="inlineStr">
         <is>
-          <t>signal.hud.tip</t>
+          <t>signal.hud.in_machine</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或者一台接入的机器。点这里或按 {0} 打开信号核。</t>
+          <t>信号：{0}</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>You are the signal sent by the Reclamation Core and are always in one place: the core or one uplinked machine. Click here or press {0} to open the Signal Core.</t>
+          <t>Signal: {0}</t>
         </is>
       </c>
     </row>
@@ -13644,17 +13644,17 @@
       <c r="A735" t="inlineStr"/>
       <c r="B735" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.source_slot</t>
+          <t>signal.hud.core_button</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>0 号格是电源源点，不能标为接入口</t>
+          <t>信号核 {0}/{1}</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Slot 0 is the power source and cannot be an uplink port</t>
+          <t>Signal Core {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -13662,17 +13662,17 @@
       <c r="A736" t="inlineStr"/>
       <c r="B736" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.sink_slot</t>
+          <t>signal.hud.core_button_locked</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>8 号格是主组件，不能标为接入口</t>
+          <t>信号核 {0}/{1} · 远征中锁定</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Slot 8 is the main component and cannot be an uplink port</t>
+          <t>Signal Core {0}/{1} · locked on expedition</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13680,17 @@
       <c r="A737" t="inlineStr"/>
       <c r="B737" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.out_of_range</t>
+          <t>signal.hud.tip_title</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>没有 {0} 号格</t>
+          <t>信号在哪里</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>There is no slot {0}</t>
+          <t>Where the signal is</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13698,17 @@
       <c r="A738" t="inlineStr"/>
       <c r="B738" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.same_slot</t>
+          <t>signal.hud.tip</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>{0} 号格已经是接入口</t>
+          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或者一台接入的机器。点这里或按 {0} 打开信号核。</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Slot {0} is already the uplink port</t>
+          <t>You are the signal sent by the Reclamation Core and are always in one place: the core or one uplinked machine. Click here or press {0} to open the Signal Core.</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13716,17 @@
       <c r="A739" t="inlineStr"/>
       <c r="B739" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.second</t>
+          <t>circuit.uplink.reason.source_slot</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>每张蓝图最多 1 个接入口：先取消 {0} 号格的接入口，再标新的位置</t>
+          <t>0 号格是电源源点，不能标为接入口</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>A blueprint can have only one uplink port: clear the port on slot {0} first, then mark the new slot</t>
+          <t>Slot 0 is the power source and cannot be an uplink port</t>
         </is>
       </c>
     </row>
@@ -13734,17 +13734,17 @@
       <c r="A740" t="inlineStr"/>
       <c r="B740" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.occupied</t>
+          <t>circuit.uplink.reason.sink_slot</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>{0} 号格装着芯片：接入口必须是空格，先把芯片卸回基元仓</t>
+          <t>8 号格是主组件，不能标为接入口</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Slot {0} holds a chip: the uplink port must be an empty slot, so return the chip to the store first</t>
+          <t>Slot 8 is the main component and cannot be an uplink port</t>
         </is>
       </c>
     </row>
@@ -13752,17 +13752,17 @@
       <c r="A741" t="inlineStr"/>
       <c r="B741" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.none</t>
+          <t>circuit.uplink.reason.out_of_range</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>这张蓝图没有接入口</t>
+          <t>没有 {0} 号格</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>This blueprint has no uplink port</t>
+          <t>There is no slot {0}</t>
         </is>
       </c>
     </row>
@@ -13770,17 +13770,17 @@
       <c r="A742" t="inlineStr"/>
       <c r="B742" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.cell_is_uplink</t>
+          <t>circuit.uplink.reason.same_slot</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>{0} 号格是接入口：先取消接入口，才能在这里装芯片</t>
+          <t>{0} 号格已经是接入口</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Slot {0} is the uplink port: clear the port before installing a chip here</t>
+          <t>Slot {0} is already the uplink port</t>
         </is>
       </c>
     </row>
@@ -13788,17 +13788,17 @@
       <c r="A743" t="inlineStr"/>
       <c r="B743" t="inlineStr">
         <is>
-          <t>circuit.uplink.reason.no_slot</t>
+          <t>circuit.uplink.reason.second</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>先点选一个空的 1～7 号格，再标为接入口</t>
+          <t>每张蓝图最多 1 个接入口：先取消 {0} 号格的接入口，再标新的位置</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Pick an empty slot 1-7 first, then mark it as the uplink port</t>
+          <t>A blueprint can have only one uplink port: clear the port on slot {0} first, then mark the new slot</t>
         </is>
       </c>
     </row>
@@ -13806,17 +13806,17 @@
       <c r="A744" t="inlineStr"/>
       <c r="B744" t="inlineStr">
         <is>
-          <t>circuit.uplink.tag</t>
+          <t>circuit.uplink.reason.occupied</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>接入口</t>
+          <t>{0} 号格装着芯片：接入口必须是空格，先把芯片卸回基元仓</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>Slot {0} holds a chip: the uplink port must be an empty slot, so return the chip to the store first</t>
         </is>
       </c>
     </row>
@@ -13824,17 +13824,17 @@
       <c r="A745" t="inlineStr"/>
       <c r="B745" t="inlineStr">
         <is>
-          <t>circuit.uplink.mark</t>
+          <t>circuit.uplink.reason.none</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>标为接入口</t>
+          <t>这张蓝图没有接入口</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Mark as uplink port</t>
+          <t>This blueprint has no uplink port</t>
         </is>
       </c>
     </row>
@@ -13842,17 +13842,17 @@
       <c r="A746" t="inlineStr"/>
       <c r="B746" t="inlineStr">
         <is>
-          <t>circuit.uplink.unmark</t>
+          <t>circuit.uplink.reason.cell_is_uplink</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>取消接入口</t>
+          <t>{0} 号格是接入口：先取消接入口，才能在这里装芯片</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Clear uplink port</t>
+          <t>Slot {0} is the uplink port: clear the port before installing a chip here</t>
         </is>
       </c>
     </row>
@@ -13860,17 +13860,17 @@
       <c r="A747" t="inlineStr"/>
       <c r="B747" t="inlineStr">
         <is>
-          <t>circuit.uplink.marked</t>
+          <t>circuit.uplink.reason.no_slot</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>已把 {0} 号格标为接入口</t>
+          <t>先点选一个空的 1～7 号格，再标为接入口</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Slot {0} is now the uplink port</t>
+          <t>Pick an empty slot 1-7 first, then mark it as the uplink port</t>
         </is>
       </c>
     </row>
@@ -13878,17 +13878,17 @@
       <c r="A748" t="inlineStr"/>
       <c r="B748" t="inlineStr">
         <is>
-          <t>circuit.uplink.cleared</t>
+          <t>circuit.uplink.tag</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>已取消接入口</t>
+          <t>接入口</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Uplink port cleared</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       <c r="A749" t="inlineStr"/>
       <c r="B749" t="inlineStr">
         <is>
-          <t>circuit.uplink.slot_detail</t>
+          <t>circuit.uplink.mark</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>◇ 接入口：你接入这台机器时，信号核的固件按槽位顺序插在这一格（最多 {0} 个，不占电路负载）；AI 驾驶时它只是空槽，照样传导。</t>
+          <t>标为接入口</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>◇ Uplink port: when you uplink into this machine, Signal Core firmware is inserted here in slot order (up to {0}, not counted against circuit load). Under AI control it is an empty slot that still conducts.</t>
+          <t>Mark as uplink port</t>
         </is>
       </c>
     </row>
@@ -13914,17 +13914,17 @@
       <c r="A750" t="inlineStr"/>
       <c r="B750" t="inlineStr">
         <is>
-          <t>circuit.uplink.title</t>
+          <t>circuit.uplink.unmark</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>双态编译预览</t>
+          <t>取消接入口</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Dual compile preview</t>
+          <t>Clear uplink port</t>
         </is>
       </c>
     </row>
@@ -13932,17 +13932,17 @@
       <c r="A751" t="inlineStr"/>
       <c r="B751" t="inlineStr">
         <is>
-          <t>circuit.uplink.col_ai</t>
+          <t>circuit.uplink.marked</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>AI 驾驶时</t>
+          <t>已把 {0} 号格标为接入口</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>AI driving</t>
+          <t>Slot {0} is now the uplink port</t>
         </is>
       </c>
     </row>
@@ -13950,17 +13950,17 @@
       <c r="A752" t="inlineStr"/>
       <c r="B752" t="inlineStr">
         <is>
-          <t>circuit.uplink.col_uplinked</t>
+          <t>circuit.uplink.cleared</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>你接入时</t>
+          <t>已取消接入口</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>When you uplink</t>
+          <t>Uplink port cleared</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       <c r="A753" t="inlineStr"/>
       <c r="B753" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff_title</t>
+          <t>circuit.uplink.slot_detail</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>接入后的变化</t>
+          <t>◇ 接入口：你接入这台机器时，信号核的固件按槽位顺序插在这一格（最多 {0} 个，不占电路负载）；AI 驾驶时它只是空槽，照样传导。</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>What changes when you uplink</t>
+          <t>◇ Uplink port: when you uplink into this machine, Signal Core firmware is inserted here in slot order (up to {0}, not counted against circuit load). Under AI control it is an empty slot that still conducts.</t>
         </is>
       </c>
     </row>
@@ -13986,17 +13986,17 @@
       <c r="A754" t="inlineStr"/>
       <c r="B754" t="inlineStr">
         <is>
-          <t>circuit.uplink.core_line</t>
+          <t>circuit.uplink.title</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>按当前信号核计算（{0}）</t>
+          <t>双态编译预览</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Using your current Signal Core ({0})</t>
+          <t>Dual compile preview</t>
         </is>
       </c>
     </row>
@@ -14004,17 +14004,17 @@
       <c r="A755" t="inlineStr"/>
       <c r="B755" t="inlineStr">
         <is>
-          <t>circuit.uplink.none_word</t>
+          <t>circuit.uplink.col_ai</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>AI 驾驶时</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>AI driving</t>
         </is>
       </c>
     </row>
@@ -14022,17 +14022,17 @@
       <c r="A756" t="inlineStr"/>
       <c r="B756" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.no_uplink</t>
+          <t>circuit.uplink.col_uplinked</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>接入口：没有</t>
+          <t>你接入时</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Uplink port: none</t>
+          <t>When you uplink</t>
         </is>
       </c>
     </row>
@@ -14040,17 +14040,17 @@
       <c r="A757" t="inlineStr"/>
       <c r="B757" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.uplink_empty</t>
+          <t>circuit.uplink.diff_title</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>接入口 {0} 号格：空（按空槽传导）</t>
+          <t>接入后的变化</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Uplink slot {0}: empty (conducts as an empty slot)</t>
+          <t>What changes when you uplink</t>
         </is>
       </c>
     </row>
@@ -14058,17 +14058,17 @@
       <c r="A758" t="inlineStr"/>
       <c r="B758" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.uplink_filled</t>
+          <t>circuit.uplink.core_line</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>接入口 {0} 号格：{1}（{2}/{3}）</t>
+          <t>按当前信号核计算（{0}）</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Uplink slot {0}: {1} ({2}/{3})</t>
+          <t>Using your current Signal Core ({0})</t>
         </is>
       </c>
     </row>
@@ -14076,17 +14076,17 @@
       <c r="A759" t="inlineStr"/>
       <c r="B759" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.paths</t>
+          <t>circuit.uplink.none_word</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>有效路径 {0} 条</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>{0} valid paths</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -14094,17 +14094,17 @@
       <c r="A760" t="inlineStr"/>
       <c r="B760" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.no_output</t>
+          <t>circuit.uplink.line.no_uplink</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>没有可攻击输出</t>
+          <t>接入口：没有</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>No attack output</t>
+          <t>Uplink port: none</t>
         </is>
       </c>
     </row>
@@ -14112,17 +14112,17 @@
       <c r="A761" t="inlineStr"/>
       <c r="B761" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.damage</t>
+          <t>circuit.uplink.line.uplink_empty</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>平均伤害 {0}</t>
+          <t>接入口 {0} 号格：空（按空槽传导）</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Average damage {0}</t>
+          <t>Uplink slot {0}: empty (conducts as an empty slot)</t>
         </is>
       </c>
     </row>
@@ -14130,17 +14130,17 @@
       <c r="A762" t="inlineStr"/>
       <c r="B762" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.heat</t>
+          <t>circuit.uplink.line.uplink_filled</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>热量预算 {0}</t>
+          <t>接入口 {0} 号格：{1}（{2}/{3}）</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Heat budget {0}</t>
+          <t>Uplink slot {0}: {1} ({2}/{3})</t>
         </is>
       </c>
     </row>
@@ -14148,17 +14148,17 @@
       <c r="A763" t="inlineStr"/>
       <c r="B763" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.reaction</t>
+          <t>circuit.uplink.line.paths</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>反应：{0}</t>
+          <t>有效路径 {0} 条</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Reaction: {0}</t>
+          <t>{0} valid paths</t>
         </is>
       </c>
     </row>
@@ -14166,17 +14166,17 @@
       <c r="A764" t="inlineStr"/>
       <c r="B764" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.reaction_none</t>
+          <t>circuit.uplink.line.no_output</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>反应：无</t>
+          <t>没有可攻击输出</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Reaction: none</t>
+          <t>No attack output</t>
         </is>
       </c>
     </row>
@@ -14184,17 +14184,17 @@
       <c r="A765" t="inlineStr"/>
       <c r="B765" t="inlineStr">
         <is>
-          <t>circuit.uplink.line.firmware</t>
+          <t>circuit.uplink.line.damage</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>生效固件：{0}</t>
+          <t>平均伤害 {0}</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Active firmware: {0}</t>
+          <t>Average damage {0}</t>
         </is>
       </c>
     </row>
@@ -14202,17 +14202,17 @@
       <c r="A766" t="inlineStr"/>
       <c r="B766" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.none</t>
+          <t>circuit.uplink.line.heat</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>与 AI 驾驶时相同</t>
+          <t>热量预算 {0}</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Same as under AI control</t>
+          <t>Heat budget {0}</t>
         </is>
       </c>
     </row>
@@ -14220,17 +14220,17 @@
       <c r="A767" t="inlineStr"/>
       <c r="B767" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.path_added</t>
+          <t>circuit.uplink.line.reaction</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>＋新增路径 {0}（伤害 {1}）</t>
+          <t>反应：{0}</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>+ New path {0} (damage {1})</t>
+          <t>Reaction: {0}</t>
         </is>
       </c>
     </row>
@@ -14238,17 +14238,17 @@
       <c r="A768" t="inlineStr"/>
       <c r="B768" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.path</t>
+          <t>circuit.uplink.line.reaction_none</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>＋路径 {0} 插入 {1}：伤害 {2} → {3}</t>
+          <t>反应：无</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>+ Path {0} gets {1}: damage {2} → {3}</t>
+          <t>Reaction: none</t>
         </is>
       </c>
     </row>
@@ -14256,17 +14256,17 @@
       <c r="A769" t="inlineStr"/>
       <c r="B769" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.path_same</t>
+          <t>circuit.uplink.line.firmware</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>＋路径 {0} 插入 {1}（伤害不变 {2}，效果见固件说明）</t>
+          <t>生效固件：{0}</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>+ Path {0} gets {1} (damage unchanged at {2}; see the firmware description)</t>
+          <t>Active firmware: {0}</t>
         </is>
       </c>
     </row>
@@ -14274,17 +14274,17 @@
       <c r="A770" t="inlineStr"/>
       <c r="B770" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.reaction_added</t>
+          <t>circuit.uplink.diff.none</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>＋新增反应：{0}</t>
+          <t>与 AI 驾驶时相同</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>+ New reaction: {0}</t>
+          <t>Same as under AI control</t>
         </is>
       </c>
     </row>
@@ -14292,17 +14292,17 @@
       <c r="A771" t="inlineStr"/>
       <c r="B771" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.reaction_changed</t>
+          <t>circuit.uplink.diff.path_added</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>反应变化：{0} → {1}</t>
+          <t>＋新增路径 {0}（伤害 {1}）</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Reaction changes: {0} → {1}</t>
+          <t>+ New path {0} (damage {1})</t>
         </is>
       </c>
     </row>
@@ -14310,17 +14310,17 @@
       <c r="A772" t="inlineStr"/>
       <c r="B772" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.heat</t>
+          <t>circuit.uplink.diff.path</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>热量预算 {0} → {1}</t>
+          <t>＋路径 {0} 插入 {1}：伤害 {2} → {3}</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Heat budget {0} → {1}</t>
+          <t>+ Path {0} gets {1}: damage {2} → {3}</t>
         </is>
       </c>
     </row>
@@ -14328,17 +14328,17 @@
       <c r="A773" t="inlineStr"/>
       <c r="B773" t="inlineStr">
         <is>
-          <t>circuit.uplink.diff.damage</t>
+          <t>circuit.uplink.diff.path_same</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>平均伤害 {0} → {1}</t>
+          <t>＋路径 {0} 插入 {1}（伤害不变 {2}，效果见固件说明）</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Average damage {0} → {1}</t>
+          <t>+ Path {0} gets {1} (damage unchanged at {2}; see the firmware description)</t>
         </is>
       </c>
     </row>
@@ -14346,17 +14346,17 @@
       <c r="A774" t="inlineStr"/>
       <c r="B774" t="inlineStr">
         <is>
-          <t>circuit.uplink.note.no_uplink</t>
+          <t>circuit.uplink.diff.reaction_added</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>这张蓝图没有接入口：接入后可以驾驶、瞄准、使用主动作，但不插入固件。在电路上选一个空格“标为接入口”即可加上</t>
+          <t>＋新增反应：{0}</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>This blueprint has no uplink port: you can drive, aim and use the main action, but no firmware is inserted. Pick an empty slot and mark it as the uplink port to add one</t>
+          <t>+ New reaction: {0}</t>
         </is>
       </c>
     </row>
@@ -14364,17 +14364,17 @@
       <c r="A775" t="inlineStr"/>
       <c r="B775" t="inlineStr">
         <is>
-          <t>circuit.uplink.note.core_empty</t>
+          <t>circuit.uplink.diff.reaction_changed</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>信号核没有固件：接入后接入口为空，与 AI 驾驶时相同（按 {0} 打开信号核装固件）</t>
+          <t>反应变化：{0} → {1}</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>The Signal Core has no firmware: after uplinking the port stays empty, same as AI control (press {0} to open the Signal Core)</t>
+          <t>Reaction changes: {0} → {1}</t>
         </is>
       </c>
     </row>
@@ -14382,17 +14382,17 @@
       <c r="A776" t="inlineStr"/>
       <c r="B776" t="inlineStr">
         <is>
-          <t>circuit.uplink.note.off_path</t>
+          <t>circuit.uplink.diff.heat</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>接入口 {0} 号格不在任何源→汇路径上：插进去的固件不会生效——把导线连过这一格</t>
+          <t>热量预算 {0} → {1}</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Uplink slot {0} is not on any source→sink path, so inserted firmware has no effect: route a wire through it</t>
+          <t>Heat budget {0} → {1}</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       <c r="A777" t="inlineStr"/>
       <c r="B777" t="inlineStr">
         <is>
-          <t>circuit.uplink.skip.over_quota</t>
+          <t>circuit.uplink.diff.damage</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>未插入：{0}（超出接入口配额 {1} 个）</t>
+          <t>平均伤害 {0} → {1}</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Not inserted: {0} (over the uplink quota of {1})</t>
+          <t>Average damage {0} → {1}</t>
         </is>
       </c>
     </row>
@@ -14418,17 +14418,17 @@
       <c r="A778" t="inlineStr"/>
       <c r="B778" t="inlineStr">
         <is>
-          <t>circuit.uplink.skip.path_limit</t>
+          <t>circuit.uplink.note.no_uplink</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>未插入：{0}（插入后路径会超过上限 {1} 条）</t>
+          <t>这张蓝图没有接入口：接入后可以驾驶、瞄准、使用主动作，但不插入固件。在电路上选一个空格“标为接入口”即可加上</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Not inserted: {0} (paths would exceed the limit of {1})</t>
+          <t>This blueprint has no uplink port: you can drive, aim and use the main action, but no firmware is inserted. Pick an empty slot and mark it as the uplink port to add one</t>
         </is>
       </c>
     </row>
@@ -14436,17 +14436,17 @@
       <c r="A779" t="inlineStr"/>
       <c r="B779" t="inlineStr">
         <is>
-          <t>circuit.uplink.skip.unknown</t>
+          <t>circuit.uplink.note.core_empty</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>未插入：{0}（不是已知的固件）</t>
+          <t>信号核没有固件：接入后接入口为空，与 AI 驾驶时相同（按 {0} 打开信号核装固件）</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Not inserted: {0} (not a known firmware)</t>
+          <t>The Signal Core has no firmware: after uplinking the port stays empty, same as AI control (press {0} to open the Signal Core)</t>
         </is>
       </c>
     </row>
@@ -14454,17 +14454,17 @@
       <c r="A780" t="inlineStr"/>
       <c r="B780" t="inlineStr">
         <is>
-          <t>circuit.uplink.skip.no_uplink</t>
+          <t>circuit.uplink.note.off_path</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>未插入：{0}（此机器没有接入口）</t>
+          <t>接入口 {0} 号格不在任何源→汇路径上：插进去的固件不会生效——把导线连过这一格</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>Not inserted: {0} (this machine has no uplink port)</t>
+          <t>Uplink slot {0} is not on any source→sink path, so inserted firmware has no effect: route a wire through it</t>
         </is>
       </c>
     </row>
@@ -14472,17 +14472,17 @@
       <c r="A781" t="inlineStr"/>
       <c r="B781" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.no_campaign</t>
+          <t>circuit.uplink.skip.over_quota</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>没有进行中的战役</t>
+          <t>未插入：{0}（超出接入口配额 {1} 个）</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>No campaign in progress</t>
+          <t>Not inserted: {0} (over the uplink quota of {1})</t>
         </is>
       </c>
     </row>
@@ -14490,17 +14490,17 @@
       <c r="A782" t="inlineStr"/>
       <c r="B782" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.no_selection</t>
+          <t>circuit.uplink.skip.path_limit</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>先选中一台机器（左键点选或框选），再按 {0} 接入；也可以在机器列表里直接点它</t>
+          <t>未插入：{0}（插入后路径会超过上限 {1} 条）</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Select a machine first (click or box-select), then press {0}; or click it in the machine list</t>
+          <t>Not inserted: {0} (paths would exceed the limit of {1})</t>
         </is>
       </c>
     </row>
@@ -14508,17 +14508,17 @@
       <c r="A783" t="inlineStr"/>
       <c r="B783" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.not_found</t>
+          <t>circuit.uplink.skip.unknown</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>找不到这台机器</t>
+          <t>未插入：{0}（不是已知的固件）</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>That machine no longer exists</t>
+          <t>Not inserted: {0} (not a known firmware)</t>
         </is>
       </c>
     </row>
@@ -14526,17 +14526,17 @@
       <c r="A784" t="inlineStr"/>
       <c r="B784" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.dead</t>
+          <t>circuit.uplink.skip.no_uplink</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>{0} 已阵亡，不能接入</t>
+          <t>未插入：{0}（此机器没有接入口）</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>{0} has been destroyed and cannot be uplinked</t>
+          <t>Not inserted: {0} (this machine has no uplink port)</t>
         </is>
       </c>
     </row>
@@ -14544,17 +14544,17 @@
       <c r="A785" t="inlineStr"/>
       <c r="B785" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.other_site</t>
+          <t>signal.uplink.reason.no_campaign</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>{0} 不在当前查看的地点：先把镜头切到它所在的地点</t>
+          <t>没有进行中的战役</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>{0} is not at the site you are viewing: move the camera to its site first</t>
+          <t>No campaign in progress</t>
         </is>
       </c>
     </row>
@@ -14562,17 +14562,17 @@
       <c r="A786" t="inlineStr"/>
       <c r="B786" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.out_of_coverage</t>
+          <t>signal.uplink.reason.no_selection</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>超出信号覆盖：{0} 不在与归还核心连通的覆盖范围里，需要信号中继塔或中继模块</t>
+          <t>先选中一台机器（左键点选或框选），再按 {0} 接入；也可以在机器列表里直接点它</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Out of coverage: {0} is outside the coverage connected to the Reclamation Core; build a signal relay tower or fit a relay module</t>
+          <t>Select a machine first (click or box-select), then press {0}; or click it in the machine list</t>
         </is>
       </c>
     </row>
@@ -14580,17 +14580,17 @@
       <c r="A787" t="inlineStr"/>
       <c r="B787" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.jammed</t>
+          <t>signal.uplink.reason.not_found</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>被干扰：{0} 在干扰场里，让它先离开干扰场</t>
+          <t>找不到这台机器</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Jammed: {0} is inside a jamming field; move it out first</t>
+          <t>That machine no longer exists</t>
         </is>
       </c>
     </row>
@@ -14598,17 +14598,17 @@
       <c r="A788" t="inlineStr"/>
       <c r="B788" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.silent_night</t>
+          <t>signal.uplink.reason.dead</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>静默夜：信号发不出去，天亮后再接入</t>
+          <t>{0} 已阵亡，不能接入</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Silent night: the signal cannot go out; uplink again after dawn</t>
+          <t>{0} has been destroyed and cannot be uplinked</t>
         </is>
       </c>
     </row>
@@ -14616,17 +14616,17 @@
       <c r="A789" t="inlineStr"/>
       <c r="B789" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.in_factory</t>
+          <t>signal.uplink.reason.other_site</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>{0} 还在装配站里：出厂后才能接入</t>
+          <t>{0} 不在当前查看的地点：先把镜头切到它所在的地点</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>{0} is still in the Assembly Station: uplink after it rolls out</t>
+          <t>{0} is not at the site you are viewing: move the camera to its site first</t>
         </is>
       </c>
     </row>
@@ -14634,17 +14634,17 @@
       <c r="A790" t="inlineStr"/>
       <c r="B790" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.on_repair_bay</t>
+          <t>signal.uplink.reason.out_of_coverage</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>{0} 在维修台上：维修结束后才能接入</t>
+          <t>超出信号覆盖：{0} 不在与归还核心连通的覆盖范围里，需要信号中继塔或中继模块</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>{0} is on the repair bay: uplink after the repair</t>
+          <t>Out of coverage: {0} is outside the coverage connected to the Reclamation Core; build a signal relay tower or fit a relay module</t>
         </is>
       </c>
     </row>
@@ -14652,17 +14652,17 @@
       <c r="A791" t="inlineStr"/>
       <c r="B791" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.in_delivery</t>
+          <t>signal.uplink.reason.jammed</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>{0} 正在投送途中：到达后才能接入</t>
+          <t>被干扰：{0} 在干扰场里，让它先离开干扰场</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>{0} is being delivered: uplink after it arrives</t>
+          <t>Jammed: {0} is inside a jamming field; move it out first</t>
         </is>
       </c>
     </row>
@@ -14670,17 +14670,17 @@
       <c r="A792" t="inlineStr"/>
       <c r="B792" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.modal</t>
+          <t>signal.uplink.reason.silent_night</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>先关闭当前面板再接入</t>
+          <t>静默夜：信号发不出去，天亮后再接入</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Close the open panel before uplinking</t>
+          <t>Silent night: the signal cannot go out; uplink again after dawn</t>
         </is>
       </c>
     </row>
@@ -14688,17 +14688,17 @@
       <c r="A793" t="inlineStr"/>
       <c r="B793" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.busy</t>
+          <t>signal.uplink.reason.in_factory</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>正在接入 {0}，请稍候</t>
+          <t>{0} 还在装配站里：出厂后才能接入</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Uplinking into {0}, please wait</t>
+          <t>{0} is still in the Assembly Station: uplink after it rolls out</t>
         </is>
       </c>
     </row>
@@ -14706,17 +14706,17 @@
       <c r="A794" t="inlineStr"/>
       <c r="B794" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.already</t>
+          <t>signal.uplink.reason.on_repair_bay</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>信号已经在 {0} 里</t>
+          <t>{0} 在维修台上：维修结束后才能接入</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>The signal is already in {0}</t>
+          <t>{0} is on the repair bay: uplink after the repair</t>
         </is>
       </c>
     </row>
@@ -14724,17 +14724,17 @@
       <c r="A795" t="inlineStr"/>
       <c r="B795" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.no_candidate</t>
+          <t>signal.uplink.reason.in_delivery</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>这里没有别的机器可以切换</t>
+          <t>{0} 正在投送途中：到达后才能接入</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>There is no other machine here to switch to</t>
+          <t>{0} is being delivered: uplink after it arrives</t>
         </is>
       </c>
     </row>
@@ -14742,17 +14742,17 @@
       <c r="A796" t="inlineStr"/>
       <c r="B796" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.view_leaving</t>
+          <t>signal.uplink.reason.modal</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>镜头正在拉回战略视角：落地后再接入</t>
+          <t>先关闭当前面板再接入</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>The camera is pulling back to the strategic view: uplink once it lands</t>
+          <t>Close the open panel before uplinking</t>
         </is>
       </c>
     </row>
@@ -14760,17 +14760,17 @@
       <c r="A797" t="inlineStr"/>
       <c r="B797" t="inlineStr">
         <is>
-          <t>signal.uplink.reason.enemy</t>
+          <t>signal.uplink.reason.busy</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>{0} 不是友方机器</t>
+          <t>正在接入 {0}，请稍候</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>{0} is not a friendly machine</t>
+          <t>Uplinking into {0}, please wait</t>
         </is>
       </c>
     </row>
@@ -14778,17 +14778,17 @@
       <c r="A798" t="inlineStr"/>
       <c r="B798" t="inlineStr">
         <is>
-          <t>signal.uplink.pending</t>
+          <t>signal.uplink.reason.already</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>正在接入 {0}…</t>
+          <t>信号已经在 {0} 里</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>Uplinking into {0}…</t>
+          <t>The signal is already in {0}</t>
         </is>
       </c>
     </row>
@@ -14796,17 +14796,17 @@
       <c r="A799" t="inlineStr"/>
       <c r="B799" t="inlineStr">
         <is>
-          <t>signal.uplink.pending_paused</t>
+          <t>signal.uplink.reason.no_candidate</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>接入 {0}：恢复运行后完成（Esc 取消）</t>
+          <t>这里没有别的机器可以切换</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Uplink to {0}: completes when the game resumes (Esc to cancel)</t>
+          <t>There is no other machine here to switch to</t>
         </is>
       </c>
     </row>
@@ -14814,17 +14814,17 @@
       <c r="A800" t="inlineStr"/>
       <c r="B800" t="inlineStr">
         <is>
-          <t>signal.uplink.cancel.dead</t>
+          <t>signal.uplink.reason.view_leaving</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>接入途中 {0} 阵亡：接入已取消，信号留在原处</t>
+          <t>镜头正在拉回战略视角：落地后再接入</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>{0} was destroyed during the uplink: uplink cancelled, the signal stays where it was</t>
+          <t>The camera is pulling back to the strategic view: uplink once it lands</t>
         </is>
       </c>
     </row>
@@ -14832,17 +14832,17 @@
       <c r="A801" t="inlineStr"/>
       <c r="B801" t="inlineStr">
         <is>
-          <t>signal.uplink.cancel.gone</t>
+          <t>signal.uplink.reason.enemy</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>接入途中 {0} 不可接入了（{1}）：接入已取消，信号留在原处</t>
+          <t>{0} 不是友方机器</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>{0} became unavailable during the uplink ({1}): uplink cancelled, the signal stays where it was</t>
+          <t>{0} is not a friendly machine</t>
         </is>
       </c>
     </row>
@@ -14850,17 +14850,17 @@
       <c r="A802" t="inlineStr"/>
       <c r="B802" t="inlineStr">
         <is>
-          <t>signal.uplink.cancel.player</t>
+          <t>signal.uplink.pending</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>已取消接入 {0}</t>
+          <t>正在接入 {0}…</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Uplink to {0} cancelled</t>
+          <t>Uplinking into {0}…</t>
         </is>
       </c>
     </row>
@@ -14868,17 +14868,17 @@
       <c r="A803" t="inlineStr"/>
       <c r="B803" t="inlineStr">
         <is>
-          <t>signal.uplink.entered</t>
+          <t>signal.uplink.pending_paused</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>已接入 {0}</t>
+          <t>接入 {0}：恢复运行后完成（Esc 取消）</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Uplinked into {0}</t>
+          <t>Uplink to {0}: completes when the game resumes (Esc to cancel)</t>
         </is>
       </c>
     </row>
@@ -14886,17 +14886,17 @@
       <c r="A804" t="inlineStr"/>
       <c r="B804" t="inlineStr">
         <is>
-          <t>signal.uplink.left</t>
+          <t>signal.uplink.cancel.dead</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>已离开 {0}：固件随信号带走，机器回到本地配置</t>
+          <t>接入途中 {0} 阵亡：接入已取消，信号留在原处</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>Left {0}: your firmware went with the signal and the machine is back on its own loadout</t>
+          <t>{0} was destroyed during the uplink: uplink cancelled, the signal stays where it was</t>
         </is>
       </c>
     </row>
@@ -14904,17 +14904,17 @@
       <c r="A805" t="inlineStr"/>
       <c r="B805" t="inlineStr">
         <is>
-          <t>signal.uplink.restored</t>
+          <t>signal.uplink.cancel.gone</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>读档：信号仍在 {0} 里</t>
+          <t>接入途中 {0} 不可接入了（{1}）：接入已取消，信号留在原处</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Loaded: the signal is still in {0}</t>
+          <t>{0} became unavailable during the uplink ({1}): uplink cancelled, the signal stays where it was</t>
         </is>
       </c>
     </row>
@@ -14922,17 +14922,17 @@
       <c r="A806" t="inlineStr"/>
       <c r="B806" t="inlineStr">
         <is>
-          <t>signal.uplink.restore_failed</t>
+          <t>signal.uplink.cancel.player</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>读档：{0} 已不可接入，信号回到归还核心</t>
+          <t>已取消接入 {0}</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Loaded: {0} can no longer be uplinked, so the signal is back at the core</t>
+          <t>Uplink to {0} cancelled</t>
         </is>
       </c>
     </row>
@@ -14940,17 +14940,17 @@
       <c r="A807" t="inlineStr"/>
       <c r="B807" t="inlineStr">
         <is>
-          <t>signal.uplink.status.inserted</t>
+          <t>signal.uplink.entered</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>接入口：{0}</t>
+          <t>已接入 {0}</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Uplink port: {0}</t>
+          <t>Uplinked into {0}</t>
         </is>
       </c>
     </row>
@@ -14958,17 +14958,17 @@
       <c r="A808" t="inlineStr"/>
       <c r="B808" t="inlineStr">
         <is>
-          <t>signal.uplink.status.no_uplink</t>
+          <t>signal.uplink.left</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>此机器没有接入口：可以驾驶、瞄准和攻击，但不插入固件</t>
+          <t>已离开 {0}：固件随信号带走，机器回到本地配置</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>This machine has no uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+          <t>Left {0}: your firmware went with the signal and the machine is back on its own loadout</t>
         </is>
       </c>
     </row>
@@ -14976,17 +14976,17 @@
       <c r="A809" t="inlineStr"/>
       <c r="B809" t="inlineStr">
         <is>
-          <t>signal.uplink.status.core_empty</t>
+          <t>signal.uplink.restored</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>信号核没有固件：接入口为空（按 {0} 打开信号核）</t>
+          <t>读档：信号仍在 {0} 里</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>The Signal Core has no firmware: the uplink port is empty (press {0} to open the Signal Core)</t>
+          <t>Loaded: the signal is still in {0}</t>
         </is>
       </c>
     </row>
@@ -14994,17 +14994,17 @@
       <c r="A810" t="inlineStr"/>
       <c r="B810" t="inlineStr">
         <is>
-          <t>signal.uplink.status.off_path</t>
+          <t>signal.uplink.restore_failed</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>接入口不在导线上：插入的固件不生效</t>
+          <t>读档：{0} 已不可接入，信号回到归还核心</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>The uplink port is not on a wire: inserted firmware has no effect</t>
+          <t>Loaded: {0} can no longer be uplinked, so the signal is back at the core</t>
         </is>
       </c>
     </row>
@@ -15012,17 +15012,17 @@
       <c r="A811" t="inlineStr"/>
       <c r="B811" t="inlineStr">
         <is>
-          <t>signal.uplink.status.cooling</t>
+          <t>signal.uplink.status.inserted</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>{0}（冷却 {1} 秒）</t>
+          <t>接入口：{0}</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>{0} (cooldown {1}s)</t>
+          <t>Uplink port: {0}</t>
         </is>
       </c>
     </row>
@@ -15030,17 +15030,17 @@
       <c r="A812" t="inlineStr"/>
       <c r="B812" t="inlineStr">
         <is>
-          <t>signal.uplink.status.sep</t>
+          <t>signal.uplink.status.no_uplink</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>；</t>
+          <t>此机器没有接入口：可以驾驶、瞄准和攻击，但不插入固件</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t xml:space="preserve">; </t>
+          <t>This machine has no uplink port: you can drive, aim and attack, but no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -15048,17 +15048,17 @@
       <c r="A813" t="inlineStr"/>
       <c r="B813" t="inlineStr">
         <is>
-          <t>signal.uplink.status.list_sep</t>
+          <t>signal.uplink.status.core_empty</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>信号核没有固件：接入口为空（按 {0} 打开信号核）</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>The Signal Core has no firmware: the uplink port is empty (press {0} to open the Signal Core)</t>
         </is>
       </c>
     </row>
@@ -15066,17 +15066,17 @@
       <c r="A814" t="inlineStr"/>
       <c r="B814" t="inlineStr">
         <is>
-          <t>signal.uplink.core_fired</t>
+          <t>signal.uplink.status.off_path</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>{0} 发动：冷却 {1} 秒（冷却跟着信号，换机器也不会重置）</t>
+          <t>接入口不在导线上：插入的固件不生效</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>{0} fired: {1}s cooldown (the cooldown follows the signal and does not reset on another machine)</t>
+          <t>The uplink port is not on a wire: inserted firmware has no effect</t>
         </is>
       </c>
     </row>
@@ -15084,17 +15084,17 @@
       <c r="A815" t="inlineStr"/>
       <c r="B815" t="inlineStr">
         <is>
-          <t>signal.uplink.list_tip</t>
+          <t>signal.uplink.status.cooling</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>点一下直接接入这台机器（选中后按 {0} 也可以；接入后按 {1} 在机器间切换）</t>
+          <t>{0}（冷却 {1} 秒）</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Click to uplink into this machine directly (or select it and press {0}; press {1} to switch machines while uplinked)</t>
+          <t>{0} (cooldown {1}s)</t>
         </is>
       </c>
     </row>
@@ -15102,17 +15102,17 @@
       <c r="A816" t="inlineStr"/>
       <c r="B816" t="inlineStr">
         <is>
-          <t>signal.link.reason_name.out_of_coverage</t>
+          <t>signal.uplink.status.sep</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>走出信号覆盖</t>
+          <t>；</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>left signal coverage</t>
+          <t xml:space="preserve">; </t>
         </is>
       </c>
     </row>
@@ -15120,17 +15120,17 @@
       <c r="A817" t="inlineStr"/>
       <c r="B817" t="inlineStr">
         <is>
-          <t>signal.link.reason_name.jammed</t>
+          <t>signal.uplink.status.list_sep</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>进入干扰场</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>entered a jamming field</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -15138,17 +15138,17 @@
       <c r="A818" t="inlineStr"/>
       <c r="B818" t="inlineStr">
         <is>
-          <t>signal.link.reason_name.silent_night</t>
+          <t>signal.uplink.core_fired</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>静默夜</t>
+          <t>{0} 发动：冷却 {1} 秒（冷却跟着信号，换机器也不会重置）</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>silent night</t>
+          <t>{0} fired: {1}s cooldown (the cooldown follows the signal and does not reset on another machine)</t>
         </is>
       </c>
     </row>
@@ -15156,17 +15156,17 @@
       <c r="A819" t="inlineStr"/>
       <c r="B819" t="inlineStr">
         <is>
-          <t>signal.link.reason_name.destroyed</t>
+          <t>signal.uplink.list_tip</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>机器阵亡</t>
+          <t>点一下直接接入这台机器（选中后按 {0} 也可以；接入后按 {1} 在机器间切换）</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>machine destroyed</t>
+          <t>Click to uplink into this machine directly (or select it and press {0}; press {1} to switch machines while uplinked)</t>
         </is>
       </c>
     </row>
@@ -15174,17 +15174,17 @@
       <c r="A820" t="inlineStr"/>
       <c r="B820" t="inlineStr">
         <is>
-          <t>signal.link.warn.edge</t>
+          <t>signal.link.reason_name.out_of_coverage</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>接近信号覆盖边缘：{0} 离边缘还有 {1} 格，走出去信号会被弹回归还核心</t>
+          <t>走出信号覆盖</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Near the edge of signal coverage: {0} is {1} cells from the edge; leaving it sends the signal back to the core</t>
+          <t>left signal coverage</t>
         </is>
       </c>
     </row>
@@ -15192,17 +15192,17 @@
       <c r="A821" t="inlineStr"/>
       <c r="B821" t="inlineStr">
         <is>
-          <t>signal.link.warn.jammed</t>
+          <t>signal.link.reason_name.jammed</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>{0} 受到干扰：{1} 秒内离开干扰区可恢复，否则信号弹回归还核心</t>
+          <t>进入干扰场</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>{0} is being jammed: leave the field within {1}s or the signal returns to the core</t>
+          <t>entered a jamming field</t>
         </is>
       </c>
     </row>
@@ -15210,17 +15210,17 @@
       <c r="A822" t="inlineStr"/>
       <c r="B822" t="inlineStr">
         <is>
-          <t>signal.link.warn.out_of_coverage</t>
+          <t>signal.link.reason_name.silent_night</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>{0} 走出了信号覆盖：{1} 秒内回到覆盖内可恢复，否则信号弹回归还核心</t>
+          <t>静默夜</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>{0} left signal coverage: get back within {1}s or the signal returns to the core</t>
+          <t>silent night</t>
         </is>
       </c>
     </row>
@@ -15228,17 +15228,17 @@
       <c r="A823" t="inlineStr"/>
       <c r="B823" t="inlineStr">
         <is>
-          <t>signal.link.warn.silent_night</t>
+          <t>signal.link.reason_name.destroyed</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>静默夜将在 {0} 秒后开始：届时信号会被弹回归还核心，接入中的机器进入安全模式</t>
+          <t>机器阵亡</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Silent night begins in {0}s: the signal will be sent back to the core and the uplinked machine will enter safe mode</t>
+          <t>machine destroyed</t>
         </is>
       </c>
     </row>
@@ -15246,17 +15246,17 @@
       <c r="A824" t="inlineStr"/>
       <c r="B824" t="inlineStr">
         <is>
-          <t>signal.link.recovered</t>
+          <t>signal.link.warn.edge</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>{0} 信号恢复</t>
+          <t>接近信号覆盖边缘：{0} 离边缘还有 {1} 格，走出去信号会被弹回归还核心</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>{0}: signal restored</t>
+          <t>Near the edge of signal coverage: {0} is {1} cells from the edge; leaving it sends the signal back to the core</t>
         </is>
       </c>
     </row>
@@ -15264,17 +15264,17 @@
       <c r="A825" t="inlineStr"/>
       <c r="B825" t="inlineStr">
         <is>
-          <t>signal.link.break.jammed</t>
+          <t>signal.link.warn.jammed</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>断链：{0} 在干扰场里失联，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
+          <t>{0} 受到干扰：{1} 秒内离开干扰区可恢复，否则信号弹回归还核心</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Link lost: {0} was jammed and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
+          <t>{0} is being jammed: leave the field within {1}s or the signal returns to the core</t>
         </is>
       </c>
     </row>
@@ -15282,17 +15282,17 @@
       <c r="A826" t="inlineStr"/>
       <c r="B826" t="inlineStr">
         <is>
-          <t>signal.link.break.out_of_coverage</t>
+          <t>signal.link.warn.out_of_coverage</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>断链：{0} 走出了信号覆盖，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
+          <t>{0} 走出了信号覆盖：{1} 秒内回到覆盖内可恢复，否则信号弹回归还核心</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Link lost: {0} left signal coverage and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
+          <t>{0} left signal coverage: get back within {1}s or the signal returns to the core</t>
         </is>
       </c>
     </row>
@@ -15300,17 +15300,17 @@
       <c r="A827" t="inlineStr"/>
       <c r="B827" t="inlineStr">
         <is>
-          <t>signal.link.break.silent_night</t>
+          <t>signal.link.warn.silent_night</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>断链：静默夜开始，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
+          <t>静默夜将在 {0} 秒后开始：届时信号会被弹回归还核心，接入中的机器进入安全模式</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Link lost: silent night began and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
+          <t>Silent night begins in {0}s: the signal will be sent back to the core and the uplinked machine will enter safe mode</t>
         </is>
       </c>
     </row>
@@ -15318,17 +15318,17 @@
       <c r="A828" t="inlineStr"/>
       <c r="B828" t="inlineStr">
         <is>
-          <t>signal.link.break.destroyed_rebound</t>
+          <t>signal.link.recovered</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>{0} 阵亡：信号弹到最近能接入的 {1}</t>
+          <t>{0} 信号恢复</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>{0} was destroyed: the signal jumped to the nearest machine it can reach, {1}</t>
+          <t>{0}: signal restored</t>
         </is>
       </c>
     </row>
@@ -15336,17 +15336,17 @@
       <c r="A829" t="inlineStr"/>
       <c r="B829" t="inlineStr">
         <is>
-          <t>signal.link.break.destroyed_core</t>
+          <t>signal.link.break.jammed</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>{0} 阵亡：附近没有能接入的机器，信号回到归还核心</t>
+          <t>断链：{0} 在干扰场里失联，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>{0} was destroyed: no machine nearby can take the signal, so it returned to the core</t>
+          <t>Link lost: {0} was jammed and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
         </is>
       </c>
     </row>
@@ -15354,17 +15354,17 @@
       <c r="A830" t="inlineStr"/>
       <c r="B830" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit</t>
+          <t>signal.link.break.out_of_coverage</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>{0} 信号恢复，退出安全模式</t>
+          <t>断链：{0} 走出了信号覆盖，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>{0}: signal restored, safe mode ended</t>
+          <t>Link lost: {0} left signal coverage and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
         </is>
       </c>
     </row>
@@ -15372,17 +15372,17 @@
       <c r="A831" t="inlineStr"/>
       <c r="B831" t="inlineStr">
         <is>
-          <t>signal.safe_mode.list_tag</t>
+          <t>signal.link.break.silent_night</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>断链：静默夜开始，信号弹回归还核心；{0} 进入安全模式（只跑本地常规固件，按最后的命令或 AI 教义行动）</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>Link lost: silent night began and the signal returned to the core; {0} is in safe mode (local regular firmware only, following its last order or AI doctrine)</t>
         </is>
       </c>
     </row>
@@ -15390,17 +15390,449 @@
       <c r="A832" t="inlineStr"/>
       <c r="B832" t="inlineStr">
         <is>
+          <t>signal.link.break.destroyed_rebound</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>{0} 阵亡：信号弹到最近能接入的 {1}</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>{0} was destroyed: the signal jumped to the nearest machine it can reach, {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr"/>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>signal.link.break.destroyed_core</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>{0} 阵亡：附近没有能接入的机器，信号回到归还核心</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>{0} was destroyed: no machine nearby can take the signal, so it returned to the core</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr"/>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.exit</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>{0} 信号恢复，退出安全模式</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>{0}: signal restored, safe mode ended</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr"/>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.list_tag</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>安全</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr"/>
+      <c r="B836" t="inlineStr">
+        <is>
           <t>signal.safe_mode.tooltip</t>
         </is>
       </c>
-      <c r="C832" t="inlineStr">
+      <c r="C836" t="inlineStr">
         <is>
           <t>安全模式（{1}）：{0} 只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；断链条件消失后自动退出，也可以重新接入</t>
         </is>
       </c>
-      <c r="D832" t="inlineStr">
+      <c r="D836" t="inlineStr">
         <is>
           <t>Safe mode ({1}): {0} runs only its local regular firmware with an empty uplink port and follows its last order or AI doctrine; it ends once the link problem is gone, or when you uplink again</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr"/>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>circuit.uplink.note.core_inert</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>机器电路里的“{0}”是核心固件：AI 驾驶时不生效，也不能再保存进机器电路——把它卸下、放进信号核，接入时插在接入口</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>"{0}" in the machine circuit is core firmware: it does nothing under AI control and can no longer be saved into a machine circuit. Remove it and carry it in the Signal Core; it is inserted into the uplink port when you uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr"/>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>circuit.reaction.uplink_ready</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>{0}（接入时：信号核带上“{1}”，插进接入口触发）</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>{0} (when you uplink: carry {1} in the Signal Core; it goes into the uplink port)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr"/>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>circuit.reaction.charged</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>{0}（本战役已研究，再次保存免费）</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>{0} (already researched this campaign; saving again is free)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr"/>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>circuit.reaction.first_cost</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>{0}（首次保存研究，扣技术数据 {1}，当前 {2}；不够也照样保存，攒够后再保存一次即可）</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>{0} (the first save researches it for {1} tech data, you have {2}; if short, the blueprint still saves, save again later)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr"/>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>blueprint.save.reaction_charged</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>；首次保存接入时能打出“{0}”的蓝图，已扣技术数据 {1}</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>; first blueprint that can fire "{0}" when uplinked: {1} tech data spent</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr"/>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>blueprint.save.reaction_free</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>；接入时可打出“{0}”（本战役已研究，本次免费）</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>; fires "{0}" when uplinked (already researched, free)</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr"/>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>blueprint.save.reaction_pending</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>；接入时的“{0}”还没研究：需要技术数据 {1}（当前 {2}），攒够后再保存一次即可</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>; "{0}" when uplinked is not researched yet: needs {1} tech data (you have {2}); save again once you have enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr"/>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>foundry.gate.lamp.cannon</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>重炮解析</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Cannon analysed</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr"/>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>foundry.gate.lamp.overload_saved</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>熔穿过载接入蓝图保存</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Melt Overload uplink blueprint saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr"/>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>foundry.gate.lamp.machine_ready</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>现役机带接入口的重炮</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Active machine with an uplink-ready cannon</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr"/>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>foundry.gate.blocked</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>核心分区封锁：缺少 {0}。</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Core zone sealed: missing {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr"/>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>foundry.gate.log.title</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>核心分区封锁门：</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core zone gate: </t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr"/>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>foundry.gate.log.done</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>√ {0}</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>✓ {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr"/>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>foundry.gate.log.todo</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>○ {0}</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>○ missing: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr"/>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>foundry.gate.log.all_ready</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>——三灯全亮，核心分区已开放</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — all three lit, the core zone is open</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr"/>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>foundry.gate.log.need_all</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>——三灯全亮才能进入核心分区（熔穿过载要你接入重炮机、信号核带上过载才打得出）</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — light all three to enter (Melt Overload fires only when you uplink into the cannon machine carrying Overload)</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr"/>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>objective.obj06.save_markjump</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>在蓝图编辑器保存带接入口的“标记跳转”蓝图（连射器或切割束 + 标记器 + 接通的接入口）</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Save a Mark Jump uplink blueprint in the editor (repeater or cutting beam + marker + a connected uplink port)</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr"/>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>objective.obj08.save_overload</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>在蓝图编辑器保存带接入口的重炮蓝图（接入时插过载即熔穿过载）</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Save a cannon blueprint with an uplink port (Overload inserted when you uplink = Melt Overload)</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr"/>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>objective.obj08.machine_ready</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>在装配站给一台现役机器装上带接入口的重炮蓝图</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Give an active machine the uplink-ready cannon blueprint at the Assembly Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr"/>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>signal.uplink.handoff_overheated</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>{0} 交还 AI 时仍在过热：散热到 {1} 以下才会再开火</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>{0} returned to AI while overheated: it will not fire until heat drops below {1}</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D965"/>
+  <dimension ref="A1:D1125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17798,6 +17798,2886 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="inlineStr"/>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink.title</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>信号接入</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Signal uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr"/>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink.body</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr"/>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink.hint</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>第一次接入一台机器，或打开信号核时解锁</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr"/>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink_port.title</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>接入口</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr"/>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink_port.body</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr"/>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>codex.signal.uplink_port.hint</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr"/>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>codex.signal.core_firmware.title</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>核心固件</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Core firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr"/>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>codex.signal.core_firmware.body</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr"/>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>codex.signal.core_firmware.hint</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>第一次打开信号核时解锁</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Unlocks the first time you open the Signal Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr"/>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>codex.signal.safe_mode.title</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>安全模式</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Safe mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr"/>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>codex.signal.safe_mode.body</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr"/>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>codex.signal.safe_mode.hint</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr"/>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>codex.signal.raw.title</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>裸跑</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Running raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr"/>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>codex.signal.raw.body</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr"/>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>codex.signal.raw.hint</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>第一次带回加密固件时解锁</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Unlocks the first time you bring back encrypted firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr"/>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>codex.signal.exposure.title</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>信号暴露</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Signal exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr"/>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>codex.signal.exposure.body</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr"/>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>codex.signal.exposure.hint</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>第一次打开暴露面板或带回加密固件时解锁</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr"/>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>codex.signal.coverage.title</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>信号覆盖网络</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Signal coverage network</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr"/>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>codex.signal.coverage.body</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr"/>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>codex.signal.coverage.hint</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr"/>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>codex.signal.far_jump.title</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>远距离跳转</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Long-range jump</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr"/>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>codex.signal.far_jump.body</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr"/>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>codex.signal.far_jump.hint</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>第一次远距离跳转时解锁</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Unlocks the first time you make a long-range jump</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr"/>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>codex.signal.relay.title</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>信号中继</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Signal relays</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr"/>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>codex.signal.relay.body</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr"/>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>codex.signal.relay.hint</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr"/>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>codex.firmware.morph.title</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>机身形变</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Machine morph</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr"/>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>codex.firmware.morph.body</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr"/>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>codex.firmware.morph.hint</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>第一次看到机身形变时解锁</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Unlocks the first time you see a machine morph</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr"/>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>codex.panel.title</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>图鉴 · 系统说明</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Codex · Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr"/>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>codex.panel.close</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr"/>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>codex.panel.list_title</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>条目 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Entries {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr"/>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>codex.panel.related</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>相关条目</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr"/>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>codex.panel.locked_title</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>？？？</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr"/>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>codex.panel.locked_body</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>尚未接触。{0}</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Not encountered yet. {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr"/>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>codex.panel.none_selected</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>在左侧选一个条目</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Pick an entry on the left</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr"/>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>codex.panel.footer</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>固件、反应、敌人等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Firmware, reaction and enemy tabs arrive in a later version; press {act:Cancel} to close</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr"/>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>codex.panel.error</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr"/>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>codex.help.tip_title</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>查看图鉴</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Open codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr"/>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>codex.help.tip</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>打开图鉴条目：{0}</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Open the codex entry: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr"/>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>uplink.hud.title</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>{0} · {1}</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>{0} · {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr"/>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>uplink.hud.help_button</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr"/>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>uplink.hud.help_tip_title</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>接入 HUD</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Uplink HUD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr"/>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>uplink.hud.help_tip</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr"/>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>uplink.hud.slot</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>{0} {1}</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>{0} {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr"/>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.active</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>生效</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr"/>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.cooling</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>冷却 {0} 秒</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>cooling {0}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr"/>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.raw</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>裸跑</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr"/>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.not_inserted</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>未插入：{0}</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>not inserted: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr"/>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.ineffective</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>不生效：{0}</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>no effect: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr"/>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.empty</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>空槽</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr"/>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>uplink.hud.state.locked</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>未解锁</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr"/>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>uplink.hud.reason.over_quota</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>超出接入口配额 {0} 个</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>over the port quota of {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr"/>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>uplink.hud.reason.path_limit</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>路径会超过上限 {0} 条</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>paths would exceed {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr"/>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>uplink.hud.reason.unknown</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>不是已知的固件</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>unknown firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr"/>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>uplink.hud.reason.no_uplink</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>这台机器没有接入口</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>this machine has no uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr"/>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>uplink.hud.reason.off_path</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>接入口不在导线上</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>the uplink port is not on a wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr"/>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>uplink.hud.slot_tip</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>{0} 号槽：{1}</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Slot {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr"/>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>uplink.hud.heat</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>热量 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Heat {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr"/>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>uplink.hud.overheated</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>过热：散热到 {0} 以下才开火</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Overheated: fires again below {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr"/>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>uplink.hud.heat_tip</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr"/>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>uplink.hud.battery</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>电池 {0}%</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Battery {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr"/>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>uplink.hud.battery_tip</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr"/>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>uplink.hud.health</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>耐久 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Durability {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr"/>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>uplink.hud.injury_none</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>伤势：无</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Injuries: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr"/>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>uplink.hud.injury</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>伤势：{0}</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Injuries: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr"/>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>uplink.hud.health_tip</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr"/>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>uplink.hud.link</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>链路 {0}% · {1}</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Link {0}% · {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr"/>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>uplink.hud.link.strong</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr"/>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>uplink.hud.link.medium</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr"/>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>uplink.hud.link.weak</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>弱</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr"/>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>uplink.hud.link.edge</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>边缘 · 还剩 {0} 格</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>edge · {0} cells left</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr"/>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>uplink.hud.link.unbounded</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>链路 满 · 此地不受覆盖限制</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Link full · no coverage limit here</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr"/>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>uplink.hud.link.grace</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>链路中断（{0}）：{1} 秒内恢复</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Link lost ({0}): recover within {1}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr"/>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>uplink.hud.link_tip</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr"/>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>uplink.hud.exposure</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>暴露 {0}</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Exposure {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr"/>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>uplink.hud.exposure_tip</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr"/>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>uplink.hud.morph</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>机身：{0}</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Body: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr"/>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>uplink.hud.morph_source</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>{0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>{0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr"/>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>uplink.hud.no_port</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr"/>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>uplink.hud.core_empty</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>信号核没有固件（按 {0} 打开信号核）</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>The Signal Core is empty (press {0} to open it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr"/>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>uplink.hud.experience</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>With the signal {0} times · {1} total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr"/>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>uplink.hud.keys</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr"/>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>morph.state.none</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>常态</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr"/>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>morph.state.limiter</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>形变态</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>morph state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr"/>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>morph.state.fluid</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>喷口态</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>vent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr"/>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>morph.state.em</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>线圈态</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>coil state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr"/>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>morph.state.join</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> + </t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> + </t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr"/>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>signal.list.port_tag</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>◇口</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>◇PORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr"/>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>signal.list.overheat_tag</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>过热</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr"/>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>signal.list.port_line</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr"/>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>signal.list.no_port_line</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>没有接入口：接入后只能驾驶，不插入固件</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr"/>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>signal.list.overheat_line</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Overheated (heat {0}): it fires again once below {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr"/>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>signal.list.morph_line</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>机身：{0}</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Body: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr"/>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>signal.list.experience_line</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>With the signal {0} times · {1} total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr"/>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>signal.port_badge.tip</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>带接入口的机器</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Machine with an uplink port</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr"/>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>machine.exp.produced</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>生产</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Produced</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr"/>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>machine.exp.first_job</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>首次工作</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>First job</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr"/>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>machine.exp.controlled</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>首次与信号同行</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>First time with the signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr"/>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>machine.exp.expedition</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>远征</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Expedition</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr"/>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>machine.exp.severely_injured</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>重伤</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Severely injured</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr"/>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>machine.exp.elite_kill</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>精英击破</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Elite kill</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr"/>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>machine.exp.boss_participation</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>首领战</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Boss fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr"/>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>machine.exp.returned</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>返航</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr"/>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>machine.exp.sep</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>、</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t xml:space="preserve">, </t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr"/>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>machine.injury.combat</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>战斗损伤（HP {0}/{1}）</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Combat damage (HP {0}/{1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr"/>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>machine.exp.none</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>无记录经历</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>No recorded experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr"/>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>machine.exp.signal</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>与信号同行 {0} 次，累计 {1}</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>With the signal {0} times, {1} in total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr"/>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>machine.exp.signal_none</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>尚未与信号同行</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Never carried the signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr"/>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>machine.status.dead</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>阵亡（纪念记录）</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Destroyed (memorial record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr"/>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>machine.status.in_factory</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>厂内待驶出</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Waiting in the factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr"/>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>machine.status.uplinked</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>接入中</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr"/>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>machine.status.idle</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>空闲</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr"/>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>machine.status.working</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>工作中</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr"/>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>machine.detail.none</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr"/>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>machine.detail.injury_none</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>无记录</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>none recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr"/>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>machine.detail.port_yes</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr"/>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>machine.detail.port_no</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>没有</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr"/>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>machine.detail.line_id</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr"/>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>machine.detail.line_vitals</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr"/>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>machine.detail.line_exp</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>经历：{0}</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Experience: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr"/>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>machine.detail.line_signal</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr"/>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>machine.detail.line_stats</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr"/>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>machine.detail.line_morph</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>机身：{0}</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Body: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr"/>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>victory.summary</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr"/>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>victory.row.number</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>#{0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>#{0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr"/>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>victory.row.alive</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>幸存</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr"/>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>victory.row.dead</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>阵亡</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr"/>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>expedition.return.row_status_alive</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>幸存，将随撤离返回家园；{0}</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Survived and returns home with the evacuation; {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr"/>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>expedition.return.row_status_dead</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr"/>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>factory.reason.uplinked</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>这台机器正被你接入，先退出接入</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>You are uplinked into this machine: leave the uplink first</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr"/>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>signal.cmd.uplinked</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>接入：{0}</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Uplinked: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr"/>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>signal.cmd.reconnecting</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>重连中：{0}</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Reconnecting: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr"/>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>signal.cmd.strategy</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>战略视角</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Strategy view</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr"/>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>region.control.fail.not_found</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>没有可以接入的目标。</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>There is nothing to uplink into.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr"/>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>region.control.fail.not_friendly</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>目标不属于本地点。</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>The target does not belong to this site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr"/>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>region.control.fail.dead</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>目标已阵亡。</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>The target is destroyed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr"/>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>region.control.fail.out_of_range</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>目标当前不在场。</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>The target is not here right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr"/>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>region.control.fail.jammed</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>信号被干扰，接入失败。</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>The signal is jammed; uplink failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr"/>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>region.control.fail.transition</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>镜头切换中，请稍候。</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>The camera is moving; please wait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr"/>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>region.control.fail.modal</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>请先关闭当前面板。</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Close the current panel first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr"/>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>region.control.fail.already</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>已经接入这台机器。</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>You are already uplinked into this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr"/>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>region.control.fail.ineligible</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>目标暂时不能接入。</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>The target cannot be uplinked right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr"/>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>region.control.fail.other</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>接入失败。</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Uplink failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr"/>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>feedback.tag.uplink</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>接入</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr"/>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>feedback.caption.uplink</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>已接入</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr"/>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>feedback.tag.uplink_leave</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr"/>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>feedback.caption.uplink_leave</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>信号离开机器</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>The signal left the machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr"/>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>pause.codex</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>图鉴</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr"/>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>pause.camera_title</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>接入镜头</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Uplink camera</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr"/>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>pause.camera_zoom</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>接入时镜头距离 {0}%</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Uplink camera distance {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr"/>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>pause.camera_follow</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>接入时跟随力度 {0}%</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Uplink follow strength {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr"/>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>pause.camera_reset</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Reset to default</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr"/>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>pause.camera_zoom_tip</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr"/>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>pause.camera_follow_tip</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr"/>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>camera.follow.started</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Camera following {0} (pan or press {1} again to stop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr"/>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>camera.follow.stopped</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>镜头停止跟随</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Camera follow stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr"/>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>camera.follow.nothing</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>先选中一台机器再按 {0} 跟随</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Select a machine first, then press {0} to follow it</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr"/>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>camera.follow.group</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>{0} 台机器</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>{0} machines</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1707"/>
+  <dimension ref="A1:D1754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28278,17 +28278,17 @@
       <c r="A1548" t="inlineStr"/>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.title</t>
+          <t>reaction.steam.name</t>
         </is>
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>信号接入</t>
+          <t>蒸汽</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>Signal uplink</t>
+          <t>Steam</t>
         </is>
       </c>
     </row>
@@ -28296,17 +28296,17 @@
       <c r="A1549" t="inlineStr"/>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.body</t>
+          <t>reaction.steam.desc</t>
         </is>
       </c>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
+          <t>燃烧 + 浸湿：这一击伤害 ×1；消耗浸湿。</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
+          <t>Burning + Soaked: this hit deals ×1 damage; consumes Soaked.</t>
         </is>
       </c>
     </row>
@@ -28314,17 +28314,17 @@
       <c r="A1550" t="inlineStr"/>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.hint</t>
+          <t>reaction.deflagrate.name</t>
         </is>
       </c>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>第一次接入一台机器，或打开信号核时解锁</t>
+          <t>爆燃</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
+          <t>Deflagration</t>
         </is>
       </c>
     </row>
@@ -28332,17 +28332,17 @@
       <c r="A1551" t="inlineStr"/>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.title</t>
+          <t>reaction.deflagrate.desc</t>
         </is>
       </c>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>接入口</t>
+          <t>燃烧 + 油污：这一击伤害 ×1.5；消耗油污；附加燃烧；在目标脚下留下燃烧区（3 秒）。</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>Uplink port</t>
+          <t>Burning + Oiled: this hit deals ×1.5 damage; consumes Oiled; applies Burning; leaves a Burning Zone underfoot (3s).</t>
         </is>
       </c>
     </row>
@@ -28350,17 +28350,17 @@
       <c r="A1552" t="inlineStr"/>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.body</t>
+          <t>reaction.deflagrate.residue</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
+          <t>燃烧区</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
+          <t>Burning Zone</t>
         </is>
       </c>
     </row>
@@ -28368,17 +28368,17 @@
       <c r="A1553" t="inlineStr"/>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.hint</t>
+          <t>reaction.conduct.name</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
+          <t>短路</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
+          <t>Short Circuit</t>
         </is>
       </c>
     </row>
@@ -28386,17 +28386,17 @@
       <c r="A1554" t="inlineStr"/>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.title</t>
+          <t>reaction.conduct.desc</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>核心固件</t>
+          <t>浸湿 + 电击：这一击伤害 ×1.3；消耗浸湿、电击。</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>Core firmware</t>
+          <t>Soaked + Shocked: this hit deals ×1.3 damage; consumes Soaked and Shocked.</t>
         </is>
       </c>
     </row>
@@ -28404,17 +28404,17 @@
       <c r="A1555" t="inlineStr"/>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.body</t>
+          <t>reaction.shatter.name</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
+          <t>脆裂</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
+          <t>Brittle Fracture</t>
         </is>
       </c>
     </row>
@@ -28422,17 +28422,17 @@
       <c r="A1556" t="inlineStr"/>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.hint</t>
+          <t>reaction.shatter.desc</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>第一次打开信号核时解锁</t>
+          <t>冻结 + 动能：这一击伤害 ×1.4；消耗冻结。</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>Unlocks the first time you open the Signal Core</t>
+          <t>Frozen + Kinetic: this hit deals ×1.4 damage; consumes Frozen.</t>
         </is>
       </c>
     </row>
@@ -28440,17 +28440,17 @@
       <c r="A1557" t="inlineStr"/>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.title</t>
+          <t>reaction.sticky.name</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>安全模式</t>
+          <t>粘滞</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>Safe mode</t>
+          <t>Gum-Up</t>
         </is>
       </c>
     </row>
@@ -28458,17 +28458,17 @@
       <c r="A1558" t="inlineStr"/>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.body</t>
+          <t>reaction.sticky.desc</t>
         </is>
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
+          <t>腐蚀 + 胶膜：这一击伤害 ×1；消耗胶膜。</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
+          <t>Corroding + Glued: this hit deals ×1 damage; consumes Glued.</t>
         </is>
       </c>
     </row>
@@ -28476,17 +28476,17 @@
       <c r="A1559" t="inlineStr"/>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.hint</t>
+          <t>reaction.electrolysis.name</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
+          <t>电解</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
+          <t>Electrolysis</t>
         </is>
       </c>
     </row>
@@ -28494,17 +28494,17 @@
       <c r="A1560" t="inlineStr"/>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>codex.signal.raw.title</t>
+          <t>reaction.electrolysis.desc</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>电击 + 腐蚀：这一击伤害 ×1.25；消耗腐蚀。</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>Running raw</t>
+          <t>Shocked + Corroding: this hit deals ×1.25 damage; consumes Corroding.</t>
         </is>
       </c>
     </row>
@@ -28512,17 +28512,17 @@
       <c r="A1561" t="inlineStr"/>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>codex.signal.raw.body</t>
+          <t>reaction.insulate.name</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
+          <t>绝缘</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
+          <t>Insulation</t>
         </is>
       </c>
     </row>
@@ -28530,17 +28530,17 @@
       <c r="A1562" t="inlineStr"/>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>codex.signal.raw.hint</t>
+          <t>reaction.insulate.desc</t>
         </is>
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>第一次带回加密固件时解锁</t>
+          <t>电击 + 油污：这一击伤害 ×0.6；消耗电击。</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Unlocks the first time you bring back encrypted firmware</t>
+          <t>Shocked + Oiled: this hit deals ×0.6 damage; consumes Shocked.</t>
         </is>
       </c>
     </row>
@@ -28548,17 +28548,17 @@
       <c r="A1563" t="inlineStr"/>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.title</t>
+          <t>reaction.thermalshock.name</t>
         </is>
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>信号暴露</t>
+          <t>热震</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>Signal exposure</t>
+          <t>Thermal Shock</t>
         </is>
       </c>
     </row>
@@ -28566,17 +28566,17 @@
       <c r="A1564" t="inlineStr"/>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.body</t>
+          <t>reaction.thermalshock.desc</t>
         </is>
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
+          <t>燃烧 + 冻结：这一击伤害 ×1.4；消耗冻结。</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
+          <t>Burning + Frozen: this hit deals ×1.4 damage; consumes Frozen.</t>
         </is>
       </c>
     </row>
@@ -28584,17 +28584,17 @@
       <c r="A1565" t="inlineStr"/>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.hint</t>
+          <t>reaction.causticburn.name</t>
         </is>
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>第一次打开暴露面板或带回加密固件时解锁</t>
+          <t>腐蚀灼烧</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
+          <t>Corrosive Burn</t>
         </is>
       </c>
     </row>
@@ -28602,17 +28602,17 @@
       <c r="A1566" t="inlineStr"/>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.title</t>
+          <t>reaction.causticburn.desc</t>
         </is>
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>信号覆盖网络</t>
+          <t>燃烧 + 腐蚀：这一击伤害 ×1.1；消耗腐蚀；附加燃烧。</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>Signal coverage network</t>
+          <t>Burning + Corroding: this hit deals ×1.1 damage; consumes Corroding; applies Burning.</t>
         </is>
       </c>
     </row>
@@ -28620,17 +28620,17 @@
       <c r="A1567" t="inlineStr"/>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.body</t>
+          <t>reaction.hemolysis.name</t>
         </is>
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
+          <t>回路溶断</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
+          <t>Circuit Meltdown</t>
         </is>
       </c>
     </row>
@@ -28638,17 +28638,17 @@
       <c r="A1568" t="inlineStr"/>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.hint</t>
+          <t>reaction.hemolysis.desc</t>
         </is>
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
+          <t>回收 + 腐蚀：这一击伤害 ×1.3；消耗回收。</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
+          <t>Reclaiming + Corroding: this hit deals ×1.3 damage; consumes Reclaiming.</t>
         </is>
       </c>
     </row>
@@ -28656,17 +28656,17 @@
       <c r="A1569" t="inlineStr"/>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.title</t>
+          <t>reaction.syrup.name</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>远距离跳转</t>
+          <t>胶结</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>Long-range jump</t>
+          <t>Binding</t>
         </is>
       </c>
     </row>
@@ -28674,17 +28674,17 @@
       <c r="A1570" t="inlineStr"/>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.body</t>
+          <t>reaction.syrup.desc</t>
         </is>
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
+          <t>浸湿 + 胶膜：这一击伤害 ×1.15；消耗胶膜。</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
+          <t>Soaked + Glued: this hit deals ×1.15 damage; consumes Glued.</t>
         </is>
       </c>
     </row>
@@ -28692,17 +28692,17 @@
       <c r="A1571" t="inlineStr"/>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.hint</t>
+          <t>reaction.dissolve.name</t>
         </is>
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>第一次远距离跳转时解锁</t>
+          <t>溶蚀</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>Unlocks the first time you make a long-range jump</t>
+          <t>Etching</t>
         </is>
       </c>
     </row>
@@ -28710,17 +28710,17 @@
       <c r="A1572" t="inlineStr"/>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>codex.signal.relay.title</t>
+          <t>reaction.dissolve.desc</t>
         </is>
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>信号中继</t>
+          <t>腐蚀 + 油污：这一击伤害 ×1.2；消耗油污。</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>Signal relays</t>
+          <t>Corroding + Oiled: this hit deals ×1.2 damage; consumes Oiled.</t>
         </is>
       </c>
     </row>
@@ -28728,17 +28728,17 @@
       <c r="A1573" t="inlineStr"/>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>codex.signal.relay.body</t>
+          <t>reaction.annihilate.name</t>
         </is>
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
+          <t>湮灭</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
+          <t>Annihilation</t>
         </is>
       </c>
     </row>
@@ -28746,17 +28746,17 @@
       <c r="A1574" t="inlineStr"/>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>codex.signal.relay.hint</t>
+          <t>reaction.annihilate.desc</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
+          <t>偏折 + 处决：这一击伤害 ×1.6；消耗偏折、处决。</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
+          <t>Deflecting + Execute: this hit deals ×1.6 damage; consumes Deflecting and Execute.</t>
         </is>
       </c>
     </row>
@@ -28764,17 +28764,17 @@
       <c r="A1575" t="inlineStr"/>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.title</t>
+          <t>reaction.vitrify.name</t>
         </is>
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>机身形变</t>
+          <t>玻化</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>Machine morph</t>
+          <t>Vitrification</t>
         </is>
       </c>
     </row>
@@ -28782,17 +28782,17 @@
       <c r="A1576" t="inlineStr"/>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.body</t>
+          <t>reaction.vitrify.desc</t>
         </is>
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
+          <t>扬尘 + 燃烧：这一击伤害 ×1.3；消耗扬尘。</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
+          <t>Dusted + Burning: this hit deals ×1.3 damage; consumes Dusted.</t>
         </is>
       </c>
     </row>
@@ -28800,17 +28800,17 @@
       <c r="A1577" t="inlineStr"/>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.hint</t>
+          <t>reaction.mudify.name</t>
         </is>
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>第一次看到机身形变时解锁</t>
+          <t>淤塞</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Unlocks the first time you see a machine morph</t>
+          <t>Clogging</t>
         </is>
       </c>
     </row>
@@ -28818,17 +28818,17 @@
       <c r="A1578" t="inlineStr"/>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>codex.panel.title</t>
+          <t>reaction.mudify.desc</t>
         </is>
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>图鉴 · 系统说明</t>
+          <t>扬尘 + 浸湿：这一击伤害 ×0.9；消耗浸湿。</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Codex · Systems</t>
+          <t>Dusted + Soaked: this hit deals ×0.9 damage; consumes Soaked.</t>
         </is>
       </c>
     </row>
@@ -28836,17 +28836,17 @@
       <c r="A1579" t="inlineStr"/>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>codex.panel.close</t>
+          <t>reaction.sepsis.name</t>
         </is>
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>连锁锈蚀</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Cascading Rust</t>
         </is>
       </c>
     </row>
@@ -28854,17 +28854,17 @@
       <c r="A1580" t="inlineStr"/>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>codex.panel.list_title</t>
+          <t>reaction.sepsis.desc</t>
         </is>
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>条目 {0}/{1}</t>
+          <t>污染 + 回收：这一击伤害 ×1.35；消耗污染。</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>Entries {0}/{1}</t>
+          <t>Contaminated + Reclaiming: this hit deals ×1.35 damage; consumes Contaminated.</t>
         </is>
       </c>
     </row>
@@ -28872,17 +28872,17 @@
       <c r="A1581" t="inlineStr"/>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>codex.panel.related</t>
+          <t>reaction.marktag.name</t>
         </is>
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>相关条目</t>
+          <t>标记跳转</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>Related</t>
+          <t>Mark Jump</t>
         </is>
       </c>
     </row>
@@ -28890,17 +28890,17 @@
       <c r="A1582" t="inlineStr"/>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>codex.panel.locked_title</t>
+          <t>reaction.marktag.desc</t>
         </is>
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>标记器与连射器 / 切割束同装、接入时信号核带上标记跳转：命中会额外跳向已被标记的邻近敌人。AI 驾驶时不会触发。</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>With a Marker and a Repeater or Cutting Beam fitted and Mark Jump in the uplinked Signal Core, hits also leap to nearby marked enemies. Never triggers under AI control.</t>
         </is>
       </c>
     </row>
@@ -28908,17 +28908,17 @@
       <c r="A1583" t="inlineStr"/>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>codex.panel.locked_body</t>
+          <t>reaction.meltoverload.name</t>
         </is>
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>尚未接触。{0}</t>
+          <t>熔穿过载</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>Not encountered yet. {0}</t>
+          <t>Meltdown Overload</t>
         </is>
       </c>
     </row>
@@ -28926,17 +28926,17 @@
       <c r="A1584" t="inlineStr"/>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>codex.panel.none_selected</t>
+          <t>reaction.meltoverload.desc</t>
         </is>
       </c>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>在左侧选一个条目</t>
+          <t>接入铸造重炮机、信号核带上过载时触发：额外穿甲，热量代价大幅提高。AI 驾驶时不会触发。</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>Pick an entry on the left</t>
+          <t>Triggers when you uplink into a Foundry Cannon unit with Overload in the Signal Core: extra armour piercing at a much higher heat cost. Never triggers under AI control.</t>
         </is>
       </c>
     </row>
@@ -28944,17 +28944,17 @@
       <c r="A1585" t="inlineStr"/>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>codex.panel.footer</t>
+          <t>reaction.batch.act1</t>
         </is>
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>固件、反应、敌人等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
+          <t>第一幕</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>Firmware, reaction and enemy tabs arrive in a later version; press {act:Cancel} to close</t>
+          <t>Act I</t>
         </is>
       </c>
     </row>
@@ -28962,17 +28962,17 @@
       <c r="A1586" t="inlineStr"/>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>codex.panel.error</t>
+          <t>reaction.batch.clarity</t>
         </is>
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
+          <t>澄净</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
+          <t>the Pristine</t>
         </is>
       </c>
     </row>
@@ -28980,17 +28980,17 @@
       <c r="A1587" t="inlineStr"/>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>codex.help.tip_title</t>
+          <t>reaction.batch.overclock</t>
         </is>
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>超频</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>the Overclocked</t>
         </is>
       </c>
     </row>
@@ -28998,17 +28998,17 @@
       <c r="A1588" t="inlineStr"/>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>codex.help.tip</t>
+          <t>reaction.batch.cross</t>
         </is>
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>打开图鉴条目：{0}</t>
+          <t>跨阵营</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Open the codex entry: {0}</t>
+          <t>Cross-faction</t>
         </is>
       </c>
     </row>
@@ -29016,17 +29016,17 @@
       <c r="A1589" t="inlineStr"/>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>uplink.hud.title</t>
+          <t>reaction.unnamed</t>
         </is>
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>未知反应</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>Unknown reaction</t>
         </is>
       </c>
     </row>
@@ -29034,17 +29034,17 @@
       <c r="A1590" t="inlineStr"/>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>uplink.hud.help_button</t>
+          <t>reaction.cue</t>
         </is>
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>{0}！</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>{0}!</t>
         </is>
       </c>
     </row>
@@ -29052,17 +29052,17 @@
       <c r="A1591" t="inlineStr"/>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip_title</t>
+          <t>feedback.tag.reaction</t>
         </is>
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>接入 HUD</t>
+          <t>反应</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>Uplink HUD</t>
+          <t>Reaction</t>
         </is>
       </c>
     </row>
@@ -29070,17 +29070,17 @@
       <c r="A1592" t="inlineStr"/>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip</t>
+          <t>tag.hover.title</t>
         </is>
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
+          <t>状态标签</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
+          <t>Status tags</t>
         </is>
       </c>
     </row>
@@ -29088,17 +29088,17 @@
       <c r="A1593" t="inlineStr"/>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>uplink.hud.slot</t>
+          <t>tag.hover.line</t>
         </is>
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>{0} {1}　剩余 {2} 秒　×{3}</t>
         </is>
       </c>
       <c r="D1593" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>{0} {1}  {2}s left  ×{3}</t>
         </is>
       </c>
     </row>
@@ -29106,17 +29106,17 @@
       <c r="A1594" t="inlineStr"/>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>uplink.hud.state.active</t>
+          <t>tag.hover.more</t>
         </is>
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>生效</t>
+          <t>另有 {0} 个标签</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>{0} more tags</t>
         </is>
       </c>
     </row>
@@ -29124,17 +29124,17 @@
       <c r="A1595" t="inlineStr"/>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>uplink.hud.state.cooling</t>
+          <t>codex.signal.uplink.title</t>
         </is>
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>冷却 {0} 秒</t>
+          <t>信号接入</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>cooling {0}s</t>
+          <t>Signal uplink</t>
         </is>
       </c>
     </row>
@@ -29142,17 +29142,17 @@
       <c r="A1596" t="inlineStr"/>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>uplink.hud.state.raw</t>
+          <t>codex.signal.uplink.body</t>
         </is>
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
         </is>
       </c>
     </row>
@@ -29160,17 +29160,17 @@
       <c r="A1597" t="inlineStr"/>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>uplink.hud.state.not_inserted</t>
+          <t>codex.signal.uplink.hint</t>
         </is>
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>未插入：{0}</t>
+          <t>第一次接入一台机器，或打开信号核时解锁</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>not inserted: {0}</t>
+          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
         </is>
       </c>
     </row>
@@ -29178,17 +29178,17 @@
       <c r="A1598" t="inlineStr"/>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>uplink.hud.state.ineffective</t>
+          <t>codex.signal.uplink_port.title</t>
         </is>
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>不生效：{0}</t>
+          <t>接入口</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>no effect: {0}</t>
+          <t>Uplink port</t>
         </is>
       </c>
     </row>
@@ -29196,17 +29196,17 @@
       <c r="A1599" t="inlineStr"/>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>uplink.hud.state.empty</t>
+          <t>codex.signal.uplink_port.body</t>
         </is>
       </c>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>空槽</t>
+          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
         </is>
       </c>
     </row>
@@ -29214,17 +29214,17 @@
       <c r="A1600" t="inlineStr"/>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>uplink.hud.state.locked</t>
+          <t>codex.signal.uplink_port.hint</t>
         </is>
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>未解锁</t>
+          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
         </is>
       </c>
     </row>
@@ -29232,17 +29232,17 @@
       <c r="A1601" t="inlineStr"/>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.over_quota</t>
+          <t>codex.signal.core_firmware.title</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>超出接入口配额 {0} 个</t>
+          <t>核心固件</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>over the port quota of {0}</t>
+          <t>Core firmware</t>
         </is>
       </c>
     </row>
@@ -29250,17 +29250,17 @@
       <c r="A1602" t="inlineStr"/>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.path_limit</t>
+          <t>codex.signal.core_firmware.body</t>
         </is>
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>路径会超过上限 {0} 条</t>
+          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>paths would exceed {0}</t>
+          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
         </is>
       </c>
     </row>
@@ -29268,17 +29268,17 @@
       <c r="A1603" t="inlineStr"/>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.unknown</t>
+          <t>codex.signal.core_firmware.hint</t>
         </is>
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>不是已知的固件</t>
+          <t>第一次打开信号核时解锁</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>unknown firmware</t>
+          <t>Unlocks the first time you open the Signal Core</t>
         </is>
       </c>
     </row>
@@ -29286,17 +29286,17 @@
       <c r="A1604" t="inlineStr"/>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.no_uplink</t>
+          <t>codex.signal.safe_mode.title</t>
         </is>
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>这台机器没有接入口</t>
+          <t>安全模式</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>this machine has no uplink port</t>
+          <t>Safe mode</t>
         </is>
       </c>
     </row>
@@ -29304,17 +29304,17 @@
       <c r="A1605" t="inlineStr"/>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.off_path</t>
+          <t>codex.signal.safe_mode.body</t>
         </is>
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>接入口不在导线上</t>
+          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>the uplink port is not on a wire</t>
+          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
         </is>
       </c>
     </row>
@@ -29322,17 +29322,17 @@
       <c r="A1606" t="inlineStr"/>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>uplink.hud.slot_tip</t>
+          <t>codex.signal.safe_mode.hint</t>
         </is>
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>{0} 号槽：{1}</t>
+          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Slot {0}: {1}</t>
+          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
         </is>
       </c>
     </row>
@@ -29340,17 +29340,17 @@
       <c r="A1607" t="inlineStr"/>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>uplink.hud.heat</t>
+          <t>codex.signal.raw.title</t>
         </is>
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>热量 {0}/{1}</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>Heat {0}/{1}</t>
+          <t>Running raw</t>
         </is>
       </c>
     </row>
@@ -29358,17 +29358,17 @@
       <c r="A1608" t="inlineStr"/>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>uplink.hud.overheated</t>
+          <t>codex.signal.raw.body</t>
         </is>
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>过热：散热到 {0} 以下才开火</t>
+          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Overheated: fires again below {0}</t>
+          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
         </is>
       </c>
     </row>
@@ -29376,17 +29376,17 @@
       <c r="A1609" t="inlineStr"/>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>uplink.hud.heat_tip</t>
+          <t>codex.signal.raw.hint</t>
         </is>
       </c>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
+          <t>第一次带回加密固件时解锁</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
+          <t>Unlocks the first time you bring back encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -29394,17 +29394,17 @@
       <c r="A1610" t="inlineStr"/>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>uplink.hud.battery</t>
+          <t>codex.signal.exposure.title</t>
         </is>
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>电池 {0}%</t>
+          <t>信号暴露</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Battery {0}%</t>
+          <t>Signal exposure</t>
         </is>
       </c>
     </row>
@@ -29412,17 +29412,17 @@
       <c r="A1611" t="inlineStr"/>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>uplink.hud.battery_tip</t>
+          <t>codex.signal.exposure.body</t>
         </is>
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
+          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
+          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
         </is>
       </c>
     </row>
@@ -29430,17 +29430,17 @@
       <c r="A1612" t="inlineStr"/>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>uplink.hud.health</t>
+          <t>codex.signal.exposure.hint</t>
         </is>
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}</t>
+          <t>第一次打开暴露面板或带回加密固件时解锁</t>
         </is>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Durability {0}/{1}</t>
+          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -29448,17 +29448,17 @@
       <c r="A1613" t="inlineStr"/>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>uplink.hud.injury_none</t>
+          <t>codex.signal.coverage.title</t>
         </is>
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>伤势：无</t>
+          <t>信号覆盖网络</t>
         </is>
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>Injuries: none</t>
+          <t>Signal coverage network</t>
         </is>
       </c>
     </row>
@@ -29466,17 +29466,17 @@
       <c r="A1614" t="inlineStr"/>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>uplink.hud.injury</t>
+          <t>codex.signal.coverage.body</t>
         </is>
       </c>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>伤势：{0}</t>
+          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
-          <t>Injuries: {0}</t>
+          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
         </is>
       </c>
     </row>
@@ -29484,17 +29484,17 @@
       <c r="A1615" t="inlineStr"/>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>uplink.hud.health_tip</t>
+          <t>codex.signal.coverage.hint</t>
         </is>
       </c>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
+          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
-          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
+          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
         </is>
       </c>
     </row>
@@ -29502,17 +29502,17 @@
       <c r="A1616" t="inlineStr"/>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>uplink.hud.link</t>
+          <t>codex.signal.far_jump.title</t>
         </is>
       </c>
       <c r="C1616" t="inlineStr">
         <is>
-          <t>链路 {0}% · {1}</t>
+          <t>远距离跳转</t>
         </is>
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>Link {0}% · {1}</t>
+          <t>Long-range jump</t>
         </is>
       </c>
     </row>
@@ -29520,17 +29520,17 @@
       <c r="A1617" t="inlineStr"/>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>uplink.hud.link.strong</t>
+          <t>codex.signal.far_jump.body</t>
         </is>
       </c>
       <c r="C1617" t="inlineStr">
         <is>
-          <t>强</t>
+          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
         </is>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
         </is>
       </c>
     </row>
@@ -29538,17 +29538,17 @@
       <c r="A1618" t="inlineStr"/>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>uplink.hud.link.medium</t>
+          <t>codex.signal.far_jump.hint</t>
         </is>
       </c>
       <c r="C1618" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>第一次远距离跳转时解锁</t>
         </is>
       </c>
       <c r="D1618" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Unlocks the first time you make a long-range jump</t>
         </is>
       </c>
     </row>
@@ -29556,17 +29556,17 @@
       <c r="A1619" t="inlineStr"/>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>uplink.hud.link.weak</t>
+          <t>codex.signal.relay.title</t>
         </is>
       </c>
       <c r="C1619" t="inlineStr">
         <is>
-          <t>弱</t>
+          <t>信号中继</t>
         </is>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>Signal relays</t>
         </is>
       </c>
     </row>
@@ -29574,17 +29574,17 @@
       <c r="A1620" t="inlineStr"/>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>uplink.hud.link.edge</t>
+          <t>codex.signal.relay.body</t>
         </is>
       </c>
       <c r="C1620" t="inlineStr">
         <is>
-          <t>边缘 · 还剩 {0} 格</t>
+          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
         </is>
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>edge · {0} cells left</t>
+          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
         </is>
       </c>
     </row>
@@ -29592,17 +29592,17 @@
       <c r="A1621" t="inlineStr"/>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>uplink.hud.link.unbounded</t>
+          <t>codex.signal.relay.hint</t>
         </is>
       </c>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>链路 满 · 此地不受覆盖限制</t>
+          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">
         <is>
-          <t>Link full · no coverage limit here</t>
+          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
         </is>
       </c>
     </row>
@@ -29610,17 +29610,17 @@
       <c r="A1622" t="inlineStr"/>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>uplink.hud.link.grace</t>
+          <t>codex.firmware.morph.title</t>
         </is>
       </c>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>链路中断（{0}）：{1} 秒内恢复</t>
+          <t>机身形变</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
         <is>
-          <t>Link lost ({0}): recover within {1}s</t>
+          <t>Machine morph</t>
         </is>
       </c>
     </row>
@@ -29628,17 +29628,17 @@
       <c r="A1623" t="inlineStr"/>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>uplink.hud.link_tip</t>
+          <t>codex.firmware.morph.body</t>
         </is>
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
+          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
         </is>
       </c>
       <c r="D1623" t="inlineStr">
         <is>
-          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
+          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
         </is>
       </c>
     </row>
@@ -29646,17 +29646,17 @@
       <c r="A1624" t="inlineStr"/>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure</t>
+          <t>codex.firmware.morph.hint</t>
         </is>
       </c>
       <c r="C1624" t="inlineStr">
         <is>
-          <t>暴露 {0}</t>
+          <t>第一次看到机身形变时解锁</t>
         </is>
       </c>
       <c r="D1624" t="inlineStr">
         <is>
-          <t>Exposure {0}</t>
+          <t>Unlocks the first time you see a machine morph</t>
         </is>
       </c>
     </row>
@@ -29664,17 +29664,17 @@
       <c r="A1625" t="inlineStr"/>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure_tip</t>
+          <t>codex.panel.title</t>
         </is>
       </c>
       <c r="C1625" t="inlineStr">
         <is>
-          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
+          <t>图鉴 · 系统说明</t>
         </is>
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
+          <t>Codex · Systems</t>
         </is>
       </c>
     </row>
@@ -29682,17 +29682,17 @@
       <c r="A1626" t="inlineStr"/>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>uplink.hud.morph</t>
+          <t>codex.panel.close</t>
         </is>
       </c>
       <c r="C1626" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1626" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -29700,17 +29700,17 @@
       <c r="A1627" t="inlineStr"/>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>uplink.hud.morph_source</t>
+          <t>codex.panel.list_title</t>
         </is>
       </c>
       <c r="C1627" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>条目 {0}/{1}</t>
         </is>
       </c>
       <c r="D1627" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Entries {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -29718,17 +29718,17 @@
       <c r="A1628" t="inlineStr"/>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>uplink.hud.no_port</t>
+          <t>codex.panel.related</t>
         </is>
       </c>
       <c r="C1628" t="inlineStr">
         <is>
-          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
+          <t>相关条目</t>
         </is>
       </c>
       <c r="D1628" t="inlineStr">
         <is>
-          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+          <t>Related</t>
         </is>
       </c>
     </row>
@@ -29736,17 +29736,17 @@
       <c r="A1629" t="inlineStr"/>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>uplink.hud.core_empty</t>
+          <t>codex.panel.locked_title</t>
         </is>
       </c>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>信号核没有固件（按 {0} 打开信号核）</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>The Signal Core is empty (press {0} to open it)</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -29754,17 +29754,17 @@
       <c r="A1630" t="inlineStr"/>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>uplink.hud.experience</t>
+          <t>codex.panel.locked_body</t>
         </is>
       </c>
       <c r="C1630" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>尚未接触。{0}</t>
         </is>
       </c>
       <c r="D1630" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>Not encountered yet. {0}</t>
         </is>
       </c>
     </row>
@@ -29772,17 +29772,17 @@
       <c r="A1631" t="inlineStr"/>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>uplink.hud.keys</t>
+          <t>codex.panel.none_selected</t>
         </is>
       </c>
       <c r="C1631" t="inlineStr">
         <is>
-          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
+          <t>在左侧选一个条目</t>
         </is>
       </c>
       <c r="D1631" t="inlineStr">
         <is>
-          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
+          <t>Pick an entry on the left</t>
         </is>
       </c>
     </row>
@@ -29790,17 +29790,17 @@
       <c r="A1632" t="inlineStr"/>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>morph.state.none</t>
+          <t>codex.panel.footer</t>
         </is>
       </c>
       <c r="C1632" t="inlineStr">
         <is>
-          <t>常态</t>
+          <t>固件、反应、敌人等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1632" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>Firmware, reaction and enemy tabs arrive in a later version; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -29808,17 +29808,17 @@
       <c r="A1633" t="inlineStr"/>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>morph.state.limiter</t>
+          <t>codex.panel.error</t>
         </is>
       </c>
       <c r="C1633" t="inlineStr">
         <is>
-          <t>形变态</t>
+          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
         </is>
       </c>
       <c r="D1633" t="inlineStr">
         <is>
-          <t>morph state</t>
+          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
         </is>
       </c>
     </row>
@@ -29826,17 +29826,17 @@
       <c r="A1634" t="inlineStr"/>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>morph.state.fluid</t>
+          <t>codex.help.tip_title</t>
         </is>
       </c>
       <c r="C1634" t="inlineStr">
         <is>
-          <t>喷口态</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1634" t="inlineStr">
         <is>
-          <t>vent state</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -29844,17 +29844,17 @@
       <c r="A1635" t="inlineStr"/>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>morph.state.em</t>
+          <t>codex.help.tip</t>
         </is>
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>线圈态</t>
+          <t>打开图鉴条目：{0}</t>
         </is>
       </c>
       <c r="D1635" t="inlineStr">
         <is>
-          <t>coil state</t>
+          <t>Open the codex entry: {0}</t>
         </is>
       </c>
     </row>
@@ -29862,17 +29862,17 @@
       <c r="A1636" t="inlineStr"/>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>morph.state.join</t>
+          <t>uplink.hud.title</t>
         </is>
       </c>
       <c r="C1636" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>{0} · {1}</t>
         </is>
       </c>
       <c r="D1636" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>{0} · {1}</t>
         </is>
       </c>
     </row>
@@ -29880,17 +29880,17 @@
       <c r="A1637" t="inlineStr"/>
       <c r="B1637" t="inlineStr">
         <is>
-          <t>signal.list.port_tag</t>
+          <t>uplink.hud.help_button</t>
         </is>
       </c>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>◇口</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
         <is>
-          <t>◇PORT</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -29898,17 +29898,17 @@
       <c r="A1638" t="inlineStr"/>
       <c r="B1638" t="inlineStr">
         <is>
-          <t>signal.list.overheat_tag</t>
+          <t>uplink.hud.help_tip_title</t>
         </is>
       </c>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>过热</t>
+          <t>接入 HUD</t>
         </is>
       </c>
       <c r="D1638" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>Uplink HUD</t>
         </is>
       </c>
     </row>
@@ -29916,17 +29916,17 @@
       <c r="A1639" t="inlineStr"/>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>signal.list.port_line</t>
+          <t>uplink.hud.help_tip</t>
         </is>
       </c>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
+          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
         </is>
       </c>
       <c r="D1639" t="inlineStr">
         <is>
-          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
+          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
         </is>
       </c>
     </row>
@@ -29934,17 +29934,17 @@
       <c r="A1640" t="inlineStr"/>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>signal.list.no_port_line</t>
+          <t>uplink.hud.slot</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>没有接入口：接入后只能驾驶，不插入固件</t>
+          <t>{0} {1}</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
         <is>
-          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
+          <t>{0} {1}</t>
         </is>
       </c>
     </row>
@@ -29952,17 +29952,17 @@
       <c r="A1641" t="inlineStr"/>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>signal.list.overheat_line</t>
+          <t>uplink.hud.state.active</t>
         </is>
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
+          <t>生效</t>
         </is>
       </c>
       <c r="D1641" t="inlineStr">
         <is>
-          <t>Overheated (heat {0}): it fires again once below {1}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -29970,17 +29970,17 @@
       <c r="A1642" t="inlineStr"/>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>signal.list.morph_line</t>
+          <t>uplink.hud.state.cooling</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>冷却 {0} 秒</t>
         </is>
       </c>
       <c r="D1642" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>cooling {0}s</t>
         </is>
       </c>
     </row>
@@ -29988,17 +29988,17 @@
       <c r="A1643" t="inlineStr"/>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>signal.list.experience_line</t>
+          <t>uplink.hud.state.raw</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1643" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>raw</t>
         </is>
       </c>
     </row>
@@ -30006,17 +30006,17 @@
       <c r="A1644" t="inlineStr"/>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>signal.port_badge.tip</t>
+          <t>uplink.hud.state.not_inserted</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>带接入口的机器</t>
+          <t>未插入：{0}</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
         <is>
-          <t>Machine with an uplink port</t>
+          <t>not inserted: {0}</t>
         </is>
       </c>
     </row>
@@ -30024,17 +30024,17 @@
       <c r="A1645" t="inlineStr"/>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>machine.exp.produced</t>
+          <t>uplink.hud.state.ineffective</t>
         </is>
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>不生效：{0}</t>
         </is>
       </c>
       <c r="D1645" t="inlineStr">
         <is>
-          <t>Produced</t>
+          <t>no effect: {0}</t>
         </is>
       </c>
     </row>
@@ -30042,17 +30042,17 @@
       <c r="A1646" t="inlineStr"/>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>machine.exp.first_job</t>
+          <t>uplink.hud.state.empty</t>
         </is>
       </c>
       <c r="C1646" t="inlineStr">
         <is>
-          <t>首次工作</t>
+          <t>空槽</t>
         </is>
       </c>
       <c r="D1646" t="inlineStr">
         <is>
-          <t>First job</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -30060,17 +30060,17 @@
       <c r="A1647" t="inlineStr"/>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>machine.exp.controlled</t>
+          <t>uplink.hud.state.locked</t>
         </is>
       </c>
       <c r="C1647" t="inlineStr">
         <is>
-          <t>首次与信号同行</t>
+          <t>未解锁</t>
         </is>
       </c>
       <c r="D1647" t="inlineStr">
         <is>
-          <t>First time with the signal</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -30078,17 +30078,17 @@
       <c r="A1648" t="inlineStr"/>
       <c r="B1648" t="inlineStr">
         <is>
-          <t>machine.exp.expedition</t>
+          <t>uplink.hud.reason.over_quota</t>
         </is>
       </c>
       <c r="C1648" t="inlineStr">
         <is>
-          <t>远征</t>
+          <t>超出接入口配额 {0} 个</t>
         </is>
       </c>
       <c r="D1648" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>over the port quota of {0}</t>
         </is>
       </c>
     </row>
@@ -30096,17 +30096,17 @@
       <c r="A1649" t="inlineStr"/>
       <c r="B1649" t="inlineStr">
         <is>
-          <t>machine.exp.severely_injured</t>
+          <t>uplink.hud.reason.path_limit</t>
         </is>
       </c>
       <c r="C1649" t="inlineStr">
         <is>
-          <t>重伤</t>
+          <t>路径会超过上限 {0} 条</t>
         </is>
       </c>
       <c r="D1649" t="inlineStr">
         <is>
-          <t>Severely injured</t>
+          <t>paths would exceed {0}</t>
         </is>
       </c>
     </row>
@@ -30114,17 +30114,17 @@
       <c r="A1650" t="inlineStr"/>
       <c r="B1650" t="inlineStr">
         <is>
-          <t>machine.exp.elite_kill</t>
+          <t>uplink.hud.reason.unknown</t>
         </is>
       </c>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>精英击破</t>
+          <t>不是已知的固件</t>
         </is>
       </c>
       <c r="D1650" t="inlineStr">
         <is>
-          <t>Elite kill</t>
+          <t>unknown firmware</t>
         </is>
       </c>
     </row>
@@ -30132,17 +30132,17 @@
       <c r="A1651" t="inlineStr"/>
       <c r="B1651" t="inlineStr">
         <is>
-          <t>machine.exp.boss_participation</t>
+          <t>uplink.hud.reason.no_uplink</t>
         </is>
       </c>
       <c r="C1651" t="inlineStr">
         <is>
-          <t>首领战</t>
+          <t>这台机器没有接入口</t>
         </is>
       </c>
       <c r="D1651" t="inlineStr">
         <is>
-          <t>Boss fight</t>
+          <t>this machine has no uplink port</t>
         </is>
       </c>
     </row>
@@ -30150,17 +30150,17 @@
       <c r="A1652" t="inlineStr"/>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>machine.exp.returned</t>
+          <t>uplink.hud.reason.off_path</t>
         </is>
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>返航</t>
+          <t>接入口不在导线上</t>
         </is>
       </c>
       <c r="D1652" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>the uplink port is not on a wire</t>
         </is>
       </c>
     </row>
@@ -30168,17 +30168,17 @@
       <c r="A1653" t="inlineStr"/>
       <c r="B1653" t="inlineStr">
         <is>
-          <t>machine.exp.sep</t>
+          <t>uplink.hud.slot_tip</t>
         </is>
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>{0} 号槽：{1}</t>
         </is>
       </c>
       <c r="D1653" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>Slot {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -30186,17 +30186,17 @@
       <c r="A1654" t="inlineStr"/>
       <c r="B1654" t="inlineStr">
         <is>
-          <t>machine.injury.combat</t>
+          <t>uplink.hud.heat</t>
         </is>
       </c>
       <c r="C1654" t="inlineStr">
         <is>
-          <t>战斗损伤（HP {0}/{1}）</t>
+          <t>热量 {0}/{1}</t>
         </is>
       </c>
       <c r="D1654" t="inlineStr">
         <is>
-          <t>Combat damage (HP {0}/{1})</t>
+          <t>Heat {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -30204,17 +30204,17 @@
       <c r="A1655" t="inlineStr"/>
       <c r="B1655" t="inlineStr">
         <is>
-          <t>machine.exp.none</t>
+          <t>uplink.hud.overheated</t>
         </is>
       </c>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>无记录经历</t>
+          <t>过热：散热到 {0} 以下才开火</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
         <is>
-          <t>No recorded experience</t>
+          <t>Overheated: fires again below {0}</t>
         </is>
       </c>
     </row>
@@ -30222,17 +30222,17 @@
       <c r="A1656" t="inlineStr"/>
       <c r="B1656" t="inlineStr">
         <is>
-          <t>machine.exp.signal</t>
+          <t>uplink.hud.heat_tip</t>
         </is>
       </c>
       <c r="C1656" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次，累计 {1}</t>
+          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
         </is>
       </c>
       <c r="D1656" t="inlineStr">
         <is>
-          <t>With the signal {0} times, {1} in total</t>
+          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
         </is>
       </c>
     </row>
@@ -30240,17 +30240,17 @@
       <c r="A1657" t="inlineStr"/>
       <c r="B1657" t="inlineStr">
         <is>
-          <t>machine.exp.signal_none</t>
+          <t>uplink.hud.battery</t>
         </is>
       </c>
       <c r="C1657" t="inlineStr">
         <is>
-          <t>尚未与信号同行</t>
+          <t>电池 {0}%</t>
         </is>
       </c>
       <c r="D1657" t="inlineStr">
         <is>
-          <t>Never carried the signal</t>
+          <t>Battery {0}%</t>
         </is>
       </c>
     </row>
@@ -30258,17 +30258,17 @@
       <c r="A1658" t="inlineStr"/>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>machine.status.dead</t>
+          <t>uplink.hud.battery_tip</t>
         </is>
       </c>
       <c r="C1658" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录）</t>
+          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
         </is>
       </c>
       <c r="D1658" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record)</t>
+          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
         </is>
       </c>
     </row>
@@ -30276,17 +30276,17 @@
       <c r="A1659" t="inlineStr"/>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>machine.status.in_factory</t>
+          <t>uplink.hud.health</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
         <is>
-          <t>厂内待驶出</t>
+          <t>耐久 {0}/{1}</t>
         </is>
       </c>
       <c r="D1659" t="inlineStr">
         <is>
-          <t>Waiting in the factory</t>
+          <t>Durability {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -30294,17 +30294,17 @@
       <c r="A1660" t="inlineStr"/>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>machine.status.uplinked</t>
+          <t>uplink.hud.injury_none</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>接入中</t>
+          <t>伤势：无</t>
         </is>
       </c>
       <c r="D1660" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>Injuries: none</t>
         </is>
       </c>
     </row>
@@ -30312,17 +30312,17 @@
       <c r="A1661" t="inlineStr"/>
       <c r="B1661" t="inlineStr">
         <is>
-          <t>machine.status.idle</t>
+          <t>uplink.hud.injury</t>
         </is>
       </c>
       <c r="C1661" t="inlineStr">
         <is>
-          <t>空闲</t>
+          <t>伤势：{0}</t>
         </is>
       </c>
       <c r="D1661" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>Injuries: {0}</t>
         </is>
       </c>
     </row>
@@ -30330,17 +30330,17 @@
       <c r="A1662" t="inlineStr"/>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>machine.status.working</t>
+          <t>uplink.hud.health_tip</t>
         </is>
       </c>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
         </is>
       </c>
       <c r="D1662" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
         </is>
       </c>
     </row>
@@ -30348,17 +30348,17 @@
       <c r="A1663" t="inlineStr"/>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>machine.detail.none</t>
+          <t>uplink.hud.link</t>
         </is>
       </c>
       <c r="C1663" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>链路 {0}% · {1}</t>
         </is>
       </c>
       <c r="D1663" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Link {0}% · {1}</t>
         </is>
       </c>
     </row>
@@ -30366,17 +30366,17 @@
       <c r="A1664" t="inlineStr"/>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>machine.detail.injury_none</t>
+          <t>uplink.hud.link.strong</t>
         </is>
       </c>
       <c r="C1664" t="inlineStr">
         <is>
-          <t>无记录</t>
+          <t>强</t>
         </is>
       </c>
       <c r="D1664" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -30384,17 +30384,17 @@
       <c r="A1665" t="inlineStr"/>
       <c r="B1665" t="inlineStr">
         <is>
-          <t>machine.detail.port_yes</t>
+          <t>uplink.hud.link.medium</t>
         </is>
       </c>
       <c r="C1665" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D1665" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -30402,17 +30402,17 @@
       <c r="A1666" t="inlineStr"/>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>machine.detail.port_no</t>
+          <t>uplink.hud.link.weak</t>
         </is>
       </c>
       <c r="C1666" t="inlineStr">
         <is>
-          <t>没有</t>
+          <t>弱</t>
         </is>
       </c>
       <c r="D1666" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weak</t>
         </is>
       </c>
     </row>
@@ -30420,17 +30420,17 @@
       <c r="A1667" t="inlineStr"/>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>machine.detail.line_id</t>
+          <t>uplink.hud.link.edge</t>
         </is>
       </c>
       <c r="C1667" t="inlineStr">
         <is>
-          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+          <t>边缘 · 还剩 {0} 格</t>
         </is>
       </c>
       <c r="D1667" t="inlineStr">
         <is>
-          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+          <t>edge · {0} cells left</t>
         </is>
       </c>
     </row>
@@ -30438,17 +30438,17 @@
       <c r="A1668" t="inlineStr"/>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>machine.detail.line_vitals</t>
+          <t>uplink.hud.link.unbounded</t>
         </is>
       </c>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+          <t>链路 满 · 此地不受覆盖限制</t>
         </is>
       </c>
       <c r="D1668" t="inlineStr">
         <is>
-          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+          <t>Link full · no coverage limit here</t>
         </is>
       </c>
     </row>
@@ -30456,17 +30456,17 @@
       <c r="A1669" t="inlineStr"/>
       <c r="B1669" t="inlineStr">
         <is>
-          <t>machine.detail.line_exp</t>
+          <t>uplink.hud.link.grace</t>
         </is>
       </c>
       <c r="C1669" t="inlineStr">
         <is>
-          <t>经历：{0}</t>
+          <t>链路中断（{0}）：{1} 秒内恢复</t>
         </is>
       </c>
       <c r="D1669" t="inlineStr">
         <is>
-          <t>Experience: {0}</t>
+          <t>Link lost ({0}): recover within {1}s</t>
         </is>
       </c>
     </row>
@@ -30474,17 +30474,17 @@
       <c r="A1670" t="inlineStr"/>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>machine.detail.line_signal</t>
+          <t>uplink.hud.link_tip</t>
         </is>
       </c>
       <c r="C1670" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
         </is>
       </c>
       <c r="D1670" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
         </is>
       </c>
     </row>
@@ -30492,17 +30492,17 @@
       <c r="A1671" t="inlineStr"/>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>machine.detail.line_stats</t>
+          <t>uplink.hud.exposure</t>
         </is>
       </c>
       <c r="C1671" t="inlineStr">
         <is>
-          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+          <t>暴露 {0}</t>
         </is>
       </c>
       <c r="D1671" t="inlineStr">
         <is>
-          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+          <t>Exposure {0}</t>
         </is>
       </c>
     </row>
@@ -30510,17 +30510,17 @@
       <c r="A1672" t="inlineStr"/>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>machine.detail.line_morph</t>
+          <t>uplink.hud.exposure_tip</t>
         </is>
       </c>
       <c r="C1672" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
         </is>
       </c>
       <c r="D1672" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
         </is>
       </c>
     </row>
@@ -30528,17 +30528,17 @@
       <c r="A1673" t="inlineStr"/>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>victory.summary</t>
+          <t>uplink.hud.morph</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1673" t="inlineStr">
         <is>
-          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -30546,17 +30546,17 @@
       <c r="A1674" t="inlineStr"/>
       <c r="B1674" t="inlineStr">
         <is>
-          <t>victory.row.number</t>
+          <t>uplink.hud.morph_source</t>
         </is>
       </c>
       <c r="C1674" t="inlineStr">
         <is>
-          <t>#{0}（{1}）</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D1674" t="inlineStr">
         <is>
-          <t>#{0} ({1})</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -30564,17 +30564,17 @@
       <c r="A1675" t="inlineStr"/>
       <c r="B1675" t="inlineStr">
         <is>
-          <t>victory.row.alive</t>
+          <t>uplink.hud.no_port</t>
         </is>
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>幸存</t>
+          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
         </is>
       </c>
       <c r="D1675" t="inlineStr">
         <is>
-          <t>survived</t>
+          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -30582,17 +30582,17 @@
       <c r="A1676" t="inlineStr"/>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>victory.row.dead</t>
+          <t>uplink.hud.core_empty</t>
         </is>
       </c>
       <c r="C1676" t="inlineStr">
         <is>
-          <t>阵亡</t>
+          <t>信号核没有固件（按 {0} 打开信号核）</t>
         </is>
       </c>
       <c r="D1676" t="inlineStr">
         <is>
-          <t>destroyed</t>
+          <t>The Signal Core is empty (press {0} to open it)</t>
         </is>
       </c>
     </row>
@@ -30600,17 +30600,17 @@
       <c r="A1677" t="inlineStr"/>
       <c r="B1677" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_alive</t>
+          <t>uplink.hud.experience</t>
         </is>
       </c>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>幸存，将随撤离返回家园；{0}</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
         <is>
-          <t>Survived and returns home with the evacuation; {0}</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -30618,17 +30618,17 @@
       <c r="A1678" t="inlineStr"/>
       <c r="B1678" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_dead</t>
+          <t>uplink.hud.keys</t>
         </is>
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
         </is>
       </c>
       <c r="D1678" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
         </is>
       </c>
     </row>
@@ -30636,17 +30636,17 @@
       <c r="A1679" t="inlineStr"/>
       <c r="B1679" t="inlineStr">
         <is>
-          <t>factory.reason.uplinked</t>
+          <t>morph.state.none</t>
         </is>
       </c>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>这台机器正被你接入，先退出接入</t>
+          <t>常态</t>
         </is>
       </c>
       <c r="D1679" t="inlineStr">
         <is>
-          <t>You are uplinked into this machine: leave the uplink first</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -30654,17 +30654,17 @@
       <c r="A1680" t="inlineStr"/>
       <c r="B1680" t="inlineStr">
         <is>
-          <t>signal.cmd.uplinked</t>
+          <t>morph.state.limiter</t>
         </is>
       </c>
       <c r="C1680" t="inlineStr">
         <is>
-          <t>接入：{0}</t>
+          <t>形变态</t>
         </is>
       </c>
       <c r="D1680" t="inlineStr">
         <is>
-          <t>Uplinked: {0}</t>
+          <t>morph state</t>
         </is>
       </c>
     </row>
@@ -30672,17 +30672,17 @@
       <c r="A1681" t="inlineStr"/>
       <c r="B1681" t="inlineStr">
         <is>
-          <t>signal.cmd.reconnecting</t>
+          <t>morph.state.fluid</t>
         </is>
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>重连中：{0}</t>
+          <t>喷口态</t>
         </is>
       </c>
       <c r="D1681" t="inlineStr">
         <is>
-          <t>Reconnecting: {0}</t>
+          <t>vent state</t>
         </is>
       </c>
     </row>
@@ -30690,17 +30690,17 @@
       <c r="A1682" t="inlineStr"/>
       <c r="B1682" t="inlineStr">
         <is>
-          <t>signal.cmd.strategy</t>
+          <t>morph.state.em</t>
         </is>
       </c>
       <c r="C1682" t="inlineStr">
         <is>
-          <t>战略视角</t>
+          <t>线圈态</t>
         </is>
       </c>
       <c r="D1682" t="inlineStr">
         <is>
-          <t>Strategy view</t>
+          <t>coil state</t>
         </is>
       </c>
     </row>
@@ -30708,17 +30708,17 @@
       <c r="A1683" t="inlineStr"/>
       <c r="B1683" t="inlineStr">
         <is>
-          <t>region.control.fail.not_found</t>
+          <t>morph.state.join</t>
         </is>
       </c>
       <c r="C1683" t="inlineStr">
         <is>
-          <t>没有可以接入的目标。</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
       <c r="D1683" t="inlineStr">
         <is>
-          <t>There is nothing to uplink into.</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
     </row>
@@ -30726,17 +30726,17 @@
       <c r="A1684" t="inlineStr"/>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>region.control.fail.not_friendly</t>
+          <t>signal.list.port_tag</t>
         </is>
       </c>
       <c r="C1684" t="inlineStr">
         <is>
-          <t>目标不属于本地点。</t>
+          <t>◇口</t>
         </is>
       </c>
       <c r="D1684" t="inlineStr">
         <is>
-          <t>The target does not belong to this site.</t>
+          <t>◇PORT</t>
         </is>
       </c>
     </row>
@@ -30744,17 +30744,17 @@
       <c r="A1685" t="inlineStr"/>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>region.control.fail.dead</t>
+          <t>signal.list.overheat_tag</t>
         </is>
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>目标已阵亡。</t>
+          <t>过热</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
         <is>
-          <t>The target is destroyed.</t>
+          <t>HOT</t>
         </is>
       </c>
     </row>
@@ -30762,17 +30762,17 @@
       <c r="A1686" t="inlineStr"/>
       <c r="B1686" t="inlineStr">
         <is>
-          <t>region.control.fail.out_of_range</t>
+          <t>signal.list.port_line</t>
         </is>
       </c>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>目标当前不在场。</t>
+          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
         </is>
       </c>
       <c r="D1686" t="inlineStr">
         <is>
-          <t>The target is not here right now.</t>
+          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
         </is>
       </c>
     </row>
@@ -30780,17 +30780,17 @@
       <c r="A1687" t="inlineStr"/>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>region.control.fail.jammed</t>
+          <t>signal.list.no_port_line</t>
         </is>
       </c>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>信号被干扰，接入失败。</t>
+          <t>没有接入口：接入后只能驾驶，不插入固件</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
         <is>
-          <t>The signal is jammed; uplink failed.</t>
+          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -30798,17 +30798,17 @@
       <c r="A1688" t="inlineStr"/>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>region.control.fail.transition</t>
+          <t>signal.list.overheat_line</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>镜头切换中，请稍候。</t>
+          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
         </is>
       </c>
       <c r="D1688" t="inlineStr">
         <is>
-          <t>The camera is moving; please wait.</t>
+          <t>Overheated (heat {0}): it fires again once below {1}</t>
         </is>
       </c>
     </row>
@@ -30816,17 +30816,17 @@
       <c r="A1689" t="inlineStr"/>
       <c r="B1689" t="inlineStr">
         <is>
-          <t>region.control.fail.modal</t>
+          <t>signal.list.morph_line</t>
         </is>
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>请先关闭当前面板。</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1689" t="inlineStr">
         <is>
-          <t>Close the current panel first.</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -30834,17 +30834,17 @@
       <c r="A1690" t="inlineStr"/>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>region.control.fail.already</t>
+          <t>signal.list.experience_line</t>
         </is>
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>已经接入这台机器。</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1690" t="inlineStr">
         <is>
-          <t>You are already uplinked into this machine.</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -30852,17 +30852,17 @@
       <c r="A1691" t="inlineStr"/>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>region.control.fail.ineligible</t>
+          <t>signal.port_badge.tip</t>
         </is>
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>目标暂时不能接入。</t>
+          <t>带接入口的机器</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
         <is>
-          <t>The target cannot be uplinked right now.</t>
+          <t>Machine with an uplink port</t>
         </is>
       </c>
     </row>
@@ -30870,17 +30870,17 @@
       <c r="A1692" t="inlineStr"/>
       <c r="B1692" t="inlineStr">
         <is>
-          <t>region.control.fail.other</t>
+          <t>machine.exp.produced</t>
         </is>
       </c>
       <c r="C1692" t="inlineStr">
         <is>
-          <t>接入失败。</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="D1692" t="inlineStr">
         <is>
-          <t>Uplink failed.</t>
+          <t>Produced</t>
         </is>
       </c>
     </row>
@@ -30888,17 +30888,17 @@
       <c r="A1693" t="inlineStr"/>
       <c r="B1693" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink</t>
+          <t>machine.exp.first_job</t>
         </is>
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>首次工作</t>
         </is>
       </c>
       <c r="D1693" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>First job</t>
         </is>
       </c>
     </row>
@@ -30906,17 +30906,17 @@
       <c r="A1694" t="inlineStr"/>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink</t>
+          <t>machine.exp.controlled</t>
         </is>
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>已接入</t>
+          <t>首次与信号同行</t>
         </is>
       </c>
       <c r="D1694" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>First time with the signal</t>
         </is>
       </c>
     </row>
@@ -30924,17 +30924,17 @@
       <c r="A1695" t="inlineStr"/>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink_leave</t>
+          <t>machine.exp.expedition</t>
         </is>
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>远征</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Expedition</t>
         </is>
       </c>
     </row>
@@ -30942,17 +30942,17 @@
       <c r="A1696" t="inlineStr"/>
       <c r="B1696" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink_leave</t>
+          <t>machine.exp.severely_injured</t>
         </is>
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>信号离开机器</t>
+          <t>重伤</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
         <is>
-          <t>The signal left the machine</t>
+          <t>Severely injured</t>
         </is>
       </c>
     </row>
@@ -30960,17 +30960,17 @@
       <c r="A1697" t="inlineStr"/>
       <c r="B1697" t="inlineStr">
         <is>
-          <t>pause.codex</t>
+          <t>machine.exp.elite_kill</t>
         </is>
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>精英击破</t>
         </is>
       </c>
       <c r="D1697" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Elite kill</t>
         </is>
       </c>
     </row>
@@ -30978,17 +30978,17 @@
       <c r="A1698" t="inlineStr"/>
       <c r="B1698" t="inlineStr">
         <is>
-          <t>pause.camera_title</t>
+          <t>machine.exp.boss_participation</t>
         </is>
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>接入镜头</t>
+          <t>首领战</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
         <is>
-          <t>Uplink camera</t>
+          <t>Boss fight</t>
         </is>
       </c>
     </row>
@@ -30996,17 +30996,17 @@
       <c r="A1699" t="inlineStr"/>
       <c r="B1699" t="inlineStr">
         <is>
-          <t>pause.camera_zoom</t>
+          <t>machine.exp.returned</t>
         </is>
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>接入时镜头距离 {0}%</t>
+          <t>返航</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
         <is>
-          <t>Uplink camera distance {0}%</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
@@ -31014,17 +31014,17 @@
       <c r="A1700" t="inlineStr"/>
       <c r="B1700" t="inlineStr">
         <is>
-          <t>pause.camera_follow</t>
+          <t>machine.exp.sep</t>
         </is>
       </c>
       <c r="C1700" t="inlineStr">
         <is>
-          <t>接入时跟随力度 {0}%</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1700" t="inlineStr">
         <is>
-          <t>Uplink follow strength {0}%</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -31032,17 +31032,17 @@
       <c r="A1701" t="inlineStr"/>
       <c r="B1701" t="inlineStr">
         <is>
-          <t>pause.camera_reset</t>
+          <t>machine.injury.combat</t>
         </is>
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>战斗损伤（HP {0}/{1}）</t>
         </is>
       </c>
       <c r="D1701" t="inlineStr">
         <is>
-          <t>Reset to default</t>
+          <t>Combat damage (HP {0}/{1})</t>
         </is>
       </c>
     </row>
@@ -31050,17 +31050,17 @@
       <c r="A1702" t="inlineStr"/>
       <c r="B1702" t="inlineStr">
         <is>
-          <t>pause.camera_zoom_tip</t>
+          <t>machine.exp.none</t>
         </is>
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>无记录经历</t>
         </is>
       </c>
       <c r="D1702" t="inlineStr">
         <is>
-          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>No recorded experience</t>
         </is>
       </c>
     </row>
@@ -31068,17 +31068,17 @@
       <c r="A1703" t="inlineStr"/>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>pause.camera_follow_tip</t>
+          <t>machine.exp.signal</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>与信号同行 {0} 次，累计 {1}</t>
         </is>
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>With the signal {0} times, {1} in total</t>
         </is>
       </c>
     </row>
@@ -31086,17 +31086,17 @@
       <c r="A1704" t="inlineStr"/>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>camera.follow.started</t>
+          <t>machine.exp.signal_none</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+          <t>尚未与信号同行</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
         <is>
-          <t>Camera following {0} (pan or press {1} again to stop)</t>
+          <t>Never carried the signal</t>
         </is>
       </c>
     </row>
@@ -31104,17 +31104,17 @@
       <c r="A1705" t="inlineStr"/>
       <c r="B1705" t="inlineStr">
         <is>
-          <t>camera.follow.stopped</t>
+          <t>machine.status.dead</t>
         </is>
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>镜头停止跟随</t>
+          <t>阵亡（纪念记录）</t>
         </is>
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>Camera follow stopped</t>
+          <t>Destroyed (memorial record)</t>
         </is>
       </c>
     </row>
@@ -31122,17 +31122,17 @@
       <c r="A1706" t="inlineStr"/>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>camera.follow.nothing</t>
+          <t>machine.status.in_factory</t>
         </is>
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>先选中一台机器再按 {0} 跟随</t>
+          <t>厂内待驶出</t>
         </is>
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>Select a machine first, then press {0} to follow it</t>
+          <t>Waiting in the factory</t>
         </is>
       </c>
     </row>
@@ -31140,15 +31140,861 @@
       <c r="A1707" t="inlineStr"/>
       <c r="B1707" t="inlineStr">
         <is>
+          <t>machine.status.uplinked</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>接入中</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr"/>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>machine.status.idle</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>空闲</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr"/>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>machine.status.working</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>工作中</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr"/>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>machine.detail.none</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr"/>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>machine.detail.injury_none</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>无记录</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>none recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr"/>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>machine.detail.port_yes</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr"/>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>machine.detail.port_no</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>没有</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr"/>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>machine.detail.line_id</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr"/>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>machine.detail.line_vitals</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr"/>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>machine.detail.line_exp</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>经历：{0}</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>Experience: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr"/>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>machine.detail.line_signal</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr"/>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>machine.detail.line_stats</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr"/>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>machine.detail.line_morph</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>机身：{0}</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>Body: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr"/>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>victory.summary</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr"/>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>victory.row.number</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>#{0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>#{0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr"/>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>victory.row.alive</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>幸存</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr"/>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>victory.row.dead</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>阵亡</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr"/>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>expedition.return.row_status_alive</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>幸存，将随撤离返回家园；{0}</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>Survived and returns home with the evacuation; {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr"/>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>expedition.return.row_status_dead</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr"/>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>factory.reason.uplinked</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>这台机器正被你接入，先退出接入</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>You are uplinked into this machine: leave the uplink first</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr"/>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>signal.cmd.uplinked</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>接入：{0}</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>Uplinked: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr"/>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>signal.cmd.reconnecting</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>重连中：{0}</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>Reconnecting: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr"/>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>signal.cmd.strategy</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>战略视角</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>Strategy view</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr"/>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>region.control.fail.not_found</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>没有可以接入的目标。</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>There is nothing to uplink into.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr"/>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>region.control.fail.not_friendly</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>目标不属于本地点。</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>The target does not belong to this site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr"/>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>region.control.fail.dead</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>目标已阵亡。</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>The target is destroyed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr"/>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>region.control.fail.out_of_range</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>目标当前不在场。</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>The target is not here right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr"/>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>region.control.fail.jammed</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>信号被干扰，接入失败。</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>The signal is jammed; uplink failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr"/>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>region.control.fail.transition</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>镜头切换中，请稍候。</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>The camera is moving; please wait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr"/>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>region.control.fail.modal</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>请先关闭当前面板。</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>Close the current panel first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr"/>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>region.control.fail.already</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>已经接入这台机器。</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>You are already uplinked into this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr"/>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>region.control.fail.ineligible</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>目标暂时不能接入。</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>The target cannot be uplinked right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr"/>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>region.control.fail.other</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>接入失败。</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>Uplink failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr"/>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>feedback.tag.uplink</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>接入</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>Uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr"/>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>feedback.caption.uplink</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>已接入</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>Uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr"/>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>feedback.tag.uplink_leave</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr"/>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>feedback.caption.uplink_leave</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>信号离开机器</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>The signal left the machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr"/>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>pause.codex</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>图鉴</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr"/>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>pause.camera_title</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>接入镜头</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Uplink camera</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr"/>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>pause.camera_zoom</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>接入时镜头距离 {0}%</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>Uplink camera distance {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr"/>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>pause.camera_follow</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>接入时跟随力度 {0}%</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>Uplink follow strength {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr"/>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>pause.camera_reset</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>Reset to default</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr"/>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>pause.camera_zoom_tip</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr"/>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>pause.camera_follow_tip</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr"/>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>camera.follow.started</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>Camera following {0} (pan or press {1} again to stop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr"/>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>camera.follow.stopped</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>镜头停止跟随</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>Camera follow stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr"/>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>camera.follow.nothing</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>先选中一台机器再按 {0} 跟随</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>Select a machine first, then press {0} to follow it</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr"/>
+      <c r="B1754" t="inlineStr">
+        <is>
           <t>camera.follow.group</t>
         </is>
       </c>
-      <c r="C1707" t="inlineStr">
+      <c r="C1754" t="inlineStr">
         <is>
           <t>{0} 台机器</t>
         </is>
       </c>
-      <c r="D1707" t="inlineStr">
+      <c r="D1754" t="inlineStr">
         <is>
           <t>{0} machines</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1754"/>
+  <dimension ref="A1:D1813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29124,17 +29124,17 @@
       <c r="A1595" t="inlineStr"/>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.title</t>
+          <t>reaction.popup.many</t>
         </is>
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>信号接入</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>Signal uplink</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
     </row>
@@ -29142,17 +29142,17 @@
       <c r="A1596" t="inlineStr"/>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.body</t>
+          <t>reaction.popup.first</t>
         </is>
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
+          <t>新反应：{0}！</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
+          <t>New reaction: {0}!</t>
         </is>
       </c>
     </row>
@@ -29160,17 +29160,17 @@
       <c r="A1597" t="inlineStr"/>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.hint</t>
+          <t>reading.popup.zone</t>
         </is>
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>第一次接入一台机器，或打开信号核时解锁</t>
+          <t>区域展开</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
+          <t>Zone deployed</t>
         </is>
       </c>
     </row>
@@ -29178,17 +29178,17 @@
       <c r="A1598" t="inlineStr"/>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.title</t>
+          <t>reading.popup.echo</t>
         </is>
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>接入口</t>
+          <t>回波</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>Uplink port</t>
+          <t>Echo</t>
         </is>
       </c>
     </row>
@@ -29196,17 +29196,17 @@
       <c r="A1599" t="inlineStr"/>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.body</t>
+          <t>reading.popup.drone</t>
         </is>
       </c>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
+          <t>无人机出动</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
+          <t>Drone launched</t>
         </is>
       </c>
     </row>
@@ -29214,17 +29214,17 @@
       <c r="A1600" t="inlineStr"/>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.hint</t>
+          <t>reaction.attr.none</t>
         </is>
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
+          <t>本场没有打出反应</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
+          <t>No reactions this time</t>
         </is>
       </c>
     </row>
@@ -29232,17 +29232,17 @@
       <c r="A1601" t="inlineStr"/>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.title</t>
+          <t>reaction.attr.item</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>核心固件</t>
+          <t>{0} {1}%（{2} 次）</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>Core firmware</t>
+          <t>{0} {1}% ({2}×)</t>
         </is>
       </c>
     </row>
@@ -29250,17 +29250,17 @@
       <c r="A1602" t="inlineStr"/>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.body</t>
+          <t>reaction.attr.summary</t>
         </is>
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
+          <t>反应伤害占比：{0}</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
+          <t>Reaction damage share: {0}</t>
         </is>
       </c>
     </row>
@@ -29268,17 +29268,17 @@
       <c r="A1603" t="inlineStr"/>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.hint</t>
+          <t>reaction.attr.sep</t>
         </is>
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>第一次打开信号核时解锁</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>Unlocks the first time you open the Signal Core</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -29286,17 +29286,17 @@
       <c r="A1604" t="inlineStr"/>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.title</t>
+          <t>reaction.attr.title_raid</t>
         </is>
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>安全模式</t>
+          <t>突袭 · {0}</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>Safe mode</t>
+          <t>Raid · {0}</t>
         </is>
       </c>
     </row>
@@ -29304,17 +29304,17 @@
       <c r="A1605" t="inlineStr"/>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.body</t>
+          <t>reaction.attr.title_expedition</t>
         </is>
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
+          <t>远征 · {0} 第 {1} 次</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
+          <t>Expedition · {0} #{1}</t>
         </is>
       </c>
     </row>
@@ -29322,17 +29322,17 @@
       <c r="A1606" t="inlineStr"/>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.hint</t>
+          <t>reaction.attr.ongoing</t>
         </is>
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
+          <t>进行中（{0} 起）</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
+          <t>In progress (since {0})</t>
         </is>
       </c>
     </row>
@@ -29340,17 +29340,17 @@
       <c r="A1607" t="inlineStr"/>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>codex.signal.raw.title</t>
+          <t>reaction.attr.ended</t>
         </is>
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>{0} ～ {1}</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>Running raw</t>
+          <t>{0} – {1}</t>
         </is>
       </c>
     </row>
@@ -29358,17 +29358,17 @@
       <c r="A1608" t="inlineStr"/>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>codex.signal.raw.body</t>
+          <t>reaction.attr.total</t>
         </is>
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
+          <t>敌方共受伤害 {0}</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
+          <t>Total damage to enemies {0}</t>
         </is>
       </c>
     </row>
@@ -29376,17 +29376,17 @@
       <c r="A1609" t="inlineStr"/>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>codex.signal.raw.hint</t>
+          <t>reaction.log.unknown</t>
         </is>
       </c>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>第一次带回加密固件时解锁</t>
+          <t>未知单位</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Unlocks the first time you bring back encrypted firmware</t>
+          <t>Unknown unit</t>
         </is>
       </c>
     </row>
@@ -29394,17 +29394,17 @@
       <c r="A1610" t="inlineStr"/>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.title</t>
+          <t>reaction.log.machine</t>
         </is>
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>信号暴露</t>
+          <t>机器</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Signal exposure</t>
+          <t>Machine</t>
         </is>
       </c>
     </row>
@@ -29412,17 +29412,17 @@
       <c r="A1611" t="inlineStr"/>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.body</t>
+          <t>reaction.log.machine_n</t>
         </is>
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
+          <t>机器 {0}</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
+          <t>Machine {0}</t>
         </is>
       </c>
     </row>
@@ -29430,17 +29430,17 @@
       <c r="A1612" t="inlineStr"/>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.hint</t>
+          <t>reaction.log.turret</t>
         </is>
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>第一次打开暴露面板或带回加密固件时解锁</t>
+          <t>炮塔</t>
         </is>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
+          <t>Turret</t>
         </is>
       </c>
     </row>
@@ -29448,17 +29448,17 @@
       <c r="A1613" t="inlineStr"/>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.title</t>
+          <t>reaction.log.structure</t>
         </is>
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>信号覆盖网络</t>
+          <t>建筑</t>
         </is>
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>Signal coverage network</t>
+          <t>Structure</t>
         </is>
       </c>
     </row>
@@ -29466,17 +29466,17 @@
       <c r="A1614" t="inlineStr"/>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.body</t>
+          <t>reaction.log.enemy</t>
         </is>
       </c>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
+          <t>敌方单位</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
-          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
+          <t>Enemy unit</t>
         </is>
       </c>
     </row>
@@ -29484,17 +29484,17 @@
       <c r="A1615" t="inlineStr"/>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.hint</t>
+          <t>reaction.log.no_firmware</t>
         </is>
       </c>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
+          <t>无固件</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
+          <t>no firmware</t>
         </is>
       </c>
     </row>
@@ -29502,17 +29502,17 @@
       <c r="A1616" t="inlineStr"/>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.title</t>
+          <t>reaction.log.first</t>
         </is>
       </c>
       <c r="C1616" t="inlineStr">
         <is>
-          <t>远距离跳转</t>
+          <t>{0}（首次）</t>
         </is>
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>Long-range jump</t>
+          <t>{0} (first)</t>
         </is>
       </c>
     </row>
@@ -29520,17 +29520,17 @@
       <c r="A1617" t="inlineStr"/>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.body</t>
+          <t>reaction.log.line</t>
         </is>
       </c>
       <c r="C1617" t="inlineStr">
         <is>
-          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
+          <t>{0}　{1}　{2}［{3}］→ {4}</t>
         </is>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
-          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
+          <t>{0}  {1}  {2} [{3}] → {4}</t>
         </is>
       </c>
     </row>
@@ -29538,17 +29538,17 @@
       <c r="A1618" t="inlineStr"/>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.hint</t>
+          <t>reaction.panel.title</t>
         </is>
       </c>
       <c r="C1618" t="inlineStr">
         <is>
-          <t>第一次远距离跳转时解锁</t>
+          <t>反应记录</t>
         </is>
       </c>
       <c r="D1618" t="inlineStr">
         <is>
-          <t>Unlocks the first time you make a long-range jump</t>
+          <t>Reactions</t>
         </is>
       </c>
     </row>
@@ -29556,17 +29556,17 @@
       <c r="A1619" t="inlineStr"/>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>codex.signal.relay.title</t>
+          <t>reaction.panel.tab_log</t>
         </is>
       </c>
       <c r="C1619" t="inlineStr">
         <is>
-          <t>信号中继</t>
+          <t>反应日志</t>
         </is>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
-          <t>Signal relays</t>
+          <t>Reaction log</t>
         </is>
       </c>
     </row>
@@ -29574,17 +29574,17 @@
       <c r="A1620" t="inlineStr"/>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>codex.signal.relay.body</t>
+          <t>reaction.panel.tab_attr</t>
         </is>
       </c>
       <c r="C1620" t="inlineStr">
         <is>
-          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
+          <t>伤害归因</t>
         </is>
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
+          <t>Damage share</t>
         </is>
       </c>
     </row>
@@ -29592,17 +29592,17 @@
       <c r="A1621" t="inlineStr"/>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>codex.signal.relay.hint</t>
+          <t>reaction.panel.tab_codex</t>
         </is>
       </c>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
+          <t>反应图鉴</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
+          <t>Reaction codex</t>
         </is>
       </c>
     </row>
@@ -29610,17 +29610,17 @@
       <c r="A1622" t="inlineStr"/>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.title</t>
+          <t>reaction.panel.filter_all</t>
         </is>
       </c>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>机身形变</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
         <is>
-          <t>Machine morph</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -29628,17 +29628,17 @@
       <c r="A1623" t="inlineStr"/>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.body</t>
+          <t>reaction.panel.filter_expedition</t>
         </is>
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
+          <t>远征</t>
         </is>
       </c>
       <c r="D1623" t="inlineStr">
         <is>
-          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
+          <t>Expeditions</t>
         </is>
       </c>
     </row>
@@ -29646,17 +29646,17 @@
       <c r="A1624" t="inlineStr"/>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.hint</t>
+          <t>reaction.panel.filter_raid</t>
         </is>
       </c>
       <c r="C1624" t="inlineStr">
         <is>
-          <t>第一次看到机身形变时解锁</t>
+          <t>突袭</t>
         </is>
       </c>
       <c r="D1624" t="inlineStr">
         <is>
-          <t>Unlocks the first time you see a machine morph</t>
+          <t>Raids</t>
         </is>
       </c>
     </row>
@@ -29664,17 +29664,17 @@
       <c r="A1625" t="inlineStr"/>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>codex.panel.title</t>
+          <t>reaction.panel.empty_log</t>
         </is>
       </c>
       <c r="C1625" t="inlineStr">
         <is>
-          <t>图鉴 · 系统说明</t>
+          <t>还没有反应记录（只记本次载入之后的）</t>
         </is>
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>Codex · Systems</t>
+          <t>No reactions yet (only since this load)</t>
         </is>
       </c>
     </row>
@@ -29682,17 +29682,17 @@
       <c r="A1626" t="inlineStr"/>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>codex.panel.close</t>
+          <t>reaction.panel.empty_attr</t>
         </is>
       </c>
       <c r="C1626" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>还没有远征或突袭的反应伤害记录</t>
         </is>
       </c>
       <c r="D1626" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>No expedition or raid damage records yet</t>
         </is>
       </c>
     </row>
@@ -29700,17 +29700,17 @@
       <c r="A1627" t="inlineStr"/>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>codex.panel.list_title</t>
+          <t>reaction.panel.log_hint</t>
         </is>
       </c>
       <c r="C1627" t="inlineStr">
         <is>
-          <t>条目 {0}/{1}</t>
+          <t>最近 {0} 条，只保留本次载入之后的；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1627" t="inlineStr">
         <is>
-          <t>Entries {0}/{1}</t>
+          <t>Last {0} entries since this load; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -29718,17 +29718,17 @@
       <c r="A1628" t="inlineStr"/>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>codex.panel.related</t>
+          <t>reaction.panel.attr_hint</t>
         </is>
       </c>
       <c r="C1628" t="inlineStr">
         <is>
-          <t>相关条目</t>
+          <t>占比 = 反应额外伤害 / 这一场敌方受到的全部伤害；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1628" t="inlineStr">
         <is>
-          <t>Related</t>
+          <t>Share = extra reaction damage / all damage enemies took; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -29736,17 +29736,17 @@
       <c r="A1629" t="inlineStr"/>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>codex.panel.locked_title</t>
+          <t>reaction.panel.codex_hint</t>
         </is>
       </c>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>已解锁 {0} / {1}：本存档里第一次打出某条反应时解锁；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Unlocked {0}/{1}: an entry unlocks the first time you trigger it in this save; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -29754,17 +29754,17 @@
       <c r="A1630" t="inlineStr"/>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>codex.panel.locked_body</t>
+          <t>reaction.panel.count</t>
         </is>
       </c>
       <c r="C1630" t="inlineStr">
         <is>
-          <t>尚未接触。{0}</t>
+          <t>{0} 条</t>
         </is>
       </c>
       <c r="D1630" t="inlineStr">
         <is>
-          <t>Not encountered yet. {0}</t>
+          <t>{0} entries</t>
         </is>
       </c>
     </row>
@@ -29772,17 +29772,17 @@
       <c r="A1631" t="inlineStr"/>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>codex.panel.none_selected</t>
+          <t>stats.panel.title</t>
         </is>
       </c>
       <c r="C1631" t="inlineStr">
         <is>
-          <t>在左侧选一个条目</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D1631" t="inlineStr">
         <is>
-          <t>Pick an entry on the left</t>
+          <t>Statistics</t>
         </is>
       </c>
     </row>
@@ -29790,17 +29790,17 @@
       <c r="A1632" t="inlineStr"/>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>codex.panel.footer</t>
+          <t>stats.panel.section_combat</t>
         </is>
       </c>
       <c r="C1632" t="inlineStr">
         <is>
-          <t>固件、反应、敌人等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
+          <t>战斗 · 反应伤害归因</t>
         </is>
       </c>
       <c r="D1632" t="inlineStr">
         <is>
-          <t>Firmware, reaction and enemy tabs arrive in a later version; press {act:Cancel} to close</t>
+          <t>Combat · Reaction damage share</t>
         </is>
       </c>
     </row>
@@ -29808,17 +29808,17 @@
       <c r="A1633" t="inlineStr"/>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>codex.panel.error</t>
+          <t>stats.panel.count</t>
         </is>
       </c>
       <c r="C1633" t="inlineStr">
         <is>
-          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
+          <t>{0} 场</t>
         </is>
       </c>
       <c r="D1633" t="inlineStr">
         <is>
-          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
+          <t>{0} sessions</t>
         </is>
       </c>
     </row>
@@ -29826,17 +29826,17 @@
       <c r="A1634" t="inlineStr"/>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>codex.help.tip_title</t>
+          <t>stats.panel.totals_title</t>
         </is>
       </c>
       <c r="C1634" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>累计（{0} 场）</t>
         </is>
       </c>
       <c r="D1634" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>Totals ({0} sessions)</t>
         </is>
       </c>
     </row>
@@ -29844,17 +29844,17 @@
       <c r="A1635" t="inlineStr"/>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>codex.help.tip</t>
+          <t>stats.panel.totals_line</t>
         </is>
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>打开图鉴条目：{0}</t>
+          <t>敌方共受伤害 {0}，其中反应额外伤害占 {1}%</t>
         </is>
       </c>
       <c r="D1635" t="inlineStr">
         <is>
-          <t>Open the codex entry: {0}</t>
+          <t>Enemies took {0} damage in total; reaction bonus damage was {1}%</t>
         </is>
       </c>
     </row>
@@ -29862,17 +29862,17 @@
       <c r="A1636" t="inlineStr"/>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>uplink.hud.title</t>
+          <t>stats.panel.sessions_title</t>
         </is>
       </c>
       <c r="C1636" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>每场明细</t>
         </is>
       </c>
       <c r="D1636" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>Per session</t>
         </is>
       </c>
     </row>
@@ -29880,17 +29880,17 @@
       <c r="A1637" t="inlineStr"/>
       <c r="B1637" t="inlineStr">
         <is>
-          <t>uplink.hud.help_button</t>
+          <t>stats.panel.empty</t>
         </is>
       </c>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>还没有远征或突袭的战斗统计。出一次远征并在战斗中打出反应后，这里会按反应列出伤害占比。</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>No expedition or raid combat stats yet. Go on an expedition and trigger reactions in combat to see each reaction's damage share here.</t>
         </is>
       </c>
     </row>
@@ -29898,17 +29898,17 @@
       <c r="A1638" t="inlineStr"/>
       <c r="B1638" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip_title</t>
+          <t>stats.panel.hint</t>
         </is>
       </c>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>接入 HUD</t>
+          <t>只统计远征与突袭（家园平时的训练战斗不计），最近 {0} 场随存档保存；占比 = 反应额外伤害 / 敌方受到的全部伤害；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1638" t="inlineStr">
         <is>
-          <t>Uplink HUD</t>
+          <t>Only expeditions and raids count (training at home does not); the last {0} sessions are saved; share = reaction bonus damage / all damage enemies took; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -29916,17 +29916,17 @@
       <c r="A1639" t="inlineStr"/>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip</t>
+          <t>pause.stats</t>
         </is>
       </c>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D1639" t="inlineStr">
         <is>
-          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
+          <t>Statistics</t>
         </is>
       </c>
     </row>
@@ -29934,17 +29934,17 @@
       <c r="A1640" t="inlineStr"/>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>uplink.hud.slot</t>
+          <t>reaction.codex.locked_name</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -29952,17 +29952,17 @@
       <c r="A1641" t="inlineStr"/>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>uplink.hud.state.active</t>
+          <t>reaction.codex.locked</t>
         </is>
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>生效</t>
+          <t>尚未打出。战斗中触发一次即解锁本条。</t>
         </is>
       </c>
       <c r="D1641" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not triggered yet. Trigger it once in combat to unlock this entry.</t>
         </is>
       </c>
     </row>
@@ -29970,17 +29970,17 @@
       <c r="A1642" t="inlineStr"/>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>uplink.hud.state.cooling</t>
+          <t>reaction.codex.closed</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
         <is>
-          <t>冷却 {0} 秒</t>
+          <t>尚未开放命名：随阵营推进开放（{0}）。</t>
         </is>
       </c>
       <c r="D1642" t="inlineStr">
         <is>
-          <t>cooling {0}s</t>
+          <t>Not yet named: unlocks as factions advance ({0}).</t>
         </is>
       </c>
     </row>
@@ -29988,17 +29988,17 @@
       <c r="A1643" t="inlineStr"/>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>uplink.hud.state.raw</t>
+          <t>reaction.codex.unreachable</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>当前机械内容下无法触发。</t>
         </is>
       </c>
       <c r="D1643" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>Cannot trigger with current mechanical content.</t>
         </is>
       </c>
     </row>
@@ -30006,17 +30006,17 @@
       <c r="A1644" t="inlineStr"/>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>uplink.hud.state.not_inserted</t>
+          <t>reaction.codex.first</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>未插入：{0}</t>
+          <t>首次触发：{0}，{1}</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
         <is>
-          <t>not inserted: {0}</t>
+          <t>First triggered: {0}, {1}</t>
         </is>
       </c>
     </row>
@@ -30024,17 +30024,17 @@
       <c r="A1645" t="inlineStr"/>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>uplink.hud.state.ineffective</t>
+          <t>pause.reaction_title</t>
         </is>
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>不生效：{0}</t>
+          <t>战斗反馈</t>
         </is>
       </c>
       <c r="D1645" t="inlineStr">
         <is>
-          <t>no effect: {0}</t>
+          <t>Combat feedback</t>
         </is>
       </c>
     </row>
@@ -30042,17 +30042,17 @@
       <c r="A1646" t="inlineStr"/>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>uplink.hud.state.empty</t>
+          <t>pause.reaction_popups</t>
         </is>
       </c>
       <c r="C1646" t="inlineStr">
         <is>
-          <t>空槽</t>
+          <t>反应弹字</t>
         </is>
       </c>
       <c r="D1646" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>Reaction pop-ups</t>
         </is>
       </c>
     </row>
@@ -30060,17 +30060,17 @@
       <c r="A1647" t="inlineStr"/>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>uplink.hud.state.locked</t>
+          <t>pause.reaction_slowmo</t>
         </is>
       </c>
       <c r="C1647" t="inlineStr">
         <is>
-          <t>未解锁</t>
+          <t>首次反应慢放</t>
         </is>
       </c>
       <c r="D1647" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>Slow motion on first reaction</t>
         </is>
       </c>
     </row>
@@ -30078,17 +30078,17 @@
       <c r="A1648" t="inlineStr"/>
       <c r="B1648" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.over_quota</t>
+          <t>pause.reaction_nudge</t>
         </is>
       </c>
       <c r="C1648" t="inlineStr">
         <is>
-          <t>超出接入口配额 {0} 个</t>
+          <t>首次反应镜头推动</t>
         </is>
       </c>
       <c r="D1648" t="inlineStr">
         <is>
-          <t>over the port quota of {0}</t>
+          <t>Camera nudge on first reaction</t>
         </is>
       </c>
     </row>
@@ -30096,17 +30096,17 @@
       <c r="A1649" t="inlineStr"/>
       <c r="B1649" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.path_limit</t>
+          <t>pause.reaction_reset</t>
         </is>
       </c>
       <c r="C1649" t="inlineStr">
         <is>
-          <t>路径会超过上限 {0} 条</t>
+          <t>战斗反馈恢复默认</t>
         </is>
       </c>
       <c r="D1649" t="inlineStr">
         <is>
-          <t>paths would exceed {0}</t>
+          <t>Reset combat feedback</t>
         </is>
       </c>
     </row>
@@ -30114,17 +30114,17 @@
       <c r="A1650" t="inlineStr"/>
       <c r="B1650" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.unknown</t>
+          <t>pause.reaction_log</t>
         </is>
       </c>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>不是已知的固件</t>
+          <t>反应记录</t>
         </is>
       </c>
       <c r="D1650" t="inlineStr">
         <is>
-          <t>unknown firmware</t>
+          <t>Reactions</t>
         </is>
       </c>
     </row>
@@ -30132,17 +30132,17 @@
       <c r="A1651" t="inlineStr"/>
       <c r="B1651" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.no_uplink</t>
+          <t>pause.reaction_popups_tip</t>
         </is>
       </c>
       <c r="C1651" t="inlineStr">
         <is>
-          <t>这台机器没有接入口</t>
+          <t>反应名打在目标头上（大量触发时合并成“短路 ×12”，每秒最多 {0} 条）。关掉后字幕、日志与统计照常。</t>
         </is>
       </c>
       <c r="D1651" t="inlineStr">
         <is>
-          <t>this machine has no uplink port</t>
+          <t>Reaction names pop over the target (bursts merge into "Short Circuit ×12", at most {0} per second). Captions, log and stats still work when off.</t>
         </is>
       </c>
     </row>
@@ -30150,17 +30150,17 @@
       <c r="A1652" t="inlineStr"/>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.off_path</t>
+          <t>pause.reaction_slowmo_tip</t>
         </is>
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>接入口不在导线上</t>
+          <t>本存档里每条反应第一次触发时短暂慢放 {0} 秒（只在镜头正看着时）。关掉后仍解锁图鉴。</t>
         </is>
       </c>
       <c r="D1652" t="inlineStr">
         <is>
-          <t>the uplink port is not on a wire</t>
+          <t>Briefly slows time for {0}s the first time each reaction triggers in this save (only while you are watching). The codex still unlocks when off.</t>
         </is>
       </c>
     </row>
@@ -30168,17 +30168,17 @@
       <c r="A1653" t="inlineStr"/>
       <c r="B1653" t="inlineStr">
         <is>
-          <t>uplink.hud.slot_tip</t>
+          <t>pause.reaction_nudge_tip</t>
         </is>
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>{0} 号槽：{1}</t>
+          <t>本存档里每条反应第一次触发时镜头朝它轻推一下。</t>
         </is>
       </c>
       <c r="D1653" t="inlineStr">
         <is>
-          <t>Slot {0}: {1}</t>
+          <t>Nudges the camera toward each reaction the first time it triggers in this save.</t>
         </is>
       </c>
     </row>
@@ -30186,17 +30186,17 @@
       <c r="A1654" t="inlineStr"/>
       <c r="B1654" t="inlineStr">
         <is>
-          <t>uplink.hud.heat</t>
+          <t>codex.signal.uplink.title</t>
         </is>
       </c>
       <c r="C1654" t="inlineStr">
         <is>
-          <t>热量 {0}/{1}</t>
+          <t>信号接入</t>
         </is>
       </c>
       <c r="D1654" t="inlineStr">
         <is>
-          <t>Heat {0}/{1}</t>
+          <t>Signal uplink</t>
         </is>
       </c>
     </row>
@@ -30204,17 +30204,17 @@
       <c r="A1655" t="inlineStr"/>
       <c r="B1655" t="inlineStr">
         <is>
-          <t>uplink.hud.overheated</t>
+          <t>codex.signal.uplink.body</t>
         </is>
       </c>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>过热：散热到 {0} 以下才开火</t>
+          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
         <is>
-          <t>Overheated: fires again below {0}</t>
+          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
         </is>
       </c>
     </row>
@@ -30222,17 +30222,17 @@
       <c r="A1656" t="inlineStr"/>
       <c r="B1656" t="inlineStr">
         <is>
-          <t>uplink.hud.heat_tip</t>
+          <t>codex.signal.uplink.hint</t>
         </is>
       </c>
       <c r="C1656" t="inlineStr">
         <is>
-          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
+          <t>第一次接入一台机器，或打开信号核时解锁</t>
         </is>
       </c>
       <c r="D1656" t="inlineStr">
         <is>
-          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
+          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
         </is>
       </c>
     </row>
@@ -30240,17 +30240,17 @@
       <c r="A1657" t="inlineStr"/>
       <c r="B1657" t="inlineStr">
         <is>
-          <t>uplink.hud.battery</t>
+          <t>codex.signal.uplink_port.title</t>
         </is>
       </c>
       <c r="C1657" t="inlineStr">
         <is>
-          <t>电池 {0}%</t>
+          <t>接入口</t>
         </is>
       </c>
       <c r="D1657" t="inlineStr">
         <is>
-          <t>Battery {0}%</t>
+          <t>Uplink port</t>
         </is>
       </c>
     </row>
@@ -30258,17 +30258,17 @@
       <c r="A1658" t="inlineStr"/>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>uplink.hud.battery_tip</t>
+          <t>codex.signal.uplink_port.body</t>
         </is>
       </c>
       <c r="C1658" t="inlineStr">
         <is>
-          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
+          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
         </is>
       </c>
       <c r="D1658" t="inlineStr">
         <is>
-          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
+          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
         </is>
       </c>
     </row>
@@ -30276,17 +30276,17 @@
       <c r="A1659" t="inlineStr"/>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>uplink.hud.health</t>
+          <t>codex.signal.uplink_port.hint</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}</t>
+          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
         </is>
       </c>
       <c r="D1659" t="inlineStr">
         <is>
-          <t>Durability {0}/{1}</t>
+          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
         </is>
       </c>
     </row>
@@ -30294,17 +30294,17 @@
       <c r="A1660" t="inlineStr"/>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>uplink.hud.injury_none</t>
+          <t>codex.signal.core_firmware.title</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>伤势：无</t>
+          <t>核心固件</t>
         </is>
       </c>
       <c r="D1660" t="inlineStr">
         <is>
-          <t>Injuries: none</t>
+          <t>Core firmware</t>
         </is>
       </c>
     </row>
@@ -30312,17 +30312,17 @@
       <c r="A1661" t="inlineStr"/>
       <c r="B1661" t="inlineStr">
         <is>
-          <t>uplink.hud.injury</t>
+          <t>codex.signal.core_firmware.body</t>
         </is>
       </c>
       <c r="C1661" t="inlineStr">
         <is>
-          <t>伤势：{0}</t>
+          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
         </is>
       </c>
       <c r="D1661" t="inlineStr">
         <is>
-          <t>Injuries: {0}</t>
+          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
         </is>
       </c>
     </row>
@@ -30330,17 +30330,17 @@
       <c r="A1662" t="inlineStr"/>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>uplink.hud.health_tip</t>
+          <t>codex.signal.core_firmware.hint</t>
         </is>
       </c>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
+          <t>第一次打开信号核时解锁</t>
         </is>
       </c>
       <c r="D1662" t="inlineStr">
         <is>
-          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
+          <t>Unlocks the first time you open the Signal Core</t>
         </is>
       </c>
     </row>
@@ -30348,17 +30348,17 @@
       <c r="A1663" t="inlineStr"/>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>uplink.hud.link</t>
+          <t>codex.signal.safe_mode.title</t>
         </is>
       </c>
       <c r="C1663" t="inlineStr">
         <is>
-          <t>链路 {0}% · {1}</t>
+          <t>安全模式</t>
         </is>
       </c>
       <c r="D1663" t="inlineStr">
         <is>
-          <t>Link {0}% · {1}</t>
+          <t>Safe mode</t>
         </is>
       </c>
     </row>
@@ -30366,17 +30366,17 @@
       <c r="A1664" t="inlineStr"/>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>uplink.hud.link.strong</t>
+          <t>codex.signal.safe_mode.body</t>
         </is>
       </c>
       <c r="C1664" t="inlineStr">
         <is>
-          <t>强</t>
+          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
         </is>
       </c>
       <c r="D1664" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
         </is>
       </c>
     </row>
@@ -30384,17 +30384,17 @@
       <c r="A1665" t="inlineStr"/>
       <c r="B1665" t="inlineStr">
         <is>
-          <t>uplink.hud.link.medium</t>
+          <t>codex.signal.safe_mode.hint</t>
         </is>
       </c>
       <c r="C1665" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
         </is>
       </c>
       <c r="D1665" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
         </is>
       </c>
     </row>
@@ -30402,17 +30402,17 @@
       <c r="A1666" t="inlineStr"/>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>uplink.hud.link.weak</t>
+          <t>codex.signal.raw.title</t>
         </is>
       </c>
       <c r="C1666" t="inlineStr">
         <is>
-          <t>弱</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1666" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>Running raw</t>
         </is>
       </c>
     </row>
@@ -30420,17 +30420,17 @@
       <c r="A1667" t="inlineStr"/>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>uplink.hud.link.edge</t>
+          <t>codex.signal.raw.body</t>
         </is>
       </c>
       <c r="C1667" t="inlineStr">
         <is>
-          <t>边缘 · 还剩 {0} 格</t>
+          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
         </is>
       </c>
       <c r="D1667" t="inlineStr">
         <is>
-          <t>edge · {0} cells left</t>
+          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
         </is>
       </c>
     </row>
@@ -30438,17 +30438,17 @@
       <c r="A1668" t="inlineStr"/>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>uplink.hud.link.unbounded</t>
+          <t>codex.signal.raw.hint</t>
         </is>
       </c>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>链路 满 · 此地不受覆盖限制</t>
+          <t>第一次带回加密固件时解锁</t>
         </is>
       </c>
       <c r="D1668" t="inlineStr">
         <is>
-          <t>Link full · no coverage limit here</t>
+          <t>Unlocks the first time you bring back encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -30456,17 +30456,17 @@
       <c r="A1669" t="inlineStr"/>
       <c r="B1669" t="inlineStr">
         <is>
-          <t>uplink.hud.link.grace</t>
+          <t>codex.signal.exposure.title</t>
         </is>
       </c>
       <c r="C1669" t="inlineStr">
         <is>
-          <t>链路中断（{0}）：{1} 秒内恢复</t>
+          <t>信号暴露</t>
         </is>
       </c>
       <c r="D1669" t="inlineStr">
         <is>
-          <t>Link lost ({0}): recover within {1}s</t>
+          <t>Signal exposure</t>
         </is>
       </c>
     </row>
@@ -30474,17 +30474,17 @@
       <c r="A1670" t="inlineStr"/>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>uplink.hud.link_tip</t>
+          <t>codex.signal.exposure.body</t>
         </is>
       </c>
       <c r="C1670" t="inlineStr">
         <is>
-          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
+          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
         </is>
       </c>
       <c r="D1670" t="inlineStr">
         <is>
-          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
+          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
         </is>
       </c>
     </row>
@@ -30492,17 +30492,17 @@
       <c r="A1671" t="inlineStr"/>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure</t>
+          <t>codex.signal.exposure.hint</t>
         </is>
       </c>
       <c r="C1671" t="inlineStr">
         <is>
-          <t>暴露 {0}</t>
+          <t>第一次打开暴露面板或带回加密固件时解锁</t>
         </is>
       </c>
       <c r="D1671" t="inlineStr">
         <is>
-          <t>Exposure {0}</t>
+          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -30510,17 +30510,17 @@
       <c r="A1672" t="inlineStr"/>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure_tip</t>
+          <t>codex.signal.coverage.title</t>
         </is>
       </c>
       <c r="C1672" t="inlineStr">
         <is>
-          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
+          <t>信号覆盖网络</t>
         </is>
       </c>
       <c r="D1672" t="inlineStr">
         <is>
-          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
+          <t>Signal coverage network</t>
         </is>
       </c>
     </row>
@@ -30528,17 +30528,17 @@
       <c r="A1673" t="inlineStr"/>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>uplink.hud.morph</t>
+          <t>codex.signal.coverage.body</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
         </is>
       </c>
       <c r="D1673" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
         </is>
       </c>
     </row>
@@ -30546,17 +30546,17 @@
       <c r="A1674" t="inlineStr"/>
       <c r="B1674" t="inlineStr">
         <is>
-          <t>uplink.hud.morph_source</t>
+          <t>codex.signal.coverage.hint</t>
         </is>
       </c>
       <c r="C1674" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
         </is>
       </c>
       <c r="D1674" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
         </is>
       </c>
     </row>
@@ -30564,17 +30564,17 @@
       <c r="A1675" t="inlineStr"/>
       <c r="B1675" t="inlineStr">
         <is>
-          <t>uplink.hud.no_port</t>
+          <t>codex.signal.far_jump.title</t>
         </is>
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
+          <t>远距离跳转</t>
         </is>
       </c>
       <c r="D1675" t="inlineStr">
         <is>
-          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+          <t>Long-range jump</t>
         </is>
       </c>
     </row>
@@ -30582,17 +30582,17 @@
       <c r="A1676" t="inlineStr"/>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>uplink.hud.core_empty</t>
+          <t>codex.signal.far_jump.body</t>
         </is>
       </c>
       <c r="C1676" t="inlineStr">
         <is>
-          <t>信号核没有固件（按 {0} 打开信号核）</t>
+          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
         </is>
       </c>
       <c r="D1676" t="inlineStr">
         <is>
-          <t>The Signal Core is empty (press {0} to open it)</t>
+          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
         </is>
       </c>
     </row>
@@ -30600,17 +30600,17 @@
       <c r="A1677" t="inlineStr"/>
       <c r="B1677" t="inlineStr">
         <is>
-          <t>uplink.hud.experience</t>
+          <t>codex.signal.far_jump.hint</t>
         </is>
       </c>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>第一次远距离跳转时解锁</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>Unlocks the first time you make a long-range jump</t>
         </is>
       </c>
     </row>
@@ -30618,17 +30618,17 @@
       <c r="A1678" t="inlineStr"/>
       <c r="B1678" t="inlineStr">
         <is>
-          <t>uplink.hud.keys</t>
+          <t>codex.signal.relay.title</t>
         </is>
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
+          <t>信号中继</t>
         </is>
       </c>
       <c r="D1678" t="inlineStr">
         <is>
-          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
+          <t>Signal relays</t>
         </is>
       </c>
     </row>
@@ -30636,17 +30636,17 @@
       <c r="A1679" t="inlineStr"/>
       <c r="B1679" t="inlineStr">
         <is>
-          <t>morph.state.none</t>
+          <t>codex.signal.relay.body</t>
         </is>
       </c>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>常态</t>
+          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
         </is>
       </c>
       <c r="D1679" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
         </is>
       </c>
     </row>
@@ -30654,17 +30654,17 @@
       <c r="A1680" t="inlineStr"/>
       <c r="B1680" t="inlineStr">
         <is>
-          <t>morph.state.limiter</t>
+          <t>codex.signal.relay.hint</t>
         </is>
       </c>
       <c r="C1680" t="inlineStr">
         <is>
-          <t>形变态</t>
+          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
         </is>
       </c>
       <c r="D1680" t="inlineStr">
         <is>
-          <t>morph state</t>
+          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
         </is>
       </c>
     </row>
@@ -30672,17 +30672,17 @@
       <c r="A1681" t="inlineStr"/>
       <c r="B1681" t="inlineStr">
         <is>
-          <t>morph.state.fluid</t>
+          <t>codex.firmware.morph.title</t>
         </is>
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>喷口态</t>
+          <t>机身形变</t>
         </is>
       </c>
       <c r="D1681" t="inlineStr">
         <is>
-          <t>vent state</t>
+          <t>Machine morph</t>
         </is>
       </c>
     </row>
@@ -30690,17 +30690,17 @@
       <c r="A1682" t="inlineStr"/>
       <c r="B1682" t="inlineStr">
         <is>
-          <t>morph.state.em</t>
+          <t>codex.firmware.morph.body</t>
         </is>
       </c>
       <c r="C1682" t="inlineStr">
         <is>
-          <t>线圈态</t>
+          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
         </is>
       </c>
       <c r="D1682" t="inlineStr">
         <is>
-          <t>coil state</t>
+          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
         </is>
       </c>
     </row>
@@ -30708,17 +30708,17 @@
       <c r="A1683" t="inlineStr"/>
       <c r="B1683" t="inlineStr">
         <is>
-          <t>morph.state.join</t>
+          <t>codex.firmware.morph.hint</t>
         </is>
       </c>
       <c r="C1683" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>第一次看到机身形变时解锁</t>
         </is>
       </c>
       <c r="D1683" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>Unlocks the first time you see a machine morph</t>
         </is>
       </c>
     </row>
@@ -30726,17 +30726,17 @@
       <c r="A1684" t="inlineStr"/>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>signal.list.port_tag</t>
+          <t>codex.panel.title</t>
         </is>
       </c>
       <c r="C1684" t="inlineStr">
         <is>
-          <t>◇口</t>
+          <t>图鉴 · 系统说明</t>
         </is>
       </c>
       <c r="D1684" t="inlineStr">
         <is>
-          <t>◇PORT</t>
+          <t>Codex · Systems</t>
         </is>
       </c>
     </row>
@@ -30744,17 +30744,17 @@
       <c r="A1685" t="inlineStr"/>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>signal.list.overheat_tag</t>
+          <t>codex.panel.close</t>
         </is>
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>过热</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -30762,17 +30762,17 @@
       <c r="A1686" t="inlineStr"/>
       <c r="B1686" t="inlineStr">
         <is>
-          <t>signal.list.port_line</t>
+          <t>codex.panel.list_title</t>
         </is>
       </c>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
+          <t>条目 {0}/{1}</t>
         </is>
       </c>
       <c r="D1686" t="inlineStr">
         <is>
-          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
+          <t>Entries {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -30780,17 +30780,17 @@
       <c r="A1687" t="inlineStr"/>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>signal.list.no_port_line</t>
+          <t>codex.panel.related</t>
         </is>
       </c>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>没有接入口：接入后只能驾驶，不插入固件</t>
+          <t>相关条目</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
         <is>
-          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
+          <t>Related</t>
         </is>
       </c>
     </row>
@@ -30798,17 +30798,17 @@
       <c r="A1688" t="inlineStr"/>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>signal.list.overheat_line</t>
+          <t>codex.panel.locked_title</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1688" t="inlineStr">
         <is>
-          <t>Overheated (heat {0}): it fires again once below {1}</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -30816,17 +30816,17 @@
       <c r="A1689" t="inlineStr"/>
       <c r="B1689" t="inlineStr">
         <is>
-          <t>signal.list.morph_line</t>
+          <t>codex.panel.locked_body</t>
         </is>
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>尚未接触。{0}</t>
         </is>
       </c>
       <c r="D1689" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Not encountered yet. {0}</t>
         </is>
       </c>
     </row>
@@ -30834,17 +30834,17 @@
       <c r="A1690" t="inlineStr"/>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>signal.list.experience_line</t>
+          <t>codex.panel.none_selected</t>
         </is>
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>在左侧选一个条目</t>
         </is>
       </c>
       <c r="D1690" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>Pick an entry on the left</t>
         </is>
       </c>
     </row>
@@ -30852,17 +30852,17 @@
       <c r="A1691" t="inlineStr"/>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>signal.port_badge.tip</t>
+          <t>codex.panel.footer</t>
         </is>
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>带接入口的机器</t>
+          <t>固件、反应、敌人等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
         <is>
-          <t>Machine with an uplink port</t>
+          <t>Firmware, reaction and enemy tabs arrive in a later version; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -30870,17 +30870,17 @@
       <c r="A1692" t="inlineStr"/>
       <c r="B1692" t="inlineStr">
         <is>
-          <t>machine.exp.produced</t>
+          <t>codex.panel.error</t>
         </is>
       </c>
       <c r="C1692" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
         </is>
       </c>
       <c r="D1692" t="inlineStr">
         <is>
-          <t>Produced</t>
+          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
         </is>
       </c>
     </row>
@@ -30888,17 +30888,17 @@
       <c r="A1693" t="inlineStr"/>
       <c r="B1693" t="inlineStr">
         <is>
-          <t>machine.exp.first_job</t>
+          <t>codex.help.tip_title</t>
         </is>
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>首次工作</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1693" t="inlineStr">
         <is>
-          <t>First job</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -30906,17 +30906,17 @@
       <c r="A1694" t="inlineStr"/>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>machine.exp.controlled</t>
+          <t>codex.help.tip</t>
         </is>
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>首次与信号同行</t>
+          <t>打开图鉴条目：{0}</t>
         </is>
       </c>
       <c r="D1694" t="inlineStr">
         <is>
-          <t>First time with the signal</t>
+          <t>Open the codex entry: {0}</t>
         </is>
       </c>
     </row>
@@ -30924,17 +30924,17 @@
       <c r="A1695" t="inlineStr"/>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>machine.exp.expedition</t>
+          <t>uplink.hud.title</t>
         </is>
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>远征</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
     </row>
@@ -30942,17 +30942,17 @@
       <c r="A1696" t="inlineStr"/>
       <c r="B1696" t="inlineStr">
         <is>
-          <t>machine.exp.severely_injured</t>
+          <t>uplink.hud.help_button</t>
         </is>
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>重伤</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
         <is>
-          <t>Severely injured</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -30960,17 +30960,17 @@
       <c r="A1697" t="inlineStr"/>
       <c r="B1697" t="inlineStr">
         <is>
-          <t>machine.exp.elite_kill</t>
+          <t>uplink.hud.help_tip_title</t>
         </is>
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>精英击破</t>
+          <t>接入 HUD</t>
         </is>
       </c>
       <c r="D1697" t="inlineStr">
         <is>
-          <t>Elite kill</t>
+          <t>Uplink HUD</t>
         </is>
       </c>
     </row>
@@ -30978,17 +30978,17 @@
       <c r="A1698" t="inlineStr"/>
       <c r="B1698" t="inlineStr">
         <is>
-          <t>machine.exp.boss_participation</t>
+          <t>uplink.hud.help_tip</t>
         </is>
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>首领战</t>
+          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
         <is>
-          <t>Boss fight</t>
+          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
         </is>
       </c>
     </row>
@@ -30996,17 +30996,17 @@
       <c r="A1699" t="inlineStr"/>
       <c r="B1699" t="inlineStr">
         <is>
-          <t>machine.exp.returned</t>
+          <t>uplink.hud.slot</t>
         </is>
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>返航</t>
+          <t>{0} {1}</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>{0} {1}</t>
         </is>
       </c>
     </row>
@@ -31014,17 +31014,17 @@
       <c r="A1700" t="inlineStr"/>
       <c r="B1700" t="inlineStr">
         <is>
-          <t>machine.exp.sep</t>
+          <t>uplink.hud.state.active</t>
         </is>
       </c>
       <c r="C1700" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>生效</t>
         </is>
       </c>
       <c r="D1700" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -31032,17 +31032,17 @@
       <c r="A1701" t="inlineStr"/>
       <c r="B1701" t="inlineStr">
         <is>
-          <t>machine.injury.combat</t>
+          <t>uplink.hud.state.cooling</t>
         </is>
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>战斗损伤（HP {0}/{1}）</t>
+          <t>冷却 {0} 秒</t>
         </is>
       </c>
       <c r="D1701" t="inlineStr">
         <is>
-          <t>Combat damage (HP {0}/{1})</t>
+          <t>cooling {0}s</t>
         </is>
       </c>
     </row>
@@ -31050,17 +31050,17 @@
       <c r="A1702" t="inlineStr"/>
       <c r="B1702" t="inlineStr">
         <is>
-          <t>machine.exp.none</t>
+          <t>uplink.hud.state.raw</t>
         </is>
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>无记录经历</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1702" t="inlineStr">
         <is>
-          <t>No recorded experience</t>
+          <t>raw</t>
         </is>
       </c>
     </row>
@@ -31068,17 +31068,17 @@
       <c r="A1703" t="inlineStr"/>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>machine.exp.signal</t>
+          <t>uplink.hud.state.not_inserted</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次，累计 {1}</t>
+          <t>未插入：{0}</t>
         </is>
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>With the signal {0} times, {1} in total</t>
+          <t>not inserted: {0}</t>
         </is>
       </c>
     </row>
@@ -31086,17 +31086,17 @@
       <c r="A1704" t="inlineStr"/>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>machine.exp.signal_none</t>
+          <t>uplink.hud.state.ineffective</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>尚未与信号同行</t>
+          <t>不生效：{0}</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
         <is>
-          <t>Never carried the signal</t>
+          <t>no effect: {0}</t>
         </is>
       </c>
     </row>
@@ -31104,17 +31104,17 @@
       <c r="A1705" t="inlineStr"/>
       <c r="B1705" t="inlineStr">
         <is>
-          <t>machine.status.dead</t>
+          <t>uplink.hud.state.empty</t>
         </is>
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录）</t>
+          <t>空槽</t>
         </is>
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record)</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -31122,17 +31122,17 @@
       <c r="A1706" t="inlineStr"/>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>machine.status.in_factory</t>
+          <t>uplink.hud.state.locked</t>
         </is>
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>厂内待驶出</t>
+          <t>未解锁</t>
         </is>
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>Waiting in the factory</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -31140,17 +31140,17 @@
       <c r="A1707" t="inlineStr"/>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>machine.status.uplinked</t>
+          <t>uplink.hud.reason.over_quota</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>接入中</t>
+          <t>超出接入口配额 {0} 个</t>
         </is>
       </c>
       <c r="D1707" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>over the port quota of {0}</t>
         </is>
       </c>
     </row>
@@ -31158,17 +31158,17 @@
       <c r="A1708" t="inlineStr"/>
       <c r="B1708" t="inlineStr">
         <is>
-          <t>machine.status.idle</t>
+          <t>uplink.hud.reason.path_limit</t>
         </is>
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>空闲</t>
+          <t>路径会超过上限 {0} 条</t>
         </is>
       </c>
       <c r="D1708" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>paths would exceed {0}</t>
         </is>
       </c>
     </row>
@@ -31176,17 +31176,17 @@
       <c r="A1709" t="inlineStr"/>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>machine.status.working</t>
+          <t>uplink.hud.reason.unknown</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>不是已知的固件</t>
         </is>
       </c>
       <c r="D1709" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>unknown firmware</t>
         </is>
       </c>
     </row>
@@ -31194,17 +31194,17 @@
       <c r="A1710" t="inlineStr"/>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>machine.detail.none</t>
+          <t>uplink.hud.reason.no_uplink</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>这台机器没有接入口</t>
         </is>
       </c>
       <c r="D1710" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>this machine has no uplink port</t>
         </is>
       </c>
     </row>
@@ -31212,17 +31212,17 @@
       <c r="A1711" t="inlineStr"/>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>machine.detail.injury_none</t>
+          <t>uplink.hud.reason.off_path</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>无记录</t>
+          <t>接入口不在导线上</t>
         </is>
       </c>
       <c r="D1711" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>the uplink port is not on a wire</t>
         </is>
       </c>
     </row>
@@ -31230,17 +31230,17 @@
       <c r="A1712" t="inlineStr"/>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>machine.detail.port_yes</t>
+          <t>uplink.hud.slot_tip</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>{0} 号槽：{1}</t>
         </is>
       </c>
       <c r="D1712" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Slot {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -31248,17 +31248,17 @@
       <c r="A1713" t="inlineStr"/>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>machine.detail.port_no</t>
+          <t>uplink.hud.heat</t>
         </is>
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>没有</t>
+          <t>热量 {0}/{1}</t>
         </is>
       </c>
       <c r="D1713" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Heat {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31266,17 +31266,17 @@
       <c r="A1714" t="inlineStr"/>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>machine.detail.line_id</t>
+          <t>uplink.hud.overheated</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
         <is>
-          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+          <t>过热：散热到 {0} 以下才开火</t>
         </is>
       </c>
       <c r="D1714" t="inlineStr">
         <is>
-          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+          <t>Overheated: fires again below {0}</t>
         </is>
       </c>
     </row>
@@ -31284,17 +31284,17 @@
       <c r="A1715" t="inlineStr"/>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>machine.detail.line_vitals</t>
+          <t>uplink.hud.heat_tip</t>
         </is>
       </c>
       <c r="C1715" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
         </is>
       </c>
       <c r="D1715" t="inlineStr">
         <is>
-          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
         </is>
       </c>
     </row>
@@ -31302,17 +31302,17 @@
       <c r="A1716" t="inlineStr"/>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>machine.detail.line_exp</t>
+          <t>uplink.hud.battery</t>
         </is>
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>经历：{0}</t>
+          <t>电池 {0}%</t>
         </is>
       </c>
       <c r="D1716" t="inlineStr">
         <is>
-          <t>Experience: {0}</t>
+          <t>Battery {0}%</t>
         </is>
       </c>
     </row>
@@ -31320,17 +31320,17 @@
       <c r="A1717" t="inlineStr"/>
       <c r="B1717" t="inlineStr">
         <is>
-          <t>machine.detail.line_signal</t>
+          <t>uplink.hud.battery_tip</t>
         </is>
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
         </is>
       </c>
       <c r="D1717" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
         </is>
       </c>
     </row>
@@ -31338,17 +31338,17 @@
       <c r="A1718" t="inlineStr"/>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>machine.detail.line_stats</t>
+          <t>uplink.hud.health</t>
         </is>
       </c>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+          <t>耐久 {0}/{1}</t>
         </is>
       </c>
       <c r="D1718" t="inlineStr">
         <is>
-          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+          <t>Durability {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31356,17 +31356,17 @@
       <c r="A1719" t="inlineStr"/>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>machine.detail.line_morph</t>
+          <t>uplink.hud.injury_none</t>
         </is>
       </c>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>伤势：无</t>
         </is>
       </c>
       <c r="D1719" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Injuries: none</t>
         </is>
       </c>
     </row>
@@ -31374,17 +31374,17 @@
       <c r="A1720" t="inlineStr"/>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>victory.summary</t>
+          <t>uplink.hud.injury</t>
         </is>
       </c>
       <c r="C1720" t="inlineStr">
         <is>
-          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+          <t>伤势：{0}</t>
         </is>
       </c>
       <c r="D1720" t="inlineStr">
         <is>
-          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+          <t>Injuries: {0}</t>
         </is>
       </c>
     </row>
@@ -31392,17 +31392,17 @@
       <c r="A1721" t="inlineStr"/>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>victory.row.number</t>
+          <t>uplink.hud.health_tip</t>
         </is>
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>#{0}（{1}）</t>
+          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
         <is>
-          <t>#{0} ({1})</t>
+          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
         </is>
       </c>
     </row>
@@ -31410,17 +31410,17 @@
       <c r="A1722" t="inlineStr"/>
       <c r="B1722" t="inlineStr">
         <is>
-          <t>victory.row.alive</t>
+          <t>uplink.hud.link</t>
         </is>
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>幸存</t>
+          <t>链路 {0}% · {1}</t>
         </is>
       </c>
       <c r="D1722" t="inlineStr">
         <is>
-          <t>survived</t>
+          <t>Link {0}% · {1}</t>
         </is>
       </c>
     </row>
@@ -31428,17 +31428,17 @@
       <c r="A1723" t="inlineStr"/>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>victory.row.dead</t>
+          <t>uplink.hud.link.strong</t>
         </is>
       </c>
       <c r="C1723" t="inlineStr">
         <is>
-          <t>阵亡</t>
+          <t>强</t>
         </is>
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>destroyed</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -31446,17 +31446,17 @@
       <c r="A1724" t="inlineStr"/>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_alive</t>
+          <t>uplink.hud.link.medium</t>
         </is>
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>幸存，将随撤离返回家园；{0}</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>Survived and returns home with the evacuation; {0}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -31464,17 +31464,17 @@
       <c r="A1725" t="inlineStr"/>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_dead</t>
+          <t>uplink.hud.link.weak</t>
         </is>
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+          <t>弱</t>
         </is>
       </c>
       <c r="D1725" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+          <t>weak</t>
         </is>
       </c>
     </row>
@@ -31482,17 +31482,17 @@
       <c r="A1726" t="inlineStr"/>
       <c r="B1726" t="inlineStr">
         <is>
-          <t>factory.reason.uplinked</t>
+          <t>uplink.hud.link.edge</t>
         </is>
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>这台机器正被你接入，先退出接入</t>
+          <t>边缘 · 还剩 {0} 格</t>
         </is>
       </c>
       <c r="D1726" t="inlineStr">
         <is>
-          <t>You are uplinked into this machine: leave the uplink first</t>
+          <t>edge · {0} cells left</t>
         </is>
       </c>
     </row>
@@ -31500,17 +31500,17 @@
       <c r="A1727" t="inlineStr"/>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>signal.cmd.uplinked</t>
+          <t>uplink.hud.link.unbounded</t>
         </is>
       </c>
       <c r="C1727" t="inlineStr">
         <is>
-          <t>接入：{0}</t>
+          <t>链路 满 · 此地不受覆盖限制</t>
         </is>
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>Uplinked: {0}</t>
+          <t>Link full · no coverage limit here</t>
         </is>
       </c>
     </row>
@@ -31518,17 +31518,17 @@
       <c r="A1728" t="inlineStr"/>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>signal.cmd.reconnecting</t>
+          <t>uplink.hud.link.grace</t>
         </is>
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>重连中：{0}</t>
+          <t>链路中断（{0}）：{1} 秒内恢复</t>
         </is>
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>Reconnecting: {0}</t>
+          <t>Link lost ({0}): recover within {1}s</t>
         </is>
       </c>
     </row>
@@ -31536,17 +31536,17 @@
       <c r="A1729" t="inlineStr"/>
       <c r="B1729" t="inlineStr">
         <is>
-          <t>signal.cmd.strategy</t>
+          <t>uplink.hud.link_tip</t>
         </is>
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>战略视角</t>
+          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
         </is>
       </c>
       <c r="D1729" t="inlineStr">
         <is>
-          <t>Strategy view</t>
+          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
         </is>
       </c>
     </row>
@@ -31554,17 +31554,17 @@
       <c r="A1730" t="inlineStr"/>
       <c r="B1730" t="inlineStr">
         <is>
-          <t>region.control.fail.not_found</t>
+          <t>uplink.hud.exposure</t>
         </is>
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>没有可以接入的目标。</t>
+          <t>暴露 {0}</t>
         </is>
       </c>
       <c r="D1730" t="inlineStr">
         <is>
-          <t>There is nothing to uplink into.</t>
+          <t>Exposure {0}</t>
         </is>
       </c>
     </row>
@@ -31572,17 +31572,17 @@
       <c r="A1731" t="inlineStr"/>
       <c r="B1731" t="inlineStr">
         <is>
-          <t>region.control.fail.not_friendly</t>
+          <t>uplink.hud.exposure_tip</t>
         </is>
       </c>
       <c r="C1731" t="inlineStr">
         <is>
-          <t>目标不属于本地点。</t>
+          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
         </is>
       </c>
       <c r="D1731" t="inlineStr">
         <is>
-          <t>The target does not belong to this site.</t>
+          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
         </is>
       </c>
     </row>
@@ -31590,17 +31590,17 @@
       <c r="A1732" t="inlineStr"/>
       <c r="B1732" t="inlineStr">
         <is>
-          <t>region.control.fail.dead</t>
+          <t>uplink.hud.morph</t>
         </is>
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>目标已阵亡。</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1732" t="inlineStr">
         <is>
-          <t>The target is destroyed.</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -31608,17 +31608,17 @@
       <c r="A1733" t="inlineStr"/>
       <c r="B1733" t="inlineStr">
         <is>
-          <t>region.control.fail.out_of_range</t>
+          <t>uplink.hud.morph_source</t>
         </is>
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>目标当前不在场。</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D1733" t="inlineStr">
         <is>
-          <t>The target is not here right now.</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -31626,17 +31626,17 @@
       <c r="A1734" t="inlineStr"/>
       <c r="B1734" t="inlineStr">
         <is>
-          <t>region.control.fail.jammed</t>
+          <t>uplink.hud.no_port</t>
         </is>
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>信号被干扰，接入失败。</t>
+          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
         </is>
       </c>
       <c r="D1734" t="inlineStr">
         <is>
-          <t>The signal is jammed; uplink failed.</t>
+          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -31644,17 +31644,17 @@
       <c r="A1735" t="inlineStr"/>
       <c r="B1735" t="inlineStr">
         <is>
-          <t>region.control.fail.transition</t>
+          <t>uplink.hud.core_empty</t>
         </is>
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>镜头切换中，请稍候。</t>
+          <t>信号核没有固件（按 {0} 打开信号核）</t>
         </is>
       </c>
       <c r="D1735" t="inlineStr">
         <is>
-          <t>The camera is moving; please wait.</t>
+          <t>The Signal Core is empty (press {0} to open it)</t>
         </is>
       </c>
     </row>
@@ -31662,17 +31662,17 @@
       <c r="A1736" t="inlineStr"/>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>region.control.fail.modal</t>
+          <t>uplink.hud.experience</t>
         </is>
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>请先关闭当前面板。</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1736" t="inlineStr">
         <is>
-          <t>Close the current panel first.</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -31680,17 +31680,17 @@
       <c r="A1737" t="inlineStr"/>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>region.control.fail.already</t>
+          <t>uplink.hud.keys</t>
         </is>
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>已经接入这台机器。</t>
+          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
         </is>
       </c>
       <c r="D1737" t="inlineStr">
         <is>
-          <t>You are already uplinked into this machine.</t>
+          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
         </is>
       </c>
     </row>
@@ -31698,17 +31698,17 @@
       <c r="A1738" t="inlineStr"/>
       <c r="B1738" t="inlineStr">
         <is>
-          <t>region.control.fail.ineligible</t>
+          <t>morph.state.none</t>
         </is>
       </c>
       <c r="C1738" t="inlineStr">
         <is>
-          <t>目标暂时不能接入。</t>
+          <t>常态</t>
         </is>
       </c>
       <c r="D1738" t="inlineStr">
         <is>
-          <t>The target cannot be uplinked right now.</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -31716,17 +31716,17 @@
       <c r="A1739" t="inlineStr"/>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>region.control.fail.other</t>
+          <t>morph.state.limiter</t>
         </is>
       </c>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>接入失败。</t>
+          <t>形变态</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
         <is>
-          <t>Uplink failed.</t>
+          <t>morph state</t>
         </is>
       </c>
     </row>
@@ -31734,17 +31734,17 @@
       <c r="A1740" t="inlineStr"/>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink</t>
+          <t>morph.state.fluid</t>
         </is>
       </c>
       <c r="C1740" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>喷口态</t>
         </is>
       </c>
       <c r="D1740" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>vent state</t>
         </is>
       </c>
     </row>
@@ -31752,17 +31752,17 @@
       <c r="A1741" t="inlineStr"/>
       <c r="B1741" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink</t>
+          <t>morph.state.em</t>
         </is>
       </c>
       <c r="C1741" t="inlineStr">
         <is>
-          <t>已接入</t>
+          <t>线圈态</t>
         </is>
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>coil state</t>
         </is>
       </c>
     </row>
@@ -31770,17 +31770,17 @@
       <c r="A1742" t="inlineStr"/>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink_leave</t>
+          <t>morph.state.join</t>
         </is>
       </c>
       <c r="C1742" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
       <c r="D1742" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
     </row>
@@ -31788,17 +31788,17 @@
       <c r="A1743" t="inlineStr"/>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink_leave</t>
+          <t>signal.list.port_tag</t>
         </is>
       </c>
       <c r="C1743" t="inlineStr">
         <is>
-          <t>信号离开机器</t>
+          <t>◇口</t>
         </is>
       </c>
       <c r="D1743" t="inlineStr">
         <is>
-          <t>The signal left the machine</t>
+          <t>◇PORT</t>
         </is>
       </c>
     </row>
@@ -31806,17 +31806,17 @@
       <c r="A1744" t="inlineStr"/>
       <c r="B1744" t="inlineStr">
         <is>
-          <t>pause.codex</t>
+          <t>signal.list.overheat_tag</t>
         </is>
       </c>
       <c r="C1744" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>过热</t>
         </is>
       </c>
       <c r="D1744" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>HOT</t>
         </is>
       </c>
     </row>
@@ -31824,17 +31824,17 @@
       <c r="A1745" t="inlineStr"/>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>pause.camera_title</t>
+          <t>signal.list.port_line</t>
         </is>
       </c>
       <c r="C1745" t="inlineStr">
         <is>
-          <t>接入镜头</t>
+          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
         <is>
-          <t>Uplink camera</t>
+          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
         </is>
       </c>
     </row>
@@ -31842,17 +31842,17 @@
       <c r="A1746" t="inlineStr"/>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>pause.camera_zoom</t>
+          <t>signal.list.no_port_line</t>
         </is>
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>接入时镜头距离 {0}%</t>
+          <t>没有接入口：接入后只能驾驶，不插入固件</t>
         </is>
       </c>
       <c r="D1746" t="inlineStr">
         <is>
-          <t>Uplink camera distance {0}%</t>
+          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -31860,17 +31860,17 @@
       <c r="A1747" t="inlineStr"/>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>pause.camera_follow</t>
+          <t>signal.list.overheat_line</t>
         </is>
       </c>
       <c r="C1747" t="inlineStr">
         <is>
-          <t>接入时跟随力度 {0}%</t>
+          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
         </is>
       </c>
       <c r="D1747" t="inlineStr">
         <is>
-          <t>Uplink follow strength {0}%</t>
+          <t>Overheated (heat {0}): it fires again once below {1}</t>
         </is>
       </c>
     </row>
@@ -31878,17 +31878,17 @@
       <c r="A1748" t="inlineStr"/>
       <c r="B1748" t="inlineStr">
         <is>
-          <t>pause.camera_reset</t>
+          <t>signal.list.morph_line</t>
         </is>
       </c>
       <c r="C1748" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1748" t="inlineStr">
         <is>
-          <t>Reset to default</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -31896,17 +31896,17 @@
       <c r="A1749" t="inlineStr"/>
       <c r="B1749" t="inlineStr">
         <is>
-          <t>pause.camera_zoom_tip</t>
+          <t>signal.list.experience_line</t>
         </is>
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
         <is>
-          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -31914,17 +31914,17 @@
       <c r="A1750" t="inlineStr"/>
       <c r="B1750" t="inlineStr">
         <is>
-          <t>pause.camera_follow_tip</t>
+          <t>signal.port_badge.tip</t>
         </is>
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>带接入口的机器</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>Machine with an uplink port</t>
         </is>
       </c>
     </row>
@@ -31932,17 +31932,17 @@
       <c r="A1751" t="inlineStr"/>
       <c r="B1751" t="inlineStr">
         <is>
-          <t>camera.follow.started</t>
+          <t>machine.exp.produced</t>
         </is>
       </c>
       <c r="C1751" t="inlineStr">
         <is>
-          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="D1751" t="inlineStr">
         <is>
-          <t>Camera following {0} (pan or press {1} again to stop)</t>
+          <t>Produced</t>
         </is>
       </c>
     </row>
@@ -31950,17 +31950,17 @@
       <c r="A1752" t="inlineStr"/>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>camera.follow.stopped</t>
+          <t>machine.exp.first_job</t>
         </is>
       </c>
       <c r="C1752" t="inlineStr">
         <is>
-          <t>镜头停止跟随</t>
+          <t>首次工作</t>
         </is>
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>Camera follow stopped</t>
+          <t>First job</t>
         </is>
       </c>
     </row>
@@ -31968,17 +31968,17 @@
       <c r="A1753" t="inlineStr"/>
       <c r="B1753" t="inlineStr">
         <is>
-          <t>camera.follow.nothing</t>
+          <t>machine.exp.controlled</t>
         </is>
       </c>
       <c r="C1753" t="inlineStr">
         <is>
-          <t>先选中一台机器再按 {0} 跟随</t>
+          <t>首次与信号同行</t>
         </is>
       </c>
       <c r="D1753" t="inlineStr">
         <is>
-          <t>Select a machine first, then press {0} to follow it</t>
+          <t>First time with the signal</t>
         </is>
       </c>
     </row>
@@ -31986,15 +31986,1077 @@
       <c r="A1754" t="inlineStr"/>
       <c r="B1754" t="inlineStr">
         <is>
+          <t>machine.exp.expedition</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>远征</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>Expedition</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr"/>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>machine.exp.severely_injured</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>重伤</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>Severely injured</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr"/>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>machine.exp.elite_kill</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>精英击破</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>Elite kill</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr"/>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>machine.exp.boss_participation</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>首领战</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>Boss fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr"/>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>machine.exp.returned</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>返航</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr"/>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>machine.exp.sep</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>、</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t xml:space="preserve">, </t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr"/>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>machine.injury.combat</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>战斗损伤（HP {0}/{1}）</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>Combat damage (HP {0}/{1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr"/>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>machine.exp.none</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>无记录经历</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>No recorded experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr"/>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>machine.exp.signal</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>与信号同行 {0} 次，累计 {1}</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>With the signal {0} times, {1} in total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr"/>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>machine.exp.signal_none</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>尚未与信号同行</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Never carried the signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr"/>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>machine.status.dead</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>阵亡（纪念记录）</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>Destroyed (memorial record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr"/>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>machine.status.in_factory</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>厂内待驶出</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>Waiting in the factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr"/>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>machine.status.uplinked</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>接入中</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>Uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr"/>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>machine.status.idle</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>空闲</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr"/>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>machine.status.working</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>工作中</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr"/>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>machine.detail.none</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr"/>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>machine.detail.injury_none</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>无记录</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>none recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr"/>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>machine.detail.port_yes</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr"/>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>machine.detail.port_no</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>没有</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr"/>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>machine.detail.line_id</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr"/>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>machine.detail.line_vitals</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr"/>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>machine.detail.line_exp</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>经历：{0}</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>Experience: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr"/>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>machine.detail.line_signal</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr"/>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>machine.detail.line_stats</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr"/>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>machine.detail.line_morph</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>机身：{0}</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>Body: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr"/>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>victory.summary</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr"/>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>victory.row.number</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>#{0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>#{0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr"/>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>victory.row.alive</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>幸存</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr"/>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>victory.row.dead</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>阵亡</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>destroyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr"/>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>expedition.return.row_status_alive</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>幸存，将随撤离返回家园；{0}</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>Survived and returns home with the evacuation; {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr"/>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>expedition.return.row_status_dead</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr"/>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>factory.reason.uplinked</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>这台机器正被你接入，先退出接入</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>You are uplinked into this machine: leave the uplink first</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr"/>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>signal.cmd.uplinked</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>接入：{0}</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>Uplinked: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr"/>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>signal.cmd.reconnecting</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>重连中：{0}</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>Reconnecting: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr"/>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>signal.cmd.strategy</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>战略视角</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>Strategy view</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr"/>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>region.control.fail.not_found</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>没有可以接入的目标。</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>There is nothing to uplink into.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr"/>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>region.control.fail.not_friendly</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>目标不属于本地点。</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>The target does not belong to this site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr"/>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>region.control.fail.dead</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>目标已阵亡。</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>The target is destroyed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr"/>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>region.control.fail.out_of_range</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>目标当前不在场。</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>The target is not here right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr"/>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>region.control.fail.jammed</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>信号被干扰，接入失败。</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>The signal is jammed; uplink failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr"/>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>region.control.fail.transition</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>镜头切换中，请稍候。</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>The camera is moving; please wait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr"/>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>region.control.fail.modal</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>请先关闭当前面板。</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>Close the current panel first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr"/>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>region.control.fail.already</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>已经接入这台机器。</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>You are already uplinked into this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr"/>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>region.control.fail.ineligible</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>目标暂时不能接入。</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>The target cannot be uplinked right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr"/>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>region.control.fail.other</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>接入失败。</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>Uplink failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr"/>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>feedback.tag.uplink</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>接入</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>Uplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr"/>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>feedback.caption.uplink</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>已接入</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>Uplinked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr"/>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>feedback.tag.uplink_leave</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr"/>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>feedback.caption.uplink_leave</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>信号离开机器</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>The signal left the machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr"/>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>pause.codex</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>图鉴</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr"/>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>pause.camera_title</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>接入镜头</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>Uplink camera</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr"/>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>pause.camera_zoom</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>接入时镜头距离 {0}%</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>Uplink camera distance {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr"/>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>pause.camera_follow</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>接入时跟随力度 {0}%</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>Uplink follow strength {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr"/>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>pause.camera_reset</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>Reset to default</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr"/>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>pause.camera_zoom_tip</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr"/>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>pause.camera_follow_tip</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr"/>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>camera.follow.started</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>Camera following {0} (pan or press {1} again to stop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr"/>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>camera.follow.stopped</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>镜头停止跟随</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>Camera follow stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr"/>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>camera.follow.nothing</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>先选中一台机器再按 {0} 跟随</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>Select a machine first, then press {0} to follow it</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr"/>
+      <c r="B1813" t="inlineStr">
+        <is>
           <t>camera.follow.group</t>
         </is>
       </c>
-      <c r="C1754" t="inlineStr">
+      <c r="C1813" t="inlineStr">
         <is>
           <t>{0} 台机器</t>
         </is>
       </c>
-      <c r="D1754" t="inlineStr">
+      <c r="D1813" t="inlineStr">
         <is>
           <t>{0} machines</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1813"/>
+  <dimension ref="A1:D1925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30726,17 +30726,17 @@
       <c r="A1684" t="inlineStr"/>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>codex.panel.title</t>
+          <t>codex.firmware.library.title</t>
         </is>
       </c>
       <c r="C1684" t="inlineStr">
         <is>
-          <t>图鉴 · 系统说明</t>
+          <t>固件库</t>
         </is>
       </c>
       <c r="D1684" t="inlineStr">
         <is>
-          <t>Codex · Systems</t>
+          <t>Firmware library</t>
         </is>
       </c>
     </row>
@@ -30744,17 +30744,17 @@
       <c r="A1685" t="inlineStr"/>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>codex.panel.close</t>
+          <t>codex.firmware.library.body</t>
         </is>
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>固件芯片是物品，存放在归还核心和仓库里：没有仓库时能放 8 枚，每座运转中的仓库再加一批格子；放满后新拿到的芯片进入待领取，腾出位置后再领取。按 {act:OpenFirmware} 或在暂停菜单里打开固件库，可以按类别、种类、协议、是否破解、兼容载体、稀有度筛选，按名称或说明搜索，排序并并排比较两条固件。详情页列出它在各载体上的读法、标签、参与的反应、获取途径和持有位置。锁定的芯片不会被批量分解；批量分解会先弹确认框，装在信号核或被合成台预留的芯片一律跳过，每枚返还少量废料，拆掉之后要重新刻印才能再得到。悬停任何固件时按 {act:OpenCodex} 可以跳到它的图鉴条目。</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Firmware chips are items stored in the Reclamation Core and in warehouses: 8 fit without a warehouse, and every operating warehouse adds more slots; when storage is full, new chips wait to be claimed until there is room. Press {act:OpenFirmware} or use the pause menu to open the library, where you can filter by category, kind, protocol, cracked state, compatible carrier and rarity, search names and descriptions, sort, and compare two firmware side by side. The detail page lists its reading on each carrier, tags, reactions, how to get it and where your copies are. Locked chips are never batch-disassembled; batch disassembly asks for confirmation first and always skips chips in the Signal Core or reserved by crafting. Each chip refunds a little scrap and must be printed again to get it back. Hover any firmware and press {act:OpenCodex} to jump to its codex entry.</t>
         </is>
       </c>
     </row>
@@ -30762,17 +30762,17 @@
       <c r="A1686" t="inlineStr"/>
       <c r="B1686" t="inlineStr">
         <is>
-          <t>codex.panel.list_title</t>
+          <t>codex.firmware.library.hint</t>
         </is>
       </c>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>条目 {0}/{1}</t>
+          <t>第一次打开固件库时解锁</t>
         </is>
       </c>
       <c r="D1686" t="inlineStr">
         <is>
-          <t>Entries {0}/{1}</t>
+          <t>Unlocks the first time you open the firmware library</t>
         </is>
       </c>
     </row>
@@ -30780,17 +30780,17 @@
       <c r="A1687" t="inlineStr"/>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>codex.panel.related</t>
+          <t>codex.panel.title</t>
         </is>
       </c>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>相关条目</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
         <is>
-          <t>Related</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -30798,17 +30798,17 @@
       <c r="A1688" t="inlineStr"/>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>codex.panel.locked_title</t>
+          <t>codex.panel.close</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1688" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -30816,17 +30816,17 @@
       <c r="A1689" t="inlineStr"/>
       <c r="B1689" t="inlineStr">
         <is>
-          <t>codex.panel.locked_body</t>
+          <t>codex.panel.list_title</t>
         </is>
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>尚未接触。{0}</t>
+          <t>条目 {0}/{1}</t>
         </is>
       </c>
       <c r="D1689" t="inlineStr">
         <is>
-          <t>Not encountered yet. {0}</t>
+          <t>Entries {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -30834,17 +30834,17 @@
       <c r="A1690" t="inlineStr"/>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>codex.panel.none_selected</t>
+          <t>codex.panel.related</t>
         </is>
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>在左侧选一个条目</t>
+          <t>相关条目</t>
         </is>
       </c>
       <c r="D1690" t="inlineStr">
         <is>
-          <t>Pick an entry on the left</t>
+          <t>Related</t>
         </is>
       </c>
     </row>
@@ -30852,17 +30852,17 @@
       <c r="A1691" t="inlineStr"/>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>codex.panel.footer</t>
+          <t>codex.panel.locked_title</t>
         </is>
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>固件、反应、敌人等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
         <is>
-          <t>Firmware, reaction and enemy tabs arrive in a later version; press {act:Cancel} to close</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -30870,17 +30870,17 @@
       <c r="A1692" t="inlineStr"/>
       <c r="B1692" t="inlineStr">
         <is>
-          <t>codex.panel.error</t>
+          <t>codex.panel.locked_body</t>
         </is>
       </c>
       <c r="C1692" t="inlineStr">
         <is>
-          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
+          <t>尚未接触。{0}</t>
         </is>
       </c>
       <c r="D1692" t="inlineStr">
         <is>
-          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
+          <t>Not encountered yet. {0}</t>
         </is>
       </c>
     </row>
@@ -30888,17 +30888,17 @@
       <c r="A1693" t="inlineStr"/>
       <c r="B1693" t="inlineStr">
         <is>
-          <t>codex.help.tip_title</t>
+          <t>codex.panel.none_selected</t>
         </is>
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>在左侧选一个条目</t>
         </is>
       </c>
       <c r="D1693" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>Pick an entry on the left</t>
         </is>
       </c>
     </row>
@@ -30906,17 +30906,17 @@
       <c r="A1694" t="inlineStr"/>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>codex.help.tip</t>
+          <t>codex.panel.footer</t>
         </is>
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>打开图鉴条目：{0}</t>
+          <t>悬停任何带图鉴链接的提示时按 {act:OpenCodex} 跳到条目；敌人、阵营等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1694" t="inlineStr">
         <is>
-          <t>Open the codex entry: {0}</t>
+          <t>Press {act:OpenCodex} while hovering a tooltip with a codex link to jump to its entry; enemy and faction tabs arrive later; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -30924,17 +30924,17 @@
       <c r="A1695" t="inlineStr"/>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>uplink.hud.title</t>
+          <t>codex.panel.error</t>
         </is>
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
         </is>
       </c>
     </row>
@@ -30942,17 +30942,17 @@
       <c r="A1696" t="inlineStr"/>
       <c r="B1696" t="inlineStr">
         <is>
-          <t>uplink.hud.help_button</t>
+          <t>codex.help.tip_title</t>
         </is>
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -30960,17 +30960,17 @@
       <c r="A1697" t="inlineStr"/>
       <c r="B1697" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip_title</t>
+          <t>codex.help.tip</t>
         </is>
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>接入 HUD</t>
+          <t>打开图鉴条目：{0}</t>
         </is>
       </c>
       <c r="D1697" t="inlineStr">
         <is>
-          <t>Uplink HUD</t>
+          <t>Open the codex entry: {0}</t>
         </is>
       </c>
     </row>
@@ -30978,17 +30978,17 @@
       <c r="A1698" t="inlineStr"/>
       <c r="B1698" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip</t>
+          <t>uplink.hud.title</t>
         </is>
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
         <is>
-          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
     </row>
@@ -30996,17 +30996,17 @@
       <c r="A1699" t="inlineStr"/>
       <c r="B1699" t="inlineStr">
         <is>
-          <t>uplink.hud.slot</t>
+          <t>uplink.hud.help_button</t>
         </is>
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -31014,17 +31014,17 @@
       <c r="A1700" t="inlineStr"/>
       <c r="B1700" t="inlineStr">
         <is>
-          <t>uplink.hud.state.active</t>
+          <t>uplink.hud.help_tip_title</t>
         </is>
       </c>
       <c r="C1700" t="inlineStr">
         <is>
-          <t>生效</t>
+          <t>接入 HUD</t>
         </is>
       </c>
       <c r="D1700" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Uplink HUD</t>
         </is>
       </c>
     </row>
@@ -31032,17 +31032,17 @@
       <c r="A1701" t="inlineStr"/>
       <c r="B1701" t="inlineStr">
         <is>
-          <t>uplink.hud.state.cooling</t>
+          <t>uplink.hud.help_tip</t>
         </is>
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>冷却 {0} 秒</t>
+          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
         </is>
       </c>
       <c r="D1701" t="inlineStr">
         <is>
-          <t>cooling {0}s</t>
+          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
         </is>
       </c>
     </row>
@@ -31050,17 +31050,17 @@
       <c r="A1702" t="inlineStr"/>
       <c r="B1702" t="inlineStr">
         <is>
-          <t>uplink.hud.state.raw</t>
+          <t>uplink.hud.slot</t>
         </is>
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>{0} {1}</t>
         </is>
       </c>
       <c r="D1702" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>{0} {1}</t>
         </is>
       </c>
     </row>
@@ -31068,17 +31068,17 @@
       <c r="A1703" t="inlineStr"/>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>uplink.hud.state.not_inserted</t>
+          <t>uplink.hud.state.active</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>未插入：{0}</t>
+          <t>生效</t>
         </is>
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>not inserted: {0}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -31086,17 +31086,17 @@
       <c r="A1704" t="inlineStr"/>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>uplink.hud.state.ineffective</t>
+          <t>uplink.hud.state.cooling</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>不生效：{0}</t>
+          <t>冷却 {0} 秒</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
         <is>
-          <t>no effect: {0}</t>
+          <t>cooling {0}s</t>
         </is>
       </c>
     </row>
@@ -31104,17 +31104,17 @@
       <c r="A1705" t="inlineStr"/>
       <c r="B1705" t="inlineStr">
         <is>
-          <t>uplink.hud.state.empty</t>
+          <t>uplink.hud.state.raw</t>
         </is>
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>空槽</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>raw</t>
         </is>
       </c>
     </row>
@@ -31122,17 +31122,17 @@
       <c r="A1706" t="inlineStr"/>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>uplink.hud.state.locked</t>
+          <t>uplink.hud.state.not_inserted</t>
         </is>
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>未解锁</t>
+          <t>未插入：{0}</t>
         </is>
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>not inserted: {0}</t>
         </is>
       </c>
     </row>
@@ -31140,17 +31140,17 @@
       <c r="A1707" t="inlineStr"/>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.over_quota</t>
+          <t>uplink.hud.state.ineffective</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>超出接入口配额 {0} 个</t>
+          <t>不生效：{0}</t>
         </is>
       </c>
       <c r="D1707" t="inlineStr">
         <is>
-          <t>over the port quota of {0}</t>
+          <t>no effect: {0}</t>
         </is>
       </c>
     </row>
@@ -31158,17 +31158,17 @@
       <c r="A1708" t="inlineStr"/>
       <c r="B1708" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.path_limit</t>
+          <t>uplink.hud.state.empty</t>
         </is>
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>路径会超过上限 {0} 条</t>
+          <t>空槽</t>
         </is>
       </c>
       <c r="D1708" t="inlineStr">
         <is>
-          <t>paths would exceed {0}</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -31176,17 +31176,17 @@
       <c r="A1709" t="inlineStr"/>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.unknown</t>
+          <t>uplink.hud.state.locked</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>不是已知的固件</t>
+          <t>未解锁</t>
         </is>
       </c>
       <c r="D1709" t="inlineStr">
         <is>
-          <t>unknown firmware</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -31194,17 +31194,17 @@
       <c r="A1710" t="inlineStr"/>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.no_uplink</t>
+          <t>uplink.hud.reason.over_quota</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>这台机器没有接入口</t>
+          <t>超出接入口配额 {0} 个</t>
         </is>
       </c>
       <c r="D1710" t="inlineStr">
         <is>
-          <t>this machine has no uplink port</t>
+          <t>over the port quota of {0}</t>
         </is>
       </c>
     </row>
@@ -31212,17 +31212,17 @@
       <c r="A1711" t="inlineStr"/>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.off_path</t>
+          <t>uplink.hud.reason.path_limit</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>接入口不在导线上</t>
+          <t>路径会超过上限 {0} 条</t>
         </is>
       </c>
       <c r="D1711" t="inlineStr">
         <is>
-          <t>the uplink port is not on a wire</t>
+          <t>paths would exceed {0}</t>
         </is>
       </c>
     </row>
@@ -31230,17 +31230,17 @@
       <c r="A1712" t="inlineStr"/>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>uplink.hud.slot_tip</t>
+          <t>uplink.hud.reason.unknown</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>{0} 号槽：{1}</t>
+          <t>不是已知的固件</t>
         </is>
       </c>
       <c r="D1712" t="inlineStr">
         <is>
-          <t>Slot {0}: {1}</t>
+          <t>unknown firmware</t>
         </is>
       </c>
     </row>
@@ -31248,17 +31248,17 @@
       <c r="A1713" t="inlineStr"/>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>uplink.hud.heat</t>
+          <t>uplink.hud.reason.no_uplink</t>
         </is>
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>热量 {0}/{1}</t>
+          <t>这台机器没有接入口</t>
         </is>
       </c>
       <c r="D1713" t="inlineStr">
         <is>
-          <t>Heat {0}/{1}</t>
+          <t>this machine has no uplink port</t>
         </is>
       </c>
     </row>
@@ -31266,17 +31266,17 @@
       <c r="A1714" t="inlineStr"/>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>uplink.hud.overheated</t>
+          <t>uplink.hud.reason.off_path</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
         <is>
-          <t>过热：散热到 {0} 以下才开火</t>
+          <t>接入口不在导线上</t>
         </is>
       </c>
       <c r="D1714" t="inlineStr">
         <is>
-          <t>Overheated: fires again below {0}</t>
+          <t>the uplink port is not on a wire</t>
         </is>
       </c>
     </row>
@@ -31284,17 +31284,17 @@
       <c r="A1715" t="inlineStr"/>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>uplink.hud.heat_tip</t>
+          <t>uplink.hud.slot_tip</t>
         </is>
       </c>
       <c r="C1715" t="inlineStr">
         <is>
-          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
+          <t>{0} 号槽：{1}</t>
         </is>
       </c>
       <c r="D1715" t="inlineStr">
         <is>
-          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
+          <t>Slot {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -31302,17 +31302,17 @@
       <c r="A1716" t="inlineStr"/>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>uplink.hud.battery</t>
+          <t>uplink.hud.heat</t>
         </is>
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>电池 {0}%</t>
+          <t>热量 {0}/{1}</t>
         </is>
       </c>
       <c r="D1716" t="inlineStr">
         <is>
-          <t>Battery {0}%</t>
+          <t>Heat {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31320,17 +31320,17 @@
       <c r="A1717" t="inlineStr"/>
       <c r="B1717" t="inlineStr">
         <is>
-          <t>uplink.hud.battery_tip</t>
+          <t>uplink.hud.overheated</t>
         </is>
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
+          <t>过热：散热到 {0} 以下才开火</t>
         </is>
       </c>
       <c r="D1717" t="inlineStr">
         <is>
-          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
+          <t>Overheated: fires again below {0}</t>
         </is>
       </c>
     </row>
@@ -31338,17 +31338,17 @@
       <c r="A1718" t="inlineStr"/>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>uplink.hud.health</t>
+          <t>uplink.hud.heat_tip</t>
         </is>
       </c>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}</t>
+          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
         </is>
       </c>
       <c r="D1718" t="inlineStr">
         <is>
-          <t>Durability {0}/{1}</t>
+          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
         </is>
       </c>
     </row>
@@ -31356,17 +31356,17 @@
       <c r="A1719" t="inlineStr"/>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>uplink.hud.injury_none</t>
+          <t>uplink.hud.battery</t>
         </is>
       </c>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>伤势：无</t>
+          <t>电池 {0}%</t>
         </is>
       </c>
       <c r="D1719" t="inlineStr">
         <is>
-          <t>Injuries: none</t>
+          <t>Battery {0}%</t>
         </is>
       </c>
     </row>
@@ -31374,17 +31374,17 @@
       <c r="A1720" t="inlineStr"/>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>uplink.hud.injury</t>
+          <t>uplink.hud.battery_tip</t>
         </is>
       </c>
       <c r="C1720" t="inlineStr">
         <is>
-          <t>伤势：{0}</t>
+          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
         </is>
       </c>
       <c r="D1720" t="inlineStr">
         <is>
-          <t>Injuries: {0}</t>
+          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
         </is>
       </c>
     </row>
@@ -31392,17 +31392,17 @@
       <c r="A1721" t="inlineStr"/>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>uplink.hud.health_tip</t>
+          <t>uplink.hud.health</t>
         </is>
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
+          <t>耐久 {0}/{1}</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
         <is>
-          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
+          <t>Durability {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31410,17 +31410,17 @@
       <c r="A1722" t="inlineStr"/>
       <c r="B1722" t="inlineStr">
         <is>
-          <t>uplink.hud.link</t>
+          <t>uplink.hud.injury_none</t>
         </is>
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>链路 {0}% · {1}</t>
+          <t>伤势：无</t>
         </is>
       </c>
       <c r="D1722" t="inlineStr">
         <is>
-          <t>Link {0}% · {1}</t>
+          <t>Injuries: none</t>
         </is>
       </c>
     </row>
@@ -31428,17 +31428,17 @@
       <c r="A1723" t="inlineStr"/>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>uplink.hud.link.strong</t>
+          <t>uplink.hud.injury</t>
         </is>
       </c>
       <c r="C1723" t="inlineStr">
         <is>
-          <t>强</t>
+          <t>伤势：{0}</t>
         </is>
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>Injuries: {0}</t>
         </is>
       </c>
     </row>
@@ -31446,17 +31446,17 @@
       <c r="A1724" t="inlineStr"/>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>uplink.hud.link.medium</t>
+          <t>uplink.hud.health_tip</t>
         </is>
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
         </is>
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
         </is>
       </c>
     </row>
@@ -31464,17 +31464,17 @@
       <c r="A1725" t="inlineStr"/>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>uplink.hud.link.weak</t>
+          <t>uplink.hud.link</t>
         </is>
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>弱</t>
+          <t>链路 {0}% · {1}</t>
         </is>
       </c>
       <c r="D1725" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>Link {0}% · {1}</t>
         </is>
       </c>
     </row>
@@ -31482,17 +31482,17 @@
       <c r="A1726" t="inlineStr"/>
       <c r="B1726" t="inlineStr">
         <is>
-          <t>uplink.hud.link.edge</t>
+          <t>uplink.hud.link.strong</t>
         </is>
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>边缘 · 还剩 {0} 格</t>
+          <t>强</t>
         </is>
       </c>
       <c r="D1726" t="inlineStr">
         <is>
-          <t>edge · {0} cells left</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -31500,17 +31500,17 @@
       <c r="A1727" t="inlineStr"/>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>uplink.hud.link.unbounded</t>
+          <t>uplink.hud.link.medium</t>
         </is>
       </c>
       <c r="C1727" t="inlineStr">
         <is>
-          <t>链路 满 · 此地不受覆盖限制</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>Link full · no coverage limit here</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -31518,17 +31518,17 @@
       <c r="A1728" t="inlineStr"/>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>uplink.hud.link.grace</t>
+          <t>uplink.hud.link.weak</t>
         </is>
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>链路中断（{0}）：{1} 秒内恢复</t>
+          <t>弱</t>
         </is>
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>Link lost ({0}): recover within {1}s</t>
+          <t>weak</t>
         </is>
       </c>
     </row>
@@ -31536,17 +31536,17 @@
       <c r="A1729" t="inlineStr"/>
       <c r="B1729" t="inlineStr">
         <is>
-          <t>uplink.hud.link_tip</t>
+          <t>uplink.hud.link.edge</t>
         </is>
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
+          <t>边缘 · 还剩 {0} 格</t>
         </is>
       </c>
       <c r="D1729" t="inlineStr">
         <is>
-          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
+          <t>edge · {0} cells left</t>
         </is>
       </c>
     </row>
@@ -31554,17 +31554,17 @@
       <c r="A1730" t="inlineStr"/>
       <c r="B1730" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure</t>
+          <t>uplink.hud.link.unbounded</t>
         </is>
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>暴露 {0}</t>
+          <t>链路 满 · 此地不受覆盖限制</t>
         </is>
       </c>
       <c r="D1730" t="inlineStr">
         <is>
-          <t>Exposure {0}</t>
+          <t>Link full · no coverage limit here</t>
         </is>
       </c>
     </row>
@@ -31572,17 +31572,17 @@
       <c r="A1731" t="inlineStr"/>
       <c r="B1731" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure_tip</t>
+          <t>uplink.hud.link.grace</t>
         </is>
       </c>
       <c r="C1731" t="inlineStr">
         <is>
-          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
+          <t>链路中断（{0}）：{1} 秒内恢复</t>
         </is>
       </c>
       <c r="D1731" t="inlineStr">
         <is>
-          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
+          <t>Link lost ({0}): recover within {1}s</t>
         </is>
       </c>
     </row>
@@ -31590,17 +31590,17 @@
       <c r="A1732" t="inlineStr"/>
       <c r="B1732" t="inlineStr">
         <is>
-          <t>uplink.hud.morph</t>
+          <t>uplink.hud.link_tip</t>
         </is>
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
         </is>
       </c>
       <c r="D1732" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
         </is>
       </c>
     </row>
@@ -31608,17 +31608,17 @@
       <c r="A1733" t="inlineStr"/>
       <c r="B1733" t="inlineStr">
         <is>
-          <t>uplink.hud.morph_source</t>
+          <t>uplink.hud.exposure</t>
         </is>
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>暴露 {0}</t>
         </is>
       </c>
       <c r="D1733" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Exposure {0}</t>
         </is>
       </c>
     </row>
@@ -31626,17 +31626,17 @@
       <c r="A1734" t="inlineStr"/>
       <c r="B1734" t="inlineStr">
         <is>
-          <t>uplink.hud.no_port</t>
+          <t>uplink.hud.exposure_tip</t>
         </is>
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
+          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
         </is>
       </c>
       <c r="D1734" t="inlineStr">
         <is>
-          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
         </is>
       </c>
     </row>
@@ -31644,17 +31644,17 @@
       <c r="A1735" t="inlineStr"/>
       <c r="B1735" t="inlineStr">
         <is>
-          <t>uplink.hud.core_empty</t>
+          <t>uplink.hud.morph</t>
         </is>
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>信号核没有固件（按 {0} 打开信号核）</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1735" t="inlineStr">
         <is>
-          <t>The Signal Core is empty (press {0} to open it)</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -31662,17 +31662,17 @@
       <c r="A1736" t="inlineStr"/>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>uplink.hud.experience</t>
+          <t>uplink.hud.morph_source</t>
         </is>
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D1736" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -31680,17 +31680,17 @@
       <c r="A1737" t="inlineStr"/>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>uplink.hud.keys</t>
+          <t>uplink.hud.no_port</t>
         </is>
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
+          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
         </is>
       </c>
       <c r="D1737" t="inlineStr">
         <is>
-          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
+          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -31698,17 +31698,17 @@
       <c r="A1738" t="inlineStr"/>
       <c r="B1738" t="inlineStr">
         <is>
-          <t>morph.state.none</t>
+          <t>uplink.hud.core_empty</t>
         </is>
       </c>
       <c r="C1738" t="inlineStr">
         <is>
-          <t>常态</t>
+          <t>信号核没有固件（按 {0} 打开信号核）</t>
         </is>
       </c>
       <c r="D1738" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>The Signal Core is empty (press {0} to open it)</t>
         </is>
       </c>
     </row>
@@ -31716,17 +31716,17 @@
       <c r="A1739" t="inlineStr"/>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>morph.state.limiter</t>
+          <t>uplink.hud.experience</t>
         </is>
       </c>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>形变态</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
         <is>
-          <t>morph state</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -31734,17 +31734,17 @@
       <c r="A1740" t="inlineStr"/>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>morph.state.fluid</t>
+          <t>uplink.hud.keys</t>
         </is>
       </c>
       <c r="C1740" t="inlineStr">
         <is>
-          <t>喷口态</t>
+          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
         </is>
       </c>
       <c r="D1740" t="inlineStr">
         <is>
-          <t>vent state</t>
+          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
         </is>
       </c>
     </row>
@@ -31752,17 +31752,17 @@
       <c r="A1741" t="inlineStr"/>
       <c r="B1741" t="inlineStr">
         <is>
-          <t>morph.state.em</t>
+          <t>morph.state.none</t>
         </is>
       </c>
       <c r="C1741" t="inlineStr">
         <is>
-          <t>线圈态</t>
+          <t>常态</t>
         </is>
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>coil state</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -31770,17 +31770,17 @@
       <c r="A1742" t="inlineStr"/>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>morph.state.join</t>
+          <t>morph.state.limiter</t>
         </is>
       </c>
       <c r="C1742" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>形变态</t>
         </is>
       </c>
       <c r="D1742" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>morph state</t>
         </is>
       </c>
     </row>
@@ -31788,17 +31788,17 @@
       <c r="A1743" t="inlineStr"/>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>signal.list.port_tag</t>
+          <t>morph.state.fluid</t>
         </is>
       </c>
       <c r="C1743" t="inlineStr">
         <is>
-          <t>◇口</t>
+          <t>喷口态</t>
         </is>
       </c>
       <c r="D1743" t="inlineStr">
         <is>
-          <t>◇PORT</t>
+          <t>vent state</t>
         </is>
       </c>
     </row>
@@ -31806,17 +31806,17 @@
       <c r="A1744" t="inlineStr"/>
       <c r="B1744" t="inlineStr">
         <is>
-          <t>signal.list.overheat_tag</t>
+          <t>morph.state.em</t>
         </is>
       </c>
       <c r="C1744" t="inlineStr">
         <is>
-          <t>过热</t>
+          <t>线圈态</t>
         </is>
       </c>
       <c r="D1744" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>coil state</t>
         </is>
       </c>
     </row>
@@ -31824,17 +31824,17 @@
       <c r="A1745" t="inlineStr"/>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>signal.list.port_line</t>
+          <t>morph.state.join</t>
         </is>
       </c>
       <c r="C1745" t="inlineStr">
         <is>
-          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
         <is>
-          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
     </row>
@@ -31842,17 +31842,17 @@
       <c r="A1746" t="inlineStr"/>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>signal.list.no_port_line</t>
+          <t>signal.list.port_tag</t>
         </is>
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>没有接入口：接入后只能驾驶，不插入固件</t>
+          <t>◇口</t>
         </is>
       </c>
       <c r="D1746" t="inlineStr">
         <is>
-          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
+          <t>◇PORT</t>
         </is>
       </c>
     </row>
@@ -31860,17 +31860,17 @@
       <c r="A1747" t="inlineStr"/>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>signal.list.overheat_line</t>
+          <t>signal.list.overheat_tag</t>
         </is>
       </c>
       <c r="C1747" t="inlineStr">
         <is>
-          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
+          <t>过热</t>
         </is>
       </c>
       <c r="D1747" t="inlineStr">
         <is>
-          <t>Overheated (heat {0}): it fires again once below {1}</t>
+          <t>HOT</t>
         </is>
       </c>
     </row>
@@ -31878,17 +31878,17 @@
       <c r="A1748" t="inlineStr"/>
       <c r="B1748" t="inlineStr">
         <is>
-          <t>signal.list.morph_line</t>
+          <t>signal.list.port_line</t>
         </is>
       </c>
       <c r="C1748" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
         </is>
       </c>
       <c r="D1748" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
         </is>
       </c>
     </row>
@@ -31896,17 +31896,17 @@
       <c r="A1749" t="inlineStr"/>
       <c r="B1749" t="inlineStr">
         <is>
-          <t>signal.list.experience_line</t>
+          <t>signal.list.no_port_line</t>
         </is>
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>没有接入口：接入后只能驾驶，不插入固件</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -31914,17 +31914,17 @@
       <c r="A1750" t="inlineStr"/>
       <c r="B1750" t="inlineStr">
         <is>
-          <t>signal.port_badge.tip</t>
+          <t>signal.list.overheat_line</t>
         </is>
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>带接入口的机器</t>
+          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>Machine with an uplink port</t>
+          <t>Overheated (heat {0}): it fires again once below {1}</t>
         </is>
       </c>
     </row>
@@ -31932,17 +31932,17 @@
       <c r="A1751" t="inlineStr"/>
       <c r="B1751" t="inlineStr">
         <is>
-          <t>machine.exp.produced</t>
+          <t>signal.list.morph_line</t>
         </is>
       </c>
       <c r="C1751" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1751" t="inlineStr">
         <is>
-          <t>Produced</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -31950,17 +31950,17 @@
       <c r="A1752" t="inlineStr"/>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>machine.exp.first_job</t>
+          <t>signal.list.experience_line</t>
         </is>
       </c>
       <c r="C1752" t="inlineStr">
         <is>
-          <t>首次工作</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>First job</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -31968,17 +31968,17 @@
       <c r="A1753" t="inlineStr"/>
       <c r="B1753" t="inlineStr">
         <is>
-          <t>machine.exp.controlled</t>
+          <t>signal.port_badge.tip</t>
         </is>
       </c>
       <c r="C1753" t="inlineStr">
         <is>
-          <t>首次与信号同行</t>
+          <t>带接入口的机器</t>
         </is>
       </c>
       <c r="D1753" t="inlineStr">
         <is>
-          <t>First time with the signal</t>
+          <t>Machine with an uplink port</t>
         </is>
       </c>
     </row>
@@ -31986,17 +31986,17 @@
       <c r="A1754" t="inlineStr"/>
       <c r="B1754" t="inlineStr">
         <is>
-          <t>machine.exp.expedition</t>
+          <t>machine.exp.produced</t>
         </is>
       </c>
       <c r="C1754" t="inlineStr">
         <is>
-          <t>远征</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="D1754" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>Produced</t>
         </is>
       </c>
     </row>
@@ -32004,17 +32004,17 @@
       <c r="A1755" t="inlineStr"/>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>machine.exp.severely_injured</t>
+          <t>machine.exp.first_job</t>
         </is>
       </c>
       <c r="C1755" t="inlineStr">
         <is>
-          <t>重伤</t>
+          <t>首次工作</t>
         </is>
       </c>
       <c r="D1755" t="inlineStr">
         <is>
-          <t>Severely injured</t>
+          <t>First job</t>
         </is>
       </c>
     </row>
@@ -32022,17 +32022,17 @@
       <c r="A1756" t="inlineStr"/>
       <c r="B1756" t="inlineStr">
         <is>
-          <t>machine.exp.elite_kill</t>
+          <t>machine.exp.controlled</t>
         </is>
       </c>
       <c r="C1756" t="inlineStr">
         <is>
-          <t>精英击破</t>
+          <t>首次与信号同行</t>
         </is>
       </c>
       <c r="D1756" t="inlineStr">
         <is>
-          <t>Elite kill</t>
+          <t>First time with the signal</t>
         </is>
       </c>
     </row>
@@ -32040,17 +32040,17 @@
       <c r="A1757" t="inlineStr"/>
       <c r="B1757" t="inlineStr">
         <is>
-          <t>machine.exp.boss_participation</t>
+          <t>machine.exp.expedition</t>
         </is>
       </c>
       <c r="C1757" t="inlineStr">
         <is>
-          <t>首领战</t>
+          <t>远征</t>
         </is>
       </c>
       <c r="D1757" t="inlineStr">
         <is>
-          <t>Boss fight</t>
+          <t>Expedition</t>
         </is>
       </c>
     </row>
@@ -32058,17 +32058,17 @@
       <c r="A1758" t="inlineStr"/>
       <c r="B1758" t="inlineStr">
         <is>
-          <t>machine.exp.returned</t>
+          <t>machine.exp.severely_injured</t>
         </is>
       </c>
       <c r="C1758" t="inlineStr">
         <is>
-          <t>返航</t>
+          <t>重伤</t>
         </is>
       </c>
       <c r="D1758" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Severely injured</t>
         </is>
       </c>
     </row>
@@ -32076,17 +32076,17 @@
       <c r="A1759" t="inlineStr"/>
       <c r="B1759" t="inlineStr">
         <is>
-          <t>machine.exp.sep</t>
+          <t>machine.exp.elite_kill</t>
         </is>
       </c>
       <c r="C1759" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>精英击破</t>
         </is>
       </c>
       <c r="D1759" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>Elite kill</t>
         </is>
       </c>
     </row>
@@ -32094,17 +32094,17 @@
       <c r="A1760" t="inlineStr"/>
       <c r="B1760" t="inlineStr">
         <is>
-          <t>machine.injury.combat</t>
+          <t>machine.exp.boss_participation</t>
         </is>
       </c>
       <c r="C1760" t="inlineStr">
         <is>
-          <t>战斗损伤（HP {0}/{1}）</t>
+          <t>首领战</t>
         </is>
       </c>
       <c r="D1760" t="inlineStr">
         <is>
-          <t>Combat damage (HP {0}/{1})</t>
+          <t>Boss fight</t>
         </is>
       </c>
     </row>
@@ -32112,17 +32112,17 @@
       <c r="A1761" t="inlineStr"/>
       <c r="B1761" t="inlineStr">
         <is>
-          <t>machine.exp.none</t>
+          <t>machine.exp.returned</t>
         </is>
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>无记录经历</t>
+          <t>返航</t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">
         <is>
-          <t>No recorded experience</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
@@ -32130,17 +32130,17 @@
       <c r="A1762" t="inlineStr"/>
       <c r="B1762" t="inlineStr">
         <is>
-          <t>machine.exp.signal</t>
+          <t>machine.exp.sep</t>
         </is>
       </c>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次，累计 {1}</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1762" t="inlineStr">
         <is>
-          <t>With the signal {0} times, {1} in total</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -32148,17 +32148,17 @@
       <c r="A1763" t="inlineStr"/>
       <c r="B1763" t="inlineStr">
         <is>
-          <t>machine.exp.signal_none</t>
+          <t>machine.injury.combat</t>
         </is>
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>尚未与信号同行</t>
+          <t>战斗损伤（HP {0}/{1}）</t>
         </is>
       </c>
       <c r="D1763" t="inlineStr">
         <is>
-          <t>Never carried the signal</t>
+          <t>Combat damage (HP {0}/{1})</t>
         </is>
       </c>
     </row>
@@ -32166,17 +32166,17 @@
       <c r="A1764" t="inlineStr"/>
       <c r="B1764" t="inlineStr">
         <is>
-          <t>machine.status.dead</t>
+          <t>machine.exp.none</t>
         </is>
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录）</t>
+          <t>无记录经历</t>
         </is>
       </c>
       <c r="D1764" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record)</t>
+          <t>No recorded experience</t>
         </is>
       </c>
     </row>
@@ -32184,17 +32184,17 @@
       <c r="A1765" t="inlineStr"/>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>machine.status.in_factory</t>
+          <t>machine.exp.signal</t>
         </is>
       </c>
       <c r="C1765" t="inlineStr">
         <is>
-          <t>厂内待驶出</t>
+          <t>与信号同行 {0} 次，累计 {1}</t>
         </is>
       </c>
       <c r="D1765" t="inlineStr">
         <is>
-          <t>Waiting in the factory</t>
+          <t>With the signal {0} times, {1} in total</t>
         </is>
       </c>
     </row>
@@ -32202,17 +32202,17 @@
       <c r="A1766" t="inlineStr"/>
       <c r="B1766" t="inlineStr">
         <is>
-          <t>machine.status.uplinked</t>
+          <t>machine.exp.signal_none</t>
         </is>
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>接入中</t>
+          <t>尚未与信号同行</t>
         </is>
       </c>
       <c r="D1766" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>Never carried the signal</t>
         </is>
       </c>
     </row>
@@ -32220,17 +32220,17 @@
       <c r="A1767" t="inlineStr"/>
       <c r="B1767" t="inlineStr">
         <is>
-          <t>machine.status.idle</t>
+          <t>machine.status.dead</t>
         </is>
       </c>
       <c r="C1767" t="inlineStr">
         <is>
-          <t>空闲</t>
+          <t>阵亡（纪念记录）</t>
         </is>
       </c>
       <c r="D1767" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>Destroyed (memorial record)</t>
         </is>
       </c>
     </row>
@@ -32238,17 +32238,17 @@
       <c r="A1768" t="inlineStr"/>
       <c r="B1768" t="inlineStr">
         <is>
-          <t>machine.status.working</t>
+          <t>machine.status.in_factory</t>
         </is>
       </c>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>厂内待驶出</t>
         </is>
       </c>
       <c r="D1768" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Waiting in the factory</t>
         </is>
       </c>
     </row>
@@ -32256,17 +32256,17 @@
       <c r="A1769" t="inlineStr"/>
       <c r="B1769" t="inlineStr">
         <is>
-          <t>machine.detail.none</t>
+          <t>machine.status.uplinked</t>
         </is>
       </c>
       <c r="C1769" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>接入中</t>
         </is>
       </c>
       <c r="D1769" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Uplinked</t>
         </is>
       </c>
     </row>
@@ -32274,17 +32274,17 @@
       <c r="A1770" t="inlineStr"/>
       <c r="B1770" t="inlineStr">
         <is>
-          <t>machine.detail.injury_none</t>
+          <t>machine.status.idle</t>
         </is>
       </c>
       <c r="C1770" t="inlineStr">
         <is>
-          <t>无记录</t>
+          <t>空闲</t>
         </is>
       </c>
       <c r="D1770" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Idle</t>
         </is>
       </c>
     </row>
@@ -32292,17 +32292,17 @@
       <c r="A1771" t="inlineStr"/>
       <c r="B1771" t="inlineStr">
         <is>
-          <t>machine.detail.port_yes</t>
+          <t>machine.status.working</t>
         </is>
       </c>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>工作中</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -32310,17 +32310,17 @@
       <c r="A1772" t="inlineStr"/>
       <c r="B1772" t="inlineStr">
         <is>
-          <t>machine.detail.port_no</t>
+          <t>machine.detail.none</t>
         </is>
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>没有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D1772" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -32328,17 +32328,17 @@
       <c r="A1773" t="inlineStr"/>
       <c r="B1773" t="inlineStr">
         <is>
-          <t>machine.detail.line_id</t>
+          <t>machine.detail.injury_none</t>
         </is>
       </c>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+          <t>无记录</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
         <is>
-          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+          <t>none recorded</t>
         </is>
       </c>
     </row>
@@ -32346,17 +32346,17 @@
       <c r="A1774" t="inlineStr"/>
       <c r="B1774" t="inlineStr">
         <is>
-          <t>machine.detail.line_vitals</t>
+          <t>machine.detail.port_yes</t>
         </is>
       </c>
       <c r="C1774" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+          <t>有</t>
         </is>
       </c>
       <c r="D1774" t="inlineStr">
         <is>
-          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -32364,17 +32364,17 @@
       <c r="A1775" t="inlineStr"/>
       <c r="B1775" t="inlineStr">
         <is>
-          <t>machine.detail.line_exp</t>
+          <t>machine.detail.port_no</t>
         </is>
       </c>
       <c r="C1775" t="inlineStr">
         <is>
-          <t>经历：{0}</t>
+          <t>没有</t>
         </is>
       </c>
       <c r="D1775" t="inlineStr">
         <is>
-          <t>Experience: {0}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -32382,17 +32382,17 @@
       <c r="A1776" t="inlineStr"/>
       <c r="B1776" t="inlineStr">
         <is>
-          <t>machine.detail.line_signal</t>
+          <t>machine.detail.line_id</t>
         </is>
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
         </is>
       </c>
       <c r="D1776" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
         </is>
       </c>
     </row>
@@ -32400,17 +32400,17 @@
       <c r="A1777" t="inlineStr"/>
       <c r="B1777" t="inlineStr">
         <is>
-          <t>machine.detail.line_stats</t>
+          <t>machine.detail.line_vitals</t>
         </is>
       </c>
       <c r="C1777" t="inlineStr">
         <is>
-          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
         </is>
       </c>
       <c r="D1777" t="inlineStr">
         <is>
-          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
         </is>
       </c>
     </row>
@@ -32418,17 +32418,17 @@
       <c r="A1778" t="inlineStr"/>
       <c r="B1778" t="inlineStr">
         <is>
-          <t>machine.detail.line_morph</t>
+          <t>machine.detail.line_exp</t>
         </is>
       </c>
       <c r="C1778" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>经历：{0}</t>
         </is>
       </c>
       <c r="D1778" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Experience: {0}</t>
         </is>
       </c>
     </row>
@@ -32436,17 +32436,17 @@
       <c r="A1779" t="inlineStr"/>
       <c r="B1779" t="inlineStr">
         <is>
-          <t>victory.summary</t>
+          <t>machine.detail.line_signal</t>
         </is>
       </c>
       <c r="C1779" t="inlineStr">
         <is>
-          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D1779" t="inlineStr">
         <is>
-          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -32454,17 +32454,17 @@
       <c r="A1780" t="inlineStr"/>
       <c r="B1780" t="inlineStr">
         <is>
-          <t>victory.row.number</t>
+          <t>machine.detail.line_stats</t>
         </is>
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>#{0}（{1}）</t>
+          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
         </is>
       </c>
       <c r="D1780" t="inlineStr">
         <is>
-          <t>#{0} ({1})</t>
+          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
         </is>
       </c>
     </row>
@@ -32472,17 +32472,17 @@
       <c r="A1781" t="inlineStr"/>
       <c r="B1781" t="inlineStr">
         <is>
-          <t>victory.row.alive</t>
+          <t>machine.detail.line_morph</t>
         </is>
       </c>
       <c r="C1781" t="inlineStr">
         <is>
-          <t>幸存</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1781" t="inlineStr">
         <is>
-          <t>survived</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -32490,17 +32490,17 @@
       <c r="A1782" t="inlineStr"/>
       <c r="B1782" t="inlineStr">
         <is>
-          <t>victory.row.dead</t>
+          <t>victory.summary</t>
         </is>
       </c>
       <c r="C1782" t="inlineStr">
         <is>
-          <t>阵亡</t>
+          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
         </is>
       </c>
       <c r="D1782" t="inlineStr">
         <is>
-          <t>destroyed</t>
+          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
         </is>
       </c>
     </row>
@@ -32508,17 +32508,17 @@
       <c r="A1783" t="inlineStr"/>
       <c r="B1783" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_alive</t>
+          <t>victory.row.number</t>
         </is>
       </c>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>幸存，将随撤离返回家园；{0}</t>
+          <t>#{0}（{1}）</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
         <is>
-          <t>Survived and returns home with the evacuation; {0}</t>
+          <t>#{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -32526,17 +32526,17 @@
       <c r="A1784" t="inlineStr"/>
       <c r="B1784" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_dead</t>
+          <t>victory.row.alive</t>
         </is>
       </c>
       <c r="C1784" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+          <t>幸存</t>
         </is>
       </c>
       <c r="D1784" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+          <t>survived</t>
         </is>
       </c>
     </row>
@@ -32544,17 +32544,17 @@
       <c r="A1785" t="inlineStr"/>
       <c r="B1785" t="inlineStr">
         <is>
-          <t>factory.reason.uplinked</t>
+          <t>victory.row.dead</t>
         </is>
       </c>
       <c r="C1785" t="inlineStr">
         <is>
-          <t>这台机器正被你接入，先退出接入</t>
+          <t>阵亡</t>
         </is>
       </c>
       <c r="D1785" t="inlineStr">
         <is>
-          <t>You are uplinked into this machine: leave the uplink first</t>
+          <t>destroyed</t>
         </is>
       </c>
     </row>
@@ -32562,17 +32562,17 @@
       <c r="A1786" t="inlineStr"/>
       <c r="B1786" t="inlineStr">
         <is>
-          <t>signal.cmd.uplinked</t>
+          <t>expedition.return.row_status_alive</t>
         </is>
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>接入：{0}</t>
+          <t>幸存，将随撤离返回家园；{0}</t>
         </is>
       </c>
       <c r="D1786" t="inlineStr">
         <is>
-          <t>Uplinked: {0}</t>
+          <t>Survived and returns home with the evacuation; {0}</t>
         </is>
       </c>
     </row>
@@ -32580,17 +32580,17 @@
       <c r="A1787" t="inlineStr"/>
       <c r="B1787" t="inlineStr">
         <is>
-          <t>signal.cmd.reconnecting</t>
+          <t>expedition.return.row_status_dead</t>
         </is>
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>重连中：{0}</t>
+          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
         </is>
       </c>
       <c r="D1787" t="inlineStr">
         <is>
-          <t>Reconnecting: {0}</t>
+          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
         </is>
       </c>
     </row>
@@ -32598,17 +32598,17 @@
       <c r="A1788" t="inlineStr"/>
       <c r="B1788" t="inlineStr">
         <is>
-          <t>signal.cmd.strategy</t>
+          <t>factory.reason.uplinked</t>
         </is>
       </c>
       <c r="C1788" t="inlineStr">
         <is>
-          <t>战略视角</t>
+          <t>这台机器正被你接入，先退出接入</t>
         </is>
       </c>
       <c r="D1788" t="inlineStr">
         <is>
-          <t>Strategy view</t>
+          <t>You are uplinked into this machine: leave the uplink first</t>
         </is>
       </c>
     </row>
@@ -32616,17 +32616,17 @@
       <c r="A1789" t="inlineStr"/>
       <c r="B1789" t="inlineStr">
         <is>
-          <t>region.control.fail.not_found</t>
+          <t>signal.cmd.uplinked</t>
         </is>
       </c>
       <c r="C1789" t="inlineStr">
         <is>
-          <t>没有可以接入的目标。</t>
+          <t>接入：{0}</t>
         </is>
       </c>
       <c r="D1789" t="inlineStr">
         <is>
-          <t>There is nothing to uplink into.</t>
+          <t>Uplinked: {0}</t>
         </is>
       </c>
     </row>
@@ -32634,17 +32634,17 @@
       <c r="A1790" t="inlineStr"/>
       <c r="B1790" t="inlineStr">
         <is>
-          <t>region.control.fail.not_friendly</t>
+          <t>signal.cmd.reconnecting</t>
         </is>
       </c>
       <c r="C1790" t="inlineStr">
         <is>
-          <t>目标不属于本地点。</t>
+          <t>重连中：{0}</t>
         </is>
       </c>
       <c r="D1790" t="inlineStr">
         <is>
-          <t>The target does not belong to this site.</t>
+          <t>Reconnecting: {0}</t>
         </is>
       </c>
     </row>
@@ -32652,17 +32652,17 @@
       <c r="A1791" t="inlineStr"/>
       <c r="B1791" t="inlineStr">
         <is>
-          <t>region.control.fail.dead</t>
+          <t>signal.cmd.strategy</t>
         </is>
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>目标已阵亡。</t>
+          <t>战略视角</t>
         </is>
       </c>
       <c r="D1791" t="inlineStr">
         <is>
-          <t>The target is destroyed.</t>
+          <t>Strategy view</t>
         </is>
       </c>
     </row>
@@ -32670,17 +32670,17 @@
       <c r="A1792" t="inlineStr"/>
       <c r="B1792" t="inlineStr">
         <is>
-          <t>region.control.fail.out_of_range</t>
+          <t>region.control.fail.not_found</t>
         </is>
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>目标当前不在场。</t>
+          <t>没有可以接入的目标。</t>
         </is>
       </c>
       <c r="D1792" t="inlineStr">
         <is>
-          <t>The target is not here right now.</t>
+          <t>There is nothing to uplink into.</t>
         </is>
       </c>
     </row>
@@ -32688,17 +32688,17 @@
       <c r="A1793" t="inlineStr"/>
       <c r="B1793" t="inlineStr">
         <is>
-          <t>region.control.fail.jammed</t>
+          <t>region.control.fail.not_friendly</t>
         </is>
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>信号被干扰，接入失败。</t>
+          <t>目标不属于本地点。</t>
         </is>
       </c>
       <c r="D1793" t="inlineStr">
         <is>
-          <t>The signal is jammed; uplink failed.</t>
+          <t>The target does not belong to this site.</t>
         </is>
       </c>
     </row>
@@ -32706,17 +32706,17 @@
       <c r="A1794" t="inlineStr"/>
       <c r="B1794" t="inlineStr">
         <is>
-          <t>region.control.fail.transition</t>
+          <t>region.control.fail.dead</t>
         </is>
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>镜头切换中，请稍候。</t>
+          <t>目标已阵亡。</t>
         </is>
       </c>
       <c r="D1794" t="inlineStr">
         <is>
-          <t>The camera is moving; please wait.</t>
+          <t>The target is destroyed.</t>
         </is>
       </c>
     </row>
@@ -32724,17 +32724,17 @@
       <c r="A1795" t="inlineStr"/>
       <c r="B1795" t="inlineStr">
         <is>
-          <t>region.control.fail.modal</t>
+          <t>region.control.fail.out_of_range</t>
         </is>
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>请先关闭当前面板。</t>
+          <t>目标当前不在场。</t>
         </is>
       </c>
       <c r="D1795" t="inlineStr">
         <is>
-          <t>Close the current panel first.</t>
+          <t>The target is not here right now.</t>
         </is>
       </c>
     </row>
@@ -32742,17 +32742,17 @@
       <c r="A1796" t="inlineStr"/>
       <c r="B1796" t="inlineStr">
         <is>
-          <t>region.control.fail.already</t>
+          <t>region.control.fail.jammed</t>
         </is>
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>已经接入这台机器。</t>
+          <t>信号被干扰，接入失败。</t>
         </is>
       </c>
       <c r="D1796" t="inlineStr">
         <is>
-          <t>You are already uplinked into this machine.</t>
+          <t>The signal is jammed; uplink failed.</t>
         </is>
       </c>
     </row>
@@ -32760,17 +32760,17 @@
       <c r="A1797" t="inlineStr"/>
       <c r="B1797" t="inlineStr">
         <is>
-          <t>region.control.fail.ineligible</t>
+          <t>region.control.fail.transition</t>
         </is>
       </c>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>目标暂时不能接入。</t>
+          <t>镜头切换中，请稍候。</t>
         </is>
       </c>
       <c r="D1797" t="inlineStr">
         <is>
-          <t>The target cannot be uplinked right now.</t>
+          <t>The camera is moving; please wait.</t>
         </is>
       </c>
     </row>
@@ -32778,17 +32778,17 @@
       <c r="A1798" t="inlineStr"/>
       <c r="B1798" t="inlineStr">
         <is>
-          <t>region.control.fail.other</t>
+          <t>region.control.fail.modal</t>
         </is>
       </c>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>接入失败。</t>
+          <t>请先关闭当前面板。</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
         <is>
-          <t>Uplink failed.</t>
+          <t>Close the current panel first.</t>
         </is>
       </c>
     </row>
@@ -32796,17 +32796,17 @@
       <c r="A1799" t="inlineStr"/>
       <c r="B1799" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink</t>
+          <t>region.control.fail.already</t>
         </is>
       </c>
       <c r="C1799" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>已经接入这台机器。</t>
         </is>
       </c>
       <c r="D1799" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>You are already uplinked into this machine.</t>
         </is>
       </c>
     </row>
@@ -32814,17 +32814,17 @@
       <c r="A1800" t="inlineStr"/>
       <c r="B1800" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink</t>
+          <t>region.control.fail.ineligible</t>
         </is>
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>已接入</t>
+          <t>目标暂时不能接入。</t>
         </is>
       </c>
       <c r="D1800" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>The target cannot be uplinked right now.</t>
         </is>
       </c>
     </row>
@@ -32832,17 +32832,17 @@
       <c r="A1801" t="inlineStr"/>
       <c r="B1801" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink_leave</t>
+          <t>region.control.fail.other</t>
         </is>
       </c>
       <c r="C1801" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>接入失败。</t>
         </is>
       </c>
       <c r="D1801" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Uplink failed.</t>
         </is>
       </c>
     </row>
@@ -32850,17 +32850,17 @@
       <c r="A1802" t="inlineStr"/>
       <c r="B1802" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink_leave</t>
+          <t>feedback.tag.uplink</t>
         </is>
       </c>
       <c r="C1802" t="inlineStr">
         <is>
-          <t>信号离开机器</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D1802" t="inlineStr">
         <is>
-          <t>The signal left the machine</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -32868,17 +32868,17 @@
       <c r="A1803" t="inlineStr"/>
       <c r="B1803" t="inlineStr">
         <is>
-          <t>pause.codex</t>
+          <t>feedback.caption.uplink</t>
         </is>
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>已接入</t>
         </is>
       </c>
       <c r="D1803" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Uplinked</t>
         </is>
       </c>
     </row>
@@ -32886,17 +32886,17 @@
       <c r="A1804" t="inlineStr"/>
       <c r="B1804" t="inlineStr">
         <is>
-          <t>pause.camera_title</t>
+          <t>feedback.tag.uplink_leave</t>
         </is>
       </c>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>接入镜头</t>
+          <t>离开</t>
         </is>
       </c>
       <c r="D1804" t="inlineStr">
         <is>
-          <t>Uplink camera</t>
+          <t>Leave</t>
         </is>
       </c>
     </row>
@@ -32904,17 +32904,17 @@
       <c r="A1805" t="inlineStr"/>
       <c r="B1805" t="inlineStr">
         <is>
-          <t>pause.camera_zoom</t>
+          <t>feedback.caption.uplink_leave</t>
         </is>
       </c>
       <c r="C1805" t="inlineStr">
         <is>
-          <t>接入时镜头距离 {0}%</t>
+          <t>信号离开机器</t>
         </is>
       </c>
       <c r="D1805" t="inlineStr">
         <is>
-          <t>Uplink camera distance {0}%</t>
+          <t>The signal left the machine</t>
         </is>
       </c>
     </row>
@@ -32922,17 +32922,17 @@
       <c r="A1806" t="inlineStr"/>
       <c r="B1806" t="inlineStr">
         <is>
-          <t>pause.camera_follow</t>
+          <t>pause.codex</t>
         </is>
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>接入时跟随力度 {0}%</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="D1806" t="inlineStr">
         <is>
-          <t>Uplink follow strength {0}%</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -32940,17 +32940,17 @@
       <c r="A1807" t="inlineStr"/>
       <c r="B1807" t="inlineStr">
         <is>
-          <t>pause.camera_reset</t>
+          <t>pause.camera_title</t>
         </is>
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>接入镜头</t>
         </is>
       </c>
       <c r="D1807" t="inlineStr">
         <is>
-          <t>Reset to default</t>
+          <t>Uplink camera</t>
         </is>
       </c>
     </row>
@@ -32958,17 +32958,17 @@
       <c r="A1808" t="inlineStr"/>
       <c r="B1808" t="inlineStr">
         <is>
-          <t>pause.camera_zoom_tip</t>
+          <t>pause.camera_zoom</t>
         </is>
       </c>
       <c r="C1808" t="inlineStr">
         <is>
-          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>接入时镜头距离 {0}%</t>
         </is>
       </c>
       <c r="D1808" t="inlineStr">
         <is>
-          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>Uplink camera distance {0}%</t>
         </is>
       </c>
     </row>
@@ -32976,17 +32976,17 @@
       <c r="A1809" t="inlineStr"/>
       <c r="B1809" t="inlineStr">
         <is>
-          <t>pause.camera_follow_tip</t>
+          <t>pause.camera_follow</t>
         </is>
       </c>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>接入时跟随力度 {0}%</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
         <is>
-          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>Uplink follow strength {0}%</t>
         </is>
       </c>
     </row>
@@ -32994,17 +32994,17 @@
       <c r="A1810" t="inlineStr"/>
       <c r="B1810" t="inlineStr">
         <is>
-          <t>camera.follow.started</t>
+          <t>pause.camera_reset</t>
         </is>
       </c>
       <c r="C1810" t="inlineStr">
         <is>
-          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+          <t>恢复默认</t>
         </is>
       </c>
       <c r="D1810" t="inlineStr">
         <is>
-          <t>Camera following {0} (pan or press {1} again to stop)</t>
+          <t>Reset to default</t>
         </is>
       </c>
     </row>
@@ -33012,17 +33012,17 @@
       <c r="A1811" t="inlineStr"/>
       <c r="B1811" t="inlineStr">
         <is>
-          <t>camera.follow.stopped</t>
+          <t>pause.camera_zoom_tip</t>
         </is>
       </c>
       <c r="C1811" t="inlineStr">
         <is>
-          <t>镜头停止跟随</t>
+          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
         </is>
       </c>
       <c r="D1811" t="inlineStr">
         <is>
-          <t>Camera follow stopped</t>
+          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
         </is>
       </c>
     </row>
@@ -33030,17 +33030,17 @@
       <c r="A1812" t="inlineStr"/>
       <c r="B1812" t="inlineStr">
         <is>
-          <t>camera.follow.nothing</t>
+          <t>pause.camera_follow_tip</t>
         </is>
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>先选中一台机器再按 {0} 跟随</t>
+          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
         </is>
       </c>
       <c r="D1812" t="inlineStr">
         <is>
-          <t>Select a machine first, then press {0} to follow it</t>
+          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
         </is>
       </c>
     </row>
@@ -33048,17 +33048,2033 @@
       <c r="A1813" t="inlineStr"/>
       <c r="B1813" t="inlineStr">
         <is>
+          <t>camera.follow.started</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>Camera following {0} (pan or press {1} again to stop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr"/>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>camera.follow.stopped</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>镜头停止跟随</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>Camera follow stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr"/>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>camera.follow.nothing</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>先选中一台机器再按 {0} 跟随</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>Select a machine first, then press {0} to follow it</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr"/>
+      <c r="B1816" t="inlineStr">
+        <is>
           <t>camera.follow.group</t>
         </is>
       </c>
-      <c r="C1813" t="inlineStr">
+      <c r="C1816" t="inlineStr">
         <is>
           <t>{0} 台机器</t>
         </is>
       </c>
-      <c r="D1813" t="inlineStr">
+      <c r="D1816" t="inlineStr">
         <is>
           <t>{0} machines</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr"/>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>fwlib.title</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>固件库</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>Firmware library</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr"/>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>fwlib.close</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr"/>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>fwlib.count</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>芯片 {0} 枚（显示 {1}）· 仓储 {2}/{3} 格</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>Chips {0} (showing {1}) · Storage {2}/{3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr"/>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>fwlib.over_capacity</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>仓储已满：新得到的芯片会进入待领取</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>Storage is full: new chips go to the claim queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr"/>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>fwlib.search</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>搜索名称或说明</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>Search name or description</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr"/>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>fwlib.filter.category</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr"/>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>fwlib.filter.kind</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>种类</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr"/>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>fwlib.filter.protocol</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>协议</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr"/>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>fwlib.filter.cracked</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>破解</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>Cracked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr"/>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>fwlib.filter.carrier</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>兼容载体</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr"/>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>fwlib.filter.rarity</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>稀有度</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr"/>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>fwlib.sort</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr"/>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>fwlib.any</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr"/>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>fwlib.kind.regular</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>● 常规</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>● Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr"/>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>fwlib.kind.core</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>◆ 核心</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>◆ Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr"/>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>fwlib.protocol.own</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>己方 / 中立</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>Own / neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr"/>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>fwlib.cracked.yes</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>已破解</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>Cracked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr"/>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>fwlib.cracked.no</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>▲ 未破解</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>▲ Not cracked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr"/>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>fwlib.sort.name</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr"/>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>fwlib.sort.category</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr"/>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>fwlib.sort.rarity</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>稀有度（高→低）</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>Rarity (high→low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr"/>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>fwlib.sort.load</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>负载（高→低）</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>Load (high→low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr"/>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>fwlib.sort.newest</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>最新获得</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>Newest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr"/>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>fwlib.sort.location</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>所在位置</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr"/>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>fwlib.empty</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>还没有固件芯片。在信号核面板里刻印，或从远征带回。</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>No firmware chips yet. Print them in the Signal Core panel or bring them back from expeditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr"/>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>fwlib.empty_filtered</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>没有符合筛选条件的芯片。</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>No chips match the filters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr"/>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>fwlib.error</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>固件数据不可用（配置表缺失），请重新安装或联系开发者：{0}</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>Firmware data is unavailable (missing table); reinstall or contact the developers: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr"/>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>fwlib.loc.storage</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>仓储</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr"/>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>fwlib.loc.pending</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>待领取（仓储已满）</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>Awaiting claim (storage full)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr"/>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>fwlib.loc.signal</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>信号核 第 {0} 槽</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>Signal Core slot {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr"/>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>fwlib.loc.reserved</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>仓储（合成台预留中）</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>Storage (reserved by crafting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr"/>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>fwlib.loc.draft</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>蓝图电路（{0}）</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>Blueprint circuit ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr"/>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>fwlib.row.locked</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>［锁定］</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>[Locked]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr"/>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>fwlib.select_all</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>全选当前列表</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>Select all shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr"/>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>fwlib.select_none</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>清空选择</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>Clear selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr"/>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>fwlib.selected</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>已选 {0} 枚</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>{0} selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr"/>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>fwlib.row.pick</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>选</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr"/>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>fwlib.row.picked</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr"/>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>fwlib.disassemble</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>分解所选（{0}）</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>Disassemble selected ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr"/>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>fwlib.disassemble_tip</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>分解返还废料 {0}/枚。锁定的、装进信号核的、被合成台预留的会跳过。需要确认，无法撤销。</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>Each chip refunds {0} scrap. Locked chips, chips in the Signal Core and chips reserved by crafting are skipped. Needs confirmation; cannot be undone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr"/>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.title</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>分解固件芯片</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>Disassemble firmware chips</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr"/>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.lose</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>固件芯片 ×{0}（返还废料 +{1}）</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>Firmware chips ×{0} (refund +{1} scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr"/>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.unprintable</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>其中 {0} 枚目前无法再刻印（未解锁或未破解）</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>{0} of them cannot be printed again right now (locked or not cracked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr"/>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.skip_locked</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>跳过锁定的 {0} 枚</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>Skipping {0} locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr"/>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.skip_busy</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>跳过装进信号核或被合成台预留的 {0} 枚</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>Skipping {0} in the Signal Core or reserved by crafting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr"/>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.names</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>包括：{0}</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>Includes: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr"/>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.name_count</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>{0} ×{1}</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>{0} ×{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr"/>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.name_more</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>等另外 {0} 种</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>and {0} more kinds</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr"/>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.hidden</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>其中 {0} 枚不在当前筛选结果里（之前勾选的）</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>{0} of them are outside the current filter (picked earlier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr"/>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.ok</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>分解</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>Disassemble</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr"/>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>fwlib.confirm.cancel</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr"/>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>fwlib.result.done</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>已分解 {0} 枚，返还废料 {1}；跳过 {2} 枚</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>Disassembled {0}, refunded {1} scrap; skipped {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr"/>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>fwlib.result.nothing</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>没有可分解的芯片：所选的都已锁定或正在使用</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>Nothing to disassemble: every selected chip is locked or in use</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr"/>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>fwlib.lock</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>锁定</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr"/>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>fwlib.unlock</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>解除锁定</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>Unlock</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr"/>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>fwlib.lock_tip</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>锁定后，批量分解会跳过这枚芯片（不影响装进信号核）。</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>Locked chips are skipped by bulk disassembly (they can still go into the Signal Core).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr"/>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>fwlib.claim</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>领取进仓储</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>Claim into storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr"/>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>fwlib.codex</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>查看图鉴</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>Open codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr"/>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>fwlib.compare_a</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>设为比较 A</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>Compare as A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr"/>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>fwlib.compare_b</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>设为比较 B</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>Compare as B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr"/>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>fwlib.compare.title</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>比较</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr"/>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>fwlib.compare.empty</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>选一枚芯片点“设为比较 A”，再选另一枚点“设为比较 B”，两条固件会并排显示。</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>Pick a chip and press "Compare as A", then another and press "Compare as B" to see them side by side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr"/>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>fwlib.compare.clear</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>清除比较</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>Clear compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr"/>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>fwlib.compare.same</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>（相同）</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>(same)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr"/>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>fwlib.compare.tags</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>状态标签</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>Status tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr"/>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>fwlib.detail.none</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>在左侧选一枚芯片查看详情。</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>Pick a chip on the left to see its details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr"/>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>fwlib.detail.kind</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>种类：{0}</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>Kind: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr"/>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>fwlib.detail.category</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>类别：{0}</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>Category: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr"/>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>fwlib.detail.protocol</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>协议：{0}</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>Protocol: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr"/>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>fwlib.detail.rarity</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>稀有度：{0}</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>Rarity: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr"/>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>fwlib.detail.numbers</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>负载 {0} · 每发耗电 {1} · 每发积热 {2}</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>Load {0} · Power per shot {1} · Heat per shot {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr"/>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>fwlib.detail.tags</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>产生的状态标签：{0}</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>Status tags applied: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr"/>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>fwlib.detail.tags_none</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>产生的状态标签：无</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>Status tags applied: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr"/>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>fwlib.detail.reactions</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>参与的反应：{0}</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>Reactions it takes part in: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr"/>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>fwlib.detail.reactions_none</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>参与的反应：无</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>Reactions it takes part in: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr"/>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>fwlib.detail.reaction_unknown</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>？？？（尚未发现）</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>??? (not discovered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr"/>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>fwlib.detail.acquire</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>获取途径：{0}</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>How to get it: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr"/>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>fwlib.detail.held</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>当前持有 {0} 枚：{1}</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>You hold {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr"/>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>fwlib.detail.held_none</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>当前持有 0 枚</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>You hold none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr"/>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>fwlib.detail.origin</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>这一枚的来源：{0}</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>This chip came from: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr"/>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>fwlib.origin.seed</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>开局配发</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>Starting issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr"/>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>fwlib.origin.print</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>装配站刻印</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>Printed at the Assembly Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr"/>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>fwlib.origin.salvage</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>解析战利品</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>Analysed salvage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr"/>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>fwlib.origin.encrypted</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>带回的敌方加密固件</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>Recovered enemy-encrypted firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr"/>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>fwlib.origin.craft</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>电路合成台</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>Circuit Synthesizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr"/>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>fwlib.origin.unknown</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>旧存档（来源未记录）</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>Older save (source not recorded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr"/>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>fwlib.detail.route_ok</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>取用路线：{0} → 装配站，通畅</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>Fetch route: {0} → Assembly Station, clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr"/>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>fwlib.detail.route_blocked</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>取用路线：{0} → 装配站被堵住：{1}</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>Fetch route: {0} → Assembly Station is blocked: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr"/>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>fwlib.detail.route_unknown</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>取用路线：家园地形还没载入，暂时无法检查</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>Fetch route: home terrain not loaded yet; cannot check</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr"/>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>fwlib.route.storage_enclosed</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>{0} 四周被 {1} 围住</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>{0} is walled in by {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr"/>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>fwlib.route.station_enclosed</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>装配站四周被 {0} 围住</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>the Assembly Station is walled in by {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr"/>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>fwlib.route.disconnected</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>两处之间没有能走通的路（被建筑或地形隔断）</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>there is no walkable path between them (cut off by buildings or terrain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr"/>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>fwlib.route.no_station</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>家园还没有装配站</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>the home has no Assembly Station yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr"/>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>fwlib.route.terrain</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>地形</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>terrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr"/>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>fwlib.storage.core</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>归还核心应急库</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>Core emergency cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr"/>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>fwlib.footer</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>悬停固件按 {act:OpenCodex} 查看图鉴 · 按 {act:OpenFirmware} 或 {act:Cancel} 关闭</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>Hover a firmware and press {act:OpenCodex} for its codex entry · Press {act:OpenFirmware} or {act:Cancel} to close</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr"/>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>fwlib.readings_title</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>各载体读法</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>Readings by carrier</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr"/>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>pause.firmware</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>固件库</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>Firmware library</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr"/>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>codex.tab.system</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>系统说明</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr"/>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>codex.tab.firmware</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>固件</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr"/>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>codex.tab.reaction</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>反应</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>Reactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr"/>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>codex.panel.search</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>搜索条目</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>Search entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr"/>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>codex.panel.no_match</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>没有符合搜索的条目。</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>No entries match the search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr"/>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>codex.firmware.locked_body</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>尚未获得。获取途径：{0}</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>Not obtained yet. How to get it: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr"/>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>codex.reaction.recipe</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>配料：{0} + {1}</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>Ingredients: {0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr"/>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>codex.reaction.recipe_assembly</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>由装配识别：带上 {0}</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>Recognised from the loadout: carry {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr"/>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>codex.reaction.firmware</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>能提供配料的固件：{0}</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>Firmware that supplies an ingredient: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr"/>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>codex.reaction.elsewhere</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>本存档还没有打出过（在其他存档里发现）</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>Not triggered in this save yet (discovered in another save)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr"/>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>ui.common.codex_jump</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>按 {0} 查看图鉴：{1}</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>Press {0} for the codex: {1}</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1925"/>
+  <dimension ref="A1:D1941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27702,17 +27702,17 @@
       <c r="A1516" t="inlineStr"/>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>component.comp_ram.name</t>
+          <t>component.subtype.melee_orbit</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>液压刺锤</t>
+          <t>格斗·环绕</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>Hydraulic Ram</t>
+          <t>Melee · Orbit</t>
         </is>
       </c>
     </row>
@@ -27720,17 +27720,17 @@
       <c r="A1517" t="inlineStr"/>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>component.comp_ram.desc</t>
+          <t>component.subtype.drone_post</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>近身格斗组件：贴近后猛刺，命中前方窄扇形里触及的全部敌人。</t>
+          <t>无人机·定点</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>Close-quarters melee: closes in and drives forward, hitting every enemy in a narrow arc in front.</t>
+          <t>Drone · Emplaced</t>
         </is>
       </c>
     </row>
@@ -27738,17 +27738,17 @@
       <c r="A1518" t="inlineStr"/>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>component.comp_shovel.name</t>
+          <t>component.subtype.field_pulse</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>推铲</t>
+          <t>布区·脉冲</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>Push Blade</t>
+          <t>Zone · Pulse</t>
         </is>
       </c>
     </row>
@@ -27756,17 +27756,17 @@
       <c r="A1519" t="inlineStr"/>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>component.comp_shovel.desc</t>
+          <t>component.subtype.melee_grip</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>格斗·扇形：身前宽铲一扫并把敌人推开；适合搬运机。</t>
+          <t>格斗·拆解</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>Melee sweep: a wide scoop in front that shoves enemies back; suits haulers.</t>
+          <t>Melee · Dismantle</t>
         </is>
       </c>
     </row>
@@ -27774,17 +27774,17 @@
       <c r="A1520" t="inlineStr"/>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>component.comp_shovel.turret_reading</t>
+          <t>component.subtype.melee_thorns</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>装在炮塔上读作“击退铲”：把近身的敌人推开 3 米。</t>
+          <t>格斗·反伤</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>On a turret it becomes a Repulsor Blade: shoves nearby enemies back 3 m.</t>
+          <t>Melee · Retaliate</t>
         </is>
       </c>
     </row>
@@ -27792,17 +27792,17 @@
       <c r="A1521" t="inlineStr"/>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>component.comp_dronebay.name</t>
+          <t>component.comp_ram.name</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>蜂群无人机舱</t>
+          <t>液压刺锤</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>Swarm Drone Bay</t>
+          <t>Hydraulic Ram</t>
         </is>
       </c>
     </row>
@@ -27810,17 +27810,17 @@
       <c r="A1522" t="inlineStr"/>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>component.comp_dronebay.desc</t>
+          <t>component.comp_ram.desc</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>无人机：开火时放出伴飞无人机，无人机在母机附近自己索敌攻击；母机被毁时无人机一起坠毁。</t>
+          <t>近身格斗组件：贴近后猛刺，命中前方窄扇形里触及的全部敌人。</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>Drone carrier: firing launches escort drones that hunt around the parent machine; they go down with it.</t>
+          <t>Close-quarters melee: closes in and drives forward, hitting every enemy in a narrow arc in front.</t>
         </is>
       </c>
     </row>
@@ -27828,17 +27828,17 @@
       <c r="A1523" t="inlineStr"/>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>component.comp_corona.name</t>
+          <t>component.comp_shovel.name</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>电晕场</t>
+          <t>推铲</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>Corona Field</t>
+          <t>Push Blade</t>
         </is>
       </c>
     </row>
@@ -27846,17 +27846,17 @@
       <c r="A1524" t="inlineStr"/>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>component.comp_corona.desc</t>
+          <t>component.comp_shovel.desc</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>力场：以机身为中心放出一圈电晕脉冲，命中圈内全部敌人。</t>
+          <t>格斗·扇形：身前宽铲一扫并把敌人推开；适合搬运机。</t>
         </is>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>Field emitter: pulses a corona ring around the chassis, hitting every enemy inside.</t>
+          <t>Melee sweep: a wide scoop in front that shoves enemies back; suits haulers.</t>
         </is>
       </c>
     </row>
@@ -27864,17 +27864,17 @@
       <c r="A1525" t="inlineStr"/>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>component.comp_sprayer.name</t>
+          <t>component.comp_shovel.turret_reading</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>喷洒器</t>
+          <t>装在炮塔上读作“击退铲”：把近身的敌人推开 3 米。</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>Sprayer</t>
+          <t>On a turret it becomes a Repulsor Blade: shoves nearby enemies back 3 m.</t>
         </is>
       </c>
     </row>
@@ -27882,17 +27882,17 @@
       <c r="A1526" t="inlineStr"/>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>component.comp_sprayer.desc</t>
+          <t>component.comp_dronebay.name</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>布区·池：向目标脚下喷出一块区域，区域持续伤害站在里面的敌人。</t>
+          <t>蜂群无人机舱</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>Zone · pool: sprays a patch under the target that keeps damaging enemies standing in it.</t>
+          <t>Swarm Drone Bay</t>
         </is>
       </c>
     </row>
@@ -27900,17 +27900,17 @@
       <c r="A1527" t="inlineStr"/>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>component.turret.reason.dash</t>
+          <t>component.comp_dronebay.desc</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>“{0}”依赖机体位移，装不上固定底盘（炮塔）</t>
+          <t>无人机：开火时放出伴飞无人机，无人机在母机附近自己索敌攻击；母机被毁时无人机一起坠毁。</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>"{0}" relies on moving the chassis, so it cannot go on a fixed chassis (turret)</t>
+          <t>Drone carrier: firing launches escort drones that hunt around the parent machine; they go down with it.</t>
         </is>
       </c>
     </row>
@@ -27918,17 +27918,17 @@
       <c r="A1528" t="inlineStr"/>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>component.turret.option_blocked</t>
+          <t>component.comp_corona.name</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
         <is>
-          <t>{0} ✕ 装不上固定底盘</t>
+          <t>电晕场</t>
         </is>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>{0} ✕ not for a fixed chassis</t>
+          <t>Corona Field</t>
         </is>
       </c>
     </row>
@@ -27936,17 +27936,17 @@
       <c r="A1529" t="inlineStr"/>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>component.turret.reason.chassis_switch</t>
+          <t>component.comp_corona.desc</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>换成固定底盘前先卸下不兼容的组件：{0}</t>
+          <t>力场：以机身为中心放出一圈电晕脉冲，命中圈内全部敌人。</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>Remove incompatible components before switching to a fixed chassis: {0}</t>
+          <t>Field emitter: pulses a corona ring around the chassis, hitting every enemy inside.</t>
         </is>
       </c>
     </row>
@@ -27954,17 +27954,17 @@
       <c r="A1530" t="inlineStr"/>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>component.values_summary</t>
+          <t>component.comp_sprayer.name</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>载体 {0} · 基础伤害 {1} · 装配废料 {2} · 负载 {3}</t>
+          <t>喷洒器</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>Carrier {0} · Base damage {1} · Scrap to fit {2} · Load {3}</t>
+          <t>Sprayer</t>
         </is>
       </c>
     </row>
@@ -27972,17 +27972,17 @@
       <c r="A1531" t="inlineStr"/>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>component.source.base</t>
+          <t>component.comp_sprayer.desc</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>基础蓝图库：开局即可装配。</t>
+          <t>布区·池：向目标脚下喷出一块区域，区域持续伤害站在里面的敌人。</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>Base blueprint library: available from the start.</t>
+          <t>Zone · pool: sprays a patch under the target that keeps damaging enemies standing in it.</t>
         </is>
       </c>
     </row>
@@ -27990,17 +27990,17 @@
       <c r="A1532" t="inlineStr"/>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>chassis.fixed.name</t>
+          <t>component.comp_orbit.name</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>固定底盘</t>
+          <t>旋刃环</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>Fixed Chassis</t>
+          <t>Blade Ring</t>
         </is>
       </c>
     </row>
@@ -28008,17 +28008,17 @@
       <c r="A1533" t="inlineStr"/>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>chassis.fixed.desc</t>
+          <t>component.comp_orbit.desc</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>炮塔用的固定底盘：不能移动；冲刺器装不上，推铲装上后读作击退铲。</t>
+          <t>格斗·环绕：一圈旋刃绕着机身转，贴近后命中身边一整圈触及的全部敌人，不挑方向。</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>The turret's fixed chassis: it cannot move; dashers do not fit, and push blades become repulsor blades.</t>
+          <t>Melee orbit: a ring of blades spins around the chassis, hitting every enemy within reach all the way round.</t>
         </is>
       </c>
     </row>
@@ -28026,17 +28026,17 @@
       <c r="A1534" t="inlineStr"/>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>chassis.fixed.locked</t>
+          <t>component.comp_sentry.name</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>炮塔（固定底盘）随家园防御开放。</t>
+          <t>哨戒桩</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
         <is>
-          <t>Turrets (fixed chassis) open up with home defence.</t>
+          <t>Sentry Stake</t>
         </is>
       </c>
     </row>
@@ -28044,17 +28044,17 @@
       <c r="A1535" t="inlineStr"/>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>reading.detail.line</t>
+          <t>component.comp_sentry.desc</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
         <is>
-          <t>装在{0}上：{1}</t>
+          <t>无人机·定点：开火时在身前插下哨戒桩，桩子不动，自己打附近 7 米内的敌人；母机走远后旧桩到期消失，母机被毁时一起失效。</t>
         </is>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>On {0}: {1}</t>
+          <t>Emplaced drone: firing plants sentry stakes in front of the machine. They stay put and shoot enemies within 7 m; stakes left behind expire, and they fail if the parent is destroyed.</t>
         </is>
       </c>
     </row>
@@ -28062,17 +28062,17 @@
       <c r="A1536" t="inlineStr"/>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>reading.detail.title</t>
+          <t>component.comp_pulser.name</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>各载体读法</t>
+          <t>震荡脉冲器</t>
         </is>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>Readings by carrier</t>
+          <t>Shock Pulser</t>
         </is>
       </c>
     </row>
@@ -28080,17 +28080,17 @@
       <c r="A1537" t="inlineStr"/>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>reading.circuit.line</t>
+          <t>component.comp_pulser.desc</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>“{0}”装在{1}上：{2}</t>
+          <t>布区·脉冲：贴近后在自己脚下放出震荡脉冲：把正在打的敌人推开 0.8 米，脉冲区持续伤害圈内的全部敌人。</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>"{0}" on {1}: {2}</t>
+          <t>Zone pulse: up close, releases a shock pulse at its own feet: shoves the current target back 0.8 m, and the pulse zone keeps hurting every enemy inside.</t>
         </is>
       </c>
     </row>
@@ -28098,17 +28098,17 @@
       <c r="A1538" t="inlineStr"/>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>reading.circuit.named</t>
+          <t>component.comp_claw.name</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>“{0}”在这套装配上触发具名反应“{1}”（取代它的普通读法）</t>
+          <t>拆解钳</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>"{0}" triggers the named reaction "{1}" on this loadout (replacing its normal reading)</t>
+          <t>Dismantler Claw</t>
         </is>
       </c>
     </row>
@@ -28116,17 +28116,17 @@
       <c r="A1539" t="inlineStr"/>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>reading.circuit.none</t>
+          <t>component.comp_claw.desc</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>没有主组件：固件没有载体可读（先选主组件）</t>
+          <t>格斗·拆解：夹住正前方近身的敌人持续拆解（命中后再拆 3 次）。击毁时多回收废料随掉落体系开放。</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>No main component: firmware has no carrier to read (pick a main component first)</t>
+          <t>Melee dismantle: grips the enemy right in front and keeps taking it apart (3 more hits after the first). Extra salvage on kills opens with the loot system.</t>
         </is>
       </c>
     </row>
@@ -28134,17 +28134,17 @@
       <c r="A1540" t="inlineStr"/>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>reading.circuit.title</t>
+          <t>component.func_spikes.name</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>当前载体的读法</t>
+          <t>尖刺外装</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>Readings on the current carrier</t>
+          <t>Spike Plating</t>
         </is>
       </c>
     </row>
@@ -28152,17 +28152,17 @@
       <c r="A1541" t="inlineStr"/>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>reading.circuit.primary_carrier</t>
+          <t>component.func_spikes.desc</t>
         </is>
       </c>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>功能·反伤（被动）：被近身攻击时把 4 点 + 这一击伤害的一半反弹给攻击者；远程攻击不反伤。</t>
         </is>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>Utility · retaliate (passive): when hit in close combat, deals 4 + half of that hit back to the attacker. Ranged attacks are not reflected.</t>
         </is>
       </c>
     </row>
@@ -28170,17 +28170,17 @@
       <c r="A1542" t="inlineStr"/>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>reading.status_prefix</t>
+          <t>component.turret.reason.dash</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>附带</t>
+          <t>“{0}”依赖机体位移，装不上固定底盘（炮塔）</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
-          <t>Applies</t>
+          <t>"{0}" relies on moving the chassis, so it cannot go on a fixed chassis (turret)</t>
         </is>
       </c>
     </row>
@@ -28188,17 +28188,17 @@
       <c r="A1543" t="inlineStr"/>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>reading.turret_adjusted_prefix</t>
+          <t>component.turret.option_blocked</t>
         </is>
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>炮塔读法</t>
+          <t>{0} ✕ 装不上固定底盘</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>Turret reading</t>
+          <t>{0} ✕ not for a fixed chassis</t>
         </is>
       </c>
     </row>
@@ -28206,17 +28206,17 @@
       <c r="A1544" t="inlineStr"/>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>reading.turret_adjusted_line</t>
+          <t>component.turret.reason.chassis_switch</t>
         </is>
       </c>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>{0}：{1}</t>
+          <t>换成固定底盘前先卸下不兼容的组件：{0}</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>{0}: {1}</t>
+          <t>Remove incompatible components before switching to a fixed chassis: {0}</t>
         </is>
       </c>
     </row>
@@ -28224,17 +28224,17 @@
       <c r="A1545" t="inlineStr"/>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>component.turret.list_sep</t>
+          <t>component.values_summary</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>载体 {0} · 基础伤害 {1} · 装配废料 {2} · 负载 {3}</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>Carrier {0} · Base damage {1} · Scrap to fit {2} · Load {3}</t>
         </is>
       </c>
     </row>
@@ -28242,17 +28242,17 @@
       <c r="A1546" t="inlineStr"/>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>circuit.preview.summary</t>
+          <t>component.source.base</t>
         </is>
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>有效路径 {0} 条 · 每发伤害 {1}</t>
+          <t>基础蓝图库：开局即可装配。</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>{0} valid path(s) · Damage per hit {1}</t>
+          <t>Base blueprint library: available from the start.</t>
         </is>
       </c>
     </row>
@@ -28260,17 +28260,17 @@
       <c r="A1547" t="inlineStr"/>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>combat.overheat.notice</t>
+          <t>chassis.fixed.name</t>
         </is>
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>{0} 武器过热，降到 {1} 以下才能再开火</t>
+          <t>固定底盘</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>{0}'s weapon overheated; it can fire again below {1}</t>
+          <t>Fixed Chassis</t>
         </is>
       </c>
     </row>
@@ -28278,17 +28278,17 @@
       <c r="A1548" t="inlineStr"/>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>reaction.steam.name</t>
+          <t>chassis.fixed.desc</t>
         </is>
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>蒸汽</t>
+          <t>炮塔用的固定底盘：不能移动；冲刺器装不上，推铲装上后读作击退铲。</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>Steam</t>
+          <t>The turret's fixed chassis: it cannot move; dashers do not fit, and push blades become repulsor blades.</t>
         </is>
       </c>
     </row>
@@ -28296,17 +28296,17 @@
       <c r="A1549" t="inlineStr"/>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>reaction.steam.desc</t>
+          <t>chassis.fixed.locked</t>
         </is>
       </c>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>燃烧 + 浸湿：这一击伤害 ×1；消耗浸湿。</t>
+          <t>炮塔（固定底盘）随家园防御开放。</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>Burning + Soaked: this hit deals ×1 damage; consumes Soaked.</t>
+          <t>Turrets (fixed chassis) open up with home defence.</t>
         </is>
       </c>
     </row>
@@ -28314,17 +28314,17 @@
       <c r="A1550" t="inlineStr"/>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>reaction.deflagrate.name</t>
+          <t>reading.detail.line</t>
         </is>
       </c>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>爆燃</t>
+          <t>装在{0}上：{1}</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>Deflagration</t>
+          <t>On {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -28332,17 +28332,17 @@
       <c r="A1551" t="inlineStr"/>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>reaction.deflagrate.desc</t>
+          <t>reading.detail.title</t>
         </is>
       </c>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>燃烧 + 油污：这一击伤害 ×1.5；消耗油污；附加燃烧；在目标脚下留下燃烧区（3 秒）。</t>
+          <t>各载体读法</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>Burning + Oiled: this hit deals ×1.5 damage; consumes Oiled; applies Burning; leaves a Burning Zone underfoot (3s).</t>
+          <t>Readings by carrier</t>
         </is>
       </c>
     </row>
@@ -28350,17 +28350,17 @@
       <c r="A1552" t="inlineStr"/>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>reaction.deflagrate.residue</t>
+          <t>reading.circuit.line</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>燃烧区</t>
+          <t>“{0}”装在{1}上：{2}</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>Burning Zone</t>
+          <t>"{0}" on {1}: {2}</t>
         </is>
       </c>
     </row>
@@ -28368,17 +28368,17 @@
       <c r="A1553" t="inlineStr"/>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>reaction.conduct.name</t>
+          <t>reading.circuit.named</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>短路</t>
+          <t>“{0}”在这套装配上触发具名反应“{1}”（取代它的普通读法）</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>Short Circuit</t>
+          <t>"{0}" triggers the named reaction "{1}" on this loadout (replacing its normal reading)</t>
         </is>
       </c>
     </row>
@@ -28386,17 +28386,17 @@
       <c r="A1554" t="inlineStr"/>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>reaction.conduct.desc</t>
+          <t>reading.circuit.none</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>浸湿 + 电击：这一击伤害 ×1.3；消耗浸湿、电击。</t>
+          <t>没有主组件：固件没有载体可读（先选主组件）</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>Soaked + Shocked: this hit deals ×1.3 damage; consumes Soaked and Shocked.</t>
+          <t>No main component: firmware has no carrier to read (pick a main component first)</t>
         </is>
       </c>
     </row>
@@ -28404,17 +28404,17 @@
       <c r="A1555" t="inlineStr"/>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>reaction.shatter.name</t>
+          <t>reading.circuit.title</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>脆裂</t>
+          <t>当前载体的读法</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>Brittle Fracture</t>
+          <t>Readings on the current carrier</t>
         </is>
       </c>
     </row>
@@ -28422,17 +28422,17 @@
       <c r="A1556" t="inlineStr"/>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>reaction.shatter.desc</t>
+          <t>reading.circuit.primary_carrier</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>冻结 + 动能：这一击伤害 ×1.4；消耗冻结。</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>Frozen + Kinetic: this hit deals ×1.4 damage; consumes Frozen.</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
     </row>
@@ -28440,17 +28440,17 @@
       <c r="A1557" t="inlineStr"/>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>reaction.sticky.name</t>
+          <t>reading.status_prefix</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>粘滞</t>
+          <t>附带</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>Gum-Up</t>
+          <t>Applies</t>
         </is>
       </c>
     </row>
@@ -28458,17 +28458,17 @@
       <c r="A1558" t="inlineStr"/>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>reaction.sticky.desc</t>
+          <t>reading.turret_adjusted_prefix</t>
         </is>
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>腐蚀 + 胶膜：这一击伤害 ×1；消耗胶膜。</t>
+          <t>炮塔读法</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>Corroding + Glued: this hit deals ×1 damage; consumes Glued.</t>
+          <t>Turret reading</t>
         </is>
       </c>
     </row>
@@ -28476,17 +28476,17 @@
       <c r="A1559" t="inlineStr"/>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>reaction.electrolysis.name</t>
+          <t>reading.turret_adjusted_line</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>电解</t>
+          <t>{0}：{1}</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>Electrolysis</t>
+          <t>{0}: {1}</t>
         </is>
       </c>
     </row>
@@ -28494,17 +28494,17 @@
       <c r="A1560" t="inlineStr"/>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>reaction.electrolysis.desc</t>
+          <t>component.turret.list_sep</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>电击 + 腐蚀：这一击伤害 ×1.25；消耗腐蚀。</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>Shocked + Corroding: this hit deals ×1.25 damage; consumes Corroding.</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -28512,17 +28512,17 @@
       <c r="A1561" t="inlineStr"/>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>reaction.insulate.name</t>
+          <t>circuit.preview.summary</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>绝缘</t>
+          <t>有效路径 {0} 条 · 每发伤害 {1}</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>{0} valid path(s) · Damage per hit {1}</t>
         </is>
       </c>
     </row>
@@ -28530,17 +28530,17 @@
       <c r="A1562" t="inlineStr"/>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>reaction.insulate.desc</t>
+          <t>combat.overheat.notice</t>
         </is>
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>电击 + 油污：这一击伤害 ×0.6；消耗电击。</t>
+          <t>{0} 武器过热，降到 {1} 以下才能再开火</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Shocked + Oiled: this hit deals ×0.6 damage; consumes Shocked.</t>
+          <t>{0}'s weapon overheated; it can fire again below {1}</t>
         </is>
       </c>
     </row>
@@ -28548,17 +28548,17 @@
       <c r="A1563" t="inlineStr"/>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>reaction.thermalshock.name</t>
+          <t>reaction.steam.name</t>
         </is>
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>热震</t>
+          <t>蒸汽</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>Thermal Shock</t>
+          <t>Steam</t>
         </is>
       </c>
     </row>
@@ -28566,17 +28566,17 @@
       <c r="A1564" t="inlineStr"/>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>reaction.thermalshock.desc</t>
+          <t>reaction.steam.desc</t>
         </is>
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>燃烧 + 冻结：这一击伤害 ×1.4；消耗冻结。</t>
+          <t>燃烧 + 浸湿：这一击伤害 ×1；消耗浸湿。</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>Burning + Frozen: this hit deals ×1.4 damage; consumes Frozen.</t>
+          <t>Burning + Soaked: this hit deals ×1 damage; consumes Soaked.</t>
         </is>
       </c>
     </row>
@@ -28584,17 +28584,17 @@
       <c r="A1565" t="inlineStr"/>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>reaction.causticburn.name</t>
+          <t>reaction.deflagrate.name</t>
         </is>
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>腐蚀灼烧</t>
+          <t>爆燃</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>Corrosive Burn</t>
+          <t>Deflagration</t>
         </is>
       </c>
     </row>
@@ -28602,17 +28602,17 @@
       <c r="A1566" t="inlineStr"/>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>reaction.causticburn.desc</t>
+          <t>reaction.deflagrate.desc</t>
         </is>
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>燃烧 + 腐蚀：这一击伤害 ×1.1；消耗腐蚀；附加燃烧。</t>
+          <t>燃烧 + 油污：这一击伤害 ×1.5；消耗油污；附加燃烧；在目标脚下留下燃烧区（3 秒）。</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>Burning + Corroding: this hit deals ×1.1 damage; consumes Corroding; applies Burning.</t>
+          <t>Burning + Oiled: this hit deals ×1.5 damage; consumes Oiled; applies Burning; leaves a Burning Zone underfoot (3s).</t>
         </is>
       </c>
     </row>
@@ -28620,17 +28620,17 @@
       <c r="A1567" t="inlineStr"/>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>reaction.hemolysis.name</t>
+          <t>reaction.deflagrate.residue</t>
         </is>
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>回路溶断</t>
+          <t>燃烧区</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>Circuit Meltdown</t>
+          <t>Burning Zone</t>
         </is>
       </c>
     </row>
@@ -28638,17 +28638,17 @@
       <c r="A1568" t="inlineStr"/>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>reaction.hemolysis.desc</t>
+          <t>reaction.conduct.name</t>
         </is>
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>回收 + 腐蚀：这一击伤害 ×1.3；消耗回收。</t>
+          <t>短路</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>Reclaiming + Corroding: this hit deals ×1.3 damage; consumes Reclaiming.</t>
+          <t>Short Circuit</t>
         </is>
       </c>
     </row>
@@ -28656,17 +28656,17 @@
       <c r="A1569" t="inlineStr"/>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>reaction.syrup.name</t>
+          <t>reaction.conduct.desc</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>胶结</t>
+          <t>浸湿 + 电击：这一击伤害 ×1.3；消耗浸湿、电击。</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>Binding</t>
+          <t>Soaked + Shocked: this hit deals ×1.3 damage; consumes Soaked and Shocked.</t>
         </is>
       </c>
     </row>
@@ -28674,17 +28674,17 @@
       <c r="A1570" t="inlineStr"/>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>reaction.syrup.desc</t>
+          <t>reaction.shatter.name</t>
         </is>
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>浸湿 + 胶膜：这一击伤害 ×1.15；消耗胶膜。</t>
+          <t>脆裂</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>Soaked + Glued: this hit deals ×1.15 damage; consumes Glued.</t>
+          <t>Brittle Fracture</t>
         </is>
       </c>
     </row>
@@ -28692,17 +28692,17 @@
       <c r="A1571" t="inlineStr"/>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>reaction.dissolve.name</t>
+          <t>reaction.shatter.desc</t>
         </is>
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>溶蚀</t>
+          <t>冻结 + 动能：这一击伤害 ×1.4；消耗冻结。</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>Etching</t>
+          <t>Frozen + Kinetic: this hit deals ×1.4 damage; consumes Frozen.</t>
         </is>
       </c>
     </row>
@@ -28710,17 +28710,17 @@
       <c r="A1572" t="inlineStr"/>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>reaction.dissolve.desc</t>
+          <t>reaction.sticky.name</t>
         </is>
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>腐蚀 + 油污：这一击伤害 ×1.2；消耗油污。</t>
+          <t>粘滞</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>Corroding + Oiled: this hit deals ×1.2 damage; consumes Oiled.</t>
+          <t>Gum-Up</t>
         </is>
       </c>
     </row>
@@ -28728,17 +28728,17 @@
       <c r="A1573" t="inlineStr"/>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>reaction.annihilate.name</t>
+          <t>reaction.sticky.desc</t>
         </is>
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>湮灭</t>
+          <t>腐蚀 + 胶膜：这一击伤害 ×1；消耗胶膜。</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>Annihilation</t>
+          <t>Corroding + Glued: this hit deals ×1 damage; consumes Glued.</t>
         </is>
       </c>
     </row>
@@ -28746,17 +28746,17 @@
       <c r="A1574" t="inlineStr"/>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>reaction.annihilate.desc</t>
+          <t>reaction.electrolysis.name</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>偏折 + 处决：这一击伤害 ×1.6；消耗偏折、处决。</t>
+          <t>电解</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>Deflecting + Execute: this hit deals ×1.6 damage; consumes Deflecting and Execute.</t>
+          <t>Electrolysis</t>
         </is>
       </c>
     </row>
@@ -28764,17 +28764,17 @@
       <c r="A1575" t="inlineStr"/>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>reaction.vitrify.name</t>
+          <t>reaction.electrolysis.desc</t>
         </is>
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>玻化</t>
+          <t>电击 + 腐蚀：这一击伤害 ×1.25；消耗腐蚀。</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>Vitrification</t>
+          <t>Shocked + Corroding: this hit deals ×1.25 damage; consumes Corroding.</t>
         </is>
       </c>
     </row>
@@ -28782,17 +28782,17 @@
       <c r="A1576" t="inlineStr"/>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>reaction.vitrify.desc</t>
+          <t>reaction.insulate.name</t>
         </is>
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>扬尘 + 燃烧：这一击伤害 ×1.3；消耗扬尘。</t>
+          <t>绝缘</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>Dusted + Burning: this hit deals ×1.3 damage; consumes Dusted.</t>
+          <t>Insulation</t>
         </is>
       </c>
     </row>
@@ -28800,17 +28800,17 @@
       <c r="A1577" t="inlineStr"/>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>reaction.mudify.name</t>
+          <t>reaction.insulate.desc</t>
         </is>
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>淤塞</t>
+          <t>电击 + 油污：这一击伤害 ×0.6；消耗电击。</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Clogging</t>
+          <t>Shocked + Oiled: this hit deals ×0.6 damage; consumes Shocked.</t>
         </is>
       </c>
     </row>
@@ -28818,17 +28818,17 @@
       <c r="A1578" t="inlineStr"/>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>reaction.mudify.desc</t>
+          <t>reaction.thermalshock.name</t>
         </is>
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>扬尘 + 浸湿：这一击伤害 ×0.9；消耗浸湿。</t>
+          <t>热震</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Dusted + Soaked: this hit deals ×0.9 damage; consumes Soaked.</t>
+          <t>Thermal Shock</t>
         </is>
       </c>
     </row>
@@ -28836,17 +28836,17 @@
       <c r="A1579" t="inlineStr"/>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>reaction.sepsis.name</t>
+          <t>reaction.thermalshock.desc</t>
         </is>
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>连锁锈蚀</t>
+          <t>燃烧 + 冻结：这一击伤害 ×1.4；消耗冻结。</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>Cascading Rust</t>
+          <t>Burning + Frozen: this hit deals ×1.4 damage; consumes Frozen.</t>
         </is>
       </c>
     </row>
@@ -28854,17 +28854,17 @@
       <c r="A1580" t="inlineStr"/>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>reaction.sepsis.desc</t>
+          <t>reaction.causticburn.name</t>
         </is>
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>污染 + 回收：这一击伤害 ×1.35；消耗污染。</t>
+          <t>腐蚀灼烧</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>Contaminated + Reclaiming: this hit deals ×1.35 damage; consumes Contaminated.</t>
+          <t>Corrosive Burn</t>
         </is>
       </c>
     </row>
@@ -28872,17 +28872,17 @@
       <c r="A1581" t="inlineStr"/>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>reaction.marktag.name</t>
+          <t>reaction.causticburn.desc</t>
         </is>
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>标记跳转</t>
+          <t>燃烧 + 腐蚀：这一击伤害 ×1.1；消耗腐蚀；附加燃烧。</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>Mark Jump</t>
+          <t>Burning + Corroding: this hit deals ×1.1 damage; consumes Corroding; applies Burning.</t>
         </is>
       </c>
     </row>
@@ -28890,17 +28890,17 @@
       <c r="A1582" t="inlineStr"/>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>reaction.marktag.desc</t>
+          <t>reaction.hemolysis.name</t>
         </is>
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>标记器与连射器 / 切割束同装、接入时信号核带上标记跳转：命中会额外跳向已被标记的邻近敌人。AI 驾驶时不会触发。</t>
+          <t>回路溶断</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>With a Marker and a Repeater or Cutting Beam fitted and Mark Jump in the uplinked Signal Core, hits also leap to nearby marked enemies. Never triggers under AI control.</t>
+          <t>Circuit Meltdown</t>
         </is>
       </c>
     </row>
@@ -28908,17 +28908,17 @@
       <c r="A1583" t="inlineStr"/>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>reaction.meltoverload.name</t>
+          <t>reaction.hemolysis.desc</t>
         </is>
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>熔穿过载</t>
+          <t>回收 + 腐蚀：这一击伤害 ×1.3；消耗回收。</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>Meltdown Overload</t>
+          <t>Reclaiming + Corroding: this hit deals ×1.3 damage; consumes Reclaiming.</t>
         </is>
       </c>
     </row>
@@ -28926,17 +28926,17 @@
       <c r="A1584" t="inlineStr"/>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>reaction.meltoverload.desc</t>
+          <t>reaction.syrup.name</t>
         </is>
       </c>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>接入铸造重炮机、信号核带上过载时触发：额外穿甲，热量代价大幅提高。AI 驾驶时不会触发。</t>
+          <t>胶结</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>Triggers when you uplink into a Foundry Cannon unit with Overload in the Signal Core: extra armour piercing at a much higher heat cost. Never triggers under AI control.</t>
+          <t>Binding</t>
         </is>
       </c>
     </row>
@@ -28944,17 +28944,17 @@
       <c r="A1585" t="inlineStr"/>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>reaction.batch.act1</t>
+          <t>reaction.syrup.desc</t>
         </is>
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>第一幕</t>
+          <t>浸湿 + 胶膜：这一击伤害 ×1.15；消耗胶膜。</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Soaked + Glued: this hit deals ×1.15 damage; consumes Glued.</t>
         </is>
       </c>
     </row>
@@ -28962,17 +28962,17 @@
       <c r="A1586" t="inlineStr"/>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>reaction.batch.clarity</t>
+          <t>reaction.dissolve.name</t>
         </is>
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>澄净</t>
+          <t>溶蚀</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>the Pristine</t>
+          <t>Etching</t>
         </is>
       </c>
     </row>
@@ -28980,17 +28980,17 @@
       <c r="A1587" t="inlineStr"/>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>reaction.batch.overclock</t>
+          <t>reaction.dissolve.desc</t>
         </is>
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>超频</t>
+          <t>腐蚀 + 油污：这一击伤害 ×1.2；消耗油污。</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>the Overclocked</t>
+          <t>Corroding + Oiled: this hit deals ×1.2 damage; consumes Oiled.</t>
         </is>
       </c>
     </row>
@@ -28998,17 +28998,17 @@
       <c r="A1588" t="inlineStr"/>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>reaction.batch.cross</t>
+          <t>reaction.annihilate.name</t>
         </is>
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>跨阵营</t>
+          <t>湮灭</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Cross-faction</t>
+          <t>Annihilation</t>
         </is>
       </c>
     </row>
@@ -29016,17 +29016,17 @@
       <c r="A1589" t="inlineStr"/>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>reaction.unnamed</t>
+          <t>reaction.annihilate.desc</t>
         </is>
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>未知反应</t>
+          <t>偏折 + 处决：这一击伤害 ×1.6；消耗偏折、处决。</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>Unknown reaction</t>
+          <t>Deflecting + Execute: this hit deals ×1.6 damage; consumes Deflecting and Execute.</t>
         </is>
       </c>
     </row>
@@ -29034,17 +29034,17 @@
       <c r="A1590" t="inlineStr"/>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>reaction.cue</t>
+          <t>reaction.vitrify.name</t>
         </is>
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>{0}！</t>
+          <t>玻化</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>{0}!</t>
+          <t>Vitrification</t>
         </is>
       </c>
     </row>
@@ -29052,17 +29052,17 @@
       <c r="A1591" t="inlineStr"/>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>feedback.tag.reaction</t>
+          <t>reaction.vitrify.desc</t>
         </is>
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>反应</t>
+          <t>扬尘 + 燃烧：这一击伤害 ×1.3；消耗扬尘。</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Dusted + Burning: this hit deals ×1.3 damage; consumes Dusted.</t>
         </is>
       </c>
     </row>
@@ -29070,17 +29070,17 @@
       <c r="A1592" t="inlineStr"/>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>tag.hover.title</t>
+          <t>reaction.mudify.name</t>
         </is>
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>状态标签</t>
+          <t>淤塞</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>Status tags</t>
+          <t>Clogging</t>
         </is>
       </c>
     </row>
@@ -29088,17 +29088,17 @@
       <c r="A1593" t="inlineStr"/>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>tag.hover.line</t>
+          <t>reaction.mudify.desc</t>
         </is>
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>{0} {1}　剩余 {2} 秒　×{3}</t>
+          <t>扬尘 + 浸湿：这一击伤害 ×0.9；消耗浸湿。</t>
         </is>
       </c>
       <c r="D1593" t="inlineStr">
         <is>
-          <t>{0} {1}  {2}s left  ×{3}</t>
+          <t>Dusted + Soaked: this hit deals ×0.9 damage; consumes Soaked.</t>
         </is>
       </c>
     </row>
@@ -29106,17 +29106,17 @@
       <c r="A1594" t="inlineStr"/>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>tag.hover.more</t>
+          <t>reaction.sepsis.name</t>
         </is>
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>另有 {0} 个标签</t>
+          <t>连锁锈蚀</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>{0} more tags</t>
+          <t>Cascading Rust</t>
         </is>
       </c>
     </row>
@@ -29124,17 +29124,17 @@
       <c r="A1595" t="inlineStr"/>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>reaction.popup.many</t>
+          <t>reaction.sepsis.desc</t>
         </is>
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>{0} ×{1}</t>
+          <t>污染 + 回收：这一击伤害 ×1.35；消耗污染。</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>{0} ×{1}</t>
+          <t>Contaminated + Reclaiming: this hit deals ×1.35 damage; consumes Contaminated.</t>
         </is>
       </c>
     </row>
@@ -29142,17 +29142,17 @@
       <c r="A1596" t="inlineStr"/>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>reaction.popup.first</t>
+          <t>reaction.marktag.name</t>
         </is>
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>新反应：{0}！</t>
+          <t>标记跳转</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>New reaction: {0}!</t>
+          <t>Mark Jump</t>
         </is>
       </c>
     </row>
@@ -29160,17 +29160,17 @@
       <c r="A1597" t="inlineStr"/>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>reading.popup.zone</t>
+          <t>reaction.marktag.desc</t>
         </is>
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>区域展开</t>
+          <t>标记器与连射器 / 切割束同装、接入时信号核带上标记跳转：命中会额外跳向已被标记的邻近敌人。AI 驾驶时不会触发。</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>Zone deployed</t>
+          <t>With a Marker and a Repeater or Cutting Beam fitted and Mark Jump in the uplinked Signal Core, hits also leap to nearby marked enemies. Never triggers under AI control.</t>
         </is>
       </c>
     </row>
@@ -29178,17 +29178,17 @@
       <c r="A1598" t="inlineStr"/>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>reading.popup.echo</t>
+          <t>reaction.meltoverload.name</t>
         </is>
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>回波</t>
+          <t>熔穿过载</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Meltdown Overload</t>
         </is>
       </c>
     </row>
@@ -29196,17 +29196,17 @@
       <c r="A1599" t="inlineStr"/>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>reading.popup.drone</t>
+          <t>reaction.meltoverload.desc</t>
         </is>
       </c>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>无人机出动</t>
+          <t>接入铸造重炮机、信号核带上过载时触发：额外穿甲，热量代价大幅提高。AI 驾驶时不会触发。</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>Drone launched</t>
+          <t>Triggers when you uplink into a Foundry Cannon unit with Overload in the Signal Core: extra armour piercing at a much higher heat cost. Never triggers under AI control.</t>
         </is>
       </c>
     </row>
@@ -29214,17 +29214,17 @@
       <c r="A1600" t="inlineStr"/>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>reaction.attr.none</t>
+          <t>reaction.batch.act1</t>
         </is>
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>本场没有打出反应</t>
+          <t>第一幕</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>No reactions this time</t>
+          <t>Act I</t>
         </is>
       </c>
     </row>
@@ -29232,17 +29232,17 @@
       <c r="A1601" t="inlineStr"/>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>reaction.attr.item</t>
+          <t>reaction.batch.clarity</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>{0} {1}%（{2} 次）</t>
+          <t>澄净</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>{0} {1}% ({2}×)</t>
+          <t>the Pristine</t>
         </is>
       </c>
     </row>
@@ -29250,17 +29250,17 @@
       <c r="A1602" t="inlineStr"/>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>reaction.attr.summary</t>
+          <t>reaction.batch.overclock</t>
         </is>
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>反应伤害占比：{0}</t>
+          <t>超频</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>Reaction damage share: {0}</t>
+          <t>the Overclocked</t>
         </is>
       </c>
     </row>
@@ -29268,17 +29268,17 @@
       <c r="A1603" t="inlineStr"/>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>reaction.attr.sep</t>
+          <t>reaction.batch.cross</t>
         </is>
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>跨阵营</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>Cross-faction</t>
         </is>
       </c>
     </row>
@@ -29286,17 +29286,17 @@
       <c r="A1604" t="inlineStr"/>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>reaction.attr.title_raid</t>
+          <t>reaction.unnamed</t>
         </is>
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>突袭 · {0}</t>
+          <t>未知反应</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>Raid · {0}</t>
+          <t>Unknown reaction</t>
         </is>
       </c>
     </row>
@@ -29304,17 +29304,17 @@
       <c r="A1605" t="inlineStr"/>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>reaction.attr.title_expedition</t>
+          <t>reaction.cue</t>
         </is>
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>远征 · {0} 第 {1} 次</t>
+          <t>{0}！</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>Expedition · {0} #{1}</t>
+          <t>{0}!</t>
         </is>
       </c>
     </row>
@@ -29322,17 +29322,17 @@
       <c r="A1606" t="inlineStr"/>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>reaction.attr.ongoing</t>
+          <t>feedback.tag.reaction</t>
         </is>
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>进行中（{0} 起）</t>
+          <t>反应</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>In progress (since {0})</t>
+          <t>Reaction</t>
         </is>
       </c>
     </row>
@@ -29340,17 +29340,17 @@
       <c r="A1607" t="inlineStr"/>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>reaction.attr.ended</t>
+          <t>tag.hover.title</t>
         </is>
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>{0} ～ {1}</t>
+          <t>状态标签</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>{0} – {1}</t>
+          <t>Status tags</t>
         </is>
       </c>
     </row>
@@ -29358,17 +29358,17 @@
       <c r="A1608" t="inlineStr"/>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>reaction.attr.total</t>
+          <t>tag.hover.line</t>
         </is>
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>敌方共受伤害 {0}</t>
+          <t>{0} {1}　剩余 {2} 秒　×{3}</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Total damage to enemies {0}</t>
+          <t>{0} {1}  {2}s left  ×{3}</t>
         </is>
       </c>
     </row>
@@ -29376,17 +29376,17 @@
       <c r="A1609" t="inlineStr"/>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>reaction.log.unknown</t>
+          <t>tag.hover.more</t>
         </is>
       </c>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>未知单位</t>
+          <t>另有 {0} 个标签</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Unknown unit</t>
+          <t>{0} more tags</t>
         </is>
       </c>
     </row>
@@ -29394,17 +29394,17 @@
       <c r="A1610" t="inlineStr"/>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>reaction.log.machine</t>
+          <t>reaction.popup.many</t>
         </is>
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>机器</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
     </row>
@@ -29412,17 +29412,17 @@
       <c r="A1611" t="inlineStr"/>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>reaction.log.machine_n</t>
+          <t>reaction.popup.first</t>
         </is>
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>机器 {0}</t>
+          <t>新反应：{0}！</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>Machine {0}</t>
+          <t>New reaction: {0}!</t>
         </is>
       </c>
     </row>
@@ -29430,17 +29430,17 @@
       <c r="A1612" t="inlineStr"/>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>reaction.log.turret</t>
+          <t>reading.popup.zone</t>
         </is>
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>炮塔</t>
+          <t>区域展开</t>
         </is>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Turret</t>
+          <t>Zone deployed</t>
         </is>
       </c>
     </row>
@@ -29448,17 +29448,17 @@
       <c r="A1613" t="inlineStr"/>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>reaction.log.structure</t>
+          <t>reading.popup.thorns</t>
         </is>
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>建筑</t>
+          <t>反伤</t>
         </is>
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Retaliation</t>
         </is>
       </c>
     </row>
@@ -29466,17 +29466,17 @@
       <c r="A1614" t="inlineStr"/>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>reaction.log.enemy</t>
+          <t>reading.popup.echo</t>
         </is>
       </c>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>敌方单位</t>
+          <t>回波</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
-          <t>Enemy unit</t>
+          <t>Echo</t>
         </is>
       </c>
     </row>
@@ -29484,17 +29484,17 @@
       <c r="A1615" t="inlineStr"/>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>reaction.log.no_firmware</t>
+          <t>reading.popup.drone</t>
         </is>
       </c>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>无固件</t>
+          <t>无人机出动</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
-          <t>no firmware</t>
+          <t>Drone launched</t>
         </is>
       </c>
     </row>
@@ -29502,17 +29502,17 @@
       <c r="A1616" t="inlineStr"/>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>reaction.log.first</t>
+          <t>reaction.attr.none</t>
         </is>
       </c>
       <c r="C1616" t="inlineStr">
         <is>
-          <t>{0}（首次）</t>
+          <t>本场没有打出反应</t>
         </is>
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>{0} (first)</t>
+          <t>No reactions this time</t>
         </is>
       </c>
     </row>
@@ -29520,17 +29520,17 @@
       <c r="A1617" t="inlineStr"/>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>reaction.log.line</t>
+          <t>reaction.attr.item</t>
         </is>
       </c>
       <c r="C1617" t="inlineStr">
         <is>
-          <t>{0}　{1}　{2}［{3}］→ {4}</t>
+          <t>{0} {1}%（{2} 次）</t>
         </is>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
-          <t>{0}  {1}  {2} [{3}] → {4}</t>
+          <t>{0} {1}% ({2}×)</t>
         </is>
       </c>
     </row>
@@ -29538,17 +29538,17 @@
       <c r="A1618" t="inlineStr"/>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>reaction.panel.title</t>
+          <t>reaction.attr.summary</t>
         </is>
       </c>
       <c r="C1618" t="inlineStr">
         <is>
-          <t>反应记录</t>
+          <t>反应伤害占比：{0}</t>
         </is>
       </c>
       <c r="D1618" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Reaction damage share: {0}</t>
         </is>
       </c>
     </row>
@@ -29556,17 +29556,17 @@
       <c r="A1619" t="inlineStr"/>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>reaction.panel.tab_log</t>
+          <t>reaction.attr.sep</t>
         </is>
       </c>
       <c r="C1619" t="inlineStr">
         <is>
-          <t>反应日志</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
-          <t>Reaction log</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -29574,17 +29574,17 @@
       <c r="A1620" t="inlineStr"/>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>reaction.panel.tab_attr</t>
+          <t>reaction.attr.title_raid</t>
         </is>
       </c>
       <c r="C1620" t="inlineStr">
         <is>
-          <t>伤害归因</t>
+          <t>突袭 · {0}</t>
         </is>
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>Damage share</t>
+          <t>Raid · {0}</t>
         </is>
       </c>
     </row>
@@ -29592,17 +29592,17 @@
       <c r="A1621" t="inlineStr"/>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>reaction.panel.tab_codex</t>
+          <t>reaction.attr.title_expedition</t>
         </is>
       </c>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>反应图鉴</t>
+          <t>远征 · {0} 第 {1} 次</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">
         <is>
-          <t>Reaction codex</t>
+          <t>Expedition · {0} #{1}</t>
         </is>
       </c>
     </row>
@@ -29610,17 +29610,17 @@
       <c r="A1622" t="inlineStr"/>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>reaction.panel.filter_all</t>
+          <t>reaction.attr.ongoing</t>
         </is>
       </c>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>进行中（{0} 起）</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>In progress (since {0})</t>
         </is>
       </c>
     </row>
@@ -29628,17 +29628,17 @@
       <c r="A1623" t="inlineStr"/>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>reaction.panel.filter_expedition</t>
+          <t>reaction.attr.ended</t>
         </is>
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>远征</t>
+          <t>{0} ～ {1}</t>
         </is>
       </c>
       <c r="D1623" t="inlineStr">
         <is>
-          <t>Expeditions</t>
+          <t>{0} – {1}</t>
         </is>
       </c>
     </row>
@@ -29646,17 +29646,17 @@
       <c r="A1624" t="inlineStr"/>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>reaction.panel.filter_raid</t>
+          <t>reaction.attr.total</t>
         </is>
       </c>
       <c r="C1624" t="inlineStr">
         <is>
-          <t>突袭</t>
+          <t>敌方共受伤害 {0}</t>
         </is>
       </c>
       <c r="D1624" t="inlineStr">
         <is>
-          <t>Raids</t>
+          <t>Total damage to enemies {0}</t>
         </is>
       </c>
     </row>
@@ -29664,17 +29664,17 @@
       <c r="A1625" t="inlineStr"/>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>reaction.panel.empty_log</t>
+          <t>reaction.log.unknown</t>
         </is>
       </c>
       <c r="C1625" t="inlineStr">
         <is>
-          <t>还没有反应记录（只记本次载入之后的）</t>
+          <t>未知单位</t>
         </is>
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>No reactions yet (only since this load)</t>
+          <t>Unknown unit</t>
         </is>
       </c>
     </row>
@@ -29682,17 +29682,17 @@
       <c r="A1626" t="inlineStr"/>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>reaction.panel.empty_attr</t>
+          <t>reaction.log.machine</t>
         </is>
       </c>
       <c r="C1626" t="inlineStr">
         <is>
-          <t>还没有远征或突袭的反应伤害记录</t>
+          <t>机器</t>
         </is>
       </c>
       <c r="D1626" t="inlineStr">
         <is>
-          <t>No expedition or raid damage records yet</t>
+          <t>Machine</t>
         </is>
       </c>
     </row>
@@ -29700,17 +29700,17 @@
       <c r="A1627" t="inlineStr"/>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>reaction.panel.log_hint</t>
+          <t>reaction.log.machine_n</t>
         </is>
       </c>
       <c r="C1627" t="inlineStr">
         <is>
-          <t>最近 {0} 条，只保留本次载入之后的；按 {act:Cancel} 关闭</t>
+          <t>机器 {0}</t>
         </is>
       </c>
       <c r="D1627" t="inlineStr">
         <is>
-          <t>Last {0} entries since this load; press {act:Cancel} to close</t>
+          <t>Machine {0}</t>
         </is>
       </c>
     </row>
@@ -29718,17 +29718,17 @@
       <c r="A1628" t="inlineStr"/>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>reaction.panel.attr_hint</t>
+          <t>reaction.log.turret</t>
         </is>
       </c>
       <c r="C1628" t="inlineStr">
         <is>
-          <t>占比 = 反应额外伤害 / 这一场敌方受到的全部伤害；按 {act:Cancel} 关闭</t>
+          <t>炮塔</t>
         </is>
       </c>
       <c r="D1628" t="inlineStr">
         <is>
-          <t>Share = extra reaction damage / all damage enemies took; press {act:Cancel} to close</t>
+          <t>Turret</t>
         </is>
       </c>
     </row>
@@ -29736,17 +29736,17 @@
       <c r="A1629" t="inlineStr"/>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>reaction.panel.codex_hint</t>
+          <t>reaction.log.structure</t>
         </is>
       </c>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>已解锁 {0} / {1}：本存档里第一次打出某条反应时解锁；按 {act:Cancel} 关闭</t>
+          <t>建筑</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>Unlocked {0}/{1}: an entry unlocks the first time you trigger it in this save; press {act:Cancel} to close</t>
+          <t>Structure</t>
         </is>
       </c>
     </row>
@@ -29754,17 +29754,17 @@
       <c r="A1630" t="inlineStr"/>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>reaction.panel.count</t>
+          <t>reaction.log.enemy</t>
         </is>
       </c>
       <c r="C1630" t="inlineStr">
         <is>
-          <t>{0} 条</t>
+          <t>敌方单位</t>
         </is>
       </c>
       <c r="D1630" t="inlineStr">
         <is>
-          <t>{0} entries</t>
+          <t>Enemy unit</t>
         </is>
       </c>
     </row>
@@ -29772,17 +29772,17 @@
       <c r="A1631" t="inlineStr"/>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>stats.panel.title</t>
+          <t>reaction.log.no_firmware</t>
         </is>
       </c>
       <c r="C1631" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>无固件</t>
         </is>
       </c>
       <c r="D1631" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>no firmware</t>
         </is>
       </c>
     </row>
@@ -29790,17 +29790,17 @@
       <c r="A1632" t="inlineStr"/>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>stats.panel.section_combat</t>
+          <t>reaction.log.first</t>
         </is>
       </c>
       <c r="C1632" t="inlineStr">
         <is>
-          <t>战斗 · 反应伤害归因</t>
+          <t>{0}（首次）</t>
         </is>
       </c>
       <c r="D1632" t="inlineStr">
         <is>
-          <t>Combat · Reaction damage share</t>
+          <t>{0} (first)</t>
         </is>
       </c>
     </row>
@@ -29808,17 +29808,17 @@
       <c r="A1633" t="inlineStr"/>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>stats.panel.count</t>
+          <t>reaction.log.line</t>
         </is>
       </c>
       <c r="C1633" t="inlineStr">
         <is>
-          <t>{0} 场</t>
+          <t>{0}　{1}　{2}［{3}］→ {4}</t>
         </is>
       </c>
       <c r="D1633" t="inlineStr">
         <is>
-          <t>{0} sessions</t>
+          <t>{0}  {1}  {2} [{3}] → {4}</t>
         </is>
       </c>
     </row>
@@ -29826,17 +29826,17 @@
       <c r="A1634" t="inlineStr"/>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>stats.panel.totals_title</t>
+          <t>reaction.panel.title</t>
         </is>
       </c>
       <c r="C1634" t="inlineStr">
         <is>
-          <t>累计（{0} 场）</t>
+          <t>反应记录</t>
         </is>
       </c>
       <c r="D1634" t="inlineStr">
         <is>
-          <t>Totals ({0} sessions)</t>
+          <t>Reactions</t>
         </is>
       </c>
     </row>
@@ -29844,17 +29844,17 @@
       <c r="A1635" t="inlineStr"/>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>stats.panel.totals_line</t>
+          <t>reaction.panel.tab_log</t>
         </is>
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>敌方共受伤害 {0}，其中反应额外伤害占 {1}%</t>
+          <t>反应日志</t>
         </is>
       </c>
       <c r="D1635" t="inlineStr">
         <is>
-          <t>Enemies took {0} damage in total; reaction bonus damage was {1}%</t>
+          <t>Reaction log</t>
         </is>
       </c>
     </row>
@@ -29862,17 +29862,17 @@
       <c r="A1636" t="inlineStr"/>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>stats.panel.sessions_title</t>
+          <t>reaction.panel.tab_attr</t>
         </is>
       </c>
       <c r="C1636" t="inlineStr">
         <is>
-          <t>每场明细</t>
+          <t>伤害归因</t>
         </is>
       </c>
       <c r="D1636" t="inlineStr">
         <is>
-          <t>Per session</t>
+          <t>Damage share</t>
         </is>
       </c>
     </row>
@@ -29880,17 +29880,17 @@
       <c r="A1637" t="inlineStr"/>
       <c r="B1637" t="inlineStr">
         <is>
-          <t>stats.panel.empty</t>
+          <t>reaction.panel.tab_codex</t>
         </is>
       </c>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>还没有远征或突袭的战斗统计。出一次远征并在战斗中打出反应后，这里会按反应列出伤害占比。</t>
+          <t>反应图鉴</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
         <is>
-          <t>No expedition or raid combat stats yet. Go on an expedition and trigger reactions in combat to see each reaction's damage share here.</t>
+          <t>Reaction codex</t>
         </is>
       </c>
     </row>
@@ -29898,17 +29898,17 @@
       <c r="A1638" t="inlineStr"/>
       <c r="B1638" t="inlineStr">
         <is>
-          <t>stats.panel.hint</t>
+          <t>reaction.panel.filter_all</t>
         </is>
       </c>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>只统计远征与突袭（家园平时的训练战斗不计），最近 {0} 场随存档保存；占比 = 反应额外伤害 / 敌方受到的全部伤害；按 {act:Cancel} 关闭</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D1638" t="inlineStr">
         <is>
-          <t>Only expeditions and raids count (training at home does not); the last {0} sessions are saved; share = reaction bonus damage / all damage enemies took; press {act:Cancel} to close</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -29916,17 +29916,17 @@
       <c r="A1639" t="inlineStr"/>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>pause.stats</t>
+          <t>reaction.panel.filter_expedition</t>
         </is>
       </c>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>远征</t>
         </is>
       </c>
       <c r="D1639" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Expeditions</t>
         </is>
       </c>
     </row>
@@ -29934,17 +29934,17 @@
       <c r="A1640" t="inlineStr"/>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>reaction.codex.locked_name</t>
+          <t>reaction.panel.filter_raid</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>突袭</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Raids</t>
         </is>
       </c>
     </row>
@@ -29952,17 +29952,17 @@
       <c r="A1641" t="inlineStr"/>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>reaction.codex.locked</t>
+          <t>reaction.panel.empty_log</t>
         </is>
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>尚未打出。战斗中触发一次即解锁本条。</t>
+          <t>还没有反应记录（只记本次载入之后的）</t>
         </is>
       </c>
       <c r="D1641" t="inlineStr">
         <is>
-          <t>Not triggered yet. Trigger it once in combat to unlock this entry.</t>
+          <t>No reactions yet (only since this load)</t>
         </is>
       </c>
     </row>
@@ -29970,17 +29970,17 @@
       <c r="A1642" t="inlineStr"/>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>reaction.codex.closed</t>
+          <t>reaction.panel.empty_attr</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
         <is>
-          <t>尚未开放命名：随阵营推进开放（{0}）。</t>
+          <t>还没有远征或突袭的反应伤害记录</t>
         </is>
       </c>
       <c r="D1642" t="inlineStr">
         <is>
-          <t>Not yet named: unlocks as factions advance ({0}).</t>
+          <t>No expedition or raid damage records yet</t>
         </is>
       </c>
     </row>
@@ -29988,17 +29988,17 @@
       <c r="A1643" t="inlineStr"/>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>reaction.codex.unreachable</t>
+          <t>reaction.panel.log_hint</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
         <is>
-          <t>当前机械内容下无法触发。</t>
+          <t>最近 {0} 条，只保留本次载入之后的；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1643" t="inlineStr">
         <is>
-          <t>Cannot trigger with current mechanical content.</t>
+          <t>Last {0} entries since this load; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -30006,17 +30006,17 @@
       <c r="A1644" t="inlineStr"/>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>reaction.codex.first</t>
+          <t>reaction.panel.attr_hint</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>首次触发：{0}，{1}</t>
+          <t>占比 = 反应额外伤害 / 这一场敌方受到的全部伤害；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
         <is>
-          <t>First triggered: {0}, {1}</t>
+          <t>Share = extra reaction damage / all damage enemies took; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -30024,17 +30024,17 @@
       <c r="A1645" t="inlineStr"/>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>pause.reaction_title</t>
+          <t>reaction.panel.codex_hint</t>
         </is>
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>战斗反馈</t>
+          <t>已解锁 {0} / {1}：本存档里第一次打出某条反应时解锁；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1645" t="inlineStr">
         <is>
-          <t>Combat feedback</t>
+          <t>Unlocked {0}/{1}: an entry unlocks the first time you trigger it in this save; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -30042,17 +30042,17 @@
       <c r="A1646" t="inlineStr"/>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>pause.reaction_popups</t>
+          <t>reaction.panel.count</t>
         </is>
       </c>
       <c r="C1646" t="inlineStr">
         <is>
-          <t>反应弹字</t>
+          <t>{0} 条</t>
         </is>
       </c>
       <c r="D1646" t="inlineStr">
         <is>
-          <t>Reaction pop-ups</t>
+          <t>{0} entries</t>
         </is>
       </c>
     </row>
@@ -30060,17 +30060,17 @@
       <c r="A1647" t="inlineStr"/>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>pause.reaction_slowmo</t>
+          <t>stats.panel.title</t>
         </is>
       </c>
       <c r="C1647" t="inlineStr">
         <is>
-          <t>首次反应慢放</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D1647" t="inlineStr">
         <is>
-          <t>Slow motion on first reaction</t>
+          <t>Statistics</t>
         </is>
       </c>
     </row>
@@ -30078,17 +30078,17 @@
       <c r="A1648" t="inlineStr"/>
       <c r="B1648" t="inlineStr">
         <is>
-          <t>pause.reaction_nudge</t>
+          <t>stats.panel.section_combat</t>
         </is>
       </c>
       <c r="C1648" t="inlineStr">
         <is>
-          <t>首次反应镜头推动</t>
+          <t>战斗 · 反应伤害归因</t>
         </is>
       </c>
       <c r="D1648" t="inlineStr">
         <is>
-          <t>Camera nudge on first reaction</t>
+          <t>Combat · Reaction damage share</t>
         </is>
       </c>
     </row>
@@ -30096,17 +30096,17 @@
       <c r="A1649" t="inlineStr"/>
       <c r="B1649" t="inlineStr">
         <is>
-          <t>pause.reaction_reset</t>
+          <t>stats.panel.count</t>
         </is>
       </c>
       <c r="C1649" t="inlineStr">
         <is>
-          <t>战斗反馈恢复默认</t>
+          <t>{0} 场</t>
         </is>
       </c>
       <c r="D1649" t="inlineStr">
         <is>
-          <t>Reset combat feedback</t>
+          <t>{0} sessions</t>
         </is>
       </c>
     </row>
@@ -30114,17 +30114,17 @@
       <c r="A1650" t="inlineStr"/>
       <c r="B1650" t="inlineStr">
         <is>
-          <t>pause.reaction_log</t>
+          <t>stats.panel.totals_title</t>
         </is>
       </c>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>反应记录</t>
+          <t>累计（{0} 场）</t>
         </is>
       </c>
       <c r="D1650" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Totals ({0} sessions)</t>
         </is>
       </c>
     </row>
@@ -30132,17 +30132,17 @@
       <c r="A1651" t="inlineStr"/>
       <c r="B1651" t="inlineStr">
         <is>
-          <t>pause.reaction_popups_tip</t>
+          <t>stats.panel.totals_line</t>
         </is>
       </c>
       <c r="C1651" t="inlineStr">
         <is>
-          <t>反应名打在目标头上（大量触发时合并成“短路 ×12”，每秒最多 {0} 条）。关掉后字幕、日志与统计照常。</t>
+          <t>敌方共受伤害 {0}，其中反应额外伤害占 {1}%</t>
         </is>
       </c>
       <c r="D1651" t="inlineStr">
         <is>
-          <t>Reaction names pop over the target (bursts merge into "Short Circuit ×12", at most {0} per second). Captions, log and stats still work when off.</t>
+          <t>Enemies took {0} damage in total; reaction bonus damage was {1}%</t>
         </is>
       </c>
     </row>
@@ -30150,17 +30150,17 @@
       <c r="A1652" t="inlineStr"/>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>pause.reaction_slowmo_tip</t>
+          <t>stats.panel.sessions_title</t>
         </is>
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>本存档里每条反应第一次触发时短暂慢放 {0} 秒（只在镜头正看着时）。关掉后仍解锁图鉴。</t>
+          <t>每场明细</t>
         </is>
       </c>
       <c r="D1652" t="inlineStr">
         <is>
-          <t>Briefly slows time for {0}s the first time each reaction triggers in this save (only while you are watching). The codex still unlocks when off.</t>
+          <t>Per session</t>
         </is>
       </c>
     </row>
@@ -30168,17 +30168,17 @@
       <c r="A1653" t="inlineStr"/>
       <c r="B1653" t="inlineStr">
         <is>
-          <t>pause.reaction_nudge_tip</t>
+          <t>stats.panel.empty</t>
         </is>
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>本存档里每条反应第一次触发时镜头朝它轻推一下。</t>
+          <t>还没有远征或突袭的战斗统计。出一次远征并在战斗中打出反应后，这里会按反应列出伤害占比。</t>
         </is>
       </c>
       <c r="D1653" t="inlineStr">
         <is>
-          <t>Nudges the camera toward each reaction the first time it triggers in this save.</t>
+          <t>No expedition or raid combat stats yet. Go on an expedition and trigger reactions in combat to see each reaction's damage share here.</t>
         </is>
       </c>
     </row>
@@ -30186,17 +30186,17 @@
       <c r="A1654" t="inlineStr"/>
       <c r="B1654" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.title</t>
+          <t>stats.panel.hint</t>
         </is>
       </c>
       <c r="C1654" t="inlineStr">
         <is>
-          <t>信号接入</t>
+          <t>只统计远征与突袭（家园平时的训练战斗不计），最近 {0} 场随存档保存；占比 = 反应额外伤害 / 敌方受到的全部伤害；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1654" t="inlineStr">
         <is>
-          <t>Signal uplink</t>
+          <t>Only expeditions and raids count (training at home does not); the last {0} sessions are saved; share = reaction bonus damage / all damage enemies took; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -30204,17 +30204,17 @@
       <c r="A1655" t="inlineStr"/>
       <c r="B1655" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.body</t>
+          <t>pause.stats</t>
         </is>
       </c>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
         <is>
-          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
+          <t>Statistics</t>
         </is>
       </c>
     </row>
@@ -30222,17 +30222,17 @@
       <c r="A1656" t="inlineStr"/>
       <c r="B1656" t="inlineStr">
         <is>
-          <t>codex.signal.uplink.hint</t>
+          <t>reaction.codex.locked_name</t>
         </is>
       </c>
       <c r="C1656" t="inlineStr">
         <is>
-          <t>第一次接入一台机器，或打开信号核时解锁</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1656" t="inlineStr">
         <is>
-          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -30240,17 +30240,17 @@
       <c r="A1657" t="inlineStr"/>
       <c r="B1657" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.title</t>
+          <t>reaction.codex.locked</t>
         </is>
       </c>
       <c r="C1657" t="inlineStr">
         <is>
-          <t>接入口</t>
+          <t>尚未打出。战斗中触发一次即解锁本条。</t>
         </is>
       </c>
       <c r="D1657" t="inlineStr">
         <is>
-          <t>Uplink port</t>
+          <t>Not triggered yet. Trigger it once in combat to unlock this entry.</t>
         </is>
       </c>
     </row>
@@ -30258,17 +30258,17 @@
       <c r="A1658" t="inlineStr"/>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.body</t>
+          <t>reaction.codex.closed</t>
         </is>
       </c>
       <c r="C1658" t="inlineStr">
         <is>
-          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
+          <t>尚未开放命名：随阵营推进开放（{0}）。</t>
         </is>
       </c>
       <c r="D1658" t="inlineStr">
         <is>
-          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
+          <t>Not yet named: unlocks as factions advance ({0}).</t>
         </is>
       </c>
     </row>
@@ -30276,17 +30276,17 @@
       <c r="A1659" t="inlineStr"/>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>codex.signal.uplink_port.hint</t>
+          <t>reaction.codex.unreachable</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
         <is>
-          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
+          <t>当前机械内容下无法触发。</t>
         </is>
       </c>
       <c r="D1659" t="inlineStr">
         <is>
-          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
+          <t>Cannot trigger with current mechanical content.</t>
         </is>
       </c>
     </row>
@@ -30294,17 +30294,17 @@
       <c r="A1660" t="inlineStr"/>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.title</t>
+          <t>reaction.codex.first</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>核心固件</t>
+          <t>首次触发：{0}，{1}</t>
         </is>
       </c>
       <c r="D1660" t="inlineStr">
         <is>
-          <t>Core firmware</t>
+          <t>First triggered: {0}, {1}</t>
         </is>
       </c>
     </row>
@@ -30312,17 +30312,17 @@
       <c r="A1661" t="inlineStr"/>
       <c r="B1661" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.body</t>
+          <t>pause.reaction_title</t>
         </is>
       </c>
       <c r="C1661" t="inlineStr">
         <is>
-          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
+          <t>战斗反馈</t>
         </is>
       </c>
       <c r="D1661" t="inlineStr">
         <is>
-          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
+          <t>Combat feedback</t>
         </is>
       </c>
     </row>
@@ -30330,17 +30330,17 @@
       <c r="A1662" t="inlineStr"/>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>codex.signal.core_firmware.hint</t>
+          <t>pause.reaction_popups</t>
         </is>
       </c>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>第一次打开信号核时解锁</t>
+          <t>反应弹字</t>
         </is>
       </c>
       <c r="D1662" t="inlineStr">
         <is>
-          <t>Unlocks the first time you open the Signal Core</t>
+          <t>Reaction pop-ups</t>
         </is>
       </c>
     </row>
@@ -30348,17 +30348,17 @@
       <c r="A1663" t="inlineStr"/>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.title</t>
+          <t>pause.reaction_slowmo</t>
         </is>
       </c>
       <c r="C1663" t="inlineStr">
         <is>
-          <t>安全模式</t>
+          <t>首次反应慢放</t>
         </is>
       </c>
       <c r="D1663" t="inlineStr">
         <is>
-          <t>Safe mode</t>
+          <t>Slow motion on first reaction</t>
         </is>
       </c>
     </row>
@@ -30366,17 +30366,17 @@
       <c r="A1664" t="inlineStr"/>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.body</t>
+          <t>pause.reaction_nudge</t>
         </is>
       </c>
       <c r="C1664" t="inlineStr">
         <is>
-          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
+          <t>首次反应镜头推动</t>
         </is>
       </c>
       <c r="D1664" t="inlineStr">
         <is>
-          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
+          <t>Camera nudge on first reaction</t>
         </is>
       </c>
     </row>
@@ -30384,17 +30384,17 @@
       <c r="A1665" t="inlineStr"/>
       <c r="B1665" t="inlineStr">
         <is>
-          <t>codex.signal.safe_mode.hint</t>
+          <t>pause.reaction_reset</t>
         </is>
       </c>
       <c r="C1665" t="inlineStr">
         <is>
-          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
+          <t>战斗反馈恢复默认</t>
         </is>
       </c>
       <c r="D1665" t="inlineStr">
         <is>
-          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
+          <t>Reset combat feedback</t>
         </is>
       </c>
     </row>
@@ -30402,17 +30402,17 @@
       <c r="A1666" t="inlineStr"/>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>codex.signal.raw.title</t>
+          <t>pause.reaction_log</t>
         </is>
       </c>
       <c r="C1666" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>反应记录</t>
         </is>
       </c>
       <c r="D1666" t="inlineStr">
         <is>
-          <t>Running raw</t>
+          <t>Reactions</t>
         </is>
       </c>
     </row>
@@ -30420,17 +30420,17 @@
       <c r="A1667" t="inlineStr"/>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>codex.signal.raw.body</t>
+          <t>pause.reaction_popups_tip</t>
         </is>
       </c>
       <c r="C1667" t="inlineStr">
         <is>
-          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
+          <t>反应名打在目标头上（大量触发时合并成“短路 ×12”，每秒最多 {0} 条）。关掉后字幕、日志与统计照常。</t>
         </is>
       </c>
       <c r="D1667" t="inlineStr">
         <is>
-          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
+          <t>Reaction names pop over the target (bursts merge into "Short Circuit ×12", at most {0} per second). Captions, log and stats still work when off.</t>
         </is>
       </c>
     </row>
@@ -30438,17 +30438,17 @@
       <c r="A1668" t="inlineStr"/>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>codex.signal.raw.hint</t>
+          <t>pause.reaction_slowmo_tip</t>
         </is>
       </c>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>第一次带回加密固件时解锁</t>
+          <t>本存档里每条反应第一次触发时短暂慢放 {0} 秒（只在镜头正看着时）。关掉后仍解锁图鉴。</t>
         </is>
       </c>
       <c r="D1668" t="inlineStr">
         <is>
-          <t>Unlocks the first time you bring back encrypted firmware</t>
+          <t>Briefly slows time for {0}s the first time each reaction triggers in this save (only while you are watching). The codex still unlocks when off.</t>
         </is>
       </c>
     </row>
@@ -30456,17 +30456,17 @@
       <c r="A1669" t="inlineStr"/>
       <c r="B1669" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.title</t>
+          <t>pause.reaction_nudge_tip</t>
         </is>
       </c>
       <c r="C1669" t="inlineStr">
         <is>
-          <t>信号暴露</t>
+          <t>本存档里每条反应第一次触发时镜头朝它轻推一下。</t>
         </is>
       </c>
       <c r="D1669" t="inlineStr">
         <is>
-          <t>Signal exposure</t>
+          <t>Nudges the camera toward each reaction the first time it triggers in this save.</t>
         </is>
       </c>
     </row>
@@ -30474,17 +30474,17 @@
       <c r="A1670" t="inlineStr"/>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.body</t>
+          <t>codex.signal.uplink.title</t>
         </is>
       </c>
       <c r="C1670" t="inlineStr">
         <is>
-          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
+          <t>信号接入</t>
         </is>
       </c>
       <c r="D1670" t="inlineStr">
         <is>
-          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
+          <t>Signal uplink</t>
         </is>
       </c>
     </row>
@@ -30492,17 +30492,17 @@
       <c r="A1671" t="inlineStr"/>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>codex.signal.exposure.hint</t>
+          <t>codex.signal.uplink.body</t>
         </is>
       </c>
       <c r="C1671" t="inlineStr">
         <is>
-          <t>第一次打开暴露面板或带回加密固件时解锁</t>
+          <t>你是归还核心发出的信号，同一时刻只在一处：归还核心，或一台接入的机器。选中机器后按接入键（{act:ToggleCameraView}）、在机器列表里点它、或接入中按 {act:CycleControlTarget} 切换，镜头过渡约 0.35 秒后接入：信号核的固件按槽位顺序插进它的接入口并重编译，机身随之形变。接入中你亲自驾驶、瞄准、开火；离开时固件随信号带走，机器回到本地配置，按最后的命令和 AI 教义继续行动。核心固件的冷却跟着信号走，热量留在机体上——来回切换刷不掉冷却，也甩不掉热量。</t>
         </is>
       </c>
       <c r="D1671" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
+          <t>You are the signal sent by the Reclamation Core and are always in exactly one place: the core or one uplinked machine. Select a machine and press Uplink ({act:ToggleCameraView}), click it in the machine list, or press {act:CycleControlTarget} while uplinked; after a short camera transition (about 0.35s) Signal Core firmware is inserted into its uplink port in slot order and the machine recompiles and morphs. While uplinked you drive, aim and fire yourself; when you leave, the firmware goes with the signal and the machine returns to its own loadout, following its last order and AI doctrine. Core firmware cooldowns follow the signal and heat stays on the machine, so switching back and forth cannot reset either.</t>
         </is>
       </c>
     </row>
@@ -30510,17 +30510,17 @@
       <c r="A1672" t="inlineStr"/>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.title</t>
+          <t>codex.signal.uplink.hint</t>
         </is>
       </c>
       <c r="C1672" t="inlineStr">
         <is>
-          <t>信号覆盖网络</t>
+          <t>第一次接入一台机器，或打开信号核时解锁</t>
         </is>
       </c>
       <c r="D1672" t="inlineStr">
         <is>
-          <t>Signal coverage network</t>
+          <t>Unlocks the first time you uplink into a machine or open the Signal Core</t>
         </is>
       </c>
     </row>
@@ -30528,17 +30528,17 @@
       <c r="A1673" t="inlineStr"/>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.body</t>
+          <t>codex.signal.uplink_port.title</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
+          <t>接入口</t>
         </is>
       </c>
       <c r="D1673" t="inlineStr">
         <is>
-          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
+          <t>Uplink port</t>
         </is>
       </c>
     </row>
@@ -30546,17 +30546,17 @@
       <c r="A1674" t="inlineStr"/>
       <c r="B1674" t="inlineStr">
         <is>
-          <t>codex.signal.coverage.hint</t>
+          <t>codex.signal.uplink_port.body</t>
         </is>
       </c>
       <c r="C1674" t="inlineStr">
         <is>
-          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
+          <t>蓝图 3×3 电路里标为接入口的空格（每张蓝图最多一个，0 号与 8 号格不行）。AI 驾驶时它只是一格空导线；你接入时，信号核的固件按槽位顺序插在这里，最多插入配额个（初值 2），插入后路径超过上限时按槽位倒序撤下。接入口不在导线上时插进去的固件不生效。电路编辑器的双态预览同时列出“AI 驾驶时”与“你接入时”两种结果。没有接入口的机器照样能接入驾驶，只是不插入固件。</t>
         </is>
       </c>
       <c r="D1674" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
+          <t>An empty cell of a blueprint's 3x3 circuit marked as the uplink port (at most one per blueprint, never slot 0 or 8). Under AI control it is just an empty wire; when you uplink, Signal Core firmware is inserted here in slot order, up to the quota (initially 2); if the paths would exceed the limit, firmware is removed from the last slot back. If the port is not on a wire, inserted firmware has no effect. The circuit editor's dual preview shows both the AI-driving and the uplinked result. Machines without an uplink port can still be driven, they just get no firmware.</t>
         </is>
       </c>
     </row>
@@ -30564,17 +30564,17 @@
       <c r="A1675" t="inlineStr"/>
       <c r="B1675" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.title</t>
+          <t>codex.signal.uplink_port.hint</t>
         </is>
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>远距离跳转</t>
+          <t>第一次在电路编辑器里遇到接入口，或第一次接入时解锁</t>
         </is>
       </c>
       <c r="D1675" t="inlineStr">
         <is>
-          <t>Long-range jump</t>
+          <t>Unlocks when you first meet an uplink port in the circuit editor or first uplink</t>
         </is>
       </c>
     </row>
@@ -30582,17 +30582,17 @@
       <c r="A1676" t="inlineStr"/>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.body</t>
+          <t>codex.signal.core_firmware.title</t>
         </is>
       </c>
       <c r="C1676" t="inlineStr">
         <is>
-          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
+          <t>核心固件</t>
         </is>
       </c>
       <c r="D1676" t="inlineStr">
         <is>
-          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
+          <t>Core firmware</t>
         </is>
       </c>
     </row>
@@ -30600,17 +30600,17 @@
       <c r="A1677" t="inlineStr"/>
       <c r="B1677" t="inlineStr">
         <is>
-          <t>codex.signal.far_jump.hint</t>
+          <t>codex.signal.core_firmware.body</t>
         </is>
       </c>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>第一次远距离跳转时解锁</t>
+          <t>越过安全限制、或需要核心实时算力的固件（过载、标记跳转等 6 条），只能放进信号核、由你接入时插进接入口；机器电路装不下，AI 也永远不会使用。核心固件的具名反应真正打出时才算“发动”，之后进入冷却：冷却属于信号，跳到别的机器不会重置；冷却中固件仍插着，只是它的反应暂不发动。每次发动还会增加少量信号暴露。</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
         <is>
-          <t>Unlocks the first time you make a long-range jump</t>
+          <t>Firmware that breaks safety limits or needs the core's real-time compute (six of them, such as Overload and Mark Jump). It can only go in the Signal Core and is inserted when you uplink; machine circuits cannot hold it and the AI never uses it. It counts as fired only when its named reaction actually lands, then it cools down; the cooldown belongs to the signal and does not reset on another machine. While cooling it stays inserted but its reaction does not fire. Each firing also adds a little signal exposure.</t>
         </is>
       </c>
     </row>
@@ -30618,17 +30618,17 @@
       <c r="A1678" t="inlineStr"/>
       <c r="B1678" t="inlineStr">
         <is>
-          <t>codex.signal.relay.title</t>
+          <t>codex.signal.core_firmware.hint</t>
         </is>
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>信号中继</t>
+          <t>第一次打开信号核时解锁</t>
         </is>
       </c>
       <c r="D1678" t="inlineStr">
         <is>
-          <t>Signal relays</t>
+          <t>Unlocks the first time you open the Signal Core</t>
         </is>
       </c>
     </row>
@@ -30636,17 +30636,17 @@
       <c r="A1679" t="inlineStr"/>
       <c r="B1679" t="inlineStr">
         <is>
-          <t>codex.signal.relay.body</t>
+          <t>codex.signal.safe_mode.title</t>
         </is>
       </c>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
+          <t>安全模式</t>
         </is>
       </c>
       <c r="D1679" t="inlineStr">
         <is>
-          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
+          <t>Safe mode</t>
         </is>
       </c>
     </row>
@@ -30654,17 +30654,17 @@
       <c r="A1680" t="inlineStr"/>
       <c r="B1680" t="inlineStr">
         <is>
-          <t>codex.signal.relay.hint</t>
+          <t>codex.signal.safe_mode.body</t>
         </is>
       </c>
       <c r="C1680" t="inlineStr">
         <is>
-          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
+          <t>接入中的机器因为走出信号覆盖、进入干扰场或静默夜而断链时，信号弹回归还核心，那台机器进入安全模式：只运行本地常规固件，接入口为空，按最后的命令或 AI 教义行动；头顶和机器列表里有盾形标记。断链条件消失并持续约 2 秒后自动退出，你也可以再次接入它。阵亡不产生安全模式。</t>
         </is>
       </c>
       <c r="D1680" t="inlineStr">
         <is>
-          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
+          <t>When an uplinked machine loses the link by leaving signal coverage, entering a jamming field or at silent night, the signal returns to the core and the machine enters safe mode: only its local regular firmware runs, the uplink port is empty, and it follows its last order or AI doctrine, with a shield marker overhead and in the machine list. It ends about 2 seconds after the problem is gone, or when you uplink again. Destruction never causes safe mode.</t>
         </is>
       </c>
     </row>
@@ -30672,17 +30672,17 @@
       <c r="A1681" t="inlineStr"/>
       <c r="B1681" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.title</t>
+          <t>codex.signal.safe_mode.hint</t>
         </is>
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>机身形变</t>
+          <t>第一次有机器进入安全模式、或走出信号覆盖时解锁</t>
         </is>
       </c>
       <c r="D1681" t="inlineStr">
         <is>
-          <t>Machine morph</t>
+          <t>Unlocks the first time a machine enters safe mode or leaves signal coverage</t>
         </is>
       </c>
     </row>
@@ -30690,17 +30690,17 @@
       <c r="A1682" t="inlineStr"/>
       <c r="B1682" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.body</t>
+          <t>codex.signal.raw.title</t>
         </is>
       </c>
       <c r="C1682" t="inlineStr">
         <is>
-          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1682" t="inlineStr">
         <is>
-          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
+          <t>Running raw</t>
         </is>
       </c>
     </row>
@@ -30708,17 +30708,17 @@
       <c r="A1683" t="inlineStr"/>
       <c r="B1683" t="inlineStr">
         <is>
-          <t>codex.firmware.morph.hint</t>
+          <t>codex.signal.raw.body</t>
         </is>
       </c>
       <c r="C1683" t="inlineStr">
         <is>
-          <t>第一次看到机身形变时解锁</t>
+          <t>从敌人那里带回的固件是加密的（未破解）：在解析台破解之前，它只能放进信号核、由信号“裸跑”——每次发动增加信号暴露，经过接入口那条武器积热更快（初值 ×1.5）；不能装进机器电路或炮塔。破解后标记消失，按种类决定能装到哪里；破解时正插在信号核里的那枚自动更新，冷却不重置。</t>
         </is>
       </c>
       <c r="D1683" t="inlineStr">
         <is>
-          <t>Unlocks the first time you see a machine morph</t>
+          <t>Firmware brought back from enemies is encrypted. Until it is cracked at the Analysis Bench it can only sit in the Signal Core and run raw through the signal: every firing adds signal exposure and the weapon on the uplink path heats faster (initially x1.5); it cannot go into machine circuits or turrets. Once cracked the tag disappears and its kind decides where it can be installed; a copy already in the Signal Core updates in place without resetting its cooldown.</t>
         </is>
       </c>
     </row>
@@ -30726,17 +30726,17 @@
       <c r="A1684" t="inlineStr"/>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>codex.firmware.library.title</t>
+          <t>codex.signal.raw.hint</t>
         </is>
       </c>
       <c r="C1684" t="inlineStr">
         <is>
-          <t>固件库</t>
+          <t>第一次带回加密固件时解锁</t>
         </is>
       </c>
       <c r="D1684" t="inlineStr">
         <is>
-          <t>Firmware library</t>
+          <t>Unlocks the first time you bring back encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -30744,17 +30744,17 @@
       <c r="A1685" t="inlineStr"/>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>codex.firmware.library.body</t>
+          <t>codex.signal.exposure.title</t>
         </is>
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>固件芯片是物品，存放在归还核心和仓库里：没有仓库时能放 8 枚，每座运转中的仓库再加一批格子；放满后新拿到的芯片进入待领取，腾出位置后再领取。按 {act:OpenFirmware} 或在暂停菜单里打开固件库，可以按类别、种类、协议、是否破解、兼容载体、稀有度筛选，按名称或说明搜索，排序并并排比较两条固件。详情页列出它在各载体上的读法、标签、参与的反应、获取途径和持有位置。锁定的芯片不会被批量分解；批量分解会先弹确认框，装在信号核或被合成台预留的芯片一律跳过，每枚返还少量废料，拆掉之后要重新刻印才能再得到。悬停任何固件时按 {act:OpenCodex} 可以跳到它的图鉴条目。</t>
+          <t>信号暴露</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
         <is>
-          <t>Firmware chips are items stored in the Reclamation Core and in warehouses: 8 fit without a warehouse, and every operating warehouse adds more slots; when storage is full, new chips wait to be claimed until there is room. Press {act:OpenFirmware} or use the pause menu to open the library, where you can filter by category, kind, protocol, cracked state, compatible carrier and rarity, search names and descriptions, sort, and compare two firmware side by side. The detail page lists its reading on each carrier, tags, reactions, how to get it and where your copies are. Locked chips are never batch-disassembled; batch disassembly asks for confirmation first and always skips chips in the Signal Core or reserved by crafting. Each chip refunds a little scrap and must be printed again to get it back. Hover any firmware and press {act:OpenCodex} to jump to its codex entry.</t>
+          <t>Signal exposure</t>
         </is>
       </c>
     </row>
@@ -30762,17 +30762,17 @@
       <c r="A1686" t="inlineStr"/>
       <c r="B1686" t="inlineStr">
         <is>
-          <t>codex.firmware.library.hint</t>
+          <t>codex.signal.exposure.body</t>
         </is>
       </c>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>第一次打开固件库时解锁</t>
+          <t>敌人对你的信号有多警觉（0～100）。核心固件发动、裸跑、使用异派技术、摧毁敌方节点、高功率生产会增加暴露；接入本身和接入时长不计。越过阈值会依次触发侦察提示、下一次远征的敌方反制、核心战增援。摧毁监听节点、关闭信号塔主动广播可以降低暴露。暴露面板（HUD 上“暴露 N”）逐项列出最近的来源。</t>
         </is>
       </c>
       <c r="D1686" t="inlineStr">
         <is>
-          <t>Unlocks the first time you open the firmware library</t>
+          <t>How alert enemies are to your signal (0-100). Firing core firmware, running raw, using alien tech, destroying enemy nodes and high-power production raise it; uplinking and time spent uplinked do not. Crossing thresholds triggers a scouting warning, enemy countermeasures on the next expedition and core-fight reinforcements. Destroying listening nodes and turning off tower broadcasts lower it. The exposure panel ("Exposure N" on the HUD) lists the recent sources.</t>
         </is>
       </c>
     </row>
@@ -30780,17 +30780,17 @@
       <c r="A1687" t="inlineStr"/>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>codex.panel.title</t>
+          <t>codex.signal.exposure.hint</t>
         </is>
       </c>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>第一次打开暴露面板或带回加密固件时解锁</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Unlocks when you first open the exposure panel or bring back encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -30798,17 +30798,17 @@
       <c r="A1688" t="inlineStr"/>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>codex.panel.close</t>
+          <t>codex.signal.coverage.title</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>信号覆盖网络</t>
         </is>
       </c>
       <c r="D1688" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Signal coverage network</t>
         </is>
       </c>
     </row>
@@ -30816,17 +30816,17 @@
       <c r="A1689" t="inlineStr"/>
       <c r="B1689" t="inlineStr">
         <is>
-          <t>codex.panel.list_title</t>
+          <t>codex.signal.coverage.body</t>
         </is>
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>条目 {0}/{1}</t>
+          <t>归还核心、信号塔、信号中继塔和带中继模块的机器各有一圈覆盖；与归还核心连通的覆盖连成网络。网络之内可以下命令、接入、远距离跳转；走出覆盖的机器收不到命令、不能接入，只执行最后的命令和 AI 教义，回到覆盖后自动恢复。接入中的机器离覆盖边缘越近，链路越弱；走出去会在宽限后断链。按 {act:ToggleOverlay} 打开覆盖网络叠加层。</t>
         </is>
       </c>
       <c r="D1689" t="inlineStr">
         <is>
-          <t>Entries {0}/{1}</t>
+          <t>The Reclamation Core, signal towers, relay towers and machines with a relay module each project a ring of coverage; rings linked to the core form the network. Inside it you can order, uplink and jump; machines outside cannot receive orders or be uplinked and keep their last order and AI doctrine until they are back. The closer an uplinked machine gets to the edge, the weaker the link; leaving breaks it after a short grace. Press {act:ToggleOverlay} for the coverage overlay.</t>
         </is>
       </c>
     </row>
@@ -30834,17 +30834,17 @@
       <c r="A1690" t="inlineStr"/>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>codex.panel.related</t>
+          <t>codex.signal.coverage.hint</t>
         </is>
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>相关条目</t>
+          <t>第一次打开覆盖网络叠加层、或有机器走出覆盖时解锁</t>
         </is>
       </c>
       <c r="D1690" t="inlineStr">
         <is>
-          <t>Related</t>
+          <t>Unlocks when you first open the coverage overlay or a machine leaves coverage</t>
         </is>
       </c>
     </row>
@@ -30852,17 +30852,17 @@
       <c r="A1691" t="inlineStr"/>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>codex.panel.locked_title</t>
+          <t>codex.signal.far_jump.title</t>
         </is>
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>远距离跳转</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Long-range jump</t>
         </is>
       </c>
     </row>
@@ -30870,17 +30870,17 @@
       <c r="A1692" t="inlineStr"/>
       <c r="B1692" t="inlineStr">
         <is>
-          <t>codex.panel.locked_body</t>
+          <t>codex.signal.far_jump.body</t>
         </is>
       </c>
       <c r="C1692" t="inlineStr">
         <is>
-          <t>尚未接触。{0}</t>
+          <t>信号可以跳到连通覆盖网络里的任意一台机器。距离超过 500 格或跨地点的跳转要过渡约 1.5 秒，完成后 10 秒内不能再远距离跳转；跳回家园（{act:JumpHome}）不受冷却限制，跳回上一台机器按 {act:JumpPreviousMachine}。跳转期间整个世界照常运行，被离开的机器按最后的命令和 AI 教义继续行动。</t>
         </is>
       </c>
       <c r="D1692" t="inlineStr">
         <is>
-          <t>Not encountered yet. {0}</t>
+          <t>The signal can jump to any machine in the linked coverage network. Jumps over 500 cells or to another site take about 1.5 seconds and then block further long-range jumps for 10 seconds; jumping home ({act:JumpHome}) is never blocked, and {act:JumpPreviousMachine} jumps back to the previous machine. The world keeps running during the jump, and the machine you left keeps its last order and AI doctrine.</t>
         </is>
       </c>
     </row>
@@ -30888,17 +30888,17 @@
       <c r="A1693" t="inlineStr"/>
       <c r="B1693" t="inlineStr">
         <is>
-          <t>codex.panel.none_selected</t>
+          <t>codex.signal.far_jump.hint</t>
         </is>
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>在左侧选一个条目</t>
+          <t>第一次远距离跳转时解锁</t>
         </is>
       </c>
       <c r="D1693" t="inlineStr">
         <is>
-          <t>Pick an entry on the left</t>
+          <t>Unlocks the first time you make a long-range jump</t>
         </is>
       </c>
     </row>
@@ -30906,17 +30906,17 @@
       <c r="A1694" t="inlineStr"/>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>codex.panel.footer</t>
+          <t>codex.signal.relay.title</t>
         </is>
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>悬停任何带图鉴链接的提示时按 {act:OpenCodex} 跳到条目；敌人、阵营等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
+          <t>信号中继</t>
         </is>
       </c>
       <c r="D1694" t="inlineStr">
         <is>
-          <t>Press {act:OpenCodex} while hovering a tooltip with a codex link to jump to its entry; enemy and faction tabs arrive later; press {act:Cancel} to close</t>
+          <t>Signal relays</t>
         </is>
       </c>
     </row>
@@ -30924,17 +30924,17 @@
       <c r="A1695" t="inlineStr"/>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>codex.panel.error</t>
+          <t>codex.signal.relay.body</t>
         </is>
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
+          <t>信号中继塔（建成即生效，不用电）和机器结构槽里的信号中继模块（跟着机器移动）把覆盖网络往外延伸。中继必须立在已经连通的覆盖里才能接上网络；与归还核心断开的中继不提供覆盖，叠加层上显示为红圈和断开图标，并发出通知。</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">
         <is>
-          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
+          <t>Relay towers (active once built, no power needed) and relay modules in a machine's structure slot (moving with the machine) extend the coverage network. A relay only joins the network if it stands inside linked coverage; relays cut off from the core provide no coverage and show as red rings with a broken-link icon, with a notification.</t>
         </is>
       </c>
     </row>
@@ -30942,17 +30942,17 @@
       <c r="A1696" t="inlineStr"/>
       <c r="B1696" t="inlineStr">
         <is>
-          <t>codex.help.tip_title</t>
+          <t>codex.signal.relay.hint</t>
         </is>
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>第一次打开覆盖网络叠加层、或有中继断开时解锁</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>Unlocks when you first open the coverage overlay or a relay is cut off</t>
         </is>
       </c>
     </row>
@@ -30960,17 +30960,17 @@
       <c r="A1697" t="inlineStr"/>
       <c r="B1697" t="inlineStr">
         <is>
-          <t>codex.help.tip</t>
+          <t>codex.firmware.morph.title</t>
         </is>
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>打开图鉴条目：{0}</t>
+          <t>机身形变</t>
         </is>
       </c>
       <c r="D1697" t="inlineStr">
         <is>
-          <t>Open the codex entry: {0}</t>
+          <t>Machine morph</t>
         </is>
       </c>
     </row>
@@ -30978,17 +30978,17 @@
       <c r="A1698" t="inlineStr"/>
       <c r="B1698" t="inlineStr">
         <is>
-          <t>uplink.hud.title</t>
+          <t>codex.firmware.morph.body</t>
         </is>
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>机器的外形跟着它正式编译生效的固件类别变化：限制器与击发逻辑 = 形变态（散热鳍展开、天线升起），流体改道 = 喷口态，电磁场控 = 线圈态，可以叠加；引信与弹芯类只改弹体特效，不改机身。你接入时插进去的固件会让机身变形，离开后复原；AI 自带的固件让机器平时就保持对应状态。接入 HUD 与机器列表的悬停说明写着现在是什么状态、由哪枚固件引起。</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>A machine's shape follows the categories of the firmware its compiled circuit actually runs: limiter and trigger logic = morph state (fins out, antenna up), fluid rerouting = vent state, electromagnetic control = coil state, and they can stack; fuse and payload firmware only changes projectile effects. Firmware you insert when uplinking morphs the body and it reverts when you leave; firmware the AI carries keeps the machine in that state all the time. The uplink HUD and machine list tooltips name the current state and the firmware causing it.</t>
         </is>
       </c>
     </row>
@@ -30996,17 +30996,17 @@
       <c r="A1699" t="inlineStr"/>
       <c r="B1699" t="inlineStr">
         <is>
-          <t>uplink.hud.help_button</t>
+          <t>codex.firmware.morph.hint</t>
         </is>
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>第一次看到机身形变时解锁</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Unlocks the first time you see a machine morph</t>
         </is>
       </c>
     </row>
@@ -31014,17 +31014,17 @@
       <c r="A1700" t="inlineStr"/>
       <c r="B1700" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip_title</t>
+          <t>codex.firmware.library.title</t>
         </is>
       </c>
       <c r="C1700" t="inlineStr">
         <is>
-          <t>接入 HUD</t>
+          <t>固件库</t>
         </is>
       </c>
       <c r="D1700" t="inlineStr">
         <is>
-          <t>Uplink HUD</t>
+          <t>Firmware library</t>
         </is>
       </c>
     </row>
@@ -31032,17 +31032,17 @@
       <c r="A1701" t="inlineStr"/>
       <c r="B1701" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip</t>
+          <t>codex.firmware.library.body</t>
         </is>
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
+          <t>固件芯片是物品，存放在归还核心和仓库里：没有仓库时能放 8 枚，每座运转中的仓库再加一批格子；放满后新拿到的芯片进入待领取，腾出位置后再领取。按 {act:OpenFirmware} 或在暂停菜单里打开固件库，可以按类别、种类、协议、是否破解、兼容载体、稀有度筛选，按名称或说明搜索，排序并并排比较两条固件。详情页列出它在各载体上的读法、标签、参与的反应、获取途径和持有位置。锁定的芯片不会被批量分解；批量分解会先弹确认框，装在信号核或被合成台预留的芯片一律跳过，每枚返还少量废料，拆掉之后要重新刻印才能再得到。悬停任何固件时按 {act:OpenCodex} 可以跳到它的图鉴条目。</t>
         </is>
       </c>
       <c r="D1701" t="inlineStr">
         <is>
-          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
+          <t>Firmware chips are items stored in the Reclamation Core and in warehouses: 8 fit without a warehouse, and every operating warehouse adds more slots; when storage is full, new chips wait to be claimed until there is room. Press {act:OpenFirmware} or use the pause menu to open the library, where you can filter by category, kind, protocol, cracked state, compatible carrier and rarity, search names and descriptions, sort, and compare two firmware side by side. The detail page lists its reading on each carrier, tags, reactions, how to get it and where your copies are. Locked chips are never batch-disassembled; batch disassembly asks for confirmation first and always skips chips in the Signal Core or reserved by crafting. Each chip refunds a little scrap and must be printed again to get it back. Hover any firmware and press {act:OpenCodex} to jump to its codex entry.</t>
         </is>
       </c>
     </row>
@@ -31050,17 +31050,17 @@
       <c r="A1702" t="inlineStr"/>
       <c r="B1702" t="inlineStr">
         <is>
-          <t>uplink.hud.slot</t>
+          <t>codex.firmware.library.hint</t>
         </is>
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>第一次打开固件库时解锁</t>
         </is>
       </c>
       <c r="D1702" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>Unlocks the first time you open the firmware library</t>
         </is>
       </c>
     </row>
@@ -31068,17 +31068,17 @@
       <c r="A1703" t="inlineStr"/>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>uplink.hud.state.active</t>
+          <t>codex.panel.title</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>生效</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -31086,17 +31086,17 @@
       <c r="A1704" t="inlineStr"/>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>uplink.hud.state.cooling</t>
+          <t>codex.panel.close</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>冷却 {0} 秒</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
         <is>
-          <t>cooling {0}s</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -31104,17 +31104,17 @@
       <c r="A1705" t="inlineStr"/>
       <c r="B1705" t="inlineStr">
         <is>
-          <t>uplink.hud.state.raw</t>
+          <t>codex.panel.list_title</t>
         </is>
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>条目 {0}/{1}</t>
         </is>
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>Entries {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31122,17 +31122,17 @@
       <c r="A1706" t="inlineStr"/>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>uplink.hud.state.not_inserted</t>
+          <t>codex.panel.related</t>
         </is>
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>未插入：{0}</t>
+          <t>相关条目</t>
         </is>
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>not inserted: {0}</t>
+          <t>Related</t>
         </is>
       </c>
     </row>
@@ -31140,17 +31140,17 @@
       <c r="A1707" t="inlineStr"/>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>uplink.hud.state.ineffective</t>
+          <t>codex.panel.locked_title</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>不生效：{0}</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1707" t="inlineStr">
         <is>
-          <t>no effect: {0}</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -31158,17 +31158,17 @@
       <c r="A1708" t="inlineStr"/>
       <c r="B1708" t="inlineStr">
         <is>
-          <t>uplink.hud.state.empty</t>
+          <t>codex.panel.locked_body</t>
         </is>
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>空槽</t>
+          <t>尚未接触。{0}</t>
         </is>
       </c>
       <c r="D1708" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>Not encountered yet. {0}</t>
         </is>
       </c>
     </row>
@@ -31176,17 +31176,17 @@
       <c r="A1709" t="inlineStr"/>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>uplink.hud.state.locked</t>
+          <t>codex.panel.none_selected</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>未解锁</t>
+          <t>在左侧选一个条目</t>
         </is>
       </c>
       <c r="D1709" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>Pick an entry on the left</t>
         </is>
       </c>
     </row>
@@ -31194,17 +31194,17 @@
       <c r="A1710" t="inlineStr"/>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.over_quota</t>
+          <t>codex.panel.footer</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>超出接入口配额 {0} 个</t>
+          <t>悬停任何带图鉴链接的提示时按 {act:OpenCodex} 跳到条目；敌人、阵营等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1710" t="inlineStr">
         <is>
-          <t>over the port quota of {0}</t>
+          <t>Press {act:OpenCodex} while hovering a tooltip with a codex link to jump to its entry; enemy and faction tabs arrive later; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -31212,17 +31212,17 @@
       <c r="A1711" t="inlineStr"/>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.path_limit</t>
+          <t>codex.panel.error</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>路径会超过上限 {0} 条</t>
+          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
         </is>
       </c>
       <c r="D1711" t="inlineStr">
         <is>
-          <t>paths would exceed {0}</t>
+          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
         </is>
       </c>
     </row>
@@ -31230,17 +31230,17 @@
       <c r="A1712" t="inlineStr"/>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.unknown</t>
+          <t>codex.help.tip_title</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>不是已知的固件</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1712" t="inlineStr">
         <is>
-          <t>unknown firmware</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -31248,17 +31248,17 @@
       <c r="A1713" t="inlineStr"/>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.no_uplink</t>
+          <t>codex.help.tip</t>
         </is>
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>这台机器没有接入口</t>
+          <t>打开图鉴条目：{0}</t>
         </is>
       </c>
       <c r="D1713" t="inlineStr">
         <is>
-          <t>this machine has no uplink port</t>
+          <t>Open the codex entry: {0}</t>
         </is>
       </c>
     </row>
@@ -31266,17 +31266,17 @@
       <c r="A1714" t="inlineStr"/>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.off_path</t>
+          <t>uplink.hud.title</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
         <is>
-          <t>接入口不在导线上</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
       <c r="D1714" t="inlineStr">
         <is>
-          <t>the uplink port is not on a wire</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
     </row>
@@ -31284,17 +31284,17 @@
       <c r="A1715" t="inlineStr"/>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>uplink.hud.slot_tip</t>
+          <t>uplink.hud.help_button</t>
         </is>
       </c>
       <c r="C1715" t="inlineStr">
         <is>
-          <t>{0} 号槽：{1}</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D1715" t="inlineStr">
         <is>
-          <t>Slot {0}: {1}</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -31302,17 +31302,17 @@
       <c r="A1716" t="inlineStr"/>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>uplink.hud.heat</t>
+          <t>uplink.hud.help_tip_title</t>
         </is>
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>热量 {0}/{1}</t>
+          <t>接入 HUD</t>
         </is>
       </c>
       <c r="D1716" t="inlineStr">
         <is>
-          <t>Heat {0}/{1}</t>
+          <t>Uplink HUD</t>
         </is>
       </c>
     </row>
@@ -31320,17 +31320,17 @@
       <c r="A1717" t="inlineStr"/>
       <c r="B1717" t="inlineStr">
         <is>
-          <t>uplink.hud.overheated</t>
+          <t>uplink.hud.help_tip</t>
         </is>
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>过热：散热到 {0} 以下才开火</t>
+          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
         </is>
       </c>
       <c r="D1717" t="inlineStr">
         <is>
-          <t>Overheated: fires again below {0}</t>
+          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
         </is>
       </c>
     </row>
@@ -31338,17 +31338,17 @@
       <c r="A1718" t="inlineStr"/>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>uplink.hud.heat_tip</t>
+          <t>uplink.hud.slot</t>
         </is>
       </c>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
+          <t>{0} {1}</t>
         </is>
       </c>
       <c r="D1718" t="inlineStr">
         <is>
-          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
+          <t>{0} {1}</t>
         </is>
       </c>
     </row>
@@ -31356,17 +31356,17 @@
       <c r="A1719" t="inlineStr"/>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>uplink.hud.battery</t>
+          <t>uplink.hud.state.active</t>
         </is>
       </c>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>电池 {0}%</t>
+          <t>生效</t>
         </is>
       </c>
       <c r="D1719" t="inlineStr">
         <is>
-          <t>Battery {0}%</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -31374,17 +31374,17 @@
       <c r="A1720" t="inlineStr"/>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>uplink.hud.battery_tip</t>
+          <t>uplink.hud.state.cooling</t>
         </is>
       </c>
       <c r="C1720" t="inlineStr">
         <is>
-          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
+          <t>冷却 {0} 秒</t>
         </is>
       </c>
       <c r="D1720" t="inlineStr">
         <is>
-          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
+          <t>cooling {0}s</t>
         </is>
       </c>
     </row>
@@ -31392,17 +31392,17 @@
       <c r="A1721" t="inlineStr"/>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>uplink.hud.health</t>
+          <t>uplink.hud.state.raw</t>
         </is>
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
         <is>
-          <t>Durability {0}/{1}</t>
+          <t>raw</t>
         </is>
       </c>
     </row>
@@ -31410,17 +31410,17 @@
       <c r="A1722" t="inlineStr"/>
       <c r="B1722" t="inlineStr">
         <is>
-          <t>uplink.hud.injury_none</t>
+          <t>uplink.hud.state.not_inserted</t>
         </is>
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>伤势：无</t>
+          <t>未插入：{0}</t>
         </is>
       </c>
       <c r="D1722" t="inlineStr">
         <is>
-          <t>Injuries: none</t>
+          <t>not inserted: {0}</t>
         </is>
       </c>
     </row>
@@ -31428,17 +31428,17 @@
       <c r="A1723" t="inlineStr"/>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>uplink.hud.injury</t>
+          <t>uplink.hud.state.ineffective</t>
         </is>
       </c>
       <c r="C1723" t="inlineStr">
         <is>
-          <t>伤势：{0}</t>
+          <t>不生效：{0}</t>
         </is>
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>Injuries: {0}</t>
+          <t>no effect: {0}</t>
         </is>
       </c>
     </row>
@@ -31446,17 +31446,17 @@
       <c r="A1724" t="inlineStr"/>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>uplink.hud.health_tip</t>
+          <t>uplink.hud.state.empty</t>
         </is>
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
+          <t>空槽</t>
         </is>
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -31464,17 +31464,17 @@
       <c r="A1725" t="inlineStr"/>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>uplink.hud.link</t>
+          <t>uplink.hud.state.locked</t>
         </is>
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>链路 {0}% · {1}</t>
+          <t>未解锁</t>
         </is>
       </c>
       <c r="D1725" t="inlineStr">
         <is>
-          <t>Link {0}% · {1}</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -31482,17 +31482,17 @@
       <c r="A1726" t="inlineStr"/>
       <c r="B1726" t="inlineStr">
         <is>
-          <t>uplink.hud.link.strong</t>
+          <t>uplink.hud.reason.over_quota</t>
         </is>
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>强</t>
+          <t>超出接入口配额 {0} 个</t>
         </is>
       </c>
       <c r="D1726" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>over the port quota of {0}</t>
         </is>
       </c>
     </row>
@@ -31500,17 +31500,17 @@
       <c r="A1727" t="inlineStr"/>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>uplink.hud.link.medium</t>
+          <t>uplink.hud.reason.path_limit</t>
         </is>
       </c>
       <c r="C1727" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>路径会超过上限 {0} 条</t>
         </is>
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>paths would exceed {0}</t>
         </is>
       </c>
     </row>
@@ -31518,17 +31518,17 @@
       <c r="A1728" t="inlineStr"/>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>uplink.hud.link.weak</t>
+          <t>uplink.hud.reason.unknown</t>
         </is>
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>弱</t>
+          <t>不是已知的固件</t>
         </is>
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>unknown firmware</t>
         </is>
       </c>
     </row>
@@ -31536,17 +31536,17 @@
       <c r="A1729" t="inlineStr"/>
       <c r="B1729" t="inlineStr">
         <is>
-          <t>uplink.hud.link.edge</t>
+          <t>uplink.hud.reason.no_uplink</t>
         </is>
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>边缘 · 还剩 {0} 格</t>
+          <t>这台机器没有接入口</t>
         </is>
       </c>
       <c r="D1729" t="inlineStr">
         <is>
-          <t>edge · {0} cells left</t>
+          <t>this machine has no uplink port</t>
         </is>
       </c>
     </row>
@@ -31554,17 +31554,17 @@
       <c r="A1730" t="inlineStr"/>
       <c r="B1730" t="inlineStr">
         <is>
-          <t>uplink.hud.link.unbounded</t>
+          <t>uplink.hud.reason.off_path</t>
         </is>
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>链路 满 · 此地不受覆盖限制</t>
+          <t>接入口不在导线上</t>
         </is>
       </c>
       <c r="D1730" t="inlineStr">
         <is>
-          <t>Link full · no coverage limit here</t>
+          <t>the uplink port is not on a wire</t>
         </is>
       </c>
     </row>
@@ -31572,17 +31572,17 @@
       <c r="A1731" t="inlineStr"/>
       <c r="B1731" t="inlineStr">
         <is>
-          <t>uplink.hud.link.grace</t>
+          <t>uplink.hud.slot_tip</t>
         </is>
       </c>
       <c r="C1731" t="inlineStr">
         <is>
-          <t>链路中断（{0}）：{1} 秒内恢复</t>
+          <t>{0} 号槽：{1}</t>
         </is>
       </c>
       <c r="D1731" t="inlineStr">
         <is>
-          <t>Link lost ({0}): recover within {1}s</t>
+          <t>Slot {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -31590,17 +31590,17 @@
       <c r="A1732" t="inlineStr"/>
       <c r="B1732" t="inlineStr">
         <is>
-          <t>uplink.hud.link_tip</t>
+          <t>uplink.hud.heat</t>
         </is>
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
+          <t>热量 {0}/{1}</t>
         </is>
       </c>
       <c r="D1732" t="inlineStr">
         <is>
-          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
+          <t>Heat {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31608,17 +31608,17 @@
       <c r="A1733" t="inlineStr"/>
       <c r="B1733" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure</t>
+          <t>uplink.hud.overheated</t>
         </is>
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>暴露 {0}</t>
+          <t>过热：散热到 {0} 以下才开火</t>
         </is>
       </c>
       <c r="D1733" t="inlineStr">
         <is>
-          <t>Exposure {0}</t>
+          <t>Overheated: fires again below {0}</t>
         </is>
       </c>
     </row>
@@ -31626,17 +31626,17 @@
       <c r="A1734" t="inlineStr"/>
       <c r="B1734" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure_tip</t>
+          <t>uplink.hud.heat_tip</t>
         </is>
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
+          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
         </is>
       </c>
       <c r="D1734" t="inlineStr">
         <is>
-          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
+          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
         </is>
       </c>
     </row>
@@ -31644,17 +31644,17 @@
       <c r="A1735" t="inlineStr"/>
       <c r="B1735" t="inlineStr">
         <is>
-          <t>uplink.hud.morph</t>
+          <t>uplink.hud.battery</t>
         </is>
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>电池 {0}%</t>
         </is>
       </c>
       <c r="D1735" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Battery {0}%</t>
         </is>
       </c>
     </row>
@@ -31662,17 +31662,17 @@
       <c r="A1736" t="inlineStr"/>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>uplink.hud.morph_source</t>
+          <t>uplink.hud.battery_tip</t>
         </is>
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
         </is>
       </c>
       <c r="D1736" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
         </is>
       </c>
     </row>
@@ -31680,17 +31680,17 @@
       <c r="A1737" t="inlineStr"/>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>uplink.hud.no_port</t>
+          <t>uplink.hud.health</t>
         </is>
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
+          <t>耐久 {0}/{1}</t>
         </is>
       </c>
       <c r="D1737" t="inlineStr">
         <is>
-          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+          <t>Durability {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31698,17 +31698,17 @@
       <c r="A1738" t="inlineStr"/>
       <c r="B1738" t="inlineStr">
         <is>
-          <t>uplink.hud.core_empty</t>
+          <t>uplink.hud.injury_none</t>
         </is>
       </c>
       <c r="C1738" t="inlineStr">
         <is>
-          <t>信号核没有固件（按 {0} 打开信号核）</t>
+          <t>伤势：无</t>
         </is>
       </c>
       <c r="D1738" t="inlineStr">
         <is>
-          <t>The Signal Core is empty (press {0} to open it)</t>
+          <t>Injuries: none</t>
         </is>
       </c>
     </row>
@@ -31716,17 +31716,17 @@
       <c r="A1739" t="inlineStr"/>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>uplink.hud.experience</t>
+          <t>uplink.hud.injury</t>
         </is>
       </c>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>伤势：{0}</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>Injuries: {0}</t>
         </is>
       </c>
     </row>
@@ -31734,17 +31734,17 @@
       <c r="A1740" t="inlineStr"/>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>uplink.hud.keys</t>
+          <t>uplink.hud.health_tip</t>
         </is>
       </c>
       <c r="C1740" t="inlineStr">
         <is>
-          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
+          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
         </is>
       </c>
       <c r="D1740" t="inlineStr">
         <is>
-          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
+          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
         </is>
       </c>
     </row>
@@ -31752,17 +31752,17 @@
       <c r="A1741" t="inlineStr"/>
       <c r="B1741" t="inlineStr">
         <is>
-          <t>morph.state.none</t>
+          <t>uplink.hud.link</t>
         </is>
       </c>
       <c r="C1741" t="inlineStr">
         <is>
-          <t>常态</t>
+          <t>链路 {0}% · {1}</t>
         </is>
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>Link {0}% · {1}</t>
         </is>
       </c>
     </row>
@@ -31770,17 +31770,17 @@
       <c r="A1742" t="inlineStr"/>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>morph.state.limiter</t>
+          <t>uplink.hud.link.strong</t>
         </is>
       </c>
       <c r="C1742" t="inlineStr">
         <is>
-          <t>形变态</t>
+          <t>强</t>
         </is>
       </c>
       <c r="D1742" t="inlineStr">
         <is>
-          <t>morph state</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -31788,17 +31788,17 @@
       <c r="A1743" t="inlineStr"/>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>morph.state.fluid</t>
+          <t>uplink.hud.link.medium</t>
         </is>
       </c>
       <c r="C1743" t="inlineStr">
         <is>
-          <t>喷口态</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D1743" t="inlineStr">
         <is>
-          <t>vent state</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -31806,17 +31806,17 @@
       <c r="A1744" t="inlineStr"/>
       <c r="B1744" t="inlineStr">
         <is>
-          <t>morph.state.em</t>
+          <t>uplink.hud.link.weak</t>
         </is>
       </c>
       <c r="C1744" t="inlineStr">
         <is>
-          <t>线圈态</t>
+          <t>弱</t>
         </is>
       </c>
       <c r="D1744" t="inlineStr">
         <is>
-          <t>coil state</t>
+          <t>weak</t>
         </is>
       </c>
     </row>
@@ -31824,17 +31824,17 @@
       <c r="A1745" t="inlineStr"/>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>morph.state.join</t>
+          <t>uplink.hud.link.edge</t>
         </is>
       </c>
       <c r="C1745" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>边缘 · 还剩 {0} 格</t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>edge · {0} cells left</t>
         </is>
       </c>
     </row>
@@ -31842,17 +31842,17 @@
       <c r="A1746" t="inlineStr"/>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>signal.list.port_tag</t>
+          <t>uplink.hud.link.unbounded</t>
         </is>
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>◇口</t>
+          <t>链路 满 · 此地不受覆盖限制</t>
         </is>
       </c>
       <c r="D1746" t="inlineStr">
         <is>
-          <t>◇PORT</t>
+          <t>Link full · no coverage limit here</t>
         </is>
       </c>
     </row>
@@ -31860,17 +31860,17 @@
       <c r="A1747" t="inlineStr"/>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>signal.list.overheat_tag</t>
+          <t>uplink.hud.link.grace</t>
         </is>
       </c>
       <c r="C1747" t="inlineStr">
         <is>
-          <t>过热</t>
+          <t>链路中断（{0}）：{1} 秒内恢复</t>
         </is>
       </c>
       <c r="D1747" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>Link lost ({0}): recover within {1}s</t>
         </is>
       </c>
     </row>
@@ -31878,17 +31878,17 @@
       <c r="A1748" t="inlineStr"/>
       <c r="B1748" t="inlineStr">
         <is>
-          <t>signal.list.port_line</t>
+          <t>uplink.hud.link_tip</t>
         </is>
       </c>
       <c r="C1748" t="inlineStr">
         <is>
-          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
+          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
         </is>
       </c>
       <c r="D1748" t="inlineStr">
         <is>
-          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
+          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
         </is>
       </c>
     </row>
@@ -31896,17 +31896,17 @@
       <c r="A1749" t="inlineStr"/>
       <c r="B1749" t="inlineStr">
         <is>
-          <t>signal.list.no_port_line</t>
+          <t>uplink.hud.exposure</t>
         </is>
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>没有接入口：接入后只能驾驶，不插入固件</t>
+          <t>暴露 {0}</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
         <is>
-          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
+          <t>Exposure {0}</t>
         </is>
       </c>
     </row>
@@ -31914,17 +31914,17 @@
       <c r="A1750" t="inlineStr"/>
       <c r="B1750" t="inlineStr">
         <is>
-          <t>signal.list.overheat_line</t>
+          <t>uplink.hud.exposure_tip</t>
         </is>
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
+          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>Overheated (heat {0}): it fires again once below {1}</t>
+          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
         </is>
       </c>
     </row>
@@ -31932,7 +31932,7 @@
       <c r="A1751" t="inlineStr"/>
       <c r="B1751" t="inlineStr">
         <is>
-          <t>signal.list.morph_line</t>
+          <t>uplink.hud.morph</t>
         </is>
       </c>
       <c r="C1751" t="inlineStr">
@@ -31950,17 +31950,17 @@
       <c r="A1752" t="inlineStr"/>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>signal.list.experience_line</t>
+          <t>uplink.hud.morph_source</t>
         </is>
       </c>
       <c r="C1752" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -31968,17 +31968,17 @@
       <c r="A1753" t="inlineStr"/>
       <c r="B1753" t="inlineStr">
         <is>
-          <t>signal.port_badge.tip</t>
+          <t>uplink.hud.no_port</t>
         </is>
       </c>
       <c r="C1753" t="inlineStr">
         <is>
-          <t>带接入口的机器</t>
+          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
         </is>
       </c>
       <c r="D1753" t="inlineStr">
         <is>
-          <t>Machine with an uplink port</t>
+          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -31986,17 +31986,17 @@
       <c r="A1754" t="inlineStr"/>
       <c r="B1754" t="inlineStr">
         <is>
-          <t>machine.exp.produced</t>
+          <t>uplink.hud.core_empty</t>
         </is>
       </c>
       <c r="C1754" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>信号核没有固件（按 {0} 打开信号核）</t>
         </is>
       </c>
       <c r="D1754" t="inlineStr">
         <is>
-          <t>Produced</t>
+          <t>The Signal Core is empty (press {0} to open it)</t>
         </is>
       </c>
     </row>
@@ -32004,17 +32004,17 @@
       <c r="A1755" t="inlineStr"/>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>machine.exp.first_job</t>
+          <t>uplink.hud.experience</t>
         </is>
       </c>
       <c r="C1755" t="inlineStr">
         <is>
-          <t>首次工作</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1755" t="inlineStr">
         <is>
-          <t>First job</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -32022,17 +32022,17 @@
       <c r="A1756" t="inlineStr"/>
       <c r="B1756" t="inlineStr">
         <is>
-          <t>machine.exp.controlled</t>
+          <t>uplink.hud.keys</t>
         </is>
       </c>
       <c r="C1756" t="inlineStr">
         <is>
-          <t>首次与信号同行</t>
+          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
         </is>
       </c>
       <c r="D1756" t="inlineStr">
         <is>
-          <t>First time with the signal</t>
+          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
         </is>
       </c>
     </row>
@@ -32040,17 +32040,17 @@
       <c r="A1757" t="inlineStr"/>
       <c r="B1757" t="inlineStr">
         <is>
-          <t>machine.exp.expedition</t>
+          <t>morph.state.none</t>
         </is>
       </c>
       <c r="C1757" t="inlineStr">
         <is>
-          <t>远征</t>
+          <t>常态</t>
         </is>
       </c>
       <c r="D1757" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -32058,17 +32058,17 @@
       <c r="A1758" t="inlineStr"/>
       <c r="B1758" t="inlineStr">
         <is>
-          <t>machine.exp.severely_injured</t>
+          <t>morph.state.limiter</t>
         </is>
       </c>
       <c r="C1758" t="inlineStr">
         <is>
-          <t>重伤</t>
+          <t>形变态</t>
         </is>
       </c>
       <c r="D1758" t="inlineStr">
         <is>
-          <t>Severely injured</t>
+          <t>morph state</t>
         </is>
       </c>
     </row>
@@ -32076,17 +32076,17 @@
       <c r="A1759" t="inlineStr"/>
       <c r="B1759" t="inlineStr">
         <is>
-          <t>machine.exp.elite_kill</t>
+          <t>morph.state.fluid</t>
         </is>
       </c>
       <c r="C1759" t="inlineStr">
         <is>
-          <t>精英击破</t>
+          <t>喷口态</t>
         </is>
       </c>
       <c r="D1759" t="inlineStr">
         <is>
-          <t>Elite kill</t>
+          <t>vent state</t>
         </is>
       </c>
     </row>
@@ -32094,17 +32094,17 @@
       <c r="A1760" t="inlineStr"/>
       <c r="B1760" t="inlineStr">
         <is>
-          <t>machine.exp.boss_participation</t>
+          <t>morph.state.em</t>
         </is>
       </c>
       <c r="C1760" t="inlineStr">
         <is>
-          <t>首领战</t>
+          <t>线圈态</t>
         </is>
       </c>
       <c r="D1760" t="inlineStr">
         <is>
-          <t>Boss fight</t>
+          <t>coil state</t>
         </is>
       </c>
     </row>
@@ -32112,17 +32112,17 @@
       <c r="A1761" t="inlineStr"/>
       <c r="B1761" t="inlineStr">
         <is>
-          <t>machine.exp.returned</t>
+          <t>morph.state.join</t>
         </is>
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>返航</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
     </row>
@@ -32130,17 +32130,17 @@
       <c r="A1762" t="inlineStr"/>
       <c r="B1762" t="inlineStr">
         <is>
-          <t>machine.exp.sep</t>
+          <t>signal.list.port_tag</t>
         </is>
       </c>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>◇口</t>
         </is>
       </c>
       <c r="D1762" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>◇PORT</t>
         </is>
       </c>
     </row>
@@ -32148,17 +32148,17 @@
       <c r="A1763" t="inlineStr"/>
       <c r="B1763" t="inlineStr">
         <is>
-          <t>machine.injury.combat</t>
+          <t>signal.list.overheat_tag</t>
         </is>
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>战斗损伤（HP {0}/{1}）</t>
+          <t>过热</t>
         </is>
       </c>
       <c r="D1763" t="inlineStr">
         <is>
-          <t>Combat damage (HP {0}/{1})</t>
+          <t>HOT</t>
         </is>
       </c>
     </row>
@@ -32166,17 +32166,17 @@
       <c r="A1764" t="inlineStr"/>
       <c r="B1764" t="inlineStr">
         <is>
-          <t>machine.exp.none</t>
+          <t>signal.list.port_line</t>
         </is>
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>无记录经历</t>
+          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
         </is>
       </c>
       <c r="D1764" t="inlineStr">
         <is>
-          <t>No recorded experience</t>
+          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
         </is>
       </c>
     </row>
@@ -32184,17 +32184,17 @@
       <c r="A1765" t="inlineStr"/>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>machine.exp.signal</t>
+          <t>signal.list.no_port_line</t>
         </is>
       </c>
       <c r="C1765" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次，累计 {1}</t>
+          <t>没有接入口：接入后只能驾驶，不插入固件</t>
         </is>
       </c>
       <c r="D1765" t="inlineStr">
         <is>
-          <t>With the signal {0} times, {1} in total</t>
+          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -32202,17 +32202,17 @@
       <c r="A1766" t="inlineStr"/>
       <c r="B1766" t="inlineStr">
         <is>
-          <t>machine.exp.signal_none</t>
+          <t>signal.list.overheat_line</t>
         </is>
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>尚未与信号同行</t>
+          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
         </is>
       </c>
       <c r="D1766" t="inlineStr">
         <is>
-          <t>Never carried the signal</t>
+          <t>Overheated (heat {0}): it fires again once below {1}</t>
         </is>
       </c>
     </row>
@@ -32220,17 +32220,17 @@
       <c r="A1767" t="inlineStr"/>
       <c r="B1767" t="inlineStr">
         <is>
-          <t>machine.status.dead</t>
+          <t>signal.list.morph_line</t>
         </is>
       </c>
       <c r="C1767" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录）</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1767" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record)</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -32238,17 +32238,17 @@
       <c r="A1768" t="inlineStr"/>
       <c r="B1768" t="inlineStr">
         <is>
-          <t>machine.status.in_factory</t>
+          <t>signal.list.experience_line</t>
         </is>
       </c>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>厂内待驶出</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1768" t="inlineStr">
         <is>
-          <t>Waiting in the factory</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -32256,17 +32256,17 @@
       <c r="A1769" t="inlineStr"/>
       <c r="B1769" t="inlineStr">
         <is>
-          <t>machine.status.uplinked</t>
+          <t>signal.port_badge.tip</t>
         </is>
       </c>
       <c r="C1769" t="inlineStr">
         <is>
-          <t>接入中</t>
+          <t>带接入口的机器</t>
         </is>
       </c>
       <c r="D1769" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>Machine with an uplink port</t>
         </is>
       </c>
     </row>
@@ -32274,17 +32274,17 @@
       <c r="A1770" t="inlineStr"/>
       <c r="B1770" t="inlineStr">
         <is>
-          <t>machine.status.idle</t>
+          <t>machine.exp.produced</t>
         </is>
       </c>
       <c r="C1770" t="inlineStr">
         <is>
-          <t>空闲</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="D1770" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>Produced</t>
         </is>
       </c>
     </row>
@@ -32292,17 +32292,17 @@
       <c r="A1771" t="inlineStr"/>
       <c r="B1771" t="inlineStr">
         <is>
-          <t>machine.status.working</t>
+          <t>machine.exp.first_job</t>
         </is>
       </c>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>首次工作</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>First job</t>
         </is>
       </c>
     </row>
@@ -32310,17 +32310,17 @@
       <c r="A1772" t="inlineStr"/>
       <c r="B1772" t="inlineStr">
         <is>
-          <t>machine.detail.none</t>
+          <t>machine.exp.controlled</t>
         </is>
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>首次与信号同行</t>
         </is>
       </c>
       <c r="D1772" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>First time with the signal</t>
         </is>
       </c>
     </row>
@@ -32328,17 +32328,17 @@
       <c r="A1773" t="inlineStr"/>
       <c r="B1773" t="inlineStr">
         <is>
-          <t>machine.detail.injury_none</t>
+          <t>machine.exp.expedition</t>
         </is>
       </c>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>无记录</t>
+          <t>远征</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Expedition</t>
         </is>
       </c>
     </row>
@@ -32346,17 +32346,17 @@
       <c r="A1774" t="inlineStr"/>
       <c r="B1774" t="inlineStr">
         <is>
-          <t>machine.detail.port_yes</t>
+          <t>machine.exp.severely_injured</t>
         </is>
       </c>
       <c r="C1774" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>重伤</t>
         </is>
       </c>
       <c r="D1774" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Severely injured</t>
         </is>
       </c>
     </row>
@@ -32364,17 +32364,17 @@
       <c r="A1775" t="inlineStr"/>
       <c r="B1775" t="inlineStr">
         <is>
-          <t>machine.detail.port_no</t>
+          <t>machine.exp.elite_kill</t>
         </is>
       </c>
       <c r="C1775" t="inlineStr">
         <is>
-          <t>没有</t>
+          <t>精英击破</t>
         </is>
       </c>
       <c r="D1775" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Elite kill</t>
         </is>
       </c>
     </row>
@@ -32382,17 +32382,17 @@
       <c r="A1776" t="inlineStr"/>
       <c r="B1776" t="inlineStr">
         <is>
-          <t>machine.detail.line_id</t>
+          <t>machine.exp.boss_participation</t>
         </is>
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+          <t>首领战</t>
         </is>
       </c>
       <c r="D1776" t="inlineStr">
         <is>
-          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+          <t>Boss fight</t>
         </is>
       </c>
     </row>
@@ -32400,17 +32400,17 @@
       <c r="A1777" t="inlineStr"/>
       <c r="B1777" t="inlineStr">
         <is>
-          <t>machine.detail.line_vitals</t>
+          <t>machine.exp.returned</t>
         </is>
       </c>
       <c r="C1777" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+          <t>返航</t>
         </is>
       </c>
       <c r="D1777" t="inlineStr">
         <is>
-          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
@@ -32418,17 +32418,17 @@
       <c r="A1778" t="inlineStr"/>
       <c r="B1778" t="inlineStr">
         <is>
-          <t>machine.detail.line_exp</t>
+          <t>machine.exp.sep</t>
         </is>
       </c>
       <c r="C1778" t="inlineStr">
         <is>
-          <t>经历：{0}</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1778" t="inlineStr">
         <is>
-          <t>Experience: {0}</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -32436,17 +32436,17 @@
       <c r="A1779" t="inlineStr"/>
       <c r="B1779" t="inlineStr">
         <is>
-          <t>machine.detail.line_signal</t>
+          <t>machine.injury.combat</t>
         </is>
       </c>
       <c r="C1779" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>战斗损伤（HP {0}/{1}）</t>
         </is>
       </c>
       <c r="D1779" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Combat damage (HP {0}/{1})</t>
         </is>
       </c>
     </row>
@@ -32454,17 +32454,17 @@
       <c r="A1780" t="inlineStr"/>
       <c r="B1780" t="inlineStr">
         <is>
-          <t>machine.detail.line_stats</t>
+          <t>machine.exp.none</t>
         </is>
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+          <t>无记录经历</t>
         </is>
       </c>
       <c r="D1780" t="inlineStr">
         <is>
-          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+          <t>No recorded experience</t>
         </is>
       </c>
     </row>
@@ -32472,17 +32472,17 @@
       <c r="A1781" t="inlineStr"/>
       <c r="B1781" t="inlineStr">
         <is>
-          <t>machine.detail.line_morph</t>
+          <t>machine.exp.signal</t>
         </is>
       </c>
       <c r="C1781" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>与信号同行 {0} 次，累计 {1}</t>
         </is>
       </c>
       <c r="D1781" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>With the signal {0} times, {1} in total</t>
         </is>
       </c>
     </row>
@@ -32490,17 +32490,17 @@
       <c r="A1782" t="inlineStr"/>
       <c r="B1782" t="inlineStr">
         <is>
-          <t>victory.summary</t>
+          <t>machine.exp.signal_none</t>
         </is>
       </c>
       <c r="C1782" t="inlineStr">
         <is>
-          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+          <t>尚未与信号同行</t>
         </is>
       </c>
       <c r="D1782" t="inlineStr">
         <is>
-          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+          <t>Never carried the signal</t>
         </is>
       </c>
     </row>
@@ -32508,17 +32508,17 @@
       <c r="A1783" t="inlineStr"/>
       <c r="B1783" t="inlineStr">
         <is>
-          <t>victory.row.number</t>
+          <t>machine.status.dead</t>
         </is>
       </c>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>#{0}（{1}）</t>
+          <t>阵亡（纪念记录）</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
         <is>
-          <t>#{0} ({1})</t>
+          <t>Destroyed (memorial record)</t>
         </is>
       </c>
     </row>
@@ -32526,17 +32526,17 @@
       <c r="A1784" t="inlineStr"/>
       <c r="B1784" t="inlineStr">
         <is>
-          <t>victory.row.alive</t>
+          <t>machine.status.in_factory</t>
         </is>
       </c>
       <c r="C1784" t="inlineStr">
         <is>
-          <t>幸存</t>
+          <t>厂内待驶出</t>
         </is>
       </c>
       <c r="D1784" t="inlineStr">
         <is>
-          <t>survived</t>
+          <t>Waiting in the factory</t>
         </is>
       </c>
     </row>
@@ -32544,17 +32544,17 @@
       <c r="A1785" t="inlineStr"/>
       <c r="B1785" t="inlineStr">
         <is>
-          <t>victory.row.dead</t>
+          <t>machine.status.uplinked</t>
         </is>
       </c>
       <c r="C1785" t="inlineStr">
         <is>
-          <t>阵亡</t>
+          <t>接入中</t>
         </is>
       </c>
       <c r="D1785" t="inlineStr">
         <is>
-          <t>destroyed</t>
+          <t>Uplinked</t>
         </is>
       </c>
     </row>
@@ -32562,17 +32562,17 @@
       <c r="A1786" t="inlineStr"/>
       <c r="B1786" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_alive</t>
+          <t>machine.status.idle</t>
         </is>
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>幸存，将随撤离返回家园；{0}</t>
+          <t>空闲</t>
         </is>
       </c>
       <c r="D1786" t="inlineStr">
         <is>
-          <t>Survived and returns home with the evacuation; {0}</t>
+          <t>Idle</t>
         </is>
       </c>
     </row>
@@ -32580,17 +32580,17 @@
       <c r="A1787" t="inlineStr"/>
       <c r="B1787" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_dead</t>
+          <t>machine.status.working</t>
         </is>
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+          <t>工作中</t>
         </is>
       </c>
       <c r="D1787" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -32598,17 +32598,17 @@
       <c r="A1788" t="inlineStr"/>
       <c r="B1788" t="inlineStr">
         <is>
-          <t>factory.reason.uplinked</t>
+          <t>machine.detail.none</t>
         </is>
       </c>
       <c r="C1788" t="inlineStr">
         <is>
-          <t>这台机器正被你接入，先退出接入</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D1788" t="inlineStr">
         <is>
-          <t>You are uplinked into this machine: leave the uplink first</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -32616,17 +32616,17 @@
       <c r="A1789" t="inlineStr"/>
       <c r="B1789" t="inlineStr">
         <is>
-          <t>signal.cmd.uplinked</t>
+          <t>machine.detail.injury_none</t>
         </is>
       </c>
       <c r="C1789" t="inlineStr">
         <is>
-          <t>接入：{0}</t>
+          <t>无记录</t>
         </is>
       </c>
       <c r="D1789" t="inlineStr">
         <is>
-          <t>Uplinked: {0}</t>
+          <t>none recorded</t>
         </is>
       </c>
     </row>
@@ -32634,17 +32634,17 @@
       <c r="A1790" t="inlineStr"/>
       <c r="B1790" t="inlineStr">
         <is>
-          <t>signal.cmd.reconnecting</t>
+          <t>machine.detail.port_yes</t>
         </is>
       </c>
       <c r="C1790" t="inlineStr">
         <is>
-          <t>重连中：{0}</t>
+          <t>有</t>
         </is>
       </c>
       <c r="D1790" t="inlineStr">
         <is>
-          <t>Reconnecting: {0}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -32652,17 +32652,17 @@
       <c r="A1791" t="inlineStr"/>
       <c r="B1791" t="inlineStr">
         <is>
-          <t>signal.cmd.strategy</t>
+          <t>machine.detail.port_no</t>
         </is>
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>战略视角</t>
+          <t>没有</t>
         </is>
       </c>
       <c r="D1791" t="inlineStr">
         <is>
-          <t>Strategy view</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -32670,17 +32670,17 @@
       <c r="A1792" t="inlineStr"/>
       <c r="B1792" t="inlineStr">
         <is>
-          <t>region.control.fail.not_found</t>
+          <t>machine.detail.line_id</t>
         </is>
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>没有可以接入的目标。</t>
+          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
         </is>
       </c>
       <c r="D1792" t="inlineStr">
         <is>
-          <t>There is nothing to uplink into.</t>
+          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
         </is>
       </c>
     </row>
@@ -32688,17 +32688,17 @@
       <c r="A1793" t="inlineStr"/>
       <c r="B1793" t="inlineStr">
         <is>
-          <t>region.control.fail.not_friendly</t>
+          <t>machine.detail.line_vitals</t>
         </is>
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>目标不属于本地点。</t>
+          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
         </is>
       </c>
       <c r="D1793" t="inlineStr">
         <is>
-          <t>The target does not belong to this site.</t>
+          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
         </is>
       </c>
     </row>
@@ -32706,17 +32706,17 @@
       <c r="A1794" t="inlineStr"/>
       <c r="B1794" t="inlineStr">
         <is>
-          <t>region.control.fail.dead</t>
+          <t>machine.detail.line_exp</t>
         </is>
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>目标已阵亡。</t>
+          <t>经历：{0}</t>
         </is>
       </c>
       <c r="D1794" t="inlineStr">
         <is>
-          <t>The target is destroyed.</t>
+          <t>Experience: {0}</t>
         </is>
       </c>
     </row>
@@ -32724,17 +32724,17 @@
       <c r="A1795" t="inlineStr"/>
       <c r="B1795" t="inlineStr">
         <is>
-          <t>region.control.fail.out_of_range</t>
+          <t>machine.detail.line_signal</t>
         </is>
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>目标当前不在场。</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D1795" t="inlineStr">
         <is>
-          <t>The target is not here right now.</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -32742,17 +32742,17 @@
       <c r="A1796" t="inlineStr"/>
       <c r="B1796" t="inlineStr">
         <is>
-          <t>region.control.fail.jammed</t>
+          <t>machine.detail.line_stats</t>
         </is>
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>信号被干扰，接入失败。</t>
+          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
         </is>
       </c>
       <c r="D1796" t="inlineStr">
         <is>
-          <t>The signal is jammed; uplink failed.</t>
+          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
         </is>
       </c>
     </row>
@@ -32760,17 +32760,17 @@
       <c r="A1797" t="inlineStr"/>
       <c r="B1797" t="inlineStr">
         <is>
-          <t>region.control.fail.transition</t>
+          <t>machine.detail.line_morph</t>
         </is>
       </c>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>镜头切换中，请稍候。</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1797" t="inlineStr">
         <is>
-          <t>The camera is moving; please wait.</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -32778,17 +32778,17 @@
       <c r="A1798" t="inlineStr"/>
       <c r="B1798" t="inlineStr">
         <is>
-          <t>region.control.fail.modal</t>
+          <t>victory.summary</t>
         </is>
       </c>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>请先关闭当前面板。</t>
+          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
         <is>
-          <t>Close the current panel first.</t>
+          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
         </is>
       </c>
     </row>
@@ -32796,17 +32796,17 @@
       <c r="A1799" t="inlineStr"/>
       <c r="B1799" t="inlineStr">
         <is>
-          <t>region.control.fail.already</t>
+          <t>victory.row.number</t>
         </is>
       </c>
       <c r="C1799" t="inlineStr">
         <is>
-          <t>已经接入这台机器。</t>
+          <t>#{0}（{1}）</t>
         </is>
       </c>
       <c r="D1799" t="inlineStr">
         <is>
-          <t>You are already uplinked into this machine.</t>
+          <t>#{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -32814,17 +32814,17 @@
       <c r="A1800" t="inlineStr"/>
       <c r="B1800" t="inlineStr">
         <is>
-          <t>region.control.fail.ineligible</t>
+          <t>victory.row.alive</t>
         </is>
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>目标暂时不能接入。</t>
+          <t>幸存</t>
         </is>
       </c>
       <c r="D1800" t="inlineStr">
         <is>
-          <t>The target cannot be uplinked right now.</t>
+          <t>survived</t>
         </is>
       </c>
     </row>
@@ -32832,17 +32832,17 @@
       <c r="A1801" t="inlineStr"/>
       <c r="B1801" t="inlineStr">
         <is>
-          <t>region.control.fail.other</t>
+          <t>victory.row.dead</t>
         </is>
       </c>
       <c r="C1801" t="inlineStr">
         <is>
-          <t>接入失败。</t>
+          <t>阵亡</t>
         </is>
       </c>
       <c r="D1801" t="inlineStr">
         <is>
-          <t>Uplink failed.</t>
+          <t>destroyed</t>
         </is>
       </c>
     </row>
@@ -32850,17 +32850,17 @@
       <c r="A1802" t="inlineStr"/>
       <c r="B1802" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink</t>
+          <t>expedition.return.row_status_alive</t>
         </is>
       </c>
       <c r="C1802" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>幸存，将随撤离返回家园；{0}</t>
         </is>
       </c>
       <c r="D1802" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>Survived and returns home with the evacuation; {0}</t>
         </is>
       </c>
     </row>
@@ -32868,17 +32868,17 @@
       <c r="A1803" t="inlineStr"/>
       <c r="B1803" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink</t>
+          <t>expedition.return.row_status_dead</t>
         </is>
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>已接入</t>
+          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
         </is>
       </c>
       <c r="D1803" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
         </is>
       </c>
     </row>
@@ -32886,17 +32886,17 @@
       <c r="A1804" t="inlineStr"/>
       <c r="B1804" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink_leave</t>
+          <t>factory.reason.uplinked</t>
         </is>
       </c>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>这台机器正被你接入，先退出接入</t>
         </is>
       </c>
       <c r="D1804" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>You are uplinked into this machine: leave the uplink first</t>
         </is>
       </c>
     </row>
@@ -32904,17 +32904,17 @@
       <c r="A1805" t="inlineStr"/>
       <c r="B1805" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink_leave</t>
+          <t>signal.cmd.uplinked</t>
         </is>
       </c>
       <c r="C1805" t="inlineStr">
         <is>
-          <t>信号离开机器</t>
+          <t>接入：{0}</t>
         </is>
       </c>
       <c r="D1805" t="inlineStr">
         <is>
-          <t>The signal left the machine</t>
+          <t>Uplinked: {0}</t>
         </is>
       </c>
     </row>
@@ -32922,17 +32922,17 @@
       <c r="A1806" t="inlineStr"/>
       <c r="B1806" t="inlineStr">
         <is>
-          <t>pause.codex</t>
+          <t>signal.cmd.reconnecting</t>
         </is>
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>重连中：{0}</t>
         </is>
       </c>
       <c r="D1806" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Reconnecting: {0}</t>
         </is>
       </c>
     </row>
@@ -32940,17 +32940,17 @@
       <c r="A1807" t="inlineStr"/>
       <c r="B1807" t="inlineStr">
         <is>
-          <t>pause.camera_title</t>
+          <t>signal.cmd.strategy</t>
         </is>
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>接入镜头</t>
+          <t>战略视角</t>
         </is>
       </c>
       <c r="D1807" t="inlineStr">
         <is>
-          <t>Uplink camera</t>
+          <t>Strategy view</t>
         </is>
       </c>
     </row>
@@ -32958,17 +32958,17 @@
       <c r="A1808" t="inlineStr"/>
       <c r="B1808" t="inlineStr">
         <is>
-          <t>pause.camera_zoom</t>
+          <t>region.control.fail.not_found</t>
         </is>
       </c>
       <c r="C1808" t="inlineStr">
         <is>
-          <t>接入时镜头距离 {0}%</t>
+          <t>没有可以接入的目标。</t>
         </is>
       </c>
       <c r="D1808" t="inlineStr">
         <is>
-          <t>Uplink camera distance {0}%</t>
+          <t>There is nothing to uplink into.</t>
         </is>
       </c>
     </row>
@@ -32976,17 +32976,17 @@
       <c r="A1809" t="inlineStr"/>
       <c r="B1809" t="inlineStr">
         <is>
-          <t>pause.camera_follow</t>
+          <t>region.control.fail.not_friendly</t>
         </is>
       </c>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>接入时跟随力度 {0}%</t>
+          <t>目标不属于本地点。</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
         <is>
-          <t>Uplink follow strength {0}%</t>
+          <t>The target does not belong to this site.</t>
         </is>
       </c>
     </row>
@@ -32994,17 +32994,17 @@
       <c r="A1810" t="inlineStr"/>
       <c r="B1810" t="inlineStr">
         <is>
-          <t>pause.camera_reset</t>
+          <t>region.control.fail.dead</t>
         </is>
       </c>
       <c r="C1810" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>目标已阵亡。</t>
         </is>
       </c>
       <c r="D1810" t="inlineStr">
         <is>
-          <t>Reset to default</t>
+          <t>The target is destroyed.</t>
         </is>
       </c>
     </row>
@@ -33012,17 +33012,17 @@
       <c r="A1811" t="inlineStr"/>
       <c r="B1811" t="inlineStr">
         <is>
-          <t>pause.camera_zoom_tip</t>
+          <t>region.control.fail.out_of_range</t>
         </is>
       </c>
       <c r="C1811" t="inlineStr">
         <is>
-          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>目标当前不在场。</t>
         </is>
       </c>
       <c r="D1811" t="inlineStr">
         <is>
-          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>The target is not here right now.</t>
         </is>
       </c>
     </row>
@@ -33030,17 +33030,17 @@
       <c r="A1812" t="inlineStr"/>
       <c r="B1812" t="inlineStr">
         <is>
-          <t>pause.camera_follow_tip</t>
+          <t>region.control.fail.jammed</t>
         </is>
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>信号被干扰，接入失败。</t>
         </is>
       </c>
       <c r="D1812" t="inlineStr">
         <is>
-          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>The signal is jammed; uplink failed.</t>
         </is>
       </c>
     </row>
@@ -33048,17 +33048,17 @@
       <c r="A1813" t="inlineStr"/>
       <c r="B1813" t="inlineStr">
         <is>
-          <t>camera.follow.started</t>
+          <t>region.control.fail.transition</t>
         </is>
       </c>
       <c r="C1813" t="inlineStr">
         <is>
-          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+          <t>镜头切换中，请稍候。</t>
         </is>
       </c>
       <c r="D1813" t="inlineStr">
         <is>
-          <t>Camera following {0} (pan or press {1} again to stop)</t>
+          <t>The camera is moving; please wait.</t>
         </is>
       </c>
     </row>
@@ -33066,17 +33066,17 @@
       <c r="A1814" t="inlineStr"/>
       <c r="B1814" t="inlineStr">
         <is>
-          <t>camera.follow.stopped</t>
+          <t>region.control.fail.modal</t>
         </is>
       </c>
       <c r="C1814" t="inlineStr">
         <is>
-          <t>镜头停止跟随</t>
+          <t>请先关闭当前面板。</t>
         </is>
       </c>
       <c r="D1814" t="inlineStr">
         <is>
-          <t>Camera follow stopped</t>
+          <t>Close the current panel first.</t>
         </is>
       </c>
     </row>
@@ -33084,17 +33084,17 @@
       <c r="A1815" t="inlineStr"/>
       <c r="B1815" t="inlineStr">
         <is>
-          <t>camera.follow.nothing</t>
+          <t>region.control.fail.already</t>
         </is>
       </c>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>先选中一台机器再按 {0} 跟随</t>
+          <t>已经接入这台机器。</t>
         </is>
       </c>
       <c r="D1815" t="inlineStr">
         <is>
-          <t>Select a machine first, then press {0} to follow it</t>
+          <t>You are already uplinked into this machine.</t>
         </is>
       </c>
     </row>
@@ -33102,17 +33102,17 @@
       <c r="A1816" t="inlineStr"/>
       <c r="B1816" t="inlineStr">
         <is>
-          <t>camera.follow.group</t>
+          <t>region.control.fail.ineligible</t>
         </is>
       </c>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>{0} 台机器</t>
+          <t>目标暂时不能接入。</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">
         <is>
-          <t>{0} machines</t>
+          <t>The target cannot be uplinked right now.</t>
         </is>
       </c>
     </row>
@@ -33120,17 +33120,17 @@
       <c r="A1817" t="inlineStr"/>
       <c r="B1817" t="inlineStr">
         <is>
-          <t>fwlib.title</t>
+          <t>region.control.fail.other</t>
         </is>
       </c>
       <c r="C1817" t="inlineStr">
         <is>
-          <t>固件库</t>
+          <t>接入失败。</t>
         </is>
       </c>
       <c r="D1817" t="inlineStr">
         <is>
-          <t>Firmware library</t>
+          <t>Uplink failed.</t>
         </is>
       </c>
     </row>
@@ -33138,17 +33138,17 @@
       <c r="A1818" t="inlineStr"/>
       <c r="B1818" t="inlineStr">
         <is>
-          <t>fwlib.close</t>
+          <t>feedback.tag.uplink</t>
         </is>
       </c>
       <c r="C1818" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D1818" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -33156,17 +33156,17 @@
       <c r="A1819" t="inlineStr"/>
       <c r="B1819" t="inlineStr">
         <is>
-          <t>fwlib.count</t>
+          <t>feedback.caption.uplink</t>
         </is>
       </c>
       <c r="C1819" t="inlineStr">
         <is>
-          <t>芯片 {0} 枚（显示 {1}）· 仓储 {2}/{3} 格</t>
+          <t>已接入</t>
         </is>
       </c>
       <c r="D1819" t="inlineStr">
         <is>
-          <t>Chips {0} (showing {1}) · Storage {2}/{3}</t>
+          <t>Uplinked</t>
         </is>
       </c>
     </row>
@@ -33174,17 +33174,17 @@
       <c r="A1820" t="inlineStr"/>
       <c r="B1820" t="inlineStr">
         <is>
-          <t>fwlib.over_capacity</t>
+          <t>feedback.tag.uplink_leave</t>
         </is>
       </c>
       <c r="C1820" t="inlineStr">
         <is>
-          <t>仓储已满：新得到的芯片会进入待领取</t>
+          <t>离开</t>
         </is>
       </c>
       <c r="D1820" t="inlineStr">
         <is>
-          <t>Storage is full: new chips go to the claim queue</t>
+          <t>Leave</t>
         </is>
       </c>
     </row>
@@ -33192,17 +33192,17 @@
       <c r="A1821" t="inlineStr"/>
       <c r="B1821" t="inlineStr">
         <is>
-          <t>fwlib.search</t>
+          <t>feedback.caption.uplink_leave</t>
         </is>
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>搜索名称或说明</t>
+          <t>信号离开机器</t>
         </is>
       </c>
       <c r="D1821" t="inlineStr">
         <is>
-          <t>Search name or description</t>
+          <t>The signal left the machine</t>
         </is>
       </c>
     </row>
@@ -33210,17 +33210,17 @@
       <c r="A1822" t="inlineStr"/>
       <c r="B1822" t="inlineStr">
         <is>
-          <t>fwlib.filter.category</t>
+          <t>pause.codex</t>
         </is>
       </c>
       <c r="C1822" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="D1822" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -33228,17 +33228,17 @@
       <c r="A1823" t="inlineStr"/>
       <c r="B1823" t="inlineStr">
         <is>
-          <t>fwlib.filter.kind</t>
+          <t>pause.camera_title</t>
         </is>
       </c>
       <c r="C1823" t="inlineStr">
         <is>
-          <t>种类</t>
+          <t>接入镜头</t>
         </is>
       </c>
       <c r="D1823" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Uplink camera</t>
         </is>
       </c>
     </row>
@@ -33246,17 +33246,17 @@
       <c r="A1824" t="inlineStr"/>
       <c r="B1824" t="inlineStr">
         <is>
-          <t>fwlib.filter.protocol</t>
+          <t>pause.camera_zoom</t>
         </is>
       </c>
       <c r="C1824" t="inlineStr">
         <is>
-          <t>协议</t>
+          <t>接入时镜头距离 {0}%</t>
         </is>
       </c>
       <c r="D1824" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Uplink camera distance {0}%</t>
         </is>
       </c>
     </row>
@@ -33264,17 +33264,17 @@
       <c r="A1825" t="inlineStr"/>
       <c r="B1825" t="inlineStr">
         <is>
-          <t>fwlib.filter.cracked</t>
+          <t>pause.camera_follow</t>
         </is>
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>破解</t>
+          <t>接入时跟随力度 {0}%</t>
         </is>
       </c>
       <c r="D1825" t="inlineStr">
         <is>
-          <t>Cracked</t>
+          <t>Uplink follow strength {0}%</t>
         </is>
       </c>
     </row>
@@ -33282,17 +33282,17 @@
       <c r="A1826" t="inlineStr"/>
       <c r="B1826" t="inlineStr">
         <is>
-          <t>fwlib.filter.carrier</t>
+          <t>pause.camera_reset</t>
         </is>
       </c>
       <c r="C1826" t="inlineStr">
         <is>
-          <t>兼容载体</t>
+          <t>恢复默认</t>
         </is>
       </c>
       <c r="D1826" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Reset to default</t>
         </is>
       </c>
     </row>
@@ -33300,17 +33300,17 @@
       <c r="A1827" t="inlineStr"/>
       <c r="B1827" t="inlineStr">
         <is>
-          <t>fwlib.filter.rarity</t>
+          <t>pause.camera_zoom_tip</t>
         </is>
       </c>
       <c r="C1827" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
         </is>
       </c>
       <c r="D1827" t="inlineStr">
         <is>
-          <t>Rarity</t>
+          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
         </is>
       </c>
     </row>
@@ -33318,17 +33318,17 @@
       <c r="A1828" t="inlineStr"/>
       <c r="B1828" t="inlineStr">
         <is>
-          <t>fwlib.sort</t>
+          <t>pause.camera_follow_tip</t>
         </is>
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
         </is>
       </c>
       <c r="D1828" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
         </is>
       </c>
     </row>
@@ -33336,17 +33336,17 @@
       <c r="A1829" t="inlineStr"/>
       <c r="B1829" t="inlineStr">
         <is>
-          <t>fwlib.any</t>
+          <t>camera.follow.started</t>
         </is>
       </c>
       <c r="C1829" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
         </is>
       </c>
       <c r="D1829" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Camera following {0} (pan or press {1} again to stop)</t>
         </is>
       </c>
     </row>
@@ -33354,17 +33354,17 @@
       <c r="A1830" t="inlineStr"/>
       <c r="B1830" t="inlineStr">
         <is>
-          <t>fwlib.kind.regular</t>
+          <t>camera.follow.stopped</t>
         </is>
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>● 常规</t>
+          <t>镜头停止跟随</t>
         </is>
       </c>
       <c r="D1830" t="inlineStr">
         <is>
-          <t>● Regular</t>
+          <t>Camera follow stopped</t>
         </is>
       </c>
     </row>
@@ -33372,17 +33372,17 @@
       <c r="A1831" t="inlineStr"/>
       <c r="B1831" t="inlineStr">
         <is>
-          <t>fwlib.kind.core</t>
+          <t>camera.follow.nothing</t>
         </is>
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>◆ 核心</t>
+          <t>先选中一台机器再按 {0} 跟随</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
         <is>
-          <t>◆ Core</t>
+          <t>Select a machine first, then press {0} to follow it</t>
         </is>
       </c>
     </row>
@@ -33390,17 +33390,17 @@
       <c r="A1832" t="inlineStr"/>
       <c r="B1832" t="inlineStr">
         <is>
-          <t>fwlib.protocol.own</t>
+          <t>camera.follow.group</t>
         </is>
       </c>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>己方 / 中立</t>
+          <t>{0} 台机器</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
         <is>
-          <t>Own / neutral</t>
+          <t>{0} machines</t>
         </is>
       </c>
     </row>
@@ -33408,17 +33408,17 @@
       <c r="A1833" t="inlineStr"/>
       <c r="B1833" t="inlineStr">
         <is>
-          <t>fwlib.cracked.yes</t>
+          <t>fwlib.title</t>
         </is>
       </c>
       <c r="C1833" t="inlineStr">
         <is>
-          <t>已破解</t>
+          <t>固件库</t>
         </is>
       </c>
       <c r="D1833" t="inlineStr">
         <is>
-          <t>Cracked</t>
+          <t>Firmware library</t>
         </is>
       </c>
     </row>
@@ -33426,17 +33426,17 @@
       <c r="A1834" t="inlineStr"/>
       <c r="B1834" t="inlineStr">
         <is>
-          <t>fwlib.cracked.no</t>
+          <t>fwlib.close</t>
         </is>
       </c>
       <c r="C1834" t="inlineStr">
         <is>
-          <t>▲ 未破解</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1834" t="inlineStr">
         <is>
-          <t>▲ Not cracked</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -33444,17 +33444,17 @@
       <c r="A1835" t="inlineStr"/>
       <c r="B1835" t="inlineStr">
         <is>
-          <t>fwlib.sort.name</t>
+          <t>fwlib.count</t>
         </is>
       </c>
       <c r="C1835" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>芯片 {0} 枚（显示 {1}）· 仓储 {2}/{3} 格</t>
         </is>
       </c>
       <c r="D1835" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Chips {0} (showing {1}) · Storage {2}/{3}</t>
         </is>
       </c>
     </row>
@@ -33462,17 +33462,17 @@
       <c r="A1836" t="inlineStr"/>
       <c r="B1836" t="inlineStr">
         <is>
-          <t>fwlib.sort.category</t>
+          <t>fwlib.over_capacity</t>
         </is>
       </c>
       <c r="C1836" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>仓储已满：新得到的芯片会进入待领取</t>
         </is>
       </c>
       <c r="D1836" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Storage is full: new chips go to the claim queue</t>
         </is>
       </c>
     </row>
@@ -33480,17 +33480,17 @@
       <c r="A1837" t="inlineStr"/>
       <c r="B1837" t="inlineStr">
         <is>
-          <t>fwlib.sort.rarity</t>
+          <t>fwlib.search</t>
         </is>
       </c>
       <c r="C1837" t="inlineStr">
         <is>
-          <t>稀有度（高→低）</t>
+          <t>搜索名称或说明</t>
         </is>
       </c>
       <c r="D1837" t="inlineStr">
         <is>
-          <t>Rarity (high→low)</t>
+          <t>Search name or description</t>
         </is>
       </c>
     </row>
@@ -33498,17 +33498,17 @@
       <c r="A1838" t="inlineStr"/>
       <c r="B1838" t="inlineStr">
         <is>
-          <t>fwlib.sort.load</t>
+          <t>fwlib.filter.category</t>
         </is>
       </c>
       <c r="C1838" t="inlineStr">
         <is>
-          <t>负载（高→低）</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D1838" t="inlineStr">
         <is>
-          <t>Load (high→low)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -33516,17 +33516,17 @@
       <c r="A1839" t="inlineStr"/>
       <c r="B1839" t="inlineStr">
         <is>
-          <t>fwlib.sort.newest</t>
+          <t>fwlib.filter.kind</t>
         </is>
       </c>
       <c r="C1839" t="inlineStr">
         <is>
-          <t>最新获得</t>
+          <t>种类</t>
         </is>
       </c>
       <c r="D1839" t="inlineStr">
         <is>
-          <t>Newest</t>
+          <t>Kind</t>
         </is>
       </c>
     </row>
@@ -33534,17 +33534,17 @@
       <c r="A1840" t="inlineStr"/>
       <c r="B1840" t="inlineStr">
         <is>
-          <t>fwlib.sort.location</t>
+          <t>fwlib.filter.protocol</t>
         </is>
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>所在位置</t>
+          <t>协议</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Protocol</t>
         </is>
       </c>
     </row>
@@ -33552,17 +33552,17 @@
       <c r="A1841" t="inlineStr"/>
       <c r="B1841" t="inlineStr">
         <is>
-          <t>fwlib.empty</t>
+          <t>fwlib.filter.cracked</t>
         </is>
       </c>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>还没有固件芯片。在信号核面板里刻印，或从远征带回。</t>
+          <t>破解</t>
         </is>
       </c>
       <c r="D1841" t="inlineStr">
         <is>
-          <t>No firmware chips yet. Print them in the Signal Core panel or bring them back from expeditions.</t>
+          <t>Cracked</t>
         </is>
       </c>
     </row>
@@ -33570,17 +33570,17 @@
       <c r="A1842" t="inlineStr"/>
       <c r="B1842" t="inlineStr">
         <is>
-          <t>fwlib.empty_filtered</t>
+          <t>fwlib.filter.carrier</t>
         </is>
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>没有符合筛选条件的芯片。</t>
+          <t>兼容载体</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
         <is>
-          <t>No chips match the filters.</t>
+          <t>Carrier</t>
         </is>
       </c>
     </row>
@@ -33588,17 +33588,17 @@
       <c r="A1843" t="inlineStr"/>
       <c r="B1843" t="inlineStr">
         <is>
-          <t>fwlib.error</t>
+          <t>fwlib.filter.rarity</t>
         </is>
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>固件数据不可用（配置表缺失），请重新安装或联系开发者：{0}</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
         <is>
-          <t>Firmware data is unavailable (missing table); reinstall or contact the developers: {0}</t>
+          <t>Rarity</t>
         </is>
       </c>
     </row>
@@ -33606,17 +33606,17 @@
       <c r="A1844" t="inlineStr"/>
       <c r="B1844" t="inlineStr">
         <is>
-          <t>fwlib.loc.storage</t>
+          <t>fwlib.sort</t>
         </is>
       </c>
       <c r="C1844" t="inlineStr">
         <is>
-          <t>仓储</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="D1844" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Sort</t>
         </is>
       </c>
     </row>
@@ -33624,17 +33624,17 @@
       <c r="A1845" t="inlineStr"/>
       <c r="B1845" t="inlineStr">
         <is>
-          <t>fwlib.loc.pending</t>
+          <t>fwlib.any</t>
         </is>
       </c>
       <c r="C1845" t="inlineStr">
         <is>
-          <t>待领取（仓储已满）</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D1845" t="inlineStr">
         <is>
-          <t>Awaiting claim (storage full)</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -33642,17 +33642,17 @@
       <c r="A1846" t="inlineStr"/>
       <c r="B1846" t="inlineStr">
         <is>
-          <t>fwlib.loc.signal</t>
+          <t>fwlib.kind.regular</t>
         </is>
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>信号核 第 {0} 槽</t>
+          <t>● 常规</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
         <is>
-          <t>Signal Core slot {0}</t>
+          <t>● Regular</t>
         </is>
       </c>
     </row>
@@ -33660,17 +33660,17 @@
       <c r="A1847" t="inlineStr"/>
       <c r="B1847" t="inlineStr">
         <is>
-          <t>fwlib.loc.reserved</t>
+          <t>fwlib.kind.core</t>
         </is>
       </c>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>仓储（合成台预留中）</t>
+          <t>◆ 核心</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
         <is>
-          <t>Storage (reserved by crafting)</t>
+          <t>◆ Core</t>
         </is>
       </c>
     </row>
@@ -33678,17 +33678,17 @@
       <c r="A1848" t="inlineStr"/>
       <c r="B1848" t="inlineStr">
         <is>
-          <t>fwlib.loc.draft</t>
+          <t>fwlib.protocol.own</t>
         </is>
       </c>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>蓝图电路（{0}）</t>
+          <t>己方 / 中立</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">
         <is>
-          <t>Blueprint circuit ({0})</t>
+          <t>Own / neutral</t>
         </is>
       </c>
     </row>
@@ -33696,17 +33696,17 @@
       <c r="A1849" t="inlineStr"/>
       <c r="B1849" t="inlineStr">
         <is>
-          <t>fwlib.row.locked</t>
+          <t>fwlib.cracked.yes</t>
         </is>
       </c>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>［锁定］</t>
+          <t>已破解</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
         <is>
-          <t>[Locked]</t>
+          <t>Cracked</t>
         </is>
       </c>
     </row>
@@ -33714,17 +33714,17 @@
       <c r="A1850" t="inlineStr"/>
       <c r="B1850" t="inlineStr">
         <is>
-          <t>fwlib.select_all</t>
+          <t>fwlib.cracked.no</t>
         </is>
       </c>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>全选当前列表</t>
+          <t>▲ 未破解</t>
         </is>
       </c>
       <c r="D1850" t="inlineStr">
         <is>
-          <t>Select all shown</t>
+          <t>▲ Not cracked</t>
         </is>
       </c>
     </row>
@@ -33732,17 +33732,17 @@
       <c r="A1851" t="inlineStr"/>
       <c r="B1851" t="inlineStr">
         <is>
-          <t>fwlib.select_none</t>
+          <t>fwlib.sort.name</t>
         </is>
       </c>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>清空选择</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
         <is>
-          <t>Clear selection</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -33750,17 +33750,17 @@
       <c r="A1852" t="inlineStr"/>
       <c r="B1852" t="inlineStr">
         <is>
-          <t>fwlib.selected</t>
+          <t>fwlib.sort.category</t>
         </is>
       </c>
       <c r="C1852" t="inlineStr">
         <is>
-          <t>已选 {0} 枚</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D1852" t="inlineStr">
         <is>
-          <t>{0} selected</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -33768,17 +33768,17 @@
       <c r="A1853" t="inlineStr"/>
       <c r="B1853" t="inlineStr">
         <is>
-          <t>fwlib.row.pick</t>
+          <t>fwlib.sort.rarity</t>
         </is>
       </c>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>选</t>
+          <t>稀有度（高→低）</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
         <is>
-          <t>Pick</t>
+          <t>Rarity (high→low)</t>
         </is>
       </c>
     </row>
@@ -33786,17 +33786,17 @@
       <c r="A1854" t="inlineStr"/>
       <c r="B1854" t="inlineStr">
         <is>
-          <t>fwlib.row.picked</t>
+          <t>fwlib.sort.load</t>
         </is>
       </c>
       <c r="C1854" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>负载（高→低）</t>
         </is>
       </c>
       <c r="D1854" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>Load (high→low)</t>
         </is>
       </c>
     </row>
@@ -33804,17 +33804,17 @@
       <c r="A1855" t="inlineStr"/>
       <c r="B1855" t="inlineStr">
         <is>
-          <t>fwlib.disassemble</t>
+          <t>fwlib.sort.newest</t>
         </is>
       </c>
       <c r="C1855" t="inlineStr">
         <is>
-          <t>分解所选（{0}）</t>
+          <t>最新获得</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
         <is>
-          <t>Disassemble selected ({0})</t>
+          <t>Newest</t>
         </is>
       </c>
     </row>
@@ -33822,17 +33822,17 @@
       <c r="A1856" t="inlineStr"/>
       <c r="B1856" t="inlineStr">
         <is>
-          <t>fwlib.disassemble_tip</t>
+          <t>fwlib.sort.location</t>
         </is>
       </c>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>分解返还废料 {0}/枚。锁定的、装进信号核的、被合成台预留的会跳过。需要确认，无法撤销。</t>
+          <t>所在位置</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
         <is>
-          <t>Each chip refunds {0} scrap. Locked chips, chips in the Signal Core and chips reserved by crafting are skipped. Needs confirmation; cannot be undone.</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
@@ -33840,17 +33840,17 @@
       <c r="A1857" t="inlineStr"/>
       <c r="B1857" t="inlineStr">
         <is>
-          <t>fwlib.confirm.title</t>
+          <t>fwlib.empty</t>
         </is>
       </c>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>分解固件芯片</t>
+          <t>还没有固件芯片。在信号核面板里刻印，或从远征带回。</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
         <is>
-          <t>Disassemble firmware chips</t>
+          <t>No firmware chips yet. Print them in the Signal Core panel or bring them back from expeditions.</t>
         </is>
       </c>
     </row>
@@ -33858,17 +33858,17 @@
       <c r="A1858" t="inlineStr"/>
       <c r="B1858" t="inlineStr">
         <is>
-          <t>fwlib.confirm.lose</t>
+          <t>fwlib.empty_filtered</t>
         </is>
       </c>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>固件芯片 ×{0}（返还废料 +{1}）</t>
+          <t>没有符合筛选条件的芯片。</t>
         </is>
       </c>
       <c r="D1858" t="inlineStr">
         <is>
-          <t>Firmware chips ×{0} (refund +{1} scrap)</t>
+          <t>No chips match the filters.</t>
         </is>
       </c>
     </row>
@@ -33876,17 +33876,17 @@
       <c r="A1859" t="inlineStr"/>
       <c r="B1859" t="inlineStr">
         <is>
-          <t>fwlib.confirm.unprintable</t>
+          <t>fwlib.error</t>
         </is>
       </c>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>其中 {0} 枚目前无法再刻印（未解锁或未破解）</t>
+          <t>固件数据不可用（配置表缺失），请重新安装或联系开发者：{0}</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
         <is>
-          <t>{0} of them cannot be printed again right now (locked or not cracked)</t>
+          <t>Firmware data is unavailable (missing table); reinstall or contact the developers: {0}</t>
         </is>
       </c>
     </row>
@@ -33894,17 +33894,17 @@
       <c r="A1860" t="inlineStr"/>
       <c r="B1860" t="inlineStr">
         <is>
-          <t>fwlib.confirm.skip_locked</t>
+          <t>fwlib.loc.storage</t>
         </is>
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>跳过锁定的 {0} 枚</t>
+          <t>仓储</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
         <is>
-          <t>Skipping {0} locked</t>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -33912,17 +33912,17 @@
       <c r="A1861" t="inlineStr"/>
       <c r="B1861" t="inlineStr">
         <is>
-          <t>fwlib.confirm.skip_busy</t>
+          <t>fwlib.loc.pending</t>
         </is>
       </c>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>跳过装进信号核或被合成台预留的 {0} 枚</t>
+          <t>待领取（仓储已满）</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
         <is>
-          <t>Skipping {0} in the Signal Core or reserved by crafting</t>
+          <t>Awaiting claim (storage full)</t>
         </is>
       </c>
     </row>
@@ -33930,17 +33930,17 @@
       <c r="A1862" t="inlineStr"/>
       <c r="B1862" t="inlineStr">
         <is>
-          <t>fwlib.confirm.names</t>
+          <t>fwlib.loc.signal</t>
         </is>
       </c>
       <c r="C1862" t="inlineStr">
         <is>
-          <t>包括：{0}</t>
+          <t>信号核 第 {0} 槽</t>
         </is>
       </c>
       <c r="D1862" t="inlineStr">
         <is>
-          <t>Includes: {0}</t>
+          <t>Signal Core slot {0}</t>
         </is>
       </c>
     </row>
@@ -33948,17 +33948,17 @@
       <c r="A1863" t="inlineStr"/>
       <c r="B1863" t="inlineStr">
         <is>
-          <t>fwlib.confirm.name_count</t>
+          <t>fwlib.loc.reserved</t>
         </is>
       </c>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>{0} ×{1}</t>
+          <t>仓储（合成台预留中）</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
         <is>
-          <t>{0} ×{1}</t>
+          <t>Storage (reserved by crafting)</t>
         </is>
       </c>
     </row>
@@ -33966,17 +33966,17 @@
       <c r="A1864" t="inlineStr"/>
       <c r="B1864" t="inlineStr">
         <is>
-          <t>fwlib.confirm.name_more</t>
+          <t>fwlib.loc.draft</t>
         </is>
       </c>
       <c r="C1864" t="inlineStr">
         <is>
-          <t>等另外 {0} 种</t>
+          <t>蓝图电路（{0}）</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
         <is>
-          <t>and {0} more kinds</t>
+          <t>Blueprint circuit ({0})</t>
         </is>
       </c>
     </row>
@@ -33984,17 +33984,17 @@
       <c r="A1865" t="inlineStr"/>
       <c r="B1865" t="inlineStr">
         <is>
-          <t>fwlib.confirm.hidden</t>
+          <t>fwlib.row.locked</t>
         </is>
       </c>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>其中 {0} 枚不在当前筛选结果里（之前勾选的）</t>
+          <t>［锁定］</t>
         </is>
       </c>
       <c r="D1865" t="inlineStr">
         <is>
-          <t>{0} of them are outside the current filter (picked earlier)</t>
+          <t>[Locked]</t>
         </is>
       </c>
     </row>
@@ -34002,17 +34002,17 @@
       <c r="A1866" t="inlineStr"/>
       <c r="B1866" t="inlineStr">
         <is>
-          <t>fwlib.confirm.ok</t>
+          <t>fwlib.select_all</t>
         </is>
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>分解</t>
+          <t>全选当前列表</t>
         </is>
       </c>
       <c r="D1866" t="inlineStr">
         <is>
-          <t>Disassemble</t>
+          <t>Select all shown</t>
         </is>
       </c>
     </row>
@@ -34020,17 +34020,17 @@
       <c r="A1867" t="inlineStr"/>
       <c r="B1867" t="inlineStr">
         <is>
-          <t>fwlib.confirm.cancel</t>
+          <t>fwlib.select_none</t>
         </is>
       </c>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>清空选择</t>
         </is>
       </c>
       <c r="D1867" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Clear selection</t>
         </is>
       </c>
     </row>
@@ -34038,17 +34038,17 @@
       <c r="A1868" t="inlineStr"/>
       <c r="B1868" t="inlineStr">
         <is>
-          <t>fwlib.result.done</t>
+          <t>fwlib.selected</t>
         </is>
       </c>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>已分解 {0} 枚，返还废料 {1}；跳过 {2} 枚</t>
+          <t>已选 {0} 枚</t>
         </is>
       </c>
       <c r="D1868" t="inlineStr">
         <is>
-          <t>Disassembled {0}, refunded {1} scrap; skipped {2}</t>
+          <t>{0} selected</t>
         </is>
       </c>
     </row>
@@ -34056,17 +34056,17 @@
       <c r="A1869" t="inlineStr"/>
       <c r="B1869" t="inlineStr">
         <is>
-          <t>fwlib.result.nothing</t>
+          <t>fwlib.row.pick</t>
         </is>
       </c>
       <c r="C1869" t="inlineStr">
         <is>
-          <t>没有可分解的芯片：所选的都已锁定或正在使用</t>
+          <t>选</t>
         </is>
       </c>
       <c r="D1869" t="inlineStr">
         <is>
-          <t>Nothing to disassemble: every selected chip is locked or in use</t>
+          <t>Pick</t>
         </is>
       </c>
     </row>
@@ -34074,17 +34074,17 @@
       <c r="A1870" t="inlineStr"/>
       <c r="B1870" t="inlineStr">
         <is>
-          <t>fwlib.lock</t>
+          <t>fwlib.row.picked</t>
         </is>
       </c>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>锁定</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -34092,17 +34092,17 @@
       <c r="A1871" t="inlineStr"/>
       <c r="B1871" t="inlineStr">
         <is>
-          <t>fwlib.unlock</t>
+          <t>fwlib.disassemble</t>
         </is>
       </c>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>解除锁定</t>
+          <t>分解所选（{0}）</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
         <is>
-          <t>Unlock</t>
+          <t>Disassemble selected ({0})</t>
         </is>
       </c>
     </row>
@@ -34110,17 +34110,17 @@
       <c r="A1872" t="inlineStr"/>
       <c r="B1872" t="inlineStr">
         <is>
-          <t>fwlib.lock_tip</t>
+          <t>fwlib.disassemble_tip</t>
         </is>
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>锁定后，批量分解会跳过这枚芯片（不影响装进信号核）。</t>
+          <t>分解返还废料 {0}/枚。锁定的、装进信号核的、被合成台预留的会跳过。需要确认，无法撤销。</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
         <is>
-          <t>Locked chips are skipped by bulk disassembly (they can still go into the Signal Core).</t>
+          <t>Each chip refunds {0} scrap. Locked chips, chips in the Signal Core and chips reserved by crafting are skipped. Needs confirmation; cannot be undone.</t>
         </is>
       </c>
     </row>
@@ -34128,17 +34128,17 @@
       <c r="A1873" t="inlineStr"/>
       <c r="B1873" t="inlineStr">
         <is>
-          <t>fwlib.claim</t>
+          <t>fwlib.confirm.title</t>
         </is>
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>领取进仓储</t>
+          <t>分解固件芯片</t>
         </is>
       </c>
       <c r="D1873" t="inlineStr">
         <is>
-          <t>Claim into storage</t>
+          <t>Disassemble firmware chips</t>
         </is>
       </c>
     </row>
@@ -34146,17 +34146,17 @@
       <c r="A1874" t="inlineStr"/>
       <c r="B1874" t="inlineStr">
         <is>
-          <t>fwlib.codex</t>
+          <t>fwlib.confirm.lose</t>
         </is>
       </c>
       <c r="C1874" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>固件芯片 ×{0}（返还废料 +{1}）</t>
         </is>
       </c>
       <c r="D1874" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>Firmware chips ×{0} (refund +{1} scrap)</t>
         </is>
       </c>
     </row>
@@ -34164,17 +34164,17 @@
       <c r="A1875" t="inlineStr"/>
       <c r="B1875" t="inlineStr">
         <is>
-          <t>fwlib.compare_a</t>
+          <t>fwlib.confirm.unprintable</t>
         </is>
       </c>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>设为比较 A</t>
+          <t>其中 {0} 枚目前无法再刻印（未解锁或未破解）</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
         <is>
-          <t>Compare as A</t>
+          <t>{0} of them cannot be printed again right now (locked or not cracked)</t>
         </is>
       </c>
     </row>
@@ -34182,17 +34182,17 @@
       <c r="A1876" t="inlineStr"/>
       <c r="B1876" t="inlineStr">
         <is>
-          <t>fwlib.compare_b</t>
+          <t>fwlib.confirm.skip_locked</t>
         </is>
       </c>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>设为比较 B</t>
+          <t>跳过锁定的 {0} 枚</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
         <is>
-          <t>Compare as B</t>
+          <t>Skipping {0} locked</t>
         </is>
       </c>
     </row>
@@ -34200,17 +34200,17 @@
       <c r="A1877" t="inlineStr"/>
       <c r="B1877" t="inlineStr">
         <is>
-          <t>fwlib.compare.title</t>
+          <t>fwlib.confirm.skip_busy</t>
         </is>
       </c>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>比较</t>
+          <t>跳过装进信号核或被合成台预留的 {0} 枚</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Skipping {0} in the Signal Core or reserved by crafting</t>
         </is>
       </c>
     </row>
@@ -34218,17 +34218,17 @@
       <c r="A1878" t="inlineStr"/>
       <c r="B1878" t="inlineStr">
         <is>
-          <t>fwlib.compare.empty</t>
+          <t>fwlib.confirm.names</t>
         </is>
       </c>
       <c r="C1878" t="inlineStr">
         <is>
-          <t>选一枚芯片点“设为比较 A”，再选另一枚点“设为比较 B”，两条固件会并排显示。</t>
+          <t>包括：{0}</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
         <is>
-          <t>Pick a chip and press "Compare as A", then another and press "Compare as B" to see them side by side.</t>
+          <t>Includes: {0}</t>
         </is>
       </c>
     </row>
@@ -34236,17 +34236,17 @@
       <c r="A1879" t="inlineStr"/>
       <c r="B1879" t="inlineStr">
         <is>
-          <t>fwlib.compare.clear</t>
+          <t>fwlib.confirm.name_count</t>
         </is>
       </c>
       <c r="C1879" t="inlineStr">
         <is>
-          <t>清除比较</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
       <c r="D1879" t="inlineStr">
         <is>
-          <t>Clear compare</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
     </row>
@@ -34254,17 +34254,17 @@
       <c r="A1880" t="inlineStr"/>
       <c r="B1880" t="inlineStr">
         <is>
-          <t>fwlib.compare.same</t>
+          <t>fwlib.confirm.name_more</t>
         </is>
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>（相同）</t>
+          <t>等另外 {0} 种</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
         <is>
-          <t>(same)</t>
+          <t>and {0} more kinds</t>
         </is>
       </c>
     </row>
@@ -34272,17 +34272,17 @@
       <c r="A1881" t="inlineStr"/>
       <c r="B1881" t="inlineStr">
         <is>
-          <t>fwlib.compare.tags</t>
+          <t>fwlib.confirm.hidden</t>
         </is>
       </c>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>状态标签</t>
+          <t>其中 {0} 枚不在当前筛选结果里（之前勾选的）</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
         <is>
-          <t>Status tags</t>
+          <t>{0} of them are outside the current filter (picked earlier)</t>
         </is>
       </c>
     </row>
@@ -34290,17 +34290,17 @@
       <c r="A1882" t="inlineStr"/>
       <c r="B1882" t="inlineStr">
         <is>
-          <t>fwlib.detail.none</t>
+          <t>fwlib.confirm.ok</t>
         </is>
       </c>
       <c r="C1882" t="inlineStr">
         <is>
-          <t>在左侧选一枚芯片查看详情。</t>
+          <t>分解</t>
         </is>
       </c>
       <c r="D1882" t="inlineStr">
         <is>
-          <t>Pick a chip on the left to see its details.</t>
+          <t>Disassemble</t>
         </is>
       </c>
     </row>
@@ -34308,17 +34308,17 @@
       <c r="A1883" t="inlineStr"/>
       <c r="B1883" t="inlineStr">
         <is>
-          <t>fwlib.detail.kind</t>
+          <t>fwlib.confirm.cancel</t>
         </is>
       </c>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>种类：{0}</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
         <is>
-          <t>Kind: {0}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -34326,17 +34326,17 @@
       <c r="A1884" t="inlineStr"/>
       <c r="B1884" t="inlineStr">
         <is>
-          <t>fwlib.detail.category</t>
+          <t>fwlib.result.done</t>
         </is>
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>类别：{0}</t>
+          <t>已分解 {0} 枚，返还废料 {1}；跳过 {2} 枚</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
         <is>
-          <t>Category: {0}</t>
+          <t>Disassembled {0}, refunded {1} scrap; skipped {2}</t>
         </is>
       </c>
     </row>
@@ -34344,17 +34344,17 @@
       <c r="A1885" t="inlineStr"/>
       <c r="B1885" t="inlineStr">
         <is>
-          <t>fwlib.detail.protocol</t>
+          <t>fwlib.result.nothing</t>
         </is>
       </c>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>协议：{0}</t>
+          <t>没有可分解的芯片：所选的都已锁定或正在使用</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
         <is>
-          <t>Protocol: {0}</t>
+          <t>Nothing to disassemble: every selected chip is locked or in use</t>
         </is>
       </c>
     </row>
@@ -34362,17 +34362,17 @@
       <c r="A1886" t="inlineStr"/>
       <c r="B1886" t="inlineStr">
         <is>
-          <t>fwlib.detail.rarity</t>
+          <t>fwlib.lock</t>
         </is>
       </c>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>稀有度：{0}</t>
+          <t>锁定</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
         <is>
-          <t>Rarity: {0}</t>
+          <t>Lock</t>
         </is>
       </c>
     </row>
@@ -34380,17 +34380,17 @@
       <c r="A1887" t="inlineStr"/>
       <c r="B1887" t="inlineStr">
         <is>
-          <t>fwlib.detail.numbers</t>
+          <t>fwlib.unlock</t>
         </is>
       </c>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>负载 {0} · 每发耗电 {1} · 每发积热 {2}</t>
+          <t>解除锁定</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
         <is>
-          <t>Load {0} · Power per shot {1} · Heat per shot {2}</t>
+          <t>Unlock</t>
         </is>
       </c>
     </row>
@@ -34398,17 +34398,17 @@
       <c r="A1888" t="inlineStr"/>
       <c r="B1888" t="inlineStr">
         <is>
-          <t>fwlib.detail.tags</t>
+          <t>fwlib.lock_tip</t>
         </is>
       </c>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>产生的状态标签：{0}</t>
+          <t>锁定后，批量分解会跳过这枚芯片（不影响装进信号核）。</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
         <is>
-          <t>Status tags applied: {0}</t>
+          <t>Locked chips are skipped by bulk disassembly (they can still go into the Signal Core).</t>
         </is>
       </c>
     </row>
@@ -34416,17 +34416,17 @@
       <c r="A1889" t="inlineStr"/>
       <c r="B1889" t="inlineStr">
         <is>
-          <t>fwlib.detail.tags_none</t>
+          <t>fwlib.claim</t>
         </is>
       </c>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>产生的状态标签：无</t>
+          <t>领取进仓储</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
         <is>
-          <t>Status tags applied: none</t>
+          <t>Claim into storage</t>
         </is>
       </c>
     </row>
@@ -34434,17 +34434,17 @@
       <c r="A1890" t="inlineStr"/>
       <c r="B1890" t="inlineStr">
         <is>
-          <t>fwlib.detail.reactions</t>
+          <t>fwlib.codex</t>
         </is>
       </c>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>参与的反应：{0}</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
         <is>
-          <t>Reactions it takes part in: {0}</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -34452,17 +34452,17 @@
       <c r="A1891" t="inlineStr"/>
       <c r="B1891" t="inlineStr">
         <is>
-          <t>fwlib.detail.reactions_none</t>
+          <t>fwlib.compare_a</t>
         </is>
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>参与的反应：无</t>
+          <t>设为比较 A</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
         <is>
-          <t>Reactions it takes part in: none</t>
+          <t>Compare as A</t>
         </is>
       </c>
     </row>
@@ -34470,17 +34470,17 @@
       <c r="A1892" t="inlineStr"/>
       <c r="B1892" t="inlineStr">
         <is>
-          <t>fwlib.detail.reaction_unknown</t>
+          <t>fwlib.compare_b</t>
         </is>
       </c>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>？？？（尚未发现）</t>
+          <t>设为比较 B</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
         <is>
-          <t>??? (not discovered)</t>
+          <t>Compare as B</t>
         </is>
       </c>
     </row>
@@ -34488,17 +34488,17 @@
       <c r="A1893" t="inlineStr"/>
       <c r="B1893" t="inlineStr">
         <is>
-          <t>fwlib.detail.acquire</t>
+          <t>fwlib.compare.title</t>
         </is>
       </c>
       <c r="C1893" t="inlineStr">
         <is>
-          <t>获取途径：{0}</t>
+          <t>比较</t>
         </is>
       </c>
       <c r="D1893" t="inlineStr">
         <is>
-          <t>How to get it: {0}</t>
+          <t>Compare</t>
         </is>
       </c>
     </row>
@@ -34506,17 +34506,17 @@
       <c r="A1894" t="inlineStr"/>
       <c r="B1894" t="inlineStr">
         <is>
-          <t>fwlib.detail.held</t>
+          <t>fwlib.compare.empty</t>
         </is>
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>当前持有 {0} 枚：{1}</t>
+          <t>选一枚芯片点“设为比较 A”，再选另一枚点“设为比较 B”，两条固件会并排显示。</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
         <is>
-          <t>You hold {0}: {1}</t>
+          <t>Pick a chip and press "Compare as A", then another and press "Compare as B" to see them side by side.</t>
         </is>
       </c>
     </row>
@@ -34524,17 +34524,17 @@
       <c r="A1895" t="inlineStr"/>
       <c r="B1895" t="inlineStr">
         <is>
-          <t>fwlib.detail.held_none</t>
+          <t>fwlib.compare.clear</t>
         </is>
       </c>
       <c r="C1895" t="inlineStr">
         <is>
-          <t>当前持有 0 枚</t>
+          <t>清除比较</t>
         </is>
       </c>
       <c r="D1895" t="inlineStr">
         <is>
-          <t>You hold none</t>
+          <t>Clear compare</t>
         </is>
       </c>
     </row>
@@ -34542,17 +34542,17 @@
       <c r="A1896" t="inlineStr"/>
       <c r="B1896" t="inlineStr">
         <is>
-          <t>fwlib.detail.origin</t>
+          <t>fwlib.compare.same</t>
         </is>
       </c>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>这一枚的来源：{0}</t>
+          <t>（相同）</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
         <is>
-          <t>This chip came from: {0}</t>
+          <t>(same)</t>
         </is>
       </c>
     </row>
@@ -34560,17 +34560,17 @@
       <c r="A1897" t="inlineStr"/>
       <c r="B1897" t="inlineStr">
         <is>
-          <t>fwlib.origin.seed</t>
+          <t>fwlib.compare.tags</t>
         </is>
       </c>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>开局配发</t>
+          <t>状态标签</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
         <is>
-          <t>Starting issue</t>
+          <t>Status tags</t>
         </is>
       </c>
     </row>
@@ -34578,17 +34578,17 @@
       <c r="A1898" t="inlineStr"/>
       <c r="B1898" t="inlineStr">
         <is>
-          <t>fwlib.origin.print</t>
+          <t>fwlib.detail.none</t>
         </is>
       </c>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>装配站刻印</t>
+          <t>在左侧选一枚芯片查看详情。</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
         <is>
-          <t>Printed at the Assembly Station</t>
+          <t>Pick a chip on the left to see its details.</t>
         </is>
       </c>
     </row>
@@ -34596,17 +34596,17 @@
       <c r="A1899" t="inlineStr"/>
       <c r="B1899" t="inlineStr">
         <is>
-          <t>fwlib.origin.salvage</t>
+          <t>fwlib.detail.kind</t>
         </is>
       </c>
       <c r="C1899" t="inlineStr">
         <is>
-          <t>解析战利品</t>
+          <t>种类：{0}</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
         <is>
-          <t>Analysed salvage</t>
+          <t>Kind: {0}</t>
         </is>
       </c>
     </row>
@@ -34614,17 +34614,17 @@
       <c r="A1900" t="inlineStr"/>
       <c r="B1900" t="inlineStr">
         <is>
-          <t>fwlib.origin.encrypted</t>
+          <t>fwlib.detail.category</t>
         </is>
       </c>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>带回的敌方加密固件</t>
+          <t>类别：{0}</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
         <is>
-          <t>Recovered enemy-encrypted firmware</t>
+          <t>Category: {0}</t>
         </is>
       </c>
     </row>
@@ -34632,17 +34632,17 @@
       <c r="A1901" t="inlineStr"/>
       <c r="B1901" t="inlineStr">
         <is>
-          <t>fwlib.origin.craft</t>
+          <t>fwlib.detail.protocol</t>
         </is>
       </c>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>电路合成台</t>
+          <t>协议：{0}</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
         <is>
-          <t>Circuit Synthesizer</t>
+          <t>Protocol: {0}</t>
         </is>
       </c>
     </row>
@@ -34650,17 +34650,17 @@
       <c r="A1902" t="inlineStr"/>
       <c r="B1902" t="inlineStr">
         <is>
-          <t>fwlib.origin.unknown</t>
+          <t>fwlib.detail.rarity</t>
         </is>
       </c>
       <c r="C1902" t="inlineStr">
         <is>
-          <t>旧存档（来源未记录）</t>
+          <t>稀有度：{0}</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
         <is>
-          <t>Older save (source not recorded)</t>
+          <t>Rarity: {0}</t>
         </is>
       </c>
     </row>
@@ -34668,17 +34668,17 @@
       <c r="A1903" t="inlineStr"/>
       <c r="B1903" t="inlineStr">
         <is>
-          <t>fwlib.detail.route_ok</t>
+          <t>fwlib.detail.numbers</t>
         </is>
       </c>
       <c r="C1903" t="inlineStr">
         <is>
-          <t>取用路线：{0} → 装配站，通畅</t>
+          <t>负载 {0} · 每发耗电 {1} · 每发积热 {2}</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
         <is>
-          <t>Fetch route: {0} → Assembly Station, clear</t>
+          <t>Load {0} · Power per shot {1} · Heat per shot {2}</t>
         </is>
       </c>
     </row>
@@ -34686,17 +34686,17 @@
       <c r="A1904" t="inlineStr"/>
       <c r="B1904" t="inlineStr">
         <is>
-          <t>fwlib.detail.route_blocked</t>
+          <t>fwlib.detail.tags</t>
         </is>
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>取用路线：{0} → 装配站被堵住：{1}</t>
+          <t>产生的状态标签：{0}</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
         <is>
-          <t>Fetch route: {0} → Assembly Station is blocked: {1}</t>
+          <t>Status tags applied: {0}</t>
         </is>
       </c>
     </row>
@@ -34704,17 +34704,17 @@
       <c r="A1905" t="inlineStr"/>
       <c r="B1905" t="inlineStr">
         <is>
-          <t>fwlib.detail.route_unknown</t>
+          <t>fwlib.detail.tags_none</t>
         </is>
       </c>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>取用路线：家园地形还没载入，暂时无法检查</t>
+          <t>产生的状态标签：无</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
         <is>
-          <t>Fetch route: home terrain not loaded yet; cannot check</t>
+          <t>Status tags applied: none</t>
         </is>
       </c>
     </row>
@@ -34722,17 +34722,17 @@
       <c r="A1906" t="inlineStr"/>
       <c r="B1906" t="inlineStr">
         <is>
-          <t>fwlib.route.storage_enclosed</t>
+          <t>fwlib.detail.reactions</t>
         </is>
       </c>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>{0} 四周被 {1} 围住</t>
+          <t>参与的反应：{0}</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
         <is>
-          <t>{0} is walled in by {1}</t>
+          <t>Reactions it takes part in: {0}</t>
         </is>
       </c>
     </row>
@@ -34740,17 +34740,17 @@
       <c r="A1907" t="inlineStr"/>
       <c r="B1907" t="inlineStr">
         <is>
-          <t>fwlib.route.station_enclosed</t>
+          <t>fwlib.detail.reactions_none</t>
         </is>
       </c>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>装配站四周被 {0} 围住</t>
+          <t>参与的反应：无</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
         <is>
-          <t>the Assembly Station is walled in by {0}</t>
+          <t>Reactions it takes part in: none</t>
         </is>
       </c>
     </row>
@@ -34758,17 +34758,17 @@
       <c r="A1908" t="inlineStr"/>
       <c r="B1908" t="inlineStr">
         <is>
-          <t>fwlib.route.disconnected</t>
+          <t>fwlib.detail.reaction_unknown</t>
         </is>
       </c>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>两处之间没有能走通的路（被建筑或地形隔断）</t>
+          <t>？？？（尚未发现）</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
         <is>
-          <t>there is no walkable path between them (cut off by buildings or terrain)</t>
+          <t>??? (not discovered)</t>
         </is>
       </c>
     </row>
@@ -34776,17 +34776,17 @@
       <c r="A1909" t="inlineStr"/>
       <c r="B1909" t="inlineStr">
         <is>
-          <t>fwlib.route.no_station</t>
+          <t>fwlib.detail.acquire</t>
         </is>
       </c>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>家园还没有装配站</t>
+          <t>获取途径：{0}</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
         <is>
-          <t>the home has no Assembly Station yet</t>
+          <t>How to get it: {0}</t>
         </is>
       </c>
     </row>
@@ -34794,17 +34794,17 @@
       <c r="A1910" t="inlineStr"/>
       <c r="B1910" t="inlineStr">
         <is>
-          <t>fwlib.route.terrain</t>
+          <t>fwlib.detail.held</t>
         </is>
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>地形</t>
+          <t>当前持有 {0} 枚：{1}</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>You hold {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -34812,17 +34812,17 @@
       <c r="A1911" t="inlineStr"/>
       <c r="B1911" t="inlineStr">
         <is>
-          <t>fwlib.storage.core</t>
+          <t>fwlib.detail.held_none</t>
         </is>
       </c>
       <c r="C1911" t="inlineStr">
         <is>
-          <t>归还核心应急库</t>
+          <t>当前持有 0 枚</t>
         </is>
       </c>
       <c r="D1911" t="inlineStr">
         <is>
-          <t>Core emergency cache</t>
+          <t>You hold none</t>
         </is>
       </c>
     </row>
@@ -34830,17 +34830,17 @@
       <c r="A1912" t="inlineStr"/>
       <c r="B1912" t="inlineStr">
         <is>
-          <t>fwlib.footer</t>
+          <t>fwlib.detail.origin</t>
         </is>
       </c>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>悬停固件按 {act:OpenCodex} 查看图鉴 · 按 {act:OpenFirmware} 或 {act:Cancel} 关闭</t>
+          <t>这一枚的来源：{0}</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
         <is>
-          <t>Hover a firmware and press {act:OpenCodex} for its codex entry · Press {act:OpenFirmware} or {act:Cancel} to close</t>
+          <t>This chip came from: {0}</t>
         </is>
       </c>
     </row>
@@ -34848,17 +34848,17 @@
       <c r="A1913" t="inlineStr"/>
       <c r="B1913" t="inlineStr">
         <is>
-          <t>fwlib.readings_title</t>
+          <t>fwlib.origin.seed</t>
         </is>
       </c>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>各载体读法</t>
+          <t>开局配发</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
         <is>
-          <t>Readings by carrier</t>
+          <t>Starting issue</t>
         </is>
       </c>
     </row>
@@ -34866,17 +34866,17 @@
       <c r="A1914" t="inlineStr"/>
       <c r="B1914" t="inlineStr">
         <is>
-          <t>pause.firmware</t>
+          <t>fwlib.origin.print</t>
         </is>
       </c>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>固件库</t>
+          <t>装配站刻印</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
         <is>
-          <t>Firmware library</t>
+          <t>Printed at the Assembly Station</t>
         </is>
       </c>
     </row>
@@ -34884,17 +34884,17 @@
       <c r="A1915" t="inlineStr"/>
       <c r="B1915" t="inlineStr">
         <is>
-          <t>codex.tab.system</t>
+          <t>fwlib.origin.salvage</t>
         </is>
       </c>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>系统说明</t>
+          <t>解析战利品</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
         <is>
-          <t>Systems</t>
+          <t>Analysed salvage</t>
         </is>
       </c>
     </row>
@@ -34902,17 +34902,17 @@
       <c r="A1916" t="inlineStr"/>
       <c r="B1916" t="inlineStr">
         <is>
-          <t>codex.tab.firmware</t>
+          <t>fwlib.origin.encrypted</t>
         </is>
       </c>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>固件</t>
+          <t>带回的敌方加密固件</t>
         </is>
       </c>
       <c r="D1916" t="inlineStr">
         <is>
-          <t>Firmware</t>
+          <t>Recovered enemy-encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -34920,17 +34920,17 @@
       <c r="A1917" t="inlineStr"/>
       <c r="B1917" t="inlineStr">
         <is>
-          <t>codex.tab.reaction</t>
+          <t>fwlib.origin.craft</t>
         </is>
       </c>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>反应</t>
+          <t>电路合成台</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Circuit Synthesizer</t>
         </is>
       </c>
     </row>
@@ -34938,17 +34938,17 @@
       <c r="A1918" t="inlineStr"/>
       <c r="B1918" t="inlineStr">
         <is>
-          <t>codex.panel.search</t>
+          <t>fwlib.origin.unknown</t>
         </is>
       </c>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>搜索条目</t>
+          <t>旧存档（来源未记录）</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
         <is>
-          <t>Search entries</t>
+          <t>Older save (source not recorded)</t>
         </is>
       </c>
     </row>
@@ -34956,17 +34956,17 @@
       <c r="A1919" t="inlineStr"/>
       <c r="B1919" t="inlineStr">
         <is>
-          <t>codex.panel.no_match</t>
+          <t>fwlib.detail.route_ok</t>
         </is>
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>没有符合搜索的条目。</t>
+          <t>取用路线：{0} → 装配站，通畅</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
         <is>
-          <t>No entries match the search.</t>
+          <t>Fetch route: {0} → Assembly Station, clear</t>
         </is>
       </c>
     </row>
@@ -34974,17 +34974,17 @@
       <c r="A1920" t="inlineStr"/>
       <c r="B1920" t="inlineStr">
         <is>
-          <t>codex.firmware.locked_body</t>
+          <t>fwlib.detail.route_blocked</t>
         </is>
       </c>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>尚未获得。获取途径：{0}</t>
+          <t>取用路线：{0} → 装配站被堵住：{1}</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
         <is>
-          <t>Not obtained yet. How to get it: {0}</t>
+          <t>Fetch route: {0} → Assembly Station is blocked: {1}</t>
         </is>
       </c>
     </row>
@@ -34992,17 +34992,17 @@
       <c r="A1921" t="inlineStr"/>
       <c r="B1921" t="inlineStr">
         <is>
-          <t>codex.reaction.recipe</t>
+          <t>fwlib.detail.route_unknown</t>
         </is>
       </c>
       <c r="C1921" t="inlineStr">
         <is>
-          <t>配料：{0} + {1}</t>
+          <t>取用路线：家园地形还没载入，暂时无法检查</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
         <is>
-          <t>Ingredients: {0} + {1}</t>
+          <t>Fetch route: home terrain not loaded yet; cannot check</t>
         </is>
       </c>
     </row>
@@ -35010,17 +35010,17 @@
       <c r="A1922" t="inlineStr"/>
       <c r="B1922" t="inlineStr">
         <is>
-          <t>codex.reaction.recipe_assembly</t>
+          <t>fwlib.route.storage_enclosed</t>
         </is>
       </c>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>由装配识别：带上 {0}</t>
+          <t>{0} 四周被 {1} 围住</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
         <is>
-          <t>Recognised from the loadout: carry {0}</t>
+          <t>{0} is walled in by {1}</t>
         </is>
       </c>
     </row>
@@ -35028,17 +35028,17 @@
       <c r="A1923" t="inlineStr"/>
       <c r="B1923" t="inlineStr">
         <is>
-          <t>codex.reaction.firmware</t>
+          <t>fwlib.route.station_enclosed</t>
         </is>
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>能提供配料的固件：{0}</t>
+          <t>装配站四周被 {0} 围住</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
         <is>
-          <t>Firmware that supplies an ingredient: {0}</t>
+          <t>the Assembly Station is walled in by {0}</t>
         </is>
       </c>
     </row>
@@ -35046,17 +35046,17 @@
       <c r="A1924" t="inlineStr"/>
       <c r="B1924" t="inlineStr">
         <is>
-          <t>codex.reaction.elsewhere</t>
+          <t>fwlib.route.disconnected</t>
         </is>
       </c>
       <c r="C1924" t="inlineStr">
         <is>
-          <t>本存档还没有打出过（在其他存档里发现）</t>
+          <t>两处之间没有能走通的路（被建筑或地形隔断）</t>
         </is>
       </c>
       <c r="D1924" t="inlineStr">
         <is>
-          <t>Not triggered in this save yet (discovered in another save)</t>
+          <t>there is no walkable path between them (cut off by buildings or terrain)</t>
         </is>
       </c>
     </row>
@@ -35064,15 +35064,303 @@
       <c r="A1925" t="inlineStr"/>
       <c r="B1925" t="inlineStr">
         <is>
+          <t>fwlib.route.no_station</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>家园还没有装配站</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>the home has no Assembly Station yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr"/>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>fwlib.route.terrain</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>地形</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>terrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr"/>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>fwlib.storage.core</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>归还核心应急库</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>Core emergency cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr"/>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>fwlib.footer</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>悬停固件按 {act:OpenCodex} 查看图鉴 · 按 {act:OpenFirmware} 或 {act:Cancel} 关闭</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>Hover a firmware and press {act:OpenCodex} for its codex entry · Press {act:OpenFirmware} or {act:Cancel} to close</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr"/>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>fwlib.readings_title</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>各载体读法</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>Readings by carrier</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr"/>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>pause.firmware</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>固件库</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>Firmware library</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr"/>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>codex.tab.system</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>系统说明</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr"/>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>codex.tab.firmware</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>固件</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr"/>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>codex.tab.reaction</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>反应</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>Reactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr"/>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>codex.panel.search</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>搜索条目</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>Search entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr"/>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>codex.panel.no_match</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>没有符合搜索的条目。</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>No entries match the search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr"/>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>codex.firmware.locked_body</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>尚未获得。获取途径：{0}</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>Not obtained yet. How to get it: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr"/>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>codex.reaction.recipe</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>配料：{0} + {1}</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>Ingredients: {0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr"/>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>codex.reaction.recipe_assembly</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>由装配识别：带上 {0}</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>Recognised from the loadout: carry {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr"/>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>codex.reaction.firmware</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>能提供配料的固件：{0}</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>Firmware that supplies an ingredient: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr"/>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>codex.reaction.elsewhere</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>本存档还没有打出过（在其他存档里发现）</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>Not triggered in this save yet (discovered in another save)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr"/>
+      <c r="B1941" t="inlineStr">
+        <is>
           <t>ui.common.codex_jump</t>
         </is>
       </c>
-      <c r="C1925" t="inlineStr">
+      <c r="C1941" t="inlineStr">
         <is>
           <t>按 {0} 查看图鉴：{1}</t>
         </is>
       </c>
-      <c r="D1925" t="inlineStr">
+      <c r="D1941" t="inlineStr">
         <is>
           <t>Press {0} for the codex: {1}</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1941"/>
+  <dimension ref="A1:D1964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31068,17 +31068,17 @@
       <c r="A1703" t="inlineStr"/>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>codex.panel.title</t>
+          <t>codex.firmware.restore.title</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>数据复原</t>
         </is>
       </c>
       <c r="D1703" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Data restoration</t>
         </is>
       </c>
     </row>
@@ -31086,17 +31086,17 @@
       <c r="A1704" t="inlineStr"/>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>codex.panel.close</t>
+          <t>codex.firmware.restore.body</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>在归还谷地点开已通电的解析台，“数据复原”一栏列出还没获得、能复原的固件（正式来源是遗迹终端、杂兵残骸、精英数据包或阵营首领的那些）。选一条、点“复原”并确认，花掉对应的技术数据（按稀有度），这条固件的刻录数据就复原了：敌方加密的同时视为已破解。复原的是数据，不是芯片——之后在信号核刻印芯片，或在蓝图的固件槽里直接选用。解析台没电、技术数据不够时会拒绝并写明原因，不扣任何东西。这是正式掉落上线前的过渡渠道。</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Open a powered Analysis Bench in Reclamation Valley: the Data restoration section lists firmware you have not obtained that can be restored (those whose regular source is a relic terminal, rank-and-file wrecks, elite data packs or a faction leader). Pick one, press Restore and confirm to spend its tech data (by rarity) and restore its print data; enemy-encrypted firmware also counts as cracked. You restore data, not a chip: print chips at the Signal Core afterwards, or pick it directly in a blueprint firmware slot. An unpowered bench or too little tech data refuses with the reason and costs nothing. This is an interim channel until regular drops arrive.</t>
         </is>
       </c>
     </row>
@@ -31104,17 +31104,17 @@
       <c r="A1705" t="inlineStr"/>
       <c r="B1705" t="inlineStr">
         <is>
-          <t>codex.panel.list_title</t>
+          <t>codex.firmware.restore.hint</t>
         </is>
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>条目 {0}/{1}</t>
+          <t>第一次在解析台复原固件时解锁</t>
         </is>
       </c>
       <c r="D1705" t="inlineStr">
         <is>
-          <t>Entries {0}/{1}</t>
+          <t>Unlocks the first time you restore firmware at the Analysis Bench</t>
         </is>
       </c>
     </row>
@@ -31122,17 +31122,17 @@
       <c r="A1706" t="inlineStr"/>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>codex.panel.related</t>
+          <t>codex.panel.title</t>
         </is>
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>相关条目</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="D1706" t="inlineStr">
         <is>
-          <t>Related</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -31140,17 +31140,17 @@
       <c r="A1707" t="inlineStr"/>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>codex.panel.locked_title</t>
+          <t>codex.panel.close</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>？？？</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1707" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -31158,17 +31158,17 @@
       <c r="A1708" t="inlineStr"/>
       <c r="B1708" t="inlineStr">
         <is>
-          <t>codex.panel.locked_body</t>
+          <t>codex.panel.list_title</t>
         </is>
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>尚未接触。{0}</t>
+          <t>条目 {0}/{1}</t>
         </is>
       </c>
       <c r="D1708" t="inlineStr">
         <is>
-          <t>Not encountered yet. {0}</t>
+          <t>Entries {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31176,17 +31176,17 @@
       <c r="A1709" t="inlineStr"/>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>codex.panel.none_selected</t>
+          <t>codex.panel.related</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>在左侧选一个条目</t>
+          <t>相关条目</t>
         </is>
       </c>
       <c r="D1709" t="inlineStr">
         <is>
-          <t>Pick an entry on the left</t>
+          <t>Related</t>
         </is>
       </c>
     </row>
@@ -31194,17 +31194,17 @@
       <c r="A1710" t="inlineStr"/>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>codex.panel.footer</t>
+          <t>codex.panel.locked_title</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>悬停任何带图鉴链接的提示时按 {act:OpenCodex} 跳到条目；敌人、阵营等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
+          <t>？？？</t>
         </is>
       </c>
       <c r="D1710" t="inlineStr">
         <is>
-          <t>Press {act:OpenCodex} while hovering a tooltip with a codex link to jump to its entry; enemy and faction tabs arrive later; press {act:Cancel} to close</t>
+          <t>???</t>
         </is>
       </c>
     </row>
@@ -31212,17 +31212,17 @@
       <c r="A1711" t="inlineStr"/>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>codex.panel.error</t>
+          <t>codex.panel.locked_body</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
+          <t>尚未接触。{0}</t>
         </is>
       </c>
       <c r="D1711" t="inlineStr">
         <is>
-          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
+          <t>Not encountered yet. {0}</t>
         </is>
       </c>
     </row>
@@ -31230,17 +31230,17 @@
       <c r="A1712" t="inlineStr"/>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>codex.help.tip_title</t>
+          <t>codex.panel.none_selected</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>在左侧选一个条目</t>
         </is>
       </c>
       <c r="D1712" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>Pick an entry on the left</t>
         </is>
       </c>
     </row>
@@ -31248,17 +31248,17 @@
       <c r="A1713" t="inlineStr"/>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>codex.help.tip</t>
+          <t>codex.panel.footer</t>
         </is>
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>打开图鉴条目：{0}</t>
+          <t>悬停任何带图鉴链接的提示时按 {act:OpenCodex} 跳到条目；敌人、阵营等页签将在后续版本加入；按 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1713" t="inlineStr">
         <is>
-          <t>Open the codex entry: {0}</t>
+          <t>Press {act:OpenCodex} while hovering a tooltip with a codex link to jump to its entry; enemy and faction tabs arrive later; press {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -31266,17 +31266,17 @@
       <c r="A1714" t="inlineStr"/>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>uplink.hud.title</t>
+          <t>codex.panel.error</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>图鉴数据不可用（配置表缺失），请重新安装或联系开发者</t>
         </is>
       </c>
       <c r="D1714" t="inlineStr">
         <is>
-          <t>{0} · {1}</t>
+          <t>Codex data is unavailable (missing table); reinstall or contact the developers</t>
         </is>
       </c>
     </row>
@@ -31284,17 +31284,17 @@
       <c r="A1715" t="inlineStr"/>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>uplink.hud.help_button</t>
+          <t>codex.help.tip_title</t>
         </is>
       </c>
       <c r="C1715" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1715" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -31302,17 +31302,17 @@
       <c r="A1716" t="inlineStr"/>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip_title</t>
+          <t>codex.help.tip</t>
         </is>
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>接入 HUD</t>
+          <t>打开图鉴条目：{0}</t>
         </is>
       </c>
       <c r="D1716" t="inlineStr">
         <is>
-          <t>Uplink HUD</t>
+          <t>Open the codex entry: {0}</t>
         </is>
       </c>
     </row>
@@ -31320,17 +31320,17 @@
       <c r="A1717" t="inlineStr"/>
       <c r="B1717" t="inlineStr">
         <is>
-          <t>uplink.hud.help_tip</t>
+          <t>uplink.hud.title</t>
         </is>
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
       <c r="D1717" t="inlineStr">
         <is>
-          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
+          <t>{0} · {1}</t>
         </is>
       </c>
     </row>
@@ -31338,17 +31338,17 @@
       <c r="A1718" t="inlineStr"/>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>uplink.hud.slot</t>
+          <t>uplink.hud.help_button</t>
         </is>
       </c>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D1718" t="inlineStr">
         <is>
-          <t>{0} {1}</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -31356,17 +31356,17 @@
       <c r="A1719" t="inlineStr"/>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>uplink.hud.state.active</t>
+          <t>uplink.hud.help_tip_title</t>
         </is>
       </c>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>生效</t>
+          <t>接入 HUD</t>
         </is>
       </c>
       <c r="D1719" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Uplink HUD</t>
         </is>
       </c>
     </row>
@@ -31374,17 +31374,17 @@
       <c r="A1720" t="inlineStr"/>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>uplink.hud.state.cooling</t>
+          <t>uplink.hud.help_tip</t>
         </is>
       </c>
       <c r="C1720" t="inlineStr">
         <is>
-          <t>冷却 {0} 秒</t>
+          <t>你正在这台机器里。第一行是信号核各槽的固件：生效、冷却中、裸跑、未插入（写明原因）；下面是这台机体的热量、电池、耐久与伤势，链路强度（离覆盖边缘越近越弱）与信号暴露。点“?”打开图鉴。</t>
         </is>
       </c>
       <c r="D1720" t="inlineStr">
         <is>
-          <t>cooling {0}s</t>
+          <t>You are in this machine. The first row lists each Signal Core slot: active, cooling, running raw, or not inserted (with the reason). Below are this machine's heat, battery, durability and injuries, the link strength (weaker near the coverage edge) and signal exposure. Click "?" to open the codex.</t>
         </is>
       </c>
     </row>
@@ -31392,17 +31392,17 @@
       <c r="A1721" t="inlineStr"/>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>uplink.hud.state.raw</t>
+          <t>uplink.hud.slot</t>
         </is>
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>裸跑</t>
+          <t>{0} {1}</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>{0} {1}</t>
         </is>
       </c>
     </row>
@@ -31410,17 +31410,17 @@
       <c r="A1722" t="inlineStr"/>
       <c r="B1722" t="inlineStr">
         <is>
-          <t>uplink.hud.state.not_inserted</t>
+          <t>uplink.hud.state.active</t>
         </is>
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>未插入：{0}</t>
+          <t>生效</t>
         </is>
       </c>
       <c r="D1722" t="inlineStr">
         <is>
-          <t>not inserted: {0}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -31428,17 +31428,17 @@
       <c r="A1723" t="inlineStr"/>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>uplink.hud.state.ineffective</t>
+          <t>uplink.hud.state.cooling</t>
         </is>
       </c>
       <c r="C1723" t="inlineStr">
         <is>
-          <t>不生效：{0}</t>
+          <t>冷却 {0} 秒</t>
         </is>
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>no effect: {0}</t>
+          <t>cooling {0}s</t>
         </is>
       </c>
     </row>
@@ -31446,17 +31446,17 @@
       <c r="A1724" t="inlineStr"/>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>uplink.hud.state.empty</t>
+          <t>uplink.hud.state.raw</t>
         </is>
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>空槽</t>
+          <t>裸跑</t>
         </is>
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>raw</t>
         </is>
       </c>
     </row>
@@ -31464,17 +31464,17 @@
       <c r="A1725" t="inlineStr"/>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>uplink.hud.state.locked</t>
+          <t>uplink.hud.state.not_inserted</t>
         </is>
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>未解锁</t>
+          <t>未插入：{0}</t>
         </is>
       </c>
       <c r="D1725" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>not inserted: {0}</t>
         </is>
       </c>
     </row>
@@ -31482,17 +31482,17 @@
       <c r="A1726" t="inlineStr"/>
       <c r="B1726" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.over_quota</t>
+          <t>uplink.hud.state.ineffective</t>
         </is>
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>超出接入口配额 {0} 个</t>
+          <t>不生效：{0}</t>
         </is>
       </c>
       <c r="D1726" t="inlineStr">
         <is>
-          <t>over the port quota of {0}</t>
+          <t>no effect: {0}</t>
         </is>
       </c>
     </row>
@@ -31500,17 +31500,17 @@
       <c r="A1727" t="inlineStr"/>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.path_limit</t>
+          <t>uplink.hud.state.empty</t>
         </is>
       </c>
       <c r="C1727" t="inlineStr">
         <is>
-          <t>路径会超过上限 {0} 条</t>
+          <t>空槽</t>
         </is>
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>paths would exceed {0}</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -31518,17 +31518,17 @@
       <c r="A1728" t="inlineStr"/>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.unknown</t>
+          <t>uplink.hud.state.locked</t>
         </is>
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>不是已知的固件</t>
+          <t>未解锁</t>
         </is>
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>unknown firmware</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -31536,17 +31536,17 @@
       <c r="A1729" t="inlineStr"/>
       <c r="B1729" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.no_uplink</t>
+          <t>uplink.hud.reason.over_quota</t>
         </is>
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>这台机器没有接入口</t>
+          <t>超出接入口配额 {0} 个</t>
         </is>
       </c>
       <c r="D1729" t="inlineStr">
         <is>
-          <t>this machine has no uplink port</t>
+          <t>over the port quota of {0}</t>
         </is>
       </c>
     </row>
@@ -31554,17 +31554,17 @@
       <c r="A1730" t="inlineStr"/>
       <c r="B1730" t="inlineStr">
         <is>
-          <t>uplink.hud.reason.off_path</t>
+          <t>uplink.hud.reason.path_limit</t>
         </is>
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>接入口不在导线上</t>
+          <t>路径会超过上限 {0} 条</t>
         </is>
       </c>
       <c r="D1730" t="inlineStr">
         <is>
-          <t>the uplink port is not on a wire</t>
+          <t>paths would exceed {0}</t>
         </is>
       </c>
     </row>
@@ -31572,17 +31572,17 @@
       <c r="A1731" t="inlineStr"/>
       <c r="B1731" t="inlineStr">
         <is>
-          <t>uplink.hud.slot_tip</t>
+          <t>uplink.hud.reason.unknown</t>
         </is>
       </c>
       <c r="C1731" t="inlineStr">
         <is>
-          <t>{0} 号槽：{1}</t>
+          <t>不是已知的固件</t>
         </is>
       </c>
       <c r="D1731" t="inlineStr">
         <is>
-          <t>Slot {0}: {1}</t>
+          <t>unknown firmware</t>
         </is>
       </c>
     </row>
@@ -31590,17 +31590,17 @@
       <c r="A1732" t="inlineStr"/>
       <c r="B1732" t="inlineStr">
         <is>
-          <t>uplink.hud.heat</t>
+          <t>uplink.hud.reason.no_uplink</t>
         </is>
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>热量 {0}/{1}</t>
+          <t>这台机器没有接入口</t>
         </is>
       </c>
       <c r="D1732" t="inlineStr">
         <is>
-          <t>Heat {0}/{1}</t>
+          <t>this machine has no uplink port</t>
         </is>
       </c>
     </row>
@@ -31608,17 +31608,17 @@
       <c r="A1733" t="inlineStr"/>
       <c r="B1733" t="inlineStr">
         <is>
-          <t>uplink.hud.overheated</t>
+          <t>uplink.hud.reason.off_path</t>
         </is>
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>过热：散热到 {0} 以下才开火</t>
+          <t>接入口不在导线上</t>
         </is>
       </c>
       <c r="D1733" t="inlineStr">
         <is>
-          <t>Overheated: fires again below {0}</t>
+          <t>the uplink port is not on a wire</t>
         </is>
       </c>
     </row>
@@ -31626,17 +31626,17 @@
       <c r="A1734" t="inlineStr"/>
       <c r="B1734" t="inlineStr">
         <is>
-          <t>uplink.hud.heat_tip</t>
+          <t>uplink.hud.slot_tip</t>
         </is>
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
+          <t>{0} 号槽：{1}</t>
         </is>
       </c>
       <c r="D1734" t="inlineStr">
         <is>
-          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
+          <t>Slot {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -31644,17 +31644,17 @@
       <c r="A1735" t="inlineStr"/>
       <c r="B1735" t="inlineStr">
         <is>
-          <t>uplink.hud.battery</t>
+          <t>uplink.hud.heat</t>
         </is>
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>电池 {0}%</t>
+          <t>热量 {0}/{1}</t>
         </is>
       </c>
       <c r="D1735" t="inlineStr">
         <is>
-          <t>Battery {0}%</t>
+          <t>Heat {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31662,17 +31662,17 @@
       <c r="A1736" t="inlineStr"/>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>uplink.hud.battery_tip</t>
+          <t>uplink.hud.overheated</t>
         </is>
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
+          <t>过热：散热到 {0} 以下才开火</t>
         </is>
       </c>
       <c r="D1736" t="inlineStr">
         <is>
-          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
+          <t>Overheated: fires again below {0}</t>
         </is>
       </c>
     </row>
@@ -31680,17 +31680,17 @@
       <c r="A1737" t="inlineStr"/>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>uplink.hud.health</t>
+          <t>uplink.hud.heat_tip</t>
         </is>
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}</t>
+          <t>热量留在机体上（换机器、离开都不会清掉）。到 {0} 过热停火，散热到 {1} 以下才恢复开火。</t>
         </is>
       </c>
       <c r="D1737" t="inlineStr">
         <is>
-          <t>Durability {0}/{1}</t>
+          <t>Heat stays on the machine (switching or leaving does not clear it). At {0} it overheats and stops firing until it cools below {1}.</t>
         </is>
       </c>
     </row>
@@ -31698,17 +31698,17 @@
       <c r="A1738" t="inlineStr"/>
       <c r="B1738" t="inlineStr">
         <is>
-          <t>uplink.hud.injury_none</t>
+          <t>uplink.hud.battery</t>
         </is>
       </c>
       <c r="C1738" t="inlineStr">
         <is>
-          <t>伤势：无</t>
+          <t>电池 {0}%</t>
         </is>
       </c>
       <c r="D1738" t="inlineStr">
         <is>
-          <t>Injuries: none</t>
+          <t>Battery {0}%</t>
         </is>
       </c>
     </row>
@@ -31716,17 +31716,17 @@
       <c r="A1739" t="inlineStr"/>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>uplink.hud.injury</t>
+          <t>uplink.hud.battery_tip</t>
         </is>
       </c>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>伤势：{0}</t>
+          <t>电池 {0}/{1}：回家园充电桩或工单“充电”补充。</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
         <is>
-          <t>Injuries: {0}</t>
+          <t>Battery {0}/{1}: recharge at home or with a Recharge job.</t>
         </is>
       </c>
     </row>
@@ -31734,17 +31734,17 @@
       <c r="A1740" t="inlineStr"/>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>uplink.hud.health_tip</t>
+          <t>uplink.hud.health</t>
         </is>
       </c>
       <c r="C1740" t="inlineStr">
         <is>
-          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
+          <t>耐久 {0}/{1}</t>
         </is>
       </c>
       <c r="D1740" t="inlineStr">
         <is>
-          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
+          <t>Durability {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31752,17 +31752,17 @@
       <c r="A1741" t="inlineStr"/>
       <c r="B1741" t="inlineStr">
         <is>
-          <t>uplink.hud.link</t>
+          <t>uplink.hud.injury_none</t>
         </is>
       </c>
       <c r="C1741" t="inlineStr">
         <is>
-          <t>链路 {0}% · {1}</t>
+          <t>伤势：无</t>
         </is>
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>Link {0}% · {1}</t>
+          <t>Injuries: none</t>
         </is>
       </c>
     </row>
@@ -31770,17 +31770,17 @@
       <c r="A1742" t="inlineStr"/>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>uplink.hud.link.strong</t>
+          <t>uplink.hud.injury</t>
         </is>
       </c>
       <c r="C1742" t="inlineStr">
         <is>
-          <t>强</t>
+          <t>伤势：{0}</t>
         </is>
       </c>
       <c r="D1742" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>Injuries: {0}</t>
         </is>
       </c>
     </row>
@@ -31788,17 +31788,17 @@
       <c r="A1743" t="inlineStr"/>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>uplink.hud.link.medium</t>
+          <t>uplink.hud.health_tip</t>
         </is>
       </c>
       <c r="C1743" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>耐久归零机器阵亡，信号弹到最近能接入的机器或回到归还核心。维修台与维修束可以修复。</t>
         </is>
       </c>
       <c r="D1743" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>At zero durability the machine is destroyed and the signal jumps to the nearest reachable machine or back to the core. Repair bays and repair beams restore it.</t>
         </is>
       </c>
     </row>
@@ -31806,17 +31806,17 @@
       <c r="A1744" t="inlineStr"/>
       <c r="B1744" t="inlineStr">
         <is>
-          <t>uplink.hud.link.weak</t>
+          <t>uplink.hud.link</t>
         </is>
       </c>
       <c r="C1744" t="inlineStr">
         <is>
-          <t>弱</t>
+          <t>链路 {0}% · {1}</t>
         </is>
       </c>
       <c r="D1744" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>Link {0}% · {1}</t>
         </is>
       </c>
     </row>
@@ -31824,17 +31824,17 @@
       <c r="A1745" t="inlineStr"/>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>uplink.hud.link.edge</t>
+          <t>uplink.hud.link.strong</t>
         </is>
       </c>
       <c r="C1745" t="inlineStr">
         <is>
-          <t>边缘 · 还剩 {0} 格</t>
+          <t>强</t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
         <is>
-          <t>edge · {0} cells left</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -31842,17 +31842,17 @@
       <c r="A1746" t="inlineStr"/>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>uplink.hud.link.unbounded</t>
+          <t>uplink.hud.link.medium</t>
         </is>
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>链路 满 · 此地不受覆盖限制</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D1746" t="inlineStr">
         <is>
-          <t>Link full · no coverage limit here</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -31860,17 +31860,17 @@
       <c r="A1747" t="inlineStr"/>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>uplink.hud.link.grace</t>
+          <t>uplink.hud.link.weak</t>
         </is>
       </c>
       <c r="C1747" t="inlineStr">
         <is>
-          <t>链路中断（{0}）：{1} 秒内恢复</t>
+          <t>弱</t>
         </is>
       </c>
       <c r="D1747" t="inlineStr">
         <is>
-          <t>Link lost ({0}): recover within {1}s</t>
+          <t>weak</t>
         </is>
       </c>
     </row>
@@ -31878,17 +31878,17 @@
       <c r="A1748" t="inlineStr"/>
       <c r="B1748" t="inlineStr">
         <is>
-          <t>uplink.hud.link_tip</t>
+          <t>uplink.hud.link.edge</t>
         </is>
       </c>
       <c r="C1748" t="inlineStr">
         <is>
-          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
+          <t>边缘 · 还剩 {0} 格</t>
         </is>
       </c>
       <c r="D1748" t="inlineStr">
         <is>
-          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
+          <t>edge · {0} cells left</t>
         </is>
       </c>
     </row>
@@ -31896,17 +31896,17 @@
       <c r="A1749" t="inlineStr"/>
       <c r="B1749" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure</t>
+          <t>uplink.hud.link.unbounded</t>
         </is>
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>暴露 {0}</t>
+          <t>链路 满 · 此地不受覆盖限制</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
         <is>
-          <t>Exposure {0}</t>
+          <t>Link full · no coverage limit here</t>
         </is>
       </c>
     </row>
@@ -31914,17 +31914,17 @@
       <c r="A1750" t="inlineStr"/>
       <c r="B1750" t="inlineStr">
         <is>
-          <t>uplink.hud.exposure_tip</t>
+          <t>uplink.hud.link.grace</t>
         </is>
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
+          <t>链路中断（{0}）：{1} 秒内恢复</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
+          <t>Link lost ({0}): recover within {1}s</t>
         </is>
       </c>
     </row>
@@ -31932,17 +31932,17 @@
       <c r="A1751" t="inlineStr"/>
       <c r="B1751" t="inlineStr">
         <is>
-          <t>uplink.hud.morph</t>
+          <t>uplink.hud.link_tip</t>
         </is>
       </c>
       <c r="C1751" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>离信号覆盖边缘越近链路越弱：离边缘 {0} 格以上为满格，不到 {1} 格时预警，走出去 {2} 秒后断链，信号弹回归还核心。</t>
         </is>
       </c>
       <c r="D1751" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>The link weakens near the coverage edge: full at {0}+ cells from the edge, a warning under {1} cells, and {2}s after leaving the link breaks and the signal returns to the core.</t>
         </is>
       </c>
     </row>
@@ -31950,17 +31950,17 @@
       <c r="A1752" t="inlineStr"/>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>uplink.hud.morph_source</t>
+          <t>uplink.hud.exposure</t>
         </is>
       </c>
       <c r="C1752" t="inlineStr">
         <is>
-          <t>{0}（{1}）</t>
+          <t>暴露 {0}</t>
         </is>
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>{0} ({1})</t>
+          <t>Exposure {0}</t>
         </is>
       </c>
     </row>
@@ -31968,17 +31968,17 @@
       <c r="A1753" t="inlineStr"/>
       <c r="B1753" t="inlineStr">
         <is>
-          <t>uplink.hud.no_port</t>
+          <t>uplink.hud.exposure_tip</t>
         </is>
       </c>
       <c r="C1753" t="inlineStr">
         <is>
-          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
+          <t>信号暴露 {0}/{1}：接入本身不计。点 HUD 顶部的“暴露”按钮看最近的来源。</t>
         </is>
       </c>
       <c r="D1753" t="inlineStr">
         <is>
-          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
+          <t>Signal exposure {0}/{1}: uplinking itself does not count. Click the Exposure button at the top for recent sources.</t>
         </is>
       </c>
     </row>
@@ -31986,17 +31986,17 @@
       <c r="A1754" t="inlineStr"/>
       <c r="B1754" t="inlineStr">
         <is>
-          <t>uplink.hud.core_empty</t>
+          <t>uplink.hud.morph</t>
         </is>
       </c>
       <c r="C1754" t="inlineStr">
         <is>
-          <t>信号核没有固件（按 {0} 打开信号核）</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1754" t="inlineStr">
         <is>
-          <t>The Signal Core is empty (press {0} to open it)</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -32004,17 +32004,17 @@
       <c r="A1755" t="inlineStr"/>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>uplink.hud.experience</t>
+          <t>uplink.hud.morph_source</t>
         </is>
       </c>
       <c r="C1755" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>{0}（{1}）</t>
         </is>
       </c>
       <c r="D1755" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -32022,17 +32022,17 @@
       <c r="A1756" t="inlineStr"/>
       <c r="B1756" t="inlineStr">
         <is>
-          <t>uplink.hud.keys</t>
+          <t>uplink.hud.no_port</t>
         </is>
       </c>
       <c r="C1756" t="inlineStr">
         <is>
-          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
+          <t>没有接入口：可以驾驶、瞄准和攻击，不插入固件</t>
         </is>
       </c>
       <c r="D1756" t="inlineStr">
         <is>
-          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
+          <t>No uplink port: you can drive, aim and attack, but no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -32040,17 +32040,17 @@
       <c r="A1757" t="inlineStr"/>
       <c r="B1757" t="inlineStr">
         <is>
-          <t>morph.state.none</t>
+          <t>uplink.hud.core_empty</t>
         </is>
       </c>
       <c r="C1757" t="inlineStr">
         <is>
-          <t>常态</t>
+          <t>信号核没有固件（按 {0} 打开信号核）</t>
         </is>
       </c>
       <c r="D1757" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>The Signal Core is empty (press {0} to open it)</t>
         </is>
       </c>
     </row>
@@ -32058,17 +32058,17 @@
       <c r="A1758" t="inlineStr"/>
       <c r="B1758" t="inlineStr">
         <is>
-          <t>morph.state.limiter</t>
+          <t>uplink.hud.experience</t>
         </is>
       </c>
       <c r="C1758" t="inlineStr">
         <is>
-          <t>形变态</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1758" t="inlineStr">
         <is>
-          <t>morph state</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -32076,17 +32076,17 @@
       <c r="A1759" t="inlineStr"/>
       <c r="B1759" t="inlineStr">
         <is>
-          <t>morph.state.fluid</t>
+          <t>uplink.hud.keys</t>
         </is>
       </c>
       <c r="C1759" t="inlineStr">
         <is>
-          <t>喷口态</t>
+          <t>{0} 离开 · {1} 切换机器 · {2} 跳回家园 · {3} 信号核</t>
         </is>
       </c>
       <c r="D1759" t="inlineStr">
         <is>
-          <t>vent state</t>
+          <t>{0} leave · {1} switch · {2} jump home · {3} Signal Core</t>
         </is>
       </c>
     </row>
@@ -32094,17 +32094,17 @@
       <c r="A1760" t="inlineStr"/>
       <c r="B1760" t="inlineStr">
         <is>
-          <t>morph.state.em</t>
+          <t>morph.state.none</t>
         </is>
       </c>
       <c r="C1760" t="inlineStr">
         <is>
-          <t>线圈态</t>
+          <t>常态</t>
         </is>
       </c>
       <c r="D1760" t="inlineStr">
         <is>
-          <t>coil state</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -32112,17 +32112,17 @@
       <c r="A1761" t="inlineStr"/>
       <c r="B1761" t="inlineStr">
         <is>
-          <t>morph.state.join</t>
+          <t>morph.state.limiter</t>
         </is>
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>形变态</t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">
         <is>
-          <t xml:space="preserve"> + </t>
+          <t>morph state</t>
         </is>
       </c>
     </row>
@@ -32130,17 +32130,17 @@
       <c r="A1762" t="inlineStr"/>
       <c r="B1762" t="inlineStr">
         <is>
-          <t>signal.list.port_tag</t>
+          <t>morph.state.fluid</t>
         </is>
       </c>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>◇口</t>
+          <t>喷口态</t>
         </is>
       </c>
       <c r="D1762" t="inlineStr">
         <is>
-          <t>◇PORT</t>
+          <t>vent state</t>
         </is>
       </c>
     </row>
@@ -32148,17 +32148,17 @@
       <c r="A1763" t="inlineStr"/>
       <c r="B1763" t="inlineStr">
         <is>
-          <t>signal.list.overheat_tag</t>
+          <t>morph.state.em</t>
         </is>
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>过热</t>
+          <t>线圈态</t>
         </is>
       </c>
       <c r="D1763" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>coil state</t>
         </is>
       </c>
     </row>
@@ -32166,17 +32166,17 @@
       <c r="A1764" t="inlineStr"/>
       <c r="B1764" t="inlineStr">
         <is>
-          <t>signal.list.port_line</t>
+          <t>morph.state.join</t>
         </is>
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
       <c r="D1764" t="inlineStr">
         <is>
-          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
+          <t xml:space="preserve"> + </t>
         </is>
       </c>
     </row>
@@ -32184,17 +32184,17 @@
       <c r="A1765" t="inlineStr"/>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>signal.list.no_port_line</t>
+          <t>signal.list.port_tag</t>
         </is>
       </c>
       <c r="C1765" t="inlineStr">
         <is>
-          <t>没有接入口：接入后只能驾驶，不插入固件</t>
+          <t>◇口</t>
         </is>
       </c>
       <c r="D1765" t="inlineStr">
         <is>
-          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
+          <t>◇PORT</t>
         </is>
       </c>
     </row>
@@ -32202,17 +32202,17 @@
       <c r="A1766" t="inlineStr"/>
       <c r="B1766" t="inlineStr">
         <is>
-          <t>signal.list.overheat_line</t>
+          <t>signal.list.overheat_tag</t>
         </is>
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
+          <t>过热</t>
         </is>
       </c>
       <c r="D1766" t="inlineStr">
         <is>
-          <t>Overheated (heat {0}): it fires again once below {1}</t>
+          <t>HOT</t>
         </is>
       </c>
     </row>
@@ -32220,17 +32220,17 @@
       <c r="A1767" t="inlineStr"/>
       <c r="B1767" t="inlineStr">
         <is>
-          <t>signal.list.morph_line</t>
+          <t>signal.list.port_line</t>
         </is>
       </c>
       <c r="C1767" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>◇ 带接入口：接入时信号核的固件会插进去</t>
         </is>
       </c>
       <c r="D1767" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>◇ Has an uplink port: Signal Core firmware is inserted when you uplink</t>
         </is>
       </c>
     </row>
@@ -32238,17 +32238,17 @@
       <c r="A1768" t="inlineStr"/>
       <c r="B1768" t="inlineStr">
         <is>
-          <t>signal.list.experience_line</t>
+          <t>signal.list.no_port_line</t>
         </is>
       </c>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次 · 累计 {1}</t>
+          <t>没有接入口：接入后只能驾驶，不插入固件</t>
         </is>
       </c>
       <c r="D1768" t="inlineStr">
         <is>
-          <t>With the signal {0} times · {1} total</t>
+          <t>No uplink port: uplinking only lets you drive it, no firmware is inserted</t>
         </is>
       </c>
     </row>
@@ -32256,17 +32256,17 @@
       <c r="A1769" t="inlineStr"/>
       <c r="B1769" t="inlineStr">
         <is>
-          <t>signal.port_badge.tip</t>
+          <t>signal.list.overheat_line</t>
         </is>
       </c>
       <c r="C1769" t="inlineStr">
         <is>
-          <t>带接入口的机器</t>
+          <t>过热中（热量 {0}）：散热到 {1} 以下才会再开火</t>
         </is>
       </c>
       <c r="D1769" t="inlineStr">
         <is>
-          <t>Machine with an uplink port</t>
+          <t>Overheated (heat {0}): it fires again once below {1}</t>
         </is>
       </c>
     </row>
@@ -32274,17 +32274,17 @@
       <c r="A1770" t="inlineStr"/>
       <c r="B1770" t="inlineStr">
         <is>
-          <t>machine.exp.produced</t>
+          <t>signal.list.morph_line</t>
         </is>
       </c>
       <c r="C1770" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1770" t="inlineStr">
         <is>
-          <t>Produced</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -32292,17 +32292,17 @@
       <c r="A1771" t="inlineStr"/>
       <c r="B1771" t="inlineStr">
         <is>
-          <t>machine.exp.first_job</t>
+          <t>signal.list.experience_line</t>
         </is>
       </c>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>首次工作</t>
+          <t>与信号同行 {0} 次 · 累计 {1}</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
         <is>
-          <t>First job</t>
+          <t>With the signal {0} times · {1} total</t>
         </is>
       </c>
     </row>
@@ -32310,17 +32310,17 @@
       <c r="A1772" t="inlineStr"/>
       <c r="B1772" t="inlineStr">
         <is>
-          <t>machine.exp.controlled</t>
+          <t>signal.port_badge.tip</t>
         </is>
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>首次与信号同行</t>
+          <t>带接入口的机器</t>
         </is>
       </c>
       <c r="D1772" t="inlineStr">
         <is>
-          <t>First time with the signal</t>
+          <t>Machine with an uplink port</t>
         </is>
       </c>
     </row>
@@ -32328,17 +32328,17 @@
       <c r="A1773" t="inlineStr"/>
       <c r="B1773" t="inlineStr">
         <is>
-          <t>machine.exp.expedition</t>
+          <t>machine.exp.produced</t>
         </is>
       </c>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>远征</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
         <is>
-          <t>Expedition</t>
+          <t>Produced</t>
         </is>
       </c>
     </row>
@@ -32346,17 +32346,17 @@
       <c r="A1774" t="inlineStr"/>
       <c r="B1774" t="inlineStr">
         <is>
-          <t>machine.exp.severely_injured</t>
+          <t>machine.exp.first_job</t>
         </is>
       </c>
       <c r="C1774" t="inlineStr">
         <is>
-          <t>重伤</t>
+          <t>首次工作</t>
         </is>
       </c>
       <c r="D1774" t="inlineStr">
         <is>
-          <t>Severely injured</t>
+          <t>First job</t>
         </is>
       </c>
     </row>
@@ -32364,17 +32364,17 @@
       <c r="A1775" t="inlineStr"/>
       <c r="B1775" t="inlineStr">
         <is>
-          <t>machine.exp.elite_kill</t>
+          <t>machine.exp.controlled</t>
         </is>
       </c>
       <c r="C1775" t="inlineStr">
         <is>
-          <t>精英击破</t>
+          <t>首次与信号同行</t>
         </is>
       </c>
       <c r="D1775" t="inlineStr">
         <is>
-          <t>Elite kill</t>
+          <t>First time with the signal</t>
         </is>
       </c>
     </row>
@@ -32382,17 +32382,17 @@
       <c r="A1776" t="inlineStr"/>
       <c r="B1776" t="inlineStr">
         <is>
-          <t>machine.exp.boss_participation</t>
+          <t>machine.exp.expedition</t>
         </is>
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>首领战</t>
+          <t>远征</t>
         </is>
       </c>
       <c r="D1776" t="inlineStr">
         <is>
-          <t>Boss fight</t>
+          <t>Expedition</t>
         </is>
       </c>
     </row>
@@ -32400,17 +32400,17 @@
       <c r="A1777" t="inlineStr"/>
       <c r="B1777" t="inlineStr">
         <is>
-          <t>machine.exp.returned</t>
+          <t>machine.exp.severely_injured</t>
         </is>
       </c>
       <c r="C1777" t="inlineStr">
         <is>
-          <t>返航</t>
+          <t>重伤</t>
         </is>
       </c>
       <c r="D1777" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Severely injured</t>
         </is>
       </c>
     </row>
@@ -32418,17 +32418,17 @@
       <c r="A1778" t="inlineStr"/>
       <c r="B1778" t="inlineStr">
         <is>
-          <t>machine.exp.sep</t>
+          <t>machine.exp.elite_kill</t>
         </is>
       </c>
       <c r="C1778" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>精英击破</t>
         </is>
       </c>
       <c r="D1778" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>Elite kill</t>
         </is>
       </c>
     </row>
@@ -32436,17 +32436,17 @@
       <c r="A1779" t="inlineStr"/>
       <c r="B1779" t="inlineStr">
         <is>
-          <t>machine.injury.combat</t>
+          <t>machine.exp.boss_participation</t>
         </is>
       </c>
       <c r="C1779" t="inlineStr">
         <is>
-          <t>战斗损伤（HP {0}/{1}）</t>
+          <t>首领战</t>
         </is>
       </c>
       <c r="D1779" t="inlineStr">
         <is>
-          <t>Combat damage (HP {0}/{1})</t>
+          <t>Boss fight</t>
         </is>
       </c>
     </row>
@@ -32454,17 +32454,17 @@
       <c r="A1780" t="inlineStr"/>
       <c r="B1780" t="inlineStr">
         <is>
-          <t>machine.exp.none</t>
+          <t>machine.exp.returned</t>
         </is>
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>无记录经历</t>
+          <t>返航</t>
         </is>
       </c>
       <c r="D1780" t="inlineStr">
         <is>
-          <t>No recorded experience</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
@@ -32472,17 +32472,17 @@
       <c r="A1781" t="inlineStr"/>
       <c r="B1781" t="inlineStr">
         <is>
-          <t>machine.exp.signal</t>
+          <t>machine.exp.sep</t>
         </is>
       </c>
       <c r="C1781" t="inlineStr">
         <is>
-          <t>与信号同行 {0} 次，累计 {1}</t>
+          <t>、</t>
         </is>
       </c>
       <c r="D1781" t="inlineStr">
         <is>
-          <t>With the signal {0} times, {1} in total</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
     </row>
@@ -32490,17 +32490,17 @@
       <c r="A1782" t="inlineStr"/>
       <c r="B1782" t="inlineStr">
         <is>
-          <t>machine.exp.signal_none</t>
+          <t>machine.injury.combat</t>
         </is>
       </c>
       <c r="C1782" t="inlineStr">
         <is>
-          <t>尚未与信号同行</t>
+          <t>战斗损伤（HP {0}/{1}）</t>
         </is>
       </c>
       <c r="D1782" t="inlineStr">
         <is>
-          <t>Never carried the signal</t>
+          <t>Combat damage (HP {0}/{1})</t>
         </is>
       </c>
     </row>
@@ -32508,17 +32508,17 @@
       <c r="A1783" t="inlineStr"/>
       <c r="B1783" t="inlineStr">
         <is>
-          <t>machine.status.dead</t>
+          <t>machine.exp.none</t>
         </is>
       </c>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录）</t>
+          <t>无记录经历</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record)</t>
+          <t>No recorded experience</t>
         </is>
       </c>
     </row>
@@ -32526,17 +32526,17 @@
       <c r="A1784" t="inlineStr"/>
       <c r="B1784" t="inlineStr">
         <is>
-          <t>machine.status.in_factory</t>
+          <t>machine.exp.signal</t>
         </is>
       </c>
       <c r="C1784" t="inlineStr">
         <is>
-          <t>厂内待驶出</t>
+          <t>与信号同行 {0} 次，累计 {1}</t>
         </is>
       </c>
       <c r="D1784" t="inlineStr">
         <is>
-          <t>Waiting in the factory</t>
+          <t>With the signal {0} times, {1} in total</t>
         </is>
       </c>
     </row>
@@ -32544,17 +32544,17 @@
       <c r="A1785" t="inlineStr"/>
       <c r="B1785" t="inlineStr">
         <is>
-          <t>machine.status.uplinked</t>
+          <t>machine.exp.signal_none</t>
         </is>
       </c>
       <c r="C1785" t="inlineStr">
         <is>
-          <t>接入中</t>
+          <t>尚未与信号同行</t>
         </is>
       </c>
       <c r="D1785" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>Never carried the signal</t>
         </is>
       </c>
     </row>
@@ -32562,17 +32562,17 @@
       <c r="A1786" t="inlineStr"/>
       <c r="B1786" t="inlineStr">
         <is>
-          <t>machine.status.idle</t>
+          <t>machine.status.dead</t>
         </is>
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>空闲</t>
+          <t>阵亡（纪念记录）</t>
         </is>
       </c>
       <c r="D1786" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>Destroyed (memorial record)</t>
         </is>
       </c>
     </row>
@@ -32580,17 +32580,17 @@
       <c r="A1787" t="inlineStr"/>
       <c r="B1787" t="inlineStr">
         <is>
-          <t>machine.status.working</t>
+          <t>machine.status.in_factory</t>
         </is>
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>工作中</t>
+          <t>厂内待驶出</t>
         </is>
       </c>
       <c r="D1787" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Waiting in the factory</t>
         </is>
       </c>
     </row>
@@ -32598,17 +32598,17 @@
       <c r="A1788" t="inlineStr"/>
       <c r="B1788" t="inlineStr">
         <is>
-          <t>machine.detail.none</t>
+          <t>machine.status.uplinked</t>
         </is>
       </c>
       <c r="C1788" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>接入中</t>
         </is>
       </c>
       <c r="D1788" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Uplinked</t>
         </is>
       </c>
     </row>
@@ -32616,17 +32616,17 @@
       <c r="A1789" t="inlineStr"/>
       <c r="B1789" t="inlineStr">
         <is>
-          <t>machine.detail.injury_none</t>
+          <t>machine.status.idle</t>
         </is>
       </c>
       <c r="C1789" t="inlineStr">
         <is>
-          <t>无记录</t>
+          <t>空闲</t>
         </is>
       </c>
       <c r="D1789" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Idle</t>
         </is>
       </c>
     </row>
@@ -32634,17 +32634,17 @@
       <c r="A1790" t="inlineStr"/>
       <c r="B1790" t="inlineStr">
         <is>
-          <t>machine.detail.port_yes</t>
+          <t>machine.status.working</t>
         </is>
       </c>
       <c r="C1790" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>工作中</t>
         </is>
       </c>
       <c r="D1790" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -32652,17 +32652,17 @@
       <c r="A1791" t="inlineStr"/>
       <c r="B1791" t="inlineStr">
         <is>
-          <t>machine.detail.port_no</t>
+          <t>machine.detail.none</t>
         </is>
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>没有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D1791" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -32670,17 +32670,17 @@
       <c r="A1792" t="inlineStr"/>
       <c r="B1792" t="inlineStr">
         <is>
-          <t>machine.detail.line_id</t>
+          <t>machine.detail.injury_none</t>
         </is>
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
+          <t>无记录</t>
         </is>
       </c>
       <c r="D1792" t="inlineStr">
         <is>
-          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
+          <t>none recorded</t>
         </is>
       </c>
     </row>
@@ -32688,17 +32688,17 @@
       <c r="A1793" t="inlineStr"/>
       <c r="B1793" t="inlineStr">
         <is>
-          <t>machine.detail.line_vitals</t>
+          <t>machine.detail.port_yes</t>
         </is>
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
+          <t>有</t>
         </is>
       </c>
       <c r="D1793" t="inlineStr">
         <is>
-          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -32706,17 +32706,17 @@
       <c r="A1794" t="inlineStr"/>
       <c r="B1794" t="inlineStr">
         <is>
-          <t>machine.detail.line_exp</t>
+          <t>machine.detail.port_no</t>
         </is>
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>经历：{0}</t>
+          <t>没有</t>
         </is>
       </c>
       <c r="D1794" t="inlineStr">
         <is>
-          <t>Experience: {0}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -32724,17 +32724,17 @@
       <c r="A1795" t="inlineStr"/>
       <c r="B1795" t="inlineStr">
         <is>
-          <t>machine.detail.line_signal</t>
+          <t>machine.detail.line_id</t>
         </is>
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>编号 #{0}（LogicId {1}）｜底盘 {2}｜装配 v{3}｜接入口 {4}｜状态 {5}</t>
         </is>
       </c>
       <c r="D1795" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>#{0} (LogicId {1}) | Chassis {2} | Loadout v{3} | Uplink port {4} | {5}</t>
         </is>
       </c>
     </row>
@@ -32742,17 +32742,17 @@
       <c r="A1796" t="inlineStr"/>
       <c r="B1796" t="inlineStr">
         <is>
-          <t>machine.detail.line_stats</t>
+          <t>machine.detail.line_vitals</t>
         </is>
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
+          <t>耐久 {0}/{1}｜电池 {2}｜伤势 {3}</t>
         </is>
       </c>
       <c r="D1796" t="inlineStr">
         <is>
-          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
+          <t>Durability {0}/{1} | Battery {2} | Injuries {3}</t>
         </is>
       </c>
     </row>
@@ -32760,17 +32760,17 @@
       <c r="A1797" t="inlineStr"/>
       <c r="B1797" t="inlineStr">
         <is>
-          <t>machine.detail.line_morph</t>
+          <t>machine.detail.line_exp</t>
         </is>
       </c>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>机身：{0}</t>
+          <t>经历：{0}</t>
         </is>
       </c>
       <c r="D1797" t="inlineStr">
         <is>
-          <t>Body: {0}</t>
+          <t>Experience: {0}</t>
         </is>
       </c>
     </row>
@@ -32778,17 +32778,17 @@
       <c r="A1798" t="inlineStr"/>
       <c r="B1798" t="inlineStr">
         <is>
-          <t>victory.summary</t>
+          <t>machine.detail.line_signal</t>
         </is>
       </c>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
         <is>
-          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -32796,17 +32796,17 @@
       <c r="A1799" t="inlineStr"/>
       <c r="B1799" t="inlineStr">
         <is>
-          <t>victory.row.number</t>
+          <t>machine.detail.line_stats</t>
         </is>
       </c>
       <c r="C1799" t="inlineStr">
         <is>
-          <t>#{0}（{1}）</t>
+          <t>统计：工作 {0}｜远征 {1}｜击杀 {2}</t>
         </is>
       </c>
       <c r="D1799" t="inlineStr">
         <is>
-          <t>#{0} ({1})</t>
+          <t>Stats: jobs {0} | expeditions {1} | kills {2}</t>
         </is>
       </c>
     </row>
@@ -32814,17 +32814,17 @@
       <c r="A1800" t="inlineStr"/>
       <c r="B1800" t="inlineStr">
         <is>
-          <t>victory.row.alive</t>
+          <t>machine.detail.line_morph</t>
         </is>
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>幸存</t>
+          <t>机身：{0}</t>
         </is>
       </c>
       <c r="D1800" t="inlineStr">
         <is>
-          <t>survived</t>
+          <t>Body: {0}</t>
         </is>
       </c>
     </row>
@@ -32832,17 +32832,17 @@
       <c r="A1801" t="inlineStr"/>
       <c r="B1801" t="inlineStr">
         <is>
-          <t>victory.row.dead</t>
+          <t>victory.summary</t>
         </is>
       </c>
       <c r="C1801" t="inlineStr">
         <is>
-          <t>阵亡</t>
+          <t>幸存 {0} 台｜阵亡 {1} 台｜主动接入 {2} 次｜出征 {3} 次｜完成时间 {4} 秒</t>
         </is>
       </c>
       <c r="D1801" t="inlineStr">
         <is>
-          <t>destroyed</t>
+          <t>{0} survived | {1} destroyed | {2} uplinks you started | {3} expeditions | finished in {4}s</t>
         </is>
       </c>
     </row>
@@ -32850,17 +32850,17 @@
       <c r="A1802" t="inlineStr"/>
       <c r="B1802" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_alive</t>
+          <t>victory.row.number</t>
         </is>
       </c>
       <c r="C1802" t="inlineStr">
         <is>
-          <t>幸存，将随撤离返回家园；{0}</t>
+          <t>#{0}（{1}）</t>
         </is>
       </c>
       <c r="D1802" t="inlineStr">
         <is>
-          <t>Survived and returns home with the evacuation; {0}</t>
+          <t>#{0} ({1})</t>
         </is>
       </c>
     </row>
@@ -32868,17 +32868,17 @@
       <c r="A1803" t="inlineStr"/>
       <c r="B1803" t="inlineStr">
         <is>
-          <t>expedition.return.row_status_dead</t>
+          <t>victory.row.alive</t>
         </is>
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
+          <t>幸存</t>
         </is>
       </c>
       <c r="D1803" t="inlineStr">
         <is>
-          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
+          <t>survived</t>
         </is>
       </c>
     </row>
@@ -32886,17 +32886,17 @@
       <c r="A1804" t="inlineStr"/>
       <c r="B1804" t="inlineStr">
         <is>
-          <t>factory.reason.uplinked</t>
+          <t>victory.row.dead</t>
         </is>
       </c>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>这台机器正被你接入，先退出接入</t>
+          <t>阵亡</t>
         </is>
       </c>
       <c r="D1804" t="inlineStr">
         <is>
-          <t>You are uplinked into this machine: leave the uplink first</t>
+          <t>destroyed</t>
         </is>
       </c>
     </row>
@@ -32904,17 +32904,17 @@
       <c r="A1805" t="inlineStr"/>
       <c r="B1805" t="inlineStr">
         <is>
-          <t>signal.cmd.uplinked</t>
+          <t>expedition.return.row_status_alive</t>
         </is>
       </c>
       <c r="C1805" t="inlineStr">
         <is>
-          <t>接入：{0}</t>
+          <t>幸存，将随撤离返回家园；{0}</t>
         </is>
       </c>
       <c r="D1805" t="inlineStr">
         <is>
-          <t>Uplinked: {0}</t>
+          <t>Survived and returns home with the evacuation; {0}</t>
         </is>
       </c>
     </row>
@@ -32922,17 +32922,17 @@
       <c r="A1806" t="inlineStr"/>
       <c r="B1806" t="inlineStr">
         <is>
-          <t>signal.cmd.reconnecting</t>
+          <t>expedition.return.row_status_dead</t>
         </is>
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>重连中：{0}</t>
+          <t>阵亡（纪念记录，黑匣子保留经历，机体不复活）；{0}</t>
         </is>
       </c>
       <c r="D1806" t="inlineStr">
         <is>
-          <t>Reconnecting: {0}</t>
+          <t>Destroyed (memorial record; the black box keeps its experience, the body does not come back); {0}</t>
         </is>
       </c>
     </row>
@@ -32940,17 +32940,17 @@
       <c r="A1807" t="inlineStr"/>
       <c r="B1807" t="inlineStr">
         <is>
-          <t>signal.cmd.strategy</t>
+          <t>factory.reason.uplinked</t>
         </is>
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>战略视角</t>
+          <t>这台机器正被你接入，先退出接入</t>
         </is>
       </c>
       <c r="D1807" t="inlineStr">
         <is>
-          <t>Strategy view</t>
+          <t>You are uplinked into this machine: leave the uplink first</t>
         </is>
       </c>
     </row>
@@ -32958,17 +32958,17 @@
       <c r="A1808" t="inlineStr"/>
       <c r="B1808" t="inlineStr">
         <is>
-          <t>region.control.fail.not_found</t>
+          <t>signal.cmd.uplinked</t>
         </is>
       </c>
       <c r="C1808" t="inlineStr">
         <is>
-          <t>没有可以接入的目标。</t>
+          <t>接入：{0}</t>
         </is>
       </c>
       <c r="D1808" t="inlineStr">
         <is>
-          <t>There is nothing to uplink into.</t>
+          <t>Uplinked: {0}</t>
         </is>
       </c>
     </row>
@@ -32976,17 +32976,17 @@
       <c r="A1809" t="inlineStr"/>
       <c r="B1809" t="inlineStr">
         <is>
-          <t>region.control.fail.not_friendly</t>
+          <t>signal.cmd.reconnecting</t>
         </is>
       </c>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>目标不属于本地点。</t>
+          <t>重连中：{0}</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
         <is>
-          <t>The target does not belong to this site.</t>
+          <t>Reconnecting: {0}</t>
         </is>
       </c>
     </row>
@@ -32994,17 +32994,17 @@
       <c r="A1810" t="inlineStr"/>
       <c r="B1810" t="inlineStr">
         <is>
-          <t>region.control.fail.dead</t>
+          <t>signal.cmd.strategy</t>
         </is>
       </c>
       <c r="C1810" t="inlineStr">
         <is>
-          <t>目标已阵亡。</t>
+          <t>战略视角</t>
         </is>
       </c>
       <c r="D1810" t="inlineStr">
         <is>
-          <t>The target is destroyed.</t>
+          <t>Strategy view</t>
         </is>
       </c>
     </row>
@@ -33012,17 +33012,17 @@
       <c r="A1811" t="inlineStr"/>
       <c r="B1811" t="inlineStr">
         <is>
-          <t>region.control.fail.out_of_range</t>
+          <t>region.control.fail.not_found</t>
         </is>
       </c>
       <c r="C1811" t="inlineStr">
         <is>
-          <t>目标当前不在场。</t>
+          <t>没有可以接入的目标。</t>
         </is>
       </c>
       <c r="D1811" t="inlineStr">
         <is>
-          <t>The target is not here right now.</t>
+          <t>There is nothing to uplink into.</t>
         </is>
       </c>
     </row>
@@ -33030,17 +33030,17 @@
       <c r="A1812" t="inlineStr"/>
       <c r="B1812" t="inlineStr">
         <is>
-          <t>region.control.fail.jammed</t>
+          <t>region.control.fail.not_friendly</t>
         </is>
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>信号被干扰，接入失败。</t>
+          <t>目标不属于本地点。</t>
         </is>
       </c>
       <c r="D1812" t="inlineStr">
         <is>
-          <t>The signal is jammed; uplink failed.</t>
+          <t>The target does not belong to this site.</t>
         </is>
       </c>
     </row>
@@ -33048,17 +33048,17 @@
       <c r="A1813" t="inlineStr"/>
       <c r="B1813" t="inlineStr">
         <is>
-          <t>region.control.fail.transition</t>
+          <t>region.control.fail.dead</t>
         </is>
       </c>
       <c r="C1813" t="inlineStr">
         <is>
-          <t>镜头切换中，请稍候。</t>
+          <t>目标已阵亡。</t>
         </is>
       </c>
       <c r="D1813" t="inlineStr">
         <is>
-          <t>The camera is moving; please wait.</t>
+          <t>The target is destroyed.</t>
         </is>
       </c>
     </row>
@@ -33066,17 +33066,17 @@
       <c r="A1814" t="inlineStr"/>
       <c r="B1814" t="inlineStr">
         <is>
-          <t>region.control.fail.modal</t>
+          <t>region.control.fail.out_of_range</t>
         </is>
       </c>
       <c r="C1814" t="inlineStr">
         <is>
-          <t>请先关闭当前面板。</t>
+          <t>目标当前不在场。</t>
         </is>
       </c>
       <c r="D1814" t="inlineStr">
         <is>
-          <t>Close the current panel first.</t>
+          <t>The target is not here right now.</t>
         </is>
       </c>
     </row>
@@ -33084,17 +33084,17 @@
       <c r="A1815" t="inlineStr"/>
       <c r="B1815" t="inlineStr">
         <is>
-          <t>region.control.fail.already</t>
+          <t>region.control.fail.jammed</t>
         </is>
       </c>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>已经接入这台机器。</t>
+          <t>信号被干扰，接入失败。</t>
         </is>
       </c>
       <c r="D1815" t="inlineStr">
         <is>
-          <t>You are already uplinked into this machine.</t>
+          <t>The signal is jammed; uplink failed.</t>
         </is>
       </c>
     </row>
@@ -33102,17 +33102,17 @@
       <c r="A1816" t="inlineStr"/>
       <c r="B1816" t="inlineStr">
         <is>
-          <t>region.control.fail.ineligible</t>
+          <t>region.control.fail.transition</t>
         </is>
       </c>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>目标暂时不能接入。</t>
+          <t>镜头切换中，请稍候。</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">
         <is>
-          <t>The target cannot be uplinked right now.</t>
+          <t>The camera is moving; please wait.</t>
         </is>
       </c>
     </row>
@@ -33120,17 +33120,17 @@
       <c r="A1817" t="inlineStr"/>
       <c r="B1817" t="inlineStr">
         <is>
-          <t>region.control.fail.other</t>
+          <t>region.control.fail.modal</t>
         </is>
       </c>
       <c r="C1817" t="inlineStr">
         <is>
-          <t>接入失败。</t>
+          <t>请先关闭当前面板。</t>
         </is>
       </c>
       <c r="D1817" t="inlineStr">
         <is>
-          <t>Uplink failed.</t>
+          <t>Close the current panel first.</t>
         </is>
       </c>
     </row>
@@ -33138,17 +33138,17 @@
       <c r="A1818" t="inlineStr"/>
       <c r="B1818" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink</t>
+          <t>region.control.fail.already</t>
         </is>
       </c>
       <c r="C1818" t="inlineStr">
         <is>
-          <t>接入</t>
+          <t>已经接入这台机器。</t>
         </is>
       </c>
       <c r="D1818" t="inlineStr">
         <is>
-          <t>Uplink</t>
+          <t>You are already uplinked into this machine.</t>
         </is>
       </c>
     </row>
@@ -33156,17 +33156,17 @@
       <c r="A1819" t="inlineStr"/>
       <c r="B1819" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink</t>
+          <t>region.control.fail.ineligible</t>
         </is>
       </c>
       <c r="C1819" t="inlineStr">
         <is>
-          <t>已接入</t>
+          <t>目标暂时不能接入。</t>
         </is>
       </c>
       <c r="D1819" t="inlineStr">
         <is>
-          <t>Uplinked</t>
+          <t>The target cannot be uplinked right now.</t>
         </is>
       </c>
     </row>
@@ -33174,17 +33174,17 @@
       <c r="A1820" t="inlineStr"/>
       <c r="B1820" t="inlineStr">
         <is>
-          <t>feedback.tag.uplink_leave</t>
+          <t>region.control.fail.other</t>
         </is>
       </c>
       <c r="C1820" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>接入失败。</t>
         </is>
       </c>
       <c r="D1820" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Uplink failed.</t>
         </is>
       </c>
     </row>
@@ -33192,17 +33192,17 @@
       <c r="A1821" t="inlineStr"/>
       <c r="B1821" t="inlineStr">
         <is>
-          <t>feedback.caption.uplink_leave</t>
+          <t>feedback.tag.uplink</t>
         </is>
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>信号离开机器</t>
+          <t>接入</t>
         </is>
       </c>
       <c r="D1821" t="inlineStr">
         <is>
-          <t>The signal left the machine</t>
+          <t>Uplink</t>
         </is>
       </c>
     </row>
@@ -33210,17 +33210,17 @@
       <c r="A1822" t="inlineStr"/>
       <c r="B1822" t="inlineStr">
         <is>
-          <t>pause.codex</t>
+          <t>feedback.caption.uplink</t>
         </is>
       </c>
       <c r="C1822" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>已接入</t>
         </is>
       </c>
       <c r="D1822" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Uplinked</t>
         </is>
       </c>
     </row>
@@ -33228,17 +33228,17 @@
       <c r="A1823" t="inlineStr"/>
       <c r="B1823" t="inlineStr">
         <is>
-          <t>pause.camera_title</t>
+          <t>feedback.tag.uplink_leave</t>
         </is>
       </c>
       <c r="C1823" t="inlineStr">
         <is>
-          <t>接入镜头</t>
+          <t>离开</t>
         </is>
       </c>
       <c r="D1823" t="inlineStr">
         <is>
-          <t>Uplink camera</t>
+          <t>Leave</t>
         </is>
       </c>
     </row>
@@ -33246,17 +33246,17 @@
       <c r="A1824" t="inlineStr"/>
       <c r="B1824" t="inlineStr">
         <is>
-          <t>pause.camera_zoom</t>
+          <t>feedback.caption.uplink_leave</t>
         </is>
       </c>
       <c r="C1824" t="inlineStr">
         <is>
-          <t>接入时镜头距离 {0}%</t>
+          <t>信号离开机器</t>
         </is>
       </c>
       <c r="D1824" t="inlineStr">
         <is>
-          <t>Uplink camera distance {0}%</t>
+          <t>The signal left the machine</t>
         </is>
       </c>
     </row>
@@ -33264,17 +33264,17 @@
       <c r="A1825" t="inlineStr"/>
       <c r="B1825" t="inlineStr">
         <is>
-          <t>pause.camera_follow</t>
+          <t>pause.codex</t>
         </is>
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>接入时跟随力度 {0}%</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="D1825" t="inlineStr">
         <is>
-          <t>Uplink follow strength {0}%</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
@@ -33282,17 +33282,17 @@
       <c r="A1826" t="inlineStr"/>
       <c r="B1826" t="inlineStr">
         <is>
-          <t>pause.camera_reset</t>
+          <t>pause.camera_title</t>
         </is>
       </c>
       <c r="C1826" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>接入镜头</t>
         </is>
       </c>
       <c r="D1826" t="inlineStr">
         <is>
-          <t>Reset to default</t>
+          <t>Uplink camera</t>
         </is>
       </c>
     </row>
@@ -33300,17 +33300,17 @@
       <c r="A1827" t="inlineStr"/>
       <c r="B1827" t="inlineStr">
         <is>
-          <t>pause.camera_zoom_tip</t>
+          <t>pause.camera_zoom</t>
         </is>
       </c>
       <c r="C1827" t="inlineStr">
         <is>
-          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>接入时镜头距离 {0}%</t>
         </is>
       </c>
       <c r="D1827" t="inlineStr">
         <is>
-          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>Uplink camera distance {0}%</t>
         </is>
       </c>
     </row>
@@ -33318,17 +33318,17 @@
       <c r="A1828" t="inlineStr"/>
       <c r="B1828" t="inlineStr">
         <is>
-          <t>pause.camera_follow_tip</t>
+          <t>pause.camera_follow</t>
         </is>
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
+          <t>接入时跟随力度 {0}%</t>
         </is>
       </c>
       <c r="D1828" t="inlineStr">
         <is>
-          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
+          <t>Uplink follow strength {0}%</t>
         </is>
       </c>
     </row>
@@ -33336,17 +33336,17 @@
       <c r="A1829" t="inlineStr"/>
       <c r="B1829" t="inlineStr">
         <is>
-          <t>camera.follow.started</t>
+          <t>pause.camera_reset</t>
         </is>
       </c>
       <c r="C1829" t="inlineStr">
         <is>
-          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
+          <t>恢复默认</t>
         </is>
       </c>
       <c r="D1829" t="inlineStr">
         <is>
-          <t>Camera following {0} (pan or press {1} again to stop)</t>
+          <t>Reset to default</t>
         </is>
       </c>
     </row>
@@ -33354,17 +33354,17 @@
       <c r="A1830" t="inlineStr"/>
       <c r="B1830" t="inlineStr">
         <is>
-          <t>camera.follow.stopped</t>
+          <t>pause.camera_zoom_tip</t>
         </is>
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>镜头停止跟随</t>
+          <t>接入机器时镜头离机器多远：数值越大看得越广（{0}%～{1}%，默认 100%）。立即生效。</t>
         </is>
       </c>
       <c r="D1830" t="inlineStr">
         <is>
-          <t>Camera follow stopped</t>
+          <t>How far the camera sits from the uplinked machine: higher shows more (from {0}% to {1}%, default 100%). Applies immediately.</t>
         </is>
       </c>
     </row>
@@ -33372,17 +33372,17 @@
       <c r="A1831" t="inlineStr"/>
       <c r="B1831" t="inlineStr">
         <is>
-          <t>camera.follow.nothing</t>
+          <t>pause.camera_follow_tip</t>
         </is>
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>先选中一台机器再按 {0} 跟随</t>
+          <t>接入时镜头追上机器的快慢：数值越大跟得越紧，越小越平滑（{0}%～{1}%，默认 100%）。立即生效。</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
         <is>
-          <t>Select a machine first, then press {0} to follow it</t>
+          <t>How quickly the camera catches up with the uplinked machine: higher follows tighter, lower is smoother (from {0}% to {1}%, default 100%). Applies immediately.</t>
         </is>
       </c>
     </row>
@@ -33390,17 +33390,17 @@
       <c r="A1832" t="inlineStr"/>
       <c r="B1832" t="inlineStr">
         <is>
-          <t>camera.follow.group</t>
+          <t>camera.follow.started</t>
         </is>
       </c>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>{0} 台机器</t>
+          <t>镜头跟随 {0}（平移镜头或再按 {1} 停止）</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
         <is>
-          <t>{0} machines</t>
+          <t>Camera following {0} (pan or press {1} again to stop)</t>
         </is>
       </c>
     </row>
@@ -33408,17 +33408,17 @@
       <c r="A1833" t="inlineStr"/>
       <c r="B1833" t="inlineStr">
         <is>
-          <t>fwlib.title</t>
+          <t>camera.follow.stopped</t>
         </is>
       </c>
       <c r="C1833" t="inlineStr">
         <is>
-          <t>固件库</t>
+          <t>镜头停止跟随</t>
         </is>
       </c>
       <c r="D1833" t="inlineStr">
         <is>
-          <t>Firmware library</t>
+          <t>Camera follow stopped</t>
         </is>
       </c>
     </row>
@@ -33426,17 +33426,17 @@
       <c r="A1834" t="inlineStr"/>
       <c r="B1834" t="inlineStr">
         <is>
-          <t>fwlib.close</t>
+          <t>camera.follow.nothing</t>
         </is>
       </c>
       <c r="C1834" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>先选中一台机器再按 {0} 跟随</t>
         </is>
       </c>
       <c r="D1834" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Select a machine first, then press {0} to follow it</t>
         </is>
       </c>
     </row>
@@ -33444,17 +33444,17 @@
       <c r="A1835" t="inlineStr"/>
       <c r="B1835" t="inlineStr">
         <is>
-          <t>fwlib.count</t>
+          <t>camera.follow.group</t>
         </is>
       </c>
       <c r="C1835" t="inlineStr">
         <is>
-          <t>芯片 {0} 枚（显示 {1}）· 仓储 {2}/{3} 格</t>
+          <t>{0} 台机器</t>
         </is>
       </c>
       <c r="D1835" t="inlineStr">
         <is>
-          <t>Chips {0} (showing {1}) · Storage {2}/{3}</t>
+          <t>{0} machines</t>
         </is>
       </c>
     </row>
@@ -33462,17 +33462,17 @@
       <c r="A1836" t="inlineStr"/>
       <c r="B1836" t="inlineStr">
         <is>
-          <t>fwlib.over_capacity</t>
+          <t>fwlib.title</t>
         </is>
       </c>
       <c r="C1836" t="inlineStr">
         <is>
-          <t>仓储已满：新得到的芯片会进入待领取</t>
+          <t>固件库</t>
         </is>
       </c>
       <c r="D1836" t="inlineStr">
         <is>
-          <t>Storage is full: new chips go to the claim queue</t>
+          <t>Firmware library</t>
         </is>
       </c>
     </row>
@@ -33480,17 +33480,17 @@
       <c r="A1837" t="inlineStr"/>
       <c r="B1837" t="inlineStr">
         <is>
-          <t>fwlib.search</t>
+          <t>fwlib.close</t>
         </is>
       </c>
       <c r="C1837" t="inlineStr">
         <is>
-          <t>搜索名称或说明</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="D1837" t="inlineStr">
         <is>
-          <t>Search name or description</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -33498,17 +33498,17 @@
       <c r="A1838" t="inlineStr"/>
       <c r="B1838" t="inlineStr">
         <is>
-          <t>fwlib.filter.category</t>
+          <t>fwlib.count</t>
         </is>
       </c>
       <c r="C1838" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>芯片 {0} 枚（显示 {1}）· 仓储 {2}/{3} 格</t>
         </is>
       </c>
       <c r="D1838" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Chips {0} (showing {1}) · Storage {2}/{3}</t>
         </is>
       </c>
     </row>
@@ -33516,17 +33516,17 @@
       <c r="A1839" t="inlineStr"/>
       <c r="B1839" t="inlineStr">
         <is>
-          <t>fwlib.filter.kind</t>
+          <t>fwlib.over_capacity</t>
         </is>
       </c>
       <c r="C1839" t="inlineStr">
         <is>
-          <t>种类</t>
+          <t>仓储已满：新得到的芯片会进入待领取</t>
         </is>
       </c>
       <c r="D1839" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Storage is full: new chips go to the claim queue</t>
         </is>
       </c>
     </row>
@@ -33534,17 +33534,17 @@
       <c r="A1840" t="inlineStr"/>
       <c r="B1840" t="inlineStr">
         <is>
-          <t>fwlib.filter.protocol</t>
+          <t>fwlib.search</t>
         </is>
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>协议</t>
+          <t>搜索名称或说明</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Search name or description</t>
         </is>
       </c>
     </row>
@@ -33552,17 +33552,17 @@
       <c r="A1841" t="inlineStr"/>
       <c r="B1841" t="inlineStr">
         <is>
-          <t>fwlib.filter.cracked</t>
+          <t>fwlib.filter.category</t>
         </is>
       </c>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>破解</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D1841" t="inlineStr">
         <is>
-          <t>Cracked</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -33570,17 +33570,17 @@
       <c r="A1842" t="inlineStr"/>
       <c r="B1842" t="inlineStr">
         <is>
-          <t>fwlib.filter.carrier</t>
+          <t>fwlib.filter.kind</t>
         </is>
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>兼容载体</t>
+          <t>种类</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Kind</t>
         </is>
       </c>
     </row>
@@ -33588,17 +33588,17 @@
       <c r="A1843" t="inlineStr"/>
       <c r="B1843" t="inlineStr">
         <is>
-          <t>fwlib.filter.rarity</t>
+          <t>fwlib.filter.protocol</t>
         </is>
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>协议</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
         <is>
-          <t>Rarity</t>
+          <t>Protocol</t>
         </is>
       </c>
     </row>
@@ -33606,17 +33606,17 @@
       <c r="A1844" t="inlineStr"/>
       <c r="B1844" t="inlineStr">
         <is>
-          <t>fwlib.sort</t>
+          <t>fwlib.filter.cracked</t>
         </is>
       </c>
       <c r="C1844" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>破解</t>
         </is>
       </c>
       <c r="D1844" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Cracked</t>
         </is>
       </c>
     </row>
@@ -33624,17 +33624,17 @@
       <c r="A1845" t="inlineStr"/>
       <c r="B1845" t="inlineStr">
         <is>
-          <t>fwlib.any</t>
+          <t>fwlib.filter.carrier</t>
         </is>
       </c>
       <c r="C1845" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>兼容载体</t>
         </is>
       </c>
       <c r="D1845" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Carrier</t>
         </is>
       </c>
     </row>
@@ -33642,17 +33642,17 @@
       <c r="A1846" t="inlineStr"/>
       <c r="B1846" t="inlineStr">
         <is>
-          <t>fwlib.kind.regular</t>
+          <t>fwlib.filter.rarity</t>
         </is>
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>● 常规</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
         <is>
-          <t>● Regular</t>
+          <t>Rarity</t>
         </is>
       </c>
     </row>
@@ -33660,17 +33660,17 @@
       <c r="A1847" t="inlineStr"/>
       <c r="B1847" t="inlineStr">
         <is>
-          <t>fwlib.kind.core</t>
+          <t>fwlib.sort</t>
         </is>
       </c>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>◆ 核心</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
         <is>
-          <t>◆ Core</t>
+          <t>Sort</t>
         </is>
       </c>
     </row>
@@ -33678,17 +33678,17 @@
       <c r="A1848" t="inlineStr"/>
       <c r="B1848" t="inlineStr">
         <is>
-          <t>fwlib.protocol.own</t>
+          <t>fwlib.any</t>
         </is>
       </c>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>己方 / 中立</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">
         <is>
-          <t>Own / neutral</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -33696,17 +33696,17 @@
       <c r="A1849" t="inlineStr"/>
       <c r="B1849" t="inlineStr">
         <is>
-          <t>fwlib.cracked.yes</t>
+          <t>fwlib.kind.regular</t>
         </is>
       </c>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>已破解</t>
+          <t>● 常规</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
         <is>
-          <t>Cracked</t>
+          <t>● Regular</t>
         </is>
       </c>
     </row>
@@ -33714,17 +33714,17 @@
       <c r="A1850" t="inlineStr"/>
       <c r="B1850" t="inlineStr">
         <is>
-          <t>fwlib.cracked.no</t>
+          <t>fwlib.kind.core</t>
         </is>
       </c>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>▲ 未破解</t>
+          <t>◆ 核心</t>
         </is>
       </c>
       <c r="D1850" t="inlineStr">
         <is>
-          <t>▲ Not cracked</t>
+          <t>◆ Core</t>
         </is>
       </c>
     </row>
@@ -33732,17 +33732,17 @@
       <c r="A1851" t="inlineStr"/>
       <c r="B1851" t="inlineStr">
         <is>
-          <t>fwlib.sort.name</t>
+          <t>fwlib.protocol.own</t>
         </is>
       </c>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>己方 / 中立</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Own / neutral</t>
         </is>
       </c>
     </row>
@@ -33750,17 +33750,17 @@
       <c r="A1852" t="inlineStr"/>
       <c r="B1852" t="inlineStr">
         <is>
-          <t>fwlib.sort.category</t>
+          <t>fwlib.cracked.yes</t>
         </is>
       </c>
       <c r="C1852" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>已破解</t>
         </is>
       </c>
       <c r="D1852" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Cracked</t>
         </is>
       </c>
     </row>
@@ -33768,17 +33768,17 @@
       <c r="A1853" t="inlineStr"/>
       <c r="B1853" t="inlineStr">
         <is>
-          <t>fwlib.sort.rarity</t>
+          <t>fwlib.cracked.no</t>
         </is>
       </c>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>稀有度（高→低）</t>
+          <t>▲ 未破解</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
         <is>
-          <t>Rarity (high→low)</t>
+          <t>▲ Not cracked</t>
         </is>
       </c>
     </row>
@@ -33786,17 +33786,17 @@
       <c r="A1854" t="inlineStr"/>
       <c r="B1854" t="inlineStr">
         <is>
-          <t>fwlib.sort.load</t>
+          <t>fwlib.sort.name</t>
         </is>
       </c>
       <c r="C1854" t="inlineStr">
         <is>
-          <t>负载（高→低）</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="D1854" t="inlineStr">
         <is>
-          <t>Load (high→low)</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -33804,17 +33804,17 @@
       <c r="A1855" t="inlineStr"/>
       <c r="B1855" t="inlineStr">
         <is>
-          <t>fwlib.sort.newest</t>
+          <t>fwlib.sort.category</t>
         </is>
       </c>
       <c r="C1855" t="inlineStr">
         <is>
-          <t>最新获得</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
         <is>
-          <t>Newest</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -33822,17 +33822,17 @@
       <c r="A1856" t="inlineStr"/>
       <c r="B1856" t="inlineStr">
         <is>
-          <t>fwlib.sort.location</t>
+          <t>fwlib.sort.rarity</t>
         </is>
       </c>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>所在位置</t>
+          <t>稀有度（高→低）</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Rarity (high→low)</t>
         </is>
       </c>
     </row>
@@ -33840,17 +33840,17 @@
       <c r="A1857" t="inlineStr"/>
       <c r="B1857" t="inlineStr">
         <is>
-          <t>fwlib.empty</t>
+          <t>fwlib.sort.load</t>
         </is>
       </c>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>还没有固件芯片。在信号核面板里刻印，或从远征带回。</t>
+          <t>负载（高→低）</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
         <is>
-          <t>No firmware chips yet. Print them in the Signal Core panel or bring them back from expeditions.</t>
+          <t>Load (high→low)</t>
         </is>
       </c>
     </row>
@@ -33858,17 +33858,17 @@
       <c r="A1858" t="inlineStr"/>
       <c r="B1858" t="inlineStr">
         <is>
-          <t>fwlib.empty_filtered</t>
+          <t>fwlib.sort.newest</t>
         </is>
       </c>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>没有符合筛选条件的芯片。</t>
+          <t>最新获得</t>
         </is>
       </c>
       <c r="D1858" t="inlineStr">
         <is>
-          <t>No chips match the filters.</t>
+          <t>Newest</t>
         </is>
       </c>
     </row>
@@ -33876,17 +33876,17 @@
       <c r="A1859" t="inlineStr"/>
       <c r="B1859" t="inlineStr">
         <is>
-          <t>fwlib.error</t>
+          <t>fwlib.sort.location</t>
         </is>
       </c>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>固件数据不可用（配置表缺失），请重新安装或联系开发者：{0}</t>
+          <t>所在位置</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
         <is>
-          <t>Firmware data is unavailable (missing table); reinstall or contact the developers: {0}</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
@@ -33894,17 +33894,17 @@
       <c r="A1860" t="inlineStr"/>
       <c r="B1860" t="inlineStr">
         <is>
-          <t>fwlib.loc.storage</t>
+          <t>fwlib.empty</t>
         </is>
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>仓储</t>
+          <t>还没有固件芯片。在信号核面板里刻印，或从远征带回。</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>No firmware chips yet. Print them in the Signal Core panel or bring them back from expeditions.</t>
         </is>
       </c>
     </row>
@@ -33912,17 +33912,17 @@
       <c r="A1861" t="inlineStr"/>
       <c r="B1861" t="inlineStr">
         <is>
-          <t>fwlib.loc.pending</t>
+          <t>fwlib.empty_filtered</t>
         </is>
       </c>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>待领取（仓储已满）</t>
+          <t>没有符合筛选条件的芯片。</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
         <is>
-          <t>Awaiting claim (storage full)</t>
+          <t>No chips match the filters.</t>
         </is>
       </c>
     </row>
@@ -33930,17 +33930,17 @@
       <c r="A1862" t="inlineStr"/>
       <c r="B1862" t="inlineStr">
         <is>
-          <t>fwlib.loc.signal</t>
+          <t>fwlib.error</t>
         </is>
       </c>
       <c r="C1862" t="inlineStr">
         <is>
-          <t>信号核 第 {0} 槽</t>
+          <t>固件数据不可用（配置表缺失），请重新安装或联系开发者：{0}</t>
         </is>
       </c>
       <c r="D1862" t="inlineStr">
         <is>
-          <t>Signal Core slot {0}</t>
+          <t>Firmware data is unavailable (missing table); reinstall or contact the developers: {0}</t>
         </is>
       </c>
     </row>
@@ -33948,17 +33948,17 @@
       <c r="A1863" t="inlineStr"/>
       <c r="B1863" t="inlineStr">
         <is>
-          <t>fwlib.loc.reserved</t>
+          <t>fwlib.loc.storage</t>
         </is>
       </c>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>仓储（合成台预留中）</t>
+          <t>仓储</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
         <is>
-          <t>Storage (reserved by crafting)</t>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -33966,17 +33966,17 @@
       <c r="A1864" t="inlineStr"/>
       <c r="B1864" t="inlineStr">
         <is>
-          <t>fwlib.loc.draft</t>
+          <t>fwlib.loc.pending</t>
         </is>
       </c>
       <c r="C1864" t="inlineStr">
         <is>
-          <t>蓝图电路（{0}）</t>
+          <t>待领取（仓储已满）</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
         <is>
-          <t>Blueprint circuit ({0})</t>
+          <t>Awaiting claim (storage full)</t>
         </is>
       </c>
     </row>
@@ -33984,17 +33984,17 @@
       <c r="A1865" t="inlineStr"/>
       <c r="B1865" t="inlineStr">
         <is>
-          <t>fwlib.row.locked</t>
+          <t>fwlib.loc.signal</t>
         </is>
       </c>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>［锁定］</t>
+          <t>信号核 第 {0} 槽</t>
         </is>
       </c>
       <c r="D1865" t="inlineStr">
         <is>
-          <t>[Locked]</t>
+          <t>Signal Core slot {0}</t>
         </is>
       </c>
     </row>
@@ -34002,17 +34002,17 @@
       <c r="A1866" t="inlineStr"/>
       <c r="B1866" t="inlineStr">
         <is>
-          <t>fwlib.select_all</t>
+          <t>fwlib.loc.reserved</t>
         </is>
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>全选当前列表</t>
+          <t>仓储（合成台预留中）</t>
         </is>
       </c>
       <c r="D1866" t="inlineStr">
         <is>
-          <t>Select all shown</t>
+          <t>Storage (reserved by crafting)</t>
         </is>
       </c>
     </row>
@@ -34020,17 +34020,17 @@
       <c r="A1867" t="inlineStr"/>
       <c r="B1867" t="inlineStr">
         <is>
-          <t>fwlib.select_none</t>
+          <t>fwlib.loc.draft</t>
         </is>
       </c>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>清空选择</t>
+          <t>蓝图电路（{0}）</t>
         </is>
       </c>
       <c r="D1867" t="inlineStr">
         <is>
-          <t>Clear selection</t>
+          <t>Blueprint circuit ({0})</t>
         </is>
       </c>
     </row>
@@ -34038,17 +34038,17 @@
       <c r="A1868" t="inlineStr"/>
       <c r="B1868" t="inlineStr">
         <is>
-          <t>fwlib.selected</t>
+          <t>fwlib.row.locked</t>
         </is>
       </c>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>已选 {0} 枚</t>
+          <t>［锁定］</t>
         </is>
       </c>
       <c r="D1868" t="inlineStr">
         <is>
-          <t>{0} selected</t>
+          <t>[Locked]</t>
         </is>
       </c>
     </row>
@@ -34056,17 +34056,17 @@
       <c r="A1869" t="inlineStr"/>
       <c r="B1869" t="inlineStr">
         <is>
-          <t>fwlib.row.pick</t>
+          <t>fwlib.select_all</t>
         </is>
       </c>
       <c r="C1869" t="inlineStr">
         <is>
-          <t>选</t>
+          <t>全选当前列表</t>
         </is>
       </c>
       <c r="D1869" t="inlineStr">
         <is>
-          <t>Pick</t>
+          <t>Select all shown</t>
         </is>
       </c>
     </row>
@@ -34074,17 +34074,17 @@
       <c r="A1870" t="inlineStr"/>
       <c r="B1870" t="inlineStr">
         <is>
-          <t>fwlib.row.picked</t>
+          <t>fwlib.select_none</t>
         </is>
       </c>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>清空选择</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>Clear selection</t>
         </is>
       </c>
     </row>
@@ -34092,17 +34092,17 @@
       <c r="A1871" t="inlineStr"/>
       <c r="B1871" t="inlineStr">
         <is>
-          <t>fwlib.disassemble</t>
+          <t>fwlib.selected</t>
         </is>
       </c>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>分解所选（{0}）</t>
+          <t>已选 {0} 枚</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
         <is>
-          <t>Disassemble selected ({0})</t>
+          <t>{0} selected</t>
         </is>
       </c>
     </row>
@@ -34110,17 +34110,17 @@
       <c r="A1872" t="inlineStr"/>
       <c r="B1872" t="inlineStr">
         <is>
-          <t>fwlib.disassemble_tip</t>
+          <t>fwlib.row.pick</t>
         </is>
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>分解返还废料 {0}/枚。锁定的、装进信号核的、被合成台预留的会跳过。需要确认，无法撤销。</t>
+          <t>选</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
         <is>
-          <t>Each chip refunds {0} scrap. Locked chips, chips in the Signal Core and chips reserved by crafting are skipped. Needs confirmation; cannot be undone.</t>
+          <t>Pick</t>
         </is>
       </c>
     </row>
@@ -34128,17 +34128,17 @@
       <c r="A1873" t="inlineStr"/>
       <c r="B1873" t="inlineStr">
         <is>
-          <t>fwlib.confirm.title</t>
+          <t>fwlib.row.picked</t>
         </is>
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>分解固件芯片</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="D1873" t="inlineStr">
         <is>
-          <t>Disassemble firmware chips</t>
+          <t>✔</t>
         </is>
       </c>
     </row>
@@ -34146,17 +34146,17 @@
       <c r="A1874" t="inlineStr"/>
       <c r="B1874" t="inlineStr">
         <is>
-          <t>fwlib.confirm.lose</t>
+          <t>fwlib.disassemble</t>
         </is>
       </c>
       <c r="C1874" t="inlineStr">
         <is>
-          <t>固件芯片 ×{0}（返还废料 +{1}）</t>
+          <t>分解所选（{0}）</t>
         </is>
       </c>
       <c r="D1874" t="inlineStr">
         <is>
-          <t>Firmware chips ×{0} (refund +{1} scrap)</t>
+          <t>Disassemble selected ({0})</t>
         </is>
       </c>
     </row>
@@ -34164,17 +34164,17 @@
       <c r="A1875" t="inlineStr"/>
       <c r="B1875" t="inlineStr">
         <is>
-          <t>fwlib.confirm.unprintable</t>
+          <t>fwlib.disassemble_tip</t>
         </is>
       </c>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>其中 {0} 枚目前无法再刻印（未解锁或未破解）</t>
+          <t>分解返还废料 {0}/枚。锁定的、装进信号核的、被合成台预留的会跳过。需要确认，无法撤销。</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
         <is>
-          <t>{0} of them cannot be printed again right now (locked or not cracked)</t>
+          <t>Each chip refunds {0} scrap. Locked chips, chips in the Signal Core and chips reserved by crafting are skipped. Needs confirmation; cannot be undone.</t>
         </is>
       </c>
     </row>
@@ -34182,17 +34182,17 @@
       <c r="A1876" t="inlineStr"/>
       <c r="B1876" t="inlineStr">
         <is>
-          <t>fwlib.confirm.skip_locked</t>
+          <t>fwlib.confirm.title</t>
         </is>
       </c>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>跳过锁定的 {0} 枚</t>
+          <t>分解固件芯片</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
         <is>
-          <t>Skipping {0} locked</t>
+          <t>Disassemble firmware chips</t>
         </is>
       </c>
     </row>
@@ -34200,17 +34200,17 @@
       <c r="A1877" t="inlineStr"/>
       <c r="B1877" t="inlineStr">
         <is>
-          <t>fwlib.confirm.skip_busy</t>
+          <t>fwlib.confirm.lose</t>
         </is>
       </c>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>跳过装进信号核或被合成台预留的 {0} 枚</t>
+          <t>固件芯片 ×{0}（返还废料 +{1}）</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
         <is>
-          <t>Skipping {0} in the Signal Core or reserved by crafting</t>
+          <t>Firmware chips ×{0} (refund +{1} scrap)</t>
         </is>
       </c>
     </row>
@@ -34218,17 +34218,17 @@
       <c r="A1878" t="inlineStr"/>
       <c r="B1878" t="inlineStr">
         <is>
-          <t>fwlib.confirm.names</t>
+          <t>fwlib.confirm.unprintable</t>
         </is>
       </c>
       <c r="C1878" t="inlineStr">
         <is>
-          <t>包括：{0}</t>
+          <t>其中 {0} 枚目前无法再刻印（未解锁或未破解）</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
         <is>
-          <t>Includes: {0}</t>
+          <t>{0} of them cannot be printed again right now (locked or not cracked)</t>
         </is>
       </c>
     </row>
@@ -34236,17 +34236,17 @@
       <c r="A1879" t="inlineStr"/>
       <c r="B1879" t="inlineStr">
         <is>
-          <t>fwlib.confirm.name_count</t>
+          <t>fwlib.confirm.skip_locked</t>
         </is>
       </c>
       <c r="C1879" t="inlineStr">
         <is>
-          <t>{0} ×{1}</t>
+          <t>跳过锁定的 {0} 枚</t>
         </is>
       </c>
       <c r="D1879" t="inlineStr">
         <is>
-          <t>{0} ×{1}</t>
+          <t>Skipping {0} locked</t>
         </is>
       </c>
     </row>
@@ -34254,17 +34254,17 @@
       <c r="A1880" t="inlineStr"/>
       <c r="B1880" t="inlineStr">
         <is>
-          <t>fwlib.confirm.name_more</t>
+          <t>fwlib.confirm.skip_busy</t>
         </is>
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>等另外 {0} 种</t>
+          <t>跳过装进信号核或被合成台预留的 {0} 枚</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
         <is>
-          <t>and {0} more kinds</t>
+          <t>Skipping {0} in the Signal Core or reserved by crafting</t>
         </is>
       </c>
     </row>
@@ -34272,17 +34272,17 @@
       <c r="A1881" t="inlineStr"/>
       <c r="B1881" t="inlineStr">
         <is>
-          <t>fwlib.confirm.hidden</t>
+          <t>fwlib.confirm.names</t>
         </is>
       </c>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>其中 {0} 枚不在当前筛选结果里（之前勾选的）</t>
+          <t>包括：{0}</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
         <is>
-          <t>{0} of them are outside the current filter (picked earlier)</t>
+          <t>Includes: {0}</t>
         </is>
       </c>
     </row>
@@ -34290,17 +34290,17 @@
       <c r="A1882" t="inlineStr"/>
       <c r="B1882" t="inlineStr">
         <is>
-          <t>fwlib.confirm.ok</t>
+          <t>fwlib.confirm.name_count</t>
         </is>
       </c>
       <c r="C1882" t="inlineStr">
         <is>
-          <t>分解</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
       <c r="D1882" t="inlineStr">
         <is>
-          <t>Disassemble</t>
+          <t>{0} ×{1}</t>
         </is>
       </c>
     </row>
@@ -34308,17 +34308,17 @@
       <c r="A1883" t="inlineStr"/>
       <c r="B1883" t="inlineStr">
         <is>
-          <t>fwlib.confirm.cancel</t>
+          <t>fwlib.confirm.name_more</t>
         </is>
       </c>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>等另外 {0} 种</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>and {0} more kinds</t>
         </is>
       </c>
     </row>
@@ -34326,17 +34326,17 @@
       <c r="A1884" t="inlineStr"/>
       <c r="B1884" t="inlineStr">
         <is>
-          <t>fwlib.result.done</t>
+          <t>fwlib.confirm.hidden</t>
         </is>
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>已分解 {0} 枚，返还废料 {1}；跳过 {2} 枚</t>
+          <t>其中 {0} 枚不在当前筛选结果里（之前勾选的）</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
         <is>
-          <t>Disassembled {0}, refunded {1} scrap; skipped {2}</t>
+          <t>{0} of them are outside the current filter (picked earlier)</t>
         </is>
       </c>
     </row>
@@ -34344,17 +34344,17 @@
       <c r="A1885" t="inlineStr"/>
       <c r="B1885" t="inlineStr">
         <is>
-          <t>fwlib.result.nothing</t>
+          <t>fwlib.confirm.ok</t>
         </is>
       </c>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>没有可分解的芯片：所选的都已锁定或正在使用</t>
+          <t>分解</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
         <is>
-          <t>Nothing to disassemble: every selected chip is locked or in use</t>
+          <t>Disassemble</t>
         </is>
       </c>
     </row>
@@ -34362,17 +34362,17 @@
       <c r="A1886" t="inlineStr"/>
       <c r="B1886" t="inlineStr">
         <is>
-          <t>fwlib.lock</t>
+          <t>fwlib.confirm.cancel</t>
         </is>
       </c>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>锁定</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -34380,17 +34380,17 @@
       <c r="A1887" t="inlineStr"/>
       <c r="B1887" t="inlineStr">
         <is>
-          <t>fwlib.unlock</t>
+          <t>fwlib.result.done</t>
         </is>
       </c>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>解除锁定</t>
+          <t>已分解 {0} 枚，返还废料 {1}；跳过 {2} 枚</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
         <is>
-          <t>Unlock</t>
+          <t>Disassembled {0}, refunded {1} scrap; skipped {2}</t>
         </is>
       </c>
     </row>
@@ -34398,17 +34398,17 @@
       <c r="A1888" t="inlineStr"/>
       <c r="B1888" t="inlineStr">
         <is>
-          <t>fwlib.lock_tip</t>
+          <t>fwlib.result.nothing</t>
         </is>
       </c>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>锁定后，批量分解会跳过这枚芯片（不影响装进信号核）。</t>
+          <t>没有可分解的芯片：所选的都已锁定或正在使用</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
         <is>
-          <t>Locked chips are skipped by bulk disassembly (they can still go into the Signal Core).</t>
+          <t>Nothing to disassemble: every selected chip is locked or in use</t>
         </is>
       </c>
     </row>
@@ -34416,17 +34416,17 @@
       <c r="A1889" t="inlineStr"/>
       <c r="B1889" t="inlineStr">
         <is>
-          <t>fwlib.claim</t>
+          <t>fwlib.lock</t>
         </is>
       </c>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>领取进仓储</t>
+          <t>锁定</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
         <is>
-          <t>Claim into storage</t>
+          <t>Lock</t>
         </is>
       </c>
     </row>
@@ -34434,17 +34434,17 @@
       <c r="A1890" t="inlineStr"/>
       <c r="B1890" t="inlineStr">
         <is>
-          <t>fwlib.codex</t>
+          <t>fwlib.unlock</t>
         </is>
       </c>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>查看图鉴</t>
+          <t>解除锁定</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
         <is>
-          <t>Open codex</t>
+          <t>Unlock</t>
         </is>
       </c>
     </row>
@@ -34452,17 +34452,17 @@
       <c r="A1891" t="inlineStr"/>
       <c r="B1891" t="inlineStr">
         <is>
-          <t>fwlib.compare_a</t>
+          <t>fwlib.lock_tip</t>
         </is>
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>设为比较 A</t>
+          <t>锁定后，批量分解会跳过这枚芯片（不影响装进信号核）。</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
         <is>
-          <t>Compare as A</t>
+          <t>Locked chips are skipped by bulk disassembly (they can still go into the Signal Core).</t>
         </is>
       </c>
     </row>
@@ -34470,17 +34470,17 @@
       <c r="A1892" t="inlineStr"/>
       <c r="B1892" t="inlineStr">
         <is>
-          <t>fwlib.compare_b</t>
+          <t>fwlib.claim</t>
         </is>
       </c>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>设为比较 B</t>
+          <t>领取进仓储</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
         <is>
-          <t>Compare as B</t>
+          <t>Claim into storage</t>
         </is>
       </c>
     </row>
@@ -34488,17 +34488,17 @@
       <c r="A1893" t="inlineStr"/>
       <c r="B1893" t="inlineStr">
         <is>
-          <t>fwlib.compare.title</t>
+          <t>fwlib.codex</t>
         </is>
       </c>
       <c r="C1893" t="inlineStr">
         <is>
-          <t>比较</t>
+          <t>查看图鉴</t>
         </is>
       </c>
       <c r="D1893" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Open codex</t>
         </is>
       </c>
     </row>
@@ -34506,17 +34506,17 @@
       <c r="A1894" t="inlineStr"/>
       <c r="B1894" t="inlineStr">
         <is>
-          <t>fwlib.compare.empty</t>
+          <t>fwlib.compare_a</t>
         </is>
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>选一枚芯片点“设为比较 A”，再选另一枚点“设为比较 B”，两条固件会并排显示。</t>
+          <t>设为比较 A</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
         <is>
-          <t>Pick a chip and press "Compare as A", then another and press "Compare as B" to see them side by side.</t>
+          <t>Compare as A</t>
         </is>
       </c>
     </row>
@@ -34524,17 +34524,17 @@
       <c r="A1895" t="inlineStr"/>
       <c r="B1895" t="inlineStr">
         <is>
-          <t>fwlib.compare.clear</t>
+          <t>fwlib.compare_b</t>
         </is>
       </c>
       <c r="C1895" t="inlineStr">
         <is>
-          <t>清除比较</t>
+          <t>设为比较 B</t>
         </is>
       </c>
       <c r="D1895" t="inlineStr">
         <is>
-          <t>Clear compare</t>
+          <t>Compare as B</t>
         </is>
       </c>
     </row>
@@ -34542,17 +34542,17 @@
       <c r="A1896" t="inlineStr"/>
       <c r="B1896" t="inlineStr">
         <is>
-          <t>fwlib.compare.same</t>
+          <t>fwlib.compare.title</t>
         </is>
       </c>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>（相同）</t>
+          <t>比较</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
         <is>
-          <t>(same)</t>
+          <t>Compare</t>
         </is>
       </c>
     </row>
@@ -34560,17 +34560,17 @@
       <c r="A1897" t="inlineStr"/>
       <c r="B1897" t="inlineStr">
         <is>
-          <t>fwlib.compare.tags</t>
+          <t>fwlib.compare.empty</t>
         </is>
       </c>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>状态标签</t>
+          <t>选一枚芯片点“设为比较 A”，再选另一枚点“设为比较 B”，两条固件会并排显示。</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
         <is>
-          <t>Status tags</t>
+          <t>Pick a chip and press "Compare as A", then another and press "Compare as B" to see them side by side.</t>
         </is>
       </c>
     </row>
@@ -34578,17 +34578,17 @@
       <c r="A1898" t="inlineStr"/>
       <c r="B1898" t="inlineStr">
         <is>
-          <t>fwlib.detail.none</t>
+          <t>fwlib.compare.clear</t>
         </is>
       </c>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>在左侧选一枚芯片查看详情。</t>
+          <t>清除比较</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
         <is>
-          <t>Pick a chip on the left to see its details.</t>
+          <t>Clear compare</t>
         </is>
       </c>
     </row>
@@ -34596,17 +34596,17 @@
       <c r="A1899" t="inlineStr"/>
       <c r="B1899" t="inlineStr">
         <is>
-          <t>fwlib.detail.kind</t>
+          <t>fwlib.compare.same</t>
         </is>
       </c>
       <c r="C1899" t="inlineStr">
         <is>
-          <t>种类：{0}</t>
+          <t>（相同）</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
         <is>
-          <t>Kind: {0}</t>
+          <t>(same)</t>
         </is>
       </c>
     </row>
@@ -34614,17 +34614,17 @@
       <c r="A1900" t="inlineStr"/>
       <c r="B1900" t="inlineStr">
         <is>
-          <t>fwlib.detail.category</t>
+          <t>fwlib.compare.tags</t>
         </is>
       </c>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>类别：{0}</t>
+          <t>状态标签</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
         <is>
-          <t>Category: {0}</t>
+          <t>Status tags</t>
         </is>
       </c>
     </row>
@@ -34632,17 +34632,17 @@
       <c r="A1901" t="inlineStr"/>
       <c r="B1901" t="inlineStr">
         <is>
-          <t>fwlib.detail.protocol</t>
+          <t>fwlib.detail.none</t>
         </is>
       </c>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>协议：{0}</t>
+          <t>在左侧选一枚芯片查看详情。</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
         <is>
-          <t>Protocol: {0}</t>
+          <t>Pick a chip on the left to see its details.</t>
         </is>
       </c>
     </row>
@@ -34650,17 +34650,17 @@
       <c r="A1902" t="inlineStr"/>
       <c r="B1902" t="inlineStr">
         <is>
-          <t>fwlib.detail.rarity</t>
+          <t>fwlib.detail.kind</t>
         </is>
       </c>
       <c r="C1902" t="inlineStr">
         <is>
-          <t>稀有度：{0}</t>
+          <t>种类：{0}</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
         <is>
-          <t>Rarity: {0}</t>
+          <t>Kind: {0}</t>
         </is>
       </c>
     </row>
@@ -34668,17 +34668,17 @@
       <c r="A1903" t="inlineStr"/>
       <c r="B1903" t="inlineStr">
         <is>
-          <t>fwlib.detail.numbers</t>
+          <t>fwlib.detail.category</t>
         </is>
       </c>
       <c r="C1903" t="inlineStr">
         <is>
-          <t>负载 {0} · 每发耗电 {1} · 每发积热 {2}</t>
+          <t>类别：{0}</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
         <is>
-          <t>Load {0} · Power per shot {1} · Heat per shot {2}</t>
+          <t>Category: {0}</t>
         </is>
       </c>
     </row>
@@ -34686,17 +34686,17 @@
       <c r="A1904" t="inlineStr"/>
       <c r="B1904" t="inlineStr">
         <is>
-          <t>fwlib.detail.tags</t>
+          <t>fwlib.detail.protocol</t>
         </is>
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>产生的状态标签：{0}</t>
+          <t>协议：{0}</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
         <is>
-          <t>Status tags applied: {0}</t>
+          <t>Protocol: {0}</t>
         </is>
       </c>
     </row>
@@ -34704,17 +34704,17 @@
       <c r="A1905" t="inlineStr"/>
       <c r="B1905" t="inlineStr">
         <is>
-          <t>fwlib.detail.tags_none</t>
+          <t>fwlib.detail.rarity</t>
         </is>
       </c>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>产生的状态标签：无</t>
+          <t>稀有度：{0}</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
         <is>
-          <t>Status tags applied: none</t>
+          <t>Rarity: {0}</t>
         </is>
       </c>
     </row>
@@ -34722,17 +34722,17 @@
       <c r="A1906" t="inlineStr"/>
       <c r="B1906" t="inlineStr">
         <is>
-          <t>fwlib.detail.reactions</t>
+          <t>fwlib.detail.numbers</t>
         </is>
       </c>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>参与的反应：{0}</t>
+          <t>负载 {0} · 每发耗电 {1} · 每发积热 {2}</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
         <is>
-          <t>Reactions it takes part in: {0}</t>
+          <t>Load {0} · Power per shot {1} · Heat per shot {2}</t>
         </is>
       </c>
     </row>
@@ -34740,17 +34740,17 @@
       <c r="A1907" t="inlineStr"/>
       <c r="B1907" t="inlineStr">
         <is>
-          <t>fwlib.detail.reactions_none</t>
+          <t>fwlib.detail.tags</t>
         </is>
       </c>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>参与的反应：无</t>
+          <t>产生的状态标签：{0}</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
         <is>
-          <t>Reactions it takes part in: none</t>
+          <t>Status tags applied: {0}</t>
         </is>
       </c>
     </row>
@@ -34758,17 +34758,17 @@
       <c r="A1908" t="inlineStr"/>
       <c r="B1908" t="inlineStr">
         <is>
-          <t>fwlib.detail.reaction_unknown</t>
+          <t>fwlib.detail.tags_none</t>
         </is>
       </c>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>？？？（尚未发现）</t>
+          <t>产生的状态标签：无</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
         <is>
-          <t>??? (not discovered)</t>
+          <t>Status tags applied: none</t>
         </is>
       </c>
     </row>
@@ -34776,17 +34776,17 @@
       <c r="A1909" t="inlineStr"/>
       <c r="B1909" t="inlineStr">
         <is>
-          <t>fwlib.detail.acquire</t>
+          <t>fwlib.detail.reactions</t>
         </is>
       </c>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>获取途径：{0}</t>
+          <t>参与的反应：{0}</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
         <is>
-          <t>How to get it: {0}</t>
+          <t>Reactions it takes part in: {0}</t>
         </is>
       </c>
     </row>
@@ -34794,17 +34794,17 @@
       <c r="A1910" t="inlineStr"/>
       <c r="B1910" t="inlineStr">
         <is>
-          <t>fwlib.detail.held</t>
+          <t>fwlib.detail.reactions_none</t>
         </is>
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>当前持有 {0} 枚：{1}</t>
+          <t>参与的反应：无</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
         <is>
-          <t>You hold {0}: {1}</t>
+          <t>Reactions it takes part in: none</t>
         </is>
       </c>
     </row>
@@ -34812,17 +34812,17 @@
       <c r="A1911" t="inlineStr"/>
       <c r="B1911" t="inlineStr">
         <is>
-          <t>fwlib.detail.held_none</t>
+          <t>fwlib.detail.reaction_unknown</t>
         </is>
       </c>
       <c r="C1911" t="inlineStr">
         <is>
-          <t>当前持有 0 枚</t>
+          <t>？？？（尚未发现）</t>
         </is>
       </c>
       <c r="D1911" t="inlineStr">
         <is>
-          <t>You hold none</t>
+          <t>??? (not discovered)</t>
         </is>
       </c>
     </row>
@@ -34830,17 +34830,17 @@
       <c r="A1912" t="inlineStr"/>
       <c r="B1912" t="inlineStr">
         <is>
-          <t>fwlib.detail.origin</t>
+          <t>fwlib.detail.acquire</t>
         </is>
       </c>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>这一枚的来源：{0}</t>
+          <t>获取途径：{0}</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
         <is>
-          <t>This chip came from: {0}</t>
+          <t>How to get it: {0}</t>
         </is>
       </c>
     </row>
@@ -34848,17 +34848,17 @@
       <c r="A1913" t="inlineStr"/>
       <c r="B1913" t="inlineStr">
         <is>
-          <t>fwlib.origin.seed</t>
+          <t>fwlib.detail.held</t>
         </is>
       </c>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>开局配发</t>
+          <t>当前持有 {0} 枚：{1}</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
         <is>
-          <t>Starting issue</t>
+          <t>You hold {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -34866,17 +34866,17 @@
       <c r="A1914" t="inlineStr"/>
       <c r="B1914" t="inlineStr">
         <is>
-          <t>fwlib.origin.print</t>
+          <t>fwlib.detail.held_none</t>
         </is>
       </c>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>装配站刻印</t>
+          <t>当前持有 0 枚</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
         <is>
-          <t>Printed at the Assembly Station</t>
+          <t>You hold none</t>
         </is>
       </c>
     </row>
@@ -34884,17 +34884,17 @@
       <c r="A1915" t="inlineStr"/>
       <c r="B1915" t="inlineStr">
         <is>
-          <t>fwlib.origin.salvage</t>
+          <t>fwlib.detail.origin</t>
         </is>
       </c>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>解析战利品</t>
+          <t>这一枚的来源：{0}</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
         <is>
-          <t>Analysed salvage</t>
+          <t>This chip came from: {0}</t>
         </is>
       </c>
     </row>
@@ -34902,17 +34902,17 @@
       <c r="A1916" t="inlineStr"/>
       <c r="B1916" t="inlineStr">
         <is>
-          <t>fwlib.origin.encrypted</t>
+          <t>fwlib.origin.seed</t>
         </is>
       </c>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>带回的敌方加密固件</t>
+          <t>开局配发</t>
         </is>
       </c>
       <c r="D1916" t="inlineStr">
         <is>
-          <t>Recovered enemy-encrypted firmware</t>
+          <t>Starting issue</t>
         </is>
       </c>
     </row>
@@ -34920,17 +34920,17 @@
       <c r="A1917" t="inlineStr"/>
       <c r="B1917" t="inlineStr">
         <is>
-          <t>fwlib.origin.craft</t>
+          <t>fwlib.origin.print</t>
         </is>
       </c>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>电路合成台</t>
+          <t>装配站刻印</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
         <is>
-          <t>Circuit Synthesizer</t>
+          <t>Printed at the Assembly Station</t>
         </is>
       </c>
     </row>
@@ -34938,17 +34938,17 @@
       <c r="A1918" t="inlineStr"/>
       <c r="B1918" t="inlineStr">
         <is>
-          <t>fwlib.origin.unknown</t>
+          <t>fwlib.origin.salvage</t>
         </is>
       </c>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>旧存档（来源未记录）</t>
+          <t>解析战利品</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
         <is>
-          <t>Older save (source not recorded)</t>
+          <t>Analysed salvage</t>
         </is>
       </c>
     </row>
@@ -34956,17 +34956,17 @@
       <c r="A1919" t="inlineStr"/>
       <c r="B1919" t="inlineStr">
         <is>
-          <t>fwlib.detail.route_ok</t>
+          <t>fwlib.origin.encrypted</t>
         </is>
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>取用路线：{0} → 装配站，通畅</t>
+          <t>带回的敌方加密固件</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
         <is>
-          <t>Fetch route: {0} → Assembly Station, clear</t>
+          <t>Recovered enemy-encrypted firmware</t>
         </is>
       </c>
     </row>
@@ -34974,17 +34974,17 @@
       <c r="A1920" t="inlineStr"/>
       <c r="B1920" t="inlineStr">
         <is>
-          <t>fwlib.detail.route_blocked</t>
+          <t>fwlib.origin.craft</t>
         </is>
       </c>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>取用路线：{0} → 装配站被堵住：{1}</t>
+          <t>电路合成台</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
         <is>
-          <t>Fetch route: {0} → Assembly Station is blocked: {1}</t>
+          <t>Circuit Synthesizer</t>
         </is>
       </c>
     </row>
@@ -34992,17 +34992,17 @@
       <c r="A1921" t="inlineStr"/>
       <c r="B1921" t="inlineStr">
         <is>
-          <t>fwlib.detail.route_unknown</t>
+          <t>fwlib.origin.unknown</t>
         </is>
       </c>
       <c r="C1921" t="inlineStr">
         <is>
-          <t>取用路线：家园地形还没载入，暂时无法检查</t>
+          <t>旧存档（来源未记录）</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
         <is>
-          <t>Fetch route: home terrain not loaded yet; cannot check</t>
+          <t>Older save (source not recorded)</t>
         </is>
       </c>
     </row>
@@ -35010,17 +35010,17 @@
       <c r="A1922" t="inlineStr"/>
       <c r="B1922" t="inlineStr">
         <is>
-          <t>fwlib.route.storage_enclosed</t>
+          <t>fwlib.detail.route_ok</t>
         </is>
       </c>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>{0} 四周被 {1} 围住</t>
+          <t>取用路线：{0} → 装配站，通畅</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
         <is>
-          <t>{0} is walled in by {1}</t>
+          <t>Fetch route: {0} → Assembly Station, clear</t>
         </is>
       </c>
     </row>
@@ -35028,17 +35028,17 @@
       <c r="A1923" t="inlineStr"/>
       <c r="B1923" t="inlineStr">
         <is>
-          <t>fwlib.route.station_enclosed</t>
+          <t>fwlib.detail.route_blocked</t>
         </is>
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>装配站四周被 {0} 围住</t>
+          <t>取用路线：{0} → 装配站被堵住：{1}</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
         <is>
-          <t>the Assembly Station is walled in by {0}</t>
+          <t>Fetch route: {0} → Assembly Station is blocked: {1}</t>
         </is>
       </c>
     </row>
@@ -35046,17 +35046,17 @@
       <c r="A1924" t="inlineStr"/>
       <c r="B1924" t="inlineStr">
         <is>
-          <t>fwlib.route.disconnected</t>
+          <t>fwlib.detail.route_unknown</t>
         </is>
       </c>
       <c r="C1924" t="inlineStr">
         <is>
-          <t>两处之间没有能走通的路（被建筑或地形隔断）</t>
+          <t>取用路线：家园地形还没载入，暂时无法检查</t>
         </is>
       </c>
       <c r="D1924" t="inlineStr">
         <is>
-          <t>there is no walkable path between them (cut off by buildings or terrain)</t>
+          <t>Fetch route: home terrain not loaded yet; cannot check</t>
         </is>
       </c>
     </row>
@@ -35064,17 +35064,17 @@
       <c r="A1925" t="inlineStr"/>
       <c r="B1925" t="inlineStr">
         <is>
-          <t>fwlib.route.no_station</t>
+          <t>fwlib.route.storage_enclosed</t>
         </is>
       </c>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>家园还没有装配站</t>
+          <t>{0} 四周被 {1} 围住</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
         <is>
-          <t>the home has no Assembly Station yet</t>
+          <t>{0} is walled in by {1}</t>
         </is>
       </c>
     </row>
@@ -35082,17 +35082,17 @@
       <c r="A1926" t="inlineStr"/>
       <c r="B1926" t="inlineStr">
         <is>
-          <t>fwlib.route.terrain</t>
+          <t>fwlib.route.station_enclosed</t>
         </is>
       </c>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>地形</t>
+          <t>装配站四周被 {0} 围住</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>the Assembly Station is walled in by {0}</t>
         </is>
       </c>
     </row>
@@ -35100,17 +35100,17 @@
       <c r="A1927" t="inlineStr"/>
       <c r="B1927" t="inlineStr">
         <is>
-          <t>fwlib.storage.core</t>
+          <t>fwlib.route.disconnected</t>
         </is>
       </c>
       <c r="C1927" t="inlineStr">
         <is>
-          <t>归还核心应急库</t>
+          <t>两处之间没有能走通的路（被建筑或地形隔断）</t>
         </is>
       </c>
       <c r="D1927" t="inlineStr">
         <is>
-          <t>Core emergency cache</t>
+          <t>there is no walkable path between them (cut off by buildings or terrain)</t>
         </is>
       </c>
     </row>
@@ -35118,17 +35118,17 @@
       <c r="A1928" t="inlineStr"/>
       <c r="B1928" t="inlineStr">
         <is>
-          <t>fwlib.footer</t>
+          <t>fwlib.route.no_station</t>
         </is>
       </c>
       <c r="C1928" t="inlineStr">
         <is>
-          <t>悬停固件按 {act:OpenCodex} 查看图鉴 · 按 {act:OpenFirmware} 或 {act:Cancel} 关闭</t>
+          <t>家园还没有装配站</t>
         </is>
       </c>
       <c r="D1928" t="inlineStr">
         <is>
-          <t>Hover a firmware and press {act:OpenCodex} for its codex entry · Press {act:OpenFirmware} or {act:Cancel} to close</t>
+          <t>the home has no Assembly Station yet</t>
         </is>
       </c>
     </row>
@@ -35136,17 +35136,17 @@
       <c r="A1929" t="inlineStr"/>
       <c r="B1929" t="inlineStr">
         <is>
-          <t>fwlib.readings_title</t>
+          <t>fwlib.route.terrain</t>
         </is>
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>各载体读法</t>
+          <t>地形</t>
         </is>
       </c>
       <c r="D1929" t="inlineStr">
         <is>
-          <t>Readings by carrier</t>
+          <t>terrain</t>
         </is>
       </c>
     </row>
@@ -35154,17 +35154,17 @@
       <c r="A1930" t="inlineStr"/>
       <c r="B1930" t="inlineStr">
         <is>
-          <t>pause.firmware</t>
+          <t>fwlib.storage.core</t>
         </is>
       </c>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>固件库</t>
+          <t>归还核心应急库</t>
         </is>
       </c>
       <c r="D1930" t="inlineStr">
         <is>
-          <t>Firmware library</t>
+          <t>Core emergency cache</t>
         </is>
       </c>
     </row>
@@ -35172,17 +35172,17 @@
       <c r="A1931" t="inlineStr"/>
       <c r="B1931" t="inlineStr">
         <is>
-          <t>codex.tab.system</t>
+          <t>fwlib.footer</t>
         </is>
       </c>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>系统说明</t>
+          <t>悬停固件按 {act:OpenCodex} 查看图鉴 · 按 {act:OpenFirmware} 或 {act:Cancel} 关闭</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
         <is>
-          <t>Systems</t>
+          <t>Hover a firmware and press {act:OpenCodex} for its codex entry · Press {act:OpenFirmware} or {act:Cancel} to close</t>
         </is>
       </c>
     </row>
@@ -35190,17 +35190,17 @@
       <c r="A1932" t="inlineStr"/>
       <c r="B1932" t="inlineStr">
         <is>
-          <t>codex.tab.firmware</t>
+          <t>fwlib.readings_title</t>
         </is>
       </c>
       <c r="C1932" t="inlineStr">
         <is>
-          <t>固件</t>
+          <t>各载体读法</t>
         </is>
       </c>
       <c r="D1932" t="inlineStr">
         <is>
-          <t>Firmware</t>
+          <t>Readings by carrier</t>
         </is>
       </c>
     </row>
@@ -35208,17 +35208,17 @@
       <c r="A1933" t="inlineStr"/>
       <c r="B1933" t="inlineStr">
         <is>
-          <t>codex.tab.reaction</t>
+          <t>pause.firmware</t>
         </is>
       </c>
       <c r="C1933" t="inlineStr">
         <is>
-          <t>反应</t>
+          <t>固件库</t>
         </is>
       </c>
       <c r="D1933" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Firmware library</t>
         </is>
       </c>
     </row>
@@ -35226,17 +35226,17 @@
       <c r="A1934" t="inlineStr"/>
       <c r="B1934" t="inlineStr">
         <is>
-          <t>codex.panel.search</t>
+          <t>codex.tab.system</t>
         </is>
       </c>
       <c r="C1934" t="inlineStr">
         <is>
-          <t>搜索条目</t>
+          <t>系统说明</t>
         </is>
       </c>
       <c r="D1934" t="inlineStr">
         <is>
-          <t>Search entries</t>
+          <t>Systems</t>
         </is>
       </c>
     </row>
@@ -35244,17 +35244,17 @@
       <c r="A1935" t="inlineStr"/>
       <c r="B1935" t="inlineStr">
         <is>
-          <t>codex.panel.no_match</t>
+          <t>codex.tab.firmware</t>
         </is>
       </c>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>没有符合搜索的条目。</t>
+          <t>固件</t>
         </is>
       </c>
       <c r="D1935" t="inlineStr">
         <is>
-          <t>No entries match the search.</t>
+          <t>Firmware</t>
         </is>
       </c>
     </row>
@@ -35262,17 +35262,17 @@
       <c r="A1936" t="inlineStr"/>
       <c r="B1936" t="inlineStr">
         <is>
-          <t>codex.firmware.locked_body</t>
+          <t>codex.tab.reaction</t>
         </is>
       </c>
       <c r="C1936" t="inlineStr">
         <is>
-          <t>尚未获得。获取途径：{0}</t>
+          <t>反应</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
         <is>
-          <t>Not obtained yet. How to get it: {0}</t>
+          <t>Reactions</t>
         </is>
       </c>
     </row>
@@ -35280,17 +35280,17 @@
       <c r="A1937" t="inlineStr"/>
       <c r="B1937" t="inlineStr">
         <is>
-          <t>codex.reaction.recipe</t>
+          <t>codex.panel.search</t>
         </is>
       </c>
       <c r="C1937" t="inlineStr">
         <is>
-          <t>配料：{0} + {1}</t>
+          <t>搜索条目</t>
         </is>
       </c>
       <c r="D1937" t="inlineStr">
         <is>
-          <t>Ingredients: {0} + {1}</t>
+          <t>Search entries</t>
         </is>
       </c>
     </row>
@@ -35298,17 +35298,17 @@
       <c r="A1938" t="inlineStr"/>
       <c r="B1938" t="inlineStr">
         <is>
-          <t>codex.reaction.recipe_assembly</t>
+          <t>codex.panel.no_match</t>
         </is>
       </c>
       <c r="C1938" t="inlineStr">
         <is>
-          <t>由装配识别：带上 {0}</t>
+          <t>没有符合搜索的条目。</t>
         </is>
       </c>
       <c r="D1938" t="inlineStr">
         <is>
-          <t>Recognised from the loadout: carry {0}</t>
+          <t>No entries match the search.</t>
         </is>
       </c>
     </row>
@@ -35316,17 +35316,17 @@
       <c r="A1939" t="inlineStr"/>
       <c r="B1939" t="inlineStr">
         <is>
-          <t>codex.reaction.firmware</t>
+          <t>codex.firmware.locked_body</t>
         </is>
       </c>
       <c r="C1939" t="inlineStr">
         <is>
-          <t>能提供配料的固件：{0}</t>
+          <t>尚未获得。获取途径：{0}</t>
         </is>
       </c>
       <c r="D1939" t="inlineStr">
         <is>
-          <t>Firmware that supplies an ingredient: {0}</t>
+          <t>Not obtained yet. How to get it: {0}</t>
         </is>
       </c>
     </row>
@@ -35334,17 +35334,17 @@
       <c r="A1940" t="inlineStr"/>
       <c r="B1940" t="inlineStr">
         <is>
-          <t>codex.reaction.elsewhere</t>
+          <t>codex.reaction.recipe</t>
         </is>
       </c>
       <c r="C1940" t="inlineStr">
         <is>
-          <t>本存档还没有打出过（在其他存档里发现）</t>
+          <t>配料：{0} + {1}</t>
         </is>
       </c>
       <c r="D1940" t="inlineStr">
         <is>
-          <t>Not triggered in this save yet (discovered in another save)</t>
+          <t>Ingredients: {0} + {1}</t>
         </is>
       </c>
     </row>
@@ -35352,17 +35352,431 @@
       <c r="A1941" t="inlineStr"/>
       <c r="B1941" t="inlineStr">
         <is>
+          <t>codex.reaction.recipe_assembly</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>由装配识别：带上 {0}</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>Recognised from the loadout: carry {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr"/>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>codex.reaction.firmware</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>能提供配料的固件：{0}</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>Firmware that supplies an ingredient: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr"/>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>codex.reaction.elsewhere</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>本存档还没有打出过（在其他存档里发现）</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>Not triggered in this save yet (discovered in another save)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr"/>
+      <c r="B1944" t="inlineStr">
+        <is>
           <t>ui.common.codex_jump</t>
         </is>
       </c>
-      <c r="C1941" t="inlineStr">
+      <c r="C1944" t="inlineStr">
         <is>
           <t>按 {0} 查看图鉴：{1}</t>
         </is>
       </c>
-      <c r="D1941" t="inlineStr">
+      <c r="D1944" t="inlineStr">
         <is>
           <t>Press {0} for the codex: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr"/>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>analysis.restore.title</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>数据复原</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>Data restoration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr"/>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>analysis.restore.hint</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>花技术数据复原一条固件的刻录数据：复原后视为已破解，可在信号核刻印芯片、在蓝图固件槽里选用。正式掉落上线前的过渡渠道。</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>Spend tech data to restore a firmware's print data: it counts as cracked, can be printed at the Signal Core and chosen in blueprint firmware slots. An interim channel until regular drops arrive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr"/>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>analysis.restore.choice</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>{0}｜{1} 技术数据</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>{0} | {1} tech data</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr"/>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>analysis.restore.detail.kind</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>类别：{0} · 稀有度：{1}</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>Category: {0} · Rarity: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr"/>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>analysis.restore.button</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>复原</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>Restore</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr"/>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>analysis.restore.empty</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>能复原的固件都已获得</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>Every restorable firmware is already obtained</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr"/>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>analysis.restore.detail.source</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>正式来源：{0}</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>Regular source: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr"/>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>analysis.restore.detail.tags</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>产生的标签：{0}</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>Tags applied: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr"/>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>analysis.restore.detail.reactions</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>参与的具名反应：{0}</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>Named reactions: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr"/>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>analysis.restore.none_value</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr"/>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>analysis.restore.tech</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>现有技术数据 {0}</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>Tech data on hand: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr"/>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>analysis.restore.confirm.title</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>数据复原</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>Restore firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr"/>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>analysis.restore.confirm.body</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>花费 {0} 技术数据复原“{1}”？（现有 {2}，复原后不可撤销）</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>Spend {0} tech data to restore "{1}"? (You have {2}; this cannot be undone.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr"/>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>analysis.restore.confirm.ok</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>复原</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>Restore</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr"/>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>analysis.restore.ok</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>已复原“{0}”：可在信号核刻印、在蓝图里选用（技术数据 −{1}）</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>Restored "{0}": print it at the Signal Core or pick it in a blueprint (tech data −{1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr"/>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>analysis.restore.reason.already</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>“{0}”已经获得，不需要复原</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>"{0}" is already obtained; no need to restore it</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr"/>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>analysis.restore.reason.not_restorable</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>“{0}”不能在这里复原：{1}</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>"{0}" cannot be restored here: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr"/>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>analysis.restore.reason.no_power</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>解析台未完工或没有电，不能复原</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>The Analysis Bench is unfinished or unpowered; cannot restore</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr"/>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>analysis.restore.reason.no_tech</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>技术数据不足：复原“{0}”需要 {1}，现有 {2}。带回模块在解析台解析可以获得技术数据</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>Not enough tech data: restoring "{0}" needs {1}, you have {2}. Analyse recovered modules at the Analysis Bench to earn tech data</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr"/>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>analysis.restore.reason.none_selected</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>先在下拉里选一条固件</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>Pick a firmware in the list first</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3074"/>
+  <dimension ref="A1:D3193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55760,6 +55760,2148 @@
         </is>
       </c>
     </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr"/>
+      <c r="B3075" t="inlineStr">
+        <is>
+          <t>building.recycler.name</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>回收站</t>
+        </is>
+      </c>
+      <c r="D3075" t="inlineStr">
+        <is>
+          <t>Recycler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr"/>
+      <c r="B3076" t="inlineStr">
+        <is>
+          <t>building.extraction_drill.name</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>提取钻</t>
+        </is>
+      </c>
+      <c r="D3076" t="inlineStr">
+        <is>
+          <t>Extraction Drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr"/>
+      <c r="B3077" t="inlineStr">
+        <is>
+          <t>building.waste_pond.name</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>废液池</t>
+        </is>
+      </c>
+      <c r="D3077" t="inlineStr">
+        <is>
+          <t>Waste Pond</t>
+        </is>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr"/>
+      <c r="B3078" t="inlineStr">
+        <is>
+          <t>building.fluid_pump.name</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>流体泵</t>
+        </is>
+      </c>
+      <c r="D3078" t="inlineStr">
+        <is>
+          <t>Fluid Pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr"/>
+      <c r="B3079" t="inlineStr">
+        <is>
+          <t>building.recycler.desc</t>
+        </is>
+      </c>
+      <c r="C3079" t="inlineStr">
+        <is>
+          <t>放在废墟上持续拆解，产出废料：废墟有储量，一格拆完就变成可以建造的空地（收复土地的另一种方式）。也接收传送带送来的任何固体，分解成废料（分解得到的废料少于做它花掉的），所以废墟拆完后仍然有用。输入口在西、输出口在东（随朝向转），产出从输出口推上传送带。耗电 6。</t>
+        </is>
+      </c>
+      <c r="D3079" t="inlineStr">
+        <is>
+          <t>Placed on ruins, it keeps dismantling them into scrap. Ruins hold a limited amount: each tile, once stripped, becomes buildable ground (another way to reclaim land). It also takes any solid delivered by belt and breaks it down into scrap (always less scrap than it took to make), so it stays useful after the ruins run out. Input on the west, output on the east (turning with the building); output is pushed onto a belt. Uses 6 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr"/>
+      <c r="B3080" t="inlineStr">
+        <is>
+          <t>building.extraction_drill.desc</t>
+        </is>
+      </c>
+      <c r="C3080" t="inlineStr">
+        <is>
+          <t>放在金属或稀土矿脉上持续采矿：家园的矿脉不会采完。每 2 秒出 1 份矿（脚下哪种矿脉格多就采哪种），从东侧输出口推上传送带。工作时会让家园的震动值上升（震动过高会引来掘进蠕虫）。耗电 6。</t>
+        </is>
+      </c>
+      <c r="D3080" t="inlineStr">
+        <is>
+          <t>Placed on a metal or rare earth vein, it mines continuously; home veins never run out. One ore every 2 s (whichever vein covers more of its tiles), pushed onto a belt from its east output. While working it raises the home's vibration (too much attracts burrowing worms). Uses 6 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr"/>
+      <c r="B3081" t="inlineStr">
+        <is>
+          <t>building.refinery_furnace.desc</t>
+        </is>
+      </c>
+      <c r="C3081" t="inlineStr">
+        <is>
+          <t>冶炼合金：可选“合金（矿）”（2 金属矿 → 1 合金，4 秒）或“合金（废料）”（4 废料 → 1 合金，6 秒）。没选配方时待机、输入口不收东西。西侧输入、东侧输出。耗电 10。</t>
+        </is>
+      </c>
+      <c r="D3081" t="inlineStr">
+        <is>
+          <t>Smelts alloy: choose Alloy (ore) (2 metal ore → 1 alloy, 4 s) or Alloy (scrap) (4 scrap → 1 alloy, 6 s). With no recipe chosen it stands by and its input takes nothing. Input west, output east. Uses 10 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr"/>
+      <c r="B3082" t="inlineStr">
+        <is>
+          <t>building.refinery_tower.desc</t>
+        </is>
+      </c>
+      <c r="C3082" t="inlineStr">
+        <is>
+          <t>原油 100 升 → 燃油 60 升 + 酸液 20 升（副产品），5 秒。原油从南口进，燃油从北口出，酸液从东口出。酸液必须有去处（废液池、或用酸液的建筑），否则精炼塔会堵住。耗电 15。</t>
+        </is>
+      </c>
+      <c r="D3082" t="inlineStr">
+        <is>
+          <t>100 L crude oil → 60 L fuel + 20 L acid (byproduct) in 5 s. Crude enters from the south port, fuel leaves north, acid leaves east. The acid must have somewhere to go (a waste pond or a building that uses it), or the tower stalls. Uses 15 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr"/>
+      <c r="B3083" t="inlineStr">
+        <is>
+          <t>building.blending_station.desc</t>
+        </is>
+      </c>
+      <c r="C3083" t="inlineStr">
+        <is>
+          <t>水 100 升 + 稀土矿 1 → 冷却液 100 升，4 秒。水从南口进，稀土矿从西侧输入口进，冷却液从东口出。耗电 8。</t>
+        </is>
+      </c>
+      <c r="D3083" t="inlineStr">
+        <is>
+          <t>100 L water + 1 rare earth ore → 100 L coolant in 4 s. Water enters from the south port, rare earth ore from the west input, coolant leaves east. Uses 8 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr"/>
+      <c r="B3084" t="inlineStr">
+        <is>
+          <t>building.waste_pond.desc</t>
+        </is>
+      </c>
+      <c r="C3084" t="inlineStr">
+        <is>
+          <t>缓慢销毁送来的任何流体（120 升/分钟），防止副产品堵住产线。西口接管线；销毁的流体不返还。耗电 4。</t>
+        </is>
+      </c>
+      <c r="D3084" t="inlineStr">
+        <is>
+          <t>Slowly destroys any fluid sent to it (120 L/min) so byproducts never stall a line. Connect a pipe to its west port; destroyed fluid is gone for good. Uses 4 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr"/>
+      <c r="B3085" t="inlineStr">
+        <is>
+          <t>building.fluid_pump.desc</t>
+        </is>
+      </c>
+      <c r="C3085" t="inlineStr">
+        <is>
+          <t>放在水源或油井上抽取流体：压在水源上抽水、压在油井上抽原油（哪种格多抽哪种），每分钟 600 升，从东口（随朝向转）推进口外那一格的管线。下游用不完、储罐也满了时停抽，流体留在地下。耗电 5。比物流页签的一格泵快一倍。</t>
+        </is>
+      </c>
+      <c r="D3085" t="inlineStr">
+        <is>
+          <t>Placed on water or an oil well, it pumps fluid: water from water tiles, crude oil from oil wells (whichever covers more of its tiles), 600 L per minute, pushed into the pipe just outside its east port (turning with the building). When nothing downstream takes it and tanks are full it stops, leaving the fluid in the ground. Uses 5 power. Twice as fast as the single-tile pump in the logistics tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr"/>
+      <c r="B3086" t="inlineStr">
+        <is>
+          <t>prod.place.recycler</t>
+        </is>
+      </c>
+      <c r="C3086" t="inlineStr">
+        <is>
+          <t>回收站要压在废墟上：它拆的就是脚下的废墟（压到的废墟格越多，储量越多）</t>
+        </is>
+      </c>
+      <c r="D3086" t="inlineStr">
+        <is>
+          <t>A recycler must sit on ruins: it dismantles the ruins beneath it (the more ruin tiles it covers, the more scrap they hold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr"/>
+      <c r="B3087" t="inlineStr">
+        <is>
+          <t>prod.place.drill</t>
+        </is>
+      </c>
+      <c r="C3087" t="inlineStr">
+        <is>
+          <t>提取钻要压在金属或稀土矿脉上：它从脚下的矿脉采矿</t>
+        </is>
+      </c>
+      <c r="D3087" t="inlineStr">
+        <is>
+          <t>An extraction drill must sit on a metal or rare earth vein: it mines the vein beneath it</t>
+        </is>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr"/>
+      <c r="B3088" t="inlineStr">
+        <is>
+          <t>prod.place.pump</t>
+        </is>
+      </c>
+      <c r="C3088" t="inlineStr">
+        <is>
+          <t>流体泵要压在水源或油井上：它抽的就是脚下流体源的流体</t>
+        </is>
+      </c>
+      <c r="D3088" t="inlineStr">
+        <is>
+          <t>A fluid pump must sit on water or an oil well: it pumps the fluid source beneath it</t>
+        </is>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr"/>
+      <c r="B3089" t="inlineStr">
+        <is>
+          <t>prod.place.any</t>
+        </is>
+      </c>
+      <c r="C3089" t="inlineStr">
+        <is>
+          <t>可以放在任何可建的地方</t>
+        </is>
+      </c>
+      <c r="D3089" t="inlineStr">
+        <is>
+          <t>Can be placed on any buildable ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr"/>
+      <c r="B3090" t="inlineStr">
+        <is>
+          <t>grid.reason.needs_terrain_why</t>
+        </is>
+      </c>
+      <c r="C3090" t="inlineStr">
+        <is>
+          <t>需要放在{0}上：{1}</t>
+        </is>
+      </c>
+      <c r="D3090" t="inlineStr">
+        <is>
+          <t>Must be placed on {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr"/>
+      <c r="B3091" t="inlineStr">
+        <is>
+          <t>grid.terrain.or</t>
+        </is>
+      </c>
+      <c r="C3091" t="inlineStr">
+        <is>
+          <t>或</t>
+        </is>
+      </c>
+      <c r="D3091" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> or </t>
+        </is>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr"/>
+      <c r="B3092" t="inlineStr">
+        <is>
+          <t>prod.preview.ruin</t>
+        </is>
+      </c>
+      <c r="C3092" t="inlineStr">
+        <is>
+          <t>脚下废墟 {0} 格，储量 {1} 废料（每格 {2}）</t>
+        </is>
+      </c>
+      <c r="D3092" t="inlineStr">
+        <is>
+          <t>{0} ruin tile(s) underneath holding {1} scrap ({2} each)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr"/>
+      <c r="B3093" t="inlineStr">
+        <is>
+          <t>prod.preview.vein</t>
+        </is>
+      </c>
+      <c r="C3093" t="inlineStr">
+        <is>
+          <t>脚下{0} {1} 格：产出{2}（矿脉不会采完）</t>
+        </is>
+      </c>
+      <c r="D3093" t="inlineStr">
+        <is>
+          <t>{1} tile(s) of {0} underneath: produces {2} (the vein never runs out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr"/>
+      <c r="B3094" t="inlineStr">
+        <is>
+          <t>prod.preview.source</t>
+        </is>
+      </c>
+      <c r="C3094" t="inlineStr">
+        <is>
+          <t>脚下{0} {1} 格：抽{2}，每分钟 {3} 升（流体源不会抽干）</t>
+        </is>
+      </c>
+      <c r="D3094" t="inlineStr">
+        <is>
+          <t>{1} tile(s) of {0} underneath: pumps {2} at {3} L/min (the source never runs dry)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr"/>
+      <c r="B3095" t="inlineStr">
+        <is>
+          <t>prod.state.working</t>
+        </is>
+      </c>
+      <c r="C3095" t="inlineStr">
+        <is>
+          <t>● 工作中</t>
+        </is>
+      </c>
+      <c r="D3095" t="inlineStr">
+        <is>
+          <t>● Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr"/>
+      <c r="B3096" t="inlineStr">
+        <is>
+          <t>prod.state.idle</t>
+        </is>
+      </c>
+      <c r="C3096" t="inlineStr">
+        <is>
+          <t>○ 待机</t>
+        </is>
+      </c>
+      <c r="D3096" t="inlineStr">
+        <is>
+          <t>○ Standing by</t>
+        </is>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr"/>
+      <c r="B3097" t="inlineStr">
+        <is>
+          <t>prod.state.missing_input</t>
+        </is>
+      </c>
+      <c r="C3097" t="inlineStr">
+        <is>
+          <t>△ 缺料</t>
+        </is>
+      </c>
+      <c r="D3097" t="inlineStr">
+        <is>
+          <t>△ Missing input</t>
+        </is>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr"/>
+      <c r="B3098" t="inlineStr">
+        <is>
+          <t>prod.state.missing_fluid</t>
+        </is>
+      </c>
+      <c r="C3098" t="inlineStr">
+        <is>
+          <t>▽ 缺流体</t>
+        </is>
+      </c>
+      <c r="D3098" t="inlineStr">
+        <is>
+          <t>▽ Missing fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr"/>
+      <c r="B3099" t="inlineStr">
+        <is>
+          <t>prod.state.no_power</t>
+        </is>
+      </c>
+      <c r="C3099" t="inlineStr">
+        <is>
+          <t>◇ 缺电</t>
+        </is>
+      </c>
+      <c r="D3099" t="inlineStr">
+        <is>
+          <t>◇ No power</t>
+        </is>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr"/>
+      <c r="B3100" t="inlineStr">
+        <is>
+          <t>prod.state.output_blocked</t>
+        </is>
+      </c>
+      <c r="C3100" t="inlineStr">
+        <is>
+          <t>■ 输出堵塞</t>
+        </is>
+      </c>
+      <c r="D3100" t="inlineStr">
+        <is>
+          <t>■ Output blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr"/>
+      <c r="B3101" t="inlineStr">
+        <is>
+          <t>prod.state.building</t>
+        </is>
+      </c>
+      <c r="C3101" t="inlineStr">
+        <is>
+          <t>□ 建造中</t>
+        </is>
+      </c>
+      <c r="D3101" t="inlineStr">
+        <is>
+          <t>□ Under construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr"/>
+      <c r="B3102" t="inlineStr">
+        <is>
+          <t>prod.state.damaged</t>
+        </is>
+      </c>
+      <c r="C3102" t="inlineStr">
+        <is>
+          <t>× 损坏</t>
+        </is>
+      </c>
+      <c r="D3102" t="inlineStr">
+        <is>
+          <t>× Damaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr"/>
+      <c r="B3103" t="inlineStr">
+        <is>
+          <t>prod.state.disabled</t>
+        </is>
+      </c>
+      <c r="C3103" t="inlineStr">
+        <is>
+          <t>‖ 已关停</t>
+        </is>
+      </c>
+      <c r="D3103" t="inlineStr">
+        <is>
+          <t>‖ Switched off</t>
+        </is>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr"/>
+      <c r="B3104" t="inlineStr">
+        <is>
+          <t>prod.state.no_resource</t>
+        </is>
+      </c>
+      <c r="C3104" t="inlineStr">
+        <is>
+          <t>× 不在资源点上</t>
+        </is>
+      </c>
+      <c r="D3104" t="inlineStr">
+        <is>
+          <t>× Not on a resource</t>
+        </is>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr"/>
+      <c r="B3105" t="inlineStr">
+        <is>
+          <t>prod.reason.no_recipe</t>
+        </is>
+      </c>
+      <c r="C3105" t="inlineStr">
+        <is>
+          <t>没选配方：在面板里选一个配方后开工（没选时输入口不收东西）</t>
+        </is>
+      </c>
+      <c r="D3105" t="inlineStr">
+        <is>
+          <t>No recipe chosen: pick one in the panel to start (the input takes nothing until then)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr"/>
+      <c r="B3106" t="inlineStr">
+        <is>
+          <t>prod.reason.working_recipe</t>
+        </is>
+      </c>
+      <c r="C3106" t="inlineStr">
+        <is>
+          <t>正在生产：{0}</t>
+        </is>
+      </c>
+      <c r="D3106" t="inlineStr">
+        <is>
+          <t>Producing: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr"/>
+      <c r="B3107" t="inlineStr">
+        <is>
+          <t>prod.reason.working_ruin</t>
+        </is>
+      </c>
+      <c r="C3107" t="inlineStr">
+        <is>
+          <t>正在拆脚下的废墟（剩 {0} 废料）</t>
+        </is>
+      </c>
+      <c r="D3107" t="inlineStr">
+        <is>
+          <t>Dismantling the ruins beneath (scrap left: {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr"/>
+      <c r="B3108" t="inlineStr">
+        <is>
+          <t>prod.reason.working_item</t>
+        </is>
+      </c>
+      <c r="C3108" t="inlineStr">
+        <is>
+          <t>正在分解送来的{0}（得到 {1} 废料）</t>
+        </is>
+      </c>
+      <c r="D3108" t="inlineStr">
+        <is>
+          <t>Breaking down a delivered {0} (yields {1} scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr"/>
+      <c r="B3109" t="inlineStr">
+        <is>
+          <t>prod.reason.working_drill</t>
+        </is>
+      </c>
+      <c r="C3109" t="inlineStr">
+        <is>
+          <t>正在采{0}</t>
+        </is>
+      </c>
+      <c r="D3109" t="inlineStr">
+        <is>
+          <t>Mining {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr"/>
+      <c r="B3110" t="inlineStr">
+        <is>
+          <t>prod.reason.working_waste</t>
+        </is>
+      </c>
+      <c r="C3110" t="inlineStr">
+        <is>
+          <t>正在销毁{0}（{1} 升/分钟）</t>
+        </is>
+      </c>
+      <c r="D3110" t="inlineStr">
+        <is>
+          <t>Destroying {0} ({1} L/min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr"/>
+      <c r="B3111" t="inlineStr">
+        <is>
+          <t>prod.reason.ruin_depleted</t>
+        </is>
+      </c>
+      <c r="C3111" t="inlineStr">
+        <is>
+          <t>脚下的废墟已经拆完，等传送带把要分解的固体送到西侧输入口</t>
+        </is>
+      </c>
+      <c r="D3111" t="inlineStr">
+        <is>
+          <t>The ruins beneath are stripped; waiting for solids to be belted into the west input</t>
+        </is>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr"/>
+      <c r="B3112" t="inlineStr">
+        <is>
+          <t>prod.reason.no_vein</t>
+        </is>
+      </c>
+      <c r="C3112" t="inlineStr">
+        <is>
+          <t>脚下没有矿脉：提取钻要压在金属或稀土矿脉上</t>
+        </is>
+      </c>
+      <c r="D3112" t="inlineStr">
+        <is>
+          <t>No vein underneath: an extraction drill must sit on a metal or rare earth vein</t>
+        </is>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr"/>
+      <c r="B3113" t="inlineStr">
+        <is>
+          <t>prod.reason.no_power</t>
+        </is>
+      </c>
+      <c r="C3113" t="inlineStr">
+        <is>
+          <t>没有电：{0}</t>
+        </is>
+      </c>
+      <c r="D3113" t="inlineStr">
+        <is>
+          <t>No power: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr"/>
+      <c r="B3114" t="inlineStr">
+        <is>
+          <t>prod.reason.power_unconnected</t>
+        </is>
+      </c>
+      <c r="C3114" t="inlineStr">
+        <is>
+          <t>不在任何电塔的覆盖里</t>
+        </is>
+      </c>
+      <c r="D3114" t="inlineStr">
+        <is>
+          <t>not inside any power pole's coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr"/>
+      <c r="B3115" t="inlineStr">
+        <is>
+          <t>prod.reason.power_brownout</t>
+        </is>
+      </c>
+      <c r="C3115" t="inlineStr">
+        <is>
+          <t>电网供电不足，按优先级 {0} 停机</t>
+        </is>
+      </c>
+      <c r="D3115" t="inlineStr">
+        <is>
+          <t>the grid is short and switched it off at priority {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr"/>
+      <c r="B3116" t="inlineStr">
+        <is>
+          <t>prod.reason.damaged</t>
+        </is>
+      </c>
+      <c r="C3116" t="inlineStr">
+        <is>
+          <t>受损了：修好后自动恢复</t>
+        </is>
+      </c>
+      <c r="D3116" t="inlineStr">
+        <is>
+          <t>Damaged: it resumes once repaired</t>
+        </is>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr"/>
+      <c r="B3117" t="inlineStr">
+        <is>
+          <t>prod.reason.building</t>
+        </is>
+      </c>
+      <c r="C3117" t="inlineStr">
+        <is>
+          <t>还没建成：机器施工完成后开工</t>
+        </is>
+      </c>
+      <c r="D3117" t="inlineStr">
+        <is>
+          <t>Not built yet: it starts once machines finish building it</t>
+        </is>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr"/>
+      <c r="B3118" t="inlineStr">
+        <is>
+          <t>prod.reason.disabled</t>
+        </is>
+      </c>
+      <c r="C3118" t="inlineStr">
+        <is>
+          <t>被关停了：重新启用后恢复</t>
+        </is>
+      </c>
+      <c r="D3118" t="inlineStr">
+        <is>
+          <t>Switched off: it resumes once re-enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr"/>
+      <c r="B3119" t="inlineStr">
+        <is>
+          <t>prod.reason.in_port_unconnected</t>
+        </is>
+      </c>
+      <c r="C3119" t="inlineStr">
+        <is>
+          <t>西侧输入口没接传送带：在（{0}, {1}）铺一格朝向建筑的传送带，把{2}送进来</t>
+        </is>
+      </c>
+      <c r="D3119" t="inlineStr">
+        <is>
+          <t>The west input has no belt: lay a belt at ({0}, {1}) pointing at the building to bring in {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr"/>
+      <c r="B3120" t="inlineStr">
+        <is>
+          <t>prod.reason.in_port_empty</t>
+        </is>
+      </c>
+      <c r="C3120" t="inlineStr">
+        <is>
+          <t>输入口的传送带上没有{0}送来</t>
+        </is>
+      </c>
+      <c r="D3120" t="inlineStr">
+        <is>
+          <t>No {0} is arriving on the input belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr"/>
+      <c r="B3121" t="inlineStr">
+        <is>
+          <t>prod.reason.out_port_unconnected</t>
+        </is>
+      </c>
+      <c r="C3121" t="inlineStr">
+        <is>
+          <t>输出口没接传送带：在（{0}, {1}）铺一格背离建筑的传送带</t>
+        </is>
+      </c>
+      <c r="D3121" t="inlineStr">
+        <is>
+          <t>The output has no belt: lay a belt at ({0}, {1}) leading away from the building</t>
+        </is>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr"/>
+      <c r="B3122" t="inlineStr">
+        <is>
+          <t>prod.reason.out_port_blocked</t>
+        </is>
+      </c>
+      <c r="C3122" t="inlineStr">
+        <is>
+          <t>输出口的传送带推不动（下游堵住了）</t>
+        </is>
+      </c>
+      <c r="D3122" t="inlineStr">
+        <is>
+          <t>The output belt is not moving (blocked downstream)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr"/>
+      <c r="B3123" t="inlineStr">
+        <is>
+          <t>prod.reason.fluid_unconnected</t>
+        </is>
+      </c>
+      <c r="C3123" t="inlineStr">
+        <is>
+          <t>{0}口没接管线：在（{1}, {2}）铺一格管线</t>
+        </is>
+      </c>
+      <c r="D3123" t="inlineStr">
+        <is>
+          <t>The {0} port has no pipe: lay a pipe at ({1}, {2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr"/>
+      <c r="B3124" t="inlineStr">
+        <is>
+          <t>prod.reason.fluid_wrong</t>
+        </is>
+      </c>
+      <c r="C3124" t="inlineStr">
+        <is>
+          <t>{0}口接到的网络里是{1}：这个口只收{0}</t>
+        </is>
+      </c>
+      <c r="D3124" t="inlineStr">
+        <is>
+          <t>The {0} port is connected to a network carrying {1}: this port only takes {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr"/>
+      <c r="B3125" t="inlineStr">
+        <is>
+          <t>prod.reason.fluid_no_supply</t>
+        </is>
+      </c>
+      <c r="C3125" t="inlineStr">
+        <is>
+          <t>{0}口接到的网络没有供给（没有泵 / 储罐里没有存量）</t>
+        </is>
+      </c>
+      <c r="D3125" t="inlineStr">
+        <is>
+          <t>The network on the {0} port has no supply (no pump, or its tanks are empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="inlineStr"/>
+      <c r="B3126" t="inlineStr">
+        <is>
+          <t>prod.reason.fluid_out_wrong</t>
+        </is>
+      </c>
+      <c r="C3126" t="inlineStr">
+        <is>
+          <t>{0}出口接到的网络里是{1}：送不出去，换一条只装{0}的管线</t>
+        </is>
+      </c>
+      <c r="D3126" t="inlineStr">
+        <is>
+          <t>The {0} output is connected to a network carrying {1} and cannot deliver; give it a pipe that carries only {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="inlineStr"/>
+      <c r="B3127" t="inlineStr">
+        <is>
+          <t>prod.reason.fluid_out_full</t>
+        </is>
+      </c>
+      <c r="C3127" t="inlineStr">
+        <is>
+          <t>{0}出口的网络没有地方放（没人用、储罐也满了）</t>
+        </is>
+      </c>
+      <c r="D3127" t="inlineStr">
+        <is>
+          <t>The network on the {0} output has nowhere to put it (nothing uses it and its tanks are full)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="inlineStr"/>
+      <c r="B3128" t="inlineStr">
+        <is>
+          <t>prod.reason.waste_idle</t>
+        </is>
+      </c>
+      <c r="C3128" t="inlineStr">
+        <is>
+          <t>进口的网络里没有流体</t>
+        </is>
+      </c>
+      <c r="D3128" t="inlineStr">
+        <is>
+          <t>There is no fluid in the network on its inlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="inlineStr"/>
+      <c r="B3129" t="inlineStr">
+        <is>
+          <t>prod.panel.title</t>
+        </is>
+      </c>
+      <c r="C3129" t="inlineStr">
+        <is>
+          <t>{0}（{1}, {2}）</t>
+        </is>
+      </c>
+      <c r="D3129" t="inlineStr">
+        <is>
+          <t>{0} ({1}, {2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="inlineStr"/>
+      <c r="B3130" t="inlineStr">
+        <is>
+          <t>prod.panel.close</t>
+        </is>
+      </c>
+      <c r="C3130" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="D3130" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="inlineStr"/>
+      <c r="B3131" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe</t>
+        </is>
+      </c>
+      <c r="C3131" t="inlineStr">
+        <is>
+          <t>配方</t>
+        </is>
+      </c>
+      <c r="D3131" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="inlineStr"/>
+      <c r="B3132" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe_none</t>
+        </is>
+      </c>
+      <c r="C3132" t="inlineStr">
+        <is>
+          <t>（不选：待机）</t>
+        </is>
+      </c>
+      <c r="D3132" t="inlineStr">
+        <is>
+          <t>(none: stand by)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="inlineStr"/>
+      <c r="B3133" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe_fixed</t>
+        </is>
+      </c>
+      <c r="C3133" t="inlineStr">
+        <is>
+          <t>配方：{0}（这座建筑的固定功能）</t>
+        </is>
+      </c>
+      <c r="D3133" t="inlineStr">
+        <is>
+          <t>Recipe: {0} (this building's fixed function)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" t="inlineStr"/>
+      <c r="B3134" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe_line</t>
+        </is>
+      </c>
+      <c r="C3134" t="inlineStr">
+        <is>
+          <t>{0}：{1} → {2}（{3} 秒）</t>
+        </is>
+      </c>
+      <c r="D3134" t="inlineStr">
+        <is>
+          <t>{0}: {1} → {2} ({3} s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="inlineStr"/>
+      <c r="B3135" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe_changed</t>
+        </is>
+      </c>
+      <c r="C3135" t="inlineStr">
+        <is>
+          <t>配方改为：{0}</t>
+        </is>
+      </c>
+      <c r="D3135" t="inlineStr">
+        <is>
+          <t>Recipe set to: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="inlineStr"/>
+      <c r="B3136" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe_cleared</t>
+        </is>
+      </c>
+      <c r="C3136" t="inlineStr">
+        <is>
+          <t>已取消配方：待机</t>
+        </is>
+      </c>
+      <c r="D3136" t="inlineStr">
+        <is>
+          <t>Recipe cleared: standing by</t>
+        </is>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="inlineStr"/>
+      <c r="B3137" t="inlineStr">
+        <is>
+          <t>prod.panel.recipe_returned</t>
+        </is>
+      </c>
+      <c r="C3137" t="inlineStr">
+        <is>
+          <t>输入缓存里不再需要的 {0} 件物品已退回仓库</t>
+        </is>
+      </c>
+      <c r="D3137" t="inlineStr">
+        <is>
+          <t>{0} item(s) no longer needed in the input buffer were returned to storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="inlineStr"/>
+      <c r="B3138" t="inlineStr">
+        <is>
+          <t>prod.panel.progress</t>
+        </is>
+      </c>
+      <c r="C3138" t="inlineStr">
+        <is>
+          <t>进度 {0}%（{1} / {2} 秒）</t>
+        </is>
+      </c>
+      <c r="D3138" t="inlineStr">
+        <is>
+          <t>Progress {0}% ({1} / {2} s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" t="inlineStr"/>
+      <c r="B3139" t="inlineStr">
+        <is>
+          <t>prod.panel.progress_idle</t>
+        </is>
+      </c>
+      <c r="C3139" t="inlineStr">
+        <is>
+          <t>进度：没有在做</t>
+        </is>
+      </c>
+      <c r="D3139" t="inlineStr">
+        <is>
+          <t>Progress: nothing in production</t>
+        </is>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" t="inlineStr"/>
+      <c r="B3140" t="inlineStr">
+        <is>
+          <t>prod.panel.inputs</t>
+        </is>
+      </c>
+      <c r="C3140" t="inlineStr">
+        <is>
+          <t>输入缓存：{0}</t>
+        </is>
+      </c>
+      <c r="D3140" t="inlineStr">
+        <is>
+          <t>Input buffer: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" t="inlineStr"/>
+      <c r="B3141" t="inlineStr">
+        <is>
+          <t>prod.panel.outputs</t>
+        </is>
+      </c>
+      <c r="C3141" t="inlineStr">
+        <is>
+          <t>输出缓存：{0}</t>
+        </is>
+      </c>
+      <c r="D3141" t="inlineStr">
+        <is>
+          <t>Output buffer: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" t="inlineStr"/>
+      <c r="B3142" t="inlineStr">
+        <is>
+          <t>prod.panel.empty</t>
+        </is>
+      </c>
+      <c r="C3142" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="D3142" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" t="inlineStr"/>
+      <c r="B3143" t="inlineStr">
+        <is>
+          <t>prod.panel.stack</t>
+        </is>
+      </c>
+      <c r="C3143" t="inlineStr">
+        <is>
+          <t>{0} {1}/{2}</t>
+        </is>
+      </c>
+      <c r="D3143" t="inlineStr">
+        <is>
+          <t>{0} {1}/{2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" t="inlineStr"/>
+      <c r="B3144" t="inlineStr">
+        <is>
+          <t>prod.panel.stack_fluid</t>
+        </is>
+      </c>
+      <c r="C3144" t="inlineStr">
+        <is>
+          <t>{0} {1}/{2} 升</t>
+        </is>
+      </c>
+      <c r="D3144" t="inlineStr">
+        <is>
+          <t>{0} {1}/{2} L</t>
+        </is>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="inlineStr"/>
+      <c r="B3145" t="inlineStr">
+        <is>
+          <t>prod.panel.completed</t>
+        </is>
+      </c>
+      <c r="C3145" t="inlineStr">
+        <is>
+          <t>已完成 {0} 次</t>
+        </is>
+      </c>
+      <c r="D3145" t="inlineStr">
+        <is>
+          <t>Completed {0} time(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" t="inlineStr"/>
+      <c r="B3146" t="inlineStr">
+        <is>
+          <t>prod.panel.power</t>
+        </is>
+      </c>
+      <c r="C3146" t="inlineStr">
+        <is>
+          <t>电力：耗电 {0}，优先级 {1}（{2}）</t>
+        </is>
+      </c>
+      <c r="D3146" t="inlineStr">
+        <is>
+          <t>Power: uses {0}, priority {1} ({2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="inlineStr"/>
+      <c r="B3147" t="inlineStr">
+        <is>
+          <t>prod.panel.power_ok</t>
+        </is>
+      </c>
+      <c r="C3147" t="inlineStr">
+        <is>
+          <t>已供电</t>
+        </is>
+      </c>
+      <c r="D3147" t="inlineStr">
+        <is>
+          <t>powered</t>
+        </is>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="inlineStr"/>
+      <c r="B3148" t="inlineStr">
+        <is>
+          <t>prod.panel.power_off</t>
+        </is>
+      </c>
+      <c r="C3148" t="inlineStr">
+        <is>
+          <t>没电</t>
+        </is>
+      </c>
+      <c r="D3148" t="inlineStr">
+        <is>
+          <t>unpowered</t>
+        </is>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="inlineStr"/>
+      <c r="B3149" t="inlineStr">
+        <is>
+          <t>prod.panel.ruin</t>
+        </is>
+      </c>
+      <c r="C3149" t="inlineStr">
+        <is>
+          <t>脚下废墟：剩 {0} 格、{1} 废料（每格 {2}）</t>
+        </is>
+      </c>
+      <c r="D3149" t="inlineStr">
+        <is>
+          <t>Ruins underneath: {0} tile(s), {1} scrap left ({2} per tile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3150">
+      <c r="A3150" t="inlineStr"/>
+      <c r="B3150" t="inlineStr">
+        <is>
+          <t>prod.panel.ruin_done</t>
+        </is>
+      </c>
+      <c r="C3150" t="inlineStr">
+        <is>
+          <t>脚下废墟：已拆完（共拆出 {0} 废料），现在只分解传送带送来的固体</t>
+        </is>
+      </c>
+      <c r="D3150" t="inlineStr">
+        <is>
+          <t>Ruins underneath: stripped ({0} scrap recovered); it now only breaks down belted solids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" t="inlineStr"/>
+      <c r="B3151" t="inlineStr">
+        <is>
+          <t>prod.panel.recycle_note</t>
+        </is>
+      </c>
+      <c r="C3151" t="inlineStr">
+        <is>
+          <t>会分解送进来的任何固体（包括远征带回的物品）：别把要留的东西接到这里</t>
+        </is>
+      </c>
+      <c r="D3151" t="inlineStr">
+        <is>
+          <t>Breaks down any solid delivered to it (expedition finds included): do not route things you want to keep here</t>
+        </is>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" t="inlineStr"/>
+      <c r="B3152" t="inlineStr">
+        <is>
+          <t>prod.panel.vein</t>
+        </is>
+      </c>
+      <c r="C3152" t="inlineStr">
+        <is>
+          <t>脚下矿脉：{0} {1} 格，产出{2}</t>
+        </is>
+      </c>
+      <c r="D3152" t="inlineStr">
+        <is>
+          <t>Vein underneath: {1} tile(s) of {0}, produces {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" t="inlineStr"/>
+      <c r="B3153" t="inlineStr">
+        <is>
+          <t>prod.panel.vibration</t>
+        </is>
+      </c>
+      <c r="C3153" t="inlineStr">
+        <is>
+          <t>震动：工作时 +{0}/分钟 · 家园震动 {1}/{2}</t>
+        </is>
+      </c>
+      <c r="D3153" t="inlineStr">
+        <is>
+          <t>Vibration: +{0}/min while working · home vibration {1}/{2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" t="inlineStr"/>
+      <c r="B3154" t="inlineStr">
+        <is>
+          <t>prod.panel.vibration_sources</t>
+        </is>
+      </c>
+      <c r="C3154" t="inlineStr">
+        <is>
+          <t>主要震动来源：{0}</t>
+        </is>
+      </c>
+      <c r="D3154" t="inlineStr">
+        <is>
+          <t>Main vibration sources: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" t="inlineStr"/>
+      <c r="B3155" t="inlineStr">
+        <is>
+          <t>prod.panel.vibration_source</t>
+        </is>
+      </c>
+      <c r="C3155" t="inlineStr">
+        <is>
+          <t>{0}（{1}, {2}）+{3}/分钟</t>
+        </is>
+      </c>
+      <c r="D3155" t="inlineStr">
+        <is>
+          <t>{0} ({1}, {2}) +{3}/min</t>
+        </is>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" t="inlineStr"/>
+      <c r="B3156" t="inlineStr">
+        <is>
+          <t>prod.panel.waste</t>
+        </is>
+      </c>
+      <c r="C3156" t="inlineStr">
+        <is>
+          <t>销毁速率 {0} 升/分钟 · 累计销毁 {1} 升</t>
+        </is>
+      </c>
+      <c r="D3156" t="inlineStr">
+        <is>
+          <t>Destroys {0} L/min · destroyed so far {1} L</t>
+        </is>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" t="inlineStr"/>
+      <c r="B3157" t="inlineStr">
+        <is>
+          <t>prod.panel.pump</t>
+        </is>
+      </c>
+      <c r="C3157" t="inlineStr">
+        <is>
+          <t>脚下流体源：{0} {1} 格，抽{2} · 每分钟 {3} 升 · 累计抽出 {4} 升</t>
+        </is>
+      </c>
+      <c r="D3157" t="inlineStr">
+        <is>
+          <t>Source underneath: {1} tile(s) of {0}, pumps {2} · {3} L/min · pumped so far {4} L</t>
+        </is>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" t="inlineStr"/>
+      <c r="B3158" t="inlineStr">
+        <is>
+          <t>prod.panel.pump_none</t>
+        </is>
+      </c>
+      <c r="C3158" t="inlineStr">
+        <is>
+          <t>脚下没有流体源：流体泵要压在水源或油井上</t>
+        </is>
+      </c>
+      <c r="D3158" t="inlineStr">
+        <is>
+          <t>No fluid source underneath: a fluid pump must sit on water or an oil well</t>
+        </is>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" t="inlineStr"/>
+      <c r="B3159" t="inlineStr">
+        <is>
+          <t>prod.panel.fluid_port</t>
+        </is>
+      </c>
+      <c r="C3159" t="inlineStr">
+        <is>
+          <t>{0}（朝{1}，口外（{2}, {3}））：{4}</t>
+        </is>
+      </c>
+      <c r="D3159" t="inlineStr">
+        <is>
+          <t>{0} (facing {1}, outside at ({2}, {3})): {4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" t="inlineStr"/>
+      <c r="B3160" t="inlineStr">
+        <is>
+          <t>prod.panel.fluid_in</t>
+        </is>
+      </c>
+      <c r="C3160" t="inlineStr">
+        <is>
+          <t>{0}进口</t>
+        </is>
+      </c>
+      <c r="D3160" t="inlineStr">
+        <is>
+          <t>{0} inlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" t="inlineStr"/>
+      <c r="B3161" t="inlineStr">
+        <is>
+          <t>prod.panel.fluid_out</t>
+        </is>
+      </c>
+      <c r="C3161" t="inlineStr">
+        <is>
+          <t>{0}出口</t>
+        </is>
+      </c>
+      <c r="D3161" t="inlineStr">
+        <is>
+          <t>{0} outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" t="inlineStr"/>
+      <c r="B3162" t="inlineStr">
+        <is>
+          <t>prod.panel.fluid_any</t>
+        </is>
+      </c>
+      <c r="C3162" t="inlineStr">
+        <is>
+          <t>流体</t>
+        </is>
+      </c>
+      <c r="D3162" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" t="inlineStr"/>
+      <c r="B3163" t="inlineStr">
+        <is>
+          <t>prod.panel.any_solid</t>
+        </is>
+      </c>
+      <c r="C3163" t="inlineStr">
+        <is>
+          <t>要分解的固体</t>
+        </is>
+      </c>
+      <c r="D3163" t="inlineStr">
+        <is>
+          <t>solids to break down</t>
+        </is>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" t="inlineStr"/>
+      <c r="B3164" t="inlineStr">
+        <is>
+          <t>prod.panel.fluid_connected</t>
+        </is>
+      </c>
+      <c r="C3164" t="inlineStr">
+        <is>
+          <t>接上网络 {0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D3164" t="inlineStr">
+        <is>
+          <t>connected to network {0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" t="inlineStr"/>
+      <c r="B3165" t="inlineStr">
+        <is>
+          <t>prod.panel.fluid_disconnected</t>
+        </is>
+      </c>
+      <c r="C3165" t="inlineStr">
+        <is>
+          <t>没接管线</t>
+        </is>
+      </c>
+      <c r="D3165" t="inlineStr">
+        <is>
+          <t>no pipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" t="inlineStr"/>
+      <c r="B3166" t="inlineStr">
+        <is>
+          <t>prod.panel.ports</t>
+        </is>
+      </c>
+      <c r="C3166" t="inlineStr">
+        <is>
+          <t>端口…</t>
+        </is>
+      </c>
+      <c r="D3166" t="inlineStr">
+        <is>
+          <t>Ports…</t>
+        </is>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" t="inlineStr"/>
+      <c r="B3167" t="inlineStr">
+        <is>
+          <t>prod.panel.diagnose</t>
+        </is>
+      </c>
+      <c r="C3167" t="inlineStr">
+        <is>
+          <t>为什么不工作</t>
+        </is>
+      </c>
+      <c r="D3167" t="inlineStr">
+        <is>
+          <t>Why isn't it working</t>
+        </is>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" t="inlineStr"/>
+      <c r="B3168" t="inlineStr">
+        <is>
+          <t>prod.panel.help</t>
+        </is>
+      </c>
+      <c r="C3168" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D3168" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" t="inlineStr"/>
+      <c r="B3169" t="inlineStr">
+        <is>
+          <t>prod.panel.hint</t>
+        </is>
+      </c>
+      <c r="C3169" t="inlineStr">
+        <is>
+          <t>{act:Cancel} 关闭 · “?” 打开图鉴 · 改名、启用 / 禁用、升级、效率统计在后续版本加入</t>
+        </is>
+      </c>
+      <c r="D3169" t="inlineStr">
+        <is>
+          <t>{act:Cancel} to close · "?" opens the codex · rename, enable/disable, upgrade and efficiency stats arrive in a later version</t>
+        </is>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" t="inlineStr"/>
+      <c r="B3170" t="inlineStr">
+        <is>
+          <t>prod.panel.placeholder</t>
+        </is>
+      </c>
+      <c r="C3170" t="inlineStr">
+        <is>
+          <t>建筑外形是占位方块，美术阶段统一替换</t>
+        </is>
+      </c>
+      <c r="D3170" t="inlineStr">
+        <is>
+          <t>Building shapes are placeholder blocks and will be replaced in the art pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" t="inlineStr"/>
+      <c r="B3171" t="inlineStr">
+        <is>
+          <t>prod.reason.pump_working</t>
+        </is>
+      </c>
+      <c r="C3171" t="inlineStr">
+        <is>
+          <t>正在抽{0}（{1} 升/分钟）</t>
+        </is>
+      </c>
+      <c r="D3171" t="inlineStr">
+        <is>
+          <t>Pumping {0} ({1} L/min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" t="inlineStr"/>
+      <c r="B3172" t="inlineStr">
+        <is>
+          <t>prod.reason.pump_idle</t>
+        </is>
+      </c>
+      <c r="C3172" t="inlineStr">
+        <is>
+          <t>下游没有需要：泵待命、不抽取（接上用{0}的建筑或储罐）</t>
+        </is>
+      </c>
+      <c r="D3172" t="inlineStr">
+        <is>
+          <t>Nothing downstream needs it: the pump stands by and draws nothing (connect a building or tank that uses {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" t="inlineStr"/>
+      <c r="B3173" t="inlineStr">
+        <is>
+          <t>prod.reason.pump_no_source</t>
+        </is>
+      </c>
+      <c r="C3173" t="inlineStr">
+        <is>
+          <t>脚下不是流体源：泵要放在水源或油井上，抽不到东西</t>
+        </is>
+      </c>
+      <c r="D3173" t="inlineStr">
+        <is>
+          <t>Not on a fluid source: a pump must sit on water or an oil well; it draws nothing here</t>
+        </is>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" t="inlineStr"/>
+      <c r="B3174" t="inlineStr">
+        <is>
+          <t>prod.port.accept_any</t>
+        </is>
+      </c>
+      <c r="C3174" t="inlineStr">
+        <is>
+          <t>收：任何固体（分解成废料；缓存一次只放一种）</t>
+        </is>
+      </c>
+      <c r="D3174" t="inlineStr">
+        <is>
+          <t>Takes: any solid (broken down into scrap; one kind in the buffer at a time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" t="inlineStr"/>
+      <c r="B3175" t="inlineStr">
+        <is>
+          <t>prod.port.accept_item</t>
+        </is>
+      </c>
+      <c r="C3175" t="inlineStr">
+        <is>
+          <t>收：{0}（当前配方：{1}）</t>
+        </is>
+      </c>
+      <c r="D3175" t="inlineStr">
+        <is>
+          <t>Takes: {0} (current recipe: {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" t="inlineStr"/>
+      <c r="B3176" t="inlineStr">
+        <is>
+          <t>prod.port.accept_no_recipe</t>
+        </is>
+      </c>
+      <c r="C3176" t="inlineStr">
+        <is>
+          <t>不收：还没选配方（选了配方后只收那个配方要的固体）</t>
+        </is>
+      </c>
+      <c r="D3176" t="inlineStr">
+        <is>
+          <t>Takes nothing: no recipe chosen yet (once chosen it only takes that recipe's solid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" t="inlineStr"/>
+      <c r="B3177" t="inlineStr">
+        <is>
+          <t>prod.port.accept_no_solid</t>
+        </is>
+      </c>
+      <c r="C3177" t="inlineStr">
+        <is>
+          <t>不收：当前配方不用固体</t>
+        </is>
+      </c>
+      <c r="D3177" t="inlineStr">
+        <is>
+          <t>Takes nothing: the current recipe uses no solids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" t="inlineStr"/>
+      <c r="B3178" t="inlineStr">
+        <is>
+          <t>prod.port.push</t>
+        </is>
+      </c>
+      <c r="C3178" t="inlineStr">
+        <is>
+          <t>推：{0}</t>
+        </is>
+      </c>
+      <c r="D3178" t="inlineStr">
+        <is>
+          <t>Pushes: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3179">
+      <c r="A3179" t="inlineStr"/>
+      <c r="B3179" t="inlineStr">
+        <is>
+          <t>item.dist.production</t>
+        </is>
+      </c>
+      <c r="C3179" t="inlineStr">
+        <is>
+          <t>生产建筑缓存（在途，不算库存）</t>
+        </is>
+      </c>
+      <c r="D3179" t="inlineStr">
+        <is>
+          <t>Production building buffers (in transit, not stock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" t="inlineStr"/>
+      <c r="B3180" t="inlineStr">
+        <is>
+          <t>prod.hover.line</t>
+        </is>
+      </c>
+      <c r="C3180" t="inlineStr">
+        <is>
+          <t>{0}：{1}</t>
+        </is>
+      </c>
+      <c r="D3180" t="inlineStr">
+        <is>
+          <t>{0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" t="inlineStr"/>
+      <c r="B3181" t="inlineStr">
+        <is>
+          <t>diag.step.prod_state</t>
+        </is>
+      </c>
+      <c r="C3181" t="inlineStr">
+        <is>
+          <t>{0}：{1}——{2}</t>
+        </is>
+      </c>
+      <c r="D3181" t="inlineStr">
+        <is>
+          <t>{0}: {1}: {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" t="inlineStr"/>
+      <c r="B3182" t="inlineStr">
+        <is>
+          <t>diag.step.prod_upstream</t>
+        </is>
+      </c>
+      <c r="C3182" t="inlineStr">
+        <is>
+          <t>上游{0}（{1}, {2}）：{3}——{4}</t>
+        </is>
+      </c>
+      <c r="D3182" t="inlineStr">
+        <is>
+          <t>Upstream {0} ({1}, {2}): {3}: {4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" t="inlineStr"/>
+      <c r="B3183" t="inlineStr">
+        <is>
+          <t>diag.step.prod_upstream_working</t>
+        </is>
+      </c>
+      <c r="C3183" t="inlineStr">
+        <is>
+          <t>上游{0}（{1}, {2}）在供货：{3}还在传送带上，或者产量不够快</t>
+        </is>
+      </c>
+      <c r="D3183" t="inlineStr">
+        <is>
+          <t>Upstream {0} ({1}, {2}) is supplying: the {3} is still on the belt, or it is not produced fast enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" t="inlineStr"/>
+      <c r="B3184" t="inlineStr">
+        <is>
+          <t>diag.step.prod_store_empty</t>
+        </is>
+      </c>
+      <c r="C3184" t="inlineStr">
+        <is>
+          <t>上游{0}的输出口在供货，但仓库里没有{1}</t>
+        </is>
+      </c>
+      <c r="D3184" t="inlineStr">
+        <is>
+          <t>Upstream {0} is feeding the belt, but storage has no {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" t="inlineStr"/>
+      <c r="B3185" t="inlineStr">
+        <is>
+          <t>diag.step.prod_no_supplier</t>
+        </is>
+      </c>
+      <c r="C3185" t="inlineStr">
+        <is>
+          <t>输入传送带上没有能供应{0}的建筑：在上游接一座产出{0}的建筑，或接仓库的输出口</t>
+        </is>
+      </c>
+      <c r="D3185" t="inlineStr">
+        <is>
+          <t>Nothing on the input belt can supply {0}: connect a building that makes {0}, or a storage output, upstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" t="inlineStr"/>
+      <c r="B3186" t="inlineStr">
+        <is>
+          <t>prod.notify.ruin_depleted</t>
+        </is>
+      </c>
+      <c r="C3186" t="inlineStr">
+        <is>
+          <t>{0}脚下的废墟已拆完：{1} 格变成可以建造的空地（之后只分解传送带送来的固体）</t>
+        </is>
+      </c>
+      <c r="D3186" t="inlineStr">
+        <is>
+          <t>The ruins under the {0} are stripped: {1} tile(s) became buildable ground (it now only breaks down belted solids)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" t="inlineStr"/>
+      <c r="B3187" t="inlineStr">
+        <is>
+          <t>prod.notify.first_output</t>
+        </is>
+      </c>
+      <c r="C3187" t="inlineStr">
+        <is>
+          <t>{0}产出了第一份{1}</t>
+        </is>
+      </c>
+      <c r="D3187" t="inlineStr">
+        <is>
+          <t>The {0} produced its first {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" t="inlineStr"/>
+      <c r="B3188" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering.title</t>
+        </is>
+      </c>
+      <c r="C3188" t="inlineStr">
+        <is>
+          <t>采集建筑：回收站、提取钻、流体泵</t>
+        </is>
+      </c>
+      <c r="D3188" t="inlineStr">
+        <is>
+          <t>Gathering: recyclers, extraction drills and pumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" t="inlineStr"/>
+      <c r="B3189" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering.body</t>
+        </is>
+      </c>
+      <c r="C3189" t="inlineStr">
+        <is>
+          <t>采集建筑只能放在资源点上，放置时写明原因：回收站压在废墟上，逐格拆出废料，一格拆完就变成可建的空地；它也分解传送带送来的任何固体（得到的废料总是少于做它花掉的）。提取钻压在金属或稀土矿脉上，家园的矿脉不会采完；它工作时让家园的震动值上升（每分钟 +1，自然衰减每分钟 −2，满 100 会引来掘进蠕虫）。流体泵（2×2）压在水源或油井上，抽脚下的水或原油推进口外的管线，下游用不完时停抽。采集建筑都要电；产出从输出口推上传送带或管线，没接或下游堵住时会“输出堵塞”。</t>
+        </is>
+      </c>
+      <c r="D3189" t="inlineStr">
+        <is>
+          <t>Gathering buildings only go on resource tiles, and placement says why: recyclers sit on ruins and strip them tile by tile into scrap, each stripped tile becoming buildable ground; they also break down any solid sent by belt (always for less scrap than it took to make). Extraction drills sit on metal or rare earth veins, which never run out at home; while working they raise the home's vibration (+1 per minute, decaying 2 per minute; at 100 burrowing worms come). Fluid pumps (2×2) sit on water or oil wells and push water or crude into the pipe outside, stopping when nothing downstream takes more. Gathering buildings need power; output is pushed onto a belt or pipe, and with none connected or a jam downstream they show Output blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" t="inlineStr"/>
+      <c r="B3190" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering.hint</t>
+        </is>
+      </c>
+      <c r="C3190" t="inlineStr">
+        <is>
+          <t>放下第一座回收站、提取钻或流体泵</t>
+        </is>
+      </c>
+      <c r="D3190" t="inlineStr">
+        <is>
+          <t>Place your first recycler, extraction drill or fluid pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="inlineStr"/>
+      <c r="B3191" t="inlineStr">
+        <is>
+          <t>codex.economy.processing.title</t>
+        </is>
+      </c>
+      <c r="C3191" t="inlineStr">
+        <is>
+          <t>加工建筑：精炼炉、精炼塔、调配站、废液池</t>
+        </is>
+      </c>
+      <c r="D3191" t="inlineStr">
+        <is>
+          <t>Processing: furnace, refinery tower, blending station, waste pond</t>
+        </is>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" t="inlineStr"/>
+      <c r="B3192" t="inlineStr">
+        <is>
+          <t>codex.economy.processing.body</t>
+        </is>
+      </c>
+      <c r="C3192" t="inlineStr">
+        <is>
+          <t>加工建筑按配方生产：输入口只收当前配方要的物品，流体口外那一格接上管线。每座建筑的面板写明状态与原因——工作中、待机（没选配方）、缺料、缺流体、缺电、输出堵塞——以及配方、进度、输入 / 输出缓存。精炼炉有两个配方，要先选；精炼塔出燃油的同时出副产品酸液，酸液没有去处会堵住精炼塔：接一座废液池（缓慢销毁任何流体）或用酸液的建筑。缺料时“为什么不工作”会顺着输入传送带找到上游的供货建筑，再说明它为什么没在供货。</t>
+        </is>
+      </c>
+      <c r="D3192" t="inlineStr">
+        <is>
+          <t>Processing buildings work from recipes: an input only takes what the current recipe needs, and a fluid port connects through a pipe on the tile just outside it. Each building's panel states what it is doing and why (working, standing by with no recipe, missing input, missing fluid, no power, output blocked), with the recipe, progress and input / output buffers. The furnace has two recipes and needs one chosen; the refinery tower makes acid alongside fuel, and with nowhere for the acid to go it stalls: connect a waste pond (slowly destroys any fluid) or a building that uses acid. When input runs short, Why isn't it working follows the input belt upstream to the supplying building and says why it is not supplying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="inlineStr"/>
+      <c r="B3193" t="inlineStr">
+        <is>
+          <t>codex.economy.processing.hint</t>
+        </is>
+      </c>
+      <c r="C3193" t="inlineStr">
+        <is>
+          <t>放下第一座加工建筑</t>
+        </is>
+      </c>
+      <c r="D3193" t="inlineStr">
+        <is>
+          <t>Place your first processing building</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LocText-本地化文本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3193"/>
+  <dimension ref="A1:D3262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57902,6 +57902,1248 @@
         </is>
       </c>
     </row>
+    <row r="3194">
+      <c r="A3194" t="inlineStr"/>
+      <c r="B3194" t="inlineStr">
+        <is>
+          <t>building.parts_workshop.desc</t>
+        </is>
+      </c>
+      <c r="C3194" t="inlineStr">
+        <is>
+          <t>把合金加工成零件（1 合金 → 2 零件，3 秒）、结构材（2 合金 → 1 结构材，4 秒）或维修件（2 零件 → 1 维修件，5 秒），要先选配方。西侧输入、东侧输出。耗电 8。</t>
+        </is>
+      </c>
+      <c r="D3194" t="inlineStr">
+        <is>
+          <t>Machines alloy into parts (1 alloy → 2 parts, 3 s), structural material (2 alloy → 1, 4 s) or repair kits (2 parts → 1, 5 s); choose a recipe first. Input west, output east. Uses 8 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="inlineStr"/>
+      <c r="B3195" t="inlineStr">
+        <is>
+          <t>building.electronics_bench.desc</t>
+        </is>
+      </c>
+      <c r="C3195" t="inlineStr">
+        <is>
+          <t>组装电子件（合金 + 稀土矿）、精密零件（2 零件 + 电子件）或芯片基板（2 电子件 + 稀土矿），要先选配方。两种材料各走一个输入口：西口收配方里的第一种、南口收第二种；东侧输出。耗电 10。</t>
+        </is>
+      </c>
+      <c r="D3195" t="inlineStr">
+        <is>
+          <t>Assembles electronics (alloy + rare earth ore), precision parts (2 parts + electronics) or chip substrates (2 electronics + rare earth ore); choose a recipe first. Each ingredient has its own input: the west input takes the recipe's first ingredient, the south input the second; output east. Uses 10 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="inlineStr"/>
+      <c r="B3196" t="inlineStr">
+        <is>
+          <t>building.component_workshop.desc</t>
+        </is>
+      </c>
+      <c r="C3196" t="inlineStr">
+        <is>
+          <t>制造作战组件（2 零件 + 电子件）或结构模块（2 结构材 + 零件），要先选配方；装配站按蓝图把它们装到机器上。西口收第一种材料、南口收第二种，东侧输出。耗电 12。</t>
+        </is>
+      </c>
+      <c r="D3196" t="inlineStr">
+        <is>
+          <t>Makes combat components (2 parts + electronics) or structure modules (2 structural + parts); choose a recipe first. The assembly station fits them to machines per blueprint. West input takes the first ingredient, south input the second; output east. Uses 12 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="inlineStr"/>
+      <c r="B3197" t="inlineStr">
+        <is>
+          <t>building.firmware_burner.desc</t>
+        </is>
+      </c>
+      <c r="C3197" t="inlineStr">
+        <is>
+          <t>把已破解的固件刻进芯片基板（1 芯片基板 → 1 枚固件芯片，20 秒），要先选刻哪条固件。刻好的芯片直接进固件库，不上传送带。西侧输入芯片基板。耗电 10。</t>
+        </is>
+      </c>
+      <c r="D3197" t="inlineStr">
+        <is>
+          <t>Writes a cracked firmware onto a chip substrate (1 substrate → 1 firmware chip, 20 s); choose which firmware first. Finished chips go straight into the firmware library, not onto a belt. Chip substrates enter from the west. Uses 10 power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="inlineStr"/>
+      <c r="B3198" t="inlineStr">
+        <is>
+          <t>prod.panel.burn_target</t>
+        </is>
+      </c>
+      <c r="C3198" t="inlineStr">
+        <is>
+          <t>刻录</t>
+        </is>
+      </c>
+      <c r="D3198" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" t="inlineStr"/>
+      <c r="B3199" t="inlineStr">
+        <is>
+          <t>prod.panel.burn_none</t>
+        </is>
+      </c>
+      <c r="C3199" t="inlineStr">
+        <is>
+          <t>（不选：待机）</t>
+        </is>
+      </c>
+      <c r="D3199" t="inlineStr">
+        <is>
+          <t>(none: stand by)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" t="inlineStr"/>
+      <c r="B3200" t="inlineStr">
+        <is>
+          <t>prod.panel.burn_line</t>
+        </is>
+      </c>
+      <c r="C3200" t="inlineStr">
+        <is>
+          <t>刻录：芯片基板 ×1 → {0} 芯片 ×1（{1} 秒），刻好的芯片进固件库</t>
+        </is>
+      </c>
+      <c r="D3200" t="inlineStr">
+        <is>
+          <t>Burning: chip substrate ×1 → {0} chip ×1 ({1} s); finished chips go to the firmware library</t>
+        </is>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="inlineStr"/>
+      <c r="B3201" t="inlineStr">
+        <is>
+          <t>prod.panel.burn_changed</t>
+        </is>
+      </c>
+      <c r="C3201" t="inlineStr">
+        <is>
+          <t>刻录目标改为：{0}</t>
+        </is>
+      </c>
+      <c r="D3201" t="inlineStr">
+        <is>
+          <t>Burn target set to: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="inlineStr"/>
+      <c r="B3202" t="inlineStr">
+        <is>
+          <t>prod.panel.burn_cleared</t>
+        </is>
+      </c>
+      <c r="C3202" t="inlineStr">
+        <is>
+          <t>已取消刻录目标：待机</t>
+        </is>
+      </c>
+      <c r="D3202" t="inlineStr">
+        <is>
+          <t>Burn target cleared: standing by</t>
+        </is>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="inlineStr"/>
+      <c r="B3203" t="inlineStr">
+        <is>
+          <t>prod.panel.burn_storage</t>
+        </is>
+      </c>
+      <c r="C3203" t="inlineStr">
+        <is>
+          <t>固件芯片存放：{0} / {1}</t>
+        </is>
+      </c>
+      <c r="D3203" t="inlineStr">
+        <is>
+          <t>Firmware chip storage: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="inlineStr"/>
+      <c r="B3204" t="inlineStr">
+        <is>
+          <t>prod.panel.burned</t>
+        </is>
+      </c>
+      <c r="C3204" t="inlineStr">
+        <is>
+          <t>已刻录 {0} 枚芯片</t>
+        </is>
+      </c>
+      <c r="D3204" t="inlineStr">
+        <is>
+          <t>{0} chip(s) burned</t>
+        </is>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" t="inlineStr"/>
+      <c r="B3205" t="inlineStr">
+        <is>
+          <t>prod.reason.no_burn_target</t>
+        </is>
+      </c>
+      <c r="C3205" t="inlineStr">
+        <is>
+          <t>没选要刻录的固件：在面板里选一条已破解的固件后开工</t>
+        </is>
+      </c>
+      <c r="D3205" t="inlineStr">
+        <is>
+          <t>No firmware chosen: pick a cracked firmware in the panel to start</t>
+        </is>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="inlineStr"/>
+      <c r="B3206" t="inlineStr">
+        <is>
+          <t>prod.reason.burn_target_locked</t>
+        </is>
+      </c>
+      <c r="C3206" t="inlineStr">
+        <is>
+          <t>要刻录的{0}还没有破解：换一条已破解的固件</t>
+        </is>
+      </c>
+      <c r="D3206" t="inlineStr">
+        <is>
+          <t>{0} is not cracked yet: choose a cracked firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="inlineStr"/>
+      <c r="B3207" t="inlineStr">
+        <is>
+          <t>prod.reason.firmware_storage_full</t>
+        </is>
+      </c>
+      <c r="C3207" t="inlineStr">
+        <is>
+          <t>固件芯片存放已满（{0} / {1}）：在固件库里分解不要的芯片，或建好 / 修好仓库扩容</t>
+        </is>
+      </c>
+      <c r="D3207" t="inlineStr">
+        <is>
+          <t>Firmware chip storage is full ({0} / {1}): break down unwanted chips in the firmware library, or build / repair a warehouse for more room</t>
+        </is>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="inlineStr"/>
+      <c r="B3208" t="inlineStr">
+        <is>
+          <t>prod.reason.working_burn</t>
+        </is>
+      </c>
+      <c r="C3208" t="inlineStr">
+        <is>
+          <t>正在刻录：{0}</t>
+        </is>
+      </c>
+      <c r="D3208" t="inlineStr">
+        <is>
+          <t>Burning: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="inlineStr"/>
+      <c r="B3209" t="inlineStr">
+        <is>
+          <t>prod.reason.burn_unknown</t>
+        </is>
+      </c>
+      <c r="C3209" t="inlineStr">
+        <is>
+          <t>“{0}”不是可以刻录的固件</t>
+        </is>
+      </c>
+      <c r="D3209" t="inlineStr">
+        <is>
+          <t>"{0}" is not a firmware that can be burned</t>
+        </is>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="inlineStr"/>
+      <c r="B3210" t="inlineStr">
+        <is>
+          <t>fwlib.origin.burn</t>
+        </is>
+      </c>
+      <c r="C3210" t="inlineStr">
+        <is>
+          <t>固件刻录台</t>
+        </is>
+      </c>
+      <c r="D3210" t="inlineStr">
+        <is>
+          <t>Firmware burner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="inlineStr"/>
+      <c r="B3211" t="inlineStr">
+        <is>
+          <t>prod.notify.first_chip</t>
+        </is>
+      </c>
+      <c r="C3211" t="inlineStr">
+        <is>
+          <t>{0}刻好了第一枚“{1}”芯片（已进固件库）</t>
+        </is>
+      </c>
+      <c r="D3211" t="inlineStr">
+        <is>
+          <t>The {0} burned its first "{1}" chip (now in the firmware library)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" t="inlineStr"/>
+      <c r="B3212" t="inlineStr">
+        <is>
+          <t>prod.reason.in_port_unconnected_at</t>
+        </is>
+      </c>
+      <c r="C3212" t="inlineStr">
+        <is>
+          <t>{3}输入口没接传送带：在（{0}, {1}）铺一格朝向建筑的传送带，把{2}送进来</t>
+        </is>
+      </c>
+      <c r="D3212" t="inlineStr">
+        <is>
+          <t>The {3} input has no belt: lay a belt at ({0}, {1}) pointing at the building to bring in {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3213">
+      <c r="A3213" t="inlineStr"/>
+      <c r="B3213" t="inlineStr">
+        <is>
+          <t>prod.reason.in_port_empty_at</t>
+        </is>
+      </c>
+      <c r="C3213" t="inlineStr">
+        <is>
+          <t>{1}输入口的传送带上没有{0}送来</t>
+        </is>
+      </c>
+      <c r="D3213" t="inlineStr">
+        <is>
+          <t>No {0} is arriving on the belt at the {1} input</t>
+        </is>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="inlineStr"/>
+      <c r="B3214" t="inlineStr">
+        <is>
+          <t>prod.port.accept_unused</t>
+        </is>
+      </c>
+      <c r="C3214" t="inlineStr">
+        <is>
+          <t>不收：当前配方用不到这个口（只有一种固体材料）</t>
+        </is>
+      </c>
+      <c r="D3214" t="inlineStr">
+        <is>
+          <t>Takes nothing: the current recipe does not use this input (it has only one solid ingredient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="inlineStr"/>
+      <c r="B3215" t="inlineStr">
+        <is>
+          <t>prod.port.accept_burner</t>
+        </is>
+      </c>
+      <c r="C3215" t="inlineStr">
+        <is>
+          <t>收：芯片基板（刻录目标：{0}）</t>
+        </is>
+      </c>
+      <c r="D3215" t="inlineStr">
+        <is>
+          <t>Takes: chip substrates (burn target: {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3216">
+      <c r="A3216" t="inlineStr"/>
+      <c r="B3216" t="inlineStr">
+        <is>
+          <t>prod.port.push_none</t>
+        </is>
+      </c>
+      <c r="C3216" t="inlineStr">
+        <is>
+          <t>推：不上传送带（刻好的芯片进固件库）</t>
+        </is>
+      </c>
+      <c r="D3216" t="inlineStr">
+        <is>
+          <t>Pushes: nothing (finished chips go to the firmware library)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" t="inlineStr"/>
+      <c r="B3217" t="inlineStr">
+        <is>
+          <t>prod.panel.remembered</t>
+        </is>
+      </c>
+      <c r="C3217" t="inlineStr">
+        <is>
+          <t>新建的{0}会沿用你上一次的选择：{1}</t>
+        </is>
+      </c>
+      <c r="D3217" t="inlineStr">
+        <is>
+          <t>New {0} buildings start with your last choice: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3218">
+      <c r="A3218" t="inlineStr"/>
+      <c r="B3218" t="inlineStr">
+        <is>
+          <t>prod.panel.inherited</t>
+        </is>
+      </c>
+      <c r="C3218" t="inlineStr">
+        <is>
+          <t>沿用了你上一次给{0}选的：{1}</t>
+        </is>
+      </c>
+      <c r="D3218" t="inlineStr">
+        <is>
+          <t>Carried over your last choice for {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3219">
+      <c r="A3219" t="inlineStr"/>
+      <c r="B3219" t="inlineStr">
+        <is>
+          <t>prod.panel.copy</t>
+        </is>
+      </c>
+      <c r="C3219" t="inlineStr">
+        <is>
+          <t>复制设置到同类建筑</t>
+        </is>
+      </c>
+      <c r="D3219" t="inlineStr">
+        <is>
+          <t>Copy settings to same type</t>
+        </is>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" t="inlineStr"/>
+      <c r="B3220" t="inlineStr">
+        <is>
+          <t>prod.panel.copy_confirm_title</t>
+        </is>
+      </c>
+      <c r="C3220" t="inlineStr">
+        <is>
+          <t>复制设置到同类建筑</t>
+        </is>
+      </c>
+      <c r="D3220" t="inlineStr">
+        <is>
+          <t>Copy settings to the same type</t>
+        </is>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" t="inlineStr"/>
+      <c r="B3221" t="inlineStr">
+        <is>
+          <t>prod.panel.copy_confirm_body</t>
+        </is>
+      </c>
+      <c r="C3221" t="inlineStr">
+        <is>
+          <t>把这座{0}的设置（{1}）应用到其余 {2} 座{0}？换了配方的建筑正在做的那份会作废，料退回输入缓存或仓库。</t>
+        </is>
+      </c>
+      <c r="D3221" t="inlineStr">
+        <is>
+          <t>Apply this {0}'s settings ({1}) to the other {2} {0} building(s)? Buildings that change recipe drop the batch in progress; its materials go back to the input buffer or storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" t="inlineStr"/>
+      <c r="B3222" t="inlineStr">
+        <is>
+          <t>prod.panel.copy_confirm_ok</t>
+        </is>
+      </c>
+      <c r="C3222" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="D3222" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" t="inlineStr"/>
+      <c r="B3223" t="inlineStr">
+        <is>
+          <t>prod.panel.copy_done</t>
+        </is>
+      </c>
+      <c r="C3223" t="inlineStr">
+        <is>
+          <t>已把“{0}”应用到 {1} 座{2}（另有 {3} 座本来就是）</t>
+        </is>
+      </c>
+      <c r="D3223" t="inlineStr">
+        <is>
+          <t>Applied "{0}" to {1} {2} building(s) ({3} already had it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" t="inlineStr"/>
+      <c r="B3224" t="inlineStr">
+        <is>
+          <t>prod.panel.copy_none</t>
+        </is>
+      </c>
+      <c r="C3224" t="inlineStr">
+        <is>
+          <t>家园里没有别的{0}</t>
+        </is>
+      </c>
+      <c r="D3224" t="inlineStr">
+        <is>
+          <t>There is no other {0} at home</t>
+        </is>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="inlineStr"/>
+      <c r="B3225" t="inlineStr">
+        <is>
+          <t>prod.panel.copy_fixed</t>
+        </is>
+      </c>
+      <c r="C3225" t="inlineStr">
+        <is>
+          <t>{0}只有一种固定功能，没有设置可复制</t>
+        </is>
+      </c>
+      <c r="D3225" t="inlineStr">
+        <is>
+          <t>The {0} has a single fixed function; there is nothing to copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="inlineStr"/>
+      <c r="B3226" t="inlineStr">
+        <is>
+          <t>prod.panel.setting_recipe</t>
+        </is>
+      </c>
+      <c r="C3226" t="inlineStr">
+        <is>
+          <t>配方：{0}</t>
+        </is>
+      </c>
+      <c r="D3226" t="inlineStr">
+        <is>
+          <t>Recipe: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="inlineStr"/>
+      <c r="B3227" t="inlineStr">
+        <is>
+          <t>prod.panel.setting_target</t>
+        </is>
+      </c>
+      <c r="C3227" t="inlineStr">
+        <is>
+          <t>刻录：{0}</t>
+        </is>
+      </c>
+      <c r="D3227" t="inlineStr">
+        <is>
+          <t>Burn: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="inlineStr"/>
+      <c r="B3228" t="inlineStr">
+        <is>
+          <t>prod.panel.setting_none</t>
+        </is>
+      </c>
+      <c r="C3228" t="inlineStr">
+        <is>
+          <t>不选（待机）</t>
+        </is>
+      </c>
+      <c r="D3228" t="inlineStr">
+        <is>
+          <t>none (stand by)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="inlineStr"/>
+      <c r="B3229" t="inlineStr">
+        <is>
+          <t>asm.panel.title</t>
+        </is>
+      </c>
+      <c r="C3229" t="inlineStr">
+        <is>
+          <t>装配站</t>
+        </is>
+      </c>
+      <c r="D3229" t="inlineStr">
+        <is>
+          <t>Assembly Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="inlineStr"/>
+      <c r="B3230" t="inlineStr">
+        <is>
+          <t>asm.panel.tab_produce</t>
+        </is>
+      </c>
+      <c r="C3230" t="inlineStr">
+        <is>
+          <t>生产</t>
+        </is>
+      </c>
+      <c r="D3230" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+    </row>
+    <row r="3231">
+      <c r="A3231" t="inlineStr"/>
+      <c r="B3231" t="inlineStr">
+        <is>
+          <t>asm.panel.tab_retrofit</t>
+        </is>
+      </c>
+      <c r="C3231" t="inlineStr">
+        <is>
+          <t>改造</t>
+        </is>
+      </c>
+      <c r="D3231" t="inlineStr">
+        <is>
+          <t>Retrofit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3232">
+      <c r="A3232" t="inlineStr"/>
+      <c r="B3232" t="inlineStr">
+        <is>
+          <t>asm.panel.produce_btn</t>
+        </is>
+      </c>
+      <c r="C3232" t="inlineStr">
+        <is>
+          <t>{0}｜{1} 秒</t>
+        </is>
+      </c>
+      <c r="D3232" t="inlineStr">
+        <is>
+          <t>{0} | {1} s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" t="inlineStr"/>
+      <c r="B3233" t="inlineStr">
+        <is>
+          <t>asm.panel.materials_of</t>
+        </is>
+      </c>
+      <c r="C3233" t="inlineStr">
+        <is>
+          <t>{0}的材料：{1}</t>
+        </is>
+      </c>
+      <c r="D3233" t="inlineStr">
+        <is>
+          <t>{0} needs: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3234">
+      <c r="A3234" t="inlineStr"/>
+      <c r="B3234" t="inlineStr">
+        <is>
+          <t>asm.panel.material</t>
+        </is>
+      </c>
+      <c r="C3234" t="inlineStr">
+        <is>
+          <t>{0} ×{1}（装配站 {2}、仓库 {3}）</t>
+        </is>
+      </c>
+      <c r="D3234" t="inlineStr">
+        <is>
+          <t>{0} ×{1} (station {2}, storage {3})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3235">
+      <c r="A3235" t="inlineStr"/>
+      <c r="B3235" t="inlineStr">
+        <is>
+          <t>asm.panel.all_scrap</t>
+        </is>
+      </c>
+      <c r="C3235" t="inlineStr">
+        <is>
+          <t>材料一件都没有时，全部用废料代付要 {0} 废料</t>
+        </is>
+      </c>
+      <c r="D3235" t="inlineStr">
+        <is>
+          <t>With none of the materials on hand, paying entirely in scrap costs {0} scrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" t="inlineStr"/>
+      <c r="B3236" t="inlineStr">
+        <is>
+          <t>asm.panel.sub_toggle</t>
+        </is>
+      </c>
+      <c r="C3236" t="inlineStr">
+        <is>
+          <t>缺材料时用废料代付</t>
+        </is>
+      </c>
+      <c r="D3236" t="inlineStr">
+        <is>
+          <t>Pay for missing materials with scrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" t="inlineStr"/>
+      <c r="B3237" t="inlineStr">
+        <is>
+          <t>asm.panel.sub_on</t>
+        </is>
+      </c>
+      <c r="C3237" t="inlineStr">
+        <is>
+          <t>已开：材料先从装配站缓存、再从仓库取；还缺的按废料当量折算用废料代付</t>
+        </is>
+      </c>
+      <c r="D3237" t="inlineStr">
+        <is>
+          <t>On: materials come from the station buffer, then storage; anything still missing is paid in scrap at its scrap value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" t="inlineStr"/>
+      <c r="B3238" t="inlineStr">
+        <is>
+          <t>asm.panel.sub_off</t>
+        </is>
+      </c>
+      <c r="C3238" t="inlineStr">
+        <is>
+          <t>已关：材料不齐就等，不动用废料</t>
+        </is>
+      </c>
+      <c r="D3238" t="inlineStr">
+        <is>
+          <t>Off: waits until every material is on hand and never spends scrap instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" t="inlineStr"/>
+      <c r="B3239" t="inlineStr">
+        <is>
+          <t>asm.panel.buffer</t>
+        </is>
+      </c>
+      <c r="C3239" t="inlineStr">
+        <is>
+          <t>装配站材料缓存（西侧输入口送来）：{0}</t>
+        </is>
+      </c>
+      <c r="D3239" t="inlineStr">
+        <is>
+          <t>Station material buffer (from the west input): {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" t="inlineStr"/>
+      <c r="B3240" t="inlineStr">
+        <is>
+          <t>asm.panel.taken</t>
+        </is>
+      </c>
+      <c r="C3240" t="inlineStr">
+        <is>
+          <t>已取料：{0}；废料代付 {1}</t>
+        </is>
+      </c>
+      <c r="D3240" t="inlineStr">
+        <is>
+          <t>Materials taken: {0}; scrap paid instead {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" t="inlineStr"/>
+      <c r="B3241" t="inlineStr">
+        <is>
+          <t>asm.panel.retrofit_materials</t>
+        </is>
+      </c>
+      <c r="C3241" t="inlineStr">
+        <is>
+          <t>改造要补的材料：{0}；工时费 {1} 废料</t>
+        </is>
+      </c>
+      <c r="D3241" t="inlineStr">
+        <is>
+          <t>Materials to add for the retrofit: {0}; labour fee {1} scrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3242">
+      <c r="A3242" t="inlineStr"/>
+      <c r="B3242" t="inlineStr">
+        <is>
+          <t>asm.panel.retrofit_versions</t>
+        </is>
+      </c>
+      <c r="C3242" t="inlineStr">
+        <is>
+          <t>旧装配 v{0}（{1} 废料｜热量 {2}）→ 新装配 v{3}（{4} 废料｜热量 {5}）</t>
+        </is>
+      </c>
+      <c r="D3242" t="inlineStr">
+        <is>
+          <t>Old loadout v{0} ({1} scrap | heat {2}) → new loadout v{3} ({4} scrap | heat {5})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" t="inlineStr"/>
+      <c r="B3243" t="inlineStr">
+        <is>
+          <t>asm.panel.retrofit_total</t>
+        </is>
+      </c>
+      <c r="C3243" t="inlineStr">
+        <is>
+          <t>全部用废料：{0} 废料｜{1} 秒</t>
+        </is>
+      </c>
+      <c r="D3243" t="inlineStr">
+        <is>
+          <t>All in scrap: {0} scrap | {1} s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" t="inlineStr"/>
+      <c r="B3244" t="inlineStr">
+        <is>
+          <t>asm.panel.none</t>
+        </is>
+      </c>
+      <c r="C3244" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D3244" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" t="inlineStr"/>
+      <c r="B3245" t="inlineStr">
+        <is>
+          <t>asm.panel.stack</t>
+        </is>
+      </c>
+      <c r="C3245" t="inlineStr">
+        <is>
+          <t>{0} ×{1}</t>
+        </is>
+      </c>
+      <c r="D3245" t="inlineStr">
+        <is>
+          <t>{0} ×{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" t="inlineStr"/>
+      <c r="B3246" t="inlineStr">
+        <is>
+          <t>asm.panel.locked_hover</t>
+        </is>
+      </c>
+      <c r="C3246" t="inlineStr">
+        <is>
+          <t>维修机：先让解析台通电运转后解锁</t>
+        </is>
+      </c>
+      <c r="D3246" t="inlineStr">
+        <is>
+          <t>Repair hover: unlocks once the analysis bench is powered and running</t>
+        </is>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" t="inlineStr"/>
+      <c r="B3247" t="inlineStr">
+        <is>
+          <t>asm.reason.materials</t>
+        </is>
+      </c>
+      <c r="C3247" t="inlineStr">
+        <is>
+          <t>缺材料：{0}——用传送带送到装配站西侧输入口，或放进仓库；也可以在面板里打开“缺材料时用废料代付”</t>
+        </is>
+      </c>
+      <c r="D3247" t="inlineStr">
+        <is>
+          <t>Missing materials: {0}. Belt them to the station's west input or put them in storage, or turn on "Pay for missing materials with scrap" in the panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" t="inlineStr"/>
+      <c r="B3248" t="inlineStr">
+        <is>
+          <t>asm.reason.materials_scrap</t>
+        </is>
+      </c>
+      <c r="C3248" t="inlineStr">
+        <is>
+          <t>缺材料：{0}；用废料代付要 {1} 废料，现有 {2}</t>
+        </is>
+      </c>
+      <c r="D3248" t="inlineStr">
+        <is>
+          <t>Missing materials: {0}; paying in scrap needs {1} scrap, you have {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" t="inlineStr"/>
+      <c r="B3249" t="inlineStr">
+        <is>
+          <t>asm.reason.route</t>
+        </is>
+      </c>
+      <c r="C3249" t="inlineStr">
+        <is>
+          <t>材料在仓库里，但送不到装配站：{0}</t>
+        </is>
+      </c>
+      <c r="D3249" t="inlineStr">
+        <is>
+          <t>The materials are in storage but cannot reach the station: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" t="inlineStr"/>
+      <c r="B3250" t="inlineStr">
+        <is>
+          <t>asm.reason.short</t>
+        </is>
+      </c>
+      <c r="C3250" t="inlineStr">
+        <is>
+          <t>{0} 还差 {1}</t>
+        </is>
+      </c>
+      <c r="D3250" t="inlineStr">
+        <is>
+          <t>{0} short by {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" t="inlineStr"/>
+      <c r="B3251" t="inlineStr">
+        <is>
+          <t>asm.reason.port_jam</t>
+        </is>
+      </c>
+      <c r="C3251" t="inlineStr">
+        <is>
+          <t>。注意：装配站输入口被{0}占着（材料缓存里它已放满 {1}），同一条带后面的材料进不来——把缺的材料放进仓库，或打开“缺材料时用废料代付”，等{0}用掉后带会继续走</t>
+        </is>
+      </c>
+      <c r="D3251" t="inlineStr">
+        <is>
+          <t>. Note: the station input is held by {0} (its buffer is full at {1}), so the materials behind it on the same belt cannot get in. Put the missing materials in storage or turn on "Pay for missing materials with scrap"; the belt moves again once {0} is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" t="inlineStr"/>
+      <c r="B3252" t="inlineStr">
+        <is>
+          <t>asm.port.accept</t>
+        </is>
+      </c>
+      <c r="C3252" t="inlineStr">
+        <is>
+          <t>收：机器材料（{0}），进装配站材料缓存（每种最多 {1}）；别的物品不收，停在带末端并写明原因</t>
+        </is>
+      </c>
+      <c r="D3252" t="inlineStr">
+        <is>
+          <t>Takes: machine materials ({0}) into the station buffer (up to {1} of each); anything else is refused and waits at the belt end with the reason shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" t="inlineStr"/>
+      <c r="B3253" t="inlineStr">
+        <is>
+          <t>logistics.block.sink_rejects_set</t>
+        </is>
+      </c>
+      <c r="C3253" t="inlineStr">
+        <is>
+          <t>{0}不收{1}：它只收机器材料（{2}）</t>
+        </is>
+      </c>
+      <c r="D3253" t="inlineStr">
+        <is>
+          <t>{0} does not take {1}: it only takes machine materials ({2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" t="inlineStr"/>
+      <c r="B3254" t="inlineStr">
+        <is>
+          <t>asm.port.out</t>
+        </is>
+      </c>
+      <c r="C3254" t="inlineStr">
+        <is>
+          <t>不推：机器从装配站出口驶出，不上传送带</t>
+        </is>
+      </c>
+      <c r="D3254" t="inlineStr">
+        <is>
+          <t>Pushes nothing: machines drive out of the station exit, not onto a belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" t="inlineStr"/>
+      <c r="B3255" t="inlineStr">
+        <is>
+          <t>asm.state.waiting_materials</t>
+        </is>
+      </c>
+      <c r="C3255" t="inlineStr">
+        <is>
+          <t>缺材料</t>
+        </is>
+      </c>
+      <c r="D3255" t="inlineStr">
+        <is>
+          <t>Missing materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" t="inlineStr"/>
+      <c r="B3256" t="inlineStr">
+        <is>
+          <t>asm.notify.first_line_machine</t>
+        </is>
+      </c>
+      <c r="C3256" t="inlineStr">
+        <is>
+          <t>装配站用产线材料造出了第一台机器：{0}</t>
+        </is>
+      </c>
+      <c r="D3256" t="inlineStr">
+        <is>
+          <t>The assembly station built its first machine from production-line materials: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" t="inlineStr"/>
+      <c r="B3257" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing.title</t>
+        </is>
+      </c>
+      <c r="C3257" t="inlineStr">
+        <is>
+          <t>制造建筑：零件工坊、电子组装台、组件工坊、固件刻录台</t>
+        </is>
+      </c>
+      <c r="D3257" t="inlineStr">
+        <is>
+          <t>Manufacturing: parts workshop, electronics bench, component workshop, firmware burner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" t="inlineStr"/>
+      <c r="B3258" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing.body</t>
+        </is>
+      </c>
+      <c r="C3258" t="inlineStr">
+        <is>
+          <t>制造建筑把合金和稀土矿一层层做成零件、结构材、维修件、电子件、精密零件、芯片基板、作战组件和结构模块。多配方建筑要先选配方，没选时待机；新建的同类建筑沿用你上一次的选择，面板里的“复制设置到同类建筑”一次改好所有同类建筑。两种材料的配方各走一个输入口（西口收第一种、南口收第二种）。固件刻录台把已破解的固件刻进芯片基板，刻好的芯片直接进固件库；固件库满了它会停下并说明原因。</t>
+        </is>
+      </c>
+      <c r="D3258" t="inlineStr">
+        <is>
+          <t>Manufacturing buildings turn alloy and rare earth ore, layer by layer, into parts, structural material, repair kits, electronics, precision parts, chip substrates, combat components and structure modules. Multi-recipe buildings need a recipe and stand by without one; new buildings of the same type start with your last choice, and Copy settings to same type in the panel updates them all at once. Recipes with two ingredients use two inputs (west takes the first, south the second). The firmware burner writes cracked firmware onto chip substrates and sends finished chips straight to the firmware library; when the library is full it stops and says why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" t="inlineStr"/>
+      <c r="B3259" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing.hint</t>
+        </is>
+      </c>
+      <c r="C3259" t="inlineStr">
+        <is>
+          <t>放下第一座制造建筑</t>
+        </is>
+      </c>
+      <c r="D3259" t="inlineStr">
+        <is>
+          <t>Place your first manufacturing building</t>
+        </is>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" t="inlineStr"/>
+      <c r="B3260" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly.title</t>
+        </is>
+      </c>
+      <c r="C3260" t="inlineStr">
+        <is>
+          <t>装配站：用产线材料造机器</t>
+        </is>
+      </c>
+      <c r="D3260" t="inlineStr">
+        <is>
+          <t>Assembly station: machines from line materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="inlineStr"/>
+      <c r="B3261" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly.body</t>
+        </is>
+      </c>
+      <c r="C3261" t="inlineStr">
+        <is>
+          <t>装配站按蓝图把材料装成机器：底盘要结构材和零件，每台机器要电子件做控制电路，装了主组件 / 功能组件各要一个作战组件，装了结构模块要一个结构模块。排队的那一项轮到时，先从装配站的材料缓存（西侧输入口用传送带送来）取，再从仓库取，全有才开工；取消或装配站被毁时取走的材料退回仓库。缺材料时可以打开“用废料代付”：还缺的部分按废料当量折算用废料补上（全部代付等于旧的废料价）；关掉则一直等材料。仓库到装配站的路被建筑或地形围死时，材料送不过去，队列写明被什么堵住。改造只补新旧蓝图之间多出来的材料。</t>
+        </is>
+      </c>
+      <c r="D3261" t="inlineStr">
+        <is>
+          <t>The assembly station builds machines from materials per blueprint: the chassis takes structural material and parts, every machine needs electronics for its control circuit, each mounted primary or utility component needs a combat component, and a mounted structure module needs a structure module. When a queued item comes up it draws first from the station's material buffer (belted into the west input), then from storage, and starts only when everything is there; cancelling, or the station being destroyed, returns the taken materials to storage. With Pay for missing materials with scrap on, whatever is still missing is covered in scrap at its scrap value (paying entirely in scrap equals the old scrap price); with it off the order waits for materials. If buildings or terrain wall off the path from storage to the station, materials cannot get there and the queue says what blocks it. A retrofit only adds the materials the new blueprint needs beyond the old one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="inlineStr"/>
+      <c r="B3262" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly.hint</t>
+        </is>
+      </c>
+      <c r="C3262" t="inlineStr">
+        <is>
+          <t>用产线送来的材料在装配站造出一台机器</t>
+        </is>
+      </c>
+      <c r="D3262" t="inlineStr">
+        <is>
+          <t>Build a machine at the assembly station from production-line materials</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
